--- a/projects/splashstore/docs/splashstore-scan-curation-260816.xlsx
+++ b/projects/splashstore/docs/splashstore-scan-curation-260816.xlsx
@@ -93,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,19 +150,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -172,14 +159,9 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1404,15 +1386,15 @@
     <col width="56" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
-    <col width="34" customWidth="1" min="18" max="18"/>
-    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="56" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1468,47 +1450,47 @@
       </c>
       <c r="K1" s="16" t="inlineStr">
         <is>
+          <t>Depth (cm)</t>
+        </is>
+      </c>
+      <c r="L1" s="16" t="inlineStr">
+        <is>
+          <t>Width (cm)</t>
+        </is>
+      </c>
+      <c r="M1" s="16" t="inlineStr">
+        <is>
           <t>Height (cm)</t>
         </is>
       </c>
-      <c r="L1" s="16" t="inlineStr">
+      <c r="N1" s="16" t="inlineStr">
         <is>
           <t>Weight (kg)</t>
         </is>
       </c>
-      <c r="M1" s="16" t="inlineStr">
+      <c r="O1" s="16" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
       </c>
-      <c r="N1" s="16" t="inlineStr">
+      <c r="P1" s="16" t="inlineStr">
         <is>
           <t>Image Source</t>
         </is>
       </c>
-      <c r="O1" s="16" t="inlineStr">
+      <c r="Q1" s="16" t="inlineStr">
         <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="P1" s="16" t="inlineStr">
+      <c r="R1" s="16" t="inlineStr">
         <is>
           <t>Ingredients Source</t>
         </is>
       </c>
-      <c r="Q1" s="16" t="inlineStr">
+      <c r="S1" s="16" t="inlineStr">
         <is>
           <t>Best guess (manual)</t>
-        </is>
-      </c>
-      <c r="R1" s="16" t="inlineStr">
-        <is>
-          <t>Tags</t>
-        </is>
-      </c>
-      <c r="S1" s="16" t="inlineStr">
-        <is>
-          <t>Confirmed by</t>
         </is>
       </c>
     </row>
@@ -1566,40 +1548,28 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr"/>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="7" t="inlineStr">
+        <is>
           <t>https://www.spa-components.com/user/shop/big/1473-1_filter-cartridge-sc779-rising-dragon-plastics--eago-whirlpools.jpg?ff=1&amp;x=1024&amp;y=768&amp;q=85&amp;ts=6720c4a0&amp;sg=161563f2</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
-        <is>
-          <t>https://www.spa-components.com/user/shop/big/1473-1_filter-cartridge-sc779-rising-dragon-plastics--eago-whirlpools.jpg?ff=1&amp;x=1024&amp;y=768&amp;q=85&amp;ts=6720c4a0&amp;sg=161563f2</t>
-        </is>
-      </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="O2" s="19" t="inlineStr">
+      <c r="Q2" s="19" t="inlineStr"/>
+      <c r="R2" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P2" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q2" s="17" t="inlineStr">
-        <is>
-          <t>3 sources: barcodelookup.com, ean-search.org, spa-components.com</t>
-        </is>
-      </c>
-      <c r="R2" s="17" t="inlineStr">
-        <is>
-          <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S2" s="30" t="inlineStr">
+      <c r="S2" s="17" t="inlineStr">
         <is>
           <t>3 sources: barcodelookup.com, ean-search.org, spa-components.com</t>
         </is>
@@ -1652,43 +1622,37 @@
           <t>filters, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="K3" s="4" t="n">
-        <v>13.6</v>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bestwaystore.de/media/c6/f8/ba/1756384660/6941607353615-main-jpg.jpg?ts=1756384660</t>
+        </is>
       </c>
       <c r="L3" s="4" t="n">
         <v>10.6</v>
       </c>
-      <c r="M3" s="7" t="inlineStr">
+      <c r="M3" s="4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>https://www.bestwaystore.de/media/c6/f8/ba/1756384660/6941607353615-main-jpg.jpg?ts=1756384660</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="P3" s="7" t="inlineStr">
         <is>
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="O3" s="19" t="inlineStr">
+      <c r="Q3" s="19" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P3" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q3" s="17" t="inlineStr">
-        <is>
-          <t>3 sources: barcodelookup.com, bestwaystore.de, ean-search.org</t>
-        </is>
-      </c>
-      <c r="R3" s="17" t="inlineStr">
-        <is>
-          <t>filters, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S3" s="30" t="inlineStr">
+      <c r="S3" s="17" t="inlineStr">
         <is>
           <t>3 sources: barcodelookup.com, bestwaystore.de, ean-search.org</t>
         </is>
@@ -1748,46 +1712,34 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="7" t="inlineStr">
+        <is>
           <t>https://ap.nice-cdn.com/upload/image/product/large/default/bestway-flowclear-filter-cartridge-size-3-1-item-638140-en.jpg</t>
         </is>
       </c>
-      <c r="M4" s="7" t="inlineStr">
-        <is>
-          <t>https://ap.nice-cdn.com/upload/image/product/large/default/bestway-flowclear-filter-cartridge-size-3-1-item-638140-en.jpg</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="O4" s="19" t="inlineStr">
+      <c r="Q4" s="19" t="inlineStr"/>
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P4" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q4" s="17" t="inlineStr">
+      <c r="S4" s="17" t="inlineStr">
         <is>
           <t>3 sources: barcodelookup.com, ean-search.org, pools.shop</t>
         </is>
       </c>
-      <c r="R4" s="17" t="inlineStr">
-        <is>
-          <t>filters, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S4" s="30" t="inlineStr">
-        <is>
-          <t>3 sources: barcodelookup.com, ean-search.org, pools.shop</t>
-        </is>
-      </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr"/>
       <c r="B5" s="10" t="inlineStr">
         <is>
@@ -1824,29 +1776,21 @@
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="11" t="inlineStr"/>
+      <c r="P5" s="11" t="inlineStr">
         <is>
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="N5" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="O5" s="19" t="inlineStr">
+      <c r="Q5" s="19" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P5" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q5" s="17" t="inlineStr"/>
-      <c r="R5" s="17" t="inlineStr"/>
-      <c r="S5" s="30" t="inlineStr"/>
+      <c r="S5" s="17" t="inlineStr"/>
     </row>
     <row r="6" ht="132" customHeight="1">
       <c r="A6" s="2" t="inlineStr"/>
@@ -1902,40 +1846,28 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
+          <t>Verified — Barcode Lookup (barcode)</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
           <t>https://images.barcodelookup.com/29361/293617958-1.jpg</t>
         </is>
       </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>https://images.barcodelookup.com/29361/293617958-1.jpg</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="O6" s="19" t="inlineStr">
+      <c r="Q6" s="19" t="inlineStr"/>
+      <c r="R6" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P6" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q6" s="17" t="inlineStr">
-        <is>
-          <t>2 sources: barcodelookup.com, ean-search.org</t>
-        </is>
-      </c>
-      <c r="R6" s="17" t="inlineStr">
-        <is>
-          <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S6" s="30" t="inlineStr">
+      <c r="S6" s="17" t="inlineStr">
         <is>
           <t>2 sources: barcodelookup.com, ean-search.org</t>
         </is>
@@ -1988,43 +1920,37 @@
           <t>filters, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="K7" s="4" t="n">
-        <v>25.4</v>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bestwaystore.de/media/53/6c/e9/1756384676/6941607353622-main-jpg.jpg?ts=1756384676</t>
+        </is>
       </c>
       <c r="L7" s="4" t="n">
         <v>14.2</v>
       </c>
-      <c r="M7" s="7" t="inlineStr">
+      <c r="M7" s="4" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t>https://www.bestwaystore.de/media/53/6c/e9/1756384676/6941607353622-main-jpg.jpg?ts=1756384676</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="O7" s="19" t="inlineStr">
+      <c r="Q7" s="19" t="inlineStr"/>
+      <c r="R7" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P7" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q7" s="17" t="inlineStr">
-        <is>
-          <t>3 sources: barcodelookup.com, bestwaystore.de, ean-search.org</t>
-        </is>
-      </c>
-      <c r="R7" s="17" t="inlineStr">
-        <is>
-          <t>filters, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S7" s="30" t="inlineStr">
+      <c r="S7" s="17" t="inlineStr">
         <is>
           <t>3 sources: barcodelookup.com, bestwaystore.de, ean-search.org</t>
         </is>
@@ -2084,50 +2010,38 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
+          <t>Likely — Barcode Lookup (barcode) (unclear)</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr"/>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="14" t="inlineStr">
+        <is>
           <t>https://images.barcodelookup.com/4378/43786454-1.jpg</t>
         </is>
       </c>
-      <c r="M8" s="14" t="inlineStr">
-        <is>
-          <t>https://images.barcodelookup.com/4378/43786454-1.jpg</t>
-        </is>
-      </c>
-      <c r="N8" s="14" t="inlineStr">
+      <c r="P8" s="14" t="inlineStr">
         <is>
           <t>Likely — Barcode Lookup (barcode) (unclear)</t>
         </is>
       </c>
-      <c r="O8" s="19" t="inlineStr">
+      <c r="Q8" s="19" t="inlineStr"/>
+      <c r="R8" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q8" s="17" t="inlineStr">
-        <is>
-          <t>2 sources: barcodelookup.com, ean-search.org</t>
-        </is>
-      </c>
-      <c r="R8" s="17" t="inlineStr">
-        <is>
-          <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S8" s="30" t="inlineStr">
+      <c r="S8" s="17" t="inlineStr">
         <is>
           <t>2 sources: barcodelookup.com, ean-search.org</t>
         </is>
       </c>
     </row>
     <row r="9" ht="132" customHeight="1">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>READY</t>
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
@@ -2155,14 +2069,14 @@
           <t>Filter cartridge</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>A hot tub and spa cartridge filter compatible with Unicel C-4950, Pleatco PRB50-IN, and Darlly 40506, noted as suitable for Arctic and Beachcomber spas among others. The source lists dimensions of approximately 34 cm height and 5 cm width.</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>Verified — product page</t>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>A replacement spa filter cartridge compatible with Arctic, Beachcomber, Canadian, Hydropool and Jacuzzi spas, sold under cross-reference codes including Unicel C-4950, Pleatco PRB50-IN and Darlly 40506. It keeps hot tub water clean by trapping debris and particles as water cycles through the filtration system.</t>
+        </is>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>Likely — generic (from name)</t>
         </is>
       </c>
       <c r="J9" s="17" t="inlineStr">
@@ -2170,43 +2084,35 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="K9" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M9" s="7" t="inlineStr">
-        <is>
-          <t>https://i.ebayimg.com/images/g/7WgAAOSwQ7haxTU1/s-l1600.jpg</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>Verified — barcode</t>
-        </is>
-      </c>
-      <c r="O9" s="19" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>https://images.barcodelookup.com/4469/44699532-1.jpg</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>Likely — Barcode Lookup (barcode) (unclear)</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr"/>
+      <c r="O9" s="14" t="inlineStr">
+        <is>
+          <t>https://images.barcodelookup.com/4469/44699532-1.jpg</t>
+        </is>
+      </c>
+      <c r="P9" s="14" t="inlineStr">
+        <is>
+          <t>Likely — Barcode Lookup (barcode) (unclear)</t>
+        </is>
+      </c>
+      <c r="Q9" s="19" t="inlineStr"/>
+      <c r="R9" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P9" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q9" s="17" t="inlineStr">
-        <is>
-          <t>2 sources: barcodelookup, ean-search.org</t>
-        </is>
-      </c>
-      <c r="R9" s="17" t="inlineStr">
-        <is>
-          <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S9" s="30" t="inlineStr">
+      <c r="S9" s="17" t="inlineStr">
         <is>
           <t>2 sources: barcodelookup, ean-search.org</t>
         </is>
@@ -2221,7 +2127,7 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>Calacatta 4-person inflatable spa</t>
+          <t>Calacatta 4-person Inflatable Spa</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -2260,42 +2166,34 @@
         </is>
       </c>
       <c r="K10" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="M10" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="N10" s="4" t="n">
         <v>64.92</v>
       </c>
-      <c r="M10" s="7" t="inlineStr">
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t>https://media.intex.fr/7743-large_default_x2/28464ex-spa-gonflable-calacatta-4-places.jpg</t>
         </is>
       </c>
-      <c r="N10" s="7" t="inlineStr">
+      <c r="P10" s="7" t="inlineStr">
         <is>
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="O10" s="19" t="inlineStr">
+      <c r="Q10" s="19" t="inlineStr"/>
+      <c r="R10" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P10" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q10" s="17" t="inlineStr">
-        <is>
-          <t>3 sources: barcodelookup.com, ean-search.org, intex.fr</t>
-        </is>
-      </c>
-      <c r="R10" s="17" t="inlineStr">
-        <is>
-          <t>spa-hot-tub, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S10" s="30" t="inlineStr">
+      <c r="S10" s="17" t="inlineStr">
         <is>
           <t>3 sources: barcodelookup.com, ean-search.org, intex.fr</t>
         </is>
@@ -2348,43 +2246,37 @@
           <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="K11" s="4" t="n">
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>https://images.barcodelookup.com/12027/120276177-1.jpg</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>Verified — Barcode Lookup (barcode)</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr"/>
+      <c r="N11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M11" s="7" t="inlineStr">
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t>https://images.barcodelookup.com/12027/120276177-1.jpg</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr">
+      <c r="P11" s="7" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="O11" s="19" t="inlineStr">
+      <c r="Q11" s="19" t="inlineStr"/>
+      <c r="R11" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P11" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q11" s="17" t="inlineStr">
-        <is>
-          <t>1 source: barcodelookup</t>
-        </is>
-      </c>
-      <c r="R11" s="17" t="inlineStr">
-        <is>
-          <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S11" s="30" t="inlineStr">
+      <c r="S11" s="17" t="inlineStr">
         <is>
           <t>1 source: barcodelookup</t>
         </is>
@@ -2443,37 +2335,21 @@
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="M12" s="11" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr"/>
+      <c r="N12" s="4" t="inlineStr"/>
+      <c r="O12" s="11" t="inlineStr"/>
+      <c r="P12" s="11" t="inlineStr">
         <is>
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="O12" s="19" t="inlineStr">
+      <c r="Q12" s="19" t="inlineStr"/>
+      <c r="R12" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P12" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q12" s="17" t="inlineStr">
-        <is>
-          <t>1 source: ean-search.org</t>
-        </is>
-      </c>
-      <c r="R12" s="17" t="inlineStr">
-        <is>
-          <t>spa-hot-tub, considered-purchase, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S12" s="30" t="inlineStr">
+      <c r="S12" s="17" t="inlineStr">
         <is>
           <t>1 source: ean-search.org</t>
         </is>
@@ -2488,7 +2364,7 @@
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>Olive 8-person inflatable spa</t>
+          <t>Olive 8-person Inflatable Spa</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -2533,40 +2409,28 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr"/>
+      <c r="N13" s="4" t="inlineStr"/>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
           <t>https://media.intex.fr/11990-large_default_x2/28412np-spa-gonflable-olive-8-places.jpg</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>https://media.intex.fr/11990-large_default_x2/28412np-spa-gonflable-olive-8-places.jpg</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
+      <c r="P13" s="7" t="inlineStr">
         <is>
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="O13" s="19" t="inlineStr">
+      <c r="Q13" s="19" t="inlineStr"/>
+      <c r="R13" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P13" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q13" s="17" t="inlineStr">
-        <is>
-          <t>3 sources: barcodelookup.com, ean-search.org, intex.fr</t>
-        </is>
-      </c>
-      <c r="R13" s="17" t="inlineStr">
-        <is>
-          <t>spa-hot-tub, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S13" s="30" t="inlineStr">
+      <c r="S13" s="17" t="inlineStr">
         <is>
           <t>3 sources: barcodelookup.com, ean-search.org, intex.fr</t>
         </is>
@@ -2581,7 +2445,7 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>SC750 Filter replacement filter lamellar filter Arctic Fonteyn Rota Strong Spa - Darlly</t>
+          <t>SC750 Filter Replacement Filter Lamellar Filter Arctic Fonteyn Rota Strong Spa - Darlly</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -2626,40 +2490,28 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
+          <t>Verified — Barcode Lookup (barcode)</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr"/>
+      <c r="N14" s="4" t="inlineStr"/>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
           <t>https://images.barcodelookup.com/29338/293384728-1.jpg</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>https://images.barcodelookup.com/29338/293384728-1.jpg</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="inlineStr">
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="O14" s="19" t="inlineStr">
+      <c r="Q14" s="19" t="inlineStr"/>
+      <c r="R14" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P14" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q14" s="17" t="inlineStr">
-        <is>
-          <t>2 sources: barcodelookup.com, ean-search.org</t>
-        </is>
-      </c>
-      <c r="R14" s="17" t="inlineStr">
-        <is>
-          <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S14" s="30" t="inlineStr">
+      <c r="S14" s="17" t="inlineStr">
         <is>
           <t>2 sources: barcodelookup.com, ean-search.org</t>
         </is>
@@ -2718,43 +2570,27 @@
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr"/>
+      <c r="N15" s="4" t="inlineStr"/>
+      <c r="O15" s="11" t="inlineStr"/>
+      <c r="P15" s="11" t="inlineStr">
         <is>
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="N15" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="O15" s="19" t="inlineStr">
+      <c r="Q15" s="19" t="inlineStr"/>
+      <c r="R15" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P15" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q15" s="17" t="inlineStr">
+      <c r="S15" s="17" t="inlineStr">
         <is>
           <t>2 sources: spa-plus.eu, ean-search.org</t>
         </is>
       </c>
-      <c r="R15" s="17" t="inlineStr">
-        <is>
-          <t>cleaning, add-on, multi-source-confirmed, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S15" s="30" t="inlineStr">
-        <is>
-          <t>2 sources: spa-plus.eu, ean-search.org</t>
-        </is>
-      </c>
     </row>
-    <row r="16" ht="34" customHeight="1">
+    <row r="16" ht="20" customHeight="1">
       <c r="A16" s="9" t="inlineStr"/>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -2791,29 +2627,21 @@
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="M16" s="11" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr"/>
+      <c r="N16" s="4" t="inlineStr"/>
+      <c r="O16" s="11" t="inlineStr"/>
+      <c r="P16" s="11" t="inlineStr">
         <is>
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="N16" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="O16" s="19" t="inlineStr">
+      <c r="Q16" s="19" t="inlineStr"/>
+      <c r="R16" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P16" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q16" s="17" t="inlineStr"/>
-      <c r="R16" s="17" t="inlineStr"/>
-      <c r="S16" s="30" t="inlineStr"/>
+      <c r="S16" s="17" t="inlineStr"/>
     </row>
     <row r="17" ht="62" customHeight="1">
       <c r="A17" s="9" t="inlineStr"/>
@@ -2868,37 +2696,21 @@
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="M17" s="11" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr"/>
+      <c r="N17" s="4" t="inlineStr"/>
+      <c r="O17" s="11" t="inlineStr"/>
+      <c r="P17" s="11" t="inlineStr">
         <is>
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="N17" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="O17" s="19" t="inlineStr">
+      <c r="Q17" s="19" t="inlineStr"/>
+      <c r="R17" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q17" s="17" t="inlineStr">
-        <is>
-          <t>1 source: ean-search.org</t>
-        </is>
-      </c>
-      <c r="R17" s="17" t="inlineStr">
-        <is>
-          <t>test-measure, add-on, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S17" s="30" t="inlineStr">
+      <c r="S17" s="17" t="inlineStr">
         <is>
           <t>1 source: ean-search.org</t>
         </is>
@@ -2957,37 +2769,21 @@
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="M18" s="11" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr"/>
+      <c r="N18" s="4" t="inlineStr"/>
+      <c r="O18" s="11" t="inlineStr"/>
+      <c r="P18" s="11" t="inlineStr">
         <is>
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="N18" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="O18" s="19" t="inlineStr">
+      <c r="Q18" s="19" t="inlineStr"/>
+      <c r="R18" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P18" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q18" s="17" t="inlineStr">
-        <is>
-          <t>1 source: ean-search.org</t>
-        </is>
-      </c>
-      <c r="R18" s="17" t="inlineStr">
-        <is>
-          <t>test-measure, add-on, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S18" s="30" t="inlineStr">
+      <c r="S18" s="17" t="inlineStr">
         <is>
           <t>1 source: ean-search.org</t>
         </is>
@@ -3002,7 +2798,7 @@
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>Cristal Poolpflege CRISTAL alkaline rim cleaner 1,0 l, (material-safe, for liners, plastic surfaces</t>
+          <t>Cristal Poolpflege CRISTAL Alkaline Edge Cleaner 1,0 l, (Gentle on Materials, for Liners, Plastic Surfaces</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -3047,40 +2843,28 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
+          <t>Verified — Barcode Lookup (barcode)</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr"/>
+      <c r="N19" s="4" t="inlineStr"/>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
           <t>https://images.barcodelookup.com/21057/210579756-1.jpg</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
-        <is>
-          <t>https://images.barcodelookup.com/21057/210579756-1.jpg</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="inlineStr">
+      <c r="P19" s="7" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="O19" s="19" t="inlineStr">
+      <c r="Q19" s="19" t="inlineStr"/>
+      <c r="R19" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P19" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q19" s="17" t="inlineStr">
-        <is>
-          <t>2 sources: barcodelookup.com, ean-search.org</t>
-        </is>
-      </c>
-      <c r="R19" s="17" t="inlineStr">
-        <is>
-          <t>pool, water-treatment, cleaning, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S19" s="30" t="inlineStr">
+      <c r="S19" s="17" t="inlineStr">
         <is>
           <t>2 sources: barcodelookup.com, ean-search.org</t>
         </is>
@@ -3095,7 +2879,7 @@
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>AQUALITY pool cleaner for greasy residues 1L</t>
+          <t>AQUALITY Pool Cleaner for Greasy Residues 1L</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -3140,40 +2924,28 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr"/>
+      <c r="N20" s="4" t="inlineStr"/>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
           <t>http://mangas.com.cy/media/products/5292638000223.jpg</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr">
-        <is>
-          <t>http://mangas.com.cy/media/products/5292638000223.jpg</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="inlineStr">
+      <c r="P20" s="7" t="inlineStr">
         <is>
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="O20" s="19" t="inlineStr">
+      <c r="Q20" s="19" t="inlineStr"/>
+      <c r="R20" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P20" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q20" s="17" t="inlineStr">
-        <is>
-          <t>2 sources: mangas.com.cy, ean-search.org</t>
-        </is>
-      </c>
-      <c r="R20" s="17" t="inlineStr">
-        <is>
-          <t>pool, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S20" s="30" t="inlineStr">
+      <c r="S20" s="17" t="inlineStr">
         <is>
           <t>2 sources: mangas.com.cy, ean-search.org</t>
         </is>
@@ -3233,40 +3005,28 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr"/>
+      <c r="N21" s="4" t="inlineStr"/>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
           <t>https://poolservices.cy/storage/2026/05/California-Clear-Blue-1L-Aquality-2.jpeg</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>https://poolservices.cy/storage/2026/05/California-Clear-Blue-1L-Aquality-2.jpeg</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr">
+      <c r="P21" s="7" t="inlineStr">
         <is>
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="O21" s="19" t="inlineStr">
+      <c r="Q21" s="19" t="inlineStr"/>
+      <c r="R21" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P21" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q21" s="17" t="inlineStr">
-        <is>
-          <t>2 sources: poolservices.cy, ean-search.org</t>
-        </is>
-      </c>
-      <c r="R21" s="17" t="inlineStr">
-        <is>
-          <t>pool, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S21" s="30" t="inlineStr">
+      <c r="S21" s="17" t="inlineStr">
         <is>
           <t>2 sources: poolservices.cy, ean-search.org</t>
         </is>
@@ -3326,40 +3086,28 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr"/>
+      <c r="N22" s="4" t="inlineStr"/>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
           <t>http://mangas.com.cy/media/products/5292638000162.jpg</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>http://mangas.com.cy/media/products/5292638000162.jpg</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="inlineStr">
+      <c r="P22" s="7" t="inlineStr">
         <is>
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="O22" s="19" t="inlineStr">
+      <c r="Q22" s="19" t="inlineStr"/>
+      <c r="R22" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P22" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q22" s="17" t="inlineStr">
-        <is>
-          <t>2 sources: mangas.com.cy, ean-search.org</t>
-        </is>
-      </c>
-      <c r="R22" s="17" t="inlineStr">
-        <is>
-          <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S22" s="30" t="inlineStr">
+      <c r="S22" s="17" t="inlineStr">
         <is>
           <t>2 sources: mangas.com.cy, ean-search.org</t>
         </is>
@@ -3374,7 +3122,7 @@
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>Höfer Chemie GmbH pool care 1 L BAYZID® SPA Poolclear turbidity remover</t>
+          <t>Höfer Chemie GmbH Pool Care 1 L BAYZID® SPA Poolclear Turbidity Remover</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -3418,37 +3166,21 @@
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="M23" s="11" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr"/>
+      <c r="N23" s="4" t="inlineStr"/>
+      <c r="O23" s="11" t="inlineStr"/>
+      <c r="P23" s="11" t="inlineStr">
         <is>
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="N23" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="O23" s="19" t="inlineStr">
+      <c r="Q23" s="19" t="inlineStr"/>
+      <c r="R23" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P23" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q23" s="17" t="inlineStr">
-        <is>
-          <t>1 source: ean-search.org</t>
-        </is>
-      </c>
-      <c r="R23" s="17" t="inlineStr">
-        <is>
-          <t>spa-hot-tub, pool, water-treatment, considered-purchase, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S23" s="30" t="inlineStr">
+      <c r="S23" s="17" t="inlineStr">
         <is>
           <t>1 source: ean-search.org</t>
         </is>
@@ -3463,7 +3195,7 @@
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>HÖFER CHEMIE GMBH 1 l hydrogen peroxide 11,9%</t>
+          <t>HÖFER CHEMIE GMBH 1 l Hydrogen Peroxide 11,9%</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -3507,37 +3239,21 @@
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="M24" s="11" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr"/>
+      <c r="N24" s="4" t="inlineStr"/>
+      <c r="O24" s="11" t="inlineStr"/>
+      <c r="P24" s="11" t="inlineStr">
         <is>
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="N24" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="O24" s="19" t="inlineStr">
+      <c r="Q24" s="19" t="inlineStr"/>
+      <c r="R24" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P24" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q24" s="17" t="inlineStr">
-        <is>
-          <t>1 source: ean-search.org</t>
-        </is>
-      </c>
-      <c r="R24" s="17" t="inlineStr">
-        <is>
-          <t>water-treatment, repeat-purchase, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S24" s="30" t="inlineStr">
+      <c r="S24" s="17" t="inlineStr">
         <is>
           <t>1 source: ean-search.org</t>
         </is>
@@ -3552,7 +3268,7 @@
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>Astralpool water care Astralpool Chlorine Stabilizer 4,5 kg</t>
+          <t>Astralpool Water Care Astralpool Chlorine Stabilizer 4,5 kg</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -3590,43 +3306,29 @@
           <t>water-treatment, repeat-purchase, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="K25" s="4" t="n">
+      <c r="K25" s="4" t="inlineStr"/>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>Blank — no image</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="n">
         <v>4.5</v>
       </c>
-      <c r="L25" s="4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M25" s="11" t="inlineStr">
+      <c r="O25" s="11" t="inlineStr"/>
+      <c r="P25" s="11" t="inlineStr">
         <is>
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="N25" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="O25" s="19" t="inlineStr">
+      <c r="Q25" s="19" t="inlineStr"/>
+      <c r="R25" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P25" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q25" s="17" t="inlineStr">
-        <is>
-          <t>1 source: ean-search.org</t>
-        </is>
-      </c>
-      <c r="R25" s="17" t="inlineStr">
-        <is>
-          <t>water-treatment, repeat-purchase, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S25" s="30" t="inlineStr">
+      <c r="S25" s="17" t="inlineStr">
         <is>
           <t>1 source: ean-search.org</t>
         </is>
@@ -3686,40 +3388,28 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
+          <t>Verified — Barcode Lookup (barcode)</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="inlineStr"/>
+      <c r="O26" s="7" t="inlineStr">
+        <is>
           <t>https://images.barcodelookup.com/16704/167043133-1.jpg</t>
         </is>
       </c>
-      <c r="M26" s="7" t="inlineStr">
-        <is>
-          <t>https://images.barcodelookup.com/16704/167043133-1.jpg</t>
-        </is>
-      </c>
-      <c r="N26" s="7" t="inlineStr">
+      <c r="P26" s="7" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="O26" s="19" t="inlineStr">
+      <c r="Q26" s="19" t="inlineStr"/>
+      <c r="R26" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P26" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q26" s="17" t="inlineStr">
-        <is>
-          <t>3 sources: spa-plus.eu, barcodelookup.com, ean-search.org</t>
-        </is>
-      </c>
-      <c r="R26" s="17" t="inlineStr">
-        <is>
-          <t>water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S26" s="30" t="inlineStr">
+      <c r="S26" s="17" t="inlineStr">
         <is>
           <t>3 sources: spa-plus.eu, barcodelookup.com, ean-search.org</t>
         </is>
@@ -3779,40 +3469,28 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr"/>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
           <t>https://www.piscinarium.com/2908-thickbox_default/pool-gom-magic-rubber-eraser.jpg</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr">
-        <is>
-          <t>https://www.piscinarium.com/2908-thickbox_default/pool-gom-magic-rubber-eraser.jpg</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="inlineStr">
+      <c r="P27" s="7" t="inlineStr">
         <is>
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="O27" s="19" t="inlineStr">
+      <c r="Q27" s="19" t="inlineStr"/>
+      <c r="R27" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P27" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q27" s="17" t="inlineStr">
-        <is>
-          <t>2 sources: ean-search.org, piscinarium.com</t>
-        </is>
-      </c>
-      <c r="R27" s="17" t="inlineStr">
-        <is>
-          <t>pool, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S27" s="30" t="inlineStr">
+      <c r="S27" s="17" t="inlineStr">
         <is>
           <t>2 sources: ean-search.org, piscinarium.com</t>
         </is>
@@ -3871,37 +3549,21 @@
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="M28" s="11" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr"/>
+      <c r="N28" s="4" t="inlineStr"/>
+      <c r="O28" s="11" t="inlineStr"/>
+      <c r="P28" s="11" t="inlineStr">
         <is>
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="N28" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="O28" s="19" t="inlineStr">
+      <c r="Q28" s="19" t="inlineStr"/>
+      <c r="R28" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P28" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q28" s="17" t="inlineStr">
-        <is>
-          <t>2 sources: ean-search.org, spa-industries.eu</t>
-        </is>
-      </c>
-      <c r="R28" s="17" t="inlineStr">
-        <is>
-          <t>spa-hot-tub, considered-purchase, multi-source-confirmed, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S28" s="30" t="inlineStr">
+      <c r="S28" s="17" t="inlineStr">
         <is>
           <t>2 sources: ean-search.org, spa-industries.eu</t>
         </is>
@@ -3916,7 +3578,7 @@
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>Höfer Chemie GmbH 1 L sauna cleaner with eucalyptus scent - high-concentrate deep cleaner</t>
+          <t>Höfer Chemie GmbH 1 L Sauna Cleaner with Eucalyptus Scent - High-Concentrate Deep Cleaner</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -3960,37 +3622,21 @@
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="M29" s="11" t="inlineStr">
+      <c r="M29" s="4" t="inlineStr"/>
+      <c r="N29" s="4" t="inlineStr"/>
+      <c r="O29" s="11" t="inlineStr"/>
+      <c r="P29" s="11" t="inlineStr">
         <is>
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="N29" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="O29" s="19" t="inlineStr">
+      <c r="Q29" s="19" t="inlineStr"/>
+      <c r="R29" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P29" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q29" s="17" t="inlineStr">
-        <is>
-          <t>1 source: ean-search.org</t>
-        </is>
-      </c>
-      <c r="R29" s="17" t="inlineStr">
-        <is>
-          <t>cleaning, add-on, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S29" s="30" t="inlineStr">
+      <c r="S29" s="17" t="inlineStr">
         <is>
           <t>1 source: ean-search.org</t>
         </is>
@@ -4005,7 +3651,7 @@
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>HTH Spa spa cleaner</t>
+          <t>HTH Spa Spa Cleaner</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -4050,46 +3696,34 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr"/>
+      <c r="N30" s="4" t="inlineStr"/>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
           <t>https://www.cdiscount.com/pdt2/0/5/1/1/700x700/auc2009356289051/rw/hth-spa-nettoyant-spa-3521686010178.jpg</t>
         </is>
       </c>
-      <c r="M30" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cdiscount.com/pdt2/0/5/1/1/700x700/auc2009356289051/rw/hth-spa-nettoyant-spa-3521686010178.jpg</t>
-        </is>
-      </c>
-      <c r="N30" s="7" t="inlineStr">
+      <c r="P30" s="7" t="inlineStr">
         <is>
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="O30" s="19" t="inlineStr">
+      <c r="Q30" s="19" t="inlineStr"/>
+      <c r="R30" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P30" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q30" s="17" t="inlineStr">
+      <c r="S30" s="17" t="inlineStr">
         <is>
           <t>3 sources: barcodelookup.com, cdiscount.com, ean-search.org</t>
         </is>
       </c>
-      <c r="R30" s="17" t="inlineStr">
-        <is>
-          <t>spa-hot-tub, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S30" s="30" t="inlineStr">
-        <is>
-          <t>3 sources: barcodelookup.com, cdiscount.com, ean-search.org</t>
-        </is>
-      </c>
     </row>
-    <row r="31" ht="244" customHeight="1">
+    <row r="31" ht="132" customHeight="1">
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="5" t="inlineStr">
         <is>
@@ -4136,43 +3770,41 @@
           <t>pool, salt, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="K31" s="4" t="n">
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>http://altruan.com/cdn/shop/files/SalinenPoolSalz25kgSack.png?v=1778597596</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr"/>
+      <c r="N31" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="L31" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="M31" s="7" t="inlineStr">
+      <c r="O31" s="7" t="inlineStr">
         <is>
           <t>http://altruan.com/cdn/shop/files/SalinenPoolSalz25kgSack.png?v=1778597596</t>
         </is>
       </c>
-      <c r="N31" s="7" t="inlineStr">
+      <c r="P31" s="7" t="inlineStr">
         <is>
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="O31" s="19" t="inlineStr">
+      <c r="Q31" s="19" t="inlineStr">
         <is>
           <t>Composition: Siedesalz (min. 99.6% NaCl) 100%; Separant/sodium ferrocyanide 4.0–12.0 mg/kg | Grain: &gt;0.63 mm approx. 20%, 0.2–0.63 mm approx. 75%, &lt;0.2 mm approx. 5% | Moisture: &lt;0.08%</t>
         </is>
       </c>
-      <c r="P31" s="8" t="inlineStr">
+      <c r="R31" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="Q31" s="17" t="inlineStr">
-        <is>
-          <t>3 sources: altruan.com, barcodelookup.com, ean-search.org</t>
-        </is>
-      </c>
-      <c r="R31" s="17" t="inlineStr">
-        <is>
-          <t>pool, salt, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S31" s="30" t="inlineStr">
+      <c r="S31" s="17" t="inlineStr">
         <is>
           <t>3 sources: altruan.com, barcodelookup.com, ean-search.org</t>
         </is>
@@ -4180,14 +3812,14 @@
     </row>
     <row r="32" ht="132" customHeight="1">
       <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>READY</t>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>AIPER Scuba SE cordless robotic pool cleaner, grey</t>
+          <t>AIPER Scuba S3 Cordless Pool Robot, Automatic Floor and Wall Cleaning, WavePath™ Navigation, High-Performance Filtration and Smart Control</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -4197,7 +3829,7 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t>3 sources: barcodelookup.com, ean-search.org, shoppster.si</t>
+          <t>2 sources: barcodelookup, ean-search.org</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -4210,14 +3842,14 @@
           <t>Pool robot cleaner</t>
         </is>
       </c>
-      <c r="H32" s="18" t="inlineStr">
-        <is>
-          <t>A battery-powered robotic pool vacuum cleaner from Aiper, the Scuba SE model in grey, designed to clean pool floors autonomously without a mains connection. Cordless and self-contained, it takes the effort out of keeping the bottom of the pool tidy.</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>Verified — product page</t>
+      <c r="H32" s="21" t="inlineStr">
+        <is>
+          <t>A cordless robotic pool cleaner that scrubs both floors and walls automatically, using WavePath navigation to map and cover the pool efficiently. Built-in high-performance filtration and smart control make it a hands-off solution for keeping pool water clear.</t>
+        </is>
+      </c>
+      <c r="I32" s="15" t="inlineStr">
+        <is>
+          <t>Likely — generic (from name)</t>
         </is>
       </c>
       <c r="J32" s="17" t="inlineStr">
@@ -4227,47 +3859,35 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://www.shoppster.si/medias/?context=bWFzdGVyfGltYWdlc3wyMjk1MXxpbWFnZS9qcGVnfGFEbG1MMmd4TXk4eE16SXdNamMzTlRNek5qVTFNelF8MjA5NWI5YWZjYjFhOTY5ZWJjNGRjM2Q1Y2NmMWVmNzExODIzNTI2NDM1M2I4ZWVlMGI5YWZlNWUyNzUyNTE1Nw</t>
+          <t>https://images.barcodelookup.com/176692/1766920801-1.jpg</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>https://www.shoppster.si/medias/?context=bWFzdGVyfGltYWdlc3wyMjk1MXxpbWFnZS9qcGVnfGFEbG1MMmd4TXk4eE16SXdNamMzTlRNek5qVTFNelF8MjA5NWI5YWZjYjFhOTY5ZWJjNGRjM2Q1Y2NmMWVmNzExODIzNTI2NDM1M2I4ZWVlMGI5YWZlNWUyNzUyNTE1Nw</t>
-        </is>
-      </c>
-      <c r="M32" s="7" t="inlineStr">
-        <is>
-          <t>https://www.shoppster.si/medias/?context=bWFzdGVyfGltYWdlc3wyMjk1MXxpbWFnZS9qcGVnfGFEbG1MMmd4TXk4eE16SXdNamMzTlRNek5qVTFNelF8MjA5NWI5YWZjYjFhOTY5ZWJjNGRjM2Q1Y2NmMWVmNzExODIzNTI2NDM1M2I4ZWVlMGI5YWZlNWUyNzUyNTE1Nw</t>
-        </is>
-      </c>
-      <c r="N32" s="7" t="inlineStr">
-        <is>
-          <t>Verified — barcode</t>
-        </is>
-      </c>
-      <c r="O32" s="19" t="inlineStr">
+          <t>Verified — Barcode Lookup (barcode)</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr"/>
+      <c r="N32" s="4" t="inlineStr"/>
+      <c r="O32" s="7" t="inlineStr">
+        <is>
+          <t>https://images.barcodelookup.com/176692/1766920801-1.jpg</t>
+        </is>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>Verified — Barcode Lookup (barcode)</t>
+        </is>
+      </c>
+      <c r="Q32" s="19" t="inlineStr"/>
+      <c r="R32" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P32" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q32" s="17" t="inlineStr">
-        <is>
-          <t>3 sources: barcodelookup.com, ean-search.org, shoppster.si</t>
-        </is>
-      </c>
-      <c r="R32" s="17" t="inlineStr">
-        <is>
-          <t>pool, cleaning, robot-cleaner, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S32" s="30" t="inlineStr">
-        <is>
-          <t>3 sources: barcodelookup.com, ean-search.org, shoppster.si</t>
+      <c r="S32" s="17" t="inlineStr">
+        <is>
+          <t>2 sources: barcodelookup, ean-search.org</t>
         </is>
       </c>
     </row>
@@ -4325,40 +3945,28 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
+          <t>Verified — Barcode Lookup (barcode)</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr"/>
+      <c r="N33" s="4" t="inlineStr"/>
+      <c r="O33" s="7" t="inlineStr">
+        <is>
           <t>https://images.barcodelookup.com/124722/1247228758-1.jpg</t>
         </is>
       </c>
-      <c r="M33" s="7" t="inlineStr">
-        <is>
-          <t>https://images.barcodelookup.com/124722/1247228758-1.jpg</t>
-        </is>
-      </c>
-      <c r="N33" s="7" t="inlineStr">
+      <c r="P33" s="7" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="O33" s="19" t="inlineStr">
+      <c r="Q33" s="19" t="inlineStr"/>
+      <c r="R33" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P33" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q33" s="17" t="inlineStr">
-        <is>
-          <t>2 sources: ean-search.org, eleonto.com</t>
-        </is>
-      </c>
-      <c r="R33" s="17" t="inlineStr">
-        <is>
-          <t>robot-cleaner, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S33" s="30" t="inlineStr">
+      <c r="S33" s="17" t="inlineStr">
         <is>
           <t>2 sources: ean-search.org, eleonto.com</t>
         </is>
@@ -4418,40 +4026,28 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
+          <t>Verified — Barcode Lookup (barcode)</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr"/>
+      <c r="N34" s="4" t="inlineStr"/>
+      <c r="O34" s="7" t="inlineStr">
+        <is>
           <t>https://images.barcodelookup.com/124726/1247268298-1.jpg</t>
         </is>
       </c>
-      <c r="M34" s="7" t="inlineStr">
-        <is>
-          <t>https://images.barcodelookup.com/124726/1247268298-1.jpg</t>
-        </is>
-      </c>
-      <c r="N34" s="7" t="inlineStr">
+      <c r="P34" s="7" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="O34" s="19" t="inlineStr">
+      <c r="Q34" s="19" t="inlineStr"/>
+      <c r="R34" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P34" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q34" s="17" t="inlineStr">
-        <is>
-          <t>1 source: piscinarium.com</t>
-        </is>
-      </c>
-      <c r="R34" s="17" t="inlineStr">
-        <is>
-          <t>robot-cleaner, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S34" s="30" t="inlineStr">
+      <c r="S34" s="17" t="inlineStr">
         <is>
           <t>1 source: piscinarium.com</t>
         </is>
@@ -4505,42 +4101,34 @@
         </is>
       </c>
       <c r="K35" s="4" t="n">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L35" s="4" t="n">
         <v>191</v>
       </c>
-      <c r="M35" s="7" t="inlineStr">
+      <c r="M35" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="N35" s="4" t="n">
+        <v>191</v>
+      </c>
+      <c r="O35" s="7" t="inlineStr">
         <is>
           <t>https://www.ecoperation.com/media/catalog/product/cache/b76cf1d99a7811daa83ba86e6ad91c89/6/4/64757.jpg</t>
         </is>
       </c>
-      <c r="N35" s="7" t="inlineStr">
+      <c r="P35" s="7" t="inlineStr">
         <is>
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="O35" s="19" t="inlineStr">
+      <c r="Q35" s="19" t="inlineStr"/>
+      <c r="R35" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P35" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q35" s="17" t="inlineStr">
-        <is>
-          <t>2 sources: ean-search.org, ecoperation.com</t>
-        </is>
-      </c>
-      <c r="R35" s="17" t="inlineStr">
-        <is>
-          <t>considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S35" s="30" t="inlineStr">
+      <c r="S35" s="17" t="inlineStr">
         <is>
           <t>2 sources: ean-search.org, ecoperation.com</t>
         </is>
@@ -4594,42 +4182,34 @@
         </is>
       </c>
       <c r="K36" s="4" t="n">
-        <v>15</v>
+        <v>22.5</v>
       </c>
       <c r="L36" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="M36" s="7" t="inlineStr">
+      <c r="M36" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="O36" s="7" t="inlineStr">
         <is>
           <t>https://i.ebayimg.com/images/g/CrUAAeSwkOdqeaRR/s-l400.jpg</t>
         </is>
       </c>
-      <c r="N36" s="7" t="inlineStr">
+      <c r="P36" s="7" t="inlineStr">
         <is>
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="O36" s="19" t="inlineStr">
+      <c r="Q36" s="19" t="inlineStr"/>
+      <c r="R36" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P36" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q36" s="17" t="inlineStr">
-        <is>
-          <t>2 sources: ean-search.org, ebay.de</t>
-        </is>
-      </c>
-      <c r="R36" s="17" t="inlineStr">
-        <is>
-          <t>water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S36" s="30" t="inlineStr">
+      <c r="S36" s="17" t="inlineStr">
         <is>
           <t>2 sources: ean-search.org, ebay.de</t>
         </is>
@@ -4689,40 +4269,28 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr"/>
+      <c r="N37" s="4" t="inlineStr"/>
+      <c r="O37" s="7" t="inlineStr">
+        <is>
           <t>https://i.ebayimg.com/images/g/0e0AAOSweaplqO77/s-l400.jpg</t>
         </is>
       </c>
-      <c r="M37" s="7" t="inlineStr">
-        <is>
-          <t>https://i.ebayimg.com/images/g/0e0AAOSweaplqO77/s-l400.jpg</t>
-        </is>
-      </c>
-      <c r="N37" s="7" t="inlineStr">
+      <c r="P37" s="7" t="inlineStr">
         <is>
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="O37" s="19" t="inlineStr">
+      <c r="Q37" s="19" t="inlineStr"/>
+      <c r="R37" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P37" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q37" s="17" t="inlineStr">
-        <is>
-          <t>2 sources: barcodelookup, ean-search.org</t>
-        </is>
-      </c>
-      <c r="R37" s="17" t="inlineStr">
-        <is>
-          <t>filters, spa-hot-tub, cleaning, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S37" s="30" t="inlineStr">
+      <c r="S37" s="17" t="inlineStr">
         <is>
           <t>2 sources: barcodelookup, ean-search.org</t>
         </is>
@@ -4737,7 +4305,7 @@
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>WAYS - Pool maintenance - Scrub brush - 15 x 9 x 8 cm - Handy scrub</t>
+          <t>WAYS - Pool Maintenance - Scrub Brush - 15 x 9 x 8 cm - Handy scrub</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -4776,40 +4344,32 @@
         </is>
       </c>
       <c r="K38" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L38" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="M38" s="11" t="n">
+      <c r="M38" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="N38" s="11" t="inlineStr">
+      <c r="N38" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="O38" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="P38" s="11" t="inlineStr">
         <is>
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="O38" s="19" t="inlineStr">
+      <c r="Q38" s="19" t="inlineStr"/>
+      <c r="R38" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P38" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q38" s="17" t="inlineStr">
-        <is>
-          <t>1 source: ean-search.org</t>
-        </is>
-      </c>
-      <c r="R38" s="17" t="inlineStr">
-        <is>
-          <t>pool, cleaning, add-on, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S38" s="30" t="inlineStr">
+      <c r="S38" s="17" t="inlineStr">
         <is>
           <t>1 source: ean-search.org</t>
         </is>
@@ -4824,7 +4384,7 @@
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>Headrest pillow for INTEX inflatable SPA 28506</t>
+          <t>Headrest Pillow for INTEX Inflatable SPA 28506</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -4863,42 +4423,34 @@
         </is>
       </c>
       <c r="K39" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="M39" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="L39" s="4" t="n">
+      <c r="N39" s="4" t="n">
         <v>0.22</v>
       </c>
-      <c r="M39" s="7" t="inlineStr">
+      <c r="O39" s="7" t="inlineStr">
         <is>
           <t>https://content2.rozetka.com.ua/goods/images/big/570260745.jpg</t>
         </is>
       </c>
-      <c r="N39" s="7" t="inlineStr">
+      <c r="P39" s="7" t="inlineStr">
         <is>
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="O39" s="19" t="inlineStr">
+      <c r="Q39" s="19" t="inlineStr"/>
+      <c r="R39" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P39" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q39" s="17" t="inlineStr">
-        <is>
-          <t>3 sources: rozetka.pl, barcodelookup.com, ean-search.org</t>
-        </is>
-      </c>
-      <c r="R39" s="17" t="inlineStr">
-        <is>
-          <t>spa-hot-tub, accessories, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S39" s="30" t="inlineStr">
+      <c r="S39" s="17" t="inlineStr">
         <is>
           <t>3 sources: rozetka.pl, barcodelookup.com, ean-search.org</t>
         </is>
@@ -4913,7 +4465,7 @@
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>Active oxygen test kit x1</t>
+          <t>Active Oxygen Test Kit x1</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -4958,40 +4510,28 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr"/>
+      <c r="N40" s="4" t="inlineStr"/>
+      <c r="O40" s="7" t="inlineStr">
+        <is>
           <t>https://media.carrefour.fr/medias/8f94161f683b4e589024a5b5ebaa6873/p_200x200/cad3db6a00ef414a804b9226119bae96_image.jpg</t>
         </is>
       </c>
-      <c r="M40" s="7" t="inlineStr">
-        <is>
-          <t>https://media.carrefour.fr/medias/8f94161f683b4e589024a5b5ebaa6873/p_200x200/cad3db6a00ef414a804b9226119bae96_image.jpg</t>
-        </is>
-      </c>
-      <c r="N40" s="7" t="inlineStr">
+      <c r="P40" s="7" t="inlineStr">
         <is>
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="O40" s="19" t="inlineStr">
+      <c r="Q40" s="19" t="inlineStr"/>
+      <c r="R40" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P40" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q40" s="17" t="inlineStr">
-        <is>
-          <t>3 sources: barcodelookup.com, carrefour.fr, ean-search.org</t>
-        </is>
-      </c>
-      <c r="R40" s="17" t="inlineStr">
-        <is>
-          <t>water-treatment, test-measure, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S40" s="30" t="inlineStr">
+      <c r="S40" s="17" t="inlineStr">
         <is>
           <t>3 sources: barcodelookup.com, carrefour.fr, ean-search.org</t>
         </is>
@@ -5006,7 +4546,7 @@
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>Darlly filter cartridge pack of 2 filter cartridges compatible with Intex type H</t>
+          <t>Darlly Filter Cartridge Pack of 2 Filter Cartridges Compatible with Intex Type H</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -5050,37 +4590,21 @@
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="M41" s="11" t="inlineStr">
+      <c r="M41" s="4" t="inlineStr"/>
+      <c r="N41" s="4" t="inlineStr"/>
+      <c r="O41" s="11" t="inlineStr"/>
+      <c r="P41" s="11" t="inlineStr">
         <is>
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="N41" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="O41" s="19" t="inlineStr">
+      <c r="Q41" s="19" t="inlineStr"/>
+      <c r="R41" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P41" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q41" s="17" t="inlineStr">
-        <is>
-          <t>1 source: ean-search.org</t>
-        </is>
-      </c>
-      <c r="R41" s="17" t="inlineStr">
-        <is>
-          <t>filters, repeat-purchase, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S41" s="30" t="inlineStr">
+      <c r="S41" s="17" t="inlineStr">
         <is>
           <t>1 source: ean-search.org</t>
         </is>
@@ -5095,7 +4619,7 @@
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>Spa replacement filter Ø 22 cm x 27 cm SC713, C-8465 - Darlly</t>
+          <t>Spa Replacement Filter Ø 22 cm x 27 cm SC713, C-8465 - Darlly</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -5133,43 +4657,37 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="K42" s="4" t="n">
-        <v>27</v>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>https://images.barcodelookup.com/142259/1422591231-1.jpg</t>
+        </is>
       </c>
       <c r="L42" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="M42" s="7" t="inlineStr">
+      <c r="M42" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="N42" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="O42" s="7" t="inlineStr">
         <is>
           <t>https://images.barcodelookup.com/142259/1422591231-1.jpg</t>
         </is>
       </c>
-      <c r="N42" s="7" t="inlineStr">
+      <c r="P42" s="7" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="O42" s="19" t="inlineStr">
+      <c r="Q42" s="19" t="inlineStr"/>
+      <c r="R42" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P42" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q42" s="17" t="inlineStr">
-        <is>
-          <t>2 sources: barcodelookup.com, ean-search.org</t>
-        </is>
-      </c>
-      <c r="R42" s="17" t="inlineStr">
-        <is>
-          <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S42" s="30" t="inlineStr">
+      <c r="S42" s="17" t="inlineStr">
         <is>
           <t>2 sources: barcodelookup.com, ean-search.org</t>
         </is>
@@ -5184,7 +4702,7 @@
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>1 x 1 kg BAYZID® multitabs 20g 5in1 for pools - Höfer Chemie</t>
+          <t>1 x 1 kg BAYZID® 20g 5-in-1 Multitabs for Pools - HÖFER CHEMIE</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -5222,43 +4740,37 @@
           <t>pool, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="K43" s="4" t="n">
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>https://images.barcodelookup.com/17422/174228560-1.jpg</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>Verified — Barcode Lookup (barcode)</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr"/>
+      <c r="N43" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L43" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M43" s="7" t="inlineStr">
+      <c r="O43" s="7" t="inlineStr">
         <is>
           <t>https://images.barcodelookup.com/17422/174228560-1.jpg</t>
         </is>
       </c>
-      <c r="N43" s="7" t="inlineStr">
+      <c r="P43" s="7" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="O43" s="19" t="inlineStr">
+      <c r="Q43" s="19" t="inlineStr"/>
+      <c r="R43" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P43" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q43" s="17" t="inlineStr">
-        <is>
-          <t>2 sources: barcodelookup.com, ean-search.org</t>
-        </is>
-      </c>
-      <c r="R43" s="17" t="inlineStr">
-        <is>
-          <t>pool, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S43" s="30" t="inlineStr">
+      <c r="S43" s="17" t="inlineStr">
         <is>
           <t>2 sources: barcodelookup.com, ean-search.org</t>
         </is>
@@ -5311,49 +4823,43 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="K44" s="4" t="n">
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.north-spa.de/wp-content/uploads/2023/02/Produktbild-1-Bayrol-Randfix-07-l-4008367154134.jpg</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="inlineStr"/>
+      <c r="N44" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="L44" s="4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M44" s="7" t="inlineStr">
+      <c r="O44" s="7" t="inlineStr">
         <is>
           <t>https://www.north-spa.de/wp-content/uploads/2023/02/Produktbild-1-Bayrol-Randfix-07-l-4008367154134.jpg</t>
         </is>
       </c>
-      <c r="N44" s="7" t="inlineStr">
+      <c r="P44" s="7" t="inlineStr">
         <is>
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="O44" s="19" t="inlineStr">
+      <c r="Q44" s="19" t="inlineStr"/>
+      <c r="R44" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P44" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q44" s="17" t="inlineStr">
+      <c r="S44" s="17" t="inlineStr">
         <is>
           <t>2 sources: ean-search.org, north-spa.de</t>
         </is>
       </c>
-      <c r="R44" s="17" t="inlineStr">
-        <is>
-          <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="S44" s="30" t="inlineStr">
-        <is>
-          <t>2 sources: ean-search.org, north-spa.de</t>
-        </is>
-      </c>
     </row>
-    <row r="45" ht="34" customHeight="1">
+    <row r="45" ht="20" customHeight="1">
       <c r="A45" s="9" t="inlineStr"/>
       <c r="B45" s="10" t="inlineStr">
         <is>
@@ -5390,126 +4896,116 @@
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="M45" s="11" t="inlineStr">
+      <c r="M45" s="4" t="inlineStr"/>
+      <c r="N45" s="4" t="inlineStr"/>
+      <c r="O45" s="11" t="inlineStr"/>
+      <c r="P45" s="11" t="inlineStr">
         <is>
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="N45" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="O45" s="19" t="inlineStr">
+      <c r="Q45" s="19" t="inlineStr"/>
+      <c r="R45" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="P45" s="8" t="inlineStr">
-        <is>
-          <t>N/A (not edible)</t>
-        </is>
-      </c>
-      <c r="Q45" s="17" t="inlineStr"/>
-      <c r="R45" s="17" t="inlineStr"/>
-      <c r="S45" s="30" t="inlineStr"/>
+      <c r="S45" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q45"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId91"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId89"/>
 </worksheet>
 </file>
 
@@ -5752,17 +5248,17 @@
           <t>A cartridge filter for hot tubs and swim spas, measuring 26.0 cm outer diameter, 13.0 cm bottom part, and 3.8 cm inner thread. Compatible with Darlly SC779 and 40372 codes, it captures dirt, grease, and fine particles to keep water clean.</t>
         </is>
       </c>
-      <c r="D2" s="30" t="inlineStr">
+      <c r="D2" s="22" t="inlineStr">
         <is>
           <t>Rising Dragon</t>
         </is>
       </c>
-      <c r="E2" s="30" t="inlineStr">
+      <c r="E2" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F2" s="30" t="inlineStr">
+      <c r="F2" s="22" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5772,71 +5268,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H2" s="30" t="inlineStr">
+      <c r="H2" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I2" s="30" t="inlineStr">
+      <c r="I2" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J2" s="30" t="inlineStr">
+      <c r="J2" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K2" s="30" t="inlineStr">
+      <c r="K2" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L2" s="30" t="inlineStr">
+      <c r="L2" s="22" t="inlineStr">
         <is>
           <t>RIS-FIL-2406</t>
         </is>
       </c>
-      <c r="M2" s="31" t="inlineStr">
+      <c r="M2" s="23" t="inlineStr">
         <is>
           <t>700175992406</t>
         </is>
       </c>
-      <c r="N2" s="32" t="inlineStr"/>
-      <c r="O2" s="32" t="inlineStr"/>
-      <c r="P2" s="32" t="inlineStr"/>
-      <c r="Q2" s="30" t="inlineStr">
+      <c r="N2" s="24" t="inlineStr"/>
+      <c r="O2" s="24" t="inlineStr"/>
+      <c r="P2" s="24" t="inlineStr"/>
+      <c r="Q2" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R2" s="30" t="inlineStr">
+      <c r="R2" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S2" s="30" t="inlineStr">
+      <c r="S2" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T2" s="30" t="inlineStr">
+      <c r="T2" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U2" s="30" t="inlineStr"/>
-      <c r="V2" s="30" t="inlineStr">
+      <c r="U2" s="22" t="inlineStr"/>
+      <c r="V2" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W2" s="30" t="inlineStr">
+      <c r="W2" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X2" s="30" t="inlineStr">
+      <c r="X2" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5846,7 +5342,7 @@
           <t>https://www.spa-components.com/user/shop/big/1473-1_filter-cartridge-sc779-rising-dragon-plastics--eago-whirlpools.jpg?ff=1&amp;x=1024&amp;y=768&amp;q=85&amp;ts=6720c4a0&amp;sg=161563f2</t>
         </is>
       </c>
-      <c r="Z2" s="30" t="inlineStr">
+      <c r="Z2" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5856,7 +5352,7 @@
           <t>Filter Cartridge SC779 - Rising Dragon Plastics, EAGO Whirlpools - Spa Components</t>
         </is>
       </c>
-      <c r="AB2" s="30" t="inlineStr">
+      <c r="AB2" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5868,10 +5364,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF2" s="30" t="inlineStr"/>
-      <c r="AG2" s="30" t="inlineStr"/>
-      <c r="AH2" s="30" t="inlineStr"/>
-      <c r="AI2" s="30" t="inlineStr"/>
+      <c r="AF2" s="22" t="inlineStr"/>
+      <c r="AG2" s="22" t="inlineStr"/>
+      <c r="AH2" s="22" t="inlineStr"/>
+      <c r="AI2" s="22" t="inlineStr"/>
     </row>
     <row r="3" ht="62" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
@@ -5889,13 +5385,13 @@
           <t>A twin pack of Size II replacement filter cartridges measuring 10.6 x 13.6 cm, designed for compatible pool and spa filtration systems. The fine lamellar structure delivers thorough water cleaning and the cartridges are easy to rinse clean.</t>
         </is>
       </c>
-      <c r="D3" s="30" t="inlineStr"/>
-      <c r="E3" s="30" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr"/>
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F3" s="30" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5905,71 +5401,71 @@
           <t>filters, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H3" s="30" t="inlineStr">
+      <c r="H3" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I3" s="30" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J3" s="30" t="inlineStr">
+      <c r="J3" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K3" s="30" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L3" s="30" t="inlineStr">
+      <c r="L3" s="22" t="inlineStr">
         <is>
           <t>GEN-FIL-3615</t>
         </is>
       </c>
-      <c r="M3" s="31" t="inlineStr">
+      <c r="M3" s="23" t="inlineStr">
         <is>
           <t>6941607353615</t>
         </is>
       </c>
-      <c r="N3" s="32" t="inlineStr"/>
-      <c r="O3" s="32" t="inlineStr"/>
-      <c r="P3" s="32" t="inlineStr"/>
-      <c r="Q3" s="30" t="inlineStr">
+      <c r="N3" s="24" t="inlineStr"/>
+      <c r="O3" s="24" t="inlineStr"/>
+      <c r="P3" s="24" t="inlineStr"/>
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R3" s="30" t="inlineStr">
+      <c r="R3" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S3" s="30" t="inlineStr">
+      <c r="S3" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T3" s="30" t="inlineStr">
+      <c r="T3" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U3" s="30" t="inlineStr"/>
-      <c r="V3" s="30" t="inlineStr">
+      <c r="U3" s="22" t="inlineStr"/>
+      <c r="V3" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W3" s="30" t="inlineStr">
+      <c r="W3" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X3" s="30" t="inlineStr">
+      <c r="X3" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5979,7 +5475,7 @@
           <t>https://www.bestwaystore.de/media/c6/f8/ba/1756384660/6941607353615-main-jpg.jpg?ts=1756384660</t>
         </is>
       </c>
-      <c r="Z3" s="30" t="inlineStr">
+      <c r="Z3" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5989,7 +5485,7 @@
           <t>Filter cartridge Size II double pack, 10.6 x 13.6 cm | 58094_26</t>
         </is>
       </c>
-      <c r="AB3" s="30" t="inlineStr">
+      <c r="AB3" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6001,14 +5497,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF3" s="30" t="inlineStr"/>
-      <c r="AG3" s="30" t="inlineStr"/>
-      <c r="AH3" s="30" t="inlineStr">
+      <c r="AF3" s="22" t="inlineStr"/>
+      <c r="AG3" s="22" t="inlineStr"/>
+      <c r="AH3" s="22" t="inlineStr">
         <is>
           <t>10.6cm</t>
         </is>
       </c>
-      <c r="AI3" s="30" t="inlineStr">
+      <c r="AI3" s="22" t="inlineStr">
         <is>
           <t>13.6cm</t>
         </is>
@@ -6030,17 +5526,17 @@
           <t>A single Flowclear Size 3 replacement filter cartridge for compatible Bestway pool filtration systems, featuring a fine lamellar structure that traps deposits and dirt effectively. Easy to clean and straightforward to swap out when routine maintenance is due.</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="22" t="inlineStr">
         <is>
           <t>Bestway</t>
         </is>
       </c>
-      <c r="E4" s="30" t="inlineStr">
+      <c r="E4" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F4" s="30" t="inlineStr">
+      <c r="F4" s="22" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6050,71 +5546,71 @@
           <t>filters, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H4" s="30" t="inlineStr">
+      <c r="H4" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I4" s="30" t="inlineStr">
+      <c r="I4" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J4" s="30" t="inlineStr">
+      <c r="J4" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K4" s="30" t="inlineStr">
+      <c r="K4" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L4" s="30" t="inlineStr">
+      <c r="L4" s="22" t="inlineStr">
         <is>
           <t>BES-FIL-3592</t>
         </is>
       </c>
-      <c r="M4" s="31" t="inlineStr">
+      <c r="M4" s="23" t="inlineStr">
         <is>
           <t>6941607353592</t>
         </is>
       </c>
-      <c r="N4" s="32" t="inlineStr"/>
-      <c r="O4" s="32" t="inlineStr"/>
-      <c r="P4" s="32" t="inlineStr"/>
-      <c r="Q4" s="30" t="inlineStr">
+      <c r="N4" s="24" t="inlineStr"/>
+      <c r="O4" s="24" t="inlineStr"/>
+      <c r="P4" s="24" t="inlineStr"/>
+      <c r="Q4" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R4" s="30" t="inlineStr">
+      <c r="R4" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S4" s="30" t="inlineStr">
+      <c r="S4" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T4" s="30" t="inlineStr">
+      <c r="T4" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U4" s="30" t="inlineStr"/>
-      <c r="V4" s="30" t="inlineStr">
+      <c r="U4" s="22" t="inlineStr"/>
+      <c r="V4" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W4" s="30" t="inlineStr">
+      <c r="W4" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X4" s="30" t="inlineStr">
+      <c r="X4" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6124,7 +5620,7 @@
           <t>https://ap.nice-cdn.com/upload/image/product/large/default/bestway-flowclear-filter-cartridge-size-3-1-item-638140-en.jpg</t>
         </is>
       </c>
-      <c r="Z4" s="30" t="inlineStr">
+      <c r="Z4" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6134,7 +5630,7 @@
           <t>Bestway Flowclear™ Filter Cartridge Size 3, 1 item</t>
         </is>
       </c>
-      <c r="AB4" s="30" t="inlineStr">
+      <c r="AB4" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6146,10 +5642,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF4" s="30" t="inlineStr"/>
-      <c r="AG4" s="30" t="inlineStr"/>
-      <c r="AH4" s="30" t="inlineStr"/>
-      <c r="AI4" s="30" t="inlineStr"/>
+      <c r="AF4" s="22" t="inlineStr"/>
+      <c r="AG4" s="22" t="inlineStr"/>
+      <c r="AH4" s="22" t="inlineStr"/>
+      <c r="AI4" s="22" t="inlineStr"/>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="17" t="inlineStr">
@@ -6167,17 +5663,17 @@
           <t>A two-pack of compatible hot tub and spa cartridge filters corresponding to Unicel C-4335, Pleatco PRB35-IN, and Filbur FC-2385 references. A handy spare-pair to keep on hand so your tub is never without a fresh filter.</t>
         </is>
       </c>
-      <c r="D5" s="30" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E5" s="30" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F5" s="30" t="inlineStr">
+      <c r="F5" s="22" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6187,71 +5683,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H5" s="30" t="inlineStr">
+      <c r="H5" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I5" s="30" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J5" s="30" t="inlineStr">
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K5" s="30" t="inlineStr">
+      <c r="K5" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L5" s="30" t="inlineStr">
+      <c r="L5" s="22" t="inlineStr">
         <is>
           <t>DAR-FIL-1669</t>
         </is>
       </c>
-      <c r="M5" s="31" t="inlineStr">
+      <c r="M5" s="23" t="inlineStr">
         <is>
           <t>700175991669</t>
         </is>
       </c>
-      <c r="N5" s="32" t="inlineStr"/>
-      <c r="O5" s="32" t="inlineStr"/>
-      <c r="P5" s="32" t="inlineStr"/>
-      <c r="Q5" s="30" t="inlineStr">
+      <c r="N5" s="24" t="inlineStr"/>
+      <c r="O5" s="24" t="inlineStr"/>
+      <c r="P5" s="24" t="inlineStr"/>
+      <c r="Q5" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R5" s="30" t="inlineStr">
+      <c r="R5" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S5" s="30" t="inlineStr">
+      <c r="S5" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T5" s="30" t="inlineStr">
+      <c r="T5" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U5" s="30" t="inlineStr"/>
-      <c r="V5" s="30" t="inlineStr">
+      <c r="U5" s="22" t="inlineStr"/>
+      <c r="V5" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W5" s="30" t="inlineStr">
+      <c r="W5" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X5" s="30" t="inlineStr">
+      <c r="X5" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6261,7 +5757,7 @@
           <t>https://images.barcodelookup.com/29361/293617958-1.jpg</t>
         </is>
       </c>
-      <c r="Z5" s="30" t="inlineStr">
+      <c r="Z5" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6271,7 +5767,7 @@
           <t>Darlly Hot Tub Spa Filter SC705 40353 Compatible with Unicel C-4335 PRB35-IN Filbur FC-2385 2 Pack</t>
         </is>
       </c>
-      <c r="AB5" s="30" t="inlineStr">
+      <c r="AB5" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6283,10 +5779,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF5" s="30" t="inlineStr"/>
-      <c r="AG5" s="30" t="inlineStr"/>
-      <c r="AH5" s="30" t="inlineStr"/>
-      <c r="AI5" s="30" t="inlineStr"/>
+      <c r="AF5" s="22" t="inlineStr"/>
+      <c r="AG5" s="22" t="inlineStr"/>
+      <c r="AH5" s="22" t="inlineStr"/>
+      <c r="AI5" s="22" t="inlineStr"/>
     </row>
     <row r="6" ht="62" customHeight="1">
       <c r="A6" s="17" t="inlineStr">
@@ -6304,13 +5800,13 @@
           <t>A single Size IV replacement filter cartridge measuring 14.2 x 25.4 cm, compatible with Bestway filter pump 58391 (9,463 l/h). Its deep-fold, fine-structure media delivers thorough water cleaning and can be rinsed clean with minimal effort.</t>
         </is>
       </c>
-      <c r="D6" s="30" t="inlineStr"/>
-      <c r="E6" s="30" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr"/>
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F6" s="30" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6320,71 +5816,71 @@
           <t>filters, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H6" s="30" t="inlineStr">
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I6" s="30" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J6" s="30" t="inlineStr">
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K6" s="30" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L6" s="30" t="inlineStr">
+      <c r="L6" s="22" t="inlineStr">
         <is>
           <t>GEN-FIL-3622</t>
         </is>
       </c>
-      <c r="M6" s="31" t="inlineStr">
+      <c r="M6" s="23" t="inlineStr">
         <is>
           <t>6941607353622</t>
         </is>
       </c>
-      <c r="N6" s="32" t="inlineStr"/>
-      <c r="O6" s="32" t="inlineStr"/>
-      <c r="P6" s="32" t="inlineStr"/>
-      <c r="Q6" s="30" t="inlineStr">
+      <c r="N6" s="24" t="inlineStr"/>
+      <c r="O6" s="24" t="inlineStr"/>
+      <c r="P6" s="24" t="inlineStr"/>
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R6" s="30" t="inlineStr">
+      <c r="R6" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S6" s="30" t="inlineStr">
+      <c r="S6" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T6" s="30" t="inlineStr">
+      <c r="T6" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U6" s="30" t="inlineStr"/>
-      <c r="V6" s="30" t="inlineStr">
+      <c r="U6" s="22" t="inlineStr"/>
+      <c r="V6" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W6" s="30" t="inlineStr">
+      <c r="W6" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X6" s="30" t="inlineStr">
+      <c r="X6" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6394,7 +5890,7 @@
           <t>https://www.bestwaystore.de/media/53/6c/e9/1756384676/6941607353622-main-jpg.jpg?ts=1756384676</t>
         </is>
       </c>
-      <c r="Z6" s="30" t="inlineStr">
+      <c r="Z6" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6404,7 +5900,7 @@
           <t>Filter cartridge Size IV 14.2 x 25.4 cm | 58095_26</t>
         </is>
       </c>
-      <c r="AB6" s="30" t="inlineStr">
+      <c r="AB6" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6416,14 +5912,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF6" s="30" t="inlineStr"/>
-      <c r="AG6" s="30" t="inlineStr"/>
-      <c r="AH6" s="30" t="inlineStr">
+      <c r="AF6" s="22" t="inlineStr"/>
+      <c r="AG6" s="22" t="inlineStr"/>
+      <c r="AH6" s="22" t="inlineStr">
         <is>
           <t>14.2cm</t>
         </is>
       </c>
-      <c r="AI6" s="30" t="inlineStr">
+      <c r="AI6" s="22" t="inlineStr">
         <is>
           <t>25.4cm</t>
         </is>
@@ -6445,17 +5941,17 @@
           <t>A pair of Darlly spa filter cartridges in the SC726 reference, also cross-referenced as Unicel C-4401 and Pleatco PRB17.5SF PR. Buying in pairs means a fresh replacement is always ready when it is time to swap.</t>
         </is>
       </c>
-      <c r="D7" s="30" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E7" s="30" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F7" s="30" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6465,71 +5961,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H7" s="30" t="inlineStr">
+      <c r="H7" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I7" s="30" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J7" s="30" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K7" s="30" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L7" s="30" t="inlineStr">
+      <c r="L7" s="22" t="inlineStr">
         <is>
           <t>DAR-FIL-1874</t>
         </is>
       </c>
-      <c r="M7" s="31" t="inlineStr">
+      <c r="M7" s="23" t="inlineStr">
         <is>
           <t>700175991874</t>
         </is>
       </c>
-      <c r="N7" s="32" t="inlineStr"/>
-      <c r="O7" s="32" t="inlineStr"/>
-      <c r="P7" s="32" t="inlineStr"/>
-      <c r="Q7" s="30" t="inlineStr">
+      <c r="N7" s="24" t="inlineStr"/>
+      <c r="O7" s="24" t="inlineStr"/>
+      <c r="P7" s="24" t="inlineStr"/>
+      <c r="Q7" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R7" s="30" t="inlineStr">
+      <c r="R7" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S7" s="30" t="inlineStr">
+      <c r="S7" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T7" s="30" t="inlineStr">
+      <c r="T7" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U7" s="30" t="inlineStr"/>
-      <c r="V7" s="30" t="inlineStr">
+      <c r="U7" s="22" t="inlineStr"/>
+      <c r="V7" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W7" s="30" t="inlineStr">
+      <c r="W7" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X7" s="30" t="inlineStr">
+      <c r="X7" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6539,7 +6035,7 @@
           <t>https://images.barcodelookup.com/4378/43786454-1.jpg</t>
         </is>
       </c>
-      <c r="Z7" s="30" t="inlineStr">
+      <c r="Z7" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6549,7 +6045,7 @@
           <t>Darlly Spa Filter C-4401, PRB17.5SF PR, SC726 (Pair)</t>
         </is>
       </c>
-      <c r="AB7" s="30" t="inlineStr">
+      <c r="AB7" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6561,12 +6057,12 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF7" s="30" t="inlineStr"/>
-      <c r="AG7" s="30" t="inlineStr"/>
-      <c r="AH7" s="30" t="inlineStr"/>
-      <c r="AI7" s="30" t="inlineStr"/>
+      <c r="AF7" s="22" t="inlineStr"/>
+      <c r="AG7" s="22" t="inlineStr"/>
+      <c r="AH7" s="22" t="inlineStr"/>
+      <c r="AI7" s="22" t="inlineStr"/>
     </row>
-    <row r="8" ht="62" customHeight="1">
+    <row r="8" ht="90" customHeight="1">
       <c r="A8" s="17" t="inlineStr">
         <is>
           <t>hot-tub-filter-unicel-c4950-c-4950-50-spa-cartridge-pleatco-prb501n-darlly-40506</t>
@@ -6579,20 +6075,20 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>A hot tub and spa cartridge filter compatible with Unicel C-4950, Pleatco PRB50-IN, and Darlly 40506, noted as suitable for Arctic and Beachcomber spas among others. The source lists dimensions of approximately 34 cm height and 5 cm width.</t>
-        </is>
-      </c>
-      <c r="D8" s="30" t="inlineStr">
+          <t>A replacement spa filter cartridge compatible with Arctic, Beachcomber, Canadian, Hydropool and Jacuzzi spas, sold under cross-reference codes including Unicel C-4950, Pleatco PRB50-IN and Darlly 40506. It keeps hot tub water clean by trapping debris and particles as water cycles through the filtration system.</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F8" s="30" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6602,81 +6098,81 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H8" s="30" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I8" s="30" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J8" s="30" t="inlineStr">
+      <c r="J8" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K8" s="30" t="inlineStr">
+      <c r="K8" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L8" s="30" t="inlineStr">
+      <c r="L8" s="22" t="inlineStr">
         <is>
           <t>DAR-FIL-1676</t>
         </is>
       </c>
-      <c r="M8" s="31" t="inlineStr">
+      <c r="M8" s="23" t="inlineStr">
         <is>
           <t>700175991676</t>
         </is>
       </c>
-      <c r="N8" s="32" t="inlineStr"/>
-      <c r="O8" s="32" t="inlineStr"/>
-      <c r="P8" s="32" t="inlineStr"/>
-      <c r="Q8" s="30" t="inlineStr">
+      <c r="N8" s="24" t="inlineStr"/>
+      <c r="O8" s="24" t="inlineStr"/>
+      <c r="P8" s="24" t="inlineStr"/>
+      <c r="Q8" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R8" s="30" t="inlineStr">
+      <c r="R8" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S8" s="30" t="inlineStr">
+      <c r="S8" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T8" s="30" t="inlineStr">
+      <c r="T8" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U8" s="30" t="inlineStr"/>
-      <c r="V8" s="30" t="inlineStr">
+      <c r="U8" s="22" t="inlineStr"/>
+      <c r="V8" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W8" s="30" t="inlineStr">
+      <c r="W8" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X8" s="30" t="inlineStr">
+      <c r="X8" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y8" s="17" t="inlineStr">
         <is>
-          <t>https://i.ebayimg.com/images/g/7WgAAOSwQ7haxTU1/s-l1600.jpg</t>
-        </is>
-      </c>
-      <c r="Z8" s="30" t="inlineStr">
+          <t>https://images.barcodelookup.com/4469/44699532-1.jpg</t>
+        </is>
+      </c>
+      <c r="Z8" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6686,7 +6182,7 @@
           <t>Hot Tub Filter Unicel C4950 / C-4950 50' Spa Cartridge Pleatco PRB501N Darlly 40506 for Arctic, Beachcomber, Canadian,…</t>
         </is>
       </c>
-      <c r="AB8" s="30" t="inlineStr">
+      <c r="AB8" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6698,18 +6194,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF8" s="30" t="inlineStr"/>
-      <c r="AG8" s="30" t="inlineStr"/>
-      <c r="AH8" s="30" t="inlineStr">
-        <is>
-          <t>5.0cm</t>
-        </is>
-      </c>
-      <c r="AI8" s="30" t="inlineStr">
-        <is>
-          <t>34.0cm</t>
-        </is>
-      </c>
+      <c r="AF8" s="22" t="inlineStr"/>
+      <c r="AG8" s="22" t="inlineStr"/>
+      <c r="AH8" s="22" t="inlineStr"/>
+      <c r="AI8" s="22" t="inlineStr"/>
     </row>
     <row r="9" ht="76" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
@@ -6719,7 +6207,7 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Calacatta 4-person inflatable spa</t>
+          <t>Calacatta 4-person Inflatable Spa</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
@@ -6727,13 +6215,13 @@
           <t>A square inflatable hot tub for up to four people, with an overall outer diameter of 2.45 m and a structure measuring 1.75 x 1.75 x 0.71 m, built from high-resistance polyester for good rigidity and durability. The packaged weight is 64.92 kg, so you will want a helper on delivery day.</t>
         </is>
       </c>
-      <c r="D9" s="30" t="inlineStr"/>
-      <c r="E9" s="30" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr"/>
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F9" s="30" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -6743,75 +6231,75 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H9" s="30" t="inlineStr">
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I9" s="30" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J9" s="30" t="inlineStr">
+      <c r="J9" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K9" s="30" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L9" s="30" t="inlineStr">
+      <c r="L9" s="22" t="inlineStr">
         <is>
           <t>GEN-SPA-3395</t>
         </is>
       </c>
-      <c r="M9" s="31" t="inlineStr">
+      <c r="M9" s="23" t="inlineStr">
         <is>
           <t>6941057423395</t>
         </is>
       </c>
-      <c r="N9" s="32" t="inlineStr"/>
-      <c r="O9" s="32" t="inlineStr"/>
-      <c r="P9" s="32" t="inlineStr"/>
-      <c r="Q9" s="30" t="inlineStr">
+      <c r="N9" s="24" t="inlineStr"/>
+      <c r="O9" s="24" t="inlineStr"/>
+      <c r="P9" s="24" t="inlineStr"/>
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R9" s="30" t="inlineStr">
+      <c r="R9" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S9" s="30" t="inlineStr">
+      <c r="S9" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T9" s="30" t="inlineStr">
+      <c r="T9" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U9" s="30" t="inlineStr">
+      <c r="U9" s="22" t="inlineStr">
         <is>
           <t>64920</t>
         </is>
       </c>
-      <c r="V9" s="30" t="inlineStr">
+      <c r="V9" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W9" s="30" t="inlineStr">
+      <c r="W9" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X9" s="30" t="inlineStr">
+      <c r="X9" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6821,17 +6309,17 @@
           <t>https://media.intex.fr/7743-large_default_x2/28464ex-spa-gonflable-calacatta-4-places.jpg</t>
         </is>
       </c>
-      <c r="Z9" s="30" t="inlineStr">
+      <c r="Z9" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="AA9" s="17" t="inlineStr">
         <is>
-          <t>Calacatta 4-person inflatable spa</t>
-        </is>
-      </c>
-      <c r="AB9" s="30" t="inlineStr">
+          <t>Calacatta 4-person Inflatable Spa</t>
+        </is>
+      </c>
+      <c r="AB9" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6843,18 +6331,18 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF9" s="30" t="inlineStr"/>
-      <c r="AG9" s="30" t="inlineStr">
+      <c r="AF9" s="22" t="inlineStr"/>
+      <c r="AG9" s="22" t="inlineStr">
         <is>
           <t>175.0cm</t>
         </is>
       </c>
-      <c r="AH9" s="30" t="inlineStr">
+      <c r="AH9" s="22" t="inlineStr">
         <is>
           <t>175.0cm</t>
         </is>
       </c>
-      <c r="AI9" s="30" t="inlineStr">
+      <c r="AI9" s="22" t="inlineStr">
         <is>
           <t>71.0cm</t>
         </is>
@@ -6876,17 +6364,17 @@
           <t>A 3.0 kg tub of hth stabiliser granules for outdoor swimming pools, used to protect chlorine from UV degradation and extend its effectiveness. A reliable way to get more mileage from your sanitiser on sunny days.</t>
         </is>
       </c>
-      <c r="D10" s="30" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E10" s="30" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F10" s="30" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -6896,75 +6384,75 @@
           <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H10" s="30" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I10" s="30" t="inlineStr">
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J10" s="30" t="inlineStr">
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K10" s="30" t="inlineStr">
+      <c r="K10" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L10" s="30" t="inlineStr">
+      <c r="L10" s="22" t="inlineStr">
         <is>
           <t>HTH-CHM-5716</t>
         </is>
       </c>
-      <c r="M10" s="31" t="inlineStr">
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t>3521686005716</t>
         </is>
       </c>
-      <c r="N10" s="32" t="inlineStr"/>
-      <c r="O10" s="32" t="inlineStr"/>
-      <c r="P10" s="32" t="inlineStr"/>
-      <c r="Q10" s="30" t="inlineStr">
+      <c r="N10" s="24" t="inlineStr"/>
+      <c r="O10" s="24" t="inlineStr"/>
+      <c r="P10" s="24" t="inlineStr"/>
+      <c r="Q10" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R10" s="30" t="inlineStr">
+      <c r="R10" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S10" s="30" t="inlineStr">
+      <c r="S10" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T10" s="30" t="inlineStr">
+      <c r="T10" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U10" s="30" t="inlineStr">
+      <c r="U10" s="22" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="V10" s="30" t="inlineStr">
+      <c r="V10" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W10" s="30" t="inlineStr">
+      <c r="W10" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X10" s="30" t="inlineStr">
+      <c r="X10" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6974,7 +6462,7 @@
           <t>https://images.barcodelookup.com/12027/120276177-1.jpg</t>
         </is>
       </c>
-      <c r="Z10" s="30" t="inlineStr">
+      <c r="Z10" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6984,7 +6472,7 @@
           <t>Hth Stabilizer Granulat 3,0 Kg</t>
         </is>
       </c>
-      <c r="AB10" s="30" t="inlineStr">
+      <c r="AB10" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6996,10 +6484,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF10" s="30" t="inlineStr"/>
-      <c r="AG10" s="30" t="inlineStr"/>
-      <c r="AH10" s="30" t="inlineStr"/>
-      <c r="AI10" s="30" t="inlineStr"/>
+      <c r="AF10" s="22" t="inlineStr"/>
+      <c r="AG10" s="22" t="inlineStr"/>
+      <c r="AH10" s="22" t="inlineStr"/>
+      <c r="AI10" s="22" t="inlineStr"/>
     </row>
     <row r="11" ht="62" customHeight="1">
       <c r="A11" s="17" t="inlineStr">
@@ -7017,17 +6505,17 @@
           <t>A 1-litre bottle of hth Spa Antikalk, formulated to prevent and remove limescale in spa and hot tub water. Keeping scale under control helps protect internal components and maintain water clarity.</t>
         </is>
       </c>
-      <c r="D11" s="30" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E11" s="30" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F11" s="30" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -7037,79 +6525,79 @@
           <t>spa-hot-tub, considered-purchase, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H11" s="30" t="inlineStr">
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I11" s="30" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J11" s="30" t="inlineStr">
+      <c r="J11" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K11" s="30" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L11" s="30" t="inlineStr">
+      <c r="L11" s="22" t="inlineStr">
         <is>
           <t>HTH-SPA-0194</t>
         </is>
       </c>
-      <c r="M11" s="31" t="inlineStr">
+      <c r="M11" s="23" t="inlineStr">
         <is>
           <t>3521684700194</t>
         </is>
       </c>
-      <c r="N11" s="32" t="inlineStr"/>
-      <c r="O11" s="32" t="inlineStr"/>
-      <c r="P11" s="32" t="inlineStr"/>
-      <c r="Q11" s="30" t="inlineStr">
+      <c r="N11" s="24" t="inlineStr"/>
+      <c r="O11" s="24" t="inlineStr"/>
+      <c r="P11" s="24" t="inlineStr"/>
+      <c r="Q11" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R11" s="30" t="inlineStr">
+      <c r="R11" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S11" s="30" t="inlineStr">
+      <c r="S11" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T11" s="30" t="inlineStr">
+      <c r="T11" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U11" s="30" t="inlineStr"/>
-      <c r="V11" s="30" t="inlineStr">
+      <c r="U11" s="22" t="inlineStr"/>
+      <c r="V11" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W11" s="30" t="inlineStr">
+      <c r="W11" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X11" s="30" t="inlineStr">
+      <c r="X11" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y11" s="17" t="inlineStr"/>
-      <c r="Z11" s="30" t="inlineStr"/>
+      <c r="Z11" s="22" t="inlineStr"/>
       <c r="AA11" s="17" t="inlineStr"/>
-      <c r="AB11" s="30" t="inlineStr">
+      <c r="AB11" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7121,10 +6609,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF11" s="30" t="inlineStr"/>
-      <c r="AG11" s="30" t="inlineStr"/>
-      <c r="AH11" s="30" t="inlineStr"/>
-      <c r="AI11" s="30" t="inlineStr"/>
+      <c r="AF11" s="22" t="inlineStr"/>
+      <c r="AG11" s="22" t="inlineStr"/>
+      <c r="AH11" s="22" t="inlineStr"/>
+      <c r="AI11" s="22" t="inlineStr"/>
     </row>
     <row r="12" ht="62" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
@@ -7134,7 +6622,7 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>Olive 8-person inflatable spa</t>
+          <t>Olive 8-person Inflatable Spa</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
@@ -7142,13 +6630,13 @@
           <t>A round, olive-green inflatable spa designed to seat up to eight people comfortably, with a maximum water temperature of 40°C. Five accessories are included in the box, so there is plenty to get started with straight away.</t>
         </is>
       </c>
-      <c r="D12" s="30" t="inlineStr"/>
-      <c r="E12" s="30" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr"/>
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F12" s="30" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -7158,71 +6646,71 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H12" s="30" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I12" s="30" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J12" s="30" t="inlineStr">
+      <c r="J12" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K12" s="30" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L12" s="30" t="inlineStr">
+      <c r="L12" s="22" t="inlineStr">
         <is>
           <t>GEN-SPA-9274</t>
         </is>
       </c>
-      <c r="M12" s="31" t="inlineStr">
+      <c r="M12" s="23" t="inlineStr">
         <is>
           <t>6941057429274</t>
         </is>
       </c>
-      <c r="N12" s="32" t="inlineStr"/>
-      <c r="O12" s="32" t="inlineStr"/>
-      <c r="P12" s="32" t="inlineStr"/>
-      <c r="Q12" s="30" t="inlineStr">
+      <c r="N12" s="24" t="inlineStr"/>
+      <c r="O12" s="24" t="inlineStr"/>
+      <c r="P12" s="24" t="inlineStr"/>
+      <c r="Q12" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R12" s="30" t="inlineStr">
+      <c r="R12" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S12" s="30" t="inlineStr">
+      <c r="S12" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T12" s="30" t="inlineStr">
+      <c r="T12" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U12" s="30" t="inlineStr"/>
-      <c r="V12" s="30" t="inlineStr">
+      <c r="U12" s="22" t="inlineStr"/>
+      <c r="V12" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W12" s="30" t="inlineStr">
+      <c r="W12" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X12" s="30" t="inlineStr">
+      <c r="X12" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7232,17 +6720,17 @@
           <t>https://media.intex.fr/11990-large_default_x2/28412np-spa-gonflable-olive-8-places.jpg</t>
         </is>
       </c>
-      <c r="Z12" s="30" t="inlineStr">
+      <c r="Z12" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="AA12" s="17" t="inlineStr">
         <is>
-          <t>Olive 8-person inflatable spa</t>
-        </is>
-      </c>
-      <c r="AB12" s="30" t="inlineStr">
+          <t>Olive 8-person Inflatable Spa</t>
+        </is>
+      </c>
+      <c r="AB12" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7254,10 +6742,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF12" s="30" t="inlineStr"/>
-      <c r="AG12" s="30" t="inlineStr"/>
-      <c r="AH12" s="30" t="inlineStr"/>
-      <c r="AI12" s="30" t="inlineStr"/>
+      <c r="AF12" s="22" t="inlineStr"/>
+      <c r="AG12" s="22" t="inlineStr"/>
+      <c r="AH12" s="22" t="inlineStr"/>
+      <c r="AI12" s="22" t="inlineStr"/>
     </row>
     <row r="13" ht="62" customHeight="1">
       <c r="A13" s="17" t="inlineStr">
@@ -7267,7 +6755,7 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>SC750 Filter replacement filter lamellar filter Arctic Fonteyn Rota Strong Spa - Darlly</t>
+          <t>SC750 Filter Replacement Filter Lamellar Filter Arctic Fonteyn Rota Strong Spa - Darlly</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
@@ -7275,17 +6763,17 @@
           <t>A Darlly SC750 replacement cartridge filter compatible with Arctic, Fonteyn, Rota, and Strong Spa hot tubs, among others. A straightforward like-for-like swap to keep your spa water flowing clean.</t>
         </is>
       </c>
-      <c r="D13" s="30" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E13" s="30" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F13" s="30" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -7295,71 +6783,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H13" s="30" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I13" s="30" t="inlineStr">
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J13" s="30" t="inlineStr">
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K13" s="30" t="inlineStr">
+      <c r="K13" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L13" s="30" t="inlineStr">
+      <c r="L13" s="22" t="inlineStr">
         <is>
           <t>DAR-FIL-2116</t>
         </is>
       </c>
-      <c r="M13" s="31" t="inlineStr">
+      <c r="M13" s="23" t="inlineStr">
         <is>
           <t>700175992116</t>
         </is>
       </c>
-      <c r="N13" s="32" t="inlineStr"/>
-      <c r="O13" s="32" t="inlineStr"/>
-      <c r="P13" s="32" t="inlineStr"/>
-      <c r="Q13" s="30" t="inlineStr">
+      <c r="N13" s="24" t="inlineStr"/>
+      <c r="O13" s="24" t="inlineStr"/>
+      <c r="P13" s="24" t="inlineStr"/>
+      <c r="Q13" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R13" s="30" t="inlineStr">
+      <c r="R13" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S13" s="30" t="inlineStr">
+      <c r="S13" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T13" s="30" t="inlineStr">
+      <c r="T13" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U13" s="30" t="inlineStr"/>
-      <c r="V13" s="30" t="inlineStr">
+      <c r="U13" s="22" t="inlineStr"/>
+      <c r="V13" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W13" s="30" t="inlineStr">
+      <c r="W13" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X13" s="30" t="inlineStr">
+      <c r="X13" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7369,17 +6857,17 @@
           <t>https://images.barcodelookup.com/29338/293384728-1.jpg</t>
         </is>
       </c>
-      <c r="Z13" s="30" t="inlineStr">
+      <c r="Z13" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="AA13" s="17" t="inlineStr">
         <is>
-          <t>SC750 Filter replacement filter lamellar filter Arctic Fonteyn Rota Strong Spa - Darlly</t>
-        </is>
-      </c>
-      <c r="AB13" s="30" t="inlineStr">
+          <t>SC750 Filter Replacement Filter Lamellar Filter Arctic Fonteyn Rota Strong Spa - Darlly</t>
+        </is>
+      </c>
+      <c r="AB13" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7391,10 +6879,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF13" s="30" t="inlineStr"/>
-      <c r="AG13" s="30" t="inlineStr"/>
-      <c r="AH13" s="30" t="inlineStr"/>
-      <c r="AI13" s="30" t="inlineStr"/>
+      <c r="AF13" s="22" t="inlineStr"/>
+      <c r="AG13" s="22" t="inlineStr"/>
+      <c r="AH13" s="22" t="inlineStr"/>
+      <c r="AI13" s="22" t="inlineStr"/>
     </row>
     <row r="14" ht="62" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
@@ -7412,17 +6900,17 @@
           <t>SpaBalancer Clean and Refresh is a spa water treatment product supplied with a sprayer for easy application. It is designed to keep spa water fresh and clean as part of a regular maintenance routine.</t>
         </is>
       </c>
-      <c r="D14" s="30" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>SpaBalancer</t>
         </is>
       </c>
-      <c r="E14" s="30" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F14" s="30" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -7432,79 +6920,79 @@
           <t>cleaning, add-on, multi-source-confirmed, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H14" s="30" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I14" s="30" t="inlineStr">
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J14" s="30" t="inlineStr">
+      <c r="J14" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K14" s="30" t="inlineStr">
+      <c r="K14" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L14" s="30" t="inlineStr">
+      <c r="L14" s="22" t="inlineStr">
         <is>
           <t>SPA-CLN-0117</t>
         </is>
       </c>
-      <c r="M14" s="31" t="inlineStr">
+      <c r="M14" s="23" t="inlineStr">
         <is>
           <t>4260374980117</t>
         </is>
       </c>
-      <c r="N14" s="32" t="inlineStr"/>
-      <c r="O14" s="32" t="inlineStr"/>
-      <c r="P14" s="32" t="inlineStr"/>
-      <c r="Q14" s="30" t="inlineStr">
+      <c r="N14" s="24" t="inlineStr"/>
+      <c r="O14" s="24" t="inlineStr"/>
+      <c r="P14" s="24" t="inlineStr"/>
+      <c r="Q14" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R14" s="30" t="inlineStr">
+      <c r="R14" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S14" s="30" t="inlineStr">
+      <c r="S14" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T14" s="30" t="inlineStr">
+      <c r="T14" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U14" s="30" t="inlineStr"/>
-      <c r="V14" s="30" t="inlineStr">
+      <c r="U14" s="22" t="inlineStr"/>
+      <c r="V14" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W14" s="30" t="inlineStr">
+      <c r="W14" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X14" s="30" t="inlineStr">
+      <c r="X14" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y14" s="17" t="inlineStr"/>
-      <c r="Z14" s="30" t="inlineStr"/>
+      <c r="Z14" s="22" t="inlineStr"/>
       <c r="AA14" s="17" t="inlineStr"/>
-      <c r="AB14" s="30" t="inlineStr">
+      <c r="AB14" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7516,10 +7004,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF14" s="30" t="inlineStr"/>
-      <c r="AG14" s="30" t="inlineStr"/>
-      <c r="AH14" s="30" t="inlineStr"/>
-      <c r="AI14" s="30" t="inlineStr"/>
+      <c r="AF14" s="22" t="inlineStr"/>
+      <c r="AG14" s="22" t="inlineStr"/>
+      <c r="AH14" s="22" t="inlineStr"/>
+      <c r="AI14" s="22" t="inlineStr"/>
     </row>
     <row r="15" ht="62" customHeight="1">
       <c r="A15" s="17" t="inlineStr">
@@ -7537,17 +7025,17 @@
           <t>A pack of 500 DPD 1 reagent tablets for use with the Water-ID photometer, measuring free chlorine levels in pool or spa water. Having a full pack to hand means you will not run short mid-season.</t>
         </is>
       </c>
-      <c r="D15" s="30" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>Water-i.d.</t>
         </is>
       </c>
-      <c r="E15" s="30" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F15" s="30" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -7557,79 +7045,79 @@
           <t>test-measure, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H15" s="30" t="inlineStr">
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I15" s="30" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J15" s="30" t="inlineStr">
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K15" s="30" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L15" s="30" t="inlineStr">
+      <c r="L15" s="22" t="inlineStr">
         <is>
           <t>WAT-TST-1702</t>
         </is>
       </c>
-      <c r="M15" s="31" t="inlineStr">
+      <c r="M15" s="23" t="inlineStr">
         <is>
           <t>4260431461702</t>
         </is>
       </c>
-      <c r="N15" s="32" t="inlineStr"/>
-      <c r="O15" s="32" t="inlineStr"/>
-      <c r="P15" s="32" t="inlineStr"/>
-      <c r="Q15" s="30" t="inlineStr">
+      <c r="N15" s="24" t="inlineStr"/>
+      <c r="O15" s="24" t="inlineStr"/>
+      <c r="P15" s="24" t="inlineStr"/>
+      <c r="Q15" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R15" s="30" t="inlineStr">
+      <c r="R15" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S15" s="30" t="inlineStr">
+      <c r="S15" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T15" s="30" t="inlineStr">
+      <c r="T15" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U15" s="30" t="inlineStr"/>
-      <c r="V15" s="30" t="inlineStr">
+      <c r="U15" s="22" t="inlineStr"/>
+      <c r="V15" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W15" s="30" t="inlineStr">
+      <c r="W15" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X15" s="30" t="inlineStr">
+      <c r="X15" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y15" s="17" t="inlineStr"/>
-      <c r="Z15" s="30" t="inlineStr"/>
+      <c r="Z15" s="22" t="inlineStr"/>
       <c r="AA15" s="17" t="inlineStr"/>
-      <c r="AB15" s="30" t="inlineStr">
+      <c r="AB15" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7641,10 +7129,10 @@
           <t>Pool Accessories</t>
         </is>
       </c>
-      <c r="AF15" s="30" t="inlineStr"/>
-      <c r="AG15" s="30" t="inlineStr"/>
-      <c r="AH15" s="30" t="inlineStr"/>
-      <c r="AI15" s="30" t="inlineStr"/>
+      <c r="AF15" s="22" t="inlineStr"/>
+      <c r="AG15" s="22" t="inlineStr"/>
+      <c r="AH15" s="22" t="inlineStr"/>
+      <c r="AI15" s="22" t="inlineStr"/>
     </row>
     <row r="16" ht="62" customHeight="1">
       <c r="A16" s="17" t="inlineStr">
@@ -7662,17 +7150,17 @@
           <t>A pack of 500 Phenol Red reagent tablets compatible with the Water-ID photometer, used for measuring pH levels in pool or spa water. Accurate pH readings are the foundation of balanced, comfortable water.</t>
         </is>
       </c>
-      <c r="D16" s="30" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>Water-i.d.</t>
         </is>
       </c>
-      <c r="E16" s="30" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F16" s="30" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -7682,79 +7170,79 @@
           <t>test-measure, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H16" s="30" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I16" s="30" t="inlineStr">
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J16" s="30" t="inlineStr">
+      <c r="J16" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K16" s="30" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L16" s="30" t="inlineStr">
+      <c r="L16" s="22" t="inlineStr">
         <is>
           <t>WAT-TST-1801</t>
         </is>
       </c>
-      <c r="M16" s="31" t="inlineStr">
+      <c r="M16" s="23" t="inlineStr">
         <is>
           <t>4260431461801</t>
         </is>
       </c>
-      <c r="N16" s="32" t="inlineStr"/>
-      <c r="O16" s="32" t="inlineStr"/>
-      <c r="P16" s="32" t="inlineStr"/>
-      <c r="Q16" s="30" t="inlineStr">
+      <c r="N16" s="24" t="inlineStr"/>
+      <c r="O16" s="24" t="inlineStr"/>
+      <c r="P16" s="24" t="inlineStr"/>
+      <c r="Q16" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R16" s="30" t="inlineStr">
+      <c r="R16" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S16" s="30" t="inlineStr">
+      <c r="S16" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T16" s="30" t="inlineStr">
+      <c r="T16" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U16" s="30" t="inlineStr"/>
-      <c r="V16" s="30" t="inlineStr">
+      <c r="U16" s="22" t="inlineStr"/>
+      <c r="V16" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W16" s="30" t="inlineStr">
+      <c r="W16" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X16" s="30" t="inlineStr">
+      <c r="X16" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y16" s="17" t="inlineStr"/>
-      <c r="Z16" s="30" t="inlineStr"/>
+      <c r="Z16" s="22" t="inlineStr"/>
       <c r="AA16" s="17" t="inlineStr"/>
-      <c r="AB16" s="30" t="inlineStr">
+      <c r="AB16" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7766,20 +7254,20 @@
           <t>Pool Accessories</t>
         </is>
       </c>
-      <c r="AF16" s="30" t="inlineStr"/>
-      <c r="AG16" s="30" t="inlineStr"/>
-      <c r="AH16" s="30" t="inlineStr"/>
-      <c r="AI16" s="30" t="inlineStr"/>
+      <c r="AF16" s="22" t="inlineStr"/>
+      <c r="AG16" s="22" t="inlineStr"/>
+      <c r="AH16" s="22" t="inlineStr"/>
+      <c r="AI16" s="22" t="inlineStr"/>
     </row>
     <row r="17" ht="62" customHeight="1">
       <c r="A17" s="17" t="inlineStr">
         <is>
-          <t>cristal-poolpflege-cristal-alkaline-rim-cleaner-1-0-l-material-safe-for-liners-p</t>
+          <t>cristal-poolpflege-cristal-alkaline-edge-cleaner-1-0-l-gentle-on-materials-for-l</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>Cristal Poolpflege CRISTAL alkaline rim cleaner 1,0 l, (material-safe, for liners, plastic surfaces</t>
+          <t>Cristal Poolpflege CRISTAL Alkaline Edge Cleaner 1,0 l, (Gentle on Materials, for Liners, Plastic Surfaces</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
@@ -7787,17 +7275,17 @@
           <t>An alkaline edge and surround cleaner in a 1-litre bottle, formulated to be gentle on pool liners, foils, and plastic surfaces. It tackles waterline grime without harming the materials it touches.</t>
         </is>
       </c>
-      <c r="D17" s="30" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>Cristal</t>
         </is>
       </c>
-      <c r="E17" s="30" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F17" s="30" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -7807,71 +7295,71 @@
           <t>pool, water-treatment, cleaning, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H17" s="30" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I17" s="30" t="inlineStr">
+      <c r="I17" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J17" s="30" t="inlineStr">
+      <c r="J17" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K17" s="30" t="inlineStr">
+      <c r="K17" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L17" s="30" t="inlineStr">
+      <c r="L17" s="22" t="inlineStr">
         <is>
           <t>CRI-CHM-5212</t>
         </is>
       </c>
-      <c r="M17" s="31" t="inlineStr">
+      <c r="M17" s="23" t="inlineStr">
         <is>
           <t>4002369155212</t>
         </is>
       </c>
-      <c r="N17" s="32" t="inlineStr"/>
-      <c r="O17" s="32" t="inlineStr"/>
-      <c r="P17" s="32" t="inlineStr"/>
-      <c r="Q17" s="30" t="inlineStr">
+      <c r="N17" s="24" t="inlineStr"/>
+      <c r="O17" s="24" t="inlineStr"/>
+      <c r="P17" s="24" t="inlineStr"/>
+      <c r="Q17" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R17" s="30" t="inlineStr">
+      <c r="R17" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S17" s="30" t="inlineStr">
+      <c r="S17" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T17" s="30" t="inlineStr">
+      <c r="T17" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U17" s="30" t="inlineStr"/>
-      <c r="V17" s="30" t="inlineStr">
+      <c r="U17" s="22" t="inlineStr"/>
+      <c r="V17" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W17" s="30" t="inlineStr">
+      <c r="W17" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X17" s="30" t="inlineStr">
+      <c r="X17" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7881,17 +7369,17 @@
           <t>https://images.barcodelookup.com/21057/210579756-1.jpg</t>
         </is>
       </c>
-      <c r="Z17" s="30" t="inlineStr">
+      <c r="Z17" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="AA17" s="17" t="inlineStr">
         <is>
-          <t>Cristal Poolpflege CRISTAL alkaline rim cleaner 1,0 l, (material-safe, for liners, plastic surfaces</t>
-        </is>
-      </c>
-      <c r="AB17" s="30" t="inlineStr">
+          <t>Cristal Poolpflege CRISTAL Alkaline Edge Cleaner 1,0 l, (Gentle on Materials, for Liners, Plastic Surfaces</t>
+        </is>
+      </c>
+      <c r="AB17" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7903,10 +7391,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF17" s="30" t="inlineStr"/>
-      <c r="AG17" s="30" t="inlineStr"/>
-      <c r="AH17" s="30" t="inlineStr"/>
-      <c r="AI17" s="30" t="inlineStr"/>
+      <c r="AF17" s="22" t="inlineStr"/>
+      <c r="AG17" s="22" t="inlineStr"/>
+      <c r="AH17" s="22" t="inlineStr"/>
+      <c r="AI17" s="22" t="inlineStr"/>
     </row>
     <row r="18" ht="76" customHeight="1">
       <c r="A18" s="17" t="inlineStr">
@@ -7916,7 +7404,7 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>AQUALITY pool cleaner for greasy residues 1L</t>
+          <t>AQUALITY Pool Cleaner for Greasy Residues 1L</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
@@ -7924,17 +7412,17 @@
           <t>A 1-litre pool surface cleaner formulated to remove sunscreen oils and greasy residues from the water surface, designed specifically for warm Mediterranean climates and heavy swimming loads. It keeps the waterline and surface clear without harming pool materials.</t>
         </is>
       </c>
-      <c r="D18" s="30" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E18" s="30" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F18" s="30" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -7944,71 +7432,71 @@
           <t>pool, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H18" s="30" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I18" s="30" t="inlineStr">
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J18" s="30" t="inlineStr">
+      <c r="J18" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K18" s="30" t="inlineStr">
+      <c r="K18" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L18" s="30" t="inlineStr">
+      <c r="L18" s="22" t="inlineStr">
         <is>
           <t>AQU-CLN-0223</t>
         </is>
       </c>
-      <c r="M18" s="31" t="inlineStr">
+      <c r="M18" s="23" t="inlineStr">
         <is>
           <t>5292638000223</t>
         </is>
       </c>
-      <c r="N18" s="32" t="inlineStr"/>
-      <c r="O18" s="32" t="inlineStr"/>
-      <c r="P18" s="32" t="inlineStr"/>
-      <c r="Q18" s="30" t="inlineStr">
+      <c r="N18" s="24" t="inlineStr"/>
+      <c r="O18" s="24" t="inlineStr"/>
+      <c r="P18" s="24" t="inlineStr"/>
+      <c r="Q18" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R18" s="30" t="inlineStr">
+      <c r="R18" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S18" s="30" t="inlineStr">
+      <c r="S18" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T18" s="30" t="inlineStr">
+      <c r="T18" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U18" s="30" t="inlineStr"/>
-      <c r="V18" s="30" t="inlineStr">
+      <c r="U18" s="22" t="inlineStr"/>
+      <c r="V18" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W18" s="30" t="inlineStr">
+      <c r="W18" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X18" s="30" t="inlineStr">
+      <c r="X18" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8018,17 +7506,17 @@
           <t>http://mangas.com.cy/media/products/5292638000223.jpg</t>
         </is>
       </c>
-      <c r="Z18" s="30" t="inlineStr">
+      <c r="Z18" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="AA18" s="17" t="inlineStr">
         <is>
-          <t>AQUALITY pool cleaner for greasy residues 1L</t>
-        </is>
-      </c>
-      <c r="AB18" s="30" t="inlineStr">
+          <t>AQUALITY Pool Cleaner for Greasy Residues 1L</t>
+        </is>
+      </c>
+      <c r="AB18" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8040,10 +7528,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF18" s="30" t="inlineStr"/>
-      <c r="AG18" s="30" t="inlineStr"/>
-      <c r="AH18" s="30" t="inlineStr"/>
-      <c r="AI18" s="30" t="inlineStr"/>
+      <c r="AF18" s="22" t="inlineStr"/>
+      <c r="AG18" s="22" t="inlineStr"/>
+      <c r="AH18" s="22" t="inlineStr"/>
+      <c r="AI18" s="22" t="inlineStr"/>
     </row>
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="17" t="inlineStr">
@@ -8061,17 +7549,17 @@
           <t>California Clear Blue is a super-concentrated, pH-neutral pool clarifier in a 1-litre bottle, using a cationic polymer formula to bind microscopic particles such as dust, pollen, and oils into larger clusters your filter can catch. Non-toxic and biodegradable, it is safe for sand, zeolite, and glass filtration media.</t>
         </is>
       </c>
-      <c r="D19" s="30" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E19" s="30" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F19" s="30" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8081,71 +7569,71 @@
           <t>pool, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H19" s="30" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I19" s="30" t="inlineStr">
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J19" s="30" t="inlineStr">
+      <c r="J19" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K19" s="30" t="inlineStr">
+      <c r="K19" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L19" s="30" t="inlineStr">
+      <c r="L19" s="22" t="inlineStr">
         <is>
           <t>AQU-CHM-0070</t>
         </is>
       </c>
-      <c r="M19" s="31" t="inlineStr">
+      <c r="M19" s="23" t="inlineStr">
         <is>
           <t>5292638000070</t>
         </is>
       </c>
-      <c r="N19" s="32" t="inlineStr"/>
-      <c r="O19" s="32" t="inlineStr"/>
-      <c r="P19" s="32" t="inlineStr"/>
-      <c r="Q19" s="30" t="inlineStr">
+      <c r="N19" s="24" t="inlineStr"/>
+      <c r="O19" s="24" t="inlineStr"/>
+      <c r="P19" s="24" t="inlineStr"/>
+      <c r="Q19" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R19" s="30" t="inlineStr">
+      <c r="R19" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S19" s="30" t="inlineStr">
+      <c r="S19" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T19" s="30" t="inlineStr">
+      <c r="T19" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U19" s="30" t="inlineStr"/>
-      <c r="V19" s="30" t="inlineStr">
+      <c r="U19" s="22" t="inlineStr"/>
+      <c r="V19" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W19" s="30" t="inlineStr">
+      <c r="W19" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X19" s="30" t="inlineStr">
+      <c r="X19" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8155,7 +7643,7 @@
           <t>https://poolservices.cy/storage/2026/05/California-Clear-Blue-1L-Aquality-2.jpeg</t>
         </is>
       </c>
-      <c r="Z19" s="30" t="inlineStr">
+      <c r="Z19" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8165,7 +7653,7 @@
           <t>Pool Clarifier California Clear Blue Aquality 1L</t>
         </is>
       </c>
-      <c r="AB19" s="30" t="inlineStr">
+      <c r="AB19" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8177,10 +7665,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF19" s="30" t="inlineStr"/>
-      <c r="AG19" s="30" t="inlineStr"/>
-      <c r="AH19" s="30" t="inlineStr"/>
-      <c r="AI19" s="30" t="inlineStr"/>
+      <c r="AF19" s="22" t="inlineStr"/>
+      <c r="AG19" s="22" t="inlineStr"/>
+      <c r="AH19" s="22" t="inlineStr"/>
+      <c r="AI19" s="22" t="inlineStr"/>
     </row>
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="17" t="inlineStr">
@@ -8198,17 +7686,17 @@
           <t>A 1-litre tile and vinyl cleaner for pools, designed to clean pool tile surfaces and vinyl liners. It makes light work of the tidying up that keeps a pool looking its best.</t>
         </is>
       </c>
-      <c r="D20" s="30" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E20" s="30" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F20" s="30" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8218,71 +7706,71 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H20" s="30" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I20" s="30" t="inlineStr">
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J20" s="30" t="inlineStr">
+      <c r="J20" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K20" s="30" t="inlineStr">
+      <c r="K20" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L20" s="30" t="inlineStr">
+      <c r="L20" s="22" t="inlineStr">
         <is>
           <t>AQU-CLN-0162</t>
         </is>
       </c>
-      <c r="M20" s="31" t="inlineStr">
+      <c r="M20" s="23" t="inlineStr">
         <is>
           <t>5292638000162</t>
         </is>
       </c>
-      <c r="N20" s="32" t="inlineStr"/>
-      <c r="O20" s="32" t="inlineStr"/>
-      <c r="P20" s="32" t="inlineStr"/>
-      <c r="Q20" s="30" t="inlineStr">
+      <c r="N20" s="24" t="inlineStr"/>
+      <c r="O20" s="24" t="inlineStr"/>
+      <c r="P20" s="24" t="inlineStr"/>
+      <c r="Q20" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R20" s="30" t="inlineStr">
+      <c r="R20" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S20" s="30" t="inlineStr">
+      <c r="S20" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T20" s="30" t="inlineStr">
+      <c r="T20" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U20" s="30" t="inlineStr"/>
-      <c r="V20" s="30" t="inlineStr">
+      <c r="U20" s="22" t="inlineStr"/>
+      <c r="V20" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W20" s="30" t="inlineStr">
+      <c r="W20" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X20" s="30" t="inlineStr">
+      <c r="X20" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8292,7 +7780,7 @@
           <t>http://mangas.com.cy/media/products/5292638000162.jpg</t>
         </is>
       </c>
-      <c r="Z20" s="30" t="inlineStr">
+      <c r="Z20" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8302,7 +7790,7 @@
           <t>AQUALITY Magic tile 4 vinyl cleaner 1L</t>
         </is>
       </c>
-      <c r="AB20" s="30" t="inlineStr">
+      <c r="AB20" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8314,10 +7802,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF20" s="30" t="inlineStr"/>
-      <c r="AG20" s="30" t="inlineStr"/>
-      <c r="AH20" s="30" t="inlineStr"/>
-      <c r="AI20" s="30" t="inlineStr"/>
+      <c r="AF20" s="22" t="inlineStr"/>
+      <c r="AG20" s="22" t="inlineStr"/>
+      <c r="AH20" s="22" t="inlineStr"/>
+      <c r="AI20" s="22" t="inlineStr"/>
     </row>
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="17" t="inlineStr">
@@ -8327,7 +7815,7 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Höfer Chemie GmbH pool care 1 L BAYZID® SPA Poolclear turbidity remover</t>
+          <t>Höfer Chemie GmbH Pool Care 1 L BAYZID® SPA Poolclear Turbidity Remover</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
@@ -8335,17 +7823,17 @@
           <t>A 1-litre spa and pool water clarifier from Bayzid, formulated to clear cloudy or turbid water. A handy bottle to reach for whenever the water loses its sparkle.</t>
         </is>
       </c>
-      <c r="D21" s="30" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E21" s="30" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F21" s="30" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -8355,79 +7843,79 @@
           <t>spa-hot-tub, pool, water-treatment, considered-purchase, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H21" s="30" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I21" s="30" t="inlineStr">
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J21" s="30" t="inlineStr">
+      <c r="J21" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K21" s="30" t="inlineStr">
+      <c r="K21" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L21" s="30" t="inlineStr">
+      <c r="L21" s="22" t="inlineStr">
         <is>
           <t>HFE-SPA-7202</t>
         </is>
       </c>
-      <c r="M21" s="31" t="inlineStr">
+      <c r="M21" s="23" t="inlineStr">
         <is>
           <t>4250463127202</t>
         </is>
       </c>
-      <c r="N21" s="32" t="inlineStr"/>
-      <c r="O21" s="32" t="inlineStr"/>
-      <c r="P21" s="32" t="inlineStr"/>
-      <c r="Q21" s="30" t="inlineStr">
+      <c r="N21" s="24" t="inlineStr"/>
+      <c r="O21" s="24" t="inlineStr"/>
+      <c r="P21" s="24" t="inlineStr"/>
+      <c r="Q21" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R21" s="30" t="inlineStr">
+      <c r="R21" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S21" s="30" t="inlineStr">
+      <c r="S21" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T21" s="30" t="inlineStr">
+      <c r="T21" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U21" s="30" t="inlineStr"/>
-      <c r="V21" s="30" t="inlineStr">
+      <c r="U21" s="22" t="inlineStr"/>
+      <c r="V21" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W21" s="30" t="inlineStr">
+      <c r="W21" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X21" s="30" t="inlineStr">
+      <c r="X21" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y21" s="17" t="inlineStr"/>
-      <c r="Z21" s="30" t="inlineStr"/>
+      <c r="Z21" s="22" t="inlineStr"/>
       <c r="AA21" s="17" t="inlineStr"/>
-      <c r="AB21" s="30" t="inlineStr">
+      <c r="AB21" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8439,10 +7927,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF21" s="30" t="inlineStr"/>
-      <c r="AG21" s="30" t="inlineStr"/>
-      <c r="AH21" s="30" t="inlineStr"/>
-      <c r="AI21" s="30" t="inlineStr"/>
+      <c r="AF21" s="22" t="inlineStr"/>
+      <c r="AG21" s="22" t="inlineStr"/>
+      <c r="AH21" s="22" t="inlineStr"/>
+      <c r="AI21" s="22" t="inlineStr"/>
     </row>
     <row r="22" ht="62" customHeight="1">
       <c r="A22" s="17" t="inlineStr">
@@ -8452,7 +7940,7 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>HÖFER CHEMIE GMBH 1 l hydrogen peroxide 11,9%</t>
+          <t>HÖFER CHEMIE GMBH 1 l Hydrogen Peroxide 11,9%</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
@@ -8460,17 +7948,17 @@
           <t>A 1-litre bottle of hydrogen peroxide at 11.9% concentration, suitable for disinfection and water treatment applications. A straightforward chemical solution that keeps things clean without fuss.</t>
         </is>
       </c>
-      <c r="D22" s="30" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E22" s="30" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F22" s="30" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8480,79 +7968,79 @@
           <t>water-treatment, repeat-purchase, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H22" s="30" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I22" s="30" t="inlineStr">
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J22" s="30" t="inlineStr">
+      <c r="J22" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K22" s="30" t="inlineStr">
+      <c r="K22" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L22" s="30" t="inlineStr">
+      <c r="L22" s="22" t="inlineStr">
         <is>
           <t>HFE-CHM-6788</t>
         </is>
       </c>
-      <c r="M22" s="31" t="inlineStr">
+      <c r="M22" s="23" t="inlineStr">
         <is>
           <t>4250463106788</t>
         </is>
       </c>
-      <c r="N22" s="32" t="inlineStr"/>
-      <c r="O22" s="32" t="inlineStr"/>
-      <c r="P22" s="32" t="inlineStr"/>
-      <c r="Q22" s="30" t="inlineStr">
+      <c r="N22" s="24" t="inlineStr"/>
+      <c r="O22" s="24" t="inlineStr"/>
+      <c r="P22" s="24" t="inlineStr"/>
+      <c r="Q22" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R22" s="30" t="inlineStr">
+      <c r="R22" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S22" s="30" t="inlineStr">
+      <c r="S22" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T22" s="30" t="inlineStr">
+      <c r="T22" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U22" s="30" t="inlineStr"/>
-      <c r="V22" s="30" t="inlineStr">
+      <c r="U22" s="22" t="inlineStr"/>
+      <c r="V22" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W22" s="30" t="inlineStr">
+      <c r="W22" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X22" s="30" t="inlineStr">
+      <c r="X22" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y22" s="17" t="inlineStr"/>
-      <c r="Z22" s="30" t="inlineStr"/>
+      <c r="Z22" s="22" t="inlineStr"/>
       <c r="AA22" s="17" t="inlineStr"/>
-      <c r="AB22" s="30" t="inlineStr">
+      <c r="AB22" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8564,10 +8052,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF22" s="30" t="inlineStr"/>
-      <c r="AG22" s="30" t="inlineStr"/>
-      <c r="AH22" s="30" t="inlineStr"/>
-      <c r="AI22" s="30" t="inlineStr"/>
+      <c r="AF22" s="22" t="inlineStr"/>
+      <c r="AG22" s="22" t="inlineStr"/>
+      <c r="AH22" s="22" t="inlineStr"/>
+      <c r="AI22" s="22" t="inlineStr"/>
     </row>
     <row r="23" ht="62" customHeight="1">
       <c r="A23" s="17" t="inlineStr">
@@ -8577,7 +8065,7 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Astralpool water care Astralpool Chlorine Stabilizer 4,5 kg</t>
+          <t>Astralpool Water Care Astralpool Chlorine Stabilizer 4,5 kg</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
@@ -8585,17 +8073,17 @@
           <t>A 4.5 kg pack of chlorine stabilizer for swimming pools, used to protect chlorine from UV degradation and extend its effectiveness in the water. Steady chemistry for a pool that earns its keep.</t>
         </is>
       </c>
-      <c r="D23" s="30" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>AstralPool</t>
         </is>
       </c>
-      <c r="E23" s="30" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F23" s="30" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8605,83 +8093,83 @@
           <t>water-treatment, repeat-purchase, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H23" s="30" t="inlineStr">
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I23" s="30" t="inlineStr">
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J23" s="30" t="inlineStr">
+      <c r="J23" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K23" s="30" t="inlineStr">
+      <c r="K23" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L23" s="30" t="inlineStr">
+      <c r="L23" s="22" t="inlineStr">
         <is>
           <t>AST-CHM-0626</t>
         </is>
       </c>
-      <c r="M23" s="31" t="inlineStr">
+      <c r="M23" s="23" t="inlineStr">
         <is>
           <t>8432611960626</t>
         </is>
       </c>
-      <c r="N23" s="32" t="inlineStr"/>
-      <c r="O23" s="32" t="inlineStr"/>
-      <c r="P23" s="32" t="inlineStr"/>
-      <c r="Q23" s="30" t="inlineStr">
+      <c r="N23" s="24" t="inlineStr"/>
+      <c r="O23" s="24" t="inlineStr"/>
+      <c r="P23" s="24" t="inlineStr"/>
+      <c r="Q23" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R23" s="30" t="inlineStr">
+      <c r="R23" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S23" s="30" t="inlineStr">
+      <c r="S23" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T23" s="30" t="inlineStr">
+      <c r="T23" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U23" s="30" t="inlineStr">
+      <c r="U23" s="22" t="inlineStr">
         <is>
           <t>4500</t>
         </is>
       </c>
-      <c r="V23" s="30" t="inlineStr">
+      <c r="V23" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W23" s="30" t="inlineStr">
+      <c r="W23" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X23" s="30" t="inlineStr">
+      <c r="X23" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
-      <c r="Z23" s="30" t="inlineStr"/>
+      <c r="Z23" s="22" t="inlineStr"/>
       <c r="AA23" s="17" t="inlineStr"/>
-      <c r="AB23" s="30" t="inlineStr">
+      <c r="AB23" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8693,10 +8181,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF23" s="30" t="inlineStr"/>
-      <c r="AG23" s="30" t="inlineStr"/>
-      <c r="AH23" s="30" t="inlineStr"/>
-      <c r="AI23" s="30" t="inlineStr"/>
+      <c r="AF23" s="22" t="inlineStr"/>
+      <c r="AG23" s="22" t="inlineStr"/>
+      <c r="AH23" s="22" t="inlineStr"/>
+      <c r="AI23" s="22" t="inlineStr"/>
     </row>
     <row r="24" ht="62" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
@@ -8714,17 +8202,17 @@
           <t>UltraShock is a pool and spa shock treatment from SpaBalancer, designed to rapidly oxidise contaminants and restore water clarity. A quick reset for water that needs a little more persuasion.</t>
         </is>
       </c>
-      <c r="D24" s="30" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>SpaBalancer</t>
         </is>
       </c>
-      <c r="E24" s="30" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F24" s="30" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8734,71 +8222,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H24" s="30" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I24" s="30" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J24" s="30" t="inlineStr">
+      <c r="J24" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K24" s="30" t="inlineStr">
+      <c r="K24" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L24" s="30" t="inlineStr">
+      <c r="L24" s="22" t="inlineStr">
         <is>
           <t>SPA-CHM-0025</t>
         </is>
       </c>
-      <c r="M24" s="31" t="inlineStr">
+      <c r="M24" s="23" t="inlineStr">
         <is>
           <t>4260374980025</t>
         </is>
       </c>
-      <c r="N24" s="32" t="inlineStr"/>
-      <c r="O24" s="32" t="inlineStr"/>
-      <c r="P24" s="32" t="inlineStr"/>
-      <c r="Q24" s="30" t="inlineStr">
+      <c r="N24" s="24" t="inlineStr"/>
+      <c r="O24" s="24" t="inlineStr"/>
+      <c r="P24" s="24" t="inlineStr"/>
+      <c r="Q24" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R24" s="30" t="inlineStr">
+      <c r="R24" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S24" s="30" t="inlineStr">
+      <c r="S24" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T24" s="30" t="inlineStr">
+      <c r="T24" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U24" s="30" t="inlineStr"/>
-      <c r="V24" s="30" t="inlineStr">
+      <c r="U24" s="22" t="inlineStr"/>
+      <c r="V24" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W24" s="30" t="inlineStr">
+      <c r="W24" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X24" s="30" t="inlineStr">
+      <c r="X24" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8808,7 +8296,7 @@
           <t>https://images.barcodelookup.com/16704/167043133-1.jpg</t>
         </is>
       </c>
-      <c r="Z24" s="30" t="inlineStr">
+      <c r="Z24" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8818,7 +8306,7 @@
           <t>SpaBalancer UltraShock</t>
         </is>
       </c>
-      <c r="AB24" s="30" t="inlineStr">
+      <c r="AB24" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8830,10 +8318,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF24" s="30" t="inlineStr"/>
-      <c r="AG24" s="30" t="inlineStr"/>
-      <c r="AH24" s="30" t="inlineStr"/>
-      <c r="AI24" s="30" t="inlineStr"/>
+      <c r="AF24" s="22" t="inlineStr"/>
+      <c r="AG24" s="22" t="inlineStr"/>
+      <c r="AH24" s="22" t="inlineStr"/>
+      <c r="AI24" s="22" t="inlineStr"/>
     </row>
     <row r="25" ht="76" customHeight="1">
       <c r="A25" s="17" t="inlineStr">
@@ -8851,13 +8339,13 @@
           <t>A patented foam rubber eraser for cleaning pool surfaces, particularly suited to waterline stains on liner and vitreous ceramic finishes, and it works without detergents or chemicals. Each box contains 3 sponges, which harden when wet to scrub effectively while remaining soft and flexible in use.</t>
         </is>
       </c>
-      <c r="D25" s="30" t="inlineStr"/>
-      <c r="E25" s="30" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr"/>
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F25" s="30" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8867,71 +8355,71 @@
           <t>pool, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H25" s="30" t="inlineStr">
+      <c r="H25" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I25" s="30" t="inlineStr">
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J25" s="30" t="inlineStr">
+      <c r="J25" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K25" s="30" t="inlineStr">
+      <c r="K25" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L25" s="30" t="inlineStr">
+      <c r="L25" s="22" t="inlineStr">
         <is>
           <t>GEN-CLN-0062</t>
         </is>
       </c>
-      <c r="M25" s="31" t="inlineStr">
+      <c r="M25" s="23" t="inlineStr">
         <is>
           <t>3760015880062</t>
         </is>
       </c>
-      <c r="N25" s="32" t="inlineStr"/>
-      <c r="O25" s="32" t="inlineStr"/>
-      <c r="P25" s="32" t="inlineStr"/>
-      <c r="Q25" s="30" t="inlineStr">
+      <c r="N25" s="24" t="inlineStr"/>
+      <c r="O25" s="24" t="inlineStr"/>
+      <c r="P25" s="24" t="inlineStr"/>
+      <c r="Q25" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R25" s="30" t="inlineStr">
+      <c r="R25" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S25" s="30" t="inlineStr">
+      <c r="S25" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T25" s="30" t="inlineStr">
+      <c r="T25" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U25" s="30" t="inlineStr"/>
-      <c r="V25" s="30" t="inlineStr">
+      <c r="U25" s="22" t="inlineStr"/>
+      <c r="V25" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W25" s="30" t="inlineStr">
+      <c r="W25" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X25" s="30" t="inlineStr">
+      <c r="X25" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8941,7 +8429,7 @@
           <t>https://www.piscinarium.com/2908-thickbox_default/pool-gom-magic-rubber-eraser.jpg</t>
         </is>
       </c>
-      <c r="Z25" s="30" t="inlineStr">
+      <c r="Z25" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8951,7 +8439,7 @@
           <t>Pool'Gom Magic Rubber Eraser</t>
         </is>
       </c>
-      <c r="AB25" s="30" t="inlineStr">
+      <c r="AB25" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8963,10 +8451,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF25" s="30" t="inlineStr"/>
-      <c r="AG25" s="30" t="inlineStr"/>
-      <c r="AH25" s="30" t="inlineStr"/>
-      <c r="AI25" s="30" t="inlineStr"/>
+      <c r="AF25" s="22" t="inlineStr"/>
+      <c r="AG25" s="22" t="inlineStr"/>
+      <c r="AH25" s="22" t="inlineStr"/>
+      <c r="AI25" s="22" t="inlineStr"/>
     </row>
     <row r="26" ht="62" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
@@ -8984,13 +8472,13 @@
           <t>Spa Industries Europe appears to be a brand or supplier name rather than a specific product, so no product details can be confirmed. For accurate information, please check the full product listing.</t>
         </is>
       </c>
-      <c r="D26" s="30" t="inlineStr"/>
-      <c r="E26" s="30" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr"/>
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F26" s="30" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -9000,79 +8488,79 @@
           <t>spa-hot-tub, considered-purchase, multi-source-confirmed, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H26" s="30" t="inlineStr">
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I26" s="30" t="inlineStr">
+      <c r="I26" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J26" s="30" t="inlineStr">
+      <c r="J26" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K26" s="30" t="inlineStr">
+      <c r="K26" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L26" s="30" t="inlineStr">
+      <c r="L26" s="22" t="inlineStr">
         <is>
           <t>GEN-SPA-1968</t>
         </is>
       </c>
-      <c r="M26" s="31" t="inlineStr">
+      <c r="M26" s="23" t="inlineStr">
         <is>
           <t>5425021871968</t>
         </is>
       </c>
-      <c r="N26" s="32" t="inlineStr"/>
-      <c r="O26" s="32" t="inlineStr"/>
-      <c r="P26" s="32" t="inlineStr"/>
-      <c r="Q26" s="30" t="inlineStr">
+      <c r="N26" s="24" t="inlineStr"/>
+      <c r="O26" s="24" t="inlineStr"/>
+      <c r="P26" s="24" t="inlineStr"/>
+      <c r="Q26" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R26" s="30" t="inlineStr">
+      <c r="R26" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S26" s="30" t="inlineStr">
+      <c r="S26" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T26" s="30" t="inlineStr">
+      <c r="T26" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U26" s="30" t="inlineStr"/>
-      <c r="V26" s="30" t="inlineStr">
+      <c r="U26" s="22" t="inlineStr"/>
+      <c r="V26" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W26" s="30" t="inlineStr">
+      <c r="W26" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X26" s="30" t="inlineStr">
+      <c r="X26" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y26" s="17" t="inlineStr"/>
-      <c r="Z26" s="30" t="inlineStr"/>
+      <c r="Z26" s="22" t="inlineStr"/>
       <c r="AA26" s="17" t="inlineStr"/>
-      <c r="AB26" s="30" t="inlineStr">
+      <c r="AB26" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9084,10 +8572,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF26" s="30" t="inlineStr"/>
-      <c r="AG26" s="30" t="inlineStr"/>
-      <c r="AH26" s="30" t="inlineStr"/>
-      <c r="AI26" s="30" t="inlineStr"/>
+      <c r="AF26" s="22" t="inlineStr"/>
+      <c r="AG26" s="22" t="inlineStr"/>
+      <c r="AH26" s="22" t="inlineStr"/>
+      <c r="AI26" s="22" t="inlineStr"/>
     </row>
     <row r="27" ht="62" customHeight="1">
       <c r="A27" s="17" t="inlineStr">
@@ -9097,7 +8585,7 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>Höfer Chemie GmbH 1 L sauna cleaner with eucalyptus scent - high-concentrate deep cleaner</t>
+          <t>Höfer Chemie GmbH 1 L Sauna Cleaner with Eucalyptus Scent - High-Concentrate Deep Cleaner</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
@@ -9105,17 +8593,17 @@
           <t>A 1-litre high-concentrate sauna cleaner with eucalyptus fragrance, formulated as a deep-cleaning base cleaner for sauna surfaces. The concentrated formula means a little goes a long way, with a fresh scent to match.</t>
         </is>
       </c>
-      <c r="D27" s="30" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E27" s="30" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F27" s="30" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -9125,79 +8613,79 @@
           <t>cleaning, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H27" s="30" t="inlineStr">
+      <c r="H27" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I27" s="30" t="inlineStr">
+      <c r="I27" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J27" s="30" t="inlineStr">
+      <c r="J27" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K27" s="30" t="inlineStr">
+      <c r="K27" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L27" s="30" t="inlineStr">
+      <c r="L27" s="22" t="inlineStr">
         <is>
           <t>HFE-CLN-7004</t>
         </is>
       </c>
-      <c r="M27" s="31" t="inlineStr">
+      <c r="M27" s="23" t="inlineStr">
         <is>
           <t>4250463127004</t>
         </is>
       </c>
-      <c r="N27" s="32" t="inlineStr"/>
-      <c r="O27" s="32" t="inlineStr"/>
-      <c r="P27" s="32" t="inlineStr"/>
-      <c r="Q27" s="30" t="inlineStr">
+      <c r="N27" s="24" t="inlineStr"/>
+      <c r="O27" s="24" t="inlineStr"/>
+      <c r="P27" s="24" t="inlineStr"/>
+      <c r="Q27" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R27" s="30" t="inlineStr">
+      <c r="R27" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S27" s="30" t="inlineStr">
+      <c r="S27" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T27" s="30" t="inlineStr">
+      <c r="T27" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U27" s="30" t="inlineStr"/>
-      <c r="V27" s="30" t="inlineStr">
+      <c r="U27" s="22" t="inlineStr"/>
+      <c r="V27" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W27" s="30" t="inlineStr">
+      <c r="W27" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X27" s="30" t="inlineStr">
+      <c r="X27" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y27" s="17" t="inlineStr"/>
-      <c r="Z27" s="30" t="inlineStr"/>
+      <c r="Z27" s="22" t="inlineStr"/>
       <c r="AA27" s="17" t="inlineStr"/>
-      <c r="AB27" s="30" t="inlineStr">
+      <c r="AB27" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9209,10 +8697,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF27" s="30" t="inlineStr"/>
-      <c r="AG27" s="30" t="inlineStr"/>
-      <c r="AH27" s="30" t="inlineStr"/>
-      <c r="AI27" s="30" t="inlineStr"/>
+      <c r="AF27" s="22" t="inlineStr"/>
+      <c r="AG27" s="22" t="inlineStr"/>
+      <c r="AH27" s="22" t="inlineStr"/>
+      <c r="AI27" s="22" t="inlineStr"/>
     </row>
     <row r="28" ht="76" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
@@ -9222,7 +8710,7 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>HTH Spa spa cleaner</t>
+          <t>HTH Spa Spa Cleaner</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
@@ -9230,17 +8718,17 @@
           <t>This HTH spa cleaner removes mineral deposits such as limescale and rust, and cleans and polishes aluminium, chrome, stainless steel, and enamel surfaces with a pleasant pine fragrance. It has a high concentration of active ingredients and is recommended for periodic maintenance cleaning.</t>
         </is>
       </c>
-      <c r="D28" s="30" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E28" s="30" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F28" s="30" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -9250,71 +8738,71 @@
           <t>spa-hot-tub, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H28" s="30" t="inlineStr">
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I28" s="30" t="inlineStr">
+      <c r="I28" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J28" s="30" t="inlineStr">
+      <c r="J28" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K28" s="30" t="inlineStr">
+      <c r="K28" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L28" s="30" t="inlineStr">
+      <c r="L28" s="22" t="inlineStr">
         <is>
           <t>HTH-CLN-0178</t>
         </is>
       </c>
-      <c r="M28" s="31" t="inlineStr">
+      <c r="M28" s="23" t="inlineStr">
         <is>
           <t>3521686010178</t>
         </is>
       </c>
-      <c r="N28" s="32" t="inlineStr"/>
-      <c r="O28" s="32" t="inlineStr"/>
-      <c r="P28" s="32" t="inlineStr"/>
-      <c r="Q28" s="30" t="inlineStr">
+      <c r="N28" s="24" t="inlineStr"/>
+      <c r="O28" s="24" t="inlineStr"/>
+      <c r="P28" s="24" t="inlineStr"/>
+      <c r="Q28" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R28" s="30" t="inlineStr">
+      <c r="R28" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S28" s="30" t="inlineStr">
+      <c r="S28" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T28" s="30" t="inlineStr">
+      <c r="T28" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U28" s="30" t="inlineStr"/>
-      <c r="V28" s="30" t="inlineStr">
+      <c r="U28" s="22" t="inlineStr"/>
+      <c r="V28" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W28" s="30" t="inlineStr">
+      <c r="W28" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X28" s="30" t="inlineStr">
+      <c r="X28" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9324,17 +8812,17 @@
           <t>https://www.cdiscount.com/pdt2/0/5/1/1/700x700/auc2009356289051/rw/hth-spa-nettoyant-spa-3521686010178.jpg</t>
         </is>
       </c>
-      <c r="Z28" s="30" t="inlineStr">
+      <c r="Z28" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="AA28" s="17" t="inlineStr">
         <is>
-          <t>HTH Spa spa cleaner</t>
-        </is>
-      </c>
-      <c r="AB28" s="30" t="inlineStr">
+          <t>HTH Spa Spa Cleaner</t>
+        </is>
+      </c>
+      <c r="AB28" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9346,10 +8834,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF28" s="30" t="inlineStr"/>
-      <c r="AG28" s="30" t="inlineStr"/>
-      <c r="AH28" s="30" t="inlineStr"/>
-      <c r="AI28" s="30" t="inlineStr"/>
+      <c r="AF28" s="22" t="inlineStr"/>
+      <c r="AG28" s="22" t="inlineStr"/>
+      <c r="AH28" s="22" t="inlineStr"/>
+      <c r="AI28" s="22" t="inlineStr"/>
     </row>
     <row r="29" ht="62" customHeight="1">
       <c r="A29" s="17" t="inlineStr">
@@ -9367,13 +8855,13 @@
           <t>A 25 kg sack of pure boiling salt (minimum 99.6% NaCl) without an anti-caking agent, meeting EN 973 Type A standard and suitable for use in pool salt electrolysis systems. Not intended for human consumption or animal feed.</t>
         </is>
       </c>
-      <c r="D29" s="30" t="inlineStr"/>
-      <c r="E29" s="30" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr"/>
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F29" s="30" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>Pool salt</t>
         </is>
@@ -9383,75 +8871,75 @@
           <t>pool, salt, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H29" s="30" t="inlineStr">
+      <c r="H29" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I29" s="30" t="inlineStr">
+      <c r="I29" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J29" s="30" t="inlineStr">
+      <c r="J29" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K29" s="30" t="inlineStr">
+      <c r="K29" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L29" s="30" t="inlineStr">
+      <c r="L29" s="22" t="inlineStr">
         <is>
           <t>GEN-SLT-6110</t>
         </is>
       </c>
-      <c r="M29" s="31" t="inlineStr">
+      <c r="M29" s="23" t="inlineStr">
         <is>
           <t>9001880976110</t>
         </is>
       </c>
-      <c r="N29" s="32" t="inlineStr"/>
-      <c r="O29" s="32" t="inlineStr"/>
-      <c r="P29" s="32" t="inlineStr"/>
-      <c r="Q29" s="30" t="inlineStr">
+      <c r="N29" s="24" t="inlineStr"/>
+      <c r="O29" s="24" t="inlineStr"/>
+      <c r="P29" s="24" t="inlineStr"/>
+      <c r="Q29" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R29" s="30" t="inlineStr">
+      <c r="R29" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S29" s="30" t="inlineStr">
+      <c r="S29" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T29" s="30" t="inlineStr">
+      <c r="T29" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U29" s="30" t="inlineStr">
+      <c r="U29" s="22" t="inlineStr">
         <is>
           <t>25000</t>
         </is>
       </c>
-      <c r="V29" s="30" t="inlineStr">
+      <c r="V29" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W29" s="30" t="inlineStr">
+      <c r="W29" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X29" s="30" t="inlineStr">
+      <c r="X29" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9461,7 +8949,7 @@
           <t>http://altruan.com/cdn/shop/files/SalinenPoolSalz25kgSack.png?v=1778597596</t>
         </is>
       </c>
-      <c r="Z29" s="30" t="inlineStr">
+      <c r="Z29" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9471,7 +8959,7 @@
           <t>Saline pool salt pure boiling salt without separating agent | Sack (25 kg)</t>
         </is>
       </c>
-      <c r="AB29" s="30" t="inlineStr">
+      <c r="AB29" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9483,42 +8971,42 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF29" s="30" t="inlineStr">
+      <c r="AF29" s="22" t="inlineStr">
         <is>
           <t>Composition: Siedesalz (min. 99.6% NaCl) 100%; Separant/sodium ferrocyanide 4.0–12.0 mg/kg | Grain: &gt;0.63 mm approx. 20%, 0.2–0.63 mm approx. 75%, &lt;0.2 mm approx. 5% | Moisture: &lt;0.08%</t>
         </is>
       </c>
-      <c r="AG29" s="30" t="inlineStr"/>
-      <c r="AH29" s="30" t="inlineStr"/>
-      <c r="AI29" s="30" t="inlineStr"/>
+      <c r="AG29" s="22" t="inlineStr"/>
+      <c r="AH29" s="22" t="inlineStr"/>
+      <c r="AI29" s="22" t="inlineStr"/>
     </row>
     <row r="30" ht="76" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>aiper-scuba-se-cordless-robotic-pool-cleaner-grey</t>
+          <t>aiper-scuba-s3-cordless-pool-robot-automatic-floor-and-wall-cleaning-wavepathtm-</t>
         </is>
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>AIPER Scuba SE cordless robotic pool cleaner, grey</t>
+          <t>AIPER Scuba S3 Cordless Pool Robot, Automatic Floor and Wall Cleaning, WavePath™ Navigation, High-Performance Filtration and Smart Control</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>A battery-powered robotic pool vacuum cleaner from Aiper, the Scuba SE model in grey, designed to clean pool floors autonomously without a mains connection. Cordless and self-contained, it takes the effort out of keeping the bottom of the pool tidy.</t>
-        </is>
-      </c>
-      <c r="D30" s="30" t="inlineStr">
+          <t>A cordless robotic pool cleaner that scrubs both floors and walls automatically, using WavePath navigation to map and cover the pool efficiently. Built-in high-performance filtration and smart control make it a hands-off solution for keeping pool water clear.</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>Aiper</t>
         </is>
       </c>
-      <c r="E30" s="30" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F30" s="30" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9528,91 +9016,91 @@
           <t>pool, cleaning, robot-cleaner, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H30" s="30" t="inlineStr">
+      <c r="H30" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I30" s="30" t="inlineStr">
+      <c r="I30" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J30" s="30" t="inlineStr">
+      <c r="J30" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K30" s="30" t="inlineStr">
+      <c r="K30" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L30" s="30" t="inlineStr">
+      <c r="L30" s="22" t="inlineStr">
         <is>
           <t>AIP-ROB-4940</t>
         </is>
       </c>
-      <c r="M30" s="31" t="inlineStr">
+      <c r="M30" s="23" t="inlineStr">
         <is>
           <t>6977676344940</t>
         </is>
       </c>
-      <c r="N30" s="32" t="inlineStr"/>
-      <c r="O30" s="32" t="inlineStr"/>
-      <c r="P30" s="32" t="inlineStr"/>
-      <c r="Q30" s="30" t="inlineStr">
+      <c r="N30" s="24" t="inlineStr"/>
+      <c r="O30" s="24" t="inlineStr"/>
+      <c r="P30" s="24" t="inlineStr"/>
+      <c r="Q30" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R30" s="30" t="inlineStr">
+      <c r="R30" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S30" s="30" t="inlineStr">
+      <c r="S30" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T30" s="30" t="inlineStr">
+      <c r="T30" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U30" s="30" t="inlineStr"/>
-      <c r="V30" s="30" t="inlineStr">
+      <c r="U30" s="22" t="inlineStr"/>
+      <c r="V30" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W30" s="30" t="inlineStr">
+      <c r="W30" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X30" s="30" t="inlineStr">
+      <c r="X30" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y30" s="17" t="inlineStr">
         <is>
-          <t>https://www.shoppster.si/medias/?context=bWFzdGVyfGltYWdlc3wyMjk1MXxpbWFnZS9qcGVnfGFEbG1MMmd4TXk4eE16SXdNamMzTlRNek5qVTFNelF8MjA5NWI5YWZjYjFhOTY5ZWJjNGRjM2Q1Y2NmMWVmNzExODIzNTI2NDM1M2I4ZWVlMGI5YWZlNWUyNzUyNTE1Nw</t>
-        </is>
-      </c>
-      <c r="Z30" s="30" t="inlineStr">
+          <t>https://images.barcodelookup.com/176692/1766920801-1.jpg</t>
+        </is>
+      </c>
+      <c r="Z30" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="AA30" s="17" t="inlineStr">
         <is>
-          <t>AIPER Scuba SE cordless robotic pool cleaner, grey</t>
-        </is>
-      </c>
-      <c r="AB30" s="30" t="inlineStr">
+          <t>AIPER Scuba S3 Cordless Pool Robot, Automatic Floor and Wall Cleaning, WavePath™ Navigation, High-Performance Filtration…</t>
+        </is>
+      </c>
+      <c r="AB30" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9624,10 +9112,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF30" s="30" t="inlineStr"/>
-      <c r="AG30" s="30" t="inlineStr"/>
-      <c r="AH30" s="30" t="inlineStr"/>
-      <c r="AI30" s="30" t="inlineStr"/>
+      <c r="AF30" s="22" t="inlineStr"/>
+      <c r="AG30" s="22" t="inlineStr"/>
+      <c r="AH30" s="22" t="inlineStr"/>
+      <c r="AI30" s="22" t="inlineStr"/>
     </row>
     <row r="31" ht="62" customHeight="1">
       <c r="A31" s="17" t="inlineStr">
@@ -9645,13 +9133,13 @@
           <t>The Scuba L1 EU is a pool cleaning device, though no further specific details about its features, dimensions, or mechanism are available from the product name alone. Buyers should refer to the full product listing for specifications.</t>
         </is>
       </c>
-      <c r="D31" s="30" t="inlineStr"/>
-      <c r="E31" s="30" t="inlineStr">
+      <c r="D31" s="22" t="inlineStr"/>
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F31" s="30" t="inlineStr">
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9661,71 +9149,71 @@
           <t>robot-cleaner, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H31" s="30" t="inlineStr">
+      <c r="H31" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I31" s="30" t="inlineStr">
+      <c r="I31" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J31" s="30" t="inlineStr">
+      <c r="J31" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K31" s="30" t="inlineStr">
+      <c r="K31" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L31" s="30" t="inlineStr">
+      <c r="L31" s="22" t="inlineStr">
         <is>
           <t>GEN-ROB-5137</t>
         </is>
       </c>
-      <c r="M31" s="31" t="inlineStr">
+      <c r="M31" s="23" t="inlineStr">
         <is>
           <t>6975140315137</t>
         </is>
       </c>
-      <c r="N31" s="32" t="inlineStr"/>
-      <c r="O31" s="32" t="inlineStr"/>
-      <c r="P31" s="32" t="inlineStr"/>
-      <c r="Q31" s="30" t="inlineStr">
+      <c r="N31" s="24" t="inlineStr"/>
+      <c r="O31" s="24" t="inlineStr"/>
+      <c r="P31" s="24" t="inlineStr"/>
+      <c r="Q31" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R31" s="30" t="inlineStr">
+      <c r="R31" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S31" s="30" t="inlineStr">
+      <c r="S31" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T31" s="30" t="inlineStr">
+      <c r="T31" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U31" s="30" t="inlineStr"/>
-      <c r="V31" s="30" t="inlineStr">
+      <c r="U31" s="22" t="inlineStr"/>
+      <c r="V31" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W31" s="30" t="inlineStr">
+      <c r="W31" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X31" s="30" t="inlineStr">
+      <c r="X31" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9735,7 +9223,7 @@
           <t>https://images.barcodelookup.com/124722/1247228758-1.jpg</t>
         </is>
       </c>
-      <c r="Z31" s="30" t="inlineStr">
+      <c r="Z31" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9745,7 +9233,7 @@
           <t>Scuba L1 - EU</t>
         </is>
       </c>
-      <c r="AB31" s="30" t="inlineStr">
+      <c r="AB31" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9757,10 +9245,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF31" s="30" t="inlineStr"/>
-      <c r="AG31" s="30" t="inlineStr"/>
-      <c r="AH31" s="30" t="inlineStr"/>
-      <c r="AI31" s="30" t="inlineStr"/>
+      <c r="AF31" s="22" t="inlineStr"/>
+      <c r="AG31" s="22" t="inlineStr"/>
+      <c r="AH31" s="22" t="inlineStr"/>
+      <c r="AI31" s="22" t="inlineStr"/>
     </row>
     <row r="32" ht="48" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
@@ -9778,13 +9266,13 @@
           <t>The Gre Pools RBR120 is a 51W robotic pool cleaner designed for automatic pool floor cleaning. A reliable workhorse that takes the scrubbing off your hands.</t>
         </is>
       </c>
-      <c r="D32" s="30" t="inlineStr"/>
-      <c r="E32" s="30" t="inlineStr">
+      <c r="D32" s="22" t="inlineStr"/>
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F32" s="30" t="inlineStr">
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9794,71 +9282,71 @@
           <t>robot-cleaner, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H32" s="30" t="inlineStr">
+      <c r="H32" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I32" s="30" t="inlineStr">
+      <c r="I32" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J32" s="30" t="inlineStr">
+      <c r="J32" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K32" s="30" t="inlineStr">
+      <c r="K32" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L32" s="30" t="inlineStr">
+      <c r="L32" s="22" t="inlineStr">
         <is>
           <t>GEN-ROB-8500</t>
         </is>
       </c>
-      <c r="M32" s="31" t="inlineStr">
+      <c r="M32" s="23" t="inlineStr">
         <is>
           <t>8412081308500</t>
         </is>
       </c>
-      <c r="N32" s="32" t="inlineStr"/>
-      <c r="O32" s="32" t="inlineStr"/>
-      <c r="P32" s="32" t="inlineStr"/>
-      <c r="Q32" s="30" t="inlineStr">
+      <c r="N32" s="24" t="inlineStr"/>
+      <c r="O32" s="24" t="inlineStr"/>
+      <c r="P32" s="24" t="inlineStr"/>
+      <c r="Q32" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R32" s="30" t="inlineStr">
+      <c r="R32" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S32" s="30" t="inlineStr">
+      <c r="S32" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T32" s="30" t="inlineStr">
+      <c r="T32" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U32" s="30" t="inlineStr"/>
-      <c r="V32" s="30" t="inlineStr">
+      <c r="U32" s="22" t="inlineStr"/>
+      <c r="V32" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W32" s="30" t="inlineStr">
+      <c r="W32" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X32" s="30" t="inlineStr">
+      <c r="X32" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9868,7 +9356,7 @@
           <t>https://images.barcodelookup.com/124726/1247268298-1.jpg</t>
         </is>
       </c>
-      <c r="Z32" s="30" t="inlineStr">
+      <c r="Z32" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9878,7 +9366,7 @@
           <t>Battery Powered Robot WET RUNNER XPERT</t>
         </is>
       </c>
-      <c r="AB32" s="30" t="inlineStr">
+      <c r="AB32" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9890,10 +9378,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF32" s="30" t="inlineStr"/>
-      <c r="AG32" s="30" t="inlineStr"/>
-      <c r="AH32" s="30" t="inlineStr"/>
-      <c r="AI32" s="30" t="inlineStr"/>
+      <c r="AF32" s="22" t="inlineStr"/>
+      <c r="AG32" s="22" t="inlineStr"/>
+      <c r="AH32" s="22" t="inlineStr"/>
+      <c r="AI32" s="22" t="inlineStr"/>
     </row>
     <row r="33" ht="90" customHeight="1">
       <c r="A33" s="17" t="inlineStr">
@@ -9911,13 +9399,13 @@
           <t>A twin-size inflatable airbed measuring 99 x 191 x 25 cm, built with Fiber-Tech internal construction using polyester fibres for comfort, vinyl sides and base, and a water-resistant flocked top surface with an anti-deflation valve. It supports a maximum weight of 136 kg and packs down compactly when deflated.</t>
         </is>
       </c>
-      <c r="D33" s="30" t="inlineStr"/>
-      <c r="E33" s="30" t="inlineStr">
+      <c r="D33" s="22" t="inlineStr"/>
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-11</t>
         </is>
       </c>
-      <c r="F33" s="30" t="inlineStr">
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>Airbed / lounger</t>
         </is>
@@ -9927,71 +9415,71 @@
           <t>considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H33" s="30" t="inlineStr">
+      <c r="H33" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I33" s="30" t="inlineStr">
+      <c r="I33" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J33" s="30" t="inlineStr">
+      <c r="J33" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K33" s="30" t="inlineStr">
+      <c r="K33" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L33" s="30" t="inlineStr">
+      <c r="L33" s="22" t="inlineStr">
         <is>
           <t>GEN-BED-2443</t>
         </is>
       </c>
-      <c r="M33" s="31" t="inlineStr">
+      <c r="M33" s="23" t="inlineStr">
         <is>
           <t>6941057412443</t>
         </is>
       </c>
-      <c r="N33" s="32" t="inlineStr"/>
-      <c r="O33" s="32" t="inlineStr"/>
-      <c r="P33" s="32" t="inlineStr"/>
-      <c r="Q33" s="30" t="inlineStr">
+      <c r="N33" s="24" t="inlineStr"/>
+      <c r="O33" s="24" t="inlineStr"/>
+      <c r="P33" s="24" t="inlineStr"/>
+      <c r="Q33" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R33" s="30" t="inlineStr">
+      <c r="R33" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S33" s="30" t="inlineStr">
+      <c r="S33" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T33" s="30" t="inlineStr">
+      <c r="T33" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U33" s="30" t="inlineStr"/>
-      <c r="V33" s="30" t="inlineStr">
+      <c r="U33" s="22" t="inlineStr"/>
+      <c r="V33" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W33" s="30" t="inlineStr">
+      <c r="W33" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X33" s="30" t="inlineStr">
+      <c r="X33" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10001,7 +9489,7 @@
           <t>https://www.ecoperation.com/media/catalog/product/cache/b76cf1d99a7811daa83ba86e6ad91c89/6/4/64757.jpg</t>
         </is>
       </c>
-      <c r="Z33" s="30" t="inlineStr">
+      <c r="Z33" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10011,7 +9499,7 @@
           <t>Twin Dura-Beam Classic Downy Airbed 99x191x25 cm</t>
         </is>
       </c>
-      <c r="AB33" s="30" t="inlineStr">
+      <c r="AB33" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10023,18 +9511,18 @@
           <t>Inflatable Beds and Mattresses</t>
         </is>
       </c>
-      <c r="AF33" s="30" t="inlineStr"/>
-      <c r="AG33" s="30" t="inlineStr">
+      <c r="AF33" s="22" t="inlineStr"/>
+      <c r="AG33" s="22" t="inlineStr">
         <is>
           <t>99.0cm</t>
         </is>
       </c>
-      <c r="AH33" s="30" t="inlineStr">
+      <c r="AH33" s="22" t="inlineStr">
         <is>
           <t>191.0cm</t>
         </is>
       </c>
-      <c r="AI33" s="30" t="inlineStr">
+      <c r="AI33" s="22" t="inlineStr">
         <is>
           <t>25.0cm</t>
         </is>
@@ -10056,17 +9544,17 @@
           <t>A plastic chlorine dosing lock from Steinbach, designed exclusively for use with long-term chlorine tablets, with a 1.5-inch connection fitting. It measures 37 cm in length, 22.5 cm in width, and 15 cm in height, making it a sturdy inline dosing unit for pool water treatment systems.</t>
         </is>
       </c>
-      <c r="D34" s="30" t="inlineStr">
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>Steinbach</t>
         </is>
       </c>
-      <c r="E34" s="30" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F34" s="30" t="inlineStr">
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -10076,71 +9564,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H34" s="30" t="inlineStr">
+      <c r="H34" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I34" s="30" t="inlineStr">
+      <c r="I34" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J34" s="30" t="inlineStr">
+      <c r="J34" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K34" s="30" t="inlineStr">
+      <c r="K34" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L34" s="30" t="inlineStr">
+      <c r="L34" s="22" t="inlineStr">
         <is>
           <t>STE-CHM-0307</t>
         </is>
       </c>
-      <c r="M34" s="31" t="inlineStr">
+      <c r="M34" s="23" t="inlineStr">
         <is>
           <t>9008748790307</t>
         </is>
       </c>
-      <c r="N34" s="32" t="inlineStr"/>
-      <c r="O34" s="32" t="inlineStr"/>
-      <c r="P34" s="32" t="inlineStr"/>
-      <c r="Q34" s="30" t="inlineStr">
+      <c r="N34" s="24" t="inlineStr"/>
+      <c r="O34" s="24" t="inlineStr"/>
+      <c r="P34" s="24" t="inlineStr"/>
+      <c r="Q34" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R34" s="30" t="inlineStr">
+      <c r="R34" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S34" s="30" t="inlineStr">
+      <c r="S34" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T34" s="30" t="inlineStr">
+      <c r="T34" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U34" s="30" t="inlineStr"/>
-      <c r="V34" s="30" t="inlineStr">
+      <c r="U34" s="22" t="inlineStr"/>
+      <c r="V34" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W34" s="30" t="inlineStr">
+      <c r="W34" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X34" s="30" t="inlineStr">
+      <c r="X34" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10150,7 +9638,7 @@
           <t>https://i.ebayimg.com/images/g/CrUAAeSwkOdqeaRR/s-l400.jpg</t>
         </is>
       </c>
-      <c r="Z34" s="30" t="inlineStr">
+      <c r="Z34" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10160,7 +9648,7 @@
           <t>STEINBACH Chlorine dosing lock, only for chlorine long-term tablets, plastic, connection 1.5 inch in</t>
         </is>
       </c>
-      <c r="AB34" s="30" t="inlineStr">
+      <c r="AB34" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10172,18 +9660,18 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF34" s="30" t="inlineStr"/>
-      <c r="AG34" s="30" t="inlineStr">
+      <c r="AF34" s="22" t="inlineStr"/>
+      <c r="AG34" s="22" t="inlineStr">
         <is>
           <t>22.5cm</t>
         </is>
       </c>
-      <c r="AH34" s="30" t="inlineStr">
+      <c r="AH34" s="22" t="inlineStr">
         <is>
           <t>37.0cm</t>
         </is>
       </c>
-      <c r="AI34" s="30" t="inlineStr">
+      <c r="AI34" s="22" t="inlineStr">
         <is>
           <t>15.0cm</t>
         </is>
@@ -10205,17 +9693,17 @@
           <t>A filter cleaning system for hot tub and pool cartridge filters, designed to remove debris and residue efficiently while keeping water usage to a minimum. A practical tool for extending the life of your filter without wasting a drop more than necessary.</t>
         </is>
       </c>
-      <c r="D35" s="30" t="inlineStr">
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>Estelle</t>
         </is>
       </c>
-      <c r="E35" s="30" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F35" s="30" t="inlineStr">
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -10225,71 +9713,71 @@
           <t>filters, spa-hot-tub, cleaning, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H35" s="30" t="inlineStr">
+      <c r="H35" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I35" s="30" t="inlineStr">
+      <c r="I35" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J35" s="30" t="inlineStr">
+      <c r="J35" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K35" s="30" t="inlineStr">
+      <c r="K35" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L35" s="30" t="inlineStr">
+      <c r="L35" s="22" t="inlineStr">
         <is>
           <t>EST-FIL-3669</t>
         </is>
       </c>
-      <c r="M35" s="31" t="inlineStr">
+      <c r="M35" s="23" t="inlineStr">
         <is>
           <t>8711842033669</t>
         </is>
       </c>
-      <c r="N35" s="32" t="inlineStr"/>
-      <c r="O35" s="32" t="inlineStr"/>
-      <c r="P35" s="32" t="inlineStr"/>
-      <c r="Q35" s="30" t="inlineStr">
+      <c r="N35" s="24" t="inlineStr"/>
+      <c r="O35" s="24" t="inlineStr"/>
+      <c r="P35" s="24" t="inlineStr"/>
+      <c r="Q35" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R35" s="30" t="inlineStr">
+      <c r="R35" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S35" s="30" t="inlineStr">
+      <c r="S35" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T35" s="30" t="inlineStr">
+      <c r="T35" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U35" s="30" t="inlineStr"/>
-      <c r="V35" s="30" t="inlineStr">
+      <c r="U35" s="22" t="inlineStr"/>
+      <c r="V35" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W35" s="30" t="inlineStr">
+      <c r="W35" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X35" s="30" t="inlineStr">
+      <c r="X35" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10299,7 +9787,7 @@
           <t>https://i.ebayimg.com/images/g/0e0AAOSweaplqO77/s-l400.jpg</t>
         </is>
       </c>
-      <c r="Z35" s="30" t="inlineStr">
+      <c r="Z35" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10309,7 +9797,7 @@
           <t>Estelle Filter Cleaning System Hot tubs Cartridge Filters Cleaner Spa Amazing!</t>
         </is>
       </c>
-      <c r="AB35" s="30" t="inlineStr">
+      <c r="AB35" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10321,10 +9809,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF35" s="30" t="inlineStr"/>
-      <c r="AG35" s="30" t="inlineStr"/>
-      <c r="AH35" s="30" t="inlineStr"/>
-      <c r="AI35" s="30" t="inlineStr"/>
+      <c r="AF35" s="22" t="inlineStr"/>
+      <c r="AG35" s="22" t="inlineStr"/>
+      <c r="AH35" s="22" t="inlineStr"/>
+      <c r="AI35" s="22" t="inlineStr"/>
     </row>
     <row r="36" ht="62" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
@@ -10334,7 +9822,7 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>WAYS - Pool maintenance - Scrub brush - 15 x 9 x 8 cm - Handy scrub</t>
+          <t>WAYS - Pool Maintenance - Scrub Brush - 15 x 9 x 8 cm - Handy scrub</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
@@ -10342,17 +9830,17 @@
           <t>A compact handy scrub brush for pool maintenance, measuring 15 x 9 x 8 cm, suited to scrubbing pool surfaces and hard-to-reach areas. Small enough to manoeuvre easily, and ready to tackle whatever the waterline throws at it.</t>
         </is>
       </c>
-      <c r="D36" s="30" t="inlineStr">
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>WAYS</t>
         </is>
       </c>
-      <c r="E36" s="30" t="inlineStr">
+      <c r="E36" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F36" s="30" t="inlineStr">
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -10362,79 +9850,79 @@
           <t>pool, cleaning, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H36" s="30" t="inlineStr">
+      <c r="H36" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I36" s="30" t="inlineStr">
+      <c r="I36" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J36" s="30" t="inlineStr">
+      <c r="J36" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K36" s="30" t="inlineStr">
+      <c r="K36" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L36" s="30" t="inlineStr">
+      <c r="L36" s="22" t="inlineStr">
         <is>
           <t>WAY-CLN-2219</t>
         </is>
       </c>
-      <c r="M36" s="31" t="inlineStr">
+      <c r="M36" s="23" t="inlineStr">
         <is>
           <t>8720299182219</t>
         </is>
       </c>
-      <c r="N36" s="32" t="inlineStr"/>
-      <c r="O36" s="32" t="inlineStr"/>
-      <c r="P36" s="32" t="inlineStr"/>
-      <c r="Q36" s="30" t="inlineStr">
+      <c r="N36" s="24" t="inlineStr"/>
+      <c r="O36" s="24" t="inlineStr"/>
+      <c r="P36" s="24" t="inlineStr"/>
+      <c r="Q36" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R36" s="30" t="inlineStr">
+      <c r="R36" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S36" s="30" t="inlineStr">
+      <c r="S36" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T36" s="30" t="inlineStr">
+      <c r="T36" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U36" s="30" t="inlineStr"/>
-      <c r="V36" s="30" t="inlineStr">
+      <c r="U36" s="22" t="inlineStr"/>
+      <c r="V36" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W36" s="30" t="inlineStr">
+      <c r="W36" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X36" s="30" t="inlineStr">
+      <c r="X36" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y36" s="17" t="inlineStr"/>
-      <c r="Z36" s="30" t="inlineStr"/>
+      <c r="Z36" s="22" t="inlineStr"/>
       <c r="AA36" s="17" t="inlineStr"/>
-      <c r="AB36" s="30" t="inlineStr">
+      <c r="AB36" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10446,18 +9934,18 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF36" s="30" t="inlineStr"/>
-      <c r="AG36" s="30" t="inlineStr">
+      <c r="AF36" s="22" t="inlineStr"/>
+      <c r="AG36" s="22" t="inlineStr">
         <is>
           <t>8.0cm</t>
         </is>
       </c>
-      <c r="AH36" s="30" t="inlineStr">
+      <c r="AH36" s="22" t="inlineStr">
         <is>
           <t>15.0cm</t>
         </is>
       </c>
-      <c r="AI36" s="30" t="inlineStr">
+      <c r="AI36" s="22" t="inlineStr">
         <is>
           <t>9.0cm</t>
         </is>
@@ -10471,7 +9959,7 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>Headrest pillow for INTEX inflatable SPA 28506</t>
+          <t>Headrest Pillow for INTEX Inflatable SPA 28506</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
@@ -10479,17 +9967,17 @@
           <t>An inflatable PVC headrest pillow for the Intex inflatable spa (model 28506), measuring 24 x 19 x 6 cm and weighing 0.22 kg, designed to support the head and neck comfortably during use. It attaches to the spa rim and can also be filled with water for added stability.</t>
         </is>
       </c>
-      <c r="D37" s="30" t="inlineStr">
+      <c r="D37" s="22" t="inlineStr">
         <is>
           <t>Intex</t>
         </is>
       </c>
-      <c r="E37" s="30" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F37" s="30" t="inlineStr">
+      <c r="F37" s="22" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -10499,75 +9987,75 @@
           <t>spa-hot-tub, accessories, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H37" s="30" t="inlineStr">
+      <c r="H37" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I37" s="30" t="inlineStr">
+      <c r="I37" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J37" s="30" t="inlineStr">
+      <c r="J37" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K37" s="30" t="inlineStr">
+      <c r="K37" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L37" s="30" t="inlineStr">
+      <c r="L37" s="22" t="inlineStr">
         <is>
           <t>INT-SPA-6075</t>
         </is>
       </c>
-      <c r="M37" s="31" t="inlineStr">
+      <c r="M37" s="23" t="inlineStr">
         <is>
           <t>6941057426075</t>
         </is>
       </c>
-      <c r="N37" s="32" t="inlineStr"/>
-      <c r="O37" s="32" t="inlineStr"/>
-      <c r="P37" s="32" t="inlineStr"/>
-      <c r="Q37" s="30" t="inlineStr">
+      <c r="N37" s="24" t="inlineStr"/>
+      <c r="O37" s="24" t="inlineStr"/>
+      <c r="P37" s="24" t="inlineStr"/>
+      <c r="Q37" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R37" s="30" t="inlineStr">
+      <c r="R37" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S37" s="30" t="inlineStr">
+      <c r="S37" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T37" s="30" t="inlineStr">
+      <c r="T37" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U37" s="30" t="inlineStr">
+      <c r="U37" s="22" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="V37" s="30" t="inlineStr">
+      <c r="V37" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W37" s="30" t="inlineStr">
+      <c r="W37" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X37" s="30" t="inlineStr">
+      <c r="X37" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10577,17 +10065,17 @@
           <t>https://content2.rozetka.com.ua/goods/images/big/570260745.jpg</t>
         </is>
       </c>
-      <c r="Z37" s="30" t="inlineStr">
+      <c r="Z37" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="AA37" s="17" t="inlineStr">
         <is>
-          <t>Headrest pillow for INTEX inflatable SPA 28506</t>
-        </is>
-      </c>
-      <c r="AB37" s="30" t="inlineStr">
+          <t>Headrest Pillow for INTEX Inflatable SPA 28506</t>
+        </is>
+      </c>
+      <c r="AB37" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10599,18 +10087,18 @@
           <t>Intex Pure Spa Accessories</t>
         </is>
       </c>
-      <c r="AF37" s="30" t="inlineStr"/>
-      <c r="AG37" s="30" t="inlineStr">
+      <c r="AF37" s="22" t="inlineStr"/>
+      <c r="AG37" s="22" t="inlineStr">
         <is>
           <t>19.0cm</t>
         </is>
       </c>
-      <c r="AH37" s="30" t="inlineStr">
+      <c r="AH37" s="22" t="inlineStr">
         <is>
           <t>24.0cm</t>
         </is>
       </c>
-      <c r="AI37" s="30" t="inlineStr">
+      <c r="AI37" s="22" t="inlineStr">
         <is>
           <t>6.0cm</t>
         </is>
@@ -10624,7 +10112,7 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>Active oxygen test kit x1</t>
+          <t>Active Oxygen Test Kit x1</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
@@ -10632,13 +10120,13 @@
           <t>A DPD Pool test kit for active-oxygen pools, containing 20 DPD No. 4 reagent tablets for measuring active oxygen levels and 20 phenol red tablets for measuring pH. Results are read immediately after the tablet dissolves, with an ideal active oxygen range of 3.0 to 8.0 mg/l and a target pH of 7.0 to 7.4.</t>
         </is>
       </c>
-      <c r="D38" s="30" t="inlineStr"/>
-      <c r="E38" s="30" t="inlineStr">
+      <c r="D38" s="22" t="inlineStr"/>
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F38" s="30" t="inlineStr">
+      <c r="F38" s="22" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -10648,71 +10136,71 @@
           <t>water-treatment, test-measure, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H38" s="30" t="inlineStr">
+      <c r="H38" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I38" s="30" t="inlineStr">
+      <c r="I38" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J38" s="30" t="inlineStr">
+      <c r="J38" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K38" s="30" t="inlineStr">
+      <c r="K38" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L38" s="30" t="inlineStr">
+      <c r="L38" s="22" t="inlineStr">
         <is>
           <t>GEN-TST-1347</t>
         </is>
       </c>
-      <c r="M38" s="31" t="inlineStr">
+      <c r="M38" s="23" t="inlineStr">
         <is>
           <t>4250463121347</t>
         </is>
       </c>
-      <c r="N38" s="32" t="inlineStr"/>
-      <c r="O38" s="32" t="inlineStr"/>
-      <c r="P38" s="32" t="inlineStr"/>
-      <c r="Q38" s="30" t="inlineStr">
+      <c r="N38" s="24" t="inlineStr"/>
+      <c r="O38" s="24" t="inlineStr"/>
+      <c r="P38" s="24" t="inlineStr"/>
+      <c r="Q38" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R38" s="30" t="inlineStr">
+      <c r="R38" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S38" s="30" t="inlineStr">
+      <c r="S38" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T38" s="30" t="inlineStr">
+      <c r="T38" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U38" s="30" t="inlineStr"/>
-      <c r="V38" s="30" t="inlineStr">
+      <c r="U38" s="22" t="inlineStr"/>
+      <c r="V38" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W38" s="30" t="inlineStr">
+      <c r="W38" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X38" s="30" t="inlineStr">
+      <c r="X38" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10722,17 +10210,17 @@
           <t>https://media.carrefour.fr/medias/8f94161f683b4e589024a5b5ebaa6873/p_200x200/cad3db6a00ef414a804b9226119bae96_image.jpg</t>
         </is>
       </c>
-      <c r="Z38" s="30" t="inlineStr">
+      <c r="Z38" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="AA38" s="17" t="inlineStr">
         <is>
-          <t>Active oxygen test kit x1</t>
-        </is>
-      </c>
-      <c r="AB38" s="30" t="inlineStr">
+          <t>Active Oxygen Test Kit x1</t>
+        </is>
+      </c>
+      <c r="AB38" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10744,10 +10232,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF38" s="30" t="inlineStr"/>
-      <c r="AG38" s="30" t="inlineStr"/>
-      <c r="AH38" s="30" t="inlineStr"/>
-      <c r="AI38" s="30" t="inlineStr"/>
+      <c r="AF38" s="22" t="inlineStr"/>
+      <c r="AG38" s="22" t="inlineStr"/>
+      <c r="AH38" s="22" t="inlineStr"/>
+      <c r="AI38" s="22" t="inlineStr"/>
     </row>
     <row r="39" ht="62" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
@@ -10757,7 +10245,7 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>Darlly filter cartridge pack of 2 filter cartridges compatible with Intex type H</t>
+          <t>Darlly Filter Cartridge Pack of 2 Filter Cartridges Compatible with Intex Type H</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
@@ -10765,17 +10253,17 @@
           <t>A pack of 2 replacement filter cartridges compatible with Intex Type H pool and spa pumps, made by Darlly. Straightforward to swap out, they keep the water moving clean without any complications.</t>
         </is>
       </c>
-      <c r="D39" s="30" t="inlineStr">
+      <c r="D39" s="22" t="inlineStr">
         <is>
           <t>Intex</t>
         </is>
       </c>
-      <c r="E39" s="30" t="inlineStr">
+      <c r="E39" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F39" s="30" t="inlineStr">
+      <c r="F39" s="22" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -10785,79 +10273,79 @@
           <t>filters, repeat-purchase, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H39" s="30" t="inlineStr">
+      <c r="H39" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I39" s="30" t="inlineStr">
+      <c r="I39" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J39" s="30" t="inlineStr">
+      <c r="J39" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K39" s="30" t="inlineStr">
+      <c r="K39" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L39" s="30" t="inlineStr">
+      <c r="L39" s="22" t="inlineStr">
         <is>
           <t>INT-FIL-2895</t>
         </is>
       </c>
-      <c r="M39" s="31" t="inlineStr">
+      <c r="M39" s="23" t="inlineStr">
         <is>
           <t>700175992895</t>
         </is>
       </c>
-      <c r="N39" s="32" t="inlineStr"/>
-      <c r="O39" s="32" t="inlineStr"/>
-      <c r="P39" s="32" t="inlineStr"/>
-      <c r="Q39" s="30" t="inlineStr">
+      <c r="N39" s="24" t="inlineStr"/>
+      <c r="O39" s="24" t="inlineStr"/>
+      <c r="P39" s="24" t="inlineStr"/>
+      <c r="Q39" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R39" s="30" t="inlineStr">
+      <c r="R39" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S39" s="30" t="inlineStr">
+      <c r="S39" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T39" s="30" t="inlineStr">
+      <c r="T39" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U39" s="30" t="inlineStr"/>
-      <c r="V39" s="30" t="inlineStr">
+      <c r="U39" s="22" t="inlineStr"/>
+      <c r="V39" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W39" s="30" t="inlineStr">
+      <c r="W39" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X39" s="30" t="inlineStr">
+      <c r="X39" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y39" s="17" t="inlineStr"/>
-      <c r="Z39" s="30" t="inlineStr"/>
+      <c r="Z39" s="22" t="inlineStr"/>
       <c r="AA39" s="17" t="inlineStr"/>
-      <c r="AB39" s="30" t="inlineStr">
+      <c r="AB39" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10869,10 +10357,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF39" s="30" t="inlineStr"/>
-      <c r="AG39" s="30" t="inlineStr"/>
-      <c r="AH39" s="30" t="inlineStr"/>
-      <c r="AI39" s="30" t="inlineStr"/>
+      <c r="AF39" s="22" t="inlineStr"/>
+      <c r="AG39" s="22" t="inlineStr"/>
+      <c r="AH39" s="22" t="inlineStr"/>
+      <c r="AI39" s="22" t="inlineStr"/>
     </row>
     <row r="40" ht="62" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
@@ -10882,7 +10370,7 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>Spa replacement filter Ø 22 cm x 27 cm SC713, C-8465 - Darlly</t>
+          <t>Spa Replacement Filter Ø 22 cm x 27 cm SC713, C-8465 - Darlly</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
@@ -10890,17 +10378,17 @@
           <t>A Darlly replacement spa filter cartridge with dimensions of 22 cm diameter by 27 cm height, compatible with SC713 and C-8465 references. A reliable like-for-like swap to keep your spa filtration running smoothly.</t>
         </is>
       </c>
-      <c r="D40" s="30" t="inlineStr">
+      <c r="D40" s="22" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E40" s="30" t="inlineStr">
+      <c r="E40" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F40" s="30" t="inlineStr">
+      <c r="F40" s="22" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -10910,71 +10398,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H40" s="30" t="inlineStr">
+      <c r="H40" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I40" s="30" t="inlineStr">
+      <c r="I40" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J40" s="30" t="inlineStr">
+      <c r="J40" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K40" s="30" t="inlineStr">
+      <c r="K40" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L40" s="30" t="inlineStr">
+      <c r="L40" s="22" t="inlineStr">
         <is>
           <t>DAR-FIL-1744</t>
         </is>
       </c>
-      <c r="M40" s="31" t="inlineStr">
+      <c r="M40" s="23" t="inlineStr">
         <is>
           <t>700175991744</t>
         </is>
       </c>
-      <c r="N40" s="32" t="inlineStr"/>
-      <c r="O40" s="32" t="inlineStr"/>
-      <c r="P40" s="32" t="inlineStr"/>
-      <c r="Q40" s="30" t="inlineStr">
+      <c r="N40" s="24" t="inlineStr"/>
+      <c r="O40" s="24" t="inlineStr"/>
+      <c r="P40" s="24" t="inlineStr"/>
+      <c r="Q40" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R40" s="30" t="inlineStr">
+      <c r="R40" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S40" s="30" t="inlineStr">
+      <c r="S40" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T40" s="30" t="inlineStr">
+      <c r="T40" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U40" s="30" t="inlineStr"/>
-      <c r="V40" s="30" t="inlineStr">
+      <c r="U40" s="22" t="inlineStr"/>
+      <c r="V40" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W40" s="30" t="inlineStr">
+      <c r="W40" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X40" s="30" t="inlineStr">
+      <c r="X40" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10984,17 +10472,17 @@
           <t>https://images.barcodelookup.com/142259/1422591231-1.jpg</t>
         </is>
       </c>
-      <c r="Z40" s="30" t="inlineStr">
+      <c r="Z40" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="AA40" s="17" t="inlineStr">
         <is>
-          <t>Spa replacement filter Ø 22 cm x 27 cm SC713, C-8465 - Darlly</t>
-        </is>
-      </c>
-      <c r="AB40" s="30" t="inlineStr">
+          <t>Spa Replacement Filter Ø 22 cm x 27 cm SC713, C-8465 - Darlly</t>
+        </is>
+      </c>
+      <c r="AB40" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -11006,14 +10494,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF40" s="30" t="inlineStr"/>
-      <c r="AG40" s="30" t="inlineStr"/>
-      <c r="AH40" s="30" t="inlineStr">
+      <c r="AF40" s="22" t="inlineStr"/>
+      <c r="AG40" s="22" t="inlineStr"/>
+      <c r="AH40" s="22" t="inlineStr">
         <is>
           <t>22.0cm</t>
         </is>
       </c>
-      <c r="AI40" s="30" t="inlineStr">
+      <c r="AI40" s="22" t="inlineStr">
         <is>
           <t>27.0cm</t>
         </is>
@@ -11022,12 +10510,12 @@
     <row r="41" ht="62" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>1-x-1-kg-bayzid-multitabs-20g-5in1-for-pools-hofer-chemie</t>
+          <t>1-x-1-kg-bayzid-20g-5-in-1-multitabs-for-pools-hofer-chemie</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>1 x 1 kg BAYZID® multitabs 20g 5in1 for pools - Höfer Chemie</t>
+          <t>1 x 1 kg BAYZID® 20g 5-in-1 Multitabs for Pools - HÖFER CHEMIE</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
@@ -11035,17 +10523,17 @@
           <t>A 1 kg pack of 20g multitabs for swimming pools, offering a 5-in-1 treatment that combines multiple water care functions in a single slow-dissolving tablet. Convenient all-in-one dosing that keeps pool maintenance simple.</t>
         </is>
       </c>
-      <c r="D41" s="30" t="inlineStr">
+      <c r="D41" s="22" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E41" s="30" t="inlineStr">
+      <c r="E41" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F41" s="30" t="inlineStr">
+      <c r="F41" s="22" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -11055,75 +10543,75 @@
           <t>pool, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H41" s="30" t="inlineStr">
+      <c r="H41" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I41" s="30" t="inlineStr">
+      <c r="I41" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J41" s="30" t="inlineStr">
+      <c r="J41" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K41" s="30" t="inlineStr">
+      <c r="K41" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L41" s="30" t="inlineStr">
+      <c r="L41" s="22" t="inlineStr">
         <is>
           <t>HFE-CHM-8430</t>
         </is>
       </c>
-      <c r="M41" s="31" t="inlineStr">
+      <c r="M41" s="23" t="inlineStr">
         <is>
           <t>4250463108430</t>
         </is>
       </c>
-      <c r="N41" s="32" t="inlineStr"/>
-      <c r="O41" s="32" t="inlineStr"/>
-      <c r="P41" s="32" t="inlineStr"/>
-      <c r="Q41" s="30" t="inlineStr">
+      <c r="N41" s="24" t="inlineStr"/>
+      <c r="O41" s="24" t="inlineStr"/>
+      <c r="P41" s="24" t="inlineStr"/>
+      <c r="Q41" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R41" s="30" t="inlineStr">
+      <c r="R41" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S41" s="30" t="inlineStr">
+      <c r="S41" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T41" s="30" t="inlineStr">
+      <c r="T41" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U41" s="30" t="inlineStr">
+      <c r="U41" s="22" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="V41" s="30" t="inlineStr">
+      <c r="V41" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W41" s="30" t="inlineStr">
+      <c r="W41" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X41" s="30" t="inlineStr">
+      <c r="X41" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -11133,17 +10621,17 @@
           <t>https://images.barcodelookup.com/17422/174228560-1.jpg</t>
         </is>
       </c>
-      <c r="Z41" s="30" t="inlineStr">
+      <c r="Z41" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="AA41" s="17" t="inlineStr">
         <is>
-          <t>1 x 1 kg BAYZID® multitabs 20g 5in1 for pools - Höfer Chemie</t>
-        </is>
-      </c>
-      <c r="AB41" s="30" t="inlineStr">
+          <t>1 x 1 kg BAYZID® 20g 5-in-1 Multitabs for Pools - HÖFER CHEMIE</t>
+        </is>
+      </c>
+      <c r="AB41" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -11155,10 +10643,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF41" s="30" t="inlineStr"/>
-      <c r="AG41" s="30" t="inlineStr"/>
-      <c r="AH41" s="30" t="inlineStr"/>
-      <c r="AI41" s="30" t="inlineStr"/>
+      <c r="AF41" s="22" t="inlineStr"/>
+      <c r="AG41" s="22" t="inlineStr"/>
+      <c r="AH41" s="22" t="inlineStr"/>
+      <c r="AI41" s="22" t="inlineStr"/>
     </row>
     <row r="42" ht="76" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
@@ -11176,17 +10664,17 @@
           <t>A ready-to-use alkaline spray cleaner for removing grease and dirt marks at the waterline of pools and for cleaning skimmers. The spray bottle makes application straightforward, and it can be used on a filled pool on all alkali-resistant surfaces.</t>
         </is>
       </c>
-      <c r="D42" s="30" t="inlineStr">
+      <c r="D42" s="22" t="inlineStr">
         <is>
           <t>Bayrol</t>
         </is>
       </c>
-      <c r="E42" s="30" t="inlineStr">
+      <c r="E42" s="22" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F42" s="30" t="inlineStr">
+      <c r="F42" s="22" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -11196,75 +10684,75 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H42" s="30" t="inlineStr">
+      <c r="H42" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I42" s="30" t="inlineStr">
+      <c r="I42" s="22" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J42" s="30" t="inlineStr">
+      <c r="J42" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K42" s="30" t="inlineStr">
+      <c r="K42" s="22" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L42" s="30" t="inlineStr">
+      <c r="L42" s="22" t="inlineStr">
         <is>
           <t>BAY-CLN-4134</t>
         </is>
       </c>
-      <c r="M42" s="31" t="inlineStr">
+      <c r="M42" s="23" t="inlineStr">
         <is>
           <t>4008367154134</t>
         </is>
       </c>
-      <c r="N42" s="32" t="inlineStr"/>
-      <c r="O42" s="32" t="inlineStr"/>
-      <c r="P42" s="32" t="inlineStr"/>
-      <c r="Q42" s="30" t="inlineStr">
+      <c r="N42" s="24" t="inlineStr"/>
+      <c r="O42" s="24" t="inlineStr"/>
+      <c r="P42" s="24" t="inlineStr"/>
+      <c r="Q42" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R42" s="30" t="inlineStr">
+      <c r="R42" s="22" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S42" s="30" t="inlineStr">
+      <c r="S42" s="22" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T42" s="30" t="inlineStr">
+      <c r="T42" s="22" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U42" s="30" t="inlineStr">
+      <c r="U42" s="22" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="V42" s="30" t="inlineStr">
+      <c r="V42" s="22" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W42" s="30" t="inlineStr">
+      <c r="W42" s="22" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X42" s="30" t="inlineStr">
+      <c r="X42" s="22" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -11274,7 +10762,7 @@
           <t>https://www.north-spa.de/wp-content/uploads/2023/02/Produktbild-1-Bayrol-Randfix-07-l-4008367154134.jpg</t>
         </is>
       </c>
-      <c r="Z42" s="30" t="inlineStr">
+      <c r="Z42" s="22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -11284,7 +10772,7 @@
           <t>Bayrol Randfix 0,7 l</t>
         </is>
       </c>
-      <c r="AB42" s="30" t="inlineStr">
+      <c r="AB42" s="22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -11296,10 +10784,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF42" s="30" t="inlineStr"/>
-      <c r="AG42" s="30" t="inlineStr"/>
-      <c r="AH42" s="30" t="inlineStr"/>
-      <c r="AI42" s="30" t="inlineStr"/>
+      <c r="AF42" s="22" t="inlineStr"/>
+      <c r="AG42" s="22" t="inlineStr"/>
+      <c r="AH42" s="22" t="inlineStr"/>
+      <c r="AI42" s="22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projects/splashstore/docs/splashstore-scan-curation-260816.xlsx
+++ b/projects/splashstore/docs/splashstore-scan-curation-260816.xlsx
@@ -93,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -162,6 +162,24 @@
     <xf numFmtId="49" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +515,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1428750" cy="1428750"/>
@@ -525,7 +543,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1428750" cy="1428750"/>
@@ -553,7 +571,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1428750" cy="1428750"/>
@@ -581,7 +599,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1428750" cy="1428750"/>
@@ -609,7 +627,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1428750" cy="1428750"/>
@@ -637,7 +655,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1428750" cy="1428750"/>
@@ -665,7 +683,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>25</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1428750" cy="1428750"/>
@@ -693,7 +711,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1428750" cy="1428750"/>
@@ -721,7 +739,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>21</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1428750" cy="1428750"/>
@@ -749,7 +767,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1428750" cy="1428750"/>
@@ -777,7 +795,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1428750" cy="1428750"/>
@@ -805,7 +823,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>25</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1428750" cy="1428750"/>
@@ -833,7 +851,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>33</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1428750" cy="1428750"/>
@@ -861,7 +879,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1428750" cy="1428750"/>
@@ -889,7 +907,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1428750" cy="1428750"/>
@@ -917,7 +935,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1428750" cy="1428750"/>
@@ -945,7 +963,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1428750" cy="1428750"/>
@@ -973,7 +991,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1428750" cy="1428750"/>
@@ -1001,7 +1019,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1428750" cy="1428750"/>
@@ -1029,7 +1047,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>42</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1428750" cy="1428750"/>
@@ -1057,7 +1075,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>36</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1428750" cy="1428750"/>
@@ -1068,6 +1086,174 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>40</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1381,20 +1567,20 @@
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="56" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="56" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="56" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1494,7 +1680,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="132" customHeight="1">
+    <row r="2" ht="286" customHeight="1">
       <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="5" t="inlineStr">
         <is>
@@ -1551,8 +1737,16 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr"/>
-      <c r="N2" s="4" t="inlineStr"/>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.spa-components.com/user/shop/big/1473-1_filter-cartridge-sc779-rising-dragon-plastics--eago-whirlpools.jpg?ff=1&amp;x=1024&amp;y=768&amp;q=85&amp;ts=6720c4a0&amp;sg=161563f2</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
       <c r="O2" s="7" t="inlineStr">
         <is>
           <t>https://www.spa-components.com/user/shop/big/1473-1_filter-cartridge-sc779-rising-dragon-plastics--eago-whirlpools.jpg?ff=1&amp;x=1024&amp;y=768&amp;q=85&amp;ts=6720c4a0&amp;sg=161563f2</t>
@@ -1563,7 +1757,11 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="Q2" s="19" t="inlineStr"/>
+      <c r="Q2" s="19" t="inlineStr">
+        <is>
+          <t>3 sources: barcodelookup.com, ean-search.org, spa-components.com</t>
+        </is>
+      </c>
       <c r="R2" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -1575,7 +1773,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="132" customHeight="1">
+    <row r="3" ht="286" customHeight="1">
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="5" t="inlineStr">
         <is>
@@ -1646,7 +1844,11 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="Q3" s="19" t="inlineStr"/>
+      <c r="Q3" s="19" t="inlineStr">
+        <is>
+          <t>3 sources: barcodelookup.com, bestwaystore.de, ean-search.org</t>
+        </is>
+      </c>
       <c r="R3" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -1658,7 +1860,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="132" customHeight="1">
+    <row r="4" ht="314" customHeight="1">
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="5" t="inlineStr">
         <is>
@@ -1715,8 +1917,16 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>https://ap.nice-cdn.com/upload/image/product/large/default/bestway-flowclear-filter-cartridge-size-3-1-item-638140-en.jpg</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
           <t>https://ap.nice-cdn.com/upload/image/product/large/default/bestway-flowclear-filter-cartridge-size-3-1-item-638140-en.jpg</t>
@@ -1727,7 +1937,11 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="Q4" s="19" t="inlineStr"/>
+      <c r="Q4" s="19" t="inlineStr">
+        <is>
+          <t>3 sources: barcodelookup.com, ean-search.org, pools.shop</t>
+        </is>
+      </c>
       <c r="R4" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -1739,7 +1953,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="9" t="inlineStr"/>
       <c r="B5" s="10" t="inlineStr">
         <is>
@@ -1758,7 +1972,11 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Blank — missing</t>
+        </is>
+      </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
           <t>Blank — missing</t>
@@ -1777,7 +1995,11 @@
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>Blank — no image</t>
+        </is>
+      </c>
       <c r="O5" s="11" t="inlineStr"/>
       <c r="P5" s="11" t="inlineStr">
         <is>
@@ -1792,7 +2014,7 @@
       </c>
       <c r="S5" s="17" t="inlineStr"/>
     </row>
-    <row r="6" ht="132" customHeight="1">
+    <row r="6" ht="272" customHeight="1">
       <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -1849,8 +2071,16 @@
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>https://images.barcodelookup.com/29361/293617958-1.jpg</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>Verified — Barcode Lookup (barcode)</t>
+        </is>
+      </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
           <t>https://images.barcodelookup.com/29361/293617958-1.jpg</t>
@@ -1861,7 +2091,11 @@
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="Q6" s="19" t="inlineStr"/>
+      <c r="Q6" s="19" t="inlineStr">
+        <is>
+          <t>2 sources: barcodelookup.com, ean-search.org</t>
+        </is>
+      </c>
       <c r="R6" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -1873,7 +2107,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="132" customHeight="1">
+    <row r="7" ht="286" customHeight="1">
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -1944,7 +2178,11 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="Q7" s="19" t="inlineStr"/>
+      <c r="Q7" s="19" t="inlineStr">
+        <is>
+          <t>3 sources: barcodelookup.com, bestwaystore.de, ean-search.org</t>
+        </is>
+      </c>
       <c r="R7" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -1956,7 +2194,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="132" customHeight="1">
+    <row r="8" ht="258" customHeight="1">
       <c r="A8" s="12" t="inlineStr"/>
       <c r="B8" s="13" t="inlineStr">
         <is>
@@ -2013,8 +2251,16 @@
           <t>Likely — Barcode Lookup (barcode) (unclear)</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>https://images.barcodelookup.com/4378/43786454-1.jpg</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>Likely — Barcode Lookup (barcode) (unclear)</t>
+        </is>
+      </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
           <t>https://images.barcodelookup.com/4378/43786454-1.jpg</t>
@@ -2025,7 +2271,11 @@
           <t>Likely — Barcode Lookup (barcode) (unclear)</t>
         </is>
       </c>
-      <c r="Q8" s="19" t="inlineStr"/>
+      <c r="Q8" s="19" t="inlineStr">
+        <is>
+          <t>2 sources: barcodelookup.com, ean-search.org</t>
+        </is>
+      </c>
       <c r="R8" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -2037,7 +2287,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="132" customHeight="1">
+    <row r="9" ht="320" customHeight="1">
       <c r="A9" s="12" t="inlineStr"/>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -2094,8 +2344,16 @@
           <t>Likely — Barcode Lookup (barcode) (unclear)</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr"/>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>https://images.barcodelookup.com/4469/44699532-1.jpg</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>Likely — Barcode Lookup (barcode) (unclear)</t>
+        </is>
+      </c>
       <c r="O9" s="14" t="inlineStr">
         <is>
           <t>https://images.barcodelookup.com/4469/44699532-1.jpg</t>
@@ -2106,7 +2364,11 @@
           <t>Likely — Barcode Lookup (barcode) (unclear)</t>
         </is>
       </c>
-      <c r="Q9" s="19" t="inlineStr"/>
+      <c r="Q9" s="19" t="inlineStr">
+        <is>
+          <t>2 sources: barcodelookup, ean-search.org</t>
+        </is>
+      </c>
       <c r="R9" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -2118,7 +2380,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="132" customHeight="1">
+    <row r="10" ht="320" customHeight="1">
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -2187,7 +2449,11 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="Q10" s="19" t="inlineStr"/>
+      <c r="Q10" s="19" t="inlineStr">
+        <is>
+          <t>3 sources: barcodelookup.com, ean-search.org, intex.fr</t>
+        </is>
+      </c>
       <c r="R10" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -2199,7 +2465,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="132" customHeight="1">
+    <row r="11" ht="258" customHeight="1">
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -2256,7 +2522,11 @@
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr"/>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>https://images.barcodelookup.com/12027/120276177-1.jpg</t>
+        </is>
+      </c>
       <c r="N11" s="4" t="n">
         <v>3</v>
       </c>
@@ -2270,7 +2540,11 @@
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="Q11" s="19" t="inlineStr"/>
+      <c r="Q11" s="19" t="inlineStr">
+        <is>
+          <t>1 source: barcodelookup</t>
+        </is>
+      </c>
       <c r="R11" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -2282,11 +2556,11 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="62" customHeight="1">
-      <c r="A12" s="9" t="inlineStr"/>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+    <row r="12" ht="244" customHeight="1">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
@@ -2326,24 +2600,44 @@
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t>spa-hot-tub, considered-purchase, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr"/>
+          <t>spa-hot-tub, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.north-spa.de/wp-content/uploads/2025/02/Produktbild-1-hth-SPA-ANTIKALK-1-l-3521684700194-360x360.jpg</t>
+        </is>
+      </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr"/>
-      <c r="O12" s="11" t="inlineStr"/>
-      <c r="P12" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="Q12" s="19" t="inlineStr"/>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.north-spa.de/wp-content/uploads/2025/02/Produktbild-1-hth-SPA-ANTIKALK-1-l-3521684700194-360x360.jpg</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>https://www.north-spa.de/wp-content/uploads/2025/02/Produktbild-1-hth-SPA-ANTIKALK-1-l-3521684700194-360x360.jpg</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="Q12" s="19" t="inlineStr">
+        <is>
+          <t>1 source: ean-search.org</t>
+        </is>
+      </c>
       <c r="R12" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -2355,7 +2649,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="132" customHeight="1">
+    <row r="13" ht="272" customHeight="1">
       <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -2412,8 +2706,16 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr"/>
-      <c r="N13" s="4" t="inlineStr"/>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>https://media.intex.fr/11990-large_default_x2/28412np-spa-gonflable-olive-8-places.jpg</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
           <t>https://media.intex.fr/11990-large_default_x2/28412np-spa-gonflable-olive-8-places.jpg</t>
@@ -2424,7 +2726,11 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="Q13" s="19" t="inlineStr"/>
+      <c r="Q13" s="19" t="inlineStr">
+        <is>
+          <t>3 sources: barcodelookup.com, ean-search.org, intex.fr</t>
+        </is>
+      </c>
       <c r="R13" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -2436,7 +2742,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="132" customHeight="1">
+    <row r="14" ht="244" customHeight="1">
       <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -2493,8 +2799,16 @@
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>https://images.barcodelookup.com/29338/293384728-1.jpg</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>Verified — Barcode Lookup (barcode)</t>
+        </is>
+      </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
           <t>https://images.barcodelookup.com/29338/293384728-1.jpg</t>
@@ -2505,7 +2819,11 @@
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="Q14" s="19" t="inlineStr"/>
+      <c r="Q14" s="19" t="inlineStr">
+        <is>
+          <t>2 sources: barcodelookup.com, ean-search.org</t>
+        </is>
+      </c>
       <c r="R14" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -2517,11 +2835,11 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="62" customHeight="1">
-      <c r="A15" s="9" t="inlineStr"/>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+    <row r="15" ht="244" customHeight="1">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
@@ -2561,24 +2879,44 @@
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>cleaning, add-on, multi-source-confirmed, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr"/>
+          <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.spabalancer.ch/media/ae/20/d2/1728651174/sb111_clean-refresh_freigestellt.png?ts=1777362921</t>
+        </is>
+      </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="inlineStr"/>
-      <c r="N15" s="4" t="inlineStr"/>
-      <c r="O15" s="11" t="inlineStr"/>
-      <c r="P15" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="Q15" s="19" t="inlineStr"/>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.spabalancer.ch/media/ae/20/d2/1728651174/sb111_clean-refresh_freigestellt.png?ts=1777362921</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>https://www.spabalancer.ch/media/ae/20/d2/1728651174/sb111_clean-refresh_freigestellt.png?ts=1777362921</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="Q15" s="19" t="inlineStr">
+        <is>
+          <t>2 sources: spa-plus.eu, ean-search.org</t>
+        </is>
+      </c>
       <c r="R15" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -2590,7 +2928,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
+    <row r="16" ht="34" customHeight="1">
       <c r="A16" s="9" t="inlineStr"/>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -2609,7 +2947,11 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Blank — missing</t>
+        </is>
+      </c>
       <c r="H16" s="20" t="inlineStr">
         <is>
           <t>Blank — missing</t>
@@ -2628,7 +2970,11 @@
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr"/>
-      <c r="N16" s="4" t="inlineStr"/>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>Blank — no image</t>
+        </is>
+      </c>
       <c r="O16" s="11" t="inlineStr"/>
       <c r="P16" s="11" t="inlineStr">
         <is>
@@ -2643,7 +2989,7 @@
       </c>
       <c r="S16" s="17" t="inlineStr"/>
     </row>
-    <row r="17" ht="62" customHeight="1">
+    <row r="17" ht="244" customHeight="1">
       <c r="A17" s="9" t="inlineStr"/>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -2697,14 +3043,26 @@
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr"/>
-      <c r="N17" s="4" t="inlineStr"/>
-      <c r="O17" s="11" t="inlineStr"/>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>Blank — no image</t>
+        </is>
+      </c>
+      <c r="O17" s="11" t="inlineStr">
+        <is>
+          <t>1 source: ean-search.org</t>
+        </is>
+      </c>
       <c r="P17" s="11" t="inlineStr">
         <is>
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="Q17" s="19" t="inlineStr"/>
+      <c r="Q17" s="19" t="inlineStr">
+        <is>
+          <t>1 source: ean-search.org</t>
+        </is>
+      </c>
       <c r="R17" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -2716,11 +3074,11 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="62" customHeight="1">
-      <c r="A18" s="9" t="inlineStr"/>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+    <row r="18" ht="244" customHeight="1">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
@@ -2760,24 +3118,44 @@
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>test-measure, add-on, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr"/>
+          <t>test-measure, add-on, barcode-verified, needs-review, scanned-stock</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.poolpowershop.de/media/46/63/13/1743521499/phenol-red-testtabletten-fuer-poollab-500-stk.jpg</t>
+        </is>
+      </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr"/>
-      <c r="O18" s="11" t="inlineStr"/>
-      <c r="P18" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="Q18" s="19" t="inlineStr"/>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.poolpowershop.de/media/46/63/13/1743521499/phenol-red-testtabletten-fuer-poollab-500-stk.jpg</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>https://www.poolpowershop.de/media/46/63/13/1743521499/phenol-red-testtabletten-fuer-poollab-500-stk.jpg</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="Q18" s="19" t="inlineStr">
+        <is>
+          <t>1 source: ean-search.org</t>
+        </is>
+      </c>
       <c r="R18" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -2789,7 +3167,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="132" customHeight="1">
+    <row r="19" ht="244" customHeight="1">
       <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -2846,8 +3224,16 @@
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr"/>
-      <c r="N19" s="4" t="inlineStr"/>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>https://images.barcodelookup.com/21057/210579756-1.jpg</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>Verified — Barcode Lookup (barcode)</t>
+        </is>
+      </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
           <t>https://images.barcodelookup.com/21057/210579756-1.jpg</t>
@@ -2858,7 +3244,11 @@
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="Q19" s="19" t="inlineStr"/>
+      <c r="Q19" s="19" t="inlineStr">
+        <is>
+          <t>2 sources: barcodelookup.com, ean-search.org</t>
+        </is>
+      </c>
       <c r="R19" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -2870,7 +3260,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="132" customHeight="1">
+    <row r="20" ht="314" customHeight="1">
       <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -2927,8 +3317,16 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr"/>
-      <c r="N20" s="4" t="inlineStr"/>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>http://mangas.com.cy/media/products/5292638000223.jpg</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
           <t>http://mangas.com.cy/media/products/5292638000223.jpg</t>
@@ -2939,7 +3337,11 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="Q20" s="19" t="inlineStr"/>
+      <c r="Q20" s="19" t="inlineStr">
+        <is>
+          <t>2 sources: mangas.com.cy, ean-search.org</t>
+        </is>
+      </c>
       <c r="R20" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -2951,7 +3353,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="132" customHeight="1">
+    <row r="21" ht="320" customHeight="1">
       <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -3008,8 +3410,16 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr"/>
-      <c r="N21" s="4" t="inlineStr"/>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>https://poolservices.cy/storage/2026/05/California-Clear-Blue-1L-Aquality-2.jpeg</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
           <t>https://poolservices.cy/storage/2026/05/California-Clear-Blue-1L-Aquality-2.jpeg</t>
@@ -3020,7 +3430,11 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="Q21" s="19" t="inlineStr"/>
+      <c r="Q21" s="19" t="inlineStr">
+        <is>
+          <t>2 sources: poolservices.cy, ean-search.org</t>
+        </is>
+      </c>
       <c r="R21" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -3032,7 +3446,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="132" customHeight="1">
+    <row r="22" ht="216" customHeight="1">
       <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -3089,8 +3503,16 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr"/>
-      <c r="N22" s="4" t="inlineStr"/>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>http://mangas.com.cy/media/products/5292638000162.jpg</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
       <c r="O22" s="7" t="inlineStr">
         <is>
           <t>http://mangas.com.cy/media/products/5292638000162.jpg</t>
@@ -3101,7 +3523,11 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="Q22" s="19" t="inlineStr"/>
+      <c r="Q22" s="19" t="inlineStr">
+        <is>
+          <t>2 sources: mangas.com.cy, ean-search.org</t>
+        </is>
+      </c>
       <c r="R22" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -3113,11 +3539,11 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="48" customHeight="1">
-      <c r="A23" s="9" t="inlineStr"/>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+    <row r="23" ht="202" customHeight="1">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
@@ -3157,24 +3583,44 @@
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>spa-hot-tub, pool, water-treatment, considered-purchase, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr"/>
+          <t>spa-hot-tub, pool, water-treatment, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>https://hoefer-shop.com/cdn/shop/files/1x1L-BAYZID-Spa-Poolclear-v1-RS_1.jpg?v=1785600487&amp;width=800</t>
+        </is>
+      </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr"/>
-      <c r="N23" s="4" t="inlineStr"/>
-      <c r="O23" s="11" t="inlineStr"/>
-      <c r="P23" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="Q23" s="19" t="inlineStr"/>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>https://hoefer-shop.com/cdn/shop/files/1x1L-BAYZID-Spa-Poolclear-v1-RS_1.jpg?v=1785600487&amp;width=800</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>https://hoefer-shop.com/cdn/shop/files/1x1L-BAYZID-Spa-Poolclear-v1-RS_1.jpg?v=1785600487&amp;width=800</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="Q23" s="19" t="inlineStr">
+        <is>
+          <t>1 source: ean-search.org</t>
+        </is>
+      </c>
       <c r="R23" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -3186,11 +3632,11 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="62" customHeight="1">
-      <c r="A24" s="9" t="inlineStr"/>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+    <row r="24" ht="244" customHeight="1">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
@@ -3230,24 +3676,44 @@
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>water-treatment, repeat-purchase, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr"/>
+          <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>https://hoefer-shop.com/cdn/shop/files/1x1L-Wasserstoffperoxid-Flasche-hinten-26.jpg?v=1783777627&amp;width=1000</t>
+        </is>
+      </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr"/>
-      <c r="N24" s="4" t="inlineStr"/>
-      <c r="O24" s="11" t="inlineStr"/>
-      <c r="P24" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="Q24" s="19" t="inlineStr"/>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>https://hoefer-shop.com/cdn/shop/files/1x1L-Wasserstoffperoxid-Flasche-hinten-26.jpg?v=1783777627&amp;width=1000</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>https://hoefer-shop.com/cdn/shop/files/1x1L-Wasserstoffperoxid-Flasche-hinten-26.jpg?v=1783777627&amp;width=1000</t>
+        </is>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="Q24" s="19" t="inlineStr">
+        <is>
+          <t>1 source: ean-search.org</t>
+        </is>
+      </c>
       <c r="R24" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -3259,7 +3725,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="62" customHeight="1">
+    <row r="25" ht="244" customHeight="1">
       <c r="A25" s="9" t="inlineStr"/>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -3316,13 +3782,21 @@
       <c r="N25" s="4" t="n">
         <v>4.5</v>
       </c>
-      <c r="O25" s="11" t="inlineStr"/>
+      <c r="O25" s="11" t="inlineStr">
+        <is>
+          <t>1 source: ean-search.org</t>
+        </is>
+      </c>
       <c r="P25" s="11" t="inlineStr">
         <is>
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="Q25" s="19" t="inlineStr"/>
+      <c r="Q25" s="19" t="inlineStr">
+        <is>
+          <t>1 source: ean-search.org</t>
+        </is>
+      </c>
       <c r="R25" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -3334,7 +3808,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="132" customHeight="1">
+    <row r="26" ht="230" customHeight="1">
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -3391,8 +3865,16 @@
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr"/>
-      <c r="N26" s="4" t="inlineStr"/>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>https://images.barcodelookup.com/16704/167043133-1.jpg</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>Verified — Barcode Lookup (barcode)</t>
+        </is>
+      </c>
       <c r="O26" s="7" t="inlineStr">
         <is>
           <t>https://images.barcodelookup.com/16704/167043133-1.jpg</t>
@@ -3403,7 +3885,11 @@
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="Q26" s="19" t="inlineStr"/>
+      <c r="Q26" s="19" t="inlineStr">
+        <is>
+          <t>3 sources: spa-plus.eu, barcodelookup.com, ean-search.org</t>
+        </is>
+      </c>
       <c r="R26" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -3415,7 +3901,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="132" customHeight="1">
+    <row r="27" ht="320" customHeight="1">
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="5" t="inlineStr">
         <is>
@@ -3472,8 +3958,16 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="M27" s="4" t="inlineStr"/>
-      <c r="N27" s="4" t="inlineStr"/>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.piscinarium.com/2908-thickbox_default/pool-gom-magic-rubber-eraser.jpg</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
           <t>https://www.piscinarium.com/2908-thickbox_default/pool-gom-magic-rubber-eraser.jpg</t>
@@ -3484,7 +3978,11 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="Q27" s="19" t="inlineStr"/>
+      <c r="Q27" s="19" t="inlineStr">
+        <is>
+          <t>2 sources: ean-search.org, piscinarium.com</t>
+        </is>
+      </c>
       <c r="R27" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -3496,7 +3994,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="62" customHeight="1">
+    <row r="28" ht="244" customHeight="1">
       <c r="A28" s="9" t="inlineStr"/>
       <c r="B28" s="10" t="inlineStr">
         <is>
@@ -3550,14 +4048,26 @@
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr"/>
-      <c r="N28" s="4" t="inlineStr"/>
-      <c r="O28" s="11" t="inlineStr"/>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>Blank — no image</t>
+        </is>
+      </c>
+      <c r="O28" s="11" t="inlineStr">
+        <is>
+          <t>2 sources: ean-search.org, spa-industries.eu</t>
+        </is>
+      </c>
       <c r="P28" s="11" t="inlineStr">
         <is>
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="Q28" s="19" t="inlineStr"/>
+      <c r="Q28" s="19" t="inlineStr">
+        <is>
+          <t>2 sources: ean-search.org, spa-industries.eu</t>
+        </is>
+      </c>
       <c r="R28" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -3569,7 +4079,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="62" customHeight="1">
+    <row r="29" ht="258" customHeight="1">
       <c r="A29" s="9" t="inlineStr"/>
       <c r="B29" s="10" t="inlineStr">
         <is>
@@ -3623,14 +4133,26 @@
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr"/>
-      <c r="N29" s="4" t="inlineStr"/>
-      <c r="O29" s="11" t="inlineStr"/>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>Blank — no image</t>
+        </is>
+      </c>
+      <c r="O29" s="11" t="inlineStr">
+        <is>
+          <t>1 source: ean-search.org</t>
+        </is>
+      </c>
       <c r="P29" s="11" t="inlineStr">
         <is>
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="Q29" s="19" t="inlineStr"/>
+      <c r="Q29" s="19" t="inlineStr">
+        <is>
+          <t>1 source: ean-search.org</t>
+        </is>
+      </c>
       <c r="R29" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -3642,7 +4164,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="132" customHeight="1">
+    <row r="30" ht="320" customHeight="1">
       <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="5" t="inlineStr">
         <is>
@@ -3699,8 +4221,16 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr"/>
-      <c r="N30" s="4" t="inlineStr"/>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cdiscount.com/pdt2/0/5/1/1/700x700/auc2009356289051/rw/hth-spa-nettoyant-spa-3521686010178.jpg</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
       <c r="O30" s="7" t="inlineStr">
         <is>
           <t>https://www.cdiscount.com/pdt2/0/5/1/1/700x700/auc2009356289051/rw/hth-spa-nettoyant-spa-3521686010178.jpg</t>
@@ -3711,7 +4241,11 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="Q30" s="19" t="inlineStr"/>
+      <c r="Q30" s="19" t="inlineStr">
+        <is>
+          <t>3 sources: barcodelookup.com, cdiscount.com, ean-search.org</t>
+        </is>
+      </c>
       <c r="R30" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -3723,7 +4257,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="132" customHeight="1">
+    <row r="31" ht="272" customHeight="1">
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="5" t="inlineStr">
         <is>
@@ -3780,7 +4314,11 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="M31" s="4" t="inlineStr"/>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>http://altruan.com/cdn/shop/files/SalinenPoolSalz25kgSack.png?v=1778597596</t>
+        </is>
+      </c>
       <c r="N31" s="4" t="n">
         <v>25</v>
       </c>
@@ -3810,7 +4348,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="132" customHeight="1">
+    <row r="32" ht="314" customHeight="1">
       <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="13" t="inlineStr">
         <is>
@@ -3867,8 +4405,16 @@
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="M32" s="4" t="inlineStr"/>
-      <c r="N32" s="4" t="inlineStr"/>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>https://images.barcodelookup.com/176692/1766920801-1.jpg</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>Verified — Barcode Lookup (barcode)</t>
+        </is>
+      </c>
       <c r="O32" s="7" t="inlineStr">
         <is>
           <t>https://images.barcodelookup.com/176692/1766920801-1.jpg</t>
@@ -3879,7 +4425,11 @@
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="Q32" s="19" t="inlineStr"/>
+      <c r="Q32" s="19" t="inlineStr">
+        <is>
+          <t>2 sources: barcodelookup, ean-search.org</t>
+        </is>
+      </c>
       <c r="R32" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -3891,7 +4441,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="132" customHeight="1">
+    <row r="33" ht="286" customHeight="1">
       <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="5" t="inlineStr">
         <is>
@@ -3948,8 +4498,16 @@
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="M33" s="4" t="inlineStr"/>
-      <c r="N33" s="4" t="inlineStr"/>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>https://images.barcodelookup.com/124722/1247228758-1.jpg</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>Verified — Barcode Lookup (barcode)</t>
+        </is>
+      </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
           <t>https://images.barcodelookup.com/124722/1247228758-1.jpg</t>
@@ -3960,7 +4518,11 @@
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="Q33" s="19" t="inlineStr"/>
+      <c r="Q33" s="19" t="inlineStr">
+        <is>
+          <t>2 sources: ean-search.org, eleonto.com</t>
+        </is>
+      </c>
       <c r="R33" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -3972,7 +4534,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="132" customHeight="1">
+    <row r="34" ht="188" customHeight="1">
       <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="5" t="inlineStr">
         <is>
@@ -4029,8 +4591,16 @@
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="M34" s="4" t="inlineStr"/>
-      <c r="N34" s="4" t="inlineStr"/>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>https://images.barcodelookup.com/124726/1247268298-1.jpg</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>Verified — Barcode Lookup (barcode)</t>
+        </is>
+      </c>
       <c r="O34" s="7" t="inlineStr">
         <is>
           <t>https://images.barcodelookup.com/124726/1247268298-1.jpg</t>
@@ -4041,7 +4611,11 @@
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="Q34" s="19" t="inlineStr"/>
+      <c r="Q34" s="19" t="inlineStr">
+        <is>
+          <t>1 source: piscinarium.com</t>
+        </is>
+      </c>
       <c r="R34" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -4053,7 +4627,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="132" customHeight="1">
+    <row r="35" ht="320" customHeight="1">
       <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="5" t="inlineStr">
         <is>
@@ -4122,7 +4696,11 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="Q35" s="19" t="inlineStr"/>
+      <c r="Q35" s="19" t="inlineStr">
+        <is>
+          <t>2 sources: ean-search.org, ecoperation.com</t>
+        </is>
+      </c>
       <c r="R35" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -4134,7 +4712,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="132" customHeight="1">
+    <row r="36" ht="320" customHeight="1">
       <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -4203,7 +4781,11 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="Q36" s="19" t="inlineStr"/>
+      <c r="Q36" s="19" t="inlineStr">
+        <is>
+          <t>2 sources: ean-search.org, ebay.de</t>
+        </is>
+      </c>
       <c r="R36" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -4215,7 +4797,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="132" customHeight="1">
+    <row r="37" ht="314" customHeight="1">
       <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="5" t="inlineStr">
         <is>
@@ -4272,8 +4854,16 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="M37" s="4" t="inlineStr"/>
-      <c r="N37" s="4" t="inlineStr"/>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>https://i.ebayimg.com/images/g/0e0AAOSweaplqO77/s-l400.jpg</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
       <c r="O37" s="7" t="inlineStr">
         <is>
           <t>https://i.ebayimg.com/images/g/0e0AAOSweaplqO77/s-l400.jpg</t>
@@ -4284,7 +4874,11 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="Q37" s="19" t="inlineStr"/>
+      <c r="Q37" s="19" t="inlineStr">
+        <is>
+          <t>2 sources: barcodelookup, ean-search.org</t>
+        </is>
+      </c>
       <c r="R37" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -4296,7 +4890,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="62" customHeight="1">
+    <row r="38" ht="272" customHeight="1">
       <c r="A38" s="9" t="inlineStr"/>
       <c r="B38" s="10" t="inlineStr">
         <is>
@@ -4363,7 +4957,11 @@
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="Q38" s="19" t="inlineStr"/>
+      <c r="Q38" s="19" t="inlineStr">
+        <is>
+          <t>1 source: ean-search.org</t>
+        </is>
+      </c>
       <c r="R38" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -4375,7 +4973,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="132" customHeight="1">
+    <row r="39" ht="320" customHeight="1">
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="5" t="inlineStr">
         <is>
@@ -4444,7 +5042,11 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="Q39" s="19" t="inlineStr"/>
+      <c r="Q39" s="19" t="inlineStr">
+        <is>
+          <t>3 sources: rozetka.pl, barcodelookup.com, ean-search.org</t>
+        </is>
+      </c>
       <c r="R39" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -4456,7 +5058,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="132" customHeight="1">
+    <row r="40" ht="320" customHeight="1">
       <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="5" t="inlineStr">
         <is>
@@ -4513,8 +5115,16 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="M40" s="4" t="inlineStr"/>
-      <c r="N40" s="4" t="inlineStr"/>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>https://media.carrefour.fr/medias/8f94161f683b4e589024a5b5ebaa6873/p_200x200/cad3db6a00ef414a804b9226119bae96_image.jpg</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
       <c r="O40" s="7" t="inlineStr">
         <is>
           <t>https://media.carrefour.fr/medias/8f94161f683b4e589024a5b5ebaa6873/p_200x200/cad3db6a00ef414a804b9226119bae96_image.jpg</t>
@@ -4525,7 +5135,11 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="Q40" s="19" t="inlineStr"/>
+      <c r="Q40" s="19" t="inlineStr">
+        <is>
+          <t>3 sources: barcodelookup.com, carrefour.fr, ean-search.org</t>
+        </is>
+      </c>
       <c r="R40" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -4537,11 +5151,11 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="62" customHeight="1">
-      <c r="A41" s="9" t="inlineStr"/>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+    <row r="41" ht="244" customHeight="1">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
@@ -4581,24 +5195,44 @@
       </c>
       <c r="J41" s="17" t="inlineStr">
         <is>
-          <t>filters, repeat-purchase, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr"/>
+          <t>filters, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>https://a.allegroimg.com/original/11923c/a79785a04d36aa54f0d87384f038/Filtracni-kartuse-Intex-D-3BTZ0023-SC828</t>
+        </is>
+      </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="M41" s="4" t="inlineStr"/>
-      <c r="N41" s="4" t="inlineStr"/>
-      <c r="O41" s="11" t="inlineStr"/>
-      <c r="P41" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
-        </is>
-      </c>
-      <c r="Q41" s="19" t="inlineStr"/>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>https://a.allegroimg.com/original/11923c/a79785a04d36aa54f0d87384f038/Filtracni-kartuse-Intex-D-3BTZ0023-SC828</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="O41" s="7" t="inlineStr">
+        <is>
+          <t>https://a.allegroimg.com/original/11923c/a79785a04d36aa54f0d87384f038/Filtracni-kartuse-Intex-D-3BTZ0023-SC828</t>
+        </is>
+      </c>
+      <c r="P41" s="7" t="inlineStr">
+        <is>
+          <t>Verified — barcode</t>
+        </is>
+      </c>
+      <c r="Q41" s="19" t="inlineStr">
+        <is>
+          <t>1 source: ean-search.org</t>
+        </is>
+      </c>
       <c r="R41" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -4610,7 +5244,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="132" customHeight="1">
+    <row r="42" ht="258" customHeight="1">
       <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="5" t="inlineStr">
         <is>
@@ -4681,7 +5315,11 @@
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="Q42" s="19" t="inlineStr"/>
+      <c r="Q42" s="19" t="inlineStr">
+        <is>
+          <t>2 sources: barcodelookup.com, ean-search.org</t>
+        </is>
+      </c>
       <c r="R42" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -4693,7 +5331,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="132" customHeight="1">
+    <row r="43" ht="272" customHeight="1">
       <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="5" t="inlineStr">
         <is>
@@ -4750,7 +5388,11 @@
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="M43" s="4" t="inlineStr"/>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>https://images.barcodelookup.com/17422/174228560-1.jpg</t>
+        </is>
+      </c>
       <c r="N43" s="4" t="n">
         <v>1</v>
       </c>
@@ -4764,7 +5406,11 @@
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="Q43" s="19" t="inlineStr"/>
+      <c r="Q43" s="19" t="inlineStr">
+        <is>
+          <t>2 sources: barcodelookup.com, ean-search.org</t>
+        </is>
+      </c>
       <c r="R43" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -4776,7 +5422,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="132" customHeight="1">
+    <row r="44" ht="300" customHeight="1">
       <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="5" t="inlineStr">
         <is>
@@ -4833,7 +5479,11 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="M44" s="4" t="inlineStr"/>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.north-spa.de/wp-content/uploads/2023/02/Produktbild-1-Bayrol-Randfix-07-l-4008367154134.jpg</t>
+        </is>
+      </c>
       <c r="N44" s="4" t="n">
         <v>0.7</v>
       </c>
@@ -4847,7 +5497,11 @@
           <t>Verified — barcode</t>
         </is>
       </c>
-      <c r="Q44" s="19" t="inlineStr"/>
+      <c r="Q44" s="19" t="inlineStr">
+        <is>
+          <t>2 sources: ean-search.org, north-spa.de</t>
+        </is>
+      </c>
       <c r="R44" s="8" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
@@ -4859,7 +5513,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="20" customHeight="1">
+    <row r="45" ht="34" customHeight="1">
       <c r="A45" s="9" t="inlineStr"/>
       <c r="B45" s="10" t="inlineStr">
         <is>
@@ -4878,7 +5532,11 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Blank — missing</t>
+        </is>
+      </c>
       <c r="H45" s="20" t="inlineStr">
         <is>
           <t>Blank — missing</t>
@@ -4897,7 +5555,11 @@
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr"/>
-      <c r="N45" s="4" t="inlineStr"/>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>Blank — no image</t>
+        </is>
+      </c>
       <c r="O45" s="11" t="inlineStr"/>
       <c r="P45" s="11" t="inlineStr">
         <is>
@@ -4941,71 +5603,83 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId100"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId89"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId101"/>
 </worksheet>
 </file>
 
@@ -5248,17 +5922,17 @@
           <t>A cartridge filter for hot tubs and swim spas, measuring 26.0 cm outer diameter, 13.0 cm bottom part, and 3.8 cm inner thread. Compatible with Darlly SC779 and 40372 codes, it captures dirt, grease, and fine particles to keep water clean.</t>
         </is>
       </c>
-      <c r="D2" s="22" t="inlineStr">
+      <c r="D2" s="30" t="inlineStr">
         <is>
           <t>Rising Dragon</t>
         </is>
       </c>
-      <c r="E2" s="22" t="inlineStr">
+      <c r="E2" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F2" s="22" t="inlineStr">
+      <c r="F2" s="30" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5268,71 +5942,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H2" s="22" t="inlineStr">
+      <c r="H2" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I2" s="22" t="inlineStr">
+      <c r="I2" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J2" s="22" t="inlineStr">
+      <c r="J2" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K2" s="22" t="inlineStr">
+      <c r="K2" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L2" s="22" t="inlineStr">
+      <c r="L2" s="30" t="inlineStr">
         <is>
           <t>RIS-FIL-2406</t>
         </is>
       </c>
-      <c r="M2" s="23" t="inlineStr">
+      <c r="M2" s="31" t="inlineStr">
         <is>
           <t>700175992406</t>
         </is>
       </c>
-      <c r="N2" s="24" t="inlineStr"/>
-      <c r="O2" s="24" t="inlineStr"/>
-      <c r="P2" s="24" t="inlineStr"/>
-      <c r="Q2" s="22" t="inlineStr">
+      <c r="N2" s="32" t="inlineStr"/>
+      <c r="O2" s="32" t="inlineStr"/>
+      <c r="P2" s="32" t="inlineStr"/>
+      <c r="Q2" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R2" s="22" t="inlineStr">
+      <c r="R2" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S2" s="22" t="inlineStr">
+      <c r="S2" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T2" s="22" t="inlineStr">
+      <c r="T2" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U2" s="22" t="inlineStr"/>
-      <c r="V2" s="22" t="inlineStr">
+      <c r="U2" s="30" t="inlineStr"/>
+      <c r="V2" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W2" s="22" t="inlineStr">
+      <c r="W2" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X2" s="22" t="inlineStr">
+      <c r="X2" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5342,7 +6016,7 @@
           <t>https://www.spa-components.com/user/shop/big/1473-1_filter-cartridge-sc779-rising-dragon-plastics--eago-whirlpools.jpg?ff=1&amp;x=1024&amp;y=768&amp;q=85&amp;ts=6720c4a0&amp;sg=161563f2</t>
         </is>
       </c>
-      <c r="Z2" s="22" t="inlineStr">
+      <c r="Z2" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5352,7 +6026,7 @@
           <t>Filter Cartridge SC779 - Rising Dragon Plastics, EAGO Whirlpools - Spa Components</t>
         </is>
       </c>
-      <c r="AB2" s="22" t="inlineStr">
+      <c r="AB2" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5364,10 +6038,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF2" s="22" t="inlineStr"/>
-      <c r="AG2" s="22" t="inlineStr"/>
-      <c r="AH2" s="22" t="inlineStr"/>
-      <c r="AI2" s="22" t="inlineStr"/>
+      <c r="AF2" s="30" t="inlineStr"/>
+      <c r="AG2" s="30" t="inlineStr"/>
+      <c r="AH2" s="30" t="inlineStr"/>
+      <c r="AI2" s="30" t="inlineStr"/>
     </row>
     <row r="3" ht="62" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
@@ -5385,13 +6059,13 @@
           <t>A twin pack of Size II replacement filter cartridges measuring 10.6 x 13.6 cm, designed for compatible pool and spa filtration systems. The fine lamellar structure delivers thorough water cleaning and the cartridges are easy to rinse clean.</t>
         </is>
       </c>
-      <c r="D3" s="22" t="inlineStr"/>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="D3" s="30" t="inlineStr"/>
+      <c r="E3" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F3" s="22" t="inlineStr">
+      <c r="F3" s="30" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5401,71 +6075,71 @@
           <t>filters, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H3" s="22" t="inlineStr">
+      <c r="H3" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J3" s="22" t="inlineStr">
+      <c r="J3" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L3" s="22" t="inlineStr">
+      <c r="L3" s="30" t="inlineStr">
         <is>
           <t>GEN-FIL-3615</t>
         </is>
       </c>
-      <c r="M3" s="23" t="inlineStr">
+      <c r="M3" s="31" t="inlineStr">
         <is>
           <t>6941607353615</t>
         </is>
       </c>
-      <c r="N3" s="24" t="inlineStr"/>
-      <c r="O3" s="24" t="inlineStr"/>
-      <c r="P3" s="24" t="inlineStr"/>
-      <c r="Q3" s="22" t="inlineStr">
+      <c r="N3" s="32" t="inlineStr"/>
+      <c r="O3" s="32" t="inlineStr"/>
+      <c r="P3" s="32" t="inlineStr"/>
+      <c r="Q3" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R3" s="22" t="inlineStr">
+      <c r="R3" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S3" s="22" t="inlineStr">
+      <c r="S3" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T3" s="22" t="inlineStr">
+      <c r="T3" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U3" s="22" t="inlineStr"/>
-      <c r="V3" s="22" t="inlineStr">
+      <c r="U3" s="30" t="inlineStr"/>
+      <c r="V3" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W3" s="22" t="inlineStr">
+      <c r="W3" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X3" s="22" t="inlineStr">
+      <c r="X3" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5475,7 +6149,7 @@
           <t>https://www.bestwaystore.de/media/c6/f8/ba/1756384660/6941607353615-main-jpg.jpg?ts=1756384660</t>
         </is>
       </c>
-      <c r="Z3" s="22" t="inlineStr">
+      <c r="Z3" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5485,7 +6159,7 @@
           <t>Filter cartridge Size II double pack, 10.6 x 13.6 cm | 58094_26</t>
         </is>
       </c>
-      <c r="AB3" s="22" t="inlineStr">
+      <c r="AB3" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5497,14 +6171,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF3" s="22" t="inlineStr"/>
-      <c r="AG3" s="22" t="inlineStr"/>
-      <c r="AH3" s="22" t="inlineStr">
+      <c r="AF3" s="30" t="inlineStr"/>
+      <c r="AG3" s="30" t="inlineStr"/>
+      <c r="AH3" s="30" t="inlineStr">
         <is>
           <t>10.6cm</t>
         </is>
       </c>
-      <c r="AI3" s="22" t="inlineStr">
+      <c r="AI3" s="30" t="inlineStr">
         <is>
           <t>13.6cm</t>
         </is>
@@ -5526,17 +6200,17 @@
           <t>A single Flowclear Size 3 replacement filter cartridge for compatible Bestway pool filtration systems, featuring a fine lamellar structure that traps deposits and dirt effectively. Easy to clean and straightforward to swap out when routine maintenance is due.</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>Bestway</t>
         </is>
       </c>
-      <c r="E4" s="22" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F4" s="22" t="inlineStr">
+      <c r="F4" s="30" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5546,71 +6220,71 @@
           <t>filters, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H4" s="22" t="inlineStr">
+      <c r="H4" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I4" s="22" t="inlineStr">
+      <c r="I4" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J4" s="22" t="inlineStr">
+      <c r="J4" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K4" s="22" t="inlineStr">
+      <c r="K4" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L4" s="22" t="inlineStr">
+      <c r="L4" s="30" t="inlineStr">
         <is>
           <t>BES-FIL-3592</t>
         </is>
       </c>
-      <c r="M4" s="23" t="inlineStr">
+      <c r="M4" s="31" t="inlineStr">
         <is>
           <t>6941607353592</t>
         </is>
       </c>
-      <c r="N4" s="24" t="inlineStr"/>
-      <c r="O4" s="24" t="inlineStr"/>
-      <c r="P4" s="24" t="inlineStr"/>
-      <c r="Q4" s="22" t="inlineStr">
+      <c r="N4" s="32" t="inlineStr"/>
+      <c r="O4" s="32" t="inlineStr"/>
+      <c r="P4" s="32" t="inlineStr"/>
+      <c r="Q4" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R4" s="22" t="inlineStr">
+      <c r="R4" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S4" s="22" t="inlineStr">
+      <c r="S4" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T4" s="22" t="inlineStr">
+      <c r="T4" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U4" s="22" t="inlineStr"/>
-      <c r="V4" s="22" t="inlineStr">
+      <c r="U4" s="30" t="inlineStr"/>
+      <c r="V4" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W4" s="22" t="inlineStr">
+      <c r="W4" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X4" s="22" t="inlineStr">
+      <c r="X4" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5620,7 +6294,7 @@
           <t>https://ap.nice-cdn.com/upload/image/product/large/default/bestway-flowclear-filter-cartridge-size-3-1-item-638140-en.jpg</t>
         </is>
       </c>
-      <c r="Z4" s="22" t="inlineStr">
+      <c r="Z4" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5630,7 +6304,7 @@
           <t>Bestway Flowclear™ Filter Cartridge Size 3, 1 item</t>
         </is>
       </c>
-      <c r="AB4" s="22" t="inlineStr">
+      <c r="AB4" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5642,10 +6316,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF4" s="22" t="inlineStr"/>
-      <c r="AG4" s="22" t="inlineStr"/>
-      <c r="AH4" s="22" t="inlineStr"/>
-      <c r="AI4" s="22" t="inlineStr"/>
+      <c r="AF4" s="30" t="inlineStr"/>
+      <c r="AG4" s="30" t="inlineStr"/>
+      <c r="AH4" s="30" t="inlineStr"/>
+      <c r="AI4" s="30" t="inlineStr"/>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="17" t="inlineStr">
@@ -5663,17 +6337,17 @@
           <t>A two-pack of compatible hot tub and spa cartridge filters corresponding to Unicel C-4335, Pleatco PRB35-IN, and Filbur FC-2385 references. A handy spare-pair to keep on hand so your tub is never without a fresh filter.</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="30" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F5" s="30" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5683,71 +6357,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr">
+      <c r="H5" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="I5" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J5" s="22" t="inlineStr">
+      <c r="J5" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K5" s="22" t="inlineStr">
+      <c r="K5" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L5" s="22" t="inlineStr">
+      <c r="L5" s="30" t="inlineStr">
         <is>
           <t>DAR-FIL-1669</t>
         </is>
       </c>
-      <c r="M5" s="23" t="inlineStr">
+      <c r="M5" s="31" t="inlineStr">
         <is>
           <t>700175991669</t>
         </is>
       </c>
-      <c r="N5" s="24" t="inlineStr"/>
-      <c r="O5" s="24" t="inlineStr"/>
-      <c r="P5" s="24" t="inlineStr"/>
-      <c r="Q5" s="22" t="inlineStr">
+      <c r="N5" s="32" t="inlineStr"/>
+      <c r="O5" s="32" t="inlineStr"/>
+      <c r="P5" s="32" t="inlineStr"/>
+      <c r="Q5" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R5" s="22" t="inlineStr">
+      <c r="R5" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S5" s="22" t="inlineStr">
+      <c r="S5" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T5" s="22" t="inlineStr">
+      <c r="T5" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U5" s="22" t="inlineStr"/>
-      <c r="V5" s="22" t="inlineStr">
+      <c r="U5" s="30" t="inlineStr"/>
+      <c r="V5" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W5" s="22" t="inlineStr">
+      <c r="W5" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X5" s="22" t="inlineStr">
+      <c r="X5" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5757,7 +6431,7 @@
           <t>https://images.barcodelookup.com/29361/293617958-1.jpg</t>
         </is>
       </c>
-      <c r="Z5" s="22" t="inlineStr">
+      <c r="Z5" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5767,7 +6441,7 @@
           <t>Darlly Hot Tub Spa Filter SC705 40353 Compatible with Unicel C-4335 PRB35-IN Filbur FC-2385 2 Pack</t>
         </is>
       </c>
-      <c r="AB5" s="22" t="inlineStr">
+      <c r="AB5" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5779,10 +6453,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF5" s="22" t="inlineStr"/>
-      <c r="AG5" s="22" t="inlineStr"/>
-      <c r="AH5" s="22" t="inlineStr"/>
-      <c r="AI5" s="22" t="inlineStr"/>
+      <c r="AF5" s="30" t="inlineStr"/>
+      <c r="AG5" s="30" t="inlineStr"/>
+      <c r="AH5" s="30" t="inlineStr"/>
+      <c r="AI5" s="30" t="inlineStr"/>
     </row>
     <row r="6" ht="62" customHeight="1">
       <c r="A6" s="17" t="inlineStr">
@@ -5800,13 +6474,13 @@
           <t>A single Size IV replacement filter cartridge measuring 14.2 x 25.4 cm, compatible with Bestway filter pump 58391 (9,463 l/h). Its deep-fold, fine-structure media delivers thorough water cleaning and can be rinsed clean with minimal effort.</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr"/>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr"/>
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F6" s="22" t="inlineStr">
+      <c r="F6" s="30" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5816,71 +6490,71 @@
           <t>filters, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H6" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="J6" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L6" s="22" t="inlineStr">
+      <c r="L6" s="30" t="inlineStr">
         <is>
           <t>GEN-FIL-3622</t>
         </is>
       </c>
-      <c r="M6" s="23" t="inlineStr">
+      <c r="M6" s="31" t="inlineStr">
         <is>
           <t>6941607353622</t>
         </is>
       </c>
-      <c r="N6" s="24" t="inlineStr"/>
-      <c r="O6" s="24" t="inlineStr"/>
-      <c r="P6" s="24" t="inlineStr"/>
-      <c r="Q6" s="22" t="inlineStr">
+      <c r="N6" s="32" t="inlineStr"/>
+      <c r="O6" s="32" t="inlineStr"/>
+      <c r="P6" s="32" t="inlineStr"/>
+      <c r="Q6" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R6" s="22" t="inlineStr">
+      <c r="R6" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S6" s="22" t="inlineStr">
+      <c r="S6" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T6" s="22" t="inlineStr">
+      <c r="T6" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U6" s="22" t="inlineStr"/>
-      <c r="V6" s="22" t="inlineStr">
+      <c r="U6" s="30" t="inlineStr"/>
+      <c r="V6" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W6" s="22" t="inlineStr">
+      <c r="W6" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X6" s="22" t="inlineStr">
+      <c r="X6" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5890,7 +6564,7 @@
           <t>https://www.bestwaystore.de/media/53/6c/e9/1756384676/6941607353622-main-jpg.jpg?ts=1756384676</t>
         </is>
       </c>
-      <c r="Z6" s="22" t="inlineStr">
+      <c r="Z6" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5900,7 +6574,7 @@
           <t>Filter cartridge Size IV 14.2 x 25.4 cm | 58095_26</t>
         </is>
       </c>
-      <c r="AB6" s="22" t="inlineStr">
+      <c r="AB6" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5912,14 +6586,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF6" s="22" t="inlineStr"/>
-      <c r="AG6" s="22" t="inlineStr"/>
-      <c r="AH6" s="22" t="inlineStr">
+      <c r="AF6" s="30" t="inlineStr"/>
+      <c r="AG6" s="30" t="inlineStr"/>
+      <c r="AH6" s="30" t="inlineStr">
         <is>
           <t>14.2cm</t>
         </is>
       </c>
-      <c r="AI6" s="22" t="inlineStr">
+      <c r="AI6" s="30" t="inlineStr">
         <is>
           <t>25.4cm</t>
         </is>
@@ -5941,17 +6615,17 @@
           <t>A pair of Darlly spa filter cartridges in the SC726 reference, also cross-referenced as Unicel C-4401 and Pleatco PRB17.5SF PR. Buying in pairs means a fresh replacement is always ready when it is time to swap.</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="30" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5961,71 +6635,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H7" s="22" t="inlineStr">
+      <c r="H7" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I7" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J7" s="22" t="inlineStr">
+      <c r="J7" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K7" s="22" t="inlineStr">
+      <c r="K7" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L7" s="22" t="inlineStr">
+      <c r="L7" s="30" t="inlineStr">
         <is>
           <t>DAR-FIL-1874</t>
         </is>
       </c>
-      <c r="M7" s="23" t="inlineStr">
+      <c r="M7" s="31" t="inlineStr">
         <is>
           <t>700175991874</t>
         </is>
       </c>
-      <c r="N7" s="24" t="inlineStr"/>
-      <c r="O7" s="24" t="inlineStr"/>
-      <c r="P7" s="24" t="inlineStr"/>
-      <c r="Q7" s="22" t="inlineStr">
+      <c r="N7" s="32" t="inlineStr"/>
+      <c r="O7" s="32" t="inlineStr"/>
+      <c r="P7" s="32" t="inlineStr"/>
+      <c r="Q7" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R7" s="22" t="inlineStr">
+      <c r="R7" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S7" s="22" t="inlineStr">
+      <c r="S7" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T7" s="22" t="inlineStr">
+      <c r="T7" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U7" s="22" t="inlineStr"/>
-      <c r="V7" s="22" t="inlineStr">
+      <c r="U7" s="30" t="inlineStr"/>
+      <c r="V7" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W7" s="22" t="inlineStr">
+      <c r="W7" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X7" s="22" t="inlineStr">
+      <c r="X7" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6035,7 +6709,7 @@
           <t>https://images.barcodelookup.com/4378/43786454-1.jpg</t>
         </is>
       </c>
-      <c r="Z7" s="22" t="inlineStr">
+      <c r="Z7" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6045,7 +6719,7 @@
           <t>Darlly Spa Filter C-4401, PRB17.5SF PR, SC726 (Pair)</t>
         </is>
       </c>
-      <c r="AB7" s="22" t="inlineStr">
+      <c r="AB7" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6057,10 +6731,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF7" s="22" t="inlineStr"/>
-      <c r="AG7" s="22" t="inlineStr"/>
-      <c r="AH7" s="22" t="inlineStr"/>
-      <c r="AI7" s="22" t="inlineStr"/>
+      <c r="AF7" s="30" t="inlineStr"/>
+      <c r="AG7" s="30" t="inlineStr"/>
+      <c r="AH7" s="30" t="inlineStr"/>
+      <c r="AI7" s="30" t="inlineStr"/>
     </row>
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="17" t="inlineStr">
@@ -6078,17 +6752,17 @@
           <t>A replacement spa filter cartridge compatible with Arctic, Beachcomber, Canadian, Hydropool and Jacuzzi spas, sold under cross-reference codes including Unicel C-4950, Pleatco PRB50-IN and Darlly 40506. It keeps hot tub water clean by trapping debris and particles as water cycles through the filtration system.</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F8" s="30" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6098,71 +6772,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H8" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I8" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J8" s="22" t="inlineStr">
+      <c r="J8" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K8" s="22" t="inlineStr">
+      <c r="K8" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L8" s="22" t="inlineStr">
+      <c r="L8" s="30" t="inlineStr">
         <is>
           <t>DAR-FIL-1676</t>
         </is>
       </c>
-      <c r="M8" s="23" t="inlineStr">
+      <c r="M8" s="31" t="inlineStr">
         <is>
           <t>700175991676</t>
         </is>
       </c>
-      <c r="N8" s="24" t="inlineStr"/>
-      <c r="O8" s="24" t="inlineStr"/>
-      <c r="P8" s="24" t="inlineStr"/>
-      <c r="Q8" s="22" t="inlineStr">
+      <c r="N8" s="32" t="inlineStr"/>
+      <c r="O8" s="32" t="inlineStr"/>
+      <c r="P8" s="32" t="inlineStr"/>
+      <c r="Q8" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R8" s="22" t="inlineStr">
+      <c r="R8" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S8" s="22" t="inlineStr">
+      <c r="S8" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T8" s="22" t="inlineStr">
+      <c r="T8" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U8" s="22" t="inlineStr"/>
-      <c r="V8" s="22" t="inlineStr">
+      <c r="U8" s="30" t="inlineStr"/>
+      <c r="V8" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W8" s="22" t="inlineStr">
+      <c r="W8" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X8" s="22" t="inlineStr">
+      <c r="X8" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6172,7 +6846,7 @@
           <t>https://images.barcodelookup.com/4469/44699532-1.jpg</t>
         </is>
       </c>
-      <c r="Z8" s="22" t="inlineStr">
+      <c r="Z8" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6182,7 +6856,7 @@
           <t>Hot Tub Filter Unicel C4950 / C-4950 50' Spa Cartridge Pleatco PRB501N Darlly 40506 for Arctic, Beachcomber, Canadian,…</t>
         </is>
       </c>
-      <c r="AB8" s="22" t="inlineStr">
+      <c r="AB8" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6194,10 +6868,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF8" s="22" t="inlineStr"/>
-      <c r="AG8" s="22" t="inlineStr"/>
-      <c r="AH8" s="22" t="inlineStr"/>
-      <c r="AI8" s="22" t="inlineStr"/>
+      <c r="AF8" s="30" t="inlineStr"/>
+      <c r="AG8" s="30" t="inlineStr"/>
+      <c r="AH8" s="30" t="inlineStr"/>
+      <c r="AI8" s="30" t="inlineStr"/>
     </row>
     <row r="9" ht="76" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
@@ -6215,13 +6889,13 @@
           <t>A square inflatable hot tub for up to four people, with an overall outer diameter of 2.45 m and a structure measuring 1.75 x 1.75 x 0.71 m, built from high-resistance polyester for good rigidity and durability. The packaged weight is 64.92 kg, so you will want a helper on delivery day.</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr"/>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="D9" s="30" t="inlineStr"/>
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="30" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -6231,75 +6905,75 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr">
+      <c r="H9" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J9" s="22" t="inlineStr">
+      <c r="J9" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L9" s="22" t="inlineStr">
+      <c r="L9" s="30" t="inlineStr">
         <is>
           <t>GEN-SPA-3395</t>
         </is>
       </c>
-      <c r="M9" s="23" t="inlineStr">
+      <c r="M9" s="31" t="inlineStr">
         <is>
           <t>6941057423395</t>
         </is>
       </c>
-      <c r="N9" s="24" t="inlineStr"/>
-      <c r="O9" s="24" t="inlineStr"/>
-      <c r="P9" s="24" t="inlineStr"/>
-      <c r="Q9" s="22" t="inlineStr">
+      <c r="N9" s="32" t="inlineStr"/>
+      <c r="O9" s="32" t="inlineStr"/>
+      <c r="P9" s="32" t="inlineStr"/>
+      <c r="Q9" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R9" s="22" t="inlineStr">
+      <c r="R9" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S9" s="22" t="inlineStr">
+      <c r="S9" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T9" s="22" t="inlineStr">
+      <c r="T9" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U9" s="22" t="inlineStr">
+      <c r="U9" s="30" t="inlineStr">
         <is>
           <t>64920</t>
         </is>
       </c>
-      <c r="V9" s="22" t="inlineStr">
+      <c r="V9" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W9" s="22" t="inlineStr">
+      <c r="W9" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X9" s="22" t="inlineStr">
+      <c r="X9" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6309,7 +6983,7 @@
           <t>https://media.intex.fr/7743-large_default_x2/28464ex-spa-gonflable-calacatta-4-places.jpg</t>
         </is>
       </c>
-      <c r="Z9" s="22" t="inlineStr">
+      <c r="Z9" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6319,7 +6993,7 @@
           <t>Calacatta 4-person Inflatable Spa</t>
         </is>
       </c>
-      <c r="AB9" s="22" t="inlineStr">
+      <c r="AB9" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6331,18 +7005,18 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF9" s="22" t="inlineStr"/>
-      <c r="AG9" s="22" t="inlineStr">
+      <c r="AF9" s="30" t="inlineStr"/>
+      <c r="AG9" s="30" t="inlineStr">
         <is>
           <t>175.0cm</t>
         </is>
       </c>
-      <c r="AH9" s="22" t="inlineStr">
+      <c r="AH9" s="30" t="inlineStr">
         <is>
           <t>175.0cm</t>
         </is>
       </c>
-      <c r="AI9" s="22" t="inlineStr">
+      <c r="AI9" s="30" t="inlineStr">
         <is>
           <t>71.0cm</t>
         </is>
@@ -6364,17 +7038,17 @@
           <t>A 3.0 kg tub of hth stabiliser granules for outdoor swimming pools, used to protect chlorine from UV degradation and extend its effectiveness. A reliable way to get more mileage from your sanitiser on sunny days.</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="30" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" s="30" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -6384,75 +7058,75 @@
           <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H10" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="I10" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J10" s="22" t="inlineStr">
+      <c r="J10" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K10" s="22" t="inlineStr">
+      <c r="K10" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L10" s="22" t="inlineStr">
+      <c r="L10" s="30" t="inlineStr">
         <is>
           <t>HTH-CHM-5716</t>
         </is>
       </c>
-      <c r="M10" s="23" t="inlineStr">
+      <c r="M10" s="31" t="inlineStr">
         <is>
           <t>3521686005716</t>
         </is>
       </c>
-      <c r="N10" s="24" t="inlineStr"/>
-      <c r="O10" s="24" t="inlineStr"/>
-      <c r="P10" s="24" t="inlineStr"/>
-      <c r="Q10" s="22" t="inlineStr">
+      <c r="N10" s="32" t="inlineStr"/>
+      <c r="O10" s="32" t="inlineStr"/>
+      <c r="P10" s="32" t="inlineStr"/>
+      <c r="Q10" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R10" s="22" t="inlineStr">
+      <c r="R10" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S10" s="22" t="inlineStr">
+      <c r="S10" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T10" s="22" t="inlineStr">
+      <c r="T10" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U10" s="22" t="inlineStr">
+      <c r="U10" s="30" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="V10" s="22" t="inlineStr">
+      <c r="V10" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W10" s="22" t="inlineStr">
+      <c r="W10" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X10" s="22" t="inlineStr">
+      <c r="X10" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6462,7 +7136,7 @@
           <t>https://images.barcodelookup.com/12027/120276177-1.jpg</t>
         </is>
       </c>
-      <c r="Z10" s="22" t="inlineStr">
+      <c r="Z10" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6472,7 +7146,7 @@
           <t>Hth Stabilizer Granulat 3,0 Kg</t>
         </is>
       </c>
-      <c r="AB10" s="22" t="inlineStr">
+      <c r="AB10" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6484,10 +7158,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF10" s="22" t="inlineStr"/>
-      <c r="AG10" s="22" t="inlineStr"/>
-      <c r="AH10" s="22" t="inlineStr"/>
-      <c r="AI10" s="22" t="inlineStr"/>
+      <c r="AF10" s="30" t="inlineStr"/>
+      <c r="AG10" s="30" t="inlineStr"/>
+      <c r="AH10" s="30" t="inlineStr"/>
+      <c r="AI10" s="30" t="inlineStr"/>
     </row>
     <row r="11" ht="62" customHeight="1">
       <c r="A11" s="17" t="inlineStr">
@@ -6505,99 +7179,111 @@
           <t>A 1-litre bottle of hth Spa Antikalk, formulated to prevent and remove limescale in spa and hot tub water. Keeping scale under control helps protect internal components and maintain water clarity.</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>spa-hot-tub, considered-purchase, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="H11" s="22" t="inlineStr">
+          <t>spa-hot-tub, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
+        </is>
+      </c>
+      <c r="H11" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="I11" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J11" s="22" t="inlineStr">
+      <c r="J11" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K11" s="22" t="inlineStr">
+      <c r="K11" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L11" s="22" t="inlineStr">
+      <c r="L11" s="30" t="inlineStr">
         <is>
           <t>HTH-SPA-0194</t>
         </is>
       </c>
-      <c r="M11" s="23" t="inlineStr">
+      <c r="M11" s="31" t="inlineStr">
         <is>
           <t>3521684700194</t>
         </is>
       </c>
-      <c r="N11" s="24" t="inlineStr"/>
-      <c r="O11" s="24" t="inlineStr"/>
-      <c r="P11" s="24" t="inlineStr"/>
-      <c r="Q11" s="22" t="inlineStr">
+      <c r="N11" s="32" t="inlineStr"/>
+      <c r="O11" s="32" t="inlineStr"/>
+      <c r="P11" s="32" t="inlineStr"/>
+      <c r="Q11" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R11" s="22" t="inlineStr">
+      <c r="R11" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S11" s="22" t="inlineStr">
+      <c r="S11" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T11" s="22" t="inlineStr">
+      <c r="T11" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U11" s="22" t="inlineStr"/>
-      <c r="V11" s="22" t="inlineStr">
+      <c r="U11" s="30" t="inlineStr"/>
+      <c r="V11" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W11" s="22" t="inlineStr">
+      <c r="W11" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X11" s="22" t="inlineStr">
+      <c r="X11" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Y11" s="17" t="inlineStr"/>
-      <c r="Z11" s="22" t="inlineStr"/>
-      <c r="AA11" s="17" t="inlineStr"/>
-      <c r="AB11" s="22" t="inlineStr">
+      <c r="Y11" s="17" t="inlineStr">
+        <is>
+          <t>https://www.north-spa.de/wp-content/uploads/2025/02/Produktbild-1-hth-SPA-ANTIKALK-1-l-3521684700194-360x360.jpg</t>
+        </is>
+      </c>
+      <c r="Z11" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="17" t="inlineStr">
+        <is>
+          <t>1 l - hth® Spa ANTIKALK</t>
+        </is>
+      </c>
+      <c r="AB11" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6609,10 +7295,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF11" s="22" t="inlineStr"/>
-      <c r="AG11" s="22" t="inlineStr"/>
-      <c r="AH11" s="22" t="inlineStr"/>
-      <c r="AI11" s="22" t="inlineStr"/>
+      <c r="AF11" s="30" t="inlineStr"/>
+      <c r="AG11" s="30" t="inlineStr"/>
+      <c r="AH11" s="30" t="inlineStr"/>
+      <c r="AI11" s="30" t="inlineStr"/>
     </row>
     <row r="12" ht="62" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
@@ -6630,13 +7316,13 @@
           <t>A round, olive-green inflatable spa designed to seat up to eight people comfortably, with a maximum water temperature of 40°C. Five accessories are included in the box, so there is plenty to get started with straight away.</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr"/>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="D12" s="30" t="inlineStr"/>
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="30" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -6646,71 +7332,71 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="J12" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L12" s="22" t="inlineStr">
+      <c r="L12" s="30" t="inlineStr">
         <is>
           <t>GEN-SPA-9274</t>
         </is>
       </c>
-      <c r="M12" s="23" t="inlineStr">
+      <c r="M12" s="31" t="inlineStr">
         <is>
           <t>6941057429274</t>
         </is>
       </c>
-      <c r="N12" s="24" t="inlineStr"/>
-      <c r="O12" s="24" t="inlineStr"/>
-      <c r="P12" s="24" t="inlineStr"/>
-      <c r="Q12" s="22" t="inlineStr">
+      <c r="N12" s="32" t="inlineStr"/>
+      <c r="O12" s="32" t="inlineStr"/>
+      <c r="P12" s="32" t="inlineStr"/>
+      <c r="Q12" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R12" s="22" t="inlineStr">
+      <c r="R12" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S12" s="22" t="inlineStr">
+      <c r="S12" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T12" s="22" t="inlineStr">
+      <c r="T12" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U12" s="22" t="inlineStr"/>
-      <c r="V12" s="22" t="inlineStr">
+      <c r="U12" s="30" t="inlineStr"/>
+      <c r="V12" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W12" s="22" t="inlineStr">
+      <c r="W12" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X12" s="22" t="inlineStr">
+      <c r="X12" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6720,7 +7406,7 @@
           <t>https://media.intex.fr/11990-large_default_x2/28412np-spa-gonflable-olive-8-places.jpg</t>
         </is>
       </c>
-      <c r="Z12" s="22" t="inlineStr">
+      <c r="Z12" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6730,7 +7416,7 @@
           <t>Olive 8-person Inflatable Spa</t>
         </is>
       </c>
-      <c r="AB12" s="22" t="inlineStr">
+      <c r="AB12" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6742,10 +7428,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF12" s="22" t="inlineStr"/>
-      <c r="AG12" s="22" t="inlineStr"/>
-      <c r="AH12" s="22" t="inlineStr"/>
-      <c r="AI12" s="22" t="inlineStr"/>
+      <c r="AF12" s="30" t="inlineStr"/>
+      <c r="AG12" s="30" t="inlineStr"/>
+      <c r="AH12" s="30" t="inlineStr"/>
+      <c r="AI12" s="30" t="inlineStr"/>
     </row>
     <row r="13" ht="62" customHeight="1">
       <c r="A13" s="17" t="inlineStr">
@@ -6763,17 +7449,17 @@
           <t>A Darlly SC750 replacement cartridge filter compatible with Arctic, Fonteyn, Rota, and Strong Spa hot tubs, among others. A straightforward like-for-like swap to keep your spa water flowing clean.</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="30" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6783,71 +7469,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H13" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="I13" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J13" s="22" t="inlineStr">
+      <c r="J13" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K13" s="22" t="inlineStr">
+      <c r="K13" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L13" s="22" t="inlineStr">
+      <c r="L13" s="30" t="inlineStr">
         <is>
           <t>DAR-FIL-2116</t>
         </is>
       </c>
-      <c r="M13" s="23" t="inlineStr">
+      <c r="M13" s="31" t="inlineStr">
         <is>
           <t>700175992116</t>
         </is>
       </c>
-      <c r="N13" s="24" t="inlineStr"/>
-      <c r="O13" s="24" t="inlineStr"/>
-      <c r="P13" s="24" t="inlineStr"/>
-      <c r="Q13" s="22" t="inlineStr">
+      <c r="N13" s="32" t="inlineStr"/>
+      <c r="O13" s="32" t="inlineStr"/>
+      <c r="P13" s="32" t="inlineStr"/>
+      <c r="Q13" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R13" s="22" t="inlineStr">
+      <c r="R13" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S13" s="22" t="inlineStr">
+      <c r="S13" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T13" s="22" t="inlineStr">
+      <c r="T13" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U13" s="22" t="inlineStr"/>
-      <c r="V13" s="22" t="inlineStr">
+      <c r="U13" s="30" t="inlineStr"/>
+      <c r="V13" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W13" s="22" t="inlineStr">
+      <c r="W13" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X13" s="22" t="inlineStr">
+      <c r="X13" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6857,7 +7543,7 @@
           <t>https://images.barcodelookup.com/29338/293384728-1.jpg</t>
         </is>
       </c>
-      <c r="Z13" s="22" t="inlineStr">
+      <c r="Z13" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6867,7 +7553,7 @@
           <t>SC750 Filter Replacement Filter Lamellar Filter Arctic Fonteyn Rota Strong Spa - Darlly</t>
         </is>
       </c>
-      <c r="AB13" s="22" t="inlineStr">
+      <c r="AB13" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6879,10 +7565,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF13" s="22" t="inlineStr"/>
-      <c r="AG13" s="22" t="inlineStr"/>
-      <c r="AH13" s="22" t="inlineStr"/>
-      <c r="AI13" s="22" t="inlineStr"/>
+      <c r="AF13" s="30" t="inlineStr"/>
+      <c r="AG13" s="30" t="inlineStr"/>
+      <c r="AH13" s="30" t="inlineStr"/>
+      <c r="AI13" s="30" t="inlineStr"/>
     </row>
     <row r="14" ht="62" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
@@ -6900,99 +7586,111 @@
           <t>SpaBalancer Clean and Refresh is a spa water treatment product supplied with a sprayer for easy application. It is designed to keep spa water fresh and clean as part of a regular maintenance routine.</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="30" t="inlineStr">
         <is>
           <t>SpaBalancer</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" s="30" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>cleaning, add-on, multi-source-confirmed, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="H14" s="22" t="inlineStr">
+          <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
+        </is>
+      </c>
+      <c r="H14" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="I14" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J14" s="22" t="inlineStr">
+      <c r="J14" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K14" s="22" t="inlineStr">
+      <c r="K14" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L14" s="22" t="inlineStr">
+      <c r="L14" s="30" t="inlineStr">
         <is>
           <t>SPA-CLN-0117</t>
         </is>
       </c>
-      <c r="M14" s="23" t="inlineStr">
+      <c r="M14" s="31" t="inlineStr">
         <is>
           <t>4260374980117</t>
         </is>
       </c>
-      <c r="N14" s="24" t="inlineStr"/>
-      <c r="O14" s="24" t="inlineStr"/>
-      <c r="P14" s="24" t="inlineStr"/>
-      <c r="Q14" s="22" t="inlineStr">
+      <c r="N14" s="32" t="inlineStr"/>
+      <c r="O14" s="32" t="inlineStr"/>
+      <c r="P14" s="32" t="inlineStr"/>
+      <c r="Q14" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R14" s="22" t="inlineStr">
+      <c r="R14" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S14" s="22" t="inlineStr">
+      <c r="S14" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T14" s="22" t="inlineStr">
+      <c r="T14" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U14" s="22" t="inlineStr"/>
-      <c r="V14" s="22" t="inlineStr">
+      <c r="U14" s="30" t="inlineStr"/>
+      <c r="V14" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W14" s="22" t="inlineStr">
+      <c r="W14" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X14" s="22" t="inlineStr">
+      <c r="X14" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Y14" s="17" t="inlineStr"/>
-      <c r="Z14" s="22" t="inlineStr"/>
-      <c r="AA14" s="17" t="inlineStr"/>
-      <c r="AB14" s="22" t="inlineStr">
+      <c r="Y14" s="17" t="inlineStr">
+        <is>
+          <t>https://www.spabalancer.ch/media/ae/20/d2/1728651174/sb111_clean-refresh_freigestellt.png?ts=1777362921</t>
+        </is>
+      </c>
+      <c r="Z14" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="17" t="inlineStr">
+        <is>
+          <t>SpaBalancer Clean &amp; Refresh (+ sprayer)</t>
+        </is>
+      </c>
+      <c r="AB14" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7004,10 +7702,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF14" s="22" t="inlineStr"/>
-      <c r="AG14" s="22" t="inlineStr"/>
-      <c r="AH14" s="22" t="inlineStr"/>
-      <c r="AI14" s="22" t="inlineStr"/>
+      <c r="AF14" s="30" t="inlineStr"/>
+      <c r="AG14" s="30" t="inlineStr"/>
+      <c r="AH14" s="30" t="inlineStr"/>
+      <c r="AI14" s="30" t="inlineStr"/>
     </row>
     <row r="15" ht="62" customHeight="1">
       <c r="A15" s="17" t="inlineStr">
@@ -7025,17 +7723,17 @@
           <t>A pack of 500 DPD 1 reagent tablets for use with the Water-ID photometer, measuring free chlorine levels in pool or spa water. Having a full pack to hand means you will not run short mid-season.</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="30" t="inlineStr">
         <is>
           <t>Water-i.d.</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" s="30" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -7045,79 +7743,79 @@
           <t>test-measure, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H15" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="I15" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J15" s="22" t="inlineStr">
+      <c r="J15" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K15" s="22" t="inlineStr">
+      <c r="K15" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L15" s="22" t="inlineStr">
+      <c r="L15" s="30" t="inlineStr">
         <is>
           <t>WAT-TST-1702</t>
         </is>
       </c>
-      <c r="M15" s="23" t="inlineStr">
+      <c r="M15" s="31" t="inlineStr">
         <is>
           <t>4260431461702</t>
         </is>
       </c>
-      <c r="N15" s="24" t="inlineStr"/>
-      <c r="O15" s="24" t="inlineStr"/>
-      <c r="P15" s="24" t="inlineStr"/>
-      <c r="Q15" s="22" t="inlineStr">
+      <c r="N15" s="32" t="inlineStr"/>
+      <c r="O15" s="32" t="inlineStr"/>
+      <c r="P15" s="32" t="inlineStr"/>
+      <c r="Q15" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R15" s="22" t="inlineStr">
+      <c r="R15" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S15" s="22" t="inlineStr">
+      <c r="S15" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T15" s="22" t="inlineStr">
+      <c r="T15" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U15" s="22" t="inlineStr"/>
-      <c r="V15" s="22" t="inlineStr">
+      <c r="U15" s="30" t="inlineStr"/>
+      <c r="V15" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W15" s="22" t="inlineStr">
+      <c r="W15" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X15" s="22" t="inlineStr">
+      <c r="X15" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y15" s="17" t="inlineStr"/>
-      <c r="Z15" s="22" t="inlineStr"/>
+      <c r="Z15" s="30" t="inlineStr"/>
       <c r="AA15" s="17" t="inlineStr"/>
-      <c r="AB15" s="22" t="inlineStr">
+      <c r="AB15" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7129,10 +7827,10 @@
           <t>Pool Accessories</t>
         </is>
       </c>
-      <c r="AF15" s="22" t="inlineStr"/>
-      <c r="AG15" s="22" t="inlineStr"/>
-      <c r="AH15" s="22" t="inlineStr"/>
-      <c r="AI15" s="22" t="inlineStr"/>
+      <c r="AF15" s="30" t="inlineStr"/>
+      <c r="AG15" s="30" t="inlineStr"/>
+      <c r="AH15" s="30" t="inlineStr"/>
+      <c r="AI15" s="30" t="inlineStr"/>
     </row>
     <row r="16" ht="62" customHeight="1">
       <c r="A16" s="17" t="inlineStr">
@@ -7150,99 +7848,111 @@
           <t>A pack of 500 Phenol Red reagent tablets compatible with the Water-ID photometer, used for measuring pH levels in pool or spa water. Accurate pH readings are the foundation of balanced, comfortable water.</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="30" t="inlineStr">
         <is>
           <t>Water-i.d.</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="30" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" s="30" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>test-measure, add-on, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="H16" s="22" t="inlineStr">
+          <t>test-measure, add-on, barcode-verified, needs-review, scanned-stock</t>
+        </is>
+      </c>
+      <c r="H16" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="I16" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J16" s="22" t="inlineStr">
+      <c r="J16" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K16" s="22" t="inlineStr">
+      <c r="K16" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L16" s="22" t="inlineStr">
+      <c r="L16" s="30" t="inlineStr">
         <is>
           <t>WAT-TST-1801</t>
         </is>
       </c>
-      <c r="M16" s="23" t="inlineStr">
+      <c r="M16" s="31" t="inlineStr">
         <is>
           <t>4260431461801</t>
         </is>
       </c>
-      <c r="N16" s="24" t="inlineStr"/>
-      <c r="O16" s="24" t="inlineStr"/>
-      <c r="P16" s="24" t="inlineStr"/>
-      <c r="Q16" s="22" t="inlineStr">
+      <c r="N16" s="32" t="inlineStr"/>
+      <c r="O16" s="32" t="inlineStr"/>
+      <c r="P16" s="32" t="inlineStr"/>
+      <c r="Q16" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R16" s="22" t="inlineStr">
+      <c r="R16" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S16" s="22" t="inlineStr">
+      <c r="S16" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T16" s="22" t="inlineStr">
+      <c r="T16" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U16" s="22" t="inlineStr"/>
-      <c r="V16" s="22" t="inlineStr">
+      <c r="U16" s="30" t="inlineStr"/>
+      <c r="V16" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W16" s="22" t="inlineStr">
+      <c r="W16" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X16" s="22" t="inlineStr">
+      <c r="X16" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Y16" s="17" t="inlineStr"/>
-      <c r="Z16" s="22" t="inlineStr"/>
-      <c r="AA16" s="17" t="inlineStr"/>
-      <c r="AB16" s="22" t="inlineStr">
+      <c r="Y16" s="17" t="inlineStr">
+        <is>
+          <t>https://www.poolpowershop.de/media/46/63/13/1743521499/phenol-red-testtabletten-fuer-poollab-500-stk.jpg</t>
+        </is>
+      </c>
+      <c r="Z16" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="17" t="inlineStr">
+        <is>
+          <t>WATER-I.D. Water-ID Reagenzien Phenol Red Photometer 500</t>
+        </is>
+      </c>
+      <c r="AB16" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7254,10 +7964,10 @@
           <t>Pool Accessories</t>
         </is>
       </c>
-      <c r="AF16" s="22" t="inlineStr"/>
-      <c r="AG16" s="22" t="inlineStr"/>
-      <c r="AH16" s="22" t="inlineStr"/>
-      <c r="AI16" s="22" t="inlineStr"/>
+      <c r="AF16" s="30" t="inlineStr"/>
+      <c r="AG16" s="30" t="inlineStr"/>
+      <c r="AH16" s="30" t="inlineStr"/>
+      <c r="AI16" s="30" t="inlineStr"/>
     </row>
     <row r="17" ht="62" customHeight="1">
       <c r="A17" s="17" t="inlineStr">
@@ -7275,17 +7985,17 @@
           <t>An alkaline edge and surround cleaner in a 1-litre bottle, formulated to be gentle on pool liners, foils, and plastic surfaces. It tackles waterline grime without harming the materials it touches.</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="30" t="inlineStr">
         <is>
           <t>Cristal</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="30" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -7295,71 +8005,71 @@
           <t>pool, water-treatment, cleaning, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H17" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr">
+      <c r="I17" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J17" s="22" t="inlineStr">
+      <c r="J17" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K17" s="22" t="inlineStr">
+      <c r="K17" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L17" s="22" t="inlineStr">
+      <c r="L17" s="30" t="inlineStr">
         <is>
           <t>CRI-CHM-5212</t>
         </is>
       </c>
-      <c r="M17" s="23" t="inlineStr">
+      <c r="M17" s="31" t="inlineStr">
         <is>
           <t>4002369155212</t>
         </is>
       </c>
-      <c r="N17" s="24" t="inlineStr"/>
-      <c r="O17" s="24" t="inlineStr"/>
-      <c r="P17" s="24" t="inlineStr"/>
-      <c r="Q17" s="22" t="inlineStr">
+      <c r="N17" s="32" t="inlineStr"/>
+      <c r="O17" s="32" t="inlineStr"/>
+      <c r="P17" s="32" t="inlineStr"/>
+      <c r="Q17" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R17" s="22" t="inlineStr">
+      <c r="R17" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S17" s="22" t="inlineStr">
+      <c r="S17" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T17" s="22" t="inlineStr">
+      <c r="T17" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U17" s="22" t="inlineStr"/>
-      <c r="V17" s="22" t="inlineStr">
+      <c r="U17" s="30" t="inlineStr"/>
+      <c r="V17" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W17" s="22" t="inlineStr">
+      <c r="W17" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X17" s="22" t="inlineStr">
+      <c r="X17" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7369,7 +8079,7 @@
           <t>https://images.barcodelookup.com/21057/210579756-1.jpg</t>
         </is>
       </c>
-      <c r="Z17" s="22" t="inlineStr">
+      <c r="Z17" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7379,7 +8089,7 @@
           <t>Cristal Poolpflege CRISTAL Alkaline Edge Cleaner 1,0 l, (Gentle on Materials, for Liners, Plastic Surfaces</t>
         </is>
       </c>
-      <c r="AB17" s="22" t="inlineStr">
+      <c r="AB17" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7391,10 +8101,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF17" s="22" t="inlineStr"/>
-      <c r="AG17" s="22" t="inlineStr"/>
-      <c r="AH17" s="22" t="inlineStr"/>
-      <c r="AI17" s="22" t="inlineStr"/>
+      <c r="AF17" s="30" t="inlineStr"/>
+      <c r="AG17" s="30" t="inlineStr"/>
+      <c r="AH17" s="30" t="inlineStr"/>
+      <c r="AI17" s="30" t="inlineStr"/>
     </row>
     <row r="18" ht="76" customHeight="1">
       <c r="A18" s="17" t="inlineStr">
@@ -7412,17 +8122,17 @@
           <t>A 1-litre pool surface cleaner formulated to remove sunscreen oils and greasy residues from the water surface, designed specifically for warm Mediterranean climates and heavy swimming loads. It keeps the waterline and surface clear without harming pool materials.</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="30" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="30" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -7432,71 +8142,71 @@
           <t>pool, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H18" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="I18" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J18" s="22" t="inlineStr">
+      <c r="J18" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K18" s="22" t="inlineStr">
+      <c r="K18" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L18" s="22" t="inlineStr">
+      <c r="L18" s="30" t="inlineStr">
         <is>
           <t>AQU-CLN-0223</t>
         </is>
       </c>
-      <c r="M18" s="23" t="inlineStr">
+      <c r="M18" s="31" t="inlineStr">
         <is>
           <t>5292638000223</t>
         </is>
       </c>
-      <c r="N18" s="24" t="inlineStr"/>
-      <c r="O18" s="24" t="inlineStr"/>
-      <c r="P18" s="24" t="inlineStr"/>
-      <c r="Q18" s="22" t="inlineStr">
+      <c r="N18" s="32" t="inlineStr"/>
+      <c r="O18" s="32" t="inlineStr"/>
+      <c r="P18" s="32" t="inlineStr"/>
+      <c r="Q18" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R18" s="22" t="inlineStr">
+      <c r="R18" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S18" s="22" t="inlineStr">
+      <c r="S18" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T18" s="22" t="inlineStr">
+      <c r="T18" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U18" s="22" t="inlineStr"/>
-      <c r="V18" s="22" t="inlineStr">
+      <c r="U18" s="30" t="inlineStr"/>
+      <c r="V18" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W18" s="22" t="inlineStr">
+      <c r="W18" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X18" s="22" t="inlineStr">
+      <c r="X18" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7506,7 +8216,7 @@
           <t>http://mangas.com.cy/media/products/5292638000223.jpg</t>
         </is>
       </c>
-      <c r="Z18" s="22" t="inlineStr">
+      <c r="Z18" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7516,7 +8226,7 @@
           <t>AQUALITY Pool Cleaner for Greasy Residues 1L</t>
         </is>
       </c>
-      <c r="AB18" s="22" t="inlineStr">
+      <c r="AB18" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7528,10 +8238,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF18" s="22" t="inlineStr"/>
-      <c r="AG18" s="22" t="inlineStr"/>
-      <c r="AH18" s="22" t="inlineStr"/>
-      <c r="AI18" s="22" t="inlineStr"/>
+      <c r="AF18" s="30" t="inlineStr"/>
+      <c r="AG18" s="30" t="inlineStr"/>
+      <c r="AH18" s="30" t="inlineStr"/>
+      <c r="AI18" s="30" t="inlineStr"/>
     </row>
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="17" t="inlineStr">
@@ -7549,17 +8259,17 @@
           <t>California Clear Blue is a super-concentrated, pH-neutral pool clarifier in a 1-litre bottle, using a cationic polymer formula to bind microscopic particles such as dust, pollen, and oils into larger clusters your filter can catch. Non-toxic and biodegradable, it is safe for sand, zeolite, and glass filtration media.</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D19" s="30" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="30" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -7569,71 +8279,71 @@
           <t>pool, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="I19" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J19" s="22" t="inlineStr">
+      <c r="J19" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K19" s="22" t="inlineStr">
+      <c r="K19" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L19" s="22" t="inlineStr">
+      <c r="L19" s="30" t="inlineStr">
         <is>
           <t>AQU-CHM-0070</t>
         </is>
       </c>
-      <c r="M19" s="23" t="inlineStr">
+      <c r="M19" s="31" t="inlineStr">
         <is>
           <t>5292638000070</t>
         </is>
       </c>
-      <c r="N19" s="24" t="inlineStr"/>
-      <c r="O19" s="24" t="inlineStr"/>
-      <c r="P19" s="24" t="inlineStr"/>
-      <c r="Q19" s="22" t="inlineStr">
+      <c r="N19" s="32" t="inlineStr"/>
+      <c r="O19" s="32" t="inlineStr"/>
+      <c r="P19" s="32" t="inlineStr"/>
+      <c r="Q19" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R19" s="22" t="inlineStr">
+      <c r="R19" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S19" s="22" t="inlineStr">
+      <c r="S19" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T19" s="22" t="inlineStr">
+      <c r="T19" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U19" s="22" t="inlineStr"/>
-      <c r="V19" s="22" t="inlineStr">
+      <c r="U19" s="30" t="inlineStr"/>
+      <c r="V19" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W19" s="22" t="inlineStr">
+      <c r="W19" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X19" s="22" t="inlineStr">
+      <c r="X19" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7643,7 +8353,7 @@
           <t>https://poolservices.cy/storage/2026/05/California-Clear-Blue-1L-Aquality-2.jpeg</t>
         </is>
       </c>
-      <c r="Z19" s="22" t="inlineStr">
+      <c r="Z19" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7653,7 +8363,7 @@
           <t>Pool Clarifier California Clear Blue Aquality 1L</t>
         </is>
       </c>
-      <c r="AB19" s="22" t="inlineStr">
+      <c r="AB19" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7665,10 +8375,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF19" s="22" t="inlineStr"/>
-      <c r="AG19" s="22" t="inlineStr"/>
-      <c r="AH19" s="22" t="inlineStr"/>
-      <c r="AI19" s="22" t="inlineStr"/>
+      <c r="AF19" s="30" t="inlineStr"/>
+      <c r="AG19" s="30" t="inlineStr"/>
+      <c r="AH19" s="30" t="inlineStr"/>
+      <c r="AI19" s="30" t="inlineStr"/>
     </row>
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="17" t="inlineStr">
@@ -7686,17 +8396,17 @@
           <t>A 1-litre tile and vinyl cleaner for pools, designed to clean pool tile surfaces and vinyl liners. It makes light work of the tidying up that keeps a pool looking its best.</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="30" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="30" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -7706,71 +8416,71 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H20" s="22" t="inlineStr">
+      <c r="H20" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I20" s="22" t="inlineStr">
+      <c r="I20" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J20" s="22" t="inlineStr">
+      <c r="J20" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K20" s="22" t="inlineStr">
+      <c r="K20" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L20" s="22" t="inlineStr">
+      <c r="L20" s="30" t="inlineStr">
         <is>
           <t>AQU-CLN-0162</t>
         </is>
       </c>
-      <c r="M20" s="23" t="inlineStr">
+      <c r="M20" s="31" t="inlineStr">
         <is>
           <t>5292638000162</t>
         </is>
       </c>
-      <c r="N20" s="24" t="inlineStr"/>
-      <c r="O20" s="24" t="inlineStr"/>
-      <c r="P20" s="24" t="inlineStr"/>
-      <c r="Q20" s="22" t="inlineStr">
+      <c r="N20" s="32" t="inlineStr"/>
+      <c r="O20" s="32" t="inlineStr"/>
+      <c r="P20" s="32" t="inlineStr"/>
+      <c r="Q20" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R20" s="22" t="inlineStr">
+      <c r="R20" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S20" s="22" t="inlineStr">
+      <c r="S20" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T20" s="22" t="inlineStr">
+      <c r="T20" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U20" s="22" t="inlineStr"/>
-      <c r="V20" s="22" t="inlineStr">
+      <c r="U20" s="30" t="inlineStr"/>
+      <c r="V20" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W20" s="22" t="inlineStr">
+      <c r="W20" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X20" s="22" t="inlineStr">
+      <c r="X20" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7780,7 +8490,7 @@
           <t>http://mangas.com.cy/media/products/5292638000162.jpg</t>
         </is>
       </c>
-      <c r="Z20" s="22" t="inlineStr">
+      <c r="Z20" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7790,7 +8500,7 @@
           <t>AQUALITY Magic tile 4 vinyl cleaner 1L</t>
         </is>
       </c>
-      <c r="AB20" s="22" t="inlineStr">
+      <c r="AB20" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7802,10 +8512,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF20" s="22" t="inlineStr"/>
-      <c r="AG20" s="22" t="inlineStr"/>
-      <c r="AH20" s="22" t="inlineStr"/>
-      <c r="AI20" s="22" t="inlineStr"/>
+      <c r="AF20" s="30" t="inlineStr"/>
+      <c r="AG20" s="30" t="inlineStr"/>
+      <c r="AH20" s="30" t="inlineStr"/>
+      <c r="AI20" s="30" t="inlineStr"/>
     </row>
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="17" t="inlineStr">
@@ -7823,99 +8533,111 @@
           <t>A 1-litre spa and pool water clarifier from Bayzid, formulated to clear cloudy or turbid water. A handy bottle to reach for whenever the water loses its sparkle.</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="30" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="30" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="30" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
-          <t>spa-hot-tub, pool, water-treatment, considered-purchase, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="H21" s="22" t="inlineStr">
+          <t>spa-hot-tub, pool, water-treatment, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
+        </is>
+      </c>
+      <c r="H21" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="I21" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J21" s="22" t="inlineStr">
+      <c r="J21" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K21" s="22" t="inlineStr">
+      <c r="K21" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L21" s="22" t="inlineStr">
+      <c r="L21" s="30" t="inlineStr">
         <is>
           <t>HFE-SPA-7202</t>
         </is>
       </c>
-      <c r="M21" s="23" t="inlineStr">
+      <c r="M21" s="31" t="inlineStr">
         <is>
           <t>4250463127202</t>
         </is>
       </c>
-      <c r="N21" s="24" t="inlineStr"/>
-      <c r="O21" s="24" t="inlineStr"/>
-      <c r="P21" s="24" t="inlineStr"/>
-      <c r="Q21" s="22" t="inlineStr">
+      <c r="N21" s="32" t="inlineStr"/>
+      <c r="O21" s="32" t="inlineStr"/>
+      <c r="P21" s="32" t="inlineStr"/>
+      <c r="Q21" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R21" s="22" t="inlineStr">
+      <c r="R21" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S21" s="22" t="inlineStr">
+      <c r="S21" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T21" s="22" t="inlineStr">
+      <c r="T21" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U21" s="22" t="inlineStr"/>
-      <c r="V21" s="22" t="inlineStr">
+      <c r="U21" s="30" t="inlineStr"/>
+      <c r="V21" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W21" s="22" t="inlineStr">
+      <c r="W21" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X21" s="22" t="inlineStr">
+      <c r="X21" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Y21" s="17" t="inlineStr"/>
-      <c r="Z21" s="22" t="inlineStr"/>
-      <c r="AA21" s="17" t="inlineStr"/>
-      <c r="AB21" s="22" t="inlineStr">
+      <c r="Y21" s="17" t="inlineStr">
+        <is>
+          <t>https://hoefer-shop.com/cdn/shop/files/1x1L-BAYZID-Spa-Poolclear-v1-RS_1.jpg?v=1785600487&amp;width=800</t>
+        </is>
+      </c>
+      <c r="Z21" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="17" t="inlineStr">
+        <is>
+          <t>Höfer Chemie GmbH Pool Care 1 L BAYZID® SPA Poolclear Turbidity Remover</t>
+        </is>
+      </c>
+      <c r="AB21" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7927,10 +8649,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF21" s="22" t="inlineStr"/>
-      <c r="AG21" s="22" t="inlineStr"/>
-      <c r="AH21" s="22" t="inlineStr"/>
-      <c r="AI21" s="22" t="inlineStr"/>
+      <c r="AF21" s="30" t="inlineStr"/>
+      <c r="AG21" s="30" t="inlineStr"/>
+      <c r="AH21" s="30" t="inlineStr"/>
+      <c r="AI21" s="30" t="inlineStr"/>
     </row>
     <row r="22" ht="62" customHeight="1">
       <c r="A22" s="17" t="inlineStr">
@@ -7948,99 +8670,111 @@
           <t>A 1-litre bottle of hydrogen peroxide at 11.9% concentration, suitable for disinfection and water treatment applications. A straightforward chemical solution that keeps things clean without fuss.</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="30" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="30" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>water-treatment, repeat-purchase, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="H22" s="22" t="inlineStr">
+          <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
+        </is>
+      </c>
+      <c r="H22" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="I22" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J22" s="22" t="inlineStr">
+      <c r="J22" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K22" s="22" t="inlineStr">
+      <c r="K22" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L22" s="22" t="inlineStr">
+      <c r="L22" s="30" t="inlineStr">
         <is>
           <t>HFE-CHM-6788</t>
         </is>
       </c>
-      <c r="M22" s="23" t="inlineStr">
+      <c r="M22" s="31" t="inlineStr">
         <is>
           <t>4250463106788</t>
         </is>
       </c>
-      <c r="N22" s="24" t="inlineStr"/>
-      <c r="O22" s="24" t="inlineStr"/>
-      <c r="P22" s="24" t="inlineStr"/>
-      <c r="Q22" s="22" t="inlineStr">
+      <c r="N22" s="32" t="inlineStr"/>
+      <c r="O22" s="32" t="inlineStr"/>
+      <c r="P22" s="32" t="inlineStr"/>
+      <c r="Q22" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R22" s="22" t="inlineStr">
+      <c r="R22" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S22" s="22" t="inlineStr">
+      <c r="S22" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T22" s="22" t="inlineStr">
+      <c r="T22" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U22" s="22" t="inlineStr"/>
-      <c r="V22" s="22" t="inlineStr">
+      <c r="U22" s="30" t="inlineStr"/>
+      <c r="V22" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W22" s="22" t="inlineStr">
+      <c r="W22" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X22" s="22" t="inlineStr">
+      <c r="X22" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Y22" s="17" t="inlineStr"/>
-      <c r="Z22" s="22" t="inlineStr"/>
-      <c r="AA22" s="17" t="inlineStr"/>
-      <c r="AB22" s="22" t="inlineStr">
+      <c r="Y22" s="17" t="inlineStr">
+        <is>
+          <t>https://hoefer-shop.com/cdn/shop/files/1x1L-Wasserstoffperoxid-Flasche-hinten-26.jpg?v=1783777627&amp;width=1000</t>
+        </is>
+      </c>
+      <c r="Z22" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="17" t="inlineStr">
+        <is>
+          <t>HÖFER CHEMIE GMBH 1 l Hydrogen Peroxide 11,9%</t>
+        </is>
+      </c>
+      <c r="AB22" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8052,10 +8786,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF22" s="22" t="inlineStr"/>
-      <c r="AG22" s="22" t="inlineStr"/>
-      <c r="AH22" s="22" t="inlineStr"/>
-      <c r="AI22" s="22" t="inlineStr"/>
+      <c r="AF22" s="30" t="inlineStr"/>
+      <c r="AG22" s="30" t="inlineStr"/>
+      <c r="AH22" s="30" t="inlineStr"/>
+      <c r="AI22" s="30" t="inlineStr"/>
     </row>
     <row r="23" ht="62" customHeight="1">
       <c r="A23" s="17" t="inlineStr">
@@ -8073,17 +8807,17 @@
           <t>A 4.5 kg pack of chlorine stabilizer for swimming pools, used to protect chlorine from UV degradation and extend its effectiveness in the water. Steady chemistry for a pool that earns its keep.</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="30" t="inlineStr">
         <is>
           <t>AstralPool</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="30" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8093,83 +8827,83 @@
           <t>water-treatment, repeat-purchase, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="H23" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
+      <c r="I23" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J23" s="22" t="inlineStr">
+      <c r="J23" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K23" s="22" t="inlineStr">
+      <c r="K23" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L23" s="22" t="inlineStr">
+      <c r="L23" s="30" t="inlineStr">
         <is>
           <t>AST-CHM-0626</t>
         </is>
       </c>
-      <c r="M23" s="23" t="inlineStr">
+      <c r="M23" s="31" t="inlineStr">
         <is>
           <t>8432611960626</t>
         </is>
       </c>
-      <c r="N23" s="24" t="inlineStr"/>
-      <c r="O23" s="24" t="inlineStr"/>
-      <c r="P23" s="24" t="inlineStr"/>
-      <c r="Q23" s="22" t="inlineStr">
+      <c r="N23" s="32" t="inlineStr"/>
+      <c r="O23" s="32" t="inlineStr"/>
+      <c r="P23" s="32" t="inlineStr"/>
+      <c r="Q23" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R23" s="22" t="inlineStr">
+      <c r="R23" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S23" s="22" t="inlineStr">
+      <c r="S23" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T23" s="22" t="inlineStr">
+      <c r="T23" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U23" s="22" t="inlineStr">
+      <c r="U23" s="30" t="inlineStr">
         <is>
           <t>4500</t>
         </is>
       </c>
-      <c r="V23" s="22" t="inlineStr">
+      <c r="V23" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W23" s="22" t="inlineStr">
+      <c r="W23" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X23" s="22" t="inlineStr">
+      <c r="X23" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
-      <c r="Z23" s="22" t="inlineStr"/>
+      <c r="Z23" s="30" t="inlineStr"/>
       <c r="AA23" s="17" t="inlineStr"/>
-      <c r="AB23" s="22" t="inlineStr">
+      <c r="AB23" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8181,10 +8915,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF23" s="22" t="inlineStr"/>
-      <c r="AG23" s="22" t="inlineStr"/>
-      <c r="AH23" s="22" t="inlineStr"/>
-      <c r="AI23" s="22" t="inlineStr"/>
+      <c r="AF23" s="30" t="inlineStr"/>
+      <c r="AG23" s="30" t="inlineStr"/>
+      <c r="AH23" s="30" t="inlineStr"/>
+      <c r="AI23" s="30" t="inlineStr"/>
     </row>
     <row r="24" ht="62" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
@@ -8202,17 +8936,17 @@
           <t>UltraShock is a pool and spa shock treatment from SpaBalancer, designed to rapidly oxidise contaminants and restore water clarity. A quick reset for water that needs a little more persuasion.</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="30" t="inlineStr">
         <is>
           <t>SpaBalancer</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F24" s="30" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8222,71 +8956,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H24" s="22" t="inlineStr">
+      <c r="H24" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I24" s="22" t="inlineStr">
+      <c r="I24" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J24" s="22" t="inlineStr">
+      <c r="J24" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K24" s="22" t="inlineStr">
+      <c r="K24" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L24" s="22" t="inlineStr">
+      <c r="L24" s="30" t="inlineStr">
         <is>
           <t>SPA-CHM-0025</t>
         </is>
       </c>
-      <c r="M24" s="23" t="inlineStr">
+      <c r="M24" s="31" t="inlineStr">
         <is>
           <t>4260374980025</t>
         </is>
       </c>
-      <c r="N24" s="24" t="inlineStr"/>
-      <c r="O24" s="24" t="inlineStr"/>
-      <c r="P24" s="24" t="inlineStr"/>
-      <c r="Q24" s="22" t="inlineStr">
+      <c r="N24" s="32" t="inlineStr"/>
+      <c r="O24" s="32" t="inlineStr"/>
+      <c r="P24" s="32" t="inlineStr"/>
+      <c r="Q24" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R24" s="22" t="inlineStr">
+      <c r="R24" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S24" s="22" t="inlineStr">
+      <c r="S24" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T24" s="22" t="inlineStr">
+      <c r="T24" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U24" s="22" t="inlineStr"/>
-      <c r="V24" s="22" t="inlineStr">
+      <c r="U24" s="30" t="inlineStr"/>
+      <c r="V24" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W24" s="22" t="inlineStr">
+      <c r="W24" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X24" s="22" t="inlineStr">
+      <c r="X24" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8296,7 +9030,7 @@
           <t>https://images.barcodelookup.com/16704/167043133-1.jpg</t>
         </is>
       </c>
-      <c r="Z24" s="22" t="inlineStr">
+      <c r="Z24" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8306,7 +9040,7 @@
           <t>SpaBalancer UltraShock</t>
         </is>
       </c>
-      <c r="AB24" s="22" t="inlineStr">
+      <c r="AB24" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8318,10 +9052,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF24" s="22" t="inlineStr"/>
-      <c r="AG24" s="22" t="inlineStr"/>
-      <c r="AH24" s="22" t="inlineStr"/>
-      <c r="AI24" s="22" t="inlineStr"/>
+      <c r="AF24" s="30" t="inlineStr"/>
+      <c r="AG24" s="30" t="inlineStr"/>
+      <c r="AH24" s="30" t="inlineStr"/>
+      <c r="AI24" s="30" t="inlineStr"/>
     </row>
     <row r="25" ht="76" customHeight="1">
       <c r="A25" s="17" t="inlineStr">
@@ -8339,13 +9073,13 @@
           <t>A patented foam rubber eraser for cleaning pool surfaces, particularly suited to waterline stains on liner and vitreous ceramic finishes, and it works without detergents or chemicals. Each box contains 3 sponges, which harden when wet to scrub effectively while remaining soft and flexible in use.</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr"/>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="D25" s="30" t="inlineStr"/>
+      <c r="E25" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="30" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8355,71 +9089,71 @@
           <t>pool, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="H25" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I25" s="22" t="inlineStr">
+      <c r="I25" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J25" s="22" t="inlineStr">
+      <c r="J25" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K25" s="22" t="inlineStr">
+      <c r="K25" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L25" s="22" t="inlineStr">
+      <c r="L25" s="30" t="inlineStr">
         <is>
           <t>GEN-CLN-0062</t>
         </is>
       </c>
-      <c r="M25" s="23" t="inlineStr">
+      <c r="M25" s="31" t="inlineStr">
         <is>
           <t>3760015880062</t>
         </is>
       </c>
-      <c r="N25" s="24" t="inlineStr"/>
-      <c r="O25" s="24" t="inlineStr"/>
-      <c r="P25" s="24" t="inlineStr"/>
-      <c r="Q25" s="22" t="inlineStr">
+      <c r="N25" s="32" t="inlineStr"/>
+      <c r="O25" s="32" t="inlineStr"/>
+      <c r="P25" s="32" t="inlineStr"/>
+      <c r="Q25" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R25" s="22" t="inlineStr">
+      <c r="R25" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S25" s="22" t="inlineStr">
+      <c r="S25" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T25" s="22" t="inlineStr">
+      <c r="T25" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U25" s="22" t="inlineStr"/>
-      <c r="V25" s="22" t="inlineStr">
+      <c r="U25" s="30" t="inlineStr"/>
+      <c r="V25" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W25" s="22" t="inlineStr">
+      <c r="W25" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X25" s="22" t="inlineStr">
+      <c r="X25" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8429,7 +9163,7 @@
           <t>https://www.piscinarium.com/2908-thickbox_default/pool-gom-magic-rubber-eraser.jpg</t>
         </is>
       </c>
-      <c r="Z25" s="22" t="inlineStr">
+      <c r="Z25" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8439,7 +9173,7 @@
           <t>Pool'Gom Magic Rubber Eraser</t>
         </is>
       </c>
-      <c r="AB25" s="22" t="inlineStr">
+      <c r="AB25" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8451,10 +9185,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF25" s="22" t="inlineStr"/>
-      <c r="AG25" s="22" t="inlineStr"/>
-      <c r="AH25" s="22" t="inlineStr"/>
-      <c r="AI25" s="22" t="inlineStr"/>
+      <c r="AF25" s="30" t="inlineStr"/>
+      <c r="AG25" s="30" t="inlineStr"/>
+      <c r="AH25" s="30" t="inlineStr"/>
+      <c r="AI25" s="30" t="inlineStr"/>
     </row>
     <row r="26" ht="62" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
@@ -8472,13 +9206,13 @@
           <t>Spa Industries Europe appears to be a brand or supplier name rather than a specific product, so no product details can be confirmed. For accurate information, please check the full product listing.</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr"/>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="D26" s="30" t="inlineStr"/>
+      <c r="E26" s="30" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="30" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -8488,79 +9222,79 @@
           <t>spa-hot-tub, considered-purchase, multi-source-confirmed, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H26" s="22" t="inlineStr">
+      <c r="H26" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I26" s="22" t="inlineStr">
+      <c r="I26" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J26" s="22" t="inlineStr">
+      <c r="J26" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K26" s="22" t="inlineStr">
+      <c r="K26" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L26" s="22" t="inlineStr">
+      <c r="L26" s="30" t="inlineStr">
         <is>
           <t>GEN-SPA-1968</t>
         </is>
       </c>
-      <c r="M26" s="23" t="inlineStr">
+      <c r="M26" s="31" t="inlineStr">
         <is>
           <t>5425021871968</t>
         </is>
       </c>
-      <c r="N26" s="24" t="inlineStr"/>
-      <c r="O26" s="24" t="inlineStr"/>
-      <c r="P26" s="24" t="inlineStr"/>
-      <c r="Q26" s="22" t="inlineStr">
+      <c r="N26" s="32" t="inlineStr"/>
+      <c r="O26" s="32" t="inlineStr"/>
+      <c r="P26" s="32" t="inlineStr"/>
+      <c r="Q26" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R26" s="22" t="inlineStr">
+      <c r="R26" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S26" s="22" t="inlineStr">
+      <c r="S26" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T26" s="22" t="inlineStr">
+      <c r="T26" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U26" s="22" t="inlineStr"/>
-      <c r="V26" s="22" t="inlineStr">
+      <c r="U26" s="30" t="inlineStr"/>
+      <c r="V26" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W26" s="22" t="inlineStr">
+      <c r="W26" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X26" s="22" t="inlineStr">
+      <c r="X26" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y26" s="17" t="inlineStr"/>
-      <c r="Z26" s="22" t="inlineStr"/>
+      <c r="Z26" s="30" t="inlineStr"/>
       <c r="AA26" s="17" t="inlineStr"/>
-      <c r="AB26" s="22" t="inlineStr">
+      <c r="AB26" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8572,10 +9306,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF26" s="22" t="inlineStr"/>
-      <c r="AG26" s="22" t="inlineStr"/>
-      <c r="AH26" s="22" t="inlineStr"/>
-      <c r="AI26" s="22" t="inlineStr"/>
+      <c r="AF26" s="30" t="inlineStr"/>
+      <c r="AG26" s="30" t="inlineStr"/>
+      <c r="AH26" s="30" t="inlineStr"/>
+      <c r="AI26" s="30" t="inlineStr"/>
     </row>
     <row r="27" ht="62" customHeight="1">
       <c r="A27" s="17" t="inlineStr">
@@ -8593,17 +9327,17 @@
           <t>A 1-litre high-concentrate sauna cleaner with eucalyptus fragrance, formulated as a deep-cleaning base cleaner for sauna surfaces. The concentrated formula means a little goes a long way, with a fresh scent to match.</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="30" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="30" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8613,79 +9347,79 @@
           <t>cleaning, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H27" s="22" t="inlineStr">
+      <c r="H27" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I27" s="22" t="inlineStr">
+      <c r="I27" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J27" s="22" t="inlineStr">
+      <c r="J27" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K27" s="22" t="inlineStr">
+      <c r="K27" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L27" s="22" t="inlineStr">
+      <c r="L27" s="30" t="inlineStr">
         <is>
           <t>HFE-CLN-7004</t>
         </is>
       </c>
-      <c r="M27" s="23" t="inlineStr">
+      <c r="M27" s="31" t="inlineStr">
         <is>
           <t>4250463127004</t>
         </is>
       </c>
-      <c r="N27" s="24" t="inlineStr"/>
-      <c r="O27" s="24" t="inlineStr"/>
-      <c r="P27" s="24" t="inlineStr"/>
-      <c r="Q27" s="22" t="inlineStr">
+      <c r="N27" s="32" t="inlineStr"/>
+      <c r="O27" s="32" t="inlineStr"/>
+      <c r="P27" s="32" t="inlineStr"/>
+      <c r="Q27" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R27" s="22" t="inlineStr">
+      <c r="R27" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S27" s="22" t="inlineStr">
+      <c r="S27" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T27" s="22" t="inlineStr">
+      <c r="T27" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U27" s="22" t="inlineStr"/>
-      <c r="V27" s="22" t="inlineStr">
+      <c r="U27" s="30" t="inlineStr"/>
+      <c r="V27" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W27" s="22" t="inlineStr">
+      <c r="W27" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X27" s="22" t="inlineStr">
+      <c r="X27" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y27" s="17" t="inlineStr"/>
-      <c r="Z27" s="22" t="inlineStr"/>
+      <c r="Z27" s="30" t="inlineStr"/>
       <c r="AA27" s="17" t="inlineStr"/>
-      <c r="AB27" s="22" t="inlineStr">
+      <c r="AB27" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8697,10 +9431,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF27" s="22" t="inlineStr"/>
-      <c r="AG27" s="22" t="inlineStr"/>
-      <c r="AH27" s="22" t="inlineStr"/>
-      <c r="AI27" s="22" t="inlineStr"/>
+      <c r="AF27" s="30" t="inlineStr"/>
+      <c r="AG27" s="30" t="inlineStr"/>
+      <c r="AH27" s="30" t="inlineStr"/>
+      <c r="AI27" s="30" t="inlineStr"/>
     </row>
     <row r="28" ht="76" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
@@ -8718,17 +9452,17 @@
           <t>This HTH spa cleaner removes mineral deposits such as limescale and rust, and cleans and polishes aluminium, chrome, stainless steel, and enamel surfaces with a pleasant pine fragrance. It has a high concentration of active ingredients and is recommended for periodic maintenance cleaning.</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="30" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="30" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8738,71 +9472,71 @@
           <t>spa-hot-tub, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H28" s="22" t="inlineStr">
+      <c r="H28" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I28" s="22" t="inlineStr">
+      <c r="I28" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J28" s="22" t="inlineStr">
+      <c r="J28" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K28" s="22" t="inlineStr">
+      <c r="K28" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L28" s="22" t="inlineStr">
+      <c r="L28" s="30" t="inlineStr">
         <is>
           <t>HTH-CLN-0178</t>
         </is>
       </c>
-      <c r="M28" s="23" t="inlineStr">
+      <c r="M28" s="31" t="inlineStr">
         <is>
           <t>3521686010178</t>
         </is>
       </c>
-      <c r="N28" s="24" t="inlineStr"/>
-      <c r="O28" s="24" t="inlineStr"/>
-      <c r="P28" s="24" t="inlineStr"/>
-      <c r="Q28" s="22" t="inlineStr">
+      <c r="N28" s="32" t="inlineStr"/>
+      <c r="O28" s="32" t="inlineStr"/>
+      <c r="P28" s="32" t="inlineStr"/>
+      <c r="Q28" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R28" s="22" t="inlineStr">
+      <c r="R28" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S28" s="22" t="inlineStr">
+      <c r="S28" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T28" s="22" t="inlineStr">
+      <c r="T28" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U28" s="22" t="inlineStr"/>
-      <c r="V28" s="22" t="inlineStr">
+      <c r="U28" s="30" t="inlineStr"/>
+      <c r="V28" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W28" s="22" t="inlineStr">
+      <c r="W28" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X28" s="22" t="inlineStr">
+      <c r="X28" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8812,7 +9546,7 @@
           <t>https://www.cdiscount.com/pdt2/0/5/1/1/700x700/auc2009356289051/rw/hth-spa-nettoyant-spa-3521686010178.jpg</t>
         </is>
       </c>
-      <c r="Z28" s="22" t="inlineStr">
+      <c r="Z28" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8822,7 +9556,7 @@
           <t>HTH Spa Spa Cleaner</t>
         </is>
       </c>
-      <c r="AB28" s="22" t="inlineStr">
+      <c r="AB28" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8834,10 +9568,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF28" s="22" t="inlineStr"/>
-      <c r="AG28" s="22" t="inlineStr"/>
-      <c r="AH28" s="22" t="inlineStr"/>
-      <c r="AI28" s="22" t="inlineStr"/>
+      <c r="AF28" s="30" t="inlineStr"/>
+      <c r="AG28" s="30" t="inlineStr"/>
+      <c r="AH28" s="30" t="inlineStr"/>
+      <c r="AI28" s="30" t="inlineStr"/>
     </row>
     <row r="29" ht="62" customHeight="1">
       <c r="A29" s="17" t="inlineStr">
@@ -8855,13 +9589,13 @@
           <t>A 25 kg sack of pure boiling salt (minimum 99.6% NaCl) without an anti-caking agent, meeting EN 973 Type A standard and suitable for use in pool salt electrolysis systems. Not intended for human consumption or animal feed.</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr"/>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="D29" s="30" t="inlineStr"/>
+      <c r="E29" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="30" t="inlineStr">
         <is>
           <t>Pool salt</t>
         </is>
@@ -8871,75 +9605,75 @@
           <t>pool, salt, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H29" s="22" t="inlineStr">
+      <c r="H29" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I29" s="22" t="inlineStr">
+      <c r="I29" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J29" s="22" t="inlineStr">
+      <c r="J29" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K29" s="22" t="inlineStr">
+      <c r="K29" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L29" s="22" t="inlineStr">
+      <c r="L29" s="30" t="inlineStr">
         <is>
           <t>GEN-SLT-6110</t>
         </is>
       </c>
-      <c r="M29" s="23" t="inlineStr">
+      <c r="M29" s="31" t="inlineStr">
         <is>
           <t>9001880976110</t>
         </is>
       </c>
-      <c r="N29" s="24" t="inlineStr"/>
-      <c r="O29" s="24" t="inlineStr"/>
-      <c r="P29" s="24" t="inlineStr"/>
-      <c r="Q29" s="22" t="inlineStr">
+      <c r="N29" s="32" t="inlineStr"/>
+      <c r="O29" s="32" t="inlineStr"/>
+      <c r="P29" s="32" t="inlineStr"/>
+      <c r="Q29" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R29" s="22" t="inlineStr">
+      <c r="R29" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S29" s="22" t="inlineStr">
+      <c r="S29" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T29" s="22" t="inlineStr">
+      <c r="T29" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U29" s="22" t="inlineStr">
+      <c r="U29" s="30" t="inlineStr">
         <is>
           <t>25000</t>
         </is>
       </c>
-      <c r="V29" s="22" t="inlineStr">
+      <c r="V29" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W29" s="22" t="inlineStr">
+      <c r="W29" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X29" s="22" t="inlineStr">
+      <c r="X29" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8949,7 +9683,7 @@
           <t>http://altruan.com/cdn/shop/files/SalinenPoolSalz25kgSack.png?v=1778597596</t>
         </is>
       </c>
-      <c r="Z29" s="22" t="inlineStr">
+      <c r="Z29" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8959,7 +9693,7 @@
           <t>Saline pool salt pure boiling salt without separating agent | Sack (25 kg)</t>
         </is>
       </c>
-      <c r="AB29" s="22" t="inlineStr">
+      <c r="AB29" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8971,14 +9705,14 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF29" s="22" t="inlineStr">
+      <c r="AF29" s="30" t="inlineStr">
         <is>
           <t>Composition: Siedesalz (min. 99.6% NaCl) 100%; Separant/sodium ferrocyanide 4.0–12.0 mg/kg | Grain: &gt;0.63 mm approx. 20%, 0.2–0.63 mm approx. 75%, &lt;0.2 mm approx. 5% | Moisture: &lt;0.08%</t>
         </is>
       </c>
-      <c r="AG29" s="22" t="inlineStr"/>
-      <c r="AH29" s="22" t="inlineStr"/>
-      <c r="AI29" s="22" t="inlineStr"/>
+      <c r="AG29" s="30" t="inlineStr"/>
+      <c r="AH29" s="30" t="inlineStr"/>
+      <c r="AI29" s="30" t="inlineStr"/>
     </row>
     <row r="30" ht="76" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
@@ -8996,17 +9730,17 @@
           <t>A cordless robotic pool cleaner that scrubs both floors and walls automatically, using WavePath navigation to map and cover the pool efficiently. Built-in high-performance filtration and smart control make it a hands-off solution for keeping pool water clear.</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
+      <c r="D30" s="30" t="inlineStr">
         <is>
           <t>Aiper</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F30" s="30" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9016,71 +9750,71 @@
           <t>pool, cleaning, robot-cleaner, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H30" s="22" t="inlineStr">
+      <c r="H30" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I30" s="22" t="inlineStr">
+      <c r="I30" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J30" s="22" t="inlineStr">
+      <c r="J30" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K30" s="22" t="inlineStr">
+      <c r="K30" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L30" s="22" t="inlineStr">
+      <c r="L30" s="30" t="inlineStr">
         <is>
           <t>AIP-ROB-4940</t>
         </is>
       </c>
-      <c r="M30" s="23" t="inlineStr">
+      <c r="M30" s="31" t="inlineStr">
         <is>
           <t>6977676344940</t>
         </is>
       </c>
-      <c r="N30" s="24" t="inlineStr"/>
-      <c r="O30" s="24" t="inlineStr"/>
-      <c r="P30" s="24" t="inlineStr"/>
-      <c r="Q30" s="22" t="inlineStr">
+      <c r="N30" s="32" t="inlineStr"/>
+      <c r="O30" s="32" t="inlineStr"/>
+      <c r="P30" s="32" t="inlineStr"/>
+      <c r="Q30" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R30" s="22" t="inlineStr">
+      <c r="R30" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S30" s="22" t="inlineStr">
+      <c r="S30" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T30" s="22" t="inlineStr">
+      <c r="T30" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U30" s="22" t="inlineStr"/>
-      <c r="V30" s="22" t="inlineStr">
+      <c r="U30" s="30" t="inlineStr"/>
+      <c r="V30" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W30" s="22" t="inlineStr">
+      <c r="W30" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X30" s="22" t="inlineStr">
+      <c r="X30" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9090,7 +9824,7 @@
           <t>https://images.barcodelookup.com/176692/1766920801-1.jpg</t>
         </is>
       </c>
-      <c r="Z30" s="22" t="inlineStr">
+      <c r="Z30" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9100,7 +9834,7 @@
           <t>AIPER Scuba S3 Cordless Pool Robot, Automatic Floor and Wall Cleaning, WavePath™ Navigation, High-Performance Filtration…</t>
         </is>
       </c>
-      <c r="AB30" s="22" t="inlineStr">
+      <c r="AB30" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9112,10 +9846,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF30" s="22" t="inlineStr"/>
-      <c r="AG30" s="22" t="inlineStr"/>
-      <c r="AH30" s="22" t="inlineStr"/>
-      <c r="AI30" s="22" t="inlineStr"/>
+      <c r="AF30" s="30" t="inlineStr"/>
+      <c r="AG30" s="30" t="inlineStr"/>
+      <c r="AH30" s="30" t="inlineStr"/>
+      <c r="AI30" s="30" t="inlineStr"/>
     </row>
     <row r="31" ht="62" customHeight="1">
       <c r="A31" s="17" t="inlineStr">
@@ -9133,13 +9867,13 @@
           <t>The Scuba L1 EU is a pool cleaning device, though no further specific details about its features, dimensions, or mechanism are available from the product name alone. Buyers should refer to the full product listing for specifications.</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr"/>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="D31" s="30" t="inlineStr"/>
+      <c r="E31" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="30" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9149,71 +9883,71 @@
           <t>robot-cleaner, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H31" s="22" t="inlineStr">
+      <c r="H31" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I31" s="22" t="inlineStr">
+      <c r="I31" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J31" s="22" t="inlineStr">
+      <c r="J31" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K31" s="22" t="inlineStr">
+      <c r="K31" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L31" s="22" t="inlineStr">
+      <c r="L31" s="30" t="inlineStr">
         <is>
           <t>GEN-ROB-5137</t>
         </is>
       </c>
-      <c r="M31" s="23" t="inlineStr">
+      <c r="M31" s="31" t="inlineStr">
         <is>
           <t>6975140315137</t>
         </is>
       </c>
-      <c r="N31" s="24" t="inlineStr"/>
-      <c r="O31" s="24" t="inlineStr"/>
-      <c r="P31" s="24" t="inlineStr"/>
-      <c r="Q31" s="22" t="inlineStr">
+      <c r="N31" s="32" t="inlineStr"/>
+      <c r="O31" s="32" t="inlineStr"/>
+      <c r="P31" s="32" t="inlineStr"/>
+      <c r="Q31" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R31" s="22" t="inlineStr">
+      <c r="R31" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S31" s="22" t="inlineStr">
+      <c r="S31" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T31" s="22" t="inlineStr">
+      <c r="T31" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U31" s="22" t="inlineStr"/>
-      <c r="V31" s="22" t="inlineStr">
+      <c r="U31" s="30" t="inlineStr"/>
+      <c r="V31" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W31" s="22" t="inlineStr">
+      <c r="W31" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X31" s="22" t="inlineStr">
+      <c r="X31" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9223,7 +9957,7 @@
           <t>https://images.barcodelookup.com/124722/1247228758-1.jpg</t>
         </is>
       </c>
-      <c r="Z31" s="22" t="inlineStr">
+      <c r="Z31" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9233,7 +9967,7 @@
           <t>Scuba L1 - EU</t>
         </is>
       </c>
-      <c r="AB31" s="22" t="inlineStr">
+      <c r="AB31" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9245,10 +9979,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF31" s="22" t="inlineStr"/>
-      <c r="AG31" s="22" t="inlineStr"/>
-      <c r="AH31" s="22" t="inlineStr"/>
-      <c r="AI31" s="22" t="inlineStr"/>
+      <c r="AF31" s="30" t="inlineStr"/>
+      <c r="AG31" s="30" t="inlineStr"/>
+      <c r="AH31" s="30" t="inlineStr"/>
+      <c r="AI31" s="30" t="inlineStr"/>
     </row>
     <row r="32" ht="48" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
@@ -9266,13 +10000,13 @@
           <t>The Gre Pools RBR120 is a 51W robotic pool cleaner designed for automatic pool floor cleaning. A reliable workhorse that takes the scrubbing off your hands.</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr"/>
-      <c r="E32" s="22" t="inlineStr">
+      <c r="D32" s="30" t="inlineStr"/>
+      <c r="E32" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F32" s="30" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9282,71 +10016,71 @@
           <t>robot-cleaner, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H32" s="22" t="inlineStr">
+      <c r="H32" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I32" s="22" t="inlineStr">
+      <c r="I32" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J32" s="22" t="inlineStr">
+      <c r="J32" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K32" s="22" t="inlineStr">
+      <c r="K32" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L32" s="22" t="inlineStr">
+      <c r="L32" s="30" t="inlineStr">
         <is>
           <t>GEN-ROB-8500</t>
         </is>
       </c>
-      <c r="M32" s="23" t="inlineStr">
+      <c r="M32" s="31" t="inlineStr">
         <is>
           <t>8412081308500</t>
         </is>
       </c>
-      <c r="N32" s="24" t="inlineStr"/>
-      <c r="O32" s="24" t="inlineStr"/>
-      <c r="P32" s="24" t="inlineStr"/>
-      <c r="Q32" s="22" t="inlineStr">
+      <c r="N32" s="32" t="inlineStr"/>
+      <c r="O32" s="32" t="inlineStr"/>
+      <c r="P32" s="32" t="inlineStr"/>
+      <c r="Q32" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R32" s="22" t="inlineStr">
+      <c r="R32" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S32" s="22" t="inlineStr">
+      <c r="S32" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T32" s="22" t="inlineStr">
+      <c r="T32" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U32" s="22" t="inlineStr"/>
-      <c r="V32" s="22" t="inlineStr">
+      <c r="U32" s="30" t="inlineStr"/>
+      <c r="V32" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W32" s="22" t="inlineStr">
+      <c r="W32" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X32" s="22" t="inlineStr">
+      <c r="X32" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9356,7 +10090,7 @@
           <t>https://images.barcodelookup.com/124726/1247268298-1.jpg</t>
         </is>
       </c>
-      <c r="Z32" s="22" t="inlineStr">
+      <c r="Z32" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9366,7 +10100,7 @@
           <t>Battery Powered Robot WET RUNNER XPERT</t>
         </is>
       </c>
-      <c r="AB32" s="22" t="inlineStr">
+      <c r="AB32" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9378,10 +10112,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF32" s="22" t="inlineStr"/>
-      <c r="AG32" s="22" t="inlineStr"/>
-      <c r="AH32" s="22" t="inlineStr"/>
-      <c r="AI32" s="22" t="inlineStr"/>
+      <c r="AF32" s="30" t="inlineStr"/>
+      <c r="AG32" s="30" t="inlineStr"/>
+      <c r="AH32" s="30" t="inlineStr"/>
+      <c r="AI32" s="30" t="inlineStr"/>
     </row>
     <row r="33" ht="90" customHeight="1">
       <c r="A33" s="17" t="inlineStr">
@@ -9399,13 +10133,13 @@
           <t>A twin-size inflatable airbed measuring 99 x 191 x 25 cm, built with Fiber-Tech internal construction using polyester fibres for comfort, vinyl sides and base, and a water-resistant flocked top surface with an anti-deflation valve. It supports a maximum weight of 136 kg and packs down compactly when deflated.</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr"/>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="D33" s="30" t="inlineStr"/>
+      <c r="E33" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-11</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="30" t="inlineStr">
         <is>
           <t>Airbed / lounger</t>
         </is>
@@ -9415,71 +10149,71 @@
           <t>considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H33" s="22" t="inlineStr">
+      <c r="H33" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I33" s="22" t="inlineStr">
+      <c r="I33" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J33" s="22" t="inlineStr">
+      <c r="J33" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K33" s="22" t="inlineStr">
+      <c r="K33" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L33" s="22" t="inlineStr">
+      <c r="L33" s="30" t="inlineStr">
         <is>
           <t>GEN-BED-2443</t>
         </is>
       </c>
-      <c r="M33" s="23" t="inlineStr">
+      <c r="M33" s="31" t="inlineStr">
         <is>
           <t>6941057412443</t>
         </is>
       </c>
-      <c r="N33" s="24" t="inlineStr"/>
-      <c r="O33" s="24" t="inlineStr"/>
-      <c r="P33" s="24" t="inlineStr"/>
-      <c r="Q33" s="22" t="inlineStr">
+      <c r="N33" s="32" t="inlineStr"/>
+      <c r="O33" s="32" t="inlineStr"/>
+      <c r="P33" s="32" t="inlineStr"/>
+      <c r="Q33" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R33" s="22" t="inlineStr">
+      <c r="R33" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S33" s="22" t="inlineStr">
+      <c r="S33" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T33" s="22" t="inlineStr">
+      <c r="T33" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U33" s="22" t="inlineStr"/>
-      <c r="V33" s="22" t="inlineStr">
+      <c r="U33" s="30" t="inlineStr"/>
+      <c r="V33" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W33" s="22" t="inlineStr">
+      <c r="W33" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X33" s="22" t="inlineStr">
+      <c r="X33" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9489,7 +10223,7 @@
           <t>https://www.ecoperation.com/media/catalog/product/cache/b76cf1d99a7811daa83ba86e6ad91c89/6/4/64757.jpg</t>
         </is>
       </c>
-      <c r="Z33" s="22" t="inlineStr">
+      <c r="Z33" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9499,7 +10233,7 @@
           <t>Twin Dura-Beam Classic Downy Airbed 99x191x25 cm</t>
         </is>
       </c>
-      <c r="AB33" s="22" t="inlineStr">
+      <c r="AB33" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9511,18 +10245,18 @@
           <t>Inflatable Beds and Mattresses</t>
         </is>
       </c>
-      <c r="AF33" s="22" t="inlineStr"/>
-      <c r="AG33" s="22" t="inlineStr">
+      <c r="AF33" s="30" t="inlineStr"/>
+      <c r="AG33" s="30" t="inlineStr">
         <is>
           <t>99.0cm</t>
         </is>
       </c>
-      <c r="AH33" s="22" t="inlineStr">
+      <c r="AH33" s="30" t="inlineStr">
         <is>
           <t>191.0cm</t>
         </is>
       </c>
-      <c r="AI33" s="22" t="inlineStr">
+      <c r="AI33" s="30" t="inlineStr">
         <is>
           <t>25.0cm</t>
         </is>
@@ -9544,17 +10278,17 @@
           <t>A plastic chlorine dosing lock from Steinbach, designed exclusively for use with long-term chlorine tablets, with a 1.5-inch connection fitting. It measures 37 cm in length, 22.5 cm in width, and 15 cm in height, making it a sturdy inline dosing unit for pool water treatment systems.</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D34" s="30" t="inlineStr">
         <is>
           <t>Steinbach</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E34" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F34" s="30" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -9564,71 +10298,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H34" s="22" t="inlineStr">
+      <c r="H34" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I34" s="22" t="inlineStr">
+      <c r="I34" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J34" s="22" t="inlineStr">
+      <c r="J34" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K34" s="22" t="inlineStr">
+      <c r="K34" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L34" s="22" t="inlineStr">
+      <c r="L34" s="30" t="inlineStr">
         <is>
           <t>STE-CHM-0307</t>
         </is>
       </c>
-      <c r="M34" s="23" t="inlineStr">
+      <c r="M34" s="31" t="inlineStr">
         <is>
           <t>9008748790307</t>
         </is>
       </c>
-      <c r="N34" s="24" t="inlineStr"/>
-      <c r="O34" s="24" t="inlineStr"/>
-      <c r="P34" s="24" t="inlineStr"/>
-      <c r="Q34" s="22" t="inlineStr">
+      <c r="N34" s="32" t="inlineStr"/>
+      <c r="O34" s="32" t="inlineStr"/>
+      <c r="P34" s="32" t="inlineStr"/>
+      <c r="Q34" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R34" s="22" t="inlineStr">
+      <c r="R34" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S34" s="22" t="inlineStr">
+      <c r="S34" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T34" s="22" t="inlineStr">
+      <c r="T34" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U34" s="22" t="inlineStr"/>
-      <c r="V34" s="22" t="inlineStr">
+      <c r="U34" s="30" t="inlineStr"/>
+      <c r="V34" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W34" s="22" t="inlineStr">
+      <c r="W34" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X34" s="22" t="inlineStr">
+      <c r="X34" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9638,7 +10372,7 @@
           <t>https://i.ebayimg.com/images/g/CrUAAeSwkOdqeaRR/s-l400.jpg</t>
         </is>
       </c>
-      <c r="Z34" s="22" t="inlineStr">
+      <c r="Z34" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9648,7 +10382,7 @@
           <t>STEINBACH Chlorine dosing lock, only for chlorine long-term tablets, plastic, connection 1.5 inch in</t>
         </is>
       </c>
-      <c r="AB34" s="22" t="inlineStr">
+      <c r="AB34" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9660,18 +10394,18 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF34" s="22" t="inlineStr"/>
-      <c r="AG34" s="22" t="inlineStr">
+      <c r="AF34" s="30" t="inlineStr"/>
+      <c r="AG34" s="30" t="inlineStr">
         <is>
           <t>22.5cm</t>
         </is>
       </c>
-      <c r="AH34" s="22" t="inlineStr">
+      <c r="AH34" s="30" t="inlineStr">
         <is>
           <t>37.0cm</t>
         </is>
       </c>
-      <c r="AI34" s="22" t="inlineStr">
+      <c r="AI34" s="30" t="inlineStr">
         <is>
           <t>15.0cm</t>
         </is>
@@ -9693,17 +10427,17 @@
           <t>A filter cleaning system for hot tub and pool cartridge filters, designed to remove debris and residue efficiently while keeping water usage to a minimum. A practical tool for extending the life of your filter without wasting a drop more than necessary.</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D35" s="30" t="inlineStr">
         <is>
           <t>Estelle</t>
         </is>
       </c>
-      <c r="E35" s="22" t="inlineStr">
+      <c r="E35" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="30" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -9713,71 +10447,71 @@
           <t>filters, spa-hot-tub, cleaning, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H35" s="22" t="inlineStr">
+      <c r="H35" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I35" s="22" t="inlineStr">
+      <c r="I35" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J35" s="22" t="inlineStr">
+      <c r="J35" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K35" s="22" t="inlineStr">
+      <c r="K35" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L35" s="22" t="inlineStr">
+      <c r="L35" s="30" t="inlineStr">
         <is>
           <t>EST-FIL-3669</t>
         </is>
       </c>
-      <c r="M35" s="23" t="inlineStr">
+      <c r="M35" s="31" t="inlineStr">
         <is>
           <t>8711842033669</t>
         </is>
       </c>
-      <c r="N35" s="24" t="inlineStr"/>
-      <c r="O35" s="24" t="inlineStr"/>
-      <c r="P35" s="24" t="inlineStr"/>
-      <c r="Q35" s="22" t="inlineStr">
+      <c r="N35" s="32" t="inlineStr"/>
+      <c r="O35" s="32" t="inlineStr"/>
+      <c r="P35" s="32" t="inlineStr"/>
+      <c r="Q35" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R35" s="22" t="inlineStr">
+      <c r="R35" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S35" s="22" t="inlineStr">
+      <c r="S35" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T35" s="22" t="inlineStr">
+      <c r="T35" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U35" s="22" t="inlineStr"/>
-      <c r="V35" s="22" t="inlineStr">
+      <c r="U35" s="30" t="inlineStr"/>
+      <c r="V35" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W35" s="22" t="inlineStr">
+      <c r="W35" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X35" s="22" t="inlineStr">
+      <c r="X35" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9787,7 +10521,7 @@
           <t>https://i.ebayimg.com/images/g/0e0AAOSweaplqO77/s-l400.jpg</t>
         </is>
       </c>
-      <c r="Z35" s="22" t="inlineStr">
+      <c r="Z35" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9797,7 +10531,7 @@
           <t>Estelle Filter Cleaning System Hot tubs Cartridge Filters Cleaner Spa Amazing!</t>
         </is>
       </c>
-      <c r="AB35" s="22" t="inlineStr">
+      <c r="AB35" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9809,10 +10543,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF35" s="22" t="inlineStr"/>
-      <c r="AG35" s="22" t="inlineStr"/>
-      <c r="AH35" s="22" t="inlineStr"/>
-      <c r="AI35" s="22" t="inlineStr"/>
+      <c r="AF35" s="30" t="inlineStr"/>
+      <c r="AG35" s="30" t="inlineStr"/>
+      <c r="AH35" s="30" t="inlineStr"/>
+      <c r="AI35" s="30" t="inlineStr"/>
     </row>
     <row r="36" ht="62" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
@@ -9830,17 +10564,17 @@
           <t>A compact handy scrub brush for pool maintenance, measuring 15 x 9 x 8 cm, suited to scrubbing pool surfaces and hard-to-reach areas. Small enough to manoeuvre easily, and ready to tackle whatever the waterline throws at it.</t>
         </is>
       </c>
-      <c r="D36" s="22" t="inlineStr">
+      <c r="D36" s="30" t="inlineStr">
         <is>
           <t>WAYS</t>
         </is>
       </c>
-      <c r="E36" s="22" t="inlineStr">
+      <c r="E36" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F36" s="30" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -9850,79 +10584,79 @@
           <t>pool, cleaning, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H36" s="22" t="inlineStr">
+      <c r="H36" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I36" s="22" t="inlineStr">
+      <c r="I36" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J36" s="22" t="inlineStr">
+      <c r="J36" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K36" s="22" t="inlineStr">
+      <c r="K36" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L36" s="22" t="inlineStr">
+      <c r="L36" s="30" t="inlineStr">
         <is>
           <t>WAY-CLN-2219</t>
         </is>
       </c>
-      <c r="M36" s="23" t="inlineStr">
+      <c r="M36" s="31" t="inlineStr">
         <is>
           <t>8720299182219</t>
         </is>
       </c>
-      <c r="N36" s="24" t="inlineStr"/>
-      <c r="O36" s="24" t="inlineStr"/>
-      <c r="P36" s="24" t="inlineStr"/>
-      <c r="Q36" s="22" t="inlineStr">
+      <c r="N36" s="32" t="inlineStr"/>
+      <c r="O36" s="32" t="inlineStr"/>
+      <c r="P36" s="32" t="inlineStr"/>
+      <c r="Q36" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R36" s="22" t="inlineStr">
+      <c r="R36" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S36" s="22" t="inlineStr">
+      <c r="S36" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T36" s="22" t="inlineStr">
+      <c r="T36" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U36" s="22" t="inlineStr"/>
-      <c r="V36" s="22" t="inlineStr">
+      <c r="U36" s="30" t="inlineStr"/>
+      <c r="V36" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W36" s="22" t="inlineStr">
+      <c r="W36" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X36" s="22" t="inlineStr">
+      <c r="X36" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y36" s="17" t="inlineStr"/>
-      <c r="Z36" s="22" t="inlineStr"/>
+      <c r="Z36" s="30" t="inlineStr"/>
       <c r="AA36" s="17" t="inlineStr"/>
-      <c r="AB36" s="22" t="inlineStr">
+      <c r="AB36" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9934,18 +10668,18 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF36" s="22" t="inlineStr"/>
-      <c r="AG36" s="22" t="inlineStr">
+      <c r="AF36" s="30" t="inlineStr"/>
+      <c r="AG36" s="30" t="inlineStr">
         <is>
           <t>8.0cm</t>
         </is>
       </c>
-      <c r="AH36" s="22" t="inlineStr">
+      <c r="AH36" s="30" t="inlineStr">
         <is>
           <t>15.0cm</t>
         </is>
       </c>
-      <c r="AI36" s="22" t="inlineStr">
+      <c r="AI36" s="30" t="inlineStr">
         <is>
           <t>9.0cm</t>
         </is>
@@ -9967,17 +10701,17 @@
           <t>An inflatable PVC headrest pillow for the Intex inflatable spa (model 28506), measuring 24 x 19 x 6 cm and weighing 0.22 kg, designed to support the head and neck comfortably during use. It attaches to the spa rim and can also be filled with water for added stability.</t>
         </is>
       </c>
-      <c r="D37" s="22" t="inlineStr">
+      <c r="D37" s="30" t="inlineStr">
         <is>
           <t>Intex</t>
         </is>
       </c>
-      <c r="E37" s="22" t="inlineStr">
+      <c r="E37" s="30" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F37" s="22" t="inlineStr">
+      <c r="F37" s="30" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -9987,75 +10721,75 @@
           <t>spa-hot-tub, accessories, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H37" s="22" t="inlineStr">
+      <c r="H37" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I37" s="22" t="inlineStr">
+      <c r="I37" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J37" s="22" t="inlineStr">
+      <c r="J37" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K37" s="22" t="inlineStr">
+      <c r="K37" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L37" s="22" t="inlineStr">
+      <c r="L37" s="30" t="inlineStr">
         <is>
           <t>INT-SPA-6075</t>
         </is>
       </c>
-      <c r="M37" s="23" t="inlineStr">
+      <c r="M37" s="31" t="inlineStr">
         <is>
           <t>6941057426075</t>
         </is>
       </c>
-      <c r="N37" s="24" t="inlineStr"/>
-      <c r="O37" s="24" t="inlineStr"/>
-      <c r="P37" s="24" t="inlineStr"/>
-      <c r="Q37" s="22" t="inlineStr">
+      <c r="N37" s="32" t="inlineStr"/>
+      <c r="O37" s="32" t="inlineStr"/>
+      <c r="P37" s="32" t="inlineStr"/>
+      <c r="Q37" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R37" s="22" t="inlineStr">
+      <c r="R37" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S37" s="22" t="inlineStr">
+      <c r="S37" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T37" s="22" t="inlineStr">
+      <c r="T37" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U37" s="22" t="inlineStr">
+      <c r="U37" s="30" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="V37" s="22" t="inlineStr">
+      <c r="V37" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W37" s="22" t="inlineStr">
+      <c r="W37" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X37" s="22" t="inlineStr">
+      <c r="X37" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10065,7 +10799,7 @@
           <t>https://content2.rozetka.com.ua/goods/images/big/570260745.jpg</t>
         </is>
       </c>
-      <c r="Z37" s="22" t="inlineStr">
+      <c r="Z37" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10075,7 +10809,7 @@
           <t>Headrest Pillow for INTEX Inflatable SPA 28506</t>
         </is>
       </c>
-      <c r="AB37" s="22" t="inlineStr">
+      <c r="AB37" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10087,18 +10821,18 @@
           <t>Intex Pure Spa Accessories</t>
         </is>
       </c>
-      <c r="AF37" s="22" t="inlineStr"/>
-      <c r="AG37" s="22" t="inlineStr">
+      <c r="AF37" s="30" t="inlineStr"/>
+      <c r="AG37" s="30" t="inlineStr">
         <is>
           <t>19.0cm</t>
         </is>
       </c>
-      <c r="AH37" s="22" t="inlineStr">
+      <c r="AH37" s="30" t="inlineStr">
         <is>
           <t>24.0cm</t>
         </is>
       </c>
-      <c r="AI37" s="22" t="inlineStr">
+      <c r="AI37" s="30" t="inlineStr">
         <is>
           <t>6.0cm</t>
         </is>
@@ -10120,13 +10854,13 @@
           <t>A DPD Pool test kit for active-oxygen pools, containing 20 DPD No. 4 reagent tablets for measuring active oxygen levels and 20 phenol red tablets for measuring pH. Results are read immediately after the tablet dissolves, with an ideal active oxygen range of 3.0 to 8.0 mg/l and a target pH of 7.0 to 7.4.</t>
         </is>
       </c>
-      <c r="D38" s="22" t="inlineStr"/>
-      <c r="E38" s="22" t="inlineStr">
+      <c r="D38" s="30" t="inlineStr"/>
+      <c r="E38" s="30" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F38" s="22" t="inlineStr">
+      <c r="F38" s="30" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -10136,71 +10870,71 @@
           <t>water-treatment, test-measure, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H38" s="22" t="inlineStr">
+      <c r="H38" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I38" s="22" t="inlineStr">
+      <c r="I38" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J38" s="22" t="inlineStr">
+      <c r="J38" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K38" s="22" t="inlineStr">
+      <c r="K38" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L38" s="22" t="inlineStr">
+      <c r="L38" s="30" t="inlineStr">
         <is>
           <t>GEN-TST-1347</t>
         </is>
       </c>
-      <c r="M38" s="23" t="inlineStr">
+      <c r="M38" s="31" t="inlineStr">
         <is>
           <t>4250463121347</t>
         </is>
       </c>
-      <c r="N38" s="24" t="inlineStr"/>
-      <c r="O38" s="24" t="inlineStr"/>
-      <c r="P38" s="24" t="inlineStr"/>
-      <c r="Q38" s="22" t="inlineStr">
+      <c r="N38" s="32" t="inlineStr"/>
+      <c r="O38" s="32" t="inlineStr"/>
+      <c r="P38" s="32" t="inlineStr"/>
+      <c r="Q38" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R38" s="22" t="inlineStr">
+      <c r="R38" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S38" s="22" t="inlineStr">
+      <c r="S38" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T38" s="22" t="inlineStr">
+      <c r="T38" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U38" s="22" t="inlineStr"/>
-      <c r="V38" s="22" t="inlineStr">
+      <c r="U38" s="30" t="inlineStr"/>
+      <c r="V38" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W38" s="22" t="inlineStr">
+      <c r="W38" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X38" s="22" t="inlineStr">
+      <c r="X38" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10210,7 +10944,7 @@
           <t>https://media.carrefour.fr/medias/8f94161f683b4e589024a5b5ebaa6873/p_200x200/cad3db6a00ef414a804b9226119bae96_image.jpg</t>
         </is>
       </c>
-      <c r="Z38" s="22" t="inlineStr">
+      <c r="Z38" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10220,7 +10954,7 @@
           <t>Active Oxygen Test Kit x1</t>
         </is>
       </c>
-      <c r="AB38" s="22" t="inlineStr">
+      <c r="AB38" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10232,10 +10966,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF38" s="22" t="inlineStr"/>
-      <c r="AG38" s="22" t="inlineStr"/>
-      <c r="AH38" s="22" t="inlineStr"/>
-      <c r="AI38" s="22" t="inlineStr"/>
+      <c r="AF38" s="30" t="inlineStr"/>
+      <c r="AG38" s="30" t="inlineStr"/>
+      <c r="AH38" s="30" t="inlineStr"/>
+      <c r="AI38" s="30" t="inlineStr"/>
     </row>
     <row r="39" ht="62" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
@@ -10253,99 +10987,111 @@
           <t>A pack of 2 replacement filter cartridges compatible with Intex Type H pool and spa pumps, made by Darlly. Straightforward to swap out, they keep the water moving clean without any complications.</t>
         </is>
       </c>
-      <c r="D39" s="22" t="inlineStr">
+      <c r="D39" s="30" t="inlineStr">
         <is>
           <t>Intex</t>
         </is>
       </c>
-      <c r="E39" s="22" t="inlineStr">
+      <c r="E39" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F39" s="22" t="inlineStr">
+      <c r="F39" s="30" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
       </c>
       <c r="G39" s="17" t="inlineStr">
         <is>
-          <t>filters, repeat-purchase, needs-photo, needs-review, scanned-stock</t>
-        </is>
-      </c>
-      <c r="H39" s="22" t="inlineStr">
+          <t>filters, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
+        </is>
+      </c>
+      <c r="H39" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I39" s="22" t="inlineStr">
+      <c r="I39" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J39" s="22" t="inlineStr">
+      <c r="J39" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K39" s="22" t="inlineStr">
+      <c r="K39" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L39" s="22" t="inlineStr">
+      <c r="L39" s="30" t="inlineStr">
         <is>
           <t>INT-FIL-2895</t>
         </is>
       </c>
-      <c r="M39" s="23" t="inlineStr">
+      <c r="M39" s="31" t="inlineStr">
         <is>
           <t>700175992895</t>
         </is>
       </c>
-      <c r="N39" s="24" t="inlineStr"/>
-      <c r="O39" s="24" t="inlineStr"/>
-      <c r="P39" s="24" t="inlineStr"/>
-      <c r="Q39" s="22" t="inlineStr">
+      <c r="N39" s="32" t="inlineStr"/>
+      <c r="O39" s="32" t="inlineStr"/>
+      <c r="P39" s="32" t="inlineStr"/>
+      <c r="Q39" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R39" s="22" t="inlineStr">
+      <c r="R39" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S39" s="22" t="inlineStr">
+      <c r="S39" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T39" s="22" t="inlineStr">
+      <c r="T39" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U39" s="22" t="inlineStr"/>
-      <c r="V39" s="22" t="inlineStr">
+      <c r="U39" s="30" t="inlineStr"/>
+      <c r="V39" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W39" s="22" t="inlineStr">
+      <c r="W39" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X39" s="22" t="inlineStr">
+      <c r="X39" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Y39" s="17" t="inlineStr"/>
-      <c r="Z39" s="22" t="inlineStr"/>
-      <c r="AA39" s="17" t="inlineStr"/>
-      <c r="AB39" s="22" t="inlineStr">
+      <c r="Y39" s="17" t="inlineStr">
+        <is>
+          <t>https://a.allegroimg.com/original/11923c/a79785a04d36aa54f0d87384f038/Filtracni-kartuse-Intex-D-3BTZ0023-SC828</t>
+        </is>
+      </c>
+      <c r="Z39" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA39" s="17" t="inlineStr">
+        <is>
+          <t>Darlly Filter Cartridge Pack of 2 Filter Cartridges Compatible with Intex Type H</t>
+        </is>
+      </c>
+      <c r="AB39" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10357,10 +11103,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF39" s="22" t="inlineStr"/>
-      <c r="AG39" s="22" t="inlineStr"/>
-      <c r="AH39" s="22" t="inlineStr"/>
-      <c r="AI39" s="22" t="inlineStr"/>
+      <c r="AF39" s="30" t="inlineStr"/>
+      <c r="AG39" s="30" t="inlineStr"/>
+      <c r="AH39" s="30" t="inlineStr"/>
+      <c r="AI39" s="30" t="inlineStr"/>
     </row>
     <row r="40" ht="62" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
@@ -10378,17 +11124,17 @@
           <t>A Darlly replacement spa filter cartridge with dimensions of 22 cm diameter by 27 cm height, compatible with SC713 and C-8465 references. A reliable like-for-like swap to keep your spa filtration running smoothly.</t>
         </is>
       </c>
-      <c r="D40" s="22" t="inlineStr">
+      <c r="D40" s="30" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E40" s="22" t="inlineStr">
+      <c r="E40" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F40" s="22" t="inlineStr">
+      <c r="F40" s="30" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -10398,71 +11144,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H40" s="22" t="inlineStr">
+      <c r="H40" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I40" s="22" t="inlineStr">
+      <c r="I40" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J40" s="22" t="inlineStr">
+      <c r="J40" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K40" s="22" t="inlineStr">
+      <c r="K40" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L40" s="22" t="inlineStr">
+      <c r="L40" s="30" t="inlineStr">
         <is>
           <t>DAR-FIL-1744</t>
         </is>
       </c>
-      <c r="M40" s="23" t="inlineStr">
+      <c r="M40" s="31" t="inlineStr">
         <is>
           <t>700175991744</t>
         </is>
       </c>
-      <c r="N40" s="24" t="inlineStr"/>
-      <c r="O40" s="24" t="inlineStr"/>
-      <c r="P40" s="24" t="inlineStr"/>
-      <c r="Q40" s="22" t="inlineStr">
+      <c r="N40" s="32" t="inlineStr"/>
+      <c r="O40" s="32" t="inlineStr"/>
+      <c r="P40" s="32" t="inlineStr"/>
+      <c r="Q40" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R40" s="22" t="inlineStr">
+      <c r="R40" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S40" s="22" t="inlineStr">
+      <c r="S40" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T40" s="22" t="inlineStr">
+      <c r="T40" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U40" s="22" t="inlineStr"/>
-      <c r="V40" s="22" t="inlineStr">
+      <c r="U40" s="30" t="inlineStr"/>
+      <c r="V40" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W40" s="22" t="inlineStr">
+      <c r="W40" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X40" s="22" t="inlineStr">
+      <c r="X40" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10472,7 +11218,7 @@
           <t>https://images.barcodelookup.com/142259/1422591231-1.jpg</t>
         </is>
       </c>
-      <c r="Z40" s="22" t="inlineStr">
+      <c r="Z40" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10482,7 +11228,7 @@
           <t>Spa Replacement Filter Ø 22 cm x 27 cm SC713, C-8465 - Darlly</t>
         </is>
       </c>
-      <c r="AB40" s="22" t="inlineStr">
+      <c r="AB40" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10494,14 +11240,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF40" s="22" t="inlineStr"/>
-      <c r="AG40" s="22" t="inlineStr"/>
-      <c r="AH40" s="22" t="inlineStr">
+      <c r="AF40" s="30" t="inlineStr"/>
+      <c r="AG40" s="30" t="inlineStr"/>
+      <c r="AH40" s="30" t="inlineStr">
         <is>
           <t>22.0cm</t>
         </is>
       </c>
-      <c r="AI40" s="22" t="inlineStr">
+      <c r="AI40" s="30" t="inlineStr">
         <is>
           <t>27.0cm</t>
         </is>
@@ -10523,17 +11269,17 @@
           <t>A 1 kg pack of 20g multitabs for swimming pools, offering a 5-in-1 treatment that combines multiple water care functions in a single slow-dissolving tablet. Convenient all-in-one dosing that keeps pool maintenance simple.</t>
         </is>
       </c>
-      <c r="D41" s="22" t="inlineStr">
+      <c r="D41" s="30" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E41" s="22" t="inlineStr">
+      <c r="E41" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F41" s="22" t="inlineStr">
+      <c r="F41" s="30" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -10543,75 +11289,75 @@
           <t>pool, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H41" s="22" t="inlineStr">
+      <c r="H41" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I41" s="22" t="inlineStr">
+      <c r="I41" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J41" s="22" t="inlineStr">
+      <c r="J41" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K41" s="22" t="inlineStr">
+      <c r="K41" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L41" s="22" t="inlineStr">
+      <c r="L41" s="30" t="inlineStr">
         <is>
           <t>HFE-CHM-8430</t>
         </is>
       </c>
-      <c r="M41" s="23" t="inlineStr">
+      <c r="M41" s="31" t="inlineStr">
         <is>
           <t>4250463108430</t>
         </is>
       </c>
-      <c r="N41" s="24" t="inlineStr"/>
-      <c r="O41" s="24" t="inlineStr"/>
-      <c r="P41" s="24" t="inlineStr"/>
-      <c r="Q41" s="22" t="inlineStr">
+      <c r="N41" s="32" t="inlineStr"/>
+      <c r="O41" s="32" t="inlineStr"/>
+      <c r="P41" s="32" t="inlineStr"/>
+      <c r="Q41" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R41" s="22" t="inlineStr">
+      <c r="R41" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S41" s="22" t="inlineStr">
+      <c r="S41" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T41" s="22" t="inlineStr">
+      <c r="T41" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U41" s="22" t="inlineStr">
+      <c r="U41" s="30" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="V41" s="22" t="inlineStr">
+      <c r="V41" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W41" s="22" t="inlineStr">
+      <c r="W41" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X41" s="22" t="inlineStr">
+      <c r="X41" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10621,7 +11367,7 @@
           <t>https://images.barcodelookup.com/17422/174228560-1.jpg</t>
         </is>
       </c>
-      <c r="Z41" s="22" t="inlineStr">
+      <c r="Z41" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10631,7 +11377,7 @@
           <t>1 x 1 kg BAYZID® 20g 5-in-1 Multitabs for Pools - HÖFER CHEMIE</t>
         </is>
       </c>
-      <c r="AB41" s="22" t="inlineStr">
+      <c r="AB41" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10643,10 +11389,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF41" s="22" t="inlineStr"/>
-      <c r="AG41" s="22" t="inlineStr"/>
-      <c r="AH41" s="22" t="inlineStr"/>
-      <c r="AI41" s="22" t="inlineStr"/>
+      <c r="AF41" s="30" t="inlineStr"/>
+      <c r="AG41" s="30" t="inlineStr"/>
+      <c r="AH41" s="30" t="inlineStr"/>
+      <c r="AI41" s="30" t="inlineStr"/>
     </row>
     <row r="42" ht="76" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
@@ -10664,17 +11410,17 @@
           <t>A ready-to-use alkaline spray cleaner for removing grease and dirt marks at the waterline of pools and for cleaning skimmers. The spray bottle makes application straightforward, and it can be used on a filled pool on all alkali-resistant surfaces.</t>
         </is>
       </c>
-      <c r="D42" s="22" t="inlineStr">
+      <c r="D42" s="30" t="inlineStr">
         <is>
           <t>Bayrol</t>
         </is>
       </c>
-      <c r="E42" s="22" t="inlineStr">
+      <c r="E42" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F42" s="22" t="inlineStr">
+      <c r="F42" s="30" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -10684,75 +11430,75 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H42" s="22" t="inlineStr">
+      <c r="H42" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I42" s="22" t="inlineStr">
+      <c r="I42" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J42" s="22" t="inlineStr">
+      <c r="J42" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K42" s="22" t="inlineStr">
+      <c r="K42" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L42" s="22" t="inlineStr">
+      <c r="L42" s="30" t="inlineStr">
         <is>
           <t>BAY-CLN-4134</t>
         </is>
       </c>
-      <c r="M42" s="23" t="inlineStr">
+      <c r="M42" s="31" t="inlineStr">
         <is>
           <t>4008367154134</t>
         </is>
       </c>
-      <c r="N42" s="24" t="inlineStr"/>
-      <c r="O42" s="24" t="inlineStr"/>
-      <c r="P42" s="24" t="inlineStr"/>
-      <c r="Q42" s="22" t="inlineStr">
+      <c r="N42" s="32" t="inlineStr"/>
+      <c r="O42" s="32" t="inlineStr"/>
+      <c r="P42" s="32" t="inlineStr"/>
+      <c r="Q42" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R42" s="22" t="inlineStr">
+      <c r="R42" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S42" s="22" t="inlineStr">
+      <c r="S42" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T42" s="22" t="inlineStr">
+      <c r="T42" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U42" s="22" t="inlineStr">
+      <c r="U42" s="30" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="V42" s="22" t="inlineStr">
+      <c r="V42" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W42" s="22" t="inlineStr">
+      <c r="W42" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X42" s="22" t="inlineStr">
+      <c r="X42" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10762,7 +11508,7 @@
           <t>https://www.north-spa.de/wp-content/uploads/2023/02/Produktbild-1-Bayrol-Randfix-07-l-4008367154134.jpg</t>
         </is>
       </c>
-      <c r="Z42" s="22" t="inlineStr">
+      <c r="Z42" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10772,7 +11518,7 @@
           <t>Bayrol Randfix 0,7 l</t>
         </is>
       </c>
-      <c r="AB42" s="22" t="inlineStr">
+      <c r="AB42" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10784,10 +11530,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF42" s="22" t="inlineStr"/>
-      <c r="AG42" s="22" t="inlineStr"/>
-      <c r="AH42" s="22" t="inlineStr"/>
-      <c r="AI42" s="22" t="inlineStr"/>
+      <c r="AF42" s="30" t="inlineStr"/>
+      <c r="AG42" s="30" t="inlineStr"/>
+      <c r="AH42" s="30" t="inlineStr"/>
+      <c r="AI42" s="30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projects/splashstore/docs/splashstore-scan-curation-260816.xlsx
+++ b/projects/splashstore/docs/splashstore-scan-curation-260816.xlsx
@@ -93,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -162,6 +162,15 @@
     <xf numFmtId="49" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -1569,18 +1578,18 @@
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="56" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="56" customWidth="1" min="13" max="13"/>
     <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="40" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1680,7 +1689,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="286" customHeight="1">
+    <row r="2" ht="132" customHeight="1">
       <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="5" t="inlineStr">
         <is>
@@ -1773,7 +1782,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="286" customHeight="1">
+    <row r="3" ht="132" customHeight="1">
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="5" t="inlineStr">
         <is>
@@ -1860,7 +1869,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="314" customHeight="1">
+    <row r="4" ht="132" customHeight="1">
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="5" t="inlineStr">
         <is>
@@ -1953,7 +1962,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr"/>
       <c r="B5" s="10" t="inlineStr">
         <is>
@@ -2014,7 +2023,7 @@
       </c>
       <c r="S5" s="17" t="inlineStr"/>
     </row>
-    <row r="6" ht="272" customHeight="1">
+    <row r="6" ht="132" customHeight="1">
       <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -2107,7 +2116,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="286" customHeight="1">
+    <row r="7" ht="132" customHeight="1">
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -2194,7 +2203,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="258" customHeight="1">
+    <row r="8" ht="132" customHeight="1">
       <c r="A8" s="12" t="inlineStr"/>
       <c r="B8" s="13" t="inlineStr">
         <is>
@@ -2287,7 +2296,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="320" customHeight="1">
+    <row r="9" ht="160" customHeight="1">
       <c r="A9" s="12" t="inlineStr"/>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -2380,7 +2389,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="320" customHeight="1">
+    <row r="10" ht="146" customHeight="1">
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -2465,7 +2474,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="258" customHeight="1">
+    <row r="11" ht="132" customHeight="1">
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -2556,7 +2565,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="244" customHeight="1">
+    <row r="12" ht="132" customHeight="1">
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="13" t="inlineStr">
         <is>
@@ -2649,7 +2658,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="272" customHeight="1">
+    <row r="13" ht="132" customHeight="1">
       <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -2742,7 +2751,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="244" customHeight="1">
+    <row r="14" ht="132" customHeight="1">
       <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -2835,7 +2844,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="244" customHeight="1">
+    <row r="15" ht="132" customHeight="1">
       <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -2928,7 +2937,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="34" customHeight="1">
+    <row r="16" ht="20" customHeight="1">
       <c r="A16" s="9" t="inlineStr"/>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -2989,7 +2998,7 @@
       </c>
       <c r="S16" s="17" t="inlineStr"/>
     </row>
-    <row r="17" ht="244" customHeight="1">
+    <row r="17" ht="104" customHeight="1">
       <c r="A17" s="9" t="inlineStr"/>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -3042,7 +3051,11 @@
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr"/>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>1 source: ean-search.org</t>
+        </is>
+      </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
           <t>Blank — no image</t>
@@ -3074,7 +3087,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="244" customHeight="1">
+    <row r="18" ht="132" customHeight="1">
       <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="13" t="inlineStr">
         <is>
@@ -3167,7 +3180,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="244" customHeight="1">
+    <row r="19" ht="132" customHeight="1">
       <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -3260,7 +3273,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="314" customHeight="1">
+    <row r="20" ht="132" customHeight="1">
       <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -3353,7 +3366,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="320" customHeight="1">
+    <row r="21" ht="160" customHeight="1">
       <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -3446,7 +3459,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="216" customHeight="1">
+    <row r="22" ht="132" customHeight="1">
       <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -3539,7 +3552,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="202" customHeight="1">
+    <row r="23" ht="132" customHeight="1">
       <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="13" t="inlineStr">
         <is>
@@ -3632,7 +3645,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="244" customHeight="1">
+    <row r="24" ht="132" customHeight="1">
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="13" t="inlineStr">
         <is>
@@ -3725,7 +3738,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="244" customHeight="1">
+    <row r="25" ht="104" customHeight="1">
       <c r="A25" s="9" t="inlineStr"/>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -3778,7 +3791,11 @@
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="M25" s="4" t="inlineStr"/>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>1 source: ean-search.org</t>
+        </is>
+      </c>
       <c r="N25" s="4" t="n">
         <v>4.5</v>
       </c>
@@ -3808,7 +3825,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="230" customHeight="1">
+    <row r="26" ht="132" customHeight="1">
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -3901,7 +3918,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="320" customHeight="1">
+    <row r="27" ht="146" customHeight="1">
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="5" t="inlineStr">
         <is>
@@ -3994,7 +4011,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="244" customHeight="1">
+    <row r="28" ht="104" customHeight="1">
       <c r="A28" s="9" t="inlineStr"/>
       <c r="B28" s="10" t="inlineStr">
         <is>
@@ -4047,7 +4064,11 @@
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr"/>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>2 sources: ean-search.org, spa-industries.eu</t>
+        </is>
+      </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
           <t>Blank — no image</t>
@@ -4079,7 +4100,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="258" customHeight="1">
+    <row r="29" ht="118" customHeight="1">
       <c r="A29" s="9" t="inlineStr"/>
       <c r="B29" s="10" t="inlineStr">
         <is>
@@ -4132,7 +4153,11 @@
           <t>Blank — no image</t>
         </is>
       </c>
-      <c r="M29" s="4" t="inlineStr"/>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>1 source: ean-search.org</t>
+        </is>
+      </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
           <t>Blank — no image</t>
@@ -4164,7 +4189,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="320" customHeight="1">
+    <row r="30" ht="146" customHeight="1">
       <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="5" t="inlineStr">
         <is>
@@ -4257,7 +4282,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="272" customHeight="1">
+    <row r="31" ht="244" customHeight="1">
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="5" t="inlineStr">
         <is>
@@ -4348,7 +4373,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="314" customHeight="1">
+    <row r="32" ht="132" customHeight="1">
       <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="13" t="inlineStr">
         <is>
@@ -4441,7 +4466,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="286" customHeight="1">
+    <row r="33" ht="132" customHeight="1">
       <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="5" t="inlineStr">
         <is>
@@ -4534,7 +4559,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="188" customHeight="1">
+    <row r="34" ht="132" customHeight="1">
       <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="5" t="inlineStr">
         <is>
@@ -4627,7 +4652,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="320" customHeight="1">
+    <row r="35" ht="160" customHeight="1">
       <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="5" t="inlineStr">
         <is>
@@ -4712,7 +4737,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="320" customHeight="1">
+    <row r="36" ht="146" customHeight="1">
       <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -4797,7 +4822,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="314" customHeight="1">
+    <row r="37" ht="132" customHeight="1">
       <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="5" t="inlineStr">
         <is>
@@ -4890,7 +4915,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="272" customHeight="1">
+    <row r="38" ht="118" customHeight="1">
       <c r="A38" s="9" t="inlineStr"/>
       <c r="B38" s="10" t="inlineStr">
         <is>
@@ -4973,7 +4998,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="320" customHeight="1">
+    <row r="39" ht="132" customHeight="1">
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="5" t="inlineStr">
         <is>
@@ -5058,7 +5083,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="320" customHeight="1">
+    <row r="40" ht="160" customHeight="1">
       <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="5" t="inlineStr">
         <is>
@@ -5151,7 +5176,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="244" customHeight="1">
+    <row r="41" ht="132" customHeight="1">
       <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="13" t="inlineStr">
         <is>
@@ -5244,7 +5269,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="258" customHeight="1">
+    <row r="42" ht="132" customHeight="1">
       <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="5" t="inlineStr">
         <is>
@@ -5331,7 +5356,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="272" customHeight="1">
+    <row r="43" ht="132" customHeight="1">
       <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="5" t="inlineStr">
         <is>
@@ -5422,7 +5447,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="300" customHeight="1">
+    <row r="44" ht="132" customHeight="1">
       <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="5" t="inlineStr">
         <is>
@@ -5513,7 +5538,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="34" customHeight="1">
+    <row r="45" ht="20" customHeight="1">
       <c r="A45" s="9" t="inlineStr"/>
       <c r="B45" s="10" t="inlineStr">
         <is>
@@ -5922,17 +5947,17 @@
           <t>A cartridge filter for hot tubs and swim spas, measuring 26.0 cm outer diameter, 13.0 cm bottom part, and 3.8 cm inner thread. Compatible with Darlly SC779 and 40372 codes, it captures dirt, grease, and fine particles to keep water clean.</t>
         </is>
       </c>
-      <c r="D2" s="30" t="inlineStr">
+      <c r="D2" s="33" t="inlineStr">
         <is>
           <t>Rising Dragon</t>
         </is>
       </c>
-      <c r="E2" s="30" t="inlineStr">
+      <c r="E2" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F2" s="30" t="inlineStr">
+      <c r="F2" s="33" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5942,71 +5967,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H2" s="30" t="inlineStr">
+      <c r="H2" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I2" s="30" t="inlineStr">
+      <c r="I2" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J2" s="30" t="inlineStr">
+      <c r="J2" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K2" s="30" t="inlineStr">
+      <c r="K2" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L2" s="30" t="inlineStr">
+      <c r="L2" s="33" t="inlineStr">
         <is>
           <t>RIS-FIL-2406</t>
         </is>
       </c>
-      <c r="M2" s="31" t="inlineStr">
+      <c r="M2" s="34" t="inlineStr">
         <is>
           <t>700175992406</t>
         </is>
       </c>
-      <c r="N2" s="32" t="inlineStr"/>
-      <c r="O2" s="32" t="inlineStr"/>
-      <c r="P2" s="32" t="inlineStr"/>
-      <c r="Q2" s="30" t="inlineStr">
+      <c r="N2" s="35" t="inlineStr"/>
+      <c r="O2" s="35" t="inlineStr"/>
+      <c r="P2" s="35" t="inlineStr"/>
+      <c r="Q2" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R2" s="30" t="inlineStr">
+      <c r="R2" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S2" s="30" t="inlineStr">
+      <c r="S2" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T2" s="30" t="inlineStr">
+      <c r="T2" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U2" s="30" t="inlineStr"/>
-      <c r="V2" s="30" t="inlineStr">
+      <c r="U2" s="33" t="inlineStr"/>
+      <c r="V2" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W2" s="30" t="inlineStr">
+      <c r="W2" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X2" s="30" t="inlineStr">
+      <c r="X2" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6016,7 +6041,7 @@
           <t>https://www.spa-components.com/user/shop/big/1473-1_filter-cartridge-sc779-rising-dragon-plastics--eago-whirlpools.jpg?ff=1&amp;x=1024&amp;y=768&amp;q=85&amp;ts=6720c4a0&amp;sg=161563f2</t>
         </is>
       </c>
-      <c r="Z2" s="30" t="inlineStr">
+      <c r="Z2" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6026,7 +6051,7 @@
           <t>Filter Cartridge SC779 - Rising Dragon Plastics, EAGO Whirlpools - Spa Components</t>
         </is>
       </c>
-      <c r="AB2" s="30" t="inlineStr">
+      <c r="AB2" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6038,10 +6063,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF2" s="30" t="inlineStr"/>
-      <c r="AG2" s="30" t="inlineStr"/>
-      <c r="AH2" s="30" t="inlineStr"/>
-      <c r="AI2" s="30" t="inlineStr"/>
+      <c r="AF2" s="33" t="inlineStr"/>
+      <c r="AG2" s="33" t="inlineStr"/>
+      <c r="AH2" s="33" t="inlineStr"/>
+      <c r="AI2" s="33" t="inlineStr"/>
     </row>
     <row r="3" ht="62" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
@@ -6059,13 +6084,13 @@
           <t>A twin pack of Size II replacement filter cartridges measuring 10.6 x 13.6 cm, designed for compatible pool and spa filtration systems. The fine lamellar structure delivers thorough water cleaning and the cartridges are easy to rinse clean.</t>
         </is>
       </c>
-      <c r="D3" s="30" t="inlineStr"/>
-      <c r="E3" s="30" t="inlineStr">
+      <c r="D3" s="33" t="inlineStr"/>
+      <c r="E3" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F3" s="30" t="inlineStr">
+      <c r="F3" s="33" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6075,71 +6100,71 @@
           <t>filters, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H3" s="30" t="inlineStr">
+      <c r="H3" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I3" s="30" t="inlineStr">
+      <c r="I3" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J3" s="30" t="inlineStr">
+      <c r="J3" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K3" s="30" t="inlineStr">
+      <c r="K3" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L3" s="30" t="inlineStr">
+      <c r="L3" s="33" t="inlineStr">
         <is>
           <t>GEN-FIL-3615</t>
         </is>
       </c>
-      <c r="M3" s="31" t="inlineStr">
+      <c r="M3" s="34" t="inlineStr">
         <is>
           <t>6941607353615</t>
         </is>
       </c>
-      <c r="N3" s="32" t="inlineStr"/>
-      <c r="O3" s="32" t="inlineStr"/>
-      <c r="P3" s="32" t="inlineStr"/>
-      <c r="Q3" s="30" t="inlineStr">
+      <c r="N3" s="35" t="inlineStr"/>
+      <c r="O3" s="35" t="inlineStr"/>
+      <c r="P3" s="35" t="inlineStr"/>
+      <c r="Q3" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R3" s="30" t="inlineStr">
+      <c r="R3" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S3" s="30" t="inlineStr">
+      <c r="S3" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T3" s="30" t="inlineStr">
+      <c r="T3" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U3" s="30" t="inlineStr"/>
-      <c r="V3" s="30" t="inlineStr">
+      <c r="U3" s="33" t="inlineStr"/>
+      <c r="V3" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W3" s="30" t="inlineStr">
+      <c r="W3" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X3" s="30" t="inlineStr">
+      <c r="X3" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6149,7 +6174,7 @@
           <t>https://www.bestwaystore.de/media/c6/f8/ba/1756384660/6941607353615-main-jpg.jpg?ts=1756384660</t>
         </is>
       </c>
-      <c r="Z3" s="30" t="inlineStr">
+      <c r="Z3" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6159,7 +6184,7 @@
           <t>Filter cartridge Size II double pack, 10.6 x 13.6 cm | 58094_26</t>
         </is>
       </c>
-      <c r="AB3" s="30" t="inlineStr">
+      <c r="AB3" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6171,14 +6196,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF3" s="30" t="inlineStr"/>
-      <c r="AG3" s="30" t="inlineStr"/>
-      <c r="AH3" s="30" t="inlineStr">
+      <c r="AF3" s="33" t="inlineStr"/>
+      <c r="AG3" s="33" t="inlineStr"/>
+      <c r="AH3" s="33" t="inlineStr">
         <is>
           <t>10.6cm</t>
         </is>
       </c>
-      <c r="AI3" s="30" t="inlineStr">
+      <c r="AI3" s="33" t="inlineStr">
         <is>
           <t>13.6cm</t>
         </is>
@@ -6200,17 +6225,17 @@
           <t>A single Flowclear Size 3 replacement filter cartridge for compatible Bestway pool filtration systems, featuring a fine lamellar structure that traps deposits and dirt effectively. Easy to clean and straightforward to swap out when routine maintenance is due.</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="33" t="inlineStr">
         <is>
           <t>Bestway</t>
         </is>
       </c>
-      <c r="E4" s="30" t="inlineStr">
+      <c r="E4" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F4" s="30" t="inlineStr">
+      <c r="F4" s="33" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6220,71 +6245,71 @@
           <t>filters, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H4" s="30" t="inlineStr">
+      <c r="H4" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I4" s="30" t="inlineStr">
+      <c r="I4" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J4" s="30" t="inlineStr">
+      <c r="J4" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K4" s="30" t="inlineStr">
+      <c r="K4" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L4" s="30" t="inlineStr">
+      <c r="L4" s="33" t="inlineStr">
         <is>
           <t>BES-FIL-3592</t>
         </is>
       </c>
-      <c r="M4" s="31" t="inlineStr">
+      <c r="M4" s="34" t="inlineStr">
         <is>
           <t>6941607353592</t>
         </is>
       </c>
-      <c r="N4" s="32" t="inlineStr"/>
-      <c r="O4" s="32" t="inlineStr"/>
-      <c r="P4" s="32" t="inlineStr"/>
-      <c r="Q4" s="30" t="inlineStr">
+      <c r="N4" s="35" t="inlineStr"/>
+      <c r="O4" s="35" t="inlineStr"/>
+      <c r="P4" s="35" t="inlineStr"/>
+      <c r="Q4" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R4" s="30" t="inlineStr">
+      <c r="R4" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S4" s="30" t="inlineStr">
+      <c r="S4" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T4" s="30" t="inlineStr">
+      <c r="T4" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U4" s="30" t="inlineStr"/>
-      <c r="V4" s="30" t="inlineStr">
+      <c r="U4" s="33" t="inlineStr"/>
+      <c r="V4" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W4" s="30" t="inlineStr">
+      <c r="W4" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X4" s="30" t="inlineStr">
+      <c r="X4" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6294,7 +6319,7 @@
           <t>https://ap.nice-cdn.com/upload/image/product/large/default/bestway-flowclear-filter-cartridge-size-3-1-item-638140-en.jpg</t>
         </is>
       </c>
-      <c r="Z4" s="30" t="inlineStr">
+      <c r="Z4" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6304,7 +6329,7 @@
           <t>Bestway Flowclear™ Filter Cartridge Size 3, 1 item</t>
         </is>
       </c>
-      <c r="AB4" s="30" t="inlineStr">
+      <c r="AB4" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6316,10 +6341,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF4" s="30" t="inlineStr"/>
-      <c r="AG4" s="30" t="inlineStr"/>
-      <c r="AH4" s="30" t="inlineStr"/>
-      <c r="AI4" s="30" t="inlineStr"/>
+      <c r="AF4" s="33" t="inlineStr"/>
+      <c r="AG4" s="33" t="inlineStr"/>
+      <c r="AH4" s="33" t="inlineStr"/>
+      <c r="AI4" s="33" t="inlineStr"/>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="17" t="inlineStr">
@@ -6337,17 +6362,17 @@
           <t>A two-pack of compatible hot tub and spa cartridge filters corresponding to Unicel C-4335, Pleatco PRB35-IN, and Filbur FC-2385 references. A handy spare-pair to keep on hand so your tub is never without a fresh filter.</t>
         </is>
       </c>
-      <c r="D5" s="30" t="inlineStr">
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E5" s="30" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F5" s="30" t="inlineStr">
+      <c r="F5" s="33" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6357,71 +6382,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H5" s="30" t="inlineStr">
+      <c r="H5" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I5" s="30" t="inlineStr">
+      <c r="I5" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J5" s="30" t="inlineStr">
+      <c r="J5" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K5" s="30" t="inlineStr">
+      <c r="K5" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L5" s="30" t="inlineStr">
+      <c r="L5" s="33" t="inlineStr">
         <is>
           <t>DAR-FIL-1669</t>
         </is>
       </c>
-      <c r="M5" s="31" t="inlineStr">
+      <c r="M5" s="34" t="inlineStr">
         <is>
           <t>700175991669</t>
         </is>
       </c>
-      <c r="N5" s="32" t="inlineStr"/>
-      <c r="O5" s="32" t="inlineStr"/>
-      <c r="P5" s="32" t="inlineStr"/>
-      <c r="Q5" s="30" t="inlineStr">
+      <c r="N5" s="35" t="inlineStr"/>
+      <c r="O5" s="35" t="inlineStr"/>
+      <c r="P5" s="35" t="inlineStr"/>
+      <c r="Q5" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R5" s="30" t="inlineStr">
+      <c r="R5" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S5" s="30" t="inlineStr">
+      <c r="S5" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T5" s="30" t="inlineStr">
+      <c r="T5" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U5" s="30" t="inlineStr"/>
-      <c r="V5" s="30" t="inlineStr">
+      <c r="U5" s="33" t="inlineStr"/>
+      <c r="V5" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W5" s="30" t="inlineStr">
+      <c r="W5" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X5" s="30" t="inlineStr">
+      <c r="X5" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6431,7 +6456,7 @@
           <t>https://images.barcodelookup.com/29361/293617958-1.jpg</t>
         </is>
       </c>
-      <c r="Z5" s="30" t="inlineStr">
+      <c r="Z5" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6441,7 +6466,7 @@
           <t>Darlly Hot Tub Spa Filter SC705 40353 Compatible with Unicel C-4335 PRB35-IN Filbur FC-2385 2 Pack</t>
         </is>
       </c>
-      <c r="AB5" s="30" t="inlineStr">
+      <c r="AB5" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6453,10 +6478,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF5" s="30" t="inlineStr"/>
-      <c r="AG5" s="30" t="inlineStr"/>
-      <c r="AH5" s="30" t="inlineStr"/>
-      <c r="AI5" s="30" t="inlineStr"/>
+      <c r="AF5" s="33" t="inlineStr"/>
+      <c r="AG5" s="33" t="inlineStr"/>
+      <c r="AH5" s="33" t="inlineStr"/>
+      <c r="AI5" s="33" t="inlineStr"/>
     </row>
     <row r="6" ht="62" customHeight="1">
       <c r="A6" s="17" t="inlineStr">
@@ -6474,13 +6499,13 @@
           <t>A single Size IV replacement filter cartridge measuring 14.2 x 25.4 cm, compatible with Bestway filter pump 58391 (9,463 l/h). Its deep-fold, fine-structure media delivers thorough water cleaning and can be rinsed clean with minimal effort.</t>
         </is>
       </c>
-      <c r="D6" s="30" t="inlineStr"/>
-      <c r="E6" s="30" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr"/>
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F6" s="30" t="inlineStr">
+      <c r="F6" s="33" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6490,71 +6515,71 @@
           <t>filters, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H6" s="30" t="inlineStr">
+      <c r="H6" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I6" s="30" t="inlineStr">
+      <c r="I6" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J6" s="30" t="inlineStr">
+      <c r="J6" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K6" s="30" t="inlineStr">
+      <c r="K6" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L6" s="30" t="inlineStr">
+      <c r="L6" s="33" t="inlineStr">
         <is>
           <t>GEN-FIL-3622</t>
         </is>
       </c>
-      <c r="M6" s="31" t="inlineStr">
+      <c r="M6" s="34" t="inlineStr">
         <is>
           <t>6941607353622</t>
         </is>
       </c>
-      <c r="N6" s="32" t="inlineStr"/>
-      <c r="O6" s="32" t="inlineStr"/>
-      <c r="P6" s="32" t="inlineStr"/>
-      <c r="Q6" s="30" t="inlineStr">
+      <c r="N6" s="35" t="inlineStr"/>
+      <c r="O6" s="35" t="inlineStr"/>
+      <c r="P6" s="35" t="inlineStr"/>
+      <c r="Q6" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R6" s="30" t="inlineStr">
+      <c r="R6" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S6" s="30" t="inlineStr">
+      <c r="S6" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T6" s="30" t="inlineStr">
+      <c r="T6" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U6" s="30" t="inlineStr"/>
-      <c r="V6" s="30" t="inlineStr">
+      <c r="U6" s="33" t="inlineStr"/>
+      <c r="V6" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W6" s="30" t="inlineStr">
+      <c r="W6" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X6" s="30" t="inlineStr">
+      <c r="X6" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6564,7 +6589,7 @@
           <t>https://www.bestwaystore.de/media/53/6c/e9/1756384676/6941607353622-main-jpg.jpg?ts=1756384676</t>
         </is>
       </c>
-      <c r="Z6" s="30" t="inlineStr">
+      <c r="Z6" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6574,7 +6599,7 @@
           <t>Filter cartridge Size IV 14.2 x 25.4 cm | 58095_26</t>
         </is>
       </c>
-      <c r="AB6" s="30" t="inlineStr">
+      <c r="AB6" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6586,14 +6611,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF6" s="30" t="inlineStr"/>
-      <c r="AG6" s="30" t="inlineStr"/>
-      <c r="AH6" s="30" t="inlineStr">
+      <c r="AF6" s="33" t="inlineStr"/>
+      <c r="AG6" s="33" t="inlineStr"/>
+      <c r="AH6" s="33" t="inlineStr">
         <is>
           <t>14.2cm</t>
         </is>
       </c>
-      <c r="AI6" s="30" t="inlineStr">
+      <c r="AI6" s="33" t="inlineStr">
         <is>
           <t>25.4cm</t>
         </is>
@@ -6615,17 +6640,17 @@
           <t>A pair of Darlly spa filter cartridges in the SC726 reference, also cross-referenced as Unicel C-4401 and Pleatco PRB17.5SF PR. Buying in pairs means a fresh replacement is always ready when it is time to swap.</t>
         </is>
       </c>
-      <c r="D7" s="30" t="inlineStr">
+      <c r="D7" s="33" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E7" s="30" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F7" s="30" t="inlineStr">
+      <c r="F7" s="33" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6635,71 +6660,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H7" s="30" t="inlineStr">
+      <c r="H7" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I7" s="30" t="inlineStr">
+      <c r="I7" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J7" s="30" t="inlineStr">
+      <c r="J7" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K7" s="30" t="inlineStr">
+      <c r="K7" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L7" s="30" t="inlineStr">
+      <c r="L7" s="33" t="inlineStr">
         <is>
           <t>DAR-FIL-1874</t>
         </is>
       </c>
-      <c r="M7" s="31" t="inlineStr">
+      <c r="M7" s="34" t="inlineStr">
         <is>
           <t>700175991874</t>
         </is>
       </c>
-      <c r="N7" s="32" t="inlineStr"/>
-      <c r="O7" s="32" t="inlineStr"/>
-      <c r="P7" s="32" t="inlineStr"/>
-      <c r="Q7" s="30" t="inlineStr">
+      <c r="N7" s="35" t="inlineStr"/>
+      <c r="O7" s="35" t="inlineStr"/>
+      <c r="P7" s="35" t="inlineStr"/>
+      <c r="Q7" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R7" s="30" t="inlineStr">
+      <c r="R7" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S7" s="30" t="inlineStr">
+      <c r="S7" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T7" s="30" t="inlineStr">
+      <c r="T7" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U7" s="30" t="inlineStr"/>
-      <c r="V7" s="30" t="inlineStr">
+      <c r="U7" s="33" t="inlineStr"/>
+      <c r="V7" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W7" s="30" t="inlineStr">
+      <c r="W7" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X7" s="30" t="inlineStr">
+      <c r="X7" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6709,7 +6734,7 @@
           <t>https://images.barcodelookup.com/4378/43786454-1.jpg</t>
         </is>
       </c>
-      <c r="Z7" s="30" t="inlineStr">
+      <c r="Z7" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6719,7 +6744,7 @@
           <t>Darlly Spa Filter C-4401, PRB17.5SF PR, SC726 (Pair)</t>
         </is>
       </c>
-      <c r="AB7" s="30" t="inlineStr">
+      <c r="AB7" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6731,10 +6756,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF7" s="30" t="inlineStr"/>
-      <c r="AG7" s="30" t="inlineStr"/>
-      <c r="AH7" s="30" t="inlineStr"/>
-      <c r="AI7" s="30" t="inlineStr"/>
+      <c r="AF7" s="33" t="inlineStr"/>
+      <c r="AG7" s="33" t="inlineStr"/>
+      <c r="AH7" s="33" t="inlineStr"/>
+      <c r="AI7" s="33" t="inlineStr"/>
     </row>
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="17" t="inlineStr">
@@ -6752,17 +6777,17 @@
           <t>A replacement spa filter cartridge compatible with Arctic, Beachcomber, Canadian, Hydropool and Jacuzzi spas, sold under cross-reference codes including Unicel C-4950, Pleatco PRB50-IN and Darlly 40506. It keeps hot tub water clean by trapping debris and particles as water cycles through the filtration system.</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="D8" s="33" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F8" s="30" t="inlineStr">
+      <c r="F8" s="33" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6772,71 +6797,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H8" s="30" t="inlineStr">
+      <c r="H8" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I8" s="30" t="inlineStr">
+      <c r="I8" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J8" s="30" t="inlineStr">
+      <c r="J8" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K8" s="30" t="inlineStr">
+      <c r="K8" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L8" s="30" t="inlineStr">
+      <c r="L8" s="33" t="inlineStr">
         <is>
           <t>DAR-FIL-1676</t>
         </is>
       </c>
-      <c r="M8" s="31" t="inlineStr">
+      <c r="M8" s="34" t="inlineStr">
         <is>
           <t>700175991676</t>
         </is>
       </c>
-      <c r="N8" s="32" t="inlineStr"/>
-      <c r="O8" s="32" t="inlineStr"/>
-      <c r="P8" s="32" t="inlineStr"/>
-      <c r="Q8" s="30" t="inlineStr">
+      <c r="N8" s="35" t="inlineStr"/>
+      <c r="O8" s="35" t="inlineStr"/>
+      <c r="P8" s="35" t="inlineStr"/>
+      <c r="Q8" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R8" s="30" t="inlineStr">
+      <c r="R8" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S8" s="30" t="inlineStr">
+      <c r="S8" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T8" s="30" t="inlineStr">
+      <c r="T8" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U8" s="30" t="inlineStr"/>
-      <c r="V8" s="30" t="inlineStr">
+      <c r="U8" s="33" t="inlineStr"/>
+      <c r="V8" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W8" s="30" t="inlineStr">
+      <c r="W8" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X8" s="30" t="inlineStr">
+      <c r="X8" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6846,7 +6871,7 @@
           <t>https://images.barcodelookup.com/4469/44699532-1.jpg</t>
         </is>
       </c>
-      <c r="Z8" s="30" t="inlineStr">
+      <c r="Z8" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6856,7 +6881,7 @@
           <t>Hot Tub Filter Unicel C4950 / C-4950 50' Spa Cartridge Pleatco PRB501N Darlly 40506 for Arctic, Beachcomber, Canadian,…</t>
         </is>
       </c>
-      <c r="AB8" s="30" t="inlineStr">
+      <c r="AB8" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6868,10 +6893,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF8" s="30" t="inlineStr"/>
-      <c r="AG8" s="30" t="inlineStr"/>
-      <c r="AH8" s="30" t="inlineStr"/>
-      <c r="AI8" s="30" t="inlineStr"/>
+      <c r="AF8" s="33" t="inlineStr"/>
+      <c r="AG8" s="33" t="inlineStr"/>
+      <c r="AH8" s="33" t="inlineStr"/>
+      <c r="AI8" s="33" t="inlineStr"/>
     </row>
     <row r="9" ht="76" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
@@ -6889,13 +6914,13 @@
           <t>A square inflatable hot tub for up to four people, with an overall outer diameter of 2.45 m and a structure measuring 1.75 x 1.75 x 0.71 m, built from high-resistance polyester for good rigidity and durability. The packaged weight is 64.92 kg, so you will want a helper on delivery day.</t>
         </is>
       </c>
-      <c r="D9" s="30" t="inlineStr"/>
-      <c r="E9" s="30" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr"/>
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F9" s="30" t="inlineStr">
+      <c r="F9" s="33" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -6905,75 +6930,75 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H9" s="30" t="inlineStr">
+      <c r="H9" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I9" s="30" t="inlineStr">
+      <c r="I9" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J9" s="30" t="inlineStr">
+      <c r="J9" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K9" s="30" t="inlineStr">
+      <c r="K9" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L9" s="30" t="inlineStr">
+      <c r="L9" s="33" t="inlineStr">
         <is>
           <t>GEN-SPA-3395</t>
         </is>
       </c>
-      <c r="M9" s="31" t="inlineStr">
+      <c r="M9" s="34" t="inlineStr">
         <is>
           <t>6941057423395</t>
         </is>
       </c>
-      <c r="N9" s="32" t="inlineStr"/>
-      <c r="O9" s="32" t="inlineStr"/>
-      <c r="P9" s="32" t="inlineStr"/>
-      <c r="Q9" s="30" t="inlineStr">
+      <c r="N9" s="35" t="inlineStr"/>
+      <c r="O9" s="35" t="inlineStr"/>
+      <c r="P9" s="35" t="inlineStr"/>
+      <c r="Q9" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R9" s="30" t="inlineStr">
+      <c r="R9" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S9" s="30" t="inlineStr">
+      <c r="S9" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T9" s="30" t="inlineStr">
+      <c r="T9" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U9" s="30" t="inlineStr">
+      <c r="U9" s="33" t="inlineStr">
         <is>
           <t>64920</t>
         </is>
       </c>
-      <c r="V9" s="30" t="inlineStr">
+      <c r="V9" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W9" s="30" t="inlineStr">
+      <c r="W9" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X9" s="30" t="inlineStr">
+      <c r="X9" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6983,7 +7008,7 @@
           <t>https://media.intex.fr/7743-large_default_x2/28464ex-spa-gonflable-calacatta-4-places.jpg</t>
         </is>
       </c>
-      <c r="Z9" s="30" t="inlineStr">
+      <c r="Z9" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6993,7 +7018,7 @@
           <t>Calacatta 4-person Inflatable Spa</t>
         </is>
       </c>
-      <c r="AB9" s="30" t="inlineStr">
+      <c r="AB9" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7005,18 +7030,18 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF9" s="30" t="inlineStr"/>
-      <c r="AG9" s="30" t="inlineStr">
+      <c r="AF9" s="33" t="inlineStr"/>
+      <c r="AG9" s="33" t="inlineStr">
         <is>
           <t>175.0cm</t>
         </is>
       </c>
-      <c r="AH9" s="30" t="inlineStr">
+      <c r="AH9" s="33" t="inlineStr">
         <is>
           <t>175.0cm</t>
         </is>
       </c>
-      <c r="AI9" s="30" t="inlineStr">
+      <c r="AI9" s="33" t="inlineStr">
         <is>
           <t>71.0cm</t>
         </is>
@@ -7038,17 +7063,17 @@
           <t>A 3.0 kg tub of hth stabiliser granules for outdoor swimming pools, used to protect chlorine from UV degradation and extend its effectiveness. A reliable way to get more mileage from your sanitiser on sunny days.</t>
         </is>
       </c>
-      <c r="D10" s="30" t="inlineStr">
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E10" s="30" t="inlineStr">
+      <c r="E10" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F10" s="30" t="inlineStr">
+      <c r="F10" s="33" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -7058,75 +7083,75 @@
           <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H10" s="30" t="inlineStr">
+      <c r="H10" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I10" s="30" t="inlineStr">
+      <c r="I10" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J10" s="30" t="inlineStr">
+      <c r="J10" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K10" s="30" t="inlineStr">
+      <c r="K10" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L10" s="30" t="inlineStr">
+      <c r="L10" s="33" t="inlineStr">
         <is>
           <t>HTH-CHM-5716</t>
         </is>
       </c>
-      <c r="M10" s="31" t="inlineStr">
+      <c r="M10" s="34" t="inlineStr">
         <is>
           <t>3521686005716</t>
         </is>
       </c>
-      <c r="N10" s="32" t="inlineStr"/>
-      <c r="O10" s="32" t="inlineStr"/>
-      <c r="P10" s="32" t="inlineStr"/>
-      <c r="Q10" s="30" t="inlineStr">
+      <c r="N10" s="35" t="inlineStr"/>
+      <c r="O10" s="35" t="inlineStr"/>
+      <c r="P10" s="35" t="inlineStr"/>
+      <c r="Q10" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R10" s="30" t="inlineStr">
+      <c r="R10" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S10" s="30" t="inlineStr">
+      <c r="S10" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T10" s="30" t="inlineStr">
+      <c r="T10" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U10" s="30" t="inlineStr">
+      <c r="U10" s="33" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="V10" s="30" t="inlineStr">
+      <c r="V10" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W10" s="30" t="inlineStr">
+      <c r="W10" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X10" s="30" t="inlineStr">
+      <c r="X10" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7136,7 +7161,7 @@
           <t>https://images.barcodelookup.com/12027/120276177-1.jpg</t>
         </is>
       </c>
-      <c r="Z10" s="30" t="inlineStr">
+      <c r="Z10" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7146,7 +7171,7 @@
           <t>Hth Stabilizer Granulat 3,0 Kg</t>
         </is>
       </c>
-      <c r="AB10" s="30" t="inlineStr">
+      <c r="AB10" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7158,10 +7183,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF10" s="30" t="inlineStr"/>
-      <c r="AG10" s="30" t="inlineStr"/>
-      <c r="AH10" s="30" t="inlineStr"/>
-      <c r="AI10" s="30" t="inlineStr"/>
+      <c r="AF10" s="33" t="inlineStr"/>
+      <c r="AG10" s="33" t="inlineStr"/>
+      <c r="AH10" s="33" t="inlineStr"/>
+      <c r="AI10" s="33" t="inlineStr"/>
     </row>
     <row r="11" ht="62" customHeight="1">
       <c r="A11" s="17" t="inlineStr">
@@ -7179,17 +7204,17 @@
           <t>A 1-litre bottle of hth Spa Antikalk, formulated to prevent and remove limescale in spa and hot tub water. Keeping scale under control helps protect internal components and maintain water clarity.</t>
         </is>
       </c>
-      <c r="D11" s="30" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E11" s="30" t="inlineStr">
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F11" s="30" t="inlineStr">
+      <c r="F11" s="33" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -7199,71 +7224,71 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H11" s="30" t="inlineStr">
+      <c r="H11" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I11" s="30" t="inlineStr">
+      <c r="I11" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J11" s="30" t="inlineStr">
+      <c r="J11" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K11" s="30" t="inlineStr">
+      <c r="K11" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L11" s="30" t="inlineStr">
+      <c r="L11" s="33" t="inlineStr">
         <is>
           <t>HTH-SPA-0194</t>
         </is>
       </c>
-      <c r="M11" s="31" t="inlineStr">
+      <c r="M11" s="34" t="inlineStr">
         <is>
           <t>3521684700194</t>
         </is>
       </c>
-      <c r="N11" s="32" t="inlineStr"/>
-      <c r="O11" s="32" t="inlineStr"/>
-      <c r="P11" s="32" t="inlineStr"/>
-      <c r="Q11" s="30" t="inlineStr">
+      <c r="N11" s="35" t="inlineStr"/>
+      <c r="O11" s="35" t="inlineStr"/>
+      <c r="P11" s="35" t="inlineStr"/>
+      <c r="Q11" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R11" s="30" t="inlineStr">
+      <c r="R11" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S11" s="30" t="inlineStr">
+      <c r="S11" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T11" s="30" t="inlineStr">
+      <c r="T11" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U11" s="30" t="inlineStr"/>
-      <c r="V11" s="30" t="inlineStr">
+      <c r="U11" s="33" t="inlineStr"/>
+      <c r="V11" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W11" s="30" t="inlineStr">
+      <c r="W11" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X11" s="30" t="inlineStr">
+      <c r="X11" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7273,7 +7298,7 @@
           <t>https://www.north-spa.de/wp-content/uploads/2025/02/Produktbild-1-hth-SPA-ANTIKALK-1-l-3521684700194-360x360.jpg</t>
         </is>
       </c>
-      <c r="Z11" s="30" t="inlineStr">
+      <c r="Z11" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7283,7 +7308,7 @@
           <t>1 l - hth® Spa ANTIKALK</t>
         </is>
       </c>
-      <c r="AB11" s="30" t="inlineStr">
+      <c r="AB11" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7295,10 +7320,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF11" s="30" t="inlineStr"/>
-      <c r="AG11" s="30" t="inlineStr"/>
-      <c r="AH11" s="30" t="inlineStr"/>
-      <c r="AI11" s="30" t="inlineStr"/>
+      <c r="AF11" s="33" t="inlineStr"/>
+      <c r="AG11" s="33" t="inlineStr"/>
+      <c r="AH11" s="33" t="inlineStr"/>
+      <c r="AI11" s="33" t="inlineStr"/>
     </row>
     <row r="12" ht="62" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
@@ -7316,13 +7341,13 @@
           <t>A round, olive-green inflatable spa designed to seat up to eight people comfortably, with a maximum water temperature of 40°C. Five accessories are included in the box, so there is plenty to get started with straight away.</t>
         </is>
       </c>
-      <c r="D12" s="30" t="inlineStr"/>
-      <c r="E12" s="30" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr"/>
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F12" s="30" t="inlineStr">
+      <c r="F12" s="33" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -7332,71 +7357,71 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H12" s="30" t="inlineStr">
+      <c r="H12" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I12" s="30" t="inlineStr">
+      <c r="I12" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J12" s="30" t="inlineStr">
+      <c r="J12" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K12" s="30" t="inlineStr">
+      <c r="K12" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L12" s="30" t="inlineStr">
+      <c r="L12" s="33" t="inlineStr">
         <is>
           <t>GEN-SPA-9274</t>
         </is>
       </c>
-      <c r="M12" s="31" t="inlineStr">
+      <c r="M12" s="34" t="inlineStr">
         <is>
           <t>6941057429274</t>
         </is>
       </c>
-      <c r="N12" s="32" t="inlineStr"/>
-      <c r="O12" s="32" t="inlineStr"/>
-      <c r="P12" s="32" t="inlineStr"/>
-      <c r="Q12" s="30" t="inlineStr">
+      <c r="N12" s="35" t="inlineStr"/>
+      <c r="O12" s="35" t="inlineStr"/>
+      <c r="P12" s="35" t="inlineStr"/>
+      <c r="Q12" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R12" s="30" t="inlineStr">
+      <c r="R12" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S12" s="30" t="inlineStr">
+      <c r="S12" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T12" s="30" t="inlineStr">
+      <c r="T12" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U12" s="30" t="inlineStr"/>
-      <c r="V12" s="30" t="inlineStr">
+      <c r="U12" s="33" t="inlineStr"/>
+      <c r="V12" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W12" s="30" t="inlineStr">
+      <c r="W12" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X12" s="30" t="inlineStr">
+      <c r="X12" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7406,7 +7431,7 @@
           <t>https://media.intex.fr/11990-large_default_x2/28412np-spa-gonflable-olive-8-places.jpg</t>
         </is>
       </c>
-      <c r="Z12" s="30" t="inlineStr">
+      <c r="Z12" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7416,7 +7441,7 @@
           <t>Olive 8-person Inflatable Spa</t>
         </is>
       </c>
-      <c r="AB12" s="30" t="inlineStr">
+      <c r="AB12" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7428,10 +7453,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF12" s="30" t="inlineStr"/>
-      <c r="AG12" s="30" t="inlineStr"/>
-      <c r="AH12" s="30" t="inlineStr"/>
-      <c r="AI12" s="30" t="inlineStr"/>
+      <c r="AF12" s="33" t="inlineStr"/>
+      <c r="AG12" s="33" t="inlineStr"/>
+      <c r="AH12" s="33" t="inlineStr"/>
+      <c r="AI12" s="33" t="inlineStr"/>
     </row>
     <row r="13" ht="62" customHeight="1">
       <c r="A13" s="17" t="inlineStr">
@@ -7449,17 +7474,17 @@
           <t>A Darlly SC750 replacement cartridge filter compatible with Arctic, Fonteyn, Rota, and Strong Spa hot tubs, among others. A straightforward like-for-like swap to keep your spa water flowing clean.</t>
         </is>
       </c>
-      <c r="D13" s="30" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E13" s="30" t="inlineStr">
+      <c r="E13" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F13" s="30" t="inlineStr">
+      <c r="F13" s="33" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -7469,71 +7494,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H13" s="30" t="inlineStr">
+      <c r="H13" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I13" s="30" t="inlineStr">
+      <c r="I13" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J13" s="30" t="inlineStr">
+      <c r="J13" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K13" s="30" t="inlineStr">
+      <c r="K13" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L13" s="30" t="inlineStr">
+      <c r="L13" s="33" t="inlineStr">
         <is>
           <t>DAR-FIL-2116</t>
         </is>
       </c>
-      <c r="M13" s="31" t="inlineStr">
+      <c r="M13" s="34" t="inlineStr">
         <is>
           <t>700175992116</t>
         </is>
       </c>
-      <c r="N13" s="32" t="inlineStr"/>
-      <c r="O13" s="32" t="inlineStr"/>
-      <c r="P13" s="32" t="inlineStr"/>
-      <c r="Q13" s="30" t="inlineStr">
+      <c r="N13" s="35" t="inlineStr"/>
+      <c r="O13" s="35" t="inlineStr"/>
+      <c r="P13" s="35" t="inlineStr"/>
+      <c r="Q13" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R13" s="30" t="inlineStr">
+      <c r="R13" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S13" s="30" t="inlineStr">
+      <c r="S13" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T13" s="30" t="inlineStr">
+      <c r="T13" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U13" s="30" t="inlineStr"/>
-      <c r="V13" s="30" t="inlineStr">
+      <c r="U13" s="33" t="inlineStr"/>
+      <c r="V13" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W13" s="30" t="inlineStr">
+      <c r="W13" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X13" s="30" t="inlineStr">
+      <c r="X13" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7543,7 +7568,7 @@
           <t>https://images.barcodelookup.com/29338/293384728-1.jpg</t>
         </is>
       </c>
-      <c r="Z13" s="30" t="inlineStr">
+      <c r="Z13" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7553,7 +7578,7 @@
           <t>SC750 Filter Replacement Filter Lamellar Filter Arctic Fonteyn Rota Strong Spa - Darlly</t>
         </is>
       </c>
-      <c r="AB13" s="30" t="inlineStr">
+      <c r="AB13" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7565,10 +7590,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF13" s="30" t="inlineStr"/>
-      <c r="AG13" s="30" t="inlineStr"/>
-      <c r="AH13" s="30" t="inlineStr"/>
-      <c r="AI13" s="30" t="inlineStr"/>
+      <c r="AF13" s="33" t="inlineStr"/>
+      <c r="AG13" s="33" t="inlineStr"/>
+      <c r="AH13" s="33" t="inlineStr"/>
+      <c r="AI13" s="33" t="inlineStr"/>
     </row>
     <row r="14" ht="62" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
@@ -7586,17 +7611,17 @@
           <t>SpaBalancer Clean and Refresh is a spa water treatment product supplied with a sprayer for easy application. It is designed to keep spa water fresh and clean as part of a regular maintenance routine.</t>
         </is>
       </c>
-      <c r="D14" s="30" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>SpaBalancer</t>
         </is>
       </c>
-      <c r="E14" s="30" t="inlineStr">
+      <c r="E14" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F14" s="30" t="inlineStr">
+      <c r="F14" s="33" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -7606,71 +7631,71 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H14" s="30" t="inlineStr">
+      <c r="H14" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I14" s="30" t="inlineStr">
+      <c r="I14" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J14" s="30" t="inlineStr">
+      <c r="J14" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K14" s="30" t="inlineStr">
+      <c r="K14" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L14" s="30" t="inlineStr">
+      <c r="L14" s="33" t="inlineStr">
         <is>
           <t>SPA-CLN-0117</t>
         </is>
       </c>
-      <c r="M14" s="31" t="inlineStr">
+      <c r="M14" s="34" t="inlineStr">
         <is>
           <t>4260374980117</t>
         </is>
       </c>
-      <c r="N14" s="32" t="inlineStr"/>
-      <c r="O14" s="32" t="inlineStr"/>
-      <c r="P14" s="32" t="inlineStr"/>
-      <c r="Q14" s="30" t="inlineStr">
+      <c r="N14" s="35" t="inlineStr"/>
+      <c r="O14" s="35" t="inlineStr"/>
+      <c r="P14" s="35" t="inlineStr"/>
+      <c r="Q14" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R14" s="30" t="inlineStr">
+      <c r="R14" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S14" s="30" t="inlineStr">
+      <c r="S14" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T14" s="30" t="inlineStr">
+      <c r="T14" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U14" s="30" t="inlineStr"/>
-      <c r="V14" s="30" t="inlineStr">
+      <c r="U14" s="33" t="inlineStr"/>
+      <c r="V14" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W14" s="30" t="inlineStr">
+      <c r="W14" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X14" s="30" t="inlineStr">
+      <c r="X14" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7680,7 +7705,7 @@
           <t>https://www.spabalancer.ch/media/ae/20/d2/1728651174/sb111_clean-refresh_freigestellt.png?ts=1777362921</t>
         </is>
       </c>
-      <c r="Z14" s="30" t="inlineStr">
+      <c r="Z14" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7690,7 +7715,7 @@
           <t>SpaBalancer Clean &amp; Refresh (+ sprayer)</t>
         </is>
       </c>
-      <c r="AB14" s="30" t="inlineStr">
+      <c r="AB14" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7702,10 +7727,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF14" s="30" t="inlineStr"/>
-      <c r="AG14" s="30" t="inlineStr"/>
-      <c r="AH14" s="30" t="inlineStr"/>
-      <c r="AI14" s="30" t="inlineStr"/>
+      <c r="AF14" s="33" t="inlineStr"/>
+      <c r="AG14" s="33" t="inlineStr"/>
+      <c r="AH14" s="33" t="inlineStr"/>
+      <c r="AI14" s="33" t="inlineStr"/>
     </row>
     <row r="15" ht="62" customHeight="1">
       <c r="A15" s="17" t="inlineStr">
@@ -7723,17 +7748,17 @@
           <t>A pack of 500 DPD 1 reagent tablets for use with the Water-ID photometer, measuring free chlorine levels in pool or spa water. Having a full pack to hand means you will not run short mid-season.</t>
         </is>
       </c>
-      <c r="D15" s="30" t="inlineStr">
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>Water-i.d.</t>
         </is>
       </c>
-      <c r="E15" s="30" t="inlineStr">
+      <c r="E15" s="33" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F15" s="30" t="inlineStr">
+      <c r="F15" s="33" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -7743,79 +7768,79 @@
           <t>test-measure, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H15" s="30" t="inlineStr">
+      <c r="H15" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I15" s="30" t="inlineStr">
+      <c r="I15" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J15" s="30" t="inlineStr">
+      <c r="J15" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K15" s="30" t="inlineStr">
+      <c r="K15" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L15" s="30" t="inlineStr">
+      <c r="L15" s="33" t="inlineStr">
         <is>
           <t>WAT-TST-1702</t>
         </is>
       </c>
-      <c r="M15" s="31" t="inlineStr">
+      <c r="M15" s="34" t="inlineStr">
         <is>
           <t>4260431461702</t>
         </is>
       </c>
-      <c r="N15" s="32" t="inlineStr"/>
-      <c r="O15" s="32" t="inlineStr"/>
-      <c r="P15" s="32" t="inlineStr"/>
-      <c r="Q15" s="30" t="inlineStr">
+      <c r="N15" s="35" t="inlineStr"/>
+      <c r="O15" s="35" t="inlineStr"/>
+      <c r="P15" s="35" t="inlineStr"/>
+      <c r="Q15" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R15" s="30" t="inlineStr">
+      <c r="R15" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S15" s="30" t="inlineStr">
+      <c r="S15" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T15" s="30" t="inlineStr">
+      <c r="T15" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U15" s="30" t="inlineStr"/>
-      <c r="V15" s="30" t="inlineStr">
+      <c r="U15" s="33" t="inlineStr"/>
+      <c r="V15" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W15" s="30" t="inlineStr">
+      <c r="W15" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X15" s="30" t="inlineStr">
+      <c r="X15" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y15" s="17" t="inlineStr"/>
-      <c r="Z15" s="30" t="inlineStr"/>
+      <c r="Z15" s="33" t="inlineStr"/>
       <c r="AA15" s="17" t="inlineStr"/>
-      <c r="AB15" s="30" t="inlineStr">
+      <c r="AB15" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7827,10 +7852,10 @@
           <t>Pool Accessories</t>
         </is>
       </c>
-      <c r="AF15" s="30" t="inlineStr"/>
-      <c r="AG15" s="30" t="inlineStr"/>
-      <c r="AH15" s="30" t="inlineStr"/>
-      <c r="AI15" s="30" t="inlineStr"/>
+      <c r="AF15" s="33" t="inlineStr"/>
+      <c r="AG15" s="33" t="inlineStr"/>
+      <c r="AH15" s="33" t="inlineStr"/>
+      <c r="AI15" s="33" t="inlineStr"/>
     </row>
     <row r="16" ht="62" customHeight="1">
       <c r="A16" s="17" t="inlineStr">
@@ -7848,17 +7873,17 @@
           <t>A pack of 500 Phenol Red reagent tablets compatible with the Water-ID photometer, used for measuring pH levels in pool or spa water. Accurate pH readings are the foundation of balanced, comfortable water.</t>
         </is>
       </c>
-      <c r="D16" s="30" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>Water-i.d.</t>
         </is>
       </c>
-      <c r="E16" s="30" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F16" s="30" t="inlineStr">
+      <c r="F16" s="33" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -7868,71 +7893,71 @@
           <t>test-measure, add-on, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H16" s="30" t="inlineStr">
+      <c r="H16" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I16" s="30" t="inlineStr">
+      <c r="I16" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J16" s="30" t="inlineStr">
+      <c r="J16" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K16" s="30" t="inlineStr">
+      <c r="K16" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L16" s="30" t="inlineStr">
+      <c r="L16" s="33" t="inlineStr">
         <is>
           <t>WAT-TST-1801</t>
         </is>
       </c>
-      <c r="M16" s="31" t="inlineStr">
+      <c r="M16" s="34" t="inlineStr">
         <is>
           <t>4260431461801</t>
         </is>
       </c>
-      <c r="N16" s="32" t="inlineStr"/>
-      <c r="O16" s="32" t="inlineStr"/>
-      <c r="P16" s="32" t="inlineStr"/>
-      <c r="Q16" s="30" t="inlineStr">
+      <c r="N16" s="35" t="inlineStr"/>
+      <c r="O16" s="35" t="inlineStr"/>
+      <c r="P16" s="35" t="inlineStr"/>
+      <c r="Q16" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R16" s="30" t="inlineStr">
+      <c r="R16" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S16" s="30" t="inlineStr">
+      <c r="S16" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T16" s="30" t="inlineStr">
+      <c r="T16" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U16" s="30" t="inlineStr"/>
-      <c r="V16" s="30" t="inlineStr">
+      <c r="U16" s="33" t="inlineStr"/>
+      <c r="V16" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W16" s="30" t="inlineStr">
+      <c r="W16" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X16" s="30" t="inlineStr">
+      <c r="X16" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7942,7 +7967,7 @@
           <t>https://www.poolpowershop.de/media/46/63/13/1743521499/phenol-red-testtabletten-fuer-poollab-500-stk.jpg</t>
         </is>
       </c>
-      <c r="Z16" s="30" t="inlineStr">
+      <c r="Z16" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7952,7 +7977,7 @@
           <t>WATER-I.D. Water-ID Reagenzien Phenol Red Photometer 500</t>
         </is>
       </c>
-      <c r="AB16" s="30" t="inlineStr">
+      <c r="AB16" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7964,10 +7989,10 @@
           <t>Pool Accessories</t>
         </is>
       </c>
-      <c r="AF16" s="30" t="inlineStr"/>
-      <c r="AG16" s="30" t="inlineStr"/>
-      <c r="AH16" s="30" t="inlineStr"/>
-      <c r="AI16" s="30" t="inlineStr"/>
+      <c r="AF16" s="33" t="inlineStr"/>
+      <c r="AG16" s="33" t="inlineStr"/>
+      <c r="AH16" s="33" t="inlineStr"/>
+      <c r="AI16" s="33" t="inlineStr"/>
     </row>
     <row r="17" ht="62" customHeight="1">
       <c r="A17" s="17" t="inlineStr">
@@ -7985,17 +8010,17 @@
           <t>An alkaline edge and surround cleaner in a 1-litre bottle, formulated to be gentle on pool liners, foils, and plastic surfaces. It tackles waterline grime without harming the materials it touches.</t>
         </is>
       </c>
-      <c r="D17" s="30" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>Cristal</t>
         </is>
       </c>
-      <c r="E17" s="30" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F17" s="30" t="inlineStr">
+      <c r="F17" s="33" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8005,71 +8030,71 @@
           <t>pool, water-treatment, cleaning, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H17" s="30" t="inlineStr">
+      <c r="H17" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I17" s="30" t="inlineStr">
+      <c r="I17" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J17" s="30" t="inlineStr">
+      <c r="J17" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K17" s="30" t="inlineStr">
+      <c r="K17" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L17" s="30" t="inlineStr">
+      <c r="L17" s="33" t="inlineStr">
         <is>
           <t>CRI-CHM-5212</t>
         </is>
       </c>
-      <c r="M17" s="31" t="inlineStr">
+      <c r="M17" s="34" t="inlineStr">
         <is>
           <t>4002369155212</t>
         </is>
       </c>
-      <c r="N17" s="32" t="inlineStr"/>
-      <c r="O17" s="32" t="inlineStr"/>
-      <c r="P17" s="32" t="inlineStr"/>
-      <c r="Q17" s="30" t="inlineStr">
+      <c r="N17" s="35" t="inlineStr"/>
+      <c r="O17" s="35" t="inlineStr"/>
+      <c r="P17" s="35" t="inlineStr"/>
+      <c r="Q17" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R17" s="30" t="inlineStr">
+      <c r="R17" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S17" s="30" t="inlineStr">
+      <c r="S17" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T17" s="30" t="inlineStr">
+      <c r="T17" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U17" s="30" t="inlineStr"/>
-      <c r="V17" s="30" t="inlineStr">
+      <c r="U17" s="33" t="inlineStr"/>
+      <c r="V17" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W17" s="30" t="inlineStr">
+      <c r="W17" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X17" s="30" t="inlineStr">
+      <c r="X17" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8079,7 +8104,7 @@
           <t>https://images.barcodelookup.com/21057/210579756-1.jpg</t>
         </is>
       </c>
-      <c r="Z17" s="30" t="inlineStr">
+      <c r="Z17" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8089,7 +8114,7 @@
           <t>Cristal Poolpflege CRISTAL Alkaline Edge Cleaner 1,0 l, (Gentle on Materials, for Liners, Plastic Surfaces</t>
         </is>
       </c>
-      <c r="AB17" s="30" t="inlineStr">
+      <c r="AB17" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8101,10 +8126,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF17" s="30" t="inlineStr"/>
-      <c r="AG17" s="30" t="inlineStr"/>
-      <c r="AH17" s="30" t="inlineStr"/>
-      <c r="AI17" s="30" t="inlineStr"/>
+      <c r="AF17" s="33" t="inlineStr"/>
+      <c r="AG17" s="33" t="inlineStr"/>
+      <c r="AH17" s="33" t="inlineStr"/>
+      <c r="AI17" s="33" t="inlineStr"/>
     </row>
     <row r="18" ht="76" customHeight="1">
       <c r="A18" s="17" t="inlineStr">
@@ -8122,17 +8147,17 @@
           <t>A 1-litre pool surface cleaner formulated to remove sunscreen oils and greasy residues from the water surface, designed specifically for warm Mediterranean climates and heavy swimming loads. It keeps the waterline and surface clear without harming pool materials.</t>
         </is>
       </c>
-      <c r="D18" s="30" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E18" s="30" t="inlineStr">
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F18" s="30" t="inlineStr">
+      <c r="F18" s="33" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8142,71 +8167,71 @@
           <t>pool, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H18" s="30" t="inlineStr">
+      <c r="H18" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I18" s="30" t="inlineStr">
+      <c r="I18" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J18" s="30" t="inlineStr">
+      <c r="J18" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K18" s="30" t="inlineStr">
+      <c r="K18" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L18" s="30" t="inlineStr">
+      <c r="L18" s="33" t="inlineStr">
         <is>
           <t>AQU-CLN-0223</t>
         </is>
       </c>
-      <c r="M18" s="31" t="inlineStr">
+      <c r="M18" s="34" t="inlineStr">
         <is>
           <t>5292638000223</t>
         </is>
       </c>
-      <c r="N18" s="32" t="inlineStr"/>
-      <c r="O18" s="32" t="inlineStr"/>
-      <c r="P18" s="32" t="inlineStr"/>
-      <c r="Q18" s="30" t="inlineStr">
+      <c r="N18" s="35" t="inlineStr"/>
+      <c r="O18" s="35" t="inlineStr"/>
+      <c r="P18" s="35" t="inlineStr"/>
+      <c r="Q18" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R18" s="30" t="inlineStr">
+      <c r="R18" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S18" s="30" t="inlineStr">
+      <c r="S18" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T18" s="30" t="inlineStr">
+      <c r="T18" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U18" s="30" t="inlineStr"/>
-      <c r="V18" s="30" t="inlineStr">
+      <c r="U18" s="33" t="inlineStr"/>
+      <c r="V18" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W18" s="30" t="inlineStr">
+      <c r="W18" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X18" s="30" t="inlineStr">
+      <c r="X18" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8216,7 +8241,7 @@
           <t>http://mangas.com.cy/media/products/5292638000223.jpg</t>
         </is>
       </c>
-      <c r="Z18" s="30" t="inlineStr">
+      <c r="Z18" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8226,7 +8251,7 @@
           <t>AQUALITY Pool Cleaner for Greasy Residues 1L</t>
         </is>
       </c>
-      <c r="AB18" s="30" t="inlineStr">
+      <c r="AB18" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8238,10 +8263,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF18" s="30" t="inlineStr"/>
-      <c r="AG18" s="30" t="inlineStr"/>
-      <c r="AH18" s="30" t="inlineStr"/>
-      <c r="AI18" s="30" t="inlineStr"/>
+      <c r="AF18" s="33" t="inlineStr"/>
+      <c r="AG18" s="33" t="inlineStr"/>
+      <c r="AH18" s="33" t="inlineStr"/>
+      <c r="AI18" s="33" t="inlineStr"/>
     </row>
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="17" t="inlineStr">
@@ -8259,17 +8284,17 @@
           <t>California Clear Blue is a super-concentrated, pH-neutral pool clarifier in a 1-litre bottle, using a cationic polymer formula to bind microscopic particles such as dust, pollen, and oils into larger clusters your filter can catch. Non-toxic and biodegradable, it is safe for sand, zeolite, and glass filtration media.</t>
         </is>
       </c>
-      <c r="D19" s="30" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E19" s="30" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F19" s="30" t="inlineStr">
+      <c r="F19" s="33" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8279,71 +8304,71 @@
           <t>pool, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H19" s="30" t="inlineStr">
+      <c r="H19" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I19" s="30" t="inlineStr">
+      <c r="I19" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J19" s="30" t="inlineStr">
+      <c r="J19" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K19" s="30" t="inlineStr">
+      <c r="K19" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L19" s="30" t="inlineStr">
+      <c r="L19" s="33" t="inlineStr">
         <is>
           <t>AQU-CHM-0070</t>
         </is>
       </c>
-      <c r="M19" s="31" t="inlineStr">
+      <c r="M19" s="34" t="inlineStr">
         <is>
           <t>5292638000070</t>
         </is>
       </c>
-      <c r="N19" s="32" t="inlineStr"/>
-      <c r="O19" s="32" t="inlineStr"/>
-      <c r="P19" s="32" t="inlineStr"/>
-      <c r="Q19" s="30" t="inlineStr">
+      <c r="N19" s="35" t="inlineStr"/>
+      <c r="O19" s="35" t="inlineStr"/>
+      <c r="P19" s="35" t="inlineStr"/>
+      <c r="Q19" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R19" s="30" t="inlineStr">
+      <c r="R19" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S19" s="30" t="inlineStr">
+      <c r="S19" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T19" s="30" t="inlineStr">
+      <c r="T19" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U19" s="30" t="inlineStr"/>
-      <c r="V19" s="30" t="inlineStr">
+      <c r="U19" s="33" t="inlineStr"/>
+      <c r="V19" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W19" s="30" t="inlineStr">
+      <c r="W19" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X19" s="30" t="inlineStr">
+      <c r="X19" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8353,7 +8378,7 @@
           <t>https://poolservices.cy/storage/2026/05/California-Clear-Blue-1L-Aquality-2.jpeg</t>
         </is>
       </c>
-      <c r="Z19" s="30" t="inlineStr">
+      <c r="Z19" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8363,7 +8388,7 @@
           <t>Pool Clarifier California Clear Blue Aquality 1L</t>
         </is>
       </c>
-      <c r="AB19" s="30" t="inlineStr">
+      <c r="AB19" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8375,10 +8400,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF19" s="30" t="inlineStr"/>
-      <c r="AG19" s="30" t="inlineStr"/>
-      <c r="AH19" s="30" t="inlineStr"/>
-      <c r="AI19" s="30" t="inlineStr"/>
+      <c r="AF19" s="33" t="inlineStr"/>
+      <c r="AG19" s="33" t="inlineStr"/>
+      <c r="AH19" s="33" t="inlineStr"/>
+      <c r="AI19" s="33" t="inlineStr"/>
     </row>
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="17" t="inlineStr">
@@ -8396,17 +8421,17 @@
           <t>A 1-litre tile and vinyl cleaner for pools, designed to clean pool tile surfaces and vinyl liners. It makes light work of the tidying up that keeps a pool looking its best.</t>
         </is>
       </c>
-      <c r="D20" s="30" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E20" s="30" t="inlineStr">
+      <c r="E20" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F20" s="30" t="inlineStr">
+      <c r="F20" s="33" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8416,71 +8441,71 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H20" s="30" t="inlineStr">
+      <c r="H20" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I20" s="30" t="inlineStr">
+      <c r="I20" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J20" s="30" t="inlineStr">
+      <c r="J20" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K20" s="30" t="inlineStr">
+      <c r="K20" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L20" s="30" t="inlineStr">
+      <c r="L20" s="33" t="inlineStr">
         <is>
           <t>AQU-CLN-0162</t>
         </is>
       </c>
-      <c r="M20" s="31" t="inlineStr">
+      <c r="M20" s="34" t="inlineStr">
         <is>
           <t>5292638000162</t>
         </is>
       </c>
-      <c r="N20" s="32" t="inlineStr"/>
-      <c r="O20" s="32" t="inlineStr"/>
-      <c r="P20" s="32" t="inlineStr"/>
-      <c r="Q20" s="30" t="inlineStr">
+      <c r="N20" s="35" t="inlineStr"/>
+      <c r="O20" s="35" t="inlineStr"/>
+      <c r="P20" s="35" t="inlineStr"/>
+      <c r="Q20" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R20" s="30" t="inlineStr">
+      <c r="R20" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S20" s="30" t="inlineStr">
+      <c r="S20" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T20" s="30" t="inlineStr">
+      <c r="T20" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U20" s="30" t="inlineStr"/>
-      <c r="V20" s="30" t="inlineStr">
+      <c r="U20" s="33" t="inlineStr"/>
+      <c r="V20" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W20" s="30" t="inlineStr">
+      <c r="W20" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X20" s="30" t="inlineStr">
+      <c r="X20" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8490,7 +8515,7 @@
           <t>http://mangas.com.cy/media/products/5292638000162.jpg</t>
         </is>
       </c>
-      <c r="Z20" s="30" t="inlineStr">
+      <c r="Z20" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8500,7 +8525,7 @@
           <t>AQUALITY Magic tile 4 vinyl cleaner 1L</t>
         </is>
       </c>
-      <c r="AB20" s="30" t="inlineStr">
+      <c r="AB20" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8512,10 +8537,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF20" s="30" t="inlineStr"/>
-      <c r="AG20" s="30" t="inlineStr"/>
-      <c r="AH20" s="30" t="inlineStr"/>
-      <c r="AI20" s="30" t="inlineStr"/>
+      <c r="AF20" s="33" t="inlineStr"/>
+      <c r="AG20" s="33" t="inlineStr"/>
+      <c r="AH20" s="33" t="inlineStr"/>
+      <c r="AI20" s="33" t="inlineStr"/>
     </row>
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="17" t="inlineStr">
@@ -8533,17 +8558,17 @@
           <t>A 1-litre spa and pool water clarifier from Bayzid, formulated to clear cloudy or turbid water. A handy bottle to reach for whenever the water loses its sparkle.</t>
         </is>
       </c>
-      <c r="D21" s="30" t="inlineStr">
+      <c r="D21" s="33" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E21" s="30" t="inlineStr">
+      <c r="E21" s="33" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F21" s="30" t="inlineStr">
+      <c r="F21" s="33" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -8553,71 +8578,71 @@
           <t>spa-hot-tub, pool, water-treatment, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H21" s="30" t="inlineStr">
+      <c r="H21" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I21" s="30" t="inlineStr">
+      <c r="I21" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J21" s="30" t="inlineStr">
+      <c r="J21" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K21" s="30" t="inlineStr">
+      <c r="K21" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L21" s="30" t="inlineStr">
+      <c r="L21" s="33" t="inlineStr">
         <is>
           <t>HFE-SPA-7202</t>
         </is>
       </c>
-      <c r="M21" s="31" t="inlineStr">
+      <c r="M21" s="34" t="inlineStr">
         <is>
           <t>4250463127202</t>
         </is>
       </c>
-      <c r="N21" s="32" t="inlineStr"/>
-      <c r="O21" s="32" t="inlineStr"/>
-      <c r="P21" s="32" t="inlineStr"/>
-      <c r="Q21" s="30" t="inlineStr">
+      <c r="N21" s="35" t="inlineStr"/>
+      <c r="O21" s="35" t="inlineStr"/>
+      <c r="P21" s="35" t="inlineStr"/>
+      <c r="Q21" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R21" s="30" t="inlineStr">
+      <c r="R21" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S21" s="30" t="inlineStr">
+      <c r="S21" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T21" s="30" t="inlineStr">
+      <c r="T21" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U21" s="30" t="inlineStr"/>
-      <c r="V21" s="30" t="inlineStr">
+      <c r="U21" s="33" t="inlineStr"/>
+      <c r="V21" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W21" s="30" t="inlineStr">
+      <c r="W21" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X21" s="30" t="inlineStr">
+      <c r="X21" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8627,7 +8652,7 @@
           <t>https://hoefer-shop.com/cdn/shop/files/1x1L-BAYZID-Spa-Poolclear-v1-RS_1.jpg?v=1785600487&amp;width=800</t>
         </is>
       </c>
-      <c r="Z21" s="30" t="inlineStr">
+      <c r="Z21" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8637,7 +8662,7 @@
           <t>Höfer Chemie GmbH Pool Care 1 L BAYZID® SPA Poolclear Turbidity Remover</t>
         </is>
       </c>
-      <c r="AB21" s="30" t="inlineStr">
+      <c r="AB21" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8649,10 +8674,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF21" s="30" t="inlineStr"/>
-      <c r="AG21" s="30" t="inlineStr"/>
-      <c r="AH21" s="30" t="inlineStr"/>
-      <c r="AI21" s="30" t="inlineStr"/>
+      <c r="AF21" s="33" t="inlineStr"/>
+      <c r="AG21" s="33" t="inlineStr"/>
+      <c r="AH21" s="33" t="inlineStr"/>
+      <c r="AI21" s="33" t="inlineStr"/>
     </row>
     <row r="22" ht="62" customHeight="1">
       <c r="A22" s="17" t="inlineStr">
@@ -8670,17 +8695,17 @@
           <t>A 1-litre bottle of hydrogen peroxide at 11.9% concentration, suitable for disinfection and water treatment applications. A straightforward chemical solution that keeps things clean without fuss.</t>
         </is>
       </c>
-      <c r="D22" s="30" t="inlineStr">
+      <c r="D22" s="33" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E22" s="30" t="inlineStr">
+      <c r="E22" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F22" s="30" t="inlineStr">
+      <c r="F22" s="33" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8690,71 +8715,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H22" s="30" t="inlineStr">
+      <c r="H22" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I22" s="30" t="inlineStr">
+      <c r="I22" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J22" s="30" t="inlineStr">
+      <c r="J22" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K22" s="30" t="inlineStr">
+      <c r="K22" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L22" s="30" t="inlineStr">
+      <c r="L22" s="33" t="inlineStr">
         <is>
           <t>HFE-CHM-6788</t>
         </is>
       </c>
-      <c r="M22" s="31" t="inlineStr">
+      <c r="M22" s="34" t="inlineStr">
         <is>
           <t>4250463106788</t>
         </is>
       </c>
-      <c r="N22" s="32" t="inlineStr"/>
-      <c r="O22" s="32" t="inlineStr"/>
-      <c r="P22" s="32" t="inlineStr"/>
-      <c r="Q22" s="30" t="inlineStr">
+      <c r="N22" s="35" t="inlineStr"/>
+      <c r="O22" s="35" t="inlineStr"/>
+      <c r="P22" s="35" t="inlineStr"/>
+      <c r="Q22" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R22" s="30" t="inlineStr">
+      <c r="R22" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S22" s="30" t="inlineStr">
+      <c r="S22" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T22" s="30" t="inlineStr">
+      <c r="T22" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U22" s="30" t="inlineStr"/>
-      <c r="V22" s="30" t="inlineStr">
+      <c r="U22" s="33" t="inlineStr"/>
+      <c r="V22" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W22" s="30" t="inlineStr">
+      <c r="W22" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X22" s="30" t="inlineStr">
+      <c r="X22" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8764,7 +8789,7 @@
           <t>https://hoefer-shop.com/cdn/shop/files/1x1L-Wasserstoffperoxid-Flasche-hinten-26.jpg?v=1783777627&amp;width=1000</t>
         </is>
       </c>
-      <c r="Z22" s="30" t="inlineStr">
+      <c r="Z22" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8774,7 +8799,7 @@
           <t>HÖFER CHEMIE GMBH 1 l Hydrogen Peroxide 11,9%</t>
         </is>
       </c>
-      <c r="AB22" s="30" t="inlineStr">
+      <c r="AB22" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8786,10 +8811,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF22" s="30" t="inlineStr"/>
-      <c r="AG22" s="30" t="inlineStr"/>
-      <c r="AH22" s="30" t="inlineStr"/>
-      <c r="AI22" s="30" t="inlineStr"/>
+      <c r="AF22" s="33" t="inlineStr"/>
+      <c r="AG22" s="33" t="inlineStr"/>
+      <c r="AH22" s="33" t="inlineStr"/>
+      <c r="AI22" s="33" t="inlineStr"/>
     </row>
     <row r="23" ht="62" customHeight="1">
       <c r="A23" s="17" t="inlineStr">
@@ -8807,17 +8832,17 @@
           <t>A 4.5 kg pack of chlorine stabilizer for swimming pools, used to protect chlorine from UV degradation and extend its effectiveness in the water. Steady chemistry for a pool that earns its keep.</t>
         </is>
       </c>
-      <c r="D23" s="30" t="inlineStr">
+      <c r="D23" s="33" t="inlineStr">
         <is>
           <t>AstralPool</t>
         </is>
       </c>
-      <c r="E23" s="30" t="inlineStr">
+      <c r="E23" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F23" s="30" t="inlineStr">
+      <c r="F23" s="33" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8827,83 +8852,83 @@
           <t>water-treatment, repeat-purchase, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H23" s="30" t="inlineStr">
+      <c r="H23" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I23" s="30" t="inlineStr">
+      <c r="I23" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J23" s="30" t="inlineStr">
+      <c r="J23" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K23" s="30" t="inlineStr">
+      <c r="K23" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L23" s="30" t="inlineStr">
+      <c r="L23" s="33" t="inlineStr">
         <is>
           <t>AST-CHM-0626</t>
         </is>
       </c>
-      <c r="M23" s="31" t="inlineStr">
+      <c r="M23" s="34" t="inlineStr">
         <is>
           <t>8432611960626</t>
         </is>
       </c>
-      <c r="N23" s="32" t="inlineStr"/>
-      <c r="O23" s="32" t="inlineStr"/>
-      <c r="P23" s="32" t="inlineStr"/>
-      <c r="Q23" s="30" t="inlineStr">
+      <c r="N23" s="35" t="inlineStr"/>
+      <c r="O23" s="35" t="inlineStr"/>
+      <c r="P23" s="35" t="inlineStr"/>
+      <c r="Q23" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R23" s="30" t="inlineStr">
+      <c r="R23" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S23" s="30" t="inlineStr">
+      <c r="S23" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T23" s="30" t="inlineStr">
+      <c r="T23" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U23" s="30" t="inlineStr">
+      <c r="U23" s="33" t="inlineStr">
         <is>
           <t>4500</t>
         </is>
       </c>
-      <c r="V23" s="30" t="inlineStr">
+      <c r="V23" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W23" s="30" t="inlineStr">
+      <c r="W23" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X23" s="30" t="inlineStr">
+      <c r="X23" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
-      <c r="Z23" s="30" t="inlineStr"/>
+      <c r="Z23" s="33" t="inlineStr"/>
       <c r="AA23" s="17" t="inlineStr"/>
-      <c r="AB23" s="30" t="inlineStr">
+      <c r="AB23" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8915,10 +8940,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF23" s="30" t="inlineStr"/>
-      <c r="AG23" s="30" t="inlineStr"/>
-      <c r="AH23" s="30" t="inlineStr"/>
-      <c r="AI23" s="30" t="inlineStr"/>
+      <c r="AF23" s="33" t="inlineStr"/>
+      <c r="AG23" s="33" t="inlineStr"/>
+      <c r="AH23" s="33" t="inlineStr"/>
+      <c r="AI23" s="33" t="inlineStr"/>
     </row>
     <row r="24" ht="62" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
@@ -8936,17 +8961,17 @@
           <t>UltraShock is a pool and spa shock treatment from SpaBalancer, designed to rapidly oxidise contaminants and restore water clarity. A quick reset for water that needs a little more persuasion.</t>
         </is>
       </c>
-      <c r="D24" s="30" t="inlineStr">
+      <c r="D24" s="33" t="inlineStr">
         <is>
           <t>SpaBalancer</t>
         </is>
       </c>
-      <c r="E24" s="30" t="inlineStr">
+      <c r="E24" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F24" s="30" t="inlineStr">
+      <c r="F24" s="33" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8956,71 +8981,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H24" s="30" t="inlineStr">
+      <c r="H24" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I24" s="30" t="inlineStr">
+      <c r="I24" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J24" s="30" t="inlineStr">
+      <c r="J24" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K24" s="30" t="inlineStr">
+      <c r="K24" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L24" s="30" t="inlineStr">
+      <c r="L24" s="33" t="inlineStr">
         <is>
           <t>SPA-CHM-0025</t>
         </is>
       </c>
-      <c r="M24" s="31" t="inlineStr">
+      <c r="M24" s="34" t="inlineStr">
         <is>
           <t>4260374980025</t>
         </is>
       </c>
-      <c r="N24" s="32" t="inlineStr"/>
-      <c r="O24" s="32" t="inlineStr"/>
-      <c r="P24" s="32" t="inlineStr"/>
-      <c r="Q24" s="30" t="inlineStr">
+      <c r="N24" s="35" t="inlineStr"/>
+      <c r="O24" s="35" t="inlineStr"/>
+      <c r="P24" s="35" t="inlineStr"/>
+      <c r="Q24" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R24" s="30" t="inlineStr">
+      <c r="R24" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S24" s="30" t="inlineStr">
+      <c r="S24" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T24" s="30" t="inlineStr">
+      <c r="T24" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U24" s="30" t="inlineStr"/>
-      <c r="V24" s="30" t="inlineStr">
+      <c r="U24" s="33" t="inlineStr"/>
+      <c r="V24" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W24" s="30" t="inlineStr">
+      <c r="W24" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X24" s="30" t="inlineStr">
+      <c r="X24" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9030,7 +9055,7 @@
           <t>https://images.barcodelookup.com/16704/167043133-1.jpg</t>
         </is>
       </c>
-      <c r="Z24" s="30" t="inlineStr">
+      <c r="Z24" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9040,7 +9065,7 @@
           <t>SpaBalancer UltraShock</t>
         </is>
       </c>
-      <c r="AB24" s="30" t="inlineStr">
+      <c r="AB24" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9052,10 +9077,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF24" s="30" t="inlineStr"/>
-      <c r="AG24" s="30" t="inlineStr"/>
-      <c r="AH24" s="30" t="inlineStr"/>
-      <c r="AI24" s="30" t="inlineStr"/>
+      <c r="AF24" s="33" t="inlineStr"/>
+      <c r="AG24" s="33" t="inlineStr"/>
+      <c r="AH24" s="33" t="inlineStr"/>
+      <c r="AI24" s="33" t="inlineStr"/>
     </row>
     <row r="25" ht="76" customHeight="1">
       <c r="A25" s="17" t="inlineStr">
@@ -9073,13 +9098,13 @@
           <t>A patented foam rubber eraser for cleaning pool surfaces, particularly suited to waterline stains on liner and vitreous ceramic finishes, and it works without detergents or chemicals. Each box contains 3 sponges, which harden when wet to scrub effectively while remaining soft and flexible in use.</t>
         </is>
       </c>
-      <c r="D25" s="30" t="inlineStr"/>
-      <c r="E25" s="30" t="inlineStr">
+      <c r="D25" s="33" t="inlineStr"/>
+      <c r="E25" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F25" s="30" t="inlineStr">
+      <c r="F25" s="33" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -9089,71 +9114,71 @@
           <t>pool, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H25" s="30" t="inlineStr">
+      <c r="H25" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I25" s="30" t="inlineStr">
+      <c r="I25" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J25" s="30" t="inlineStr">
+      <c r="J25" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K25" s="30" t="inlineStr">
+      <c r="K25" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L25" s="30" t="inlineStr">
+      <c r="L25" s="33" t="inlineStr">
         <is>
           <t>GEN-CLN-0062</t>
         </is>
       </c>
-      <c r="M25" s="31" t="inlineStr">
+      <c r="M25" s="34" t="inlineStr">
         <is>
           <t>3760015880062</t>
         </is>
       </c>
-      <c r="N25" s="32" t="inlineStr"/>
-      <c r="O25" s="32" t="inlineStr"/>
-      <c r="P25" s="32" t="inlineStr"/>
-      <c r="Q25" s="30" t="inlineStr">
+      <c r="N25" s="35" t="inlineStr"/>
+      <c r="O25" s="35" t="inlineStr"/>
+      <c r="P25" s="35" t="inlineStr"/>
+      <c r="Q25" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R25" s="30" t="inlineStr">
+      <c r="R25" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S25" s="30" t="inlineStr">
+      <c r="S25" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T25" s="30" t="inlineStr">
+      <c r="T25" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U25" s="30" t="inlineStr"/>
-      <c r="V25" s="30" t="inlineStr">
+      <c r="U25" s="33" t="inlineStr"/>
+      <c r="V25" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W25" s="30" t="inlineStr">
+      <c r="W25" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X25" s="30" t="inlineStr">
+      <c r="X25" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9163,7 +9188,7 @@
           <t>https://www.piscinarium.com/2908-thickbox_default/pool-gom-magic-rubber-eraser.jpg</t>
         </is>
       </c>
-      <c r="Z25" s="30" t="inlineStr">
+      <c r="Z25" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9173,7 +9198,7 @@
           <t>Pool'Gom Magic Rubber Eraser</t>
         </is>
       </c>
-      <c r="AB25" s="30" t="inlineStr">
+      <c r="AB25" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9185,10 +9210,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF25" s="30" t="inlineStr"/>
-      <c r="AG25" s="30" t="inlineStr"/>
-      <c r="AH25" s="30" t="inlineStr"/>
-      <c r="AI25" s="30" t="inlineStr"/>
+      <c r="AF25" s="33" t="inlineStr"/>
+      <c r="AG25" s="33" t="inlineStr"/>
+      <c r="AH25" s="33" t="inlineStr"/>
+      <c r="AI25" s="33" t="inlineStr"/>
     </row>
     <row r="26" ht="62" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
@@ -9206,13 +9231,13 @@
           <t>Spa Industries Europe appears to be a brand or supplier name rather than a specific product, so no product details can be confirmed. For accurate information, please check the full product listing.</t>
         </is>
       </c>
-      <c r="D26" s="30" t="inlineStr"/>
-      <c r="E26" s="30" t="inlineStr">
+      <c r="D26" s="33" t="inlineStr"/>
+      <c r="E26" s="33" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F26" s="30" t="inlineStr">
+      <c r="F26" s="33" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -9222,79 +9247,79 @@
           <t>spa-hot-tub, considered-purchase, multi-source-confirmed, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H26" s="30" t="inlineStr">
+      <c r="H26" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I26" s="30" t="inlineStr">
+      <c r="I26" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J26" s="30" t="inlineStr">
+      <c r="J26" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K26" s="30" t="inlineStr">
+      <c r="K26" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L26" s="30" t="inlineStr">
+      <c r="L26" s="33" t="inlineStr">
         <is>
           <t>GEN-SPA-1968</t>
         </is>
       </c>
-      <c r="M26" s="31" t="inlineStr">
+      <c r="M26" s="34" t="inlineStr">
         <is>
           <t>5425021871968</t>
         </is>
       </c>
-      <c r="N26" s="32" t="inlineStr"/>
-      <c r="O26" s="32" t="inlineStr"/>
-      <c r="P26" s="32" t="inlineStr"/>
-      <c r="Q26" s="30" t="inlineStr">
+      <c r="N26" s="35" t="inlineStr"/>
+      <c r="O26" s="35" t="inlineStr"/>
+      <c r="P26" s="35" t="inlineStr"/>
+      <c r="Q26" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R26" s="30" t="inlineStr">
+      <c r="R26" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S26" s="30" t="inlineStr">
+      <c r="S26" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T26" s="30" t="inlineStr">
+      <c r="T26" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U26" s="30" t="inlineStr"/>
-      <c r="V26" s="30" t="inlineStr">
+      <c r="U26" s="33" t="inlineStr"/>
+      <c r="V26" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W26" s="30" t="inlineStr">
+      <c r="W26" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X26" s="30" t="inlineStr">
+      <c r="X26" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y26" s="17" t="inlineStr"/>
-      <c r="Z26" s="30" t="inlineStr"/>
+      <c r="Z26" s="33" t="inlineStr"/>
       <c r="AA26" s="17" t="inlineStr"/>
-      <c r="AB26" s="30" t="inlineStr">
+      <c r="AB26" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9306,10 +9331,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF26" s="30" t="inlineStr"/>
-      <c r="AG26" s="30" t="inlineStr"/>
-      <c r="AH26" s="30" t="inlineStr"/>
-      <c r="AI26" s="30" t="inlineStr"/>
+      <c r="AF26" s="33" t="inlineStr"/>
+      <c r="AG26" s="33" t="inlineStr"/>
+      <c r="AH26" s="33" t="inlineStr"/>
+      <c r="AI26" s="33" t="inlineStr"/>
     </row>
     <row r="27" ht="62" customHeight="1">
       <c r="A27" s="17" t="inlineStr">
@@ -9327,17 +9352,17 @@
           <t>A 1-litre high-concentrate sauna cleaner with eucalyptus fragrance, formulated as a deep-cleaning base cleaner for sauna surfaces. The concentrated formula means a little goes a long way, with a fresh scent to match.</t>
         </is>
       </c>
-      <c r="D27" s="30" t="inlineStr">
+      <c r="D27" s="33" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E27" s="30" t="inlineStr">
+      <c r="E27" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F27" s="30" t="inlineStr">
+      <c r="F27" s="33" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -9347,79 +9372,79 @@
           <t>cleaning, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H27" s="30" t="inlineStr">
+      <c r="H27" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I27" s="30" t="inlineStr">
+      <c r="I27" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J27" s="30" t="inlineStr">
+      <c r="J27" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K27" s="30" t="inlineStr">
+      <c r="K27" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L27" s="30" t="inlineStr">
+      <c r="L27" s="33" t="inlineStr">
         <is>
           <t>HFE-CLN-7004</t>
         </is>
       </c>
-      <c r="M27" s="31" t="inlineStr">
+      <c r="M27" s="34" t="inlineStr">
         <is>
           <t>4250463127004</t>
         </is>
       </c>
-      <c r="N27" s="32" t="inlineStr"/>
-      <c r="O27" s="32" t="inlineStr"/>
-      <c r="P27" s="32" t="inlineStr"/>
-      <c r="Q27" s="30" t="inlineStr">
+      <c r="N27" s="35" t="inlineStr"/>
+      <c r="O27" s="35" t="inlineStr"/>
+      <c r="P27" s="35" t="inlineStr"/>
+      <c r="Q27" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R27" s="30" t="inlineStr">
+      <c r="R27" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S27" s="30" t="inlineStr">
+      <c r="S27" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T27" s="30" t="inlineStr">
+      <c r="T27" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U27" s="30" t="inlineStr"/>
-      <c r="V27" s="30" t="inlineStr">
+      <c r="U27" s="33" t="inlineStr"/>
+      <c r="V27" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W27" s="30" t="inlineStr">
+      <c r="W27" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X27" s="30" t="inlineStr">
+      <c r="X27" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y27" s="17" t="inlineStr"/>
-      <c r="Z27" s="30" t="inlineStr"/>
+      <c r="Z27" s="33" t="inlineStr"/>
       <c r="AA27" s="17" t="inlineStr"/>
-      <c r="AB27" s="30" t="inlineStr">
+      <c r="AB27" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9431,10 +9456,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF27" s="30" t="inlineStr"/>
-      <c r="AG27" s="30" t="inlineStr"/>
-      <c r="AH27" s="30" t="inlineStr"/>
-      <c r="AI27" s="30" t="inlineStr"/>
+      <c r="AF27" s="33" t="inlineStr"/>
+      <c r="AG27" s="33" t="inlineStr"/>
+      <c r="AH27" s="33" t="inlineStr"/>
+      <c r="AI27" s="33" t="inlineStr"/>
     </row>
     <row r="28" ht="76" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
@@ -9452,17 +9477,17 @@
           <t>This HTH spa cleaner removes mineral deposits such as limescale and rust, and cleans and polishes aluminium, chrome, stainless steel, and enamel surfaces with a pleasant pine fragrance. It has a high concentration of active ingredients and is recommended for periodic maintenance cleaning.</t>
         </is>
       </c>
-      <c r="D28" s="30" t="inlineStr">
+      <c r="D28" s="33" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E28" s="30" t="inlineStr">
+      <c r="E28" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F28" s="30" t="inlineStr">
+      <c r="F28" s="33" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -9472,71 +9497,71 @@
           <t>spa-hot-tub, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H28" s="30" t="inlineStr">
+      <c r="H28" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I28" s="30" t="inlineStr">
+      <c r="I28" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J28" s="30" t="inlineStr">
+      <c r="J28" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K28" s="30" t="inlineStr">
+      <c r="K28" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L28" s="30" t="inlineStr">
+      <c r="L28" s="33" t="inlineStr">
         <is>
           <t>HTH-CLN-0178</t>
         </is>
       </c>
-      <c r="M28" s="31" t="inlineStr">
+      <c r="M28" s="34" t="inlineStr">
         <is>
           <t>3521686010178</t>
         </is>
       </c>
-      <c r="N28" s="32" t="inlineStr"/>
-      <c r="O28" s="32" t="inlineStr"/>
-      <c r="P28" s="32" t="inlineStr"/>
-      <c r="Q28" s="30" t="inlineStr">
+      <c r="N28" s="35" t="inlineStr"/>
+      <c r="O28" s="35" t="inlineStr"/>
+      <c r="P28" s="35" t="inlineStr"/>
+      <c r="Q28" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R28" s="30" t="inlineStr">
+      <c r="R28" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S28" s="30" t="inlineStr">
+      <c r="S28" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T28" s="30" t="inlineStr">
+      <c r="T28" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U28" s="30" t="inlineStr"/>
-      <c r="V28" s="30" t="inlineStr">
+      <c r="U28" s="33" t="inlineStr"/>
+      <c r="V28" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W28" s="30" t="inlineStr">
+      <c r="W28" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X28" s="30" t="inlineStr">
+      <c r="X28" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9546,7 +9571,7 @@
           <t>https://www.cdiscount.com/pdt2/0/5/1/1/700x700/auc2009356289051/rw/hth-spa-nettoyant-spa-3521686010178.jpg</t>
         </is>
       </c>
-      <c r="Z28" s="30" t="inlineStr">
+      <c r="Z28" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9556,7 +9581,7 @@
           <t>HTH Spa Spa Cleaner</t>
         </is>
       </c>
-      <c r="AB28" s="30" t="inlineStr">
+      <c r="AB28" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9568,10 +9593,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF28" s="30" t="inlineStr"/>
-      <c r="AG28" s="30" t="inlineStr"/>
-      <c r="AH28" s="30" t="inlineStr"/>
-      <c r="AI28" s="30" t="inlineStr"/>
+      <c r="AF28" s="33" t="inlineStr"/>
+      <c r="AG28" s="33" t="inlineStr"/>
+      <c r="AH28" s="33" t="inlineStr"/>
+      <c r="AI28" s="33" t="inlineStr"/>
     </row>
     <row r="29" ht="62" customHeight="1">
       <c r="A29" s="17" t="inlineStr">
@@ -9589,13 +9614,13 @@
           <t>A 25 kg sack of pure boiling salt (minimum 99.6% NaCl) without an anti-caking agent, meeting EN 973 Type A standard and suitable for use in pool salt electrolysis systems. Not intended for human consumption or animal feed.</t>
         </is>
       </c>
-      <c r="D29" s="30" t="inlineStr"/>
-      <c r="E29" s="30" t="inlineStr">
+      <c r="D29" s="33" t="inlineStr"/>
+      <c r="E29" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F29" s="30" t="inlineStr">
+      <c r="F29" s="33" t="inlineStr">
         <is>
           <t>Pool salt</t>
         </is>
@@ -9605,75 +9630,75 @@
           <t>pool, salt, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H29" s="30" t="inlineStr">
+      <c r="H29" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I29" s="30" t="inlineStr">
+      <c r="I29" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J29" s="30" t="inlineStr">
+      <c r="J29" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K29" s="30" t="inlineStr">
+      <c r="K29" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L29" s="30" t="inlineStr">
+      <c r="L29" s="33" t="inlineStr">
         <is>
           <t>GEN-SLT-6110</t>
         </is>
       </c>
-      <c r="M29" s="31" t="inlineStr">
+      <c r="M29" s="34" t="inlineStr">
         <is>
           <t>9001880976110</t>
         </is>
       </c>
-      <c r="N29" s="32" t="inlineStr"/>
-      <c r="O29" s="32" t="inlineStr"/>
-      <c r="P29" s="32" t="inlineStr"/>
-      <c r="Q29" s="30" t="inlineStr">
+      <c r="N29" s="35" t="inlineStr"/>
+      <c r="O29" s="35" t="inlineStr"/>
+      <c r="P29" s="35" t="inlineStr"/>
+      <c r="Q29" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R29" s="30" t="inlineStr">
+      <c r="R29" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S29" s="30" t="inlineStr">
+      <c r="S29" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T29" s="30" t="inlineStr">
+      <c r="T29" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U29" s="30" t="inlineStr">
+      <c r="U29" s="33" t="inlineStr">
         <is>
           <t>25000</t>
         </is>
       </c>
-      <c r="V29" s="30" t="inlineStr">
+      <c r="V29" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W29" s="30" t="inlineStr">
+      <c r="W29" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X29" s="30" t="inlineStr">
+      <c r="X29" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9683,7 +9708,7 @@
           <t>http://altruan.com/cdn/shop/files/SalinenPoolSalz25kgSack.png?v=1778597596</t>
         </is>
       </c>
-      <c r="Z29" s="30" t="inlineStr">
+      <c r="Z29" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9693,7 +9718,7 @@
           <t>Saline pool salt pure boiling salt without separating agent | Sack (25 kg)</t>
         </is>
       </c>
-      <c r="AB29" s="30" t="inlineStr">
+      <c r="AB29" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9705,14 +9730,14 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF29" s="30" t="inlineStr">
+      <c r="AF29" s="33" t="inlineStr">
         <is>
           <t>Composition: Siedesalz (min. 99.6% NaCl) 100%; Separant/sodium ferrocyanide 4.0–12.0 mg/kg | Grain: &gt;0.63 mm approx. 20%, 0.2–0.63 mm approx. 75%, &lt;0.2 mm approx. 5% | Moisture: &lt;0.08%</t>
         </is>
       </c>
-      <c r="AG29" s="30" t="inlineStr"/>
-      <c r="AH29" s="30" t="inlineStr"/>
-      <c r="AI29" s="30" t="inlineStr"/>
+      <c r="AG29" s="33" t="inlineStr"/>
+      <c r="AH29" s="33" t="inlineStr"/>
+      <c r="AI29" s="33" t="inlineStr"/>
     </row>
     <row r="30" ht="76" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
@@ -9730,17 +9755,17 @@
           <t>A cordless robotic pool cleaner that scrubs both floors and walls automatically, using WavePath navigation to map and cover the pool efficiently. Built-in high-performance filtration and smart control make it a hands-off solution for keeping pool water clear.</t>
         </is>
       </c>
-      <c r="D30" s="30" t="inlineStr">
+      <c r="D30" s="33" t="inlineStr">
         <is>
           <t>Aiper</t>
         </is>
       </c>
-      <c r="E30" s="30" t="inlineStr">
+      <c r="E30" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F30" s="30" t="inlineStr">
+      <c r="F30" s="33" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9750,71 +9775,71 @@
           <t>pool, cleaning, robot-cleaner, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H30" s="30" t="inlineStr">
+      <c r="H30" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I30" s="30" t="inlineStr">
+      <c r="I30" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J30" s="30" t="inlineStr">
+      <c r="J30" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K30" s="30" t="inlineStr">
+      <c r="K30" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L30" s="30" t="inlineStr">
+      <c r="L30" s="33" t="inlineStr">
         <is>
           <t>AIP-ROB-4940</t>
         </is>
       </c>
-      <c r="M30" s="31" t="inlineStr">
+      <c r="M30" s="34" t="inlineStr">
         <is>
           <t>6977676344940</t>
         </is>
       </c>
-      <c r="N30" s="32" t="inlineStr"/>
-      <c r="O30" s="32" t="inlineStr"/>
-      <c r="P30" s="32" t="inlineStr"/>
-      <c r="Q30" s="30" t="inlineStr">
+      <c r="N30" s="35" t="inlineStr"/>
+      <c r="O30" s="35" t="inlineStr"/>
+      <c r="P30" s="35" t="inlineStr"/>
+      <c r="Q30" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R30" s="30" t="inlineStr">
+      <c r="R30" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S30" s="30" t="inlineStr">
+      <c r="S30" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T30" s="30" t="inlineStr">
+      <c r="T30" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U30" s="30" t="inlineStr"/>
-      <c r="V30" s="30" t="inlineStr">
+      <c r="U30" s="33" t="inlineStr"/>
+      <c r="V30" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W30" s="30" t="inlineStr">
+      <c r="W30" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X30" s="30" t="inlineStr">
+      <c r="X30" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9824,7 +9849,7 @@
           <t>https://images.barcodelookup.com/176692/1766920801-1.jpg</t>
         </is>
       </c>
-      <c r="Z30" s="30" t="inlineStr">
+      <c r="Z30" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9834,7 +9859,7 @@
           <t>AIPER Scuba S3 Cordless Pool Robot, Automatic Floor and Wall Cleaning, WavePath™ Navigation, High-Performance Filtration…</t>
         </is>
       </c>
-      <c r="AB30" s="30" t="inlineStr">
+      <c r="AB30" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9846,10 +9871,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF30" s="30" t="inlineStr"/>
-      <c r="AG30" s="30" t="inlineStr"/>
-      <c r="AH30" s="30" t="inlineStr"/>
-      <c r="AI30" s="30" t="inlineStr"/>
+      <c r="AF30" s="33" t="inlineStr"/>
+      <c r="AG30" s="33" t="inlineStr"/>
+      <c r="AH30" s="33" t="inlineStr"/>
+      <c r="AI30" s="33" t="inlineStr"/>
     </row>
     <row r="31" ht="62" customHeight="1">
       <c r="A31" s="17" t="inlineStr">
@@ -9867,13 +9892,13 @@
           <t>The Scuba L1 EU is a pool cleaning device, though no further specific details about its features, dimensions, or mechanism are available from the product name alone. Buyers should refer to the full product listing for specifications.</t>
         </is>
       </c>
-      <c r="D31" s="30" t="inlineStr"/>
-      <c r="E31" s="30" t="inlineStr">
+      <c r="D31" s="33" t="inlineStr"/>
+      <c r="E31" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F31" s="30" t="inlineStr">
+      <c r="F31" s="33" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9883,71 +9908,71 @@
           <t>robot-cleaner, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H31" s="30" t="inlineStr">
+      <c r="H31" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I31" s="30" t="inlineStr">
+      <c r="I31" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J31" s="30" t="inlineStr">
+      <c r="J31" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K31" s="30" t="inlineStr">
+      <c r="K31" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L31" s="30" t="inlineStr">
+      <c r="L31" s="33" t="inlineStr">
         <is>
           <t>GEN-ROB-5137</t>
         </is>
       </c>
-      <c r="M31" s="31" t="inlineStr">
+      <c r="M31" s="34" t="inlineStr">
         <is>
           <t>6975140315137</t>
         </is>
       </c>
-      <c r="N31" s="32" t="inlineStr"/>
-      <c r="O31" s="32" t="inlineStr"/>
-      <c r="P31" s="32" t="inlineStr"/>
-      <c r="Q31" s="30" t="inlineStr">
+      <c r="N31" s="35" t="inlineStr"/>
+      <c r="O31" s="35" t="inlineStr"/>
+      <c r="P31" s="35" t="inlineStr"/>
+      <c r="Q31" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R31" s="30" t="inlineStr">
+      <c r="R31" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S31" s="30" t="inlineStr">
+      <c r="S31" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T31" s="30" t="inlineStr">
+      <c r="T31" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U31" s="30" t="inlineStr"/>
-      <c r="V31" s="30" t="inlineStr">
+      <c r="U31" s="33" t="inlineStr"/>
+      <c r="V31" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W31" s="30" t="inlineStr">
+      <c r="W31" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X31" s="30" t="inlineStr">
+      <c r="X31" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9957,7 +9982,7 @@
           <t>https://images.barcodelookup.com/124722/1247228758-1.jpg</t>
         </is>
       </c>
-      <c r="Z31" s="30" t="inlineStr">
+      <c r="Z31" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9967,7 +9992,7 @@
           <t>Scuba L1 - EU</t>
         </is>
       </c>
-      <c r="AB31" s="30" t="inlineStr">
+      <c r="AB31" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9979,10 +10004,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF31" s="30" t="inlineStr"/>
-      <c r="AG31" s="30" t="inlineStr"/>
-      <c r="AH31" s="30" t="inlineStr"/>
-      <c r="AI31" s="30" t="inlineStr"/>
+      <c r="AF31" s="33" t="inlineStr"/>
+      <c r="AG31" s="33" t="inlineStr"/>
+      <c r="AH31" s="33" t="inlineStr"/>
+      <c r="AI31" s="33" t="inlineStr"/>
     </row>
     <row r="32" ht="48" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
@@ -10000,13 +10025,13 @@
           <t>The Gre Pools RBR120 is a 51W robotic pool cleaner designed for automatic pool floor cleaning. A reliable workhorse that takes the scrubbing off your hands.</t>
         </is>
       </c>
-      <c r="D32" s="30" t="inlineStr"/>
-      <c r="E32" s="30" t="inlineStr">
+      <c r="D32" s="33" t="inlineStr"/>
+      <c r="E32" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F32" s="30" t="inlineStr">
+      <c r="F32" s="33" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -10016,71 +10041,71 @@
           <t>robot-cleaner, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H32" s="30" t="inlineStr">
+      <c r="H32" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I32" s="30" t="inlineStr">
+      <c r="I32" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J32" s="30" t="inlineStr">
+      <c r="J32" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K32" s="30" t="inlineStr">
+      <c r="K32" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L32" s="30" t="inlineStr">
+      <c r="L32" s="33" t="inlineStr">
         <is>
           <t>GEN-ROB-8500</t>
         </is>
       </c>
-      <c r="M32" s="31" t="inlineStr">
+      <c r="M32" s="34" t="inlineStr">
         <is>
           <t>8412081308500</t>
         </is>
       </c>
-      <c r="N32" s="32" t="inlineStr"/>
-      <c r="O32" s="32" t="inlineStr"/>
-      <c r="P32" s="32" t="inlineStr"/>
-      <c r="Q32" s="30" t="inlineStr">
+      <c r="N32" s="35" t="inlineStr"/>
+      <c r="O32" s="35" t="inlineStr"/>
+      <c r="P32" s="35" t="inlineStr"/>
+      <c r="Q32" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R32" s="30" t="inlineStr">
+      <c r="R32" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S32" s="30" t="inlineStr">
+      <c r="S32" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T32" s="30" t="inlineStr">
+      <c r="T32" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U32" s="30" t="inlineStr"/>
-      <c r="V32" s="30" t="inlineStr">
+      <c r="U32" s="33" t="inlineStr"/>
+      <c r="V32" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W32" s="30" t="inlineStr">
+      <c r="W32" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X32" s="30" t="inlineStr">
+      <c r="X32" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10090,7 +10115,7 @@
           <t>https://images.barcodelookup.com/124726/1247268298-1.jpg</t>
         </is>
       </c>
-      <c r="Z32" s="30" t="inlineStr">
+      <c r="Z32" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10100,7 +10125,7 @@
           <t>Battery Powered Robot WET RUNNER XPERT</t>
         </is>
       </c>
-      <c r="AB32" s="30" t="inlineStr">
+      <c r="AB32" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10112,10 +10137,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF32" s="30" t="inlineStr"/>
-      <c r="AG32" s="30" t="inlineStr"/>
-      <c r="AH32" s="30" t="inlineStr"/>
-      <c r="AI32" s="30" t="inlineStr"/>
+      <c r="AF32" s="33" t="inlineStr"/>
+      <c r="AG32" s="33" t="inlineStr"/>
+      <c r="AH32" s="33" t="inlineStr"/>
+      <c r="AI32" s="33" t="inlineStr"/>
     </row>
     <row r="33" ht="90" customHeight="1">
       <c r="A33" s="17" t="inlineStr">
@@ -10133,13 +10158,13 @@
           <t>A twin-size inflatable airbed measuring 99 x 191 x 25 cm, built with Fiber-Tech internal construction using polyester fibres for comfort, vinyl sides and base, and a water-resistant flocked top surface with an anti-deflation valve. It supports a maximum weight of 136 kg and packs down compactly when deflated.</t>
         </is>
       </c>
-      <c r="D33" s="30" t="inlineStr"/>
-      <c r="E33" s="30" t="inlineStr">
+      <c r="D33" s="33" t="inlineStr"/>
+      <c r="E33" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-11</t>
         </is>
       </c>
-      <c r="F33" s="30" t="inlineStr">
+      <c r="F33" s="33" t="inlineStr">
         <is>
           <t>Airbed / lounger</t>
         </is>
@@ -10149,71 +10174,71 @@
           <t>considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H33" s="30" t="inlineStr">
+      <c r="H33" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I33" s="30" t="inlineStr">
+      <c r="I33" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J33" s="30" t="inlineStr">
+      <c r="J33" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K33" s="30" t="inlineStr">
+      <c r="K33" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L33" s="30" t="inlineStr">
+      <c r="L33" s="33" t="inlineStr">
         <is>
           <t>GEN-BED-2443</t>
         </is>
       </c>
-      <c r="M33" s="31" t="inlineStr">
+      <c r="M33" s="34" t="inlineStr">
         <is>
           <t>6941057412443</t>
         </is>
       </c>
-      <c r="N33" s="32" t="inlineStr"/>
-      <c r="O33" s="32" t="inlineStr"/>
-      <c r="P33" s="32" t="inlineStr"/>
-      <c r="Q33" s="30" t="inlineStr">
+      <c r="N33" s="35" t="inlineStr"/>
+      <c r="O33" s="35" t="inlineStr"/>
+      <c r="P33" s="35" t="inlineStr"/>
+      <c r="Q33" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R33" s="30" t="inlineStr">
+      <c r="R33" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S33" s="30" t="inlineStr">
+      <c r="S33" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T33" s="30" t="inlineStr">
+      <c r="T33" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U33" s="30" t="inlineStr"/>
-      <c r="V33" s="30" t="inlineStr">
+      <c r="U33" s="33" t="inlineStr"/>
+      <c r="V33" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W33" s="30" t="inlineStr">
+      <c r="W33" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X33" s="30" t="inlineStr">
+      <c r="X33" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10223,7 +10248,7 @@
           <t>https://www.ecoperation.com/media/catalog/product/cache/b76cf1d99a7811daa83ba86e6ad91c89/6/4/64757.jpg</t>
         </is>
       </c>
-      <c r="Z33" s="30" t="inlineStr">
+      <c r="Z33" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10233,7 +10258,7 @@
           <t>Twin Dura-Beam Classic Downy Airbed 99x191x25 cm</t>
         </is>
       </c>
-      <c r="AB33" s="30" t="inlineStr">
+      <c r="AB33" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10245,18 +10270,18 @@
           <t>Inflatable Beds and Mattresses</t>
         </is>
       </c>
-      <c r="AF33" s="30" t="inlineStr"/>
-      <c r="AG33" s="30" t="inlineStr">
+      <c r="AF33" s="33" t="inlineStr"/>
+      <c r="AG33" s="33" t="inlineStr">
         <is>
           <t>99.0cm</t>
         </is>
       </c>
-      <c r="AH33" s="30" t="inlineStr">
+      <c r="AH33" s="33" t="inlineStr">
         <is>
           <t>191.0cm</t>
         </is>
       </c>
-      <c r="AI33" s="30" t="inlineStr">
+      <c r="AI33" s="33" t="inlineStr">
         <is>
           <t>25.0cm</t>
         </is>
@@ -10278,17 +10303,17 @@
           <t>A plastic chlorine dosing lock from Steinbach, designed exclusively for use with long-term chlorine tablets, with a 1.5-inch connection fitting. It measures 37 cm in length, 22.5 cm in width, and 15 cm in height, making it a sturdy inline dosing unit for pool water treatment systems.</t>
         </is>
       </c>
-      <c r="D34" s="30" t="inlineStr">
+      <c r="D34" s="33" t="inlineStr">
         <is>
           <t>Steinbach</t>
         </is>
       </c>
-      <c r="E34" s="30" t="inlineStr">
+      <c r="E34" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F34" s="30" t="inlineStr">
+      <c r="F34" s="33" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -10298,71 +10323,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H34" s="30" t="inlineStr">
+      <c r="H34" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I34" s="30" t="inlineStr">
+      <c r="I34" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J34" s="30" t="inlineStr">
+      <c r="J34" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K34" s="30" t="inlineStr">
+      <c r="K34" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L34" s="30" t="inlineStr">
+      <c r="L34" s="33" t="inlineStr">
         <is>
           <t>STE-CHM-0307</t>
         </is>
       </c>
-      <c r="M34" s="31" t="inlineStr">
+      <c r="M34" s="34" t="inlineStr">
         <is>
           <t>9008748790307</t>
         </is>
       </c>
-      <c r="N34" s="32" t="inlineStr"/>
-      <c r="O34" s="32" t="inlineStr"/>
-      <c r="P34" s="32" t="inlineStr"/>
-      <c r="Q34" s="30" t="inlineStr">
+      <c r="N34" s="35" t="inlineStr"/>
+      <c r="O34" s="35" t="inlineStr"/>
+      <c r="P34" s="35" t="inlineStr"/>
+      <c r="Q34" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R34" s="30" t="inlineStr">
+      <c r="R34" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S34" s="30" t="inlineStr">
+      <c r="S34" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T34" s="30" t="inlineStr">
+      <c r="T34" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U34" s="30" t="inlineStr"/>
-      <c r="V34" s="30" t="inlineStr">
+      <c r="U34" s="33" t="inlineStr"/>
+      <c r="V34" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W34" s="30" t="inlineStr">
+      <c r="W34" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X34" s="30" t="inlineStr">
+      <c r="X34" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10372,7 +10397,7 @@
           <t>https://i.ebayimg.com/images/g/CrUAAeSwkOdqeaRR/s-l400.jpg</t>
         </is>
       </c>
-      <c r="Z34" s="30" t="inlineStr">
+      <c r="Z34" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10382,7 +10407,7 @@
           <t>STEINBACH Chlorine dosing lock, only for chlorine long-term tablets, plastic, connection 1.5 inch in</t>
         </is>
       </c>
-      <c r="AB34" s="30" t="inlineStr">
+      <c r="AB34" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10394,18 +10419,18 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF34" s="30" t="inlineStr"/>
-      <c r="AG34" s="30" t="inlineStr">
+      <c r="AF34" s="33" t="inlineStr"/>
+      <c r="AG34" s="33" t="inlineStr">
         <is>
           <t>22.5cm</t>
         </is>
       </c>
-      <c r="AH34" s="30" t="inlineStr">
+      <c r="AH34" s="33" t="inlineStr">
         <is>
           <t>37.0cm</t>
         </is>
       </c>
-      <c r="AI34" s="30" t="inlineStr">
+      <c r="AI34" s="33" t="inlineStr">
         <is>
           <t>15.0cm</t>
         </is>
@@ -10427,17 +10452,17 @@
           <t>A filter cleaning system for hot tub and pool cartridge filters, designed to remove debris and residue efficiently while keeping water usage to a minimum. A practical tool for extending the life of your filter without wasting a drop more than necessary.</t>
         </is>
       </c>
-      <c r="D35" s="30" t="inlineStr">
+      <c r="D35" s="33" t="inlineStr">
         <is>
           <t>Estelle</t>
         </is>
       </c>
-      <c r="E35" s="30" t="inlineStr">
+      <c r="E35" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F35" s="30" t="inlineStr">
+      <c r="F35" s="33" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -10447,71 +10472,71 @@
           <t>filters, spa-hot-tub, cleaning, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H35" s="30" t="inlineStr">
+      <c r="H35" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I35" s="30" t="inlineStr">
+      <c r="I35" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J35" s="30" t="inlineStr">
+      <c r="J35" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K35" s="30" t="inlineStr">
+      <c r="K35" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L35" s="30" t="inlineStr">
+      <c r="L35" s="33" t="inlineStr">
         <is>
           <t>EST-FIL-3669</t>
         </is>
       </c>
-      <c r="M35" s="31" t="inlineStr">
+      <c r="M35" s="34" t="inlineStr">
         <is>
           <t>8711842033669</t>
         </is>
       </c>
-      <c r="N35" s="32" t="inlineStr"/>
-      <c r="O35" s="32" t="inlineStr"/>
-      <c r="P35" s="32" t="inlineStr"/>
-      <c r="Q35" s="30" t="inlineStr">
+      <c r="N35" s="35" t="inlineStr"/>
+      <c r="O35" s="35" t="inlineStr"/>
+      <c r="P35" s="35" t="inlineStr"/>
+      <c r="Q35" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R35" s="30" t="inlineStr">
+      <c r="R35" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S35" s="30" t="inlineStr">
+      <c r="S35" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T35" s="30" t="inlineStr">
+      <c r="T35" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U35" s="30" t="inlineStr"/>
-      <c r="V35" s="30" t="inlineStr">
+      <c r="U35" s="33" t="inlineStr"/>
+      <c r="V35" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W35" s="30" t="inlineStr">
+      <c r="W35" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X35" s="30" t="inlineStr">
+      <c r="X35" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10521,7 +10546,7 @@
           <t>https://i.ebayimg.com/images/g/0e0AAOSweaplqO77/s-l400.jpg</t>
         </is>
       </c>
-      <c r="Z35" s="30" t="inlineStr">
+      <c r="Z35" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10531,7 +10556,7 @@
           <t>Estelle Filter Cleaning System Hot tubs Cartridge Filters Cleaner Spa Amazing!</t>
         </is>
       </c>
-      <c r="AB35" s="30" t="inlineStr">
+      <c r="AB35" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10543,10 +10568,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF35" s="30" t="inlineStr"/>
-      <c r="AG35" s="30" t="inlineStr"/>
-      <c r="AH35" s="30" t="inlineStr"/>
-      <c r="AI35" s="30" t="inlineStr"/>
+      <c r="AF35" s="33" t="inlineStr"/>
+      <c r="AG35" s="33" t="inlineStr"/>
+      <c r="AH35" s="33" t="inlineStr"/>
+      <c r="AI35" s="33" t="inlineStr"/>
     </row>
     <row r="36" ht="62" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
@@ -10564,17 +10589,17 @@
           <t>A compact handy scrub brush for pool maintenance, measuring 15 x 9 x 8 cm, suited to scrubbing pool surfaces and hard-to-reach areas. Small enough to manoeuvre easily, and ready to tackle whatever the waterline throws at it.</t>
         </is>
       </c>
-      <c r="D36" s="30" t="inlineStr">
+      <c r="D36" s="33" t="inlineStr">
         <is>
           <t>WAYS</t>
         </is>
       </c>
-      <c r="E36" s="30" t="inlineStr">
+      <c r="E36" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F36" s="30" t="inlineStr">
+      <c r="F36" s="33" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -10584,79 +10609,79 @@
           <t>pool, cleaning, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H36" s="30" t="inlineStr">
+      <c r="H36" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I36" s="30" t="inlineStr">
+      <c r="I36" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J36" s="30" t="inlineStr">
+      <c r="J36" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K36" s="30" t="inlineStr">
+      <c r="K36" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L36" s="30" t="inlineStr">
+      <c r="L36" s="33" t="inlineStr">
         <is>
           <t>WAY-CLN-2219</t>
         </is>
       </c>
-      <c r="M36" s="31" t="inlineStr">
+      <c r="M36" s="34" t="inlineStr">
         <is>
           <t>8720299182219</t>
         </is>
       </c>
-      <c r="N36" s="32" t="inlineStr"/>
-      <c r="O36" s="32" t="inlineStr"/>
-      <c r="P36" s="32" t="inlineStr"/>
-      <c r="Q36" s="30" t="inlineStr">
+      <c r="N36" s="35" t="inlineStr"/>
+      <c r="O36" s="35" t="inlineStr"/>
+      <c r="P36" s="35" t="inlineStr"/>
+      <c r="Q36" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R36" s="30" t="inlineStr">
+      <c r="R36" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S36" s="30" t="inlineStr">
+      <c r="S36" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T36" s="30" t="inlineStr">
+      <c r="T36" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U36" s="30" t="inlineStr"/>
-      <c r="V36" s="30" t="inlineStr">
+      <c r="U36" s="33" t="inlineStr"/>
+      <c r="V36" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W36" s="30" t="inlineStr">
+      <c r="W36" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X36" s="30" t="inlineStr">
+      <c r="X36" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y36" s="17" t="inlineStr"/>
-      <c r="Z36" s="30" t="inlineStr"/>
+      <c r="Z36" s="33" t="inlineStr"/>
       <c r="AA36" s="17" t="inlineStr"/>
-      <c r="AB36" s="30" t="inlineStr">
+      <c r="AB36" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10668,18 +10693,18 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF36" s="30" t="inlineStr"/>
-      <c r="AG36" s="30" t="inlineStr">
+      <c r="AF36" s="33" t="inlineStr"/>
+      <c r="AG36" s="33" t="inlineStr">
         <is>
           <t>8.0cm</t>
         </is>
       </c>
-      <c r="AH36" s="30" t="inlineStr">
+      <c r="AH36" s="33" t="inlineStr">
         <is>
           <t>15.0cm</t>
         </is>
       </c>
-      <c r="AI36" s="30" t="inlineStr">
+      <c r="AI36" s="33" t="inlineStr">
         <is>
           <t>9.0cm</t>
         </is>
@@ -10701,17 +10726,17 @@
           <t>An inflatable PVC headrest pillow for the Intex inflatable spa (model 28506), measuring 24 x 19 x 6 cm and weighing 0.22 kg, designed to support the head and neck comfortably during use. It attaches to the spa rim and can also be filled with water for added stability.</t>
         </is>
       </c>
-      <c r="D37" s="30" t="inlineStr">
+      <c r="D37" s="33" t="inlineStr">
         <is>
           <t>Intex</t>
         </is>
       </c>
-      <c r="E37" s="30" t="inlineStr">
+      <c r="E37" s="33" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F37" s="30" t="inlineStr">
+      <c r="F37" s="33" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -10721,75 +10746,75 @@
           <t>spa-hot-tub, accessories, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H37" s="30" t="inlineStr">
+      <c r="H37" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I37" s="30" t="inlineStr">
+      <c r="I37" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J37" s="30" t="inlineStr">
+      <c r="J37" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K37" s="30" t="inlineStr">
+      <c r="K37" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L37" s="30" t="inlineStr">
+      <c r="L37" s="33" t="inlineStr">
         <is>
           <t>INT-SPA-6075</t>
         </is>
       </c>
-      <c r="M37" s="31" t="inlineStr">
+      <c r="M37" s="34" t="inlineStr">
         <is>
           <t>6941057426075</t>
         </is>
       </c>
-      <c r="N37" s="32" t="inlineStr"/>
-      <c r="O37" s="32" t="inlineStr"/>
-      <c r="P37" s="32" t="inlineStr"/>
-      <c r="Q37" s="30" t="inlineStr">
+      <c r="N37" s="35" t="inlineStr"/>
+      <c r="O37" s="35" t="inlineStr"/>
+      <c r="P37" s="35" t="inlineStr"/>
+      <c r="Q37" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R37" s="30" t="inlineStr">
+      <c r="R37" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S37" s="30" t="inlineStr">
+      <c r="S37" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T37" s="30" t="inlineStr">
+      <c r="T37" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U37" s="30" t="inlineStr">
+      <c r="U37" s="33" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="V37" s="30" t="inlineStr">
+      <c r="V37" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W37" s="30" t="inlineStr">
+      <c r="W37" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X37" s="30" t="inlineStr">
+      <c r="X37" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10799,7 +10824,7 @@
           <t>https://content2.rozetka.com.ua/goods/images/big/570260745.jpg</t>
         </is>
       </c>
-      <c r="Z37" s="30" t="inlineStr">
+      <c r="Z37" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10809,7 +10834,7 @@
           <t>Headrest Pillow for INTEX Inflatable SPA 28506</t>
         </is>
       </c>
-      <c r="AB37" s="30" t="inlineStr">
+      <c r="AB37" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10821,18 +10846,18 @@
           <t>Intex Pure Spa Accessories</t>
         </is>
       </c>
-      <c r="AF37" s="30" t="inlineStr"/>
-      <c r="AG37" s="30" t="inlineStr">
+      <c r="AF37" s="33" t="inlineStr"/>
+      <c r="AG37" s="33" t="inlineStr">
         <is>
           <t>19.0cm</t>
         </is>
       </c>
-      <c r="AH37" s="30" t="inlineStr">
+      <c r="AH37" s="33" t="inlineStr">
         <is>
           <t>24.0cm</t>
         </is>
       </c>
-      <c r="AI37" s="30" t="inlineStr">
+      <c r="AI37" s="33" t="inlineStr">
         <is>
           <t>6.0cm</t>
         </is>
@@ -10854,13 +10879,13 @@
           <t>A DPD Pool test kit for active-oxygen pools, containing 20 DPD No. 4 reagent tablets for measuring active oxygen levels and 20 phenol red tablets for measuring pH. Results are read immediately after the tablet dissolves, with an ideal active oxygen range of 3.0 to 8.0 mg/l and a target pH of 7.0 to 7.4.</t>
         </is>
       </c>
-      <c r="D38" s="30" t="inlineStr"/>
-      <c r="E38" s="30" t="inlineStr">
+      <c r="D38" s="33" t="inlineStr"/>
+      <c r="E38" s="33" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F38" s="30" t="inlineStr">
+      <c r="F38" s="33" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -10870,71 +10895,71 @@
           <t>water-treatment, test-measure, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H38" s="30" t="inlineStr">
+      <c r="H38" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I38" s="30" t="inlineStr">
+      <c r="I38" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J38" s="30" t="inlineStr">
+      <c r="J38" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K38" s="30" t="inlineStr">
+      <c r="K38" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L38" s="30" t="inlineStr">
+      <c r="L38" s="33" t="inlineStr">
         <is>
           <t>GEN-TST-1347</t>
         </is>
       </c>
-      <c r="M38" s="31" t="inlineStr">
+      <c r="M38" s="34" t="inlineStr">
         <is>
           <t>4250463121347</t>
         </is>
       </c>
-      <c r="N38" s="32" t="inlineStr"/>
-      <c r="O38" s="32" t="inlineStr"/>
-      <c r="P38" s="32" t="inlineStr"/>
-      <c r="Q38" s="30" t="inlineStr">
+      <c r="N38" s="35" t="inlineStr"/>
+      <c r="O38" s="35" t="inlineStr"/>
+      <c r="P38" s="35" t="inlineStr"/>
+      <c r="Q38" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R38" s="30" t="inlineStr">
+      <c r="R38" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S38" s="30" t="inlineStr">
+      <c r="S38" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T38" s="30" t="inlineStr">
+      <c r="T38" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U38" s="30" t="inlineStr"/>
-      <c r="V38" s="30" t="inlineStr">
+      <c r="U38" s="33" t="inlineStr"/>
+      <c r="V38" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W38" s="30" t="inlineStr">
+      <c r="W38" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X38" s="30" t="inlineStr">
+      <c r="X38" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10944,7 +10969,7 @@
           <t>https://media.carrefour.fr/medias/8f94161f683b4e589024a5b5ebaa6873/p_200x200/cad3db6a00ef414a804b9226119bae96_image.jpg</t>
         </is>
       </c>
-      <c r="Z38" s="30" t="inlineStr">
+      <c r="Z38" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10954,7 +10979,7 @@
           <t>Active Oxygen Test Kit x1</t>
         </is>
       </c>
-      <c r="AB38" s="30" t="inlineStr">
+      <c r="AB38" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10966,10 +10991,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF38" s="30" t="inlineStr"/>
-      <c r="AG38" s="30" t="inlineStr"/>
-      <c r="AH38" s="30" t="inlineStr"/>
-      <c r="AI38" s="30" t="inlineStr"/>
+      <c r="AF38" s="33" t="inlineStr"/>
+      <c r="AG38" s="33" t="inlineStr"/>
+      <c r="AH38" s="33" t="inlineStr"/>
+      <c r="AI38" s="33" t="inlineStr"/>
     </row>
     <row r="39" ht="62" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
@@ -10987,17 +11012,17 @@
           <t>A pack of 2 replacement filter cartridges compatible with Intex Type H pool and spa pumps, made by Darlly. Straightforward to swap out, they keep the water moving clean without any complications.</t>
         </is>
       </c>
-      <c r="D39" s="30" t="inlineStr">
+      <c r="D39" s="33" t="inlineStr">
         <is>
           <t>Intex</t>
         </is>
       </c>
-      <c r="E39" s="30" t="inlineStr">
+      <c r="E39" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F39" s="30" t="inlineStr">
+      <c r="F39" s="33" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -11007,71 +11032,71 @@
           <t>filters, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H39" s="30" t="inlineStr">
+      <c r="H39" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I39" s="30" t="inlineStr">
+      <c r="I39" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J39" s="30" t="inlineStr">
+      <c r="J39" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K39" s="30" t="inlineStr">
+      <c r="K39" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L39" s="30" t="inlineStr">
+      <c r="L39" s="33" t="inlineStr">
         <is>
           <t>INT-FIL-2895</t>
         </is>
       </c>
-      <c r="M39" s="31" t="inlineStr">
+      <c r="M39" s="34" t="inlineStr">
         <is>
           <t>700175992895</t>
         </is>
       </c>
-      <c r="N39" s="32" t="inlineStr"/>
-      <c r="O39" s="32" t="inlineStr"/>
-      <c r="P39" s="32" t="inlineStr"/>
-      <c r="Q39" s="30" t="inlineStr">
+      <c r="N39" s="35" t="inlineStr"/>
+      <c r="O39" s="35" t="inlineStr"/>
+      <c r="P39" s="35" t="inlineStr"/>
+      <c r="Q39" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R39" s="30" t="inlineStr">
+      <c r="R39" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S39" s="30" t="inlineStr">
+      <c r="S39" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T39" s="30" t="inlineStr">
+      <c r="T39" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U39" s="30" t="inlineStr"/>
-      <c r="V39" s="30" t="inlineStr">
+      <c r="U39" s="33" t="inlineStr"/>
+      <c r="V39" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W39" s="30" t="inlineStr">
+      <c r="W39" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X39" s="30" t="inlineStr">
+      <c r="X39" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -11081,7 +11106,7 @@
           <t>https://a.allegroimg.com/original/11923c/a79785a04d36aa54f0d87384f038/Filtracni-kartuse-Intex-D-3BTZ0023-SC828</t>
         </is>
       </c>
-      <c r="Z39" s="30" t="inlineStr">
+      <c r="Z39" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -11091,7 +11116,7 @@
           <t>Darlly Filter Cartridge Pack of 2 Filter Cartridges Compatible with Intex Type H</t>
         </is>
       </c>
-      <c r="AB39" s="30" t="inlineStr">
+      <c r="AB39" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -11103,10 +11128,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF39" s="30" t="inlineStr"/>
-      <c r="AG39" s="30" t="inlineStr"/>
-      <c r="AH39" s="30" t="inlineStr"/>
-      <c r="AI39" s="30" t="inlineStr"/>
+      <c r="AF39" s="33" t="inlineStr"/>
+      <c r="AG39" s="33" t="inlineStr"/>
+      <c r="AH39" s="33" t="inlineStr"/>
+      <c r="AI39" s="33" t="inlineStr"/>
     </row>
     <row r="40" ht="62" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
@@ -11124,17 +11149,17 @@
           <t>A Darlly replacement spa filter cartridge with dimensions of 22 cm diameter by 27 cm height, compatible with SC713 and C-8465 references. A reliable like-for-like swap to keep your spa filtration running smoothly.</t>
         </is>
       </c>
-      <c r="D40" s="30" t="inlineStr">
+      <c r="D40" s="33" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E40" s="30" t="inlineStr">
+      <c r="E40" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F40" s="30" t="inlineStr">
+      <c r="F40" s="33" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -11144,71 +11169,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H40" s="30" t="inlineStr">
+      <c r="H40" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I40" s="30" t="inlineStr">
+      <c r="I40" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J40" s="30" t="inlineStr">
+      <c r="J40" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K40" s="30" t="inlineStr">
+      <c r="K40" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L40" s="30" t="inlineStr">
+      <c r="L40" s="33" t="inlineStr">
         <is>
           <t>DAR-FIL-1744</t>
         </is>
       </c>
-      <c r="M40" s="31" t="inlineStr">
+      <c r="M40" s="34" t="inlineStr">
         <is>
           <t>700175991744</t>
         </is>
       </c>
-      <c r="N40" s="32" t="inlineStr"/>
-      <c r="O40" s="32" t="inlineStr"/>
-      <c r="P40" s="32" t="inlineStr"/>
-      <c r="Q40" s="30" t="inlineStr">
+      <c r="N40" s="35" t="inlineStr"/>
+      <c r="O40" s="35" t="inlineStr"/>
+      <c r="P40" s="35" t="inlineStr"/>
+      <c r="Q40" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R40" s="30" t="inlineStr">
+      <c r="R40" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S40" s="30" t="inlineStr">
+      <c r="S40" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T40" s="30" t="inlineStr">
+      <c r="T40" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U40" s="30" t="inlineStr"/>
-      <c r="V40" s="30" t="inlineStr">
+      <c r="U40" s="33" t="inlineStr"/>
+      <c r="V40" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W40" s="30" t="inlineStr">
+      <c r="W40" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X40" s="30" t="inlineStr">
+      <c r="X40" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -11218,7 +11243,7 @@
           <t>https://images.barcodelookup.com/142259/1422591231-1.jpg</t>
         </is>
       </c>
-      <c r="Z40" s="30" t="inlineStr">
+      <c r="Z40" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -11228,7 +11253,7 @@
           <t>Spa Replacement Filter Ø 22 cm x 27 cm SC713, C-8465 - Darlly</t>
         </is>
       </c>
-      <c r="AB40" s="30" t="inlineStr">
+      <c r="AB40" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -11240,14 +11265,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF40" s="30" t="inlineStr"/>
-      <c r="AG40" s="30" t="inlineStr"/>
-      <c r="AH40" s="30" t="inlineStr">
+      <c r="AF40" s="33" t="inlineStr"/>
+      <c r="AG40" s="33" t="inlineStr"/>
+      <c r="AH40" s="33" t="inlineStr">
         <is>
           <t>22.0cm</t>
         </is>
       </c>
-      <c r="AI40" s="30" t="inlineStr">
+      <c r="AI40" s="33" t="inlineStr">
         <is>
           <t>27.0cm</t>
         </is>
@@ -11269,17 +11294,17 @@
           <t>A 1 kg pack of 20g multitabs for swimming pools, offering a 5-in-1 treatment that combines multiple water care functions in a single slow-dissolving tablet. Convenient all-in-one dosing that keeps pool maintenance simple.</t>
         </is>
       </c>
-      <c r="D41" s="30" t="inlineStr">
+      <c r="D41" s="33" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E41" s="30" t="inlineStr">
+      <c r="E41" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F41" s="30" t="inlineStr">
+      <c r="F41" s="33" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -11289,75 +11314,75 @@
           <t>pool, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H41" s="30" t="inlineStr">
+      <c r="H41" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I41" s="30" t="inlineStr">
+      <c r="I41" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J41" s="30" t="inlineStr">
+      <c r="J41" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K41" s="30" t="inlineStr">
+      <c r="K41" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L41" s="30" t="inlineStr">
+      <c r="L41" s="33" t="inlineStr">
         <is>
           <t>HFE-CHM-8430</t>
         </is>
       </c>
-      <c r="M41" s="31" t="inlineStr">
+      <c r="M41" s="34" t="inlineStr">
         <is>
           <t>4250463108430</t>
         </is>
       </c>
-      <c r="N41" s="32" t="inlineStr"/>
-      <c r="O41" s="32" t="inlineStr"/>
-      <c r="P41" s="32" t="inlineStr"/>
-      <c r="Q41" s="30" t="inlineStr">
+      <c r="N41" s="35" t="inlineStr"/>
+      <c r="O41" s="35" t="inlineStr"/>
+      <c r="P41" s="35" t="inlineStr"/>
+      <c r="Q41" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R41" s="30" t="inlineStr">
+      <c r="R41" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S41" s="30" t="inlineStr">
+      <c r="S41" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T41" s="30" t="inlineStr">
+      <c r="T41" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U41" s="30" t="inlineStr">
+      <c r="U41" s="33" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="V41" s="30" t="inlineStr">
+      <c r="V41" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W41" s="30" t="inlineStr">
+      <c r="W41" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X41" s="30" t="inlineStr">
+      <c r="X41" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -11367,7 +11392,7 @@
           <t>https://images.barcodelookup.com/17422/174228560-1.jpg</t>
         </is>
       </c>
-      <c r="Z41" s="30" t="inlineStr">
+      <c r="Z41" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -11377,7 +11402,7 @@
           <t>1 x 1 kg BAYZID® 20g 5-in-1 Multitabs for Pools - HÖFER CHEMIE</t>
         </is>
       </c>
-      <c r="AB41" s="30" t="inlineStr">
+      <c r="AB41" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -11389,10 +11414,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF41" s="30" t="inlineStr"/>
-      <c r="AG41" s="30" t="inlineStr"/>
-      <c r="AH41" s="30" t="inlineStr"/>
-      <c r="AI41" s="30" t="inlineStr"/>
+      <c r="AF41" s="33" t="inlineStr"/>
+      <c r="AG41" s="33" t="inlineStr"/>
+      <c r="AH41" s="33" t="inlineStr"/>
+      <c r="AI41" s="33" t="inlineStr"/>
     </row>
     <row r="42" ht="76" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
@@ -11410,17 +11435,17 @@
           <t>A ready-to-use alkaline spray cleaner for removing grease and dirt marks at the waterline of pools and for cleaning skimmers. The spray bottle makes application straightforward, and it can be used on a filled pool on all alkali-resistant surfaces.</t>
         </is>
       </c>
-      <c r="D42" s="30" t="inlineStr">
+      <c r="D42" s="33" t="inlineStr">
         <is>
           <t>Bayrol</t>
         </is>
       </c>
-      <c r="E42" s="30" t="inlineStr">
+      <c r="E42" s="33" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F42" s="30" t="inlineStr">
+      <c r="F42" s="33" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -11430,75 +11455,75 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H42" s="30" t="inlineStr">
+      <c r="H42" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I42" s="30" t="inlineStr">
+      <c r="I42" s="33" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J42" s="30" t="inlineStr">
+      <c r="J42" s="33" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K42" s="30" t="inlineStr">
+      <c r="K42" s="33" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L42" s="30" t="inlineStr">
+      <c r="L42" s="33" t="inlineStr">
         <is>
           <t>BAY-CLN-4134</t>
         </is>
       </c>
-      <c r="M42" s="31" t="inlineStr">
+      <c r="M42" s="34" t="inlineStr">
         <is>
           <t>4008367154134</t>
         </is>
       </c>
-      <c r="N42" s="32" t="inlineStr"/>
-      <c r="O42" s="32" t="inlineStr"/>
-      <c r="P42" s="32" t="inlineStr"/>
-      <c r="Q42" s="30" t="inlineStr">
+      <c r="N42" s="35" t="inlineStr"/>
+      <c r="O42" s="35" t="inlineStr"/>
+      <c r="P42" s="35" t="inlineStr"/>
+      <c r="Q42" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R42" s="30" t="inlineStr">
+      <c r="R42" s="33" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S42" s="30" t="inlineStr">
+      <c r="S42" s="33" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T42" s="30" t="inlineStr">
+      <c r="T42" s="33" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U42" s="30" t="inlineStr">
+      <c r="U42" s="33" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="V42" s="30" t="inlineStr">
+      <c r="V42" s="33" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W42" s="30" t="inlineStr">
+      <c r="W42" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X42" s="30" t="inlineStr">
+      <c r="X42" s="33" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -11508,7 +11533,7 @@
           <t>https://www.north-spa.de/wp-content/uploads/2023/02/Produktbild-1-Bayrol-Randfix-07-l-4008367154134.jpg</t>
         </is>
       </c>
-      <c r="Z42" s="30" t="inlineStr">
+      <c r="Z42" s="33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -11518,7 +11543,7 @@
           <t>Bayrol Randfix 0,7 l</t>
         </is>
       </c>
-      <c r="AB42" s="30" t="inlineStr">
+      <c r="AB42" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -11530,10 +11555,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF42" s="30" t="inlineStr"/>
-      <c r="AG42" s="30" t="inlineStr"/>
-      <c r="AH42" s="30" t="inlineStr"/>
-      <c r="AI42" s="30" t="inlineStr"/>
+      <c r="AF42" s="33" t="inlineStr"/>
+      <c r="AG42" s="33" t="inlineStr"/>
+      <c r="AH42" s="33" t="inlineStr"/>
+      <c r="AI42" s="33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projects/splashstore/docs/splashstore-scan-curation-260816.xlsx
+++ b/projects/splashstore/docs/splashstore-scan-curation-260816.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curation" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shopify import" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs re-scan" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to read this" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Curation'!$A$1:$Q$45</definedName>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +37,9 @@
     <font>
       <color rgb="000563C1"/>
       <u val="single"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -93,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -190,6 +194,36 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -264,6 +298,57 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>catalogue engine</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Worst field in the row, not a judgement on the whole product.
+READY = every field present is green.
+REVIEW = at least one field is yellow.
+HOLD = at least one field is missing (red).
+A row can be REVIEW while its photo is fully verified.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>How many INDEPENDENT domains printed this barcode.
+Three sources agreeing is stronger evidence than one, though both are green.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Colour applies to THIS FIELD ONLY, and is judged separately from the photo.
+GREEN = written from the barcode-confirmed page for this exact product.
+YELLOW = written from a name-matched page, so it may describe a variant.
+RED = no description.
+A yellow description beside a green image is normal: the photo was proven by the barcode, the wording was not.</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>Colour applies to THIS FIELD ONLY.
+GREEN = the barcode was found literally on the page the photo came from.
+YELLOW = the right product, but the photo needs a look (crop, multipack, unclear).
+RED = no usable photo was found.</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t>Colour applies to THIS FIELD ONLY.
+GREY = not applicable (the product is not edible).
+GREEN = composition from a barcode-confirmed source.
+YELLOW = composition from a brand or retailer page that was not barcode-confirmed.
+RED = missing on an edible product.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1579,16 +1664,16 @@
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="56" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="56" customWidth="1" min="15" max="15"/>
     <col width="34" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="34" customWidth="1" min="18" max="18"/>
     <col width="11" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -3045,7 +3130,11 @@
           <t>test-measure, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>1 source: ean-search.org</t>
+        </is>
+      </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
           <t>Blank — no image</t>
@@ -3785,7 +3874,11 @@
           <t>water-treatment, repeat-purchase, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>1 source: ean-search.org</t>
+        </is>
+      </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
           <t>Blank — no image</t>
@@ -4058,7 +4151,11 @@
           <t>spa-hot-tub, considered-purchase, multi-source-confirmed, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>2 sources: ean-search.org, spa-industries.eu</t>
+        </is>
+      </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
           <t>Blank — no image</t>
@@ -4147,7 +4244,11 @@
           <t>cleaning, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>1 source: ean-search.org</t>
+        </is>
+      </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
           <t>Blank — no image</t>
@@ -4282,7 +4383,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="244" customHeight="1">
+    <row r="31" ht="132" customHeight="1">
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="5" t="inlineStr">
         <is>
@@ -5705,6 +5806,7 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId101"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -5947,17 +6049,17 @@
           <t>A cartridge filter for hot tubs and swim spas, measuring 26.0 cm outer diameter, 13.0 cm bottom part, and 3.8 cm inner thread. Compatible with Darlly SC779 and 40372 codes, it captures dirt, grease, and fine particles to keep water clean.</t>
         </is>
       </c>
-      <c r="D2" s="33" t="inlineStr">
+      <c r="D2" s="36" t="inlineStr">
         <is>
           <t>Rising Dragon</t>
         </is>
       </c>
-      <c r="E2" s="33" t="inlineStr">
+      <c r="E2" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F2" s="33" t="inlineStr">
+      <c r="F2" s="36" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5967,71 +6069,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H2" s="33" t="inlineStr">
+      <c r="H2" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I2" s="33" t="inlineStr">
+      <c r="I2" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J2" s="33" t="inlineStr">
+      <c r="J2" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K2" s="33" t="inlineStr">
+      <c r="K2" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L2" s="33" t="inlineStr">
+      <c r="L2" s="36" t="inlineStr">
         <is>
           <t>RIS-FIL-2406</t>
         </is>
       </c>
-      <c r="M2" s="34" t="inlineStr">
+      <c r="M2" s="37" t="inlineStr">
         <is>
           <t>700175992406</t>
         </is>
       </c>
-      <c r="N2" s="35" t="inlineStr"/>
-      <c r="O2" s="35" t="inlineStr"/>
-      <c r="P2" s="35" t="inlineStr"/>
-      <c r="Q2" s="33" t="inlineStr">
+      <c r="N2" s="38" t="inlineStr"/>
+      <c r="O2" s="38" t="inlineStr"/>
+      <c r="P2" s="38" t="inlineStr"/>
+      <c r="Q2" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R2" s="33" t="inlineStr">
+      <c r="R2" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S2" s="33" t="inlineStr">
+      <c r="S2" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T2" s="33" t="inlineStr">
+      <c r="T2" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U2" s="33" t="inlineStr"/>
-      <c r="V2" s="33" t="inlineStr">
+      <c r="U2" s="36" t="inlineStr"/>
+      <c r="V2" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W2" s="33" t="inlineStr">
+      <c r="W2" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X2" s="33" t="inlineStr">
+      <c r="X2" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6041,7 +6143,7 @@
           <t>https://www.spa-components.com/user/shop/big/1473-1_filter-cartridge-sc779-rising-dragon-plastics--eago-whirlpools.jpg?ff=1&amp;x=1024&amp;y=768&amp;q=85&amp;ts=6720c4a0&amp;sg=161563f2</t>
         </is>
       </c>
-      <c r="Z2" s="33" t="inlineStr">
+      <c r="Z2" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6051,7 +6153,7 @@
           <t>Filter Cartridge SC779 - Rising Dragon Plastics, EAGO Whirlpools - Spa Components</t>
         </is>
       </c>
-      <c r="AB2" s="33" t="inlineStr">
+      <c r="AB2" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6063,10 +6165,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF2" s="33" t="inlineStr"/>
-      <c r="AG2" s="33" t="inlineStr"/>
-      <c r="AH2" s="33" t="inlineStr"/>
-      <c r="AI2" s="33" t="inlineStr"/>
+      <c r="AF2" s="36" t="inlineStr"/>
+      <c r="AG2" s="36" t="inlineStr"/>
+      <c r="AH2" s="36" t="inlineStr"/>
+      <c r="AI2" s="36" t="inlineStr"/>
     </row>
     <row r="3" ht="62" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
@@ -6084,13 +6186,13 @@
           <t>A twin pack of Size II replacement filter cartridges measuring 10.6 x 13.6 cm, designed for compatible pool and spa filtration systems. The fine lamellar structure delivers thorough water cleaning and the cartridges are easy to rinse clean.</t>
         </is>
       </c>
-      <c r="D3" s="33" t="inlineStr"/>
-      <c r="E3" s="33" t="inlineStr">
+      <c r="D3" s="36" t="inlineStr"/>
+      <c r="E3" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F3" s="33" t="inlineStr">
+      <c r="F3" s="36" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6100,71 +6202,71 @@
           <t>filters, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H3" s="33" t="inlineStr">
+      <c r="H3" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I3" s="33" t="inlineStr">
+      <c r="I3" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J3" s="33" t="inlineStr">
+      <c r="J3" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K3" s="33" t="inlineStr">
+      <c r="K3" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L3" s="33" t="inlineStr">
+      <c r="L3" s="36" t="inlineStr">
         <is>
           <t>GEN-FIL-3615</t>
         </is>
       </c>
-      <c r="M3" s="34" t="inlineStr">
+      <c r="M3" s="37" t="inlineStr">
         <is>
           <t>6941607353615</t>
         </is>
       </c>
-      <c r="N3" s="35" t="inlineStr"/>
-      <c r="O3" s="35" t="inlineStr"/>
-      <c r="P3" s="35" t="inlineStr"/>
-      <c r="Q3" s="33" t="inlineStr">
+      <c r="N3" s="38" t="inlineStr"/>
+      <c r="O3" s="38" t="inlineStr"/>
+      <c r="P3" s="38" t="inlineStr"/>
+      <c r="Q3" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R3" s="33" t="inlineStr">
+      <c r="R3" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S3" s="33" t="inlineStr">
+      <c r="S3" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T3" s="33" t="inlineStr">
+      <c r="T3" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U3" s="33" t="inlineStr"/>
-      <c r="V3" s="33" t="inlineStr">
+      <c r="U3" s="36" t="inlineStr"/>
+      <c r="V3" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W3" s="33" t="inlineStr">
+      <c r="W3" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X3" s="33" t="inlineStr">
+      <c r="X3" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6174,7 +6276,7 @@
           <t>https://www.bestwaystore.de/media/c6/f8/ba/1756384660/6941607353615-main-jpg.jpg?ts=1756384660</t>
         </is>
       </c>
-      <c r="Z3" s="33" t="inlineStr">
+      <c r="Z3" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6184,7 +6286,7 @@
           <t>Filter cartridge Size II double pack, 10.6 x 13.6 cm | 58094_26</t>
         </is>
       </c>
-      <c r="AB3" s="33" t="inlineStr">
+      <c r="AB3" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6196,14 +6298,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF3" s="33" t="inlineStr"/>
-      <c r="AG3" s="33" t="inlineStr"/>
-      <c r="AH3" s="33" t="inlineStr">
+      <c r="AF3" s="36" t="inlineStr"/>
+      <c r="AG3" s="36" t="inlineStr"/>
+      <c r="AH3" s="36" t="inlineStr">
         <is>
           <t>10.6cm</t>
         </is>
       </c>
-      <c r="AI3" s="33" t="inlineStr">
+      <c r="AI3" s="36" t="inlineStr">
         <is>
           <t>13.6cm</t>
         </is>
@@ -6225,17 +6327,17 @@
           <t>A single Flowclear Size 3 replacement filter cartridge for compatible Bestway pool filtration systems, featuring a fine lamellar structure that traps deposits and dirt effectively. Easy to clean and straightforward to swap out when routine maintenance is due.</t>
         </is>
       </c>
-      <c r="D4" s="33" t="inlineStr">
+      <c r="D4" s="36" t="inlineStr">
         <is>
           <t>Bestway</t>
         </is>
       </c>
-      <c r="E4" s="33" t="inlineStr">
+      <c r="E4" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F4" s="33" t="inlineStr">
+      <c r="F4" s="36" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6245,71 +6347,71 @@
           <t>filters, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H4" s="33" t="inlineStr">
+      <c r="H4" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I4" s="33" t="inlineStr">
+      <c r="I4" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J4" s="33" t="inlineStr">
+      <c r="J4" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K4" s="33" t="inlineStr">
+      <c r="K4" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L4" s="33" t="inlineStr">
+      <c r="L4" s="36" t="inlineStr">
         <is>
           <t>BES-FIL-3592</t>
         </is>
       </c>
-      <c r="M4" s="34" t="inlineStr">
+      <c r="M4" s="37" t="inlineStr">
         <is>
           <t>6941607353592</t>
         </is>
       </c>
-      <c r="N4" s="35" t="inlineStr"/>
-      <c r="O4" s="35" t="inlineStr"/>
-      <c r="P4" s="35" t="inlineStr"/>
-      <c r="Q4" s="33" t="inlineStr">
+      <c r="N4" s="38" t="inlineStr"/>
+      <c r="O4" s="38" t="inlineStr"/>
+      <c r="P4" s="38" t="inlineStr"/>
+      <c r="Q4" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R4" s="33" t="inlineStr">
+      <c r="R4" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S4" s="33" t="inlineStr">
+      <c r="S4" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T4" s="33" t="inlineStr">
+      <c r="T4" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U4" s="33" t="inlineStr"/>
-      <c r="V4" s="33" t="inlineStr">
+      <c r="U4" s="36" t="inlineStr"/>
+      <c r="V4" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W4" s="33" t="inlineStr">
+      <c r="W4" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X4" s="33" t="inlineStr">
+      <c r="X4" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6319,7 +6421,7 @@
           <t>https://ap.nice-cdn.com/upload/image/product/large/default/bestway-flowclear-filter-cartridge-size-3-1-item-638140-en.jpg</t>
         </is>
       </c>
-      <c r="Z4" s="33" t="inlineStr">
+      <c r="Z4" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6329,7 +6431,7 @@
           <t>Bestway Flowclear™ Filter Cartridge Size 3, 1 item</t>
         </is>
       </c>
-      <c r="AB4" s="33" t="inlineStr">
+      <c r="AB4" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6341,10 +6443,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF4" s="33" t="inlineStr"/>
-      <c r="AG4" s="33" t="inlineStr"/>
-      <c r="AH4" s="33" t="inlineStr"/>
-      <c r="AI4" s="33" t="inlineStr"/>
+      <c r="AF4" s="36" t="inlineStr"/>
+      <c r="AG4" s="36" t="inlineStr"/>
+      <c r="AH4" s="36" t="inlineStr"/>
+      <c r="AI4" s="36" t="inlineStr"/>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="17" t="inlineStr">
@@ -6362,17 +6464,17 @@
           <t>A two-pack of compatible hot tub and spa cartridge filters corresponding to Unicel C-4335, Pleatco PRB35-IN, and Filbur FC-2385 references. A handy spare-pair to keep on hand so your tub is never without a fresh filter.</t>
         </is>
       </c>
-      <c r="D5" s="33" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E5" s="33" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F5" s="33" t="inlineStr">
+      <c r="F5" s="36" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6382,71 +6484,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H5" s="33" t="inlineStr">
+      <c r="H5" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I5" s="33" t="inlineStr">
+      <c r="I5" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J5" s="33" t="inlineStr">
+      <c r="J5" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K5" s="33" t="inlineStr">
+      <c r="K5" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L5" s="33" t="inlineStr">
+      <c r="L5" s="36" t="inlineStr">
         <is>
           <t>DAR-FIL-1669</t>
         </is>
       </c>
-      <c r="M5" s="34" t="inlineStr">
+      <c r="M5" s="37" t="inlineStr">
         <is>
           <t>700175991669</t>
         </is>
       </c>
-      <c r="N5" s="35" t="inlineStr"/>
-      <c r="O5" s="35" t="inlineStr"/>
-      <c r="P5" s="35" t="inlineStr"/>
-      <c r="Q5" s="33" t="inlineStr">
+      <c r="N5" s="38" t="inlineStr"/>
+      <c r="O5" s="38" t="inlineStr"/>
+      <c r="P5" s="38" t="inlineStr"/>
+      <c r="Q5" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R5" s="33" t="inlineStr">
+      <c r="R5" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S5" s="33" t="inlineStr">
+      <c r="S5" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T5" s="33" t="inlineStr">
+      <c r="T5" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U5" s="33" t="inlineStr"/>
-      <c r="V5" s="33" t="inlineStr">
+      <c r="U5" s="36" t="inlineStr"/>
+      <c r="V5" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W5" s="33" t="inlineStr">
+      <c r="W5" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X5" s="33" t="inlineStr">
+      <c r="X5" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6456,7 +6558,7 @@
           <t>https://images.barcodelookup.com/29361/293617958-1.jpg</t>
         </is>
       </c>
-      <c r="Z5" s="33" t="inlineStr">
+      <c r="Z5" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6466,7 +6568,7 @@
           <t>Darlly Hot Tub Spa Filter SC705 40353 Compatible with Unicel C-4335 PRB35-IN Filbur FC-2385 2 Pack</t>
         </is>
       </c>
-      <c r="AB5" s="33" t="inlineStr">
+      <c r="AB5" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6478,10 +6580,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF5" s="33" t="inlineStr"/>
-      <c r="AG5" s="33" t="inlineStr"/>
-      <c r="AH5" s="33" t="inlineStr"/>
-      <c r="AI5" s="33" t="inlineStr"/>
+      <c r="AF5" s="36" t="inlineStr"/>
+      <c r="AG5" s="36" t="inlineStr"/>
+      <c r="AH5" s="36" t="inlineStr"/>
+      <c r="AI5" s="36" t="inlineStr"/>
     </row>
     <row r="6" ht="62" customHeight="1">
       <c r="A6" s="17" t="inlineStr">
@@ -6499,13 +6601,13 @@
           <t>A single Size IV replacement filter cartridge measuring 14.2 x 25.4 cm, compatible with Bestway filter pump 58391 (9,463 l/h). Its deep-fold, fine-structure media delivers thorough water cleaning and can be rinsed clean with minimal effort.</t>
         </is>
       </c>
-      <c r="D6" s="33" t="inlineStr"/>
-      <c r="E6" s="33" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr"/>
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F6" s="33" t="inlineStr">
+      <c r="F6" s="36" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6515,71 +6617,71 @@
           <t>filters, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H6" s="33" t="inlineStr">
+      <c r="H6" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I6" s="33" t="inlineStr">
+      <c r="I6" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J6" s="33" t="inlineStr">
+      <c r="J6" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K6" s="33" t="inlineStr">
+      <c r="K6" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L6" s="33" t="inlineStr">
+      <c r="L6" s="36" t="inlineStr">
         <is>
           <t>GEN-FIL-3622</t>
         </is>
       </c>
-      <c r="M6" s="34" t="inlineStr">
+      <c r="M6" s="37" t="inlineStr">
         <is>
           <t>6941607353622</t>
         </is>
       </c>
-      <c r="N6" s="35" t="inlineStr"/>
-      <c r="O6" s="35" t="inlineStr"/>
-      <c r="P6" s="35" t="inlineStr"/>
-      <c r="Q6" s="33" t="inlineStr">
+      <c r="N6" s="38" t="inlineStr"/>
+      <c r="O6" s="38" t="inlineStr"/>
+      <c r="P6" s="38" t="inlineStr"/>
+      <c r="Q6" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R6" s="33" t="inlineStr">
+      <c r="R6" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S6" s="33" t="inlineStr">
+      <c r="S6" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T6" s="33" t="inlineStr">
+      <c r="T6" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U6" s="33" t="inlineStr"/>
-      <c r="V6" s="33" t="inlineStr">
+      <c r="U6" s="36" t="inlineStr"/>
+      <c r="V6" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W6" s="33" t="inlineStr">
+      <c r="W6" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X6" s="33" t="inlineStr">
+      <c r="X6" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6589,7 +6691,7 @@
           <t>https://www.bestwaystore.de/media/53/6c/e9/1756384676/6941607353622-main-jpg.jpg?ts=1756384676</t>
         </is>
       </c>
-      <c r="Z6" s="33" t="inlineStr">
+      <c r="Z6" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6599,7 +6701,7 @@
           <t>Filter cartridge Size IV 14.2 x 25.4 cm | 58095_26</t>
         </is>
       </c>
-      <c r="AB6" s="33" t="inlineStr">
+      <c r="AB6" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6611,14 +6713,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF6" s="33" t="inlineStr"/>
-      <c r="AG6" s="33" t="inlineStr"/>
-      <c r="AH6" s="33" t="inlineStr">
+      <c r="AF6" s="36" t="inlineStr"/>
+      <c r="AG6" s="36" t="inlineStr"/>
+      <c r="AH6" s="36" t="inlineStr">
         <is>
           <t>14.2cm</t>
         </is>
       </c>
-      <c r="AI6" s="33" t="inlineStr">
+      <c r="AI6" s="36" t="inlineStr">
         <is>
           <t>25.4cm</t>
         </is>
@@ -6640,17 +6742,17 @@
           <t>A pair of Darlly spa filter cartridges in the SC726 reference, also cross-referenced as Unicel C-4401 and Pleatco PRB17.5SF PR. Buying in pairs means a fresh replacement is always ready when it is time to swap.</t>
         </is>
       </c>
-      <c r="D7" s="33" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E7" s="33" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F7" s="33" t="inlineStr">
+      <c r="F7" s="36" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6660,71 +6762,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H7" s="33" t="inlineStr">
+      <c r="H7" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I7" s="33" t="inlineStr">
+      <c r="I7" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J7" s="33" t="inlineStr">
+      <c r="J7" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K7" s="33" t="inlineStr">
+      <c r="K7" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L7" s="33" t="inlineStr">
+      <c r="L7" s="36" t="inlineStr">
         <is>
           <t>DAR-FIL-1874</t>
         </is>
       </c>
-      <c r="M7" s="34" t="inlineStr">
+      <c r="M7" s="37" t="inlineStr">
         <is>
           <t>700175991874</t>
         </is>
       </c>
-      <c r="N7" s="35" t="inlineStr"/>
-      <c r="O7" s="35" t="inlineStr"/>
-      <c r="P7" s="35" t="inlineStr"/>
-      <c r="Q7" s="33" t="inlineStr">
+      <c r="N7" s="38" t="inlineStr"/>
+      <c r="O7" s="38" t="inlineStr"/>
+      <c r="P7" s="38" t="inlineStr"/>
+      <c r="Q7" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R7" s="33" t="inlineStr">
+      <c r="R7" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S7" s="33" t="inlineStr">
+      <c r="S7" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T7" s="33" t="inlineStr">
+      <c r="T7" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U7" s="33" t="inlineStr"/>
-      <c r="V7" s="33" t="inlineStr">
+      <c r="U7" s="36" t="inlineStr"/>
+      <c r="V7" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W7" s="33" t="inlineStr">
+      <c r="W7" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X7" s="33" t="inlineStr">
+      <c r="X7" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6734,7 +6836,7 @@
           <t>https://images.barcodelookup.com/4378/43786454-1.jpg</t>
         </is>
       </c>
-      <c r="Z7" s="33" t="inlineStr">
+      <c r="Z7" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6744,7 +6846,7 @@
           <t>Darlly Spa Filter C-4401, PRB17.5SF PR, SC726 (Pair)</t>
         </is>
       </c>
-      <c r="AB7" s="33" t="inlineStr">
+      <c r="AB7" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6756,10 +6858,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF7" s="33" t="inlineStr"/>
-      <c r="AG7" s="33" t="inlineStr"/>
-      <c r="AH7" s="33" t="inlineStr"/>
-      <c r="AI7" s="33" t="inlineStr"/>
+      <c r="AF7" s="36" t="inlineStr"/>
+      <c r="AG7" s="36" t="inlineStr"/>
+      <c r="AH7" s="36" t="inlineStr"/>
+      <c r="AI7" s="36" t="inlineStr"/>
     </row>
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="17" t="inlineStr">
@@ -6777,17 +6879,17 @@
           <t>A replacement spa filter cartridge compatible with Arctic, Beachcomber, Canadian, Hydropool and Jacuzzi spas, sold under cross-reference codes including Unicel C-4950, Pleatco PRB50-IN and Darlly 40506. It keeps hot tub water clean by trapping debris and particles as water cycles through the filtration system.</t>
         </is>
       </c>
-      <c r="D8" s="33" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E8" s="33" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F8" s="33" t="inlineStr">
+      <c r="F8" s="36" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6797,71 +6899,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H8" s="33" t="inlineStr">
+      <c r="H8" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I8" s="33" t="inlineStr">
+      <c r="I8" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J8" s="33" t="inlineStr">
+      <c r="J8" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K8" s="33" t="inlineStr">
+      <c r="K8" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L8" s="33" t="inlineStr">
+      <c r="L8" s="36" t="inlineStr">
         <is>
           <t>DAR-FIL-1676</t>
         </is>
       </c>
-      <c r="M8" s="34" t="inlineStr">
+      <c r="M8" s="37" t="inlineStr">
         <is>
           <t>700175991676</t>
         </is>
       </c>
-      <c r="N8" s="35" t="inlineStr"/>
-      <c r="O8" s="35" t="inlineStr"/>
-      <c r="P8" s="35" t="inlineStr"/>
-      <c r="Q8" s="33" t="inlineStr">
+      <c r="N8" s="38" t="inlineStr"/>
+      <c r="O8" s="38" t="inlineStr"/>
+      <c r="P8" s="38" t="inlineStr"/>
+      <c r="Q8" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R8" s="33" t="inlineStr">
+      <c r="R8" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S8" s="33" t="inlineStr">
+      <c r="S8" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T8" s="33" t="inlineStr">
+      <c r="T8" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U8" s="33" t="inlineStr"/>
-      <c r="V8" s="33" t="inlineStr">
+      <c r="U8" s="36" t="inlineStr"/>
+      <c r="V8" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W8" s="33" t="inlineStr">
+      <c r="W8" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X8" s="33" t="inlineStr">
+      <c r="X8" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6871,7 +6973,7 @@
           <t>https://images.barcodelookup.com/4469/44699532-1.jpg</t>
         </is>
       </c>
-      <c r="Z8" s="33" t="inlineStr">
+      <c r="Z8" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6881,7 +6983,7 @@
           <t>Hot Tub Filter Unicel C4950 / C-4950 50' Spa Cartridge Pleatco PRB501N Darlly 40506 for Arctic, Beachcomber, Canadian,…</t>
         </is>
       </c>
-      <c r="AB8" s="33" t="inlineStr">
+      <c r="AB8" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6893,10 +6995,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF8" s="33" t="inlineStr"/>
-      <c r="AG8" s="33" t="inlineStr"/>
-      <c r="AH8" s="33" t="inlineStr"/>
-      <c r="AI8" s="33" t="inlineStr"/>
+      <c r="AF8" s="36" t="inlineStr"/>
+      <c r="AG8" s="36" t="inlineStr"/>
+      <c r="AH8" s="36" t="inlineStr"/>
+      <c r="AI8" s="36" t="inlineStr"/>
     </row>
     <row r="9" ht="76" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
@@ -6914,13 +7016,13 @@
           <t>A square inflatable hot tub for up to four people, with an overall outer diameter of 2.45 m and a structure measuring 1.75 x 1.75 x 0.71 m, built from high-resistance polyester for good rigidity and durability. The packaged weight is 64.92 kg, so you will want a helper on delivery day.</t>
         </is>
       </c>
-      <c r="D9" s="33" t="inlineStr"/>
-      <c r="E9" s="33" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr"/>
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F9" s="33" t="inlineStr">
+      <c r="F9" s="36" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -6930,75 +7032,75 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H9" s="33" t="inlineStr">
+      <c r="H9" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I9" s="33" t="inlineStr">
+      <c r="I9" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J9" s="33" t="inlineStr">
+      <c r="J9" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K9" s="33" t="inlineStr">
+      <c r="K9" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L9" s="33" t="inlineStr">
+      <c r="L9" s="36" t="inlineStr">
         <is>
           <t>GEN-SPA-3395</t>
         </is>
       </c>
-      <c r="M9" s="34" t="inlineStr">
+      <c r="M9" s="37" t="inlineStr">
         <is>
           <t>6941057423395</t>
         </is>
       </c>
-      <c r="N9" s="35" t="inlineStr"/>
-      <c r="O9" s="35" t="inlineStr"/>
-      <c r="P9" s="35" t="inlineStr"/>
-      <c r="Q9" s="33" t="inlineStr">
+      <c r="N9" s="38" t="inlineStr"/>
+      <c r="O9" s="38" t="inlineStr"/>
+      <c r="P9" s="38" t="inlineStr"/>
+      <c r="Q9" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R9" s="33" t="inlineStr">
+      <c r="R9" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S9" s="33" t="inlineStr">
+      <c r="S9" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T9" s="33" t="inlineStr">
+      <c r="T9" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U9" s="33" t="inlineStr">
+      <c r="U9" s="36" t="inlineStr">
         <is>
           <t>64920</t>
         </is>
       </c>
-      <c r="V9" s="33" t="inlineStr">
+      <c r="V9" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W9" s="33" t="inlineStr">
+      <c r="W9" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X9" s="33" t="inlineStr">
+      <c r="X9" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7008,7 +7110,7 @@
           <t>https://media.intex.fr/7743-large_default_x2/28464ex-spa-gonflable-calacatta-4-places.jpg</t>
         </is>
       </c>
-      <c r="Z9" s="33" t="inlineStr">
+      <c r="Z9" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7018,7 +7120,7 @@
           <t>Calacatta 4-person Inflatable Spa</t>
         </is>
       </c>
-      <c r="AB9" s="33" t="inlineStr">
+      <c r="AB9" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7030,18 +7132,18 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF9" s="33" t="inlineStr"/>
-      <c r="AG9" s="33" t="inlineStr">
+      <c r="AF9" s="36" t="inlineStr"/>
+      <c r="AG9" s="36" t="inlineStr">
         <is>
           <t>175.0cm</t>
         </is>
       </c>
-      <c r="AH9" s="33" t="inlineStr">
+      <c r="AH9" s="36" t="inlineStr">
         <is>
           <t>175.0cm</t>
         </is>
       </c>
-      <c r="AI9" s="33" t="inlineStr">
+      <c r="AI9" s="36" t="inlineStr">
         <is>
           <t>71.0cm</t>
         </is>
@@ -7063,17 +7165,17 @@
           <t>A 3.0 kg tub of hth stabiliser granules for outdoor swimming pools, used to protect chlorine from UV degradation and extend its effectiveness. A reliable way to get more mileage from your sanitiser on sunny days.</t>
         </is>
       </c>
-      <c r="D10" s="33" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E10" s="33" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F10" s="33" t="inlineStr">
+      <c r="F10" s="36" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -7083,75 +7185,75 @@
           <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H10" s="33" t="inlineStr">
+      <c r="H10" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I10" s="33" t="inlineStr">
+      <c r="I10" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J10" s="33" t="inlineStr">
+      <c r="J10" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K10" s="33" t="inlineStr">
+      <c r="K10" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L10" s="33" t="inlineStr">
+      <c r="L10" s="36" t="inlineStr">
         <is>
           <t>HTH-CHM-5716</t>
         </is>
       </c>
-      <c r="M10" s="34" t="inlineStr">
+      <c r="M10" s="37" t="inlineStr">
         <is>
           <t>3521686005716</t>
         </is>
       </c>
-      <c r="N10" s="35" t="inlineStr"/>
-      <c r="O10" s="35" t="inlineStr"/>
-      <c r="P10" s="35" t="inlineStr"/>
-      <c r="Q10" s="33" t="inlineStr">
+      <c r="N10" s="38" t="inlineStr"/>
+      <c r="O10" s="38" t="inlineStr"/>
+      <c r="P10" s="38" t="inlineStr"/>
+      <c r="Q10" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R10" s="33" t="inlineStr">
+      <c r="R10" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S10" s="33" t="inlineStr">
+      <c r="S10" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T10" s="33" t="inlineStr">
+      <c r="T10" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U10" s="33" t="inlineStr">
+      <c r="U10" s="36" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="V10" s="33" t="inlineStr">
+      <c r="V10" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W10" s="33" t="inlineStr">
+      <c r="W10" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X10" s="33" t="inlineStr">
+      <c r="X10" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7161,7 +7263,7 @@
           <t>https://images.barcodelookup.com/12027/120276177-1.jpg</t>
         </is>
       </c>
-      <c r="Z10" s="33" t="inlineStr">
+      <c r="Z10" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7171,7 +7273,7 @@
           <t>Hth Stabilizer Granulat 3,0 Kg</t>
         </is>
       </c>
-      <c r="AB10" s="33" t="inlineStr">
+      <c r="AB10" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7183,10 +7285,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF10" s="33" t="inlineStr"/>
-      <c r="AG10" s="33" t="inlineStr"/>
-      <c r="AH10" s="33" t="inlineStr"/>
-      <c r="AI10" s="33" t="inlineStr"/>
+      <c r="AF10" s="36" t="inlineStr"/>
+      <c r="AG10" s="36" t="inlineStr"/>
+      <c r="AH10" s="36" t="inlineStr"/>
+      <c r="AI10" s="36" t="inlineStr"/>
     </row>
     <row r="11" ht="62" customHeight="1">
       <c r="A11" s="17" t="inlineStr">
@@ -7204,17 +7306,17 @@
           <t>A 1-litre bottle of hth Spa Antikalk, formulated to prevent and remove limescale in spa and hot tub water. Keeping scale under control helps protect internal components and maintain water clarity.</t>
         </is>
       </c>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="D11" s="36" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E11" s="33" t="inlineStr">
+      <c r="E11" s="36" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F11" s="33" t="inlineStr">
+      <c r="F11" s="36" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -7224,71 +7326,71 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H11" s="33" t="inlineStr">
+      <c r="H11" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I11" s="33" t="inlineStr">
+      <c r="I11" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J11" s="33" t="inlineStr">
+      <c r="J11" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K11" s="33" t="inlineStr">
+      <c r="K11" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L11" s="33" t="inlineStr">
+      <c r="L11" s="36" t="inlineStr">
         <is>
           <t>HTH-SPA-0194</t>
         </is>
       </c>
-      <c r="M11" s="34" t="inlineStr">
+      <c r="M11" s="37" t="inlineStr">
         <is>
           <t>3521684700194</t>
         </is>
       </c>
-      <c r="N11" s="35" t="inlineStr"/>
-      <c r="O11" s="35" t="inlineStr"/>
-      <c r="P11" s="35" t="inlineStr"/>
-      <c r="Q11" s="33" t="inlineStr">
+      <c r="N11" s="38" t="inlineStr"/>
+      <c r="O11" s="38" t="inlineStr"/>
+      <c r="P11" s="38" t="inlineStr"/>
+      <c r="Q11" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R11" s="33" t="inlineStr">
+      <c r="R11" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S11" s="33" t="inlineStr">
+      <c r="S11" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T11" s="33" t="inlineStr">
+      <c r="T11" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U11" s="33" t="inlineStr"/>
-      <c r="V11" s="33" t="inlineStr">
+      <c r="U11" s="36" t="inlineStr"/>
+      <c r="V11" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W11" s="33" t="inlineStr">
+      <c r="W11" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X11" s="33" t="inlineStr">
+      <c r="X11" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7298,7 +7400,7 @@
           <t>https://www.north-spa.de/wp-content/uploads/2025/02/Produktbild-1-hth-SPA-ANTIKALK-1-l-3521684700194-360x360.jpg</t>
         </is>
       </c>
-      <c r="Z11" s="33" t="inlineStr">
+      <c r="Z11" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7308,7 +7410,7 @@
           <t>1 l - hth® Spa ANTIKALK</t>
         </is>
       </c>
-      <c r="AB11" s="33" t="inlineStr">
+      <c r="AB11" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7320,10 +7422,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF11" s="33" t="inlineStr"/>
-      <c r="AG11" s="33" t="inlineStr"/>
-      <c r="AH11" s="33" t="inlineStr"/>
-      <c r="AI11" s="33" t="inlineStr"/>
+      <c r="AF11" s="36" t="inlineStr"/>
+      <c r="AG11" s="36" t="inlineStr"/>
+      <c r="AH11" s="36" t="inlineStr"/>
+      <c r="AI11" s="36" t="inlineStr"/>
     </row>
     <row r="12" ht="62" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
@@ -7341,13 +7443,13 @@
           <t>A round, olive-green inflatable spa designed to seat up to eight people comfortably, with a maximum water temperature of 40°C. Five accessories are included in the box, so there is plenty to get started with straight away.</t>
         </is>
       </c>
-      <c r="D12" s="33" t="inlineStr"/>
-      <c r="E12" s="33" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr"/>
+      <c r="E12" s="36" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F12" s="33" t="inlineStr">
+      <c r="F12" s="36" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -7357,71 +7459,71 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H12" s="33" t="inlineStr">
+      <c r="H12" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I12" s="33" t="inlineStr">
+      <c r="I12" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J12" s="33" t="inlineStr">
+      <c r="J12" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K12" s="33" t="inlineStr">
+      <c r="K12" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L12" s="33" t="inlineStr">
+      <c r="L12" s="36" t="inlineStr">
         <is>
           <t>GEN-SPA-9274</t>
         </is>
       </c>
-      <c r="M12" s="34" t="inlineStr">
+      <c r="M12" s="37" t="inlineStr">
         <is>
           <t>6941057429274</t>
         </is>
       </c>
-      <c r="N12" s="35" t="inlineStr"/>
-      <c r="O12" s="35" t="inlineStr"/>
-      <c r="P12" s="35" t="inlineStr"/>
-      <c r="Q12" s="33" t="inlineStr">
+      <c r="N12" s="38" t="inlineStr"/>
+      <c r="O12" s="38" t="inlineStr"/>
+      <c r="P12" s="38" t="inlineStr"/>
+      <c r="Q12" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R12" s="33" t="inlineStr">
+      <c r="R12" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S12" s="33" t="inlineStr">
+      <c r="S12" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T12" s="33" t="inlineStr">
+      <c r="T12" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U12" s="33" t="inlineStr"/>
-      <c r="V12" s="33" t="inlineStr">
+      <c r="U12" s="36" t="inlineStr"/>
+      <c r="V12" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W12" s="33" t="inlineStr">
+      <c r="W12" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X12" s="33" t="inlineStr">
+      <c r="X12" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7431,7 +7533,7 @@
           <t>https://media.intex.fr/11990-large_default_x2/28412np-spa-gonflable-olive-8-places.jpg</t>
         </is>
       </c>
-      <c r="Z12" s="33" t="inlineStr">
+      <c r="Z12" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7441,7 +7543,7 @@
           <t>Olive 8-person Inflatable Spa</t>
         </is>
       </c>
-      <c r="AB12" s="33" t="inlineStr">
+      <c r="AB12" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7453,10 +7555,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF12" s="33" t="inlineStr"/>
-      <c r="AG12" s="33" t="inlineStr"/>
-      <c r="AH12" s="33" t="inlineStr"/>
-      <c r="AI12" s="33" t="inlineStr"/>
+      <c r="AF12" s="36" t="inlineStr"/>
+      <c r="AG12" s="36" t="inlineStr"/>
+      <c r="AH12" s="36" t="inlineStr"/>
+      <c r="AI12" s="36" t="inlineStr"/>
     </row>
     <row r="13" ht="62" customHeight="1">
       <c r="A13" s="17" t="inlineStr">
@@ -7474,17 +7576,17 @@
           <t>A Darlly SC750 replacement cartridge filter compatible with Arctic, Fonteyn, Rota, and Strong Spa hot tubs, among others. A straightforward like-for-like swap to keep your spa water flowing clean.</t>
         </is>
       </c>
-      <c r="D13" s="33" t="inlineStr">
+      <c r="D13" s="36" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E13" s="33" t="inlineStr">
+      <c r="E13" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F13" s="33" t="inlineStr">
+      <c r="F13" s="36" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -7494,71 +7596,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H13" s="33" t="inlineStr">
+      <c r="H13" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I13" s="33" t="inlineStr">
+      <c r="I13" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J13" s="33" t="inlineStr">
+      <c r="J13" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K13" s="33" t="inlineStr">
+      <c r="K13" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L13" s="33" t="inlineStr">
+      <c r="L13" s="36" t="inlineStr">
         <is>
           <t>DAR-FIL-2116</t>
         </is>
       </c>
-      <c r="M13" s="34" t="inlineStr">
+      <c r="M13" s="37" t="inlineStr">
         <is>
           <t>700175992116</t>
         </is>
       </c>
-      <c r="N13" s="35" t="inlineStr"/>
-      <c r="O13" s="35" t="inlineStr"/>
-      <c r="P13" s="35" t="inlineStr"/>
-      <c r="Q13" s="33" t="inlineStr">
+      <c r="N13" s="38" t="inlineStr"/>
+      <c r="O13" s="38" t="inlineStr"/>
+      <c r="P13" s="38" t="inlineStr"/>
+      <c r="Q13" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R13" s="33" t="inlineStr">
+      <c r="R13" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S13" s="33" t="inlineStr">
+      <c r="S13" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T13" s="33" t="inlineStr">
+      <c r="T13" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U13" s="33" t="inlineStr"/>
-      <c r="V13" s="33" t="inlineStr">
+      <c r="U13" s="36" t="inlineStr"/>
+      <c r="V13" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W13" s="33" t="inlineStr">
+      <c r="W13" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X13" s="33" t="inlineStr">
+      <c r="X13" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7568,7 +7670,7 @@
           <t>https://images.barcodelookup.com/29338/293384728-1.jpg</t>
         </is>
       </c>
-      <c r="Z13" s="33" t="inlineStr">
+      <c r="Z13" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7578,7 +7680,7 @@
           <t>SC750 Filter Replacement Filter Lamellar Filter Arctic Fonteyn Rota Strong Spa - Darlly</t>
         </is>
       </c>
-      <c r="AB13" s="33" t="inlineStr">
+      <c r="AB13" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7590,10 +7692,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF13" s="33" t="inlineStr"/>
-      <c r="AG13" s="33" t="inlineStr"/>
-      <c r="AH13" s="33" t="inlineStr"/>
-      <c r="AI13" s="33" t="inlineStr"/>
+      <c r="AF13" s="36" t="inlineStr"/>
+      <c r="AG13" s="36" t="inlineStr"/>
+      <c r="AH13" s="36" t="inlineStr"/>
+      <c r="AI13" s="36" t="inlineStr"/>
     </row>
     <row r="14" ht="62" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
@@ -7611,17 +7713,17 @@
           <t>SpaBalancer Clean and Refresh is a spa water treatment product supplied with a sprayer for easy application. It is designed to keep spa water fresh and clean as part of a regular maintenance routine.</t>
         </is>
       </c>
-      <c r="D14" s="33" t="inlineStr">
+      <c r="D14" s="36" t="inlineStr">
         <is>
           <t>SpaBalancer</t>
         </is>
       </c>
-      <c r="E14" s="33" t="inlineStr">
+      <c r="E14" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F14" s="33" t="inlineStr">
+      <c r="F14" s="36" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -7631,71 +7733,71 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H14" s="33" t="inlineStr">
+      <c r="H14" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I14" s="33" t="inlineStr">
+      <c r="I14" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J14" s="33" t="inlineStr">
+      <c r="J14" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K14" s="33" t="inlineStr">
+      <c r="K14" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L14" s="33" t="inlineStr">
+      <c r="L14" s="36" t="inlineStr">
         <is>
           <t>SPA-CLN-0117</t>
         </is>
       </c>
-      <c r="M14" s="34" t="inlineStr">
+      <c r="M14" s="37" t="inlineStr">
         <is>
           <t>4260374980117</t>
         </is>
       </c>
-      <c r="N14" s="35" t="inlineStr"/>
-      <c r="O14" s="35" t="inlineStr"/>
-      <c r="P14" s="35" t="inlineStr"/>
-      <c r="Q14" s="33" t="inlineStr">
+      <c r="N14" s="38" t="inlineStr"/>
+      <c r="O14" s="38" t="inlineStr"/>
+      <c r="P14" s="38" t="inlineStr"/>
+      <c r="Q14" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R14" s="33" t="inlineStr">
+      <c r="R14" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S14" s="33" t="inlineStr">
+      <c r="S14" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T14" s="33" t="inlineStr">
+      <c r="T14" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U14" s="33" t="inlineStr"/>
-      <c r="V14" s="33" t="inlineStr">
+      <c r="U14" s="36" t="inlineStr"/>
+      <c r="V14" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W14" s="33" t="inlineStr">
+      <c r="W14" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X14" s="33" t="inlineStr">
+      <c r="X14" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7705,7 +7807,7 @@
           <t>https://www.spabalancer.ch/media/ae/20/d2/1728651174/sb111_clean-refresh_freigestellt.png?ts=1777362921</t>
         </is>
       </c>
-      <c r="Z14" s="33" t="inlineStr">
+      <c r="Z14" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7715,7 +7817,7 @@
           <t>SpaBalancer Clean &amp; Refresh (+ sprayer)</t>
         </is>
       </c>
-      <c r="AB14" s="33" t="inlineStr">
+      <c r="AB14" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7727,10 +7829,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF14" s="33" t="inlineStr"/>
-      <c r="AG14" s="33" t="inlineStr"/>
-      <c r="AH14" s="33" t="inlineStr"/>
-      <c r="AI14" s="33" t="inlineStr"/>
+      <c r="AF14" s="36" t="inlineStr"/>
+      <c r="AG14" s="36" t="inlineStr"/>
+      <c r="AH14" s="36" t="inlineStr"/>
+      <c r="AI14" s="36" t="inlineStr"/>
     </row>
     <row r="15" ht="62" customHeight="1">
       <c r="A15" s="17" t="inlineStr">
@@ -7748,17 +7850,17 @@
           <t>A pack of 500 DPD 1 reagent tablets for use with the Water-ID photometer, measuring free chlorine levels in pool or spa water. Having a full pack to hand means you will not run short mid-season.</t>
         </is>
       </c>
-      <c r="D15" s="33" t="inlineStr">
+      <c r="D15" s="36" t="inlineStr">
         <is>
           <t>Water-i.d.</t>
         </is>
       </c>
-      <c r="E15" s="33" t="inlineStr">
+      <c r="E15" s="36" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F15" s="33" t="inlineStr">
+      <c r="F15" s="36" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -7768,79 +7870,79 @@
           <t>test-measure, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H15" s="33" t="inlineStr">
+      <c r="H15" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I15" s="33" t="inlineStr">
+      <c r="I15" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J15" s="33" t="inlineStr">
+      <c r="J15" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K15" s="33" t="inlineStr">
+      <c r="K15" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L15" s="33" t="inlineStr">
+      <c r="L15" s="36" t="inlineStr">
         <is>
           <t>WAT-TST-1702</t>
         </is>
       </c>
-      <c r="M15" s="34" t="inlineStr">
+      <c r="M15" s="37" t="inlineStr">
         <is>
           <t>4260431461702</t>
         </is>
       </c>
-      <c r="N15" s="35" t="inlineStr"/>
-      <c r="O15" s="35" t="inlineStr"/>
-      <c r="P15" s="35" t="inlineStr"/>
-      <c r="Q15" s="33" t="inlineStr">
+      <c r="N15" s="38" t="inlineStr"/>
+      <c r="O15" s="38" t="inlineStr"/>
+      <c r="P15" s="38" t="inlineStr"/>
+      <c r="Q15" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R15" s="33" t="inlineStr">
+      <c r="R15" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S15" s="33" t="inlineStr">
+      <c r="S15" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T15" s="33" t="inlineStr">
+      <c r="T15" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U15" s="33" t="inlineStr"/>
-      <c r="V15" s="33" t="inlineStr">
+      <c r="U15" s="36" t="inlineStr"/>
+      <c r="V15" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W15" s="33" t="inlineStr">
+      <c r="W15" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X15" s="33" t="inlineStr">
+      <c r="X15" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y15" s="17" t="inlineStr"/>
-      <c r="Z15" s="33" t="inlineStr"/>
+      <c r="Z15" s="36" t="inlineStr"/>
       <c r="AA15" s="17" t="inlineStr"/>
-      <c r="AB15" s="33" t="inlineStr">
+      <c r="AB15" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7852,10 +7954,10 @@
           <t>Pool Accessories</t>
         </is>
       </c>
-      <c r="AF15" s="33" t="inlineStr"/>
-      <c r="AG15" s="33" t="inlineStr"/>
-      <c r="AH15" s="33" t="inlineStr"/>
-      <c r="AI15" s="33" t="inlineStr"/>
+      <c r="AF15" s="36" t="inlineStr"/>
+      <c r="AG15" s="36" t="inlineStr"/>
+      <c r="AH15" s="36" t="inlineStr"/>
+      <c r="AI15" s="36" t="inlineStr"/>
     </row>
     <row r="16" ht="62" customHeight="1">
       <c r="A16" s="17" t="inlineStr">
@@ -7873,17 +7975,17 @@
           <t>A pack of 500 Phenol Red reagent tablets compatible with the Water-ID photometer, used for measuring pH levels in pool or spa water. Accurate pH readings are the foundation of balanced, comfortable water.</t>
         </is>
       </c>
-      <c r="D16" s="33" t="inlineStr">
+      <c r="D16" s="36" t="inlineStr">
         <is>
           <t>Water-i.d.</t>
         </is>
       </c>
-      <c r="E16" s="33" t="inlineStr">
+      <c r="E16" s="36" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F16" s="33" t="inlineStr">
+      <c r="F16" s="36" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -7893,71 +7995,71 @@
           <t>test-measure, add-on, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H16" s="33" t="inlineStr">
+      <c r="H16" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I16" s="33" t="inlineStr">
+      <c r="I16" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J16" s="33" t="inlineStr">
+      <c r="J16" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K16" s="33" t="inlineStr">
+      <c r="K16" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L16" s="33" t="inlineStr">
+      <c r="L16" s="36" t="inlineStr">
         <is>
           <t>WAT-TST-1801</t>
         </is>
       </c>
-      <c r="M16" s="34" t="inlineStr">
+      <c r="M16" s="37" t="inlineStr">
         <is>
           <t>4260431461801</t>
         </is>
       </c>
-      <c r="N16" s="35" t="inlineStr"/>
-      <c r="O16" s="35" t="inlineStr"/>
-      <c r="P16" s="35" t="inlineStr"/>
-      <c r="Q16" s="33" t="inlineStr">
+      <c r="N16" s="38" t="inlineStr"/>
+      <c r="O16" s="38" t="inlineStr"/>
+      <c r="P16" s="38" t="inlineStr"/>
+      <c r="Q16" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R16" s="33" t="inlineStr">
+      <c r="R16" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S16" s="33" t="inlineStr">
+      <c r="S16" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T16" s="33" t="inlineStr">
+      <c r="T16" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U16" s="33" t="inlineStr"/>
-      <c r="V16" s="33" t="inlineStr">
+      <c r="U16" s="36" t="inlineStr"/>
+      <c r="V16" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W16" s="33" t="inlineStr">
+      <c r="W16" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X16" s="33" t="inlineStr">
+      <c r="X16" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7967,7 +8069,7 @@
           <t>https://www.poolpowershop.de/media/46/63/13/1743521499/phenol-red-testtabletten-fuer-poollab-500-stk.jpg</t>
         </is>
       </c>
-      <c r="Z16" s="33" t="inlineStr">
+      <c r="Z16" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7977,7 +8079,7 @@
           <t>WATER-I.D. Water-ID Reagenzien Phenol Red Photometer 500</t>
         </is>
       </c>
-      <c r="AB16" s="33" t="inlineStr">
+      <c r="AB16" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7989,10 +8091,10 @@
           <t>Pool Accessories</t>
         </is>
       </c>
-      <c r="AF16" s="33" t="inlineStr"/>
-      <c r="AG16" s="33" t="inlineStr"/>
-      <c r="AH16" s="33" t="inlineStr"/>
-      <c r="AI16" s="33" t="inlineStr"/>
+      <c r="AF16" s="36" t="inlineStr"/>
+      <c r="AG16" s="36" t="inlineStr"/>
+      <c r="AH16" s="36" t="inlineStr"/>
+      <c r="AI16" s="36" t="inlineStr"/>
     </row>
     <row r="17" ht="62" customHeight="1">
       <c r="A17" s="17" t="inlineStr">
@@ -8010,17 +8112,17 @@
           <t>An alkaline edge and surround cleaner in a 1-litre bottle, formulated to be gentle on pool liners, foils, and plastic surfaces. It tackles waterline grime without harming the materials it touches.</t>
         </is>
       </c>
-      <c r="D17" s="33" t="inlineStr">
+      <c r="D17" s="36" t="inlineStr">
         <is>
           <t>Cristal</t>
         </is>
       </c>
-      <c r="E17" s="33" t="inlineStr">
+      <c r="E17" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F17" s="33" t="inlineStr">
+      <c r="F17" s="36" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8030,71 +8132,71 @@
           <t>pool, water-treatment, cleaning, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H17" s="33" t="inlineStr">
+      <c r="H17" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I17" s="33" t="inlineStr">
+      <c r="I17" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J17" s="33" t="inlineStr">
+      <c r="J17" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K17" s="33" t="inlineStr">
+      <c r="K17" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L17" s="33" t="inlineStr">
+      <c r="L17" s="36" t="inlineStr">
         <is>
           <t>CRI-CHM-5212</t>
         </is>
       </c>
-      <c r="M17" s="34" t="inlineStr">
+      <c r="M17" s="37" t="inlineStr">
         <is>
           <t>4002369155212</t>
         </is>
       </c>
-      <c r="N17" s="35" t="inlineStr"/>
-      <c r="O17" s="35" t="inlineStr"/>
-      <c r="P17" s="35" t="inlineStr"/>
-      <c r="Q17" s="33" t="inlineStr">
+      <c r="N17" s="38" t="inlineStr"/>
+      <c r="O17" s="38" t="inlineStr"/>
+      <c r="P17" s="38" t="inlineStr"/>
+      <c r="Q17" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R17" s="33" t="inlineStr">
+      <c r="R17" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S17" s="33" t="inlineStr">
+      <c r="S17" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T17" s="33" t="inlineStr">
+      <c r="T17" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U17" s="33" t="inlineStr"/>
-      <c r="V17" s="33" t="inlineStr">
+      <c r="U17" s="36" t="inlineStr"/>
+      <c r="V17" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W17" s="33" t="inlineStr">
+      <c r="W17" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X17" s="33" t="inlineStr">
+      <c r="X17" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8104,7 +8206,7 @@
           <t>https://images.barcodelookup.com/21057/210579756-1.jpg</t>
         </is>
       </c>
-      <c r="Z17" s="33" t="inlineStr">
+      <c r="Z17" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8114,7 +8216,7 @@
           <t>Cristal Poolpflege CRISTAL Alkaline Edge Cleaner 1,0 l, (Gentle on Materials, for Liners, Plastic Surfaces</t>
         </is>
       </c>
-      <c r="AB17" s="33" t="inlineStr">
+      <c r="AB17" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8126,10 +8228,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF17" s="33" t="inlineStr"/>
-      <c r="AG17" s="33" t="inlineStr"/>
-      <c r="AH17" s="33" t="inlineStr"/>
-      <c r="AI17" s="33" t="inlineStr"/>
+      <c r="AF17" s="36" t="inlineStr"/>
+      <c r="AG17" s="36" t="inlineStr"/>
+      <c r="AH17" s="36" t="inlineStr"/>
+      <c r="AI17" s="36" t="inlineStr"/>
     </row>
     <row r="18" ht="76" customHeight="1">
       <c r="A18" s="17" t="inlineStr">
@@ -8147,17 +8249,17 @@
           <t>A 1-litre pool surface cleaner formulated to remove sunscreen oils and greasy residues from the water surface, designed specifically for warm Mediterranean climates and heavy swimming loads. It keeps the waterline and surface clear without harming pool materials.</t>
         </is>
       </c>
-      <c r="D18" s="33" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E18" s="33" t="inlineStr">
+      <c r="E18" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F18" s="33" t="inlineStr">
+      <c r="F18" s="36" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8167,71 +8269,71 @@
           <t>pool, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H18" s="33" t="inlineStr">
+      <c r="H18" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I18" s="33" t="inlineStr">
+      <c r="I18" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J18" s="33" t="inlineStr">
+      <c r="J18" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K18" s="33" t="inlineStr">
+      <c r="K18" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L18" s="33" t="inlineStr">
+      <c r="L18" s="36" t="inlineStr">
         <is>
           <t>AQU-CLN-0223</t>
         </is>
       </c>
-      <c r="M18" s="34" t="inlineStr">
+      <c r="M18" s="37" t="inlineStr">
         <is>
           <t>5292638000223</t>
         </is>
       </c>
-      <c r="N18" s="35" t="inlineStr"/>
-      <c r="O18" s="35" t="inlineStr"/>
-      <c r="P18" s="35" t="inlineStr"/>
-      <c r="Q18" s="33" t="inlineStr">
+      <c r="N18" s="38" t="inlineStr"/>
+      <c r="O18" s="38" t="inlineStr"/>
+      <c r="P18" s="38" t="inlineStr"/>
+      <c r="Q18" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R18" s="33" t="inlineStr">
+      <c r="R18" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S18" s="33" t="inlineStr">
+      <c r="S18" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T18" s="33" t="inlineStr">
+      <c r="T18" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U18" s="33" t="inlineStr"/>
-      <c r="V18" s="33" t="inlineStr">
+      <c r="U18" s="36" t="inlineStr"/>
+      <c r="V18" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W18" s="33" t="inlineStr">
+      <c r="W18" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X18" s="33" t="inlineStr">
+      <c r="X18" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8241,7 +8343,7 @@
           <t>http://mangas.com.cy/media/products/5292638000223.jpg</t>
         </is>
       </c>
-      <c r="Z18" s="33" t="inlineStr">
+      <c r="Z18" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8251,7 +8353,7 @@
           <t>AQUALITY Pool Cleaner for Greasy Residues 1L</t>
         </is>
       </c>
-      <c r="AB18" s="33" t="inlineStr">
+      <c r="AB18" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8263,10 +8365,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF18" s="33" t="inlineStr"/>
-      <c r="AG18" s="33" t="inlineStr"/>
-      <c r="AH18" s="33" t="inlineStr"/>
-      <c r="AI18" s="33" t="inlineStr"/>
+      <c r="AF18" s="36" t="inlineStr"/>
+      <c r="AG18" s="36" t="inlineStr"/>
+      <c r="AH18" s="36" t="inlineStr"/>
+      <c r="AI18" s="36" t="inlineStr"/>
     </row>
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="17" t="inlineStr">
@@ -8284,17 +8386,17 @@
           <t>California Clear Blue is a super-concentrated, pH-neutral pool clarifier in a 1-litre bottle, using a cationic polymer formula to bind microscopic particles such as dust, pollen, and oils into larger clusters your filter can catch. Non-toxic and biodegradable, it is safe for sand, zeolite, and glass filtration media.</t>
         </is>
       </c>
-      <c r="D19" s="33" t="inlineStr">
+      <c r="D19" s="36" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E19" s="33" t="inlineStr">
+      <c r="E19" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F19" s="33" t="inlineStr">
+      <c r="F19" s="36" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8304,71 +8406,71 @@
           <t>pool, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H19" s="33" t="inlineStr">
+      <c r="H19" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I19" s="33" t="inlineStr">
+      <c r="I19" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J19" s="33" t="inlineStr">
+      <c r="J19" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K19" s="33" t="inlineStr">
+      <c r="K19" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L19" s="33" t="inlineStr">
+      <c r="L19" s="36" t="inlineStr">
         <is>
           <t>AQU-CHM-0070</t>
         </is>
       </c>
-      <c r="M19" s="34" t="inlineStr">
+      <c r="M19" s="37" t="inlineStr">
         <is>
           <t>5292638000070</t>
         </is>
       </c>
-      <c r="N19" s="35" t="inlineStr"/>
-      <c r="O19" s="35" t="inlineStr"/>
-      <c r="P19" s="35" t="inlineStr"/>
-      <c r="Q19" s="33" t="inlineStr">
+      <c r="N19" s="38" t="inlineStr"/>
+      <c r="O19" s="38" t="inlineStr"/>
+      <c r="P19" s="38" t="inlineStr"/>
+      <c r="Q19" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R19" s="33" t="inlineStr">
+      <c r="R19" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S19" s="33" t="inlineStr">
+      <c r="S19" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T19" s="33" t="inlineStr">
+      <c r="T19" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U19" s="33" t="inlineStr"/>
-      <c r="V19" s="33" t="inlineStr">
+      <c r="U19" s="36" t="inlineStr"/>
+      <c r="V19" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W19" s="33" t="inlineStr">
+      <c r="W19" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X19" s="33" t="inlineStr">
+      <c r="X19" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8378,7 +8480,7 @@
           <t>https://poolservices.cy/storage/2026/05/California-Clear-Blue-1L-Aquality-2.jpeg</t>
         </is>
       </c>
-      <c r="Z19" s="33" t="inlineStr">
+      <c r="Z19" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8388,7 +8490,7 @@
           <t>Pool Clarifier California Clear Blue Aquality 1L</t>
         </is>
       </c>
-      <c r="AB19" s="33" t="inlineStr">
+      <c r="AB19" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8400,10 +8502,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF19" s="33" t="inlineStr"/>
-      <c r="AG19" s="33" t="inlineStr"/>
-      <c r="AH19" s="33" t="inlineStr"/>
-      <c r="AI19" s="33" t="inlineStr"/>
+      <c r="AF19" s="36" t="inlineStr"/>
+      <c r="AG19" s="36" t="inlineStr"/>
+      <c r="AH19" s="36" t="inlineStr"/>
+      <c r="AI19" s="36" t="inlineStr"/>
     </row>
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="17" t="inlineStr">
@@ -8421,17 +8523,17 @@
           <t>A 1-litre tile and vinyl cleaner for pools, designed to clean pool tile surfaces and vinyl liners. It makes light work of the tidying up that keeps a pool looking its best.</t>
         </is>
       </c>
-      <c r="D20" s="33" t="inlineStr">
+      <c r="D20" s="36" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E20" s="33" t="inlineStr">
+      <c r="E20" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F20" s="33" t="inlineStr">
+      <c r="F20" s="36" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8441,71 +8543,71 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H20" s="33" t="inlineStr">
+      <c r="H20" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I20" s="33" t="inlineStr">
+      <c r="I20" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J20" s="33" t="inlineStr">
+      <c r="J20" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K20" s="33" t="inlineStr">
+      <c r="K20" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L20" s="33" t="inlineStr">
+      <c r="L20" s="36" t="inlineStr">
         <is>
           <t>AQU-CLN-0162</t>
         </is>
       </c>
-      <c r="M20" s="34" t="inlineStr">
+      <c r="M20" s="37" t="inlineStr">
         <is>
           <t>5292638000162</t>
         </is>
       </c>
-      <c r="N20" s="35" t="inlineStr"/>
-      <c r="O20" s="35" t="inlineStr"/>
-      <c r="P20" s="35" t="inlineStr"/>
-      <c r="Q20" s="33" t="inlineStr">
+      <c r="N20" s="38" t="inlineStr"/>
+      <c r="O20" s="38" t="inlineStr"/>
+      <c r="P20" s="38" t="inlineStr"/>
+      <c r="Q20" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R20" s="33" t="inlineStr">
+      <c r="R20" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S20" s="33" t="inlineStr">
+      <c r="S20" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T20" s="33" t="inlineStr">
+      <c r="T20" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U20" s="33" t="inlineStr"/>
-      <c r="V20" s="33" t="inlineStr">
+      <c r="U20" s="36" t="inlineStr"/>
+      <c r="V20" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W20" s="33" t="inlineStr">
+      <c r="W20" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X20" s="33" t="inlineStr">
+      <c r="X20" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8515,7 +8617,7 @@
           <t>http://mangas.com.cy/media/products/5292638000162.jpg</t>
         </is>
       </c>
-      <c r="Z20" s="33" t="inlineStr">
+      <c r="Z20" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8525,7 +8627,7 @@
           <t>AQUALITY Magic tile 4 vinyl cleaner 1L</t>
         </is>
       </c>
-      <c r="AB20" s="33" t="inlineStr">
+      <c r="AB20" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8537,10 +8639,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF20" s="33" t="inlineStr"/>
-      <c r="AG20" s="33" t="inlineStr"/>
-      <c r="AH20" s="33" t="inlineStr"/>
-      <c r="AI20" s="33" t="inlineStr"/>
+      <c r="AF20" s="36" t="inlineStr"/>
+      <c r="AG20" s="36" t="inlineStr"/>
+      <c r="AH20" s="36" t="inlineStr"/>
+      <c r="AI20" s="36" t="inlineStr"/>
     </row>
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="17" t="inlineStr">
@@ -8558,17 +8660,17 @@
           <t>A 1-litre spa and pool water clarifier from Bayzid, formulated to clear cloudy or turbid water. A handy bottle to reach for whenever the water loses its sparkle.</t>
         </is>
       </c>
-      <c r="D21" s="33" t="inlineStr">
+      <c r="D21" s="36" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E21" s="33" t="inlineStr">
+      <c r="E21" s="36" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F21" s="33" t="inlineStr">
+      <c r="F21" s="36" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -8578,71 +8680,71 @@
           <t>spa-hot-tub, pool, water-treatment, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H21" s="33" t="inlineStr">
+      <c r="H21" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I21" s="33" t="inlineStr">
+      <c r="I21" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J21" s="33" t="inlineStr">
+      <c r="J21" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K21" s="33" t="inlineStr">
+      <c r="K21" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L21" s="33" t="inlineStr">
+      <c r="L21" s="36" t="inlineStr">
         <is>
           <t>HFE-SPA-7202</t>
         </is>
       </c>
-      <c r="M21" s="34" t="inlineStr">
+      <c r="M21" s="37" t="inlineStr">
         <is>
           <t>4250463127202</t>
         </is>
       </c>
-      <c r="N21" s="35" t="inlineStr"/>
-      <c r="O21" s="35" t="inlineStr"/>
-      <c r="P21" s="35" t="inlineStr"/>
-      <c r="Q21" s="33" t="inlineStr">
+      <c r="N21" s="38" t="inlineStr"/>
+      <c r="O21" s="38" t="inlineStr"/>
+      <c r="P21" s="38" t="inlineStr"/>
+      <c r="Q21" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R21" s="33" t="inlineStr">
+      <c r="R21" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S21" s="33" t="inlineStr">
+      <c r="S21" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T21" s="33" t="inlineStr">
+      <c r="T21" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U21" s="33" t="inlineStr"/>
-      <c r="V21" s="33" t="inlineStr">
+      <c r="U21" s="36" t="inlineStr"/>
+      <c r="V21" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W21" s="33" t="inlineStr">
+      <c r="W21" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X21" s="33" t="inlineStr">
+      <c r="X21" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8652,7 +8754,7 @@
           <t>https://hoefer-shop.com/cdn/shop/files/1x1L-BAYZID-Spa-Poolclear-v1-RS_1.jpg?v=1785600487&amp;width=800</t>
         </is>
       </c>
-      <c r="Z21" s="33" t="inlineStr">
+      <c r="Z21" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8662,7 +8764,7 @@
           <t>Höfer Chemie GmbH Pool Care 1 L BAYZID® SPA Poolclear Turbidity Remover</t>
         </is>
       </c>
-      <c r="AB21" s="33" t="inlineStr">
+      <c r="AB21" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8674,10 +8776,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF21" s="33" t="inlineStr"/>
-      <c r="AG21" s="33" t="inlineStr"/>
-      <c r="AH21" s="33" t="inlineStr"/>
-      <c r="AI21" s="33" t="inlineStr"/>
+      <c r="AF21" s="36" t="inlineStr"/>
+      <c r="AG21" s="36" t="inlineStr"/>
+      <c r="AH21" s="36" t="inlineStr"/>
+      <c r="AI21" s="36" t="inlineStr"/>
     </row>
     <row r="22" ht="62" customHeight="1">
       <c r="A22" s="17" t="inlineStr">
@@ -8695,17 +8797,17 @@
           <t>A 1-litre bottle of hydrogen peroxide at 11.9% concentration, suitable for disinfection and water treatment applications. A straightforward chemical solution that keeps things clean without fuss.</t>
         </is>
       </c>
-      <c r="D22" s="33" t="inlineStr">
+      <c r="D22" s="36" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E22" s="33" t="inlineStr">
+      <c r="E22" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F22" s="33" t="inlineStr">
+      <c r="F22" s="36" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8715,71 +8817,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H22" s="33" t="inlineStr">
+      <c r="H22" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I22" s="33" t="inlineStr">
+      <c r="I22" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J22" s="33" t="inlineStr">
+      <c r="J22" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K22" s="33" t="inlineStr">
+      <c r="K22" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L22" s="33" t="inlineStr">
+      <c r="L22" s="36" t="inlineStr">
         <is>
           <t>HFE-CHM-6788</t>
         </is>
       </c>
-      <c r="M22" s="34" t="inlineStr">
+      <c r="M22" s="37" t="inlineStr">
         <is>
           <t>4250463106788</t>
         </is>
       </c>
-      <c r="N22" s="35" t="inlineStr"/>
-      <c r="O22" s="35" t="inlineStr"/>
-      <c r="P22" s="35" t="inlineStr"/>
-      <c r="Q22" s="33" t="inlineStr">
+      <c r="N22" s="38" t="inlineStr"/>
+      <c r="O22" s="38" t="inlineStr"/>
+      <c r="P22" s="38" t="inlineStr"/>
+      <c r="Q22" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R22" s="33" t="inlineStr">
+      <c r="R22" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S22" s="33" t="inlineStr">
+      <c r="S22" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T22" s="33" t="inlineStr">
+      <c r="T22" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U22" s="33" t="inlineStr"/>
-      <c r="V22" s="33" t="inlineStr">
+      <c r="U22" s="36" t="inlineStr"/>
+      <c r="V22" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W22" s="33" t="inlineStr">
+      <c r="W22" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X22" s="33" t="inlineStr">
+      <c r="X22" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8789,7 +8891,7 @@
           <t>https://hoefer-shop.com/cdn/shop/files/1x1L-Wasserstoffperoxid-Flasche-hinten-26.jpg?v=1783777627&amp;width=1000</t>
         </is>
       </c>
-      <c r="Z22" s="33" t="inlineStr">
+      <c r="Z22" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8799,7 +8901,7 @@
           <t>HÖFER CHEMIE GMBH 1 l Hydrogen Peroxide 11,9%</t>
         </is>
       </c>
-      <c r="AB22" s="33" t="inlineStr">
+      <c r="AB22" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8811,10 +8913,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF22" s="33" t="inlineStr"/>
-      <c r="AG22" s="33" t="inlineStr"/>
-      <c r="AH22" s="33" t="inlineStr"/>
-      <c r="AI22" s="33" t="inlineStr"/>
+      <c r="AF22" s="36" t="inlineStr"/>
+      <c r="AG22" s="36" t="inlineStr"/>
+      <c r="AH22" s="36" t="inlineStr"/>
+      <c r="AI22" s="36" t="inlineStr"/>
     </row>
     <row r="23" ht="62" customHeight="1">
       <c r="A23" s="17" t="inlineStr">
@@ -8832,17 +8934,17 @@
           <t>A 4.5 kg pack of chlorine stabilizer for swimming pools, used to protect chlorine from UV degradation and extend its effectiveness in the water. Steady chemistry for a pool that earns its keep.</t>
         </is>
       </c>
-      <c r="D23" s="33" t="inlineStr">
+      <c r="D23" s="36" t="inlineStr">
         <is>
           <t>AstralPool</t>
         </is>
       </c>
-      <c r="E23" s="33" t="inlineStr">
+      <c r="E23" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F23" s="33" t="inlineStr">
+      <c r="F23" s="36" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8852,83 +8954,83 @@
           <t>water-treatment, repeat-purchase, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H23" s="33" t="inlineStr">
+      <c r="H23" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I23" s="33" t="inlineStr">
+      <c r="I23" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J23" s="33" t="inlineStr">
+      <c r="J23" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K23" s="33" t="inlineStr">
+      <c r="K23" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L23" s="33" t="inlineStr">
+      <c r="L23" s="36" t="inlineStr">
         <is>
           <t>AST-CHM-0626</t>
         </is>
       </c>
-      <c r="M23" s="34" t="inlineStr">
+      <c r="M23" s="37" t="inlineStr">
         <is>
           <t>8432611960626</t>
         </is>
       </c>
-      <c r="N23" s="35" t="inlineStr"/>
-      <c r="O23" s="35" t="inlineStr"/>
-      <c r="P23" s="35" t="inlineStr"/>
-      <c r="Q23" s="33" t="inlineStr">
+      <c r="N23" s="38" t="inlineStr"/>
+      <c r="O23" s="38" t="inlineStr"/>
+      <c r="P23" s="38" t="inlineStr"/>
+      <c r="Q23" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R23" s="33" t="inlineStr">
+      <c r="R23" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S23" s="33" t="inlineStr">
+      <c r="S23" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T23" s="33" t="inlineStr">
+      <c r="T23" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U23" s="33" t="inlineStr">
+      <c r="U23" s="36" t="inlineStr">
         <is>
           <t>4500</t>
         </is>
       </c>
-      <c r="V23" s="33" t="inlineStr">
+      <c r="V23" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W23" s="33" t="inlineStr">
+      <c r="W23" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X23" s="33" t="inlineStr">
+      <c r="X23" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
-      <c r="Z23" s="33" t="inlineStr"/>
+      <c r="Z23" s="36" t="inlineStr"/>
       <c r="AA23" s="17" t="inlineStr"/>
-      <c r="AB23" s="33" t="inlineStr">
+      <c r="AB23" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8940,10 +9042,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF23" s="33" t="inlineStr"/>
-      <c r="AG23" s="33" t="inlineStr"/>
-      <c r="AH23" s="33" t="inlineStr"/>
-      <c r="AI23" s="33" t="inlineStr"/>
+      <c r="AF23" s="36" t="inlineStr"/>
+      <c r="AG23" s="36" t="inlineStr"/>
+      <c r="AH23" s="36" t="inlineStr"/>
+      <c r="AI23" s="36" t="inlineStr"/>
     </row>
     <row r="24" ht="62" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
@@ -8961,17 +9063,17 @@
           <t>UltraShock is a pool and spa shock treatment from SpaBalancer, designed to rapidly oxidise contaminants and restore water clarity. A quick reset for water that needs a little more persuasion.</t>
         </is>
       </c>
-      <c r="D24" s="33" t="inlineStr">
+      <c r="D24" s="36" t="inlineStr">
         <is>
           <t>SpaBalancer</t>
         </is>
       </c>
-      <c r="E24" s="33" t="inlineStr">
+      <c r="E24" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F24" s="33" t="inlineStr">
+      <c r="F24" s="36" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8981,71 +9083,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H24" s="33" t="inlineStr">
+      <c r="H24" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I24" s="33" t="inlineStr">
+      <c r="I24" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J24" s="33" t="inlineStr">
+      <c r="J24" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K24" s="33" t="inlineStr">
+      <c r="K24" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L24" s="33" t="inlineStr">
+      <c r="L24" s="36" t="inlineStr">
         <is>
           <t>SPA-CHM-0025</t>
         </is>
       </c>
-      <c r="M24" s="34" t="inlineStr">
+      <c r="M24" s="37" t="inlineStr">
         <is>
           <t>4260374980025</t>
         </is>
       </c>
-      <c r="N24" s="35" t="inlineStr"/>
-      <c r="O24" s="35" t="inlineStr"/>
-      <c r="P24" s="35" t="inlineStr"/>
-      <c r="Q24" s="33" t="inlineStr">
+      <c r="N24" s="38" t="inlineStr"/>
+      <c r="O24" s="38" t="inlineStr"/>
+      <c r="P24" s="38" t="inlineStr"/>
+      <c r="Q24" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R24" s="33" t="inlineStr">
+      <c r="R24" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S24" s="33" t="inlineStr">
+      <c r="S24" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T24" s="33" t="inlineStr">
+      <c r="T24" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U24" s="33" t="inlineStr"/>
-      <c r="V24" s="33" t="inlineStr">
+      <c r="U24" s="36" t="inlineStr"/>
+      <c r="V24" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W24" s="33" t="inlineStr">
+      <c r="W24" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X24" s="33" t="inlineStr">
+      <c r="X24" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9055,7 +9157,7 @@
           <t>https://images.barcodelookup.com/16704/167043133-1.jpg</t>
         </is>
       </c>
-      <c r="Z24" s="33" t="inlineStr">
+      <c r="Z24" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9065,7 +9167,7 @@
           <t>SpaBalancer UltraShock</t>
         </is>
       </c>
-      <c r="AB24" s="33" t="inlineStr">
+      <c r="AB24" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9077,10 +9179,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF24" s="33" t="inlineStr"/>
-      <c r="AG24" s="33" t="inlineStr"/>
-      <c r="AH24" s="33" t="inlineStr"/>
-      <c r="AI24" s="33" t="inlineStr"/>
+      <c r="AF24" s="36" t="inlineStr"/>
+      <c r="AG24" s="36" t="inlineStr"/>
+      <c r="AH24" s="36" t="inlineStr"/>
+      <c r="AI24" s="36" t="inlineStr"/>
     </row>
     <row r="25" ht="76" customHeight="1">
       <c r="A25" s="17" t="inlineStr">
@@ -9098,13 +9200,13 @@
           <t>A patented foam rubber eraser for cleaning pool surfaces, particularly suited to waterline stains on liner and vitreous ceramic finishes, and it works without detergents or chemicals. Each box contains 3 sponges, which harden when wet to scrub effectively while remaining soft and flexible in use.</t>
         </is>
       </c>
-      <c r="D25" s="33" t="inlineStr"/>
-      <c r="E25" s="33" t="inlineStr">
+      <c r="D25" s="36" t="inlineStr"/>
+      <c r="E25" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F25" s="33" t="inlineStr">
+      <c r="F25" s="36" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -9114,71 +9216,71 @@
           <t>pool, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H25" s="33" t="inlineStr">
+      <c r="H25" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I25" s="33" t="inlineStr">
+      <c r="I25" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J25" s="33" t="inlineStr">
+      <c r="J25" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K25" s="33" t="inlineStr">
+      <c r="K25" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L25" s="33" t="inlineStr">
+      <c r="L25" s="36" t="inlineStr">
         <is>
           <t>GEN-CLN-0062</t>
         </is>
       </c>
-      <c r="M25" s="34" t="inlineStr">
+      <c r="M25" s="37" t="inlineStr">
         <is>
           <t>3760015880062</t>
         </is>
       </c>
-      <c r="N25" s="35" t="inlineStr"/>
-      <c r="O25" s="35" t="inlineStr"/>
-      <c r="P25" s="35" t="inlineStr"/>
-      <c r="Q25" s="33" t="inlineStr">
+      <c r="N25" s="38" t="inlineStr"/>
+      <c r="O25" s="38" t="inlineStr"/>
+      <c r="P25" s="38" t="inlineStr"/>
+      <c r="Q25" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R25" s="33" t="inlineStr">
+      <c r="R25" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S25" s="33" t="inlineStr">
+      <c r="S25" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T25" s="33" t="inlineStr">
+      <c r="T25" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U25" s="33" t="inlineStr"/>
-      <c r="V25" s="33" t="inlineStr">
+      <c r="U25" s="36" t="inlineStr"/>
+      <c r="V25" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W25" s="33" t="inlineStr">
+      <c r="W25" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X25" s="33" t="inlineStr">
+      <c r="X25" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9188,7 +9290,7 @@
           <t>https://www.piscinarium.com/2908-thickbox_default/pool-gom-magic-rubber-eraser.jpg</t>
         </is>
       </c>
-      <c r="Z25" s="33" t="inlineStr">
+      <c r="Z25" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9198,7 +9300,7 @@
           <t>Pool'Gom Magic Rubber Eraser</t>
         </is>
       </c>
-      <c r="AB25" s="33" t="inlineStr">
+      <c r="AB25" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9210,10 +9312,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF25" s="33" t="inlineStr"/>
-      <c r="AG25" s="33" t="inlineStr"/>
-      <c r="AH25" s="33" t="inlineStr"/>
-      <c r="AI25" s="33" t="inlineStr"/>
+      <c r="AF25" s="36" t="inlineStr"/>
+      <c r="AG25" s="36" t="inlineStr"/>
+      <c r="AH25" s="36" t="inlineStr"/>
+      <c r="AI25" s="36" t="inlineStr"/>
     </row>
     <row r="26" ht="62" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
@@ -9231,13 +9333,13 @@
           <t>Spa Industries Europe appears to be a brand or supplier name rather than a specific product, so no product details can be confirmed. For accurate information, please check the full product listing.</t>
         </is>
       </c>
-      <c r="D26" s="33" t="inlineStr"/>
-      <c r="E26" s="33" t="inlineStr">
+      <c r="D26" s="36" t="inlineStr"/>
+      <c r="E26" s="36" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F26" s="33" t="inlineStr">
+      <c r="F26" s="36" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -9247,79 +9349,79 @@
           <t>spa-hot-tub, considered-purchase, multi-source-confirmed, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H26" s="33" t="inlineStr">
+      <c r="H26" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I26" s="33" t="inlineStr">
+      <c r="I26" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J26" s="33" t="inlineStr">
+      <c r="J26" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K26" s="33" t="inlineStr">
+      <c r="K26" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L26" s="33" t="inlineStr">
+      <c r="L26" s="36" t="inlineStr">
         <is>
           <t>GEN-SPA-1968</t>
         </is>
       </c>
-      <c r="M26" s="34" t="inlineStr">
+      <c r="M26" s="37" t="inlineStr">
         <is>
           <t>5425021871968</t>
         </is>
       </c>
-      <c r="N26" s="35" t="inlineStr"/>
-      <c r="O26" s="35" t="inlineStr"/>
-      <c r="P26" s="35" t="inlineStr"/>
-      <c r="Q26" s="33" t="inlineStr">
+      <c r="N26" s="38" t="inlineStr"/>
+      <c r="O26" s="38" t="inlineStr"/>
+      <c r="P26" s="38" t="inlineStr"/>
+      <c r="Q26" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R26" s="33" t="inlineStr">
+      <c r="R26" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S26" s="33" t="inlineStr">
+      <c r="S26" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T26" s="33" t="inlineStr">
+      <c r="T26" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U26" s="33" t="inlineStr"/>
-      <c r="V26" s="33" t="inlineStr">
+      <c r="U26" s="36" t="inlineStr"/>
+      <c r="V26" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W26" s="33" t="inlineStr">
+      <c r="W26" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X26" s="33" t="inlineStr">
+      <c r="X26" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y26" s="17" t="inlineStr"/>
-      <c r="Z26" s="33" t="inlineStr"/>
+      <c r="Z26" s="36" t="inlineStr"/>
       <c r="AA26" s="17" t="inlineStr"/>
-      <c r="AB26" s="33" t="inlineStr">
+      <c r="AB26" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9331,10 +9433,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF26" s="33" t="inlineStr"/>
-      <c r="AG26" s="33" t="inlineStr"/>
-      <c r="AH26" s="33" t="inlineStr"/>
-      <c r="AI26" s="33" t="inlineStr"/>
+      <c r="AF26" s="36" t="inlineStr"/>
+      <c r="AG26" s="36" t="inlineStr"/>
+      <c r="AH26" s="36" t="inlineStr"/>
+      <c r="AI26" s="36" t="inlineStr"/>
     </row>
     <row r="27" ht="62" customHeight="1">
       <c r="A27" s="17" t="inlineStr">
@@ -9352,17 +9454,17 @@
           <t>A 1-litre high-concentrate sauna cleaner with eucalyptus fragrance, formulated as a deep-cleaning base cleaner for sauna surfaces. The concentrated formula means a little goes a long way, with a fresh scent to match.</t>
         </is>
       </c>
-      <c r="D27" s="33" t="inlineStr">
+      <c r="D27" s="36" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E27" s="33" t="inlineStr">
+      <c r="E27" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F27" s="33" t="inlineStr">
+      <c r="F27" s="36" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -9372,79 +9474,79 @@
           <t>cleaning, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H27" s="33" t="inlineStr">
+      <c r="H27" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I27" s="33" t="inlineStr">
+      <c r="I27" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J27" s="33" t="inlineStr">
+      <c r="J27" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K27" s="33" t="inlineStr">
+      <c r="K27" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L27" s="33" t="inlineStr">
+      <c r="L27" s="36" t="inlineStr">
         <is>
           <t>HFE-CLN-7004</t>
         </is>
       </c>
-      <c r="M27" s="34" t="inlineStr">
+      <c r="M27" s="37" t="inlineStr">
         <is>
           <t>4250463127004</t>
         </is>
       </c>
-      <c r="N27" s="35" t="inlineStr"/>
-      <c r="O27" s="35" t="inlineStr"/>
-      <c r="P27" s="35" t="inlineStr"/>
-      <c r="Q27" s="33" t="inlineStr">
+      <c r="N27" s="38" t="inlineStr"/>
+      <c r="O27" s="38" t="inlineStr"/>
+      <c r="P27" s="38" t="inlineStr"/>
+      <c r="Q27" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R27" s="33" t="inlineStr">
+      <c r="R27" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S27" s="33" t="inlineStr">
+      <c r="S27" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T27" s="33" t="inlineStr">
+      <c r="T27" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U27" s="33" t="inlineStr"/>
-      <c r="V27" s="33" t="inlineStr">
+      <c r="U27" s="36" t="inlineStr"/>
+      <c r="V27" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W27" s="33" t="inlineStr">
+      <c r="W27" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X27" s="33" t="inlineStr">
+      <c r="X27" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y27" s="17" t="inlineStr"/>
-      <c r="Z27" s="33" t="inlineStr"/>
+      <c r="Z27" s="36" t="inlineStr"/>
       <c r="AA27" s="17" t="inlineStr"/>
-      <c r="AB27" s="33" t="inlineStr">
+      <c r="AB27" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9456,10 +9558,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF27" s="33" t="inlineStr"/>
-      <c r="AG27" s="33" t="inlineStr"/>
-      <c r="AH27" s="33" t="inlineStr"/>
-      <c r="AI27" s="33" t="inlineStr"/>
+      <c r="AF27" s="36" t="inlineStr"/>
+      <c r="AG27" s="36" t="inlineStr"/>
+      <c r="AH27" s="36" t="inlineStr"/>
+      <c r="AI27" s="36" t="inlineStr"/>
     </row>
     <row r="28" ht="76" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
@@ -9477,17 +9579,17 @@
           <t>This HTH spa cleaner removes mineral deposits such as limescale and rust, and cleans and polishes aluminium, chrome, stainless steel, and enamel surfaces with a pleasant pine fragrance. It has a high concentration of active ingredients and is recommended for periodic maintenance cleaning.</t>
         </is>
       </c>
-      <c r="D28" s="33" t="inlineStr">
+      <c r="D28" s="36" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E28" s="33" t="inlineStr">
+      <c r="E28" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F28" s="33" t="inlineStr">
+      <c r="F28" s="36" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -9497,71 +9599,71 @@
           <t>spa-hot-tub, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H28" s="33" t="inlineStr">
+      <c r="H28" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I28" s="33" t="inlineStr">
+      <c r="I28" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J28" s="33" t="inlineStr">
+      <c r="J28" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K28" s="33" t="inlineStr">
+      <c r="K28" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L28" s="33" t="inlineStr">
+      <c r="L28" s="36" t="inlineStr">
         <is>
           <t>HTH-CLN-0178</t>
         </is>
       </c>
-      <c r="M28" s="34" t="inlineStr">
+      <c r="M28" s="37" t="inlineStr">
         <is>
           <t>3521686010178</t>
         </is>
       </c>
-      <c r="N28" s="35" t="inlineStr"/>
-      <c r="O28" s="35" t="inlineStr"/>
-      <c r="P28" s="35" t="inlineStr"/>
-      <c r="Q28" s="33" t="inlineStr">
+      <c r="N28" s="38" t="inlineStr"/>
+      <c r="O28" s="38" t="inlineStr"/>
+      <c r="P28" s="38" t="inlineStr"/>
+      <c r="Q28" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R28" s="33" t="inlineStr">
+      <c r="R28" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S28" s="33" t="inlineStr">
+      <c r="S28" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T28" s="33" t="inlineStr">
+      <c r="T28" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U28" s="33" t="inlineStr"/>
-      <c r="V28" s="33" t="inlineStr">
+      <c r="U28" s="36" t="inlineStr"/>
+      <c r="V28" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W28" s="33" t="inlineStr">
+      <c r="W28" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X28" s="33" t="inlineStr">
+      <c r="X28" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9571,7 +9673,7 @@
           <t>https://www.cdiscount.com/pdt2/0/5/1/1/700x700/auc2009356289051/rw/hth-spa-nettoyant-spa-3521686010178.jpg</t>
         </is>
       </c>
-      <c r="Z28" s="33" t="inlineStr">
+      <c r="Z28" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9581,7 +9683,7 @@
           <t>HTH Spa Spa Cleaner</t>
         </is>
       </c>
-      <c r="AB28" s="33" t="inlineStr">
+      <c r="AB28" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9593,10 +9695,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF28" s="33" t="inlineStr"/>
-      <c r="AG28" s="33" t="inlineStr"/>
-      <c r="AH28" s="33" t="inlineStr"/>
-      <c r="AI28" s="33" t="inlineStr"/>
+      <c r="AF28" s="36" t="inlineStr"/>
+      <c r="AG28" s="36" t="inlineStr"/>
+      <c r="AH28" s="36" t="inlineStr"/>
+      <c r="AI28" s="36" t="inlineStr"/>
     </row>
     <row r="29" ht="62" customHeight="1">
       <c r="A29" s="17" t="inlineStr">
@@ -9614,13 +9716,13 @@
           <t>A 25 kg sack of pure boiling salt (minimum 99.6% NaCl) without an anti-caking agent, meeting EN 973 Type A standard and suitable for use in pool salt electrolysis systems. Not intended for human consumption or animal feed.</t>
         </is>
       </c>
-      <c r="D29" s="33" t="inlineStr"/>
-      <c r="E29" s="33" t="inlineStr">
+      <c r="D29" s="36" t="inlineStr"/>
+      <c r="E29" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F29" s="33" t="inlineStr">
+      <c r="F29" s="36" t="inlineStr">
         <is>
           <t>Pool salt</t>
         </is>
@@ -9630,75 +9732,75 @@
           <t>pool, salt, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H29" s="33" t="inlineStr">
+      <c r="H29" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I29" s="33" t="inlineStr">
+      <c r="I29" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J29" s="33" t="inlineStr">
+      <c r="J29" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K29" s="33" t="inlineStr">
+      <c r="K29" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L29" s="33" t="inlineStr">
+      <c r="L29" s="36" t="inlineStr">
         <is>
           <t>GEN-SLT-6110</t>
         </is>
       </c>
-      <c r="M29" s="34" t="inlineStr">
+      <c r="M29" s="37" t="inlineStr">
         <is>
           <t>9001880976110</t>
         </is>
       </c>
-      <c r="N29" s="35" t="inlineStr"/>
-      <c r="O29" s="35" t="inlineStr"/>
-      <c r="P29" s="35" t="inlineStr"/>
-      <c r="Q29" s="33" t="inlineStr">
+      <c r="N29" s="38" t="inlineStr"/>
+      <c r="O29" s="38" t="inlineStr"/>
+      <c r="P29" s="38" t="inlineStr"/>
+      <c r="Q29" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R29" s="33" t="inlineStr">
+      <c r="R29" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S29" s="33" t="inlineStr">
+      <c r="S29" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T29" s="33" t="inlineStr">
+      <c r="T29" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U29" s="33" t="inlineStr">
+      <c r="U29" s="36" t="inlineStr">
         <is>
           <t>25000</t>
         </is>
       </c>
-      <c r="V29" s="33" t="inlineStr">
+      <c r="V29" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W29" s="33" t="inlineStr">
+      <c r="W29" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X29" s="33" t="inlineStr">
+      <c r="X29" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9708,7 +9810,7 @@
           <t>http://altruan.com/cdn/shop/files/SalinenPoolSalz25kgSack.png?v=1778597596</t>
         </is>
       </c>
-      <c r="Z29" s="33" t="inlineStr">
+      <c r="Z29" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9718,7 +9820,7 @@
           <t>Saline pool salt pure boiling salt without separating agent | Sack (25 kg)</t>
         </is>
       </c>
-      <c r="AB29" s="33" t="inlineStr">
+      <c r="AB29" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9730,14 +9832,14 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF29" s="33" t="inlineStr">
+      <c r="AF29" s="36" t="inlineStr">
         <is>
           <t>Composition: Siedesalz (min. 99.6% NaCl) 100%; Separant/sodium ferrocyanide 4.0–12.0 mg/kg | Grain: &gt;0.63 mm approx. 20%, 0.2–0.63 mm approx. 75%, &lt;0.2 mm approx. 5% | Moisture: &lt;0.08%</t>
         </is>
       </c>
-      <c r="AG29" s="33" t="inlineStr"/>
-      <c r="AH29" s="33" t="inlineStr"/>
-      <c r="AI29" s="33" t="inlineStr"/>
+      <c r="AG29" s="36" t="inlineStr"/>
+      <c r="AH29" s="36" t="inlineStr"/>
+      <c r="AI29" s="36" t="inlineStr"/>
     </row>
     <row r="30" ht="76" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
@@ -9755,17 +9857,17 @@
           <t>A cordless robotic pool cleaner that scrubs both floors and walls automatically, using WavePath navigation to map and cover the pool efficiently. Built-in high-performance filtration and smart control make it a hands-off solution for keeping pool water clear.</t>
         </is>
       </c>
-      <c r="D30" s="33" t="inlineStr">
+      <c r="D30" s="36" t="inlineStr">
         <is>
           <t>Aiper</t>
         </is>
       </c>
-      <c r="E30" s="33" t="inlineStr">
+      <c r="E30" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F30" s="33" t="inlineStr">
+      <c r="F30" s="36" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9775,71 +9877,71 @@
           <t>pool, cleaning, robot-cleaner, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H30" s="33" t="inlineStr">
+      <c r="H30" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I30" s="33" t="inlineStr">
+      <c r="I30" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J30" s="33" t="inlineStr">
+      <c r="J30" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K30" s="33" t="inlineStr">
+      <c r="K30" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L30" s="33" t="inlineStr">
+      <c r="L30" s="36" t="inlineStr">
         <is>
           <t>AIP-ROB-4940</t>
         </is>
       </c>
-      <c r="M30" s="34" t="inlineStr">
+      <c r="M30" s="37" t="inlineStr">
         <is>
           <t>6977676344940</t>
         </is>
       </c>
-      <c r="N30" s="35" t="inlineStr"/>
-      <c r="O30" s="35" t="inlineStr"/>
-      <c r="P30" s="35" t="inlineStr"/>
-      <c r="Q30" s="33" t="inlineStr">
+      <c r="N30" s="38" t="inlineStr"/>
+      <c r="O30" s="38" t="inlineStr"/>
+      <c r="P30" s="38" t="inlineStr"/>
+      <c r="Q30" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R30" s="33" t="inlineStr">
+      <c r="R30" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S30" s="33" t="inlineStr">
+      <c r="S30" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T30" s="33" t="inlineStr">
+      <c r="T30" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U30" s="33" t="inlineStr"/>
-      <c r="V30" s="33" t="inlineStr">
+      <c r="U30" s="36" t="inlineStr"/>
+      <c r="V30" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W30" s="33" t="inlineStr">
+      <c r="W30" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X30" s="33" t="inlineStr">
+      <c r="X30" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9849,7 +9951,7 @@
           <t>https://images.barcodelookup.com/176692/1766920801-1.jpg</t>
         </is>
       </c>
-      <c r="Z30" s="33" t="inlineStr">
+      <c r="Z30" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9859,7 +9961,7 @@
           <t>AIPER Scuba S3 Cordless Pool Robot, Automatic Floor and Wall Cleaning, WavePath™ Navigation, High-Performance Filtration…</t>
         </is>
       </c>
-      <c r="AB30" s="33" t="inlineStr">
+      <c r="AB30" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9871,10 +9973,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF30" s="33" t="inlineStr"/>
-      <c r="AG30" s="33" t="inlineStr"/>
-      <c r="AH30" s="33" t="inlineStr"/>
-      <c r="AI30" s="33" t="inlineStr"/>
+      <c r="AF30" s="36" t="inlineStr"/>
+      <c r="AG30" s="36" t="inlineStr"/>
+      <c r="AH30" s="36" t="inlineStr"/>
+      <c r="AI30" s="36" t="inlineStr"/>
     </row>
     <row r="31" ht="62" customHeight="1">
       <c r="A31" s="17" t="inlineStr">
@@ -9892,13 +9994,13 @@
           <t>The Scuba L1 EU is a pool cleaning device, though no further specific details about its features, dimensions, or mechanism are available from the product name alone. Buyers should refer to the full product listing for specifications.</t>
         </is>
       </c>
-      <c r="D31" s="33" t="inlineStr"/>
-      <c r="E31" s="33" t="inlineStr">
+      <c r="D31" s="36" t="inlineStr"/>
+      <c r="E31" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F31" s="33" t="inlineStr">
+      <c r="F31" s="36" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9908,71 +10010,71 @@
           <t>robot-cleaner, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H31" s="33" t="inlineStr">
+      <c r="H31" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I31" s="33" t="inlineStr">
+      <c r="I31" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J31" s="33" t="inlineStr">
+      <c r="J31" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K31" s="33" t="inlineStr">
+      <c r="K31" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L31" s="33" t="inlineStr">
+      <c r="L31" s="36" t="inlineStr">
         <is>
           <t>GEN-ROB-5137</t>
         </is>
       </c>
-      <c r="M31" s="34" t="inlineStr">
+      <c r="M31" s="37" t="inlineStr">
         <is>
           <t>6975140315137</t>
         </is>
       </c>
-      <c r="N31" s="35" t="inlineStr"/>
-      <c r="O31" s="35" t="inlineStr"/>
-      <c r="P31" s="35" t="inlineStr"/>
-      <c r="Q31" s="33" t="inlineStr">
+      <c r="N31" s="38" t="inlineStr"/>
+      <c r="O31" s="38" t="inlineStr"/>
+      <c r="P31" s="38" t="inlineStr"/>
+      <c r="Q31" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R31" s="33" t="inlineStr">
+      <c r="R31" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S31" s="33" t="inlineStr">
+      <c r="S31" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T31" s="33" t="inlineStr">
+      <c r="T31" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U31" s="33" t="inlineStr"/>
-      <c r="V31" s="33" t="inlineStr">
+      <c r="U31" s="36" t="inlineStr"/>
+      <c r="V31" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W31" s="33" t="inlineStr">
+      <c r="W31" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X31" s="33" t="inlineStr">
+      <c r="X31" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9982,7 +10084,7 @@
           <t>https://images.barcodelookup.com/124722/1247228758-1.jpg</t>
         </is>
       </c>
-      <c r="Z31" s="33" t="inlineStr">
+      <c r="Z31" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9992,7 +10094,7 @@
           <t>Scuba L1 - EU</t>
         </is>
       </c>
-      <c r="AB31" s="33" t="inlineStr">
+      <c r="AB31" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10004,10 +10106,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF31" s="33" t="inlineStr"/>
-      <c r="AG31" s="33" t="inlineStr"/>
-      <c r="AH31" s="33" t="inlineStr"/>
-      <c r="AI31" s="33" t="inlineStr"/>
+      <c r="AF31" s="36" t="inlineStr"/>
+      <c r="AG31" s="36" t="inlineStr"/>
+      <c r="AH31" s="36" t="inlineStr"/>
+      <c r="AI31" s="36" t="inlineStr"/>
     </row>
     <row r="32" ht="48" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
@@ -10025,13 +10127,13 @@
           <t>The Gre Pools RBR120 is a 51W robotic pool cleaner designed for automatic pool floor cleaning. A reliable workhorse that takes the scrubbing off your hands.</t>
         </is>
       </c>
-      <c r="D32" s="33" t="inlineStr"/>
-      <c r="E32" s="33" t="inlineStr">
+      <c r="D32" s="36" t="inlineStr"/>
+      <c r="E32" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F32" s="33" t="inlineStr">
+      <c r="F32" s="36" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -10041,71 +10143,71 @@
           <t>robot-cleaner, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H32" s="33" t="inlineStr">
+      <c r="H32" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I32" s="33" t="inlineStr">
+      <c r="I32" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J32" s="33" t="inlineStr">
+      <c r="J32" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K32" s="33" t="inlineStr">
+      <c r="K32" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L32" s="33" t="inlineStr">
+      <c r="L32" s="36" t="inlineStr">
         <is>
           <t>GEN-ROB-8500</t>
         </is>
       </c>
-      <c r="M32" s="34" t="inlineStr">
+      <c r="M32" s="37" t="inlineStr">
         <is>
           <t>8412081308500</t>
         </is>
       </c>
-      <c r="N32" s="35" t="inlineStr"/>
-      <c r="O32" s="35" t="inlineStr"/>
-      <c r="P32" s="35" t="inlineStr"/>
-      <c r="Q32" s="33" t="inlineStr">
+      <c r="N32" s="38" t="inlineStr"/>
+      <c r="O32" s="38" t="inlineStr"/>
+      <c r="P32" s="38" t="inlineStr"/>
+      <c r="Q32" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R32" s="33" t="inlineStr">
+      <c r="R32" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S32" s="33" t="inlineStr">
+      <c r="S32" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T32" s="33" t="inlineStr">
+      <c r="T32" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U32" s="33" t="inlineStr"/>
-      <c r="V32" s="33" t="inlineStr">
+      <c r="U32" s="36" t="inlineStr"/>
+      <c r="V32" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W32" s="33" t="inlineStr">
+      <c r="W32" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X32" s="33" t="inlineStr">
+      <c r="X32" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10115,7 +10217,7 @@
           <t>https://images.barcodelookup.com/124726/1247268298-1.jpg</t>
         </is>
       </c>
-      <c r="Z32" s="33" t="inlineStr">
+      <c r="Z32" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10125,7 +10227,7 @@
           <t>Battery Powered Robot WET RUNNER XPERT</t>
         </is>
       </c>
-      <c r="AB32" s="33" t="inlineStr">
+      <c r="AB32" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10137,10 +10239,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF32" s="33" t="inlineStr"/>
-      <c r="AG32" s="33" t="inlineStr"/>
-      <c r="AH32" s="33" t="inlineStr"/>
-      <c r="AI32" s="33" t="inlineStr"/>
+      <c r="AF32" s="36" t="inlineStr"/>
+      <c r="AG32" s="36" t="inlineStr"/>
+      <c r="AH32" s="36" t="inlineStr"/>
+      <c r="AI32" s="36" t="inlineStr"/>
     </row>
     <row r="33" ht="90" customHeight="1">
       <c r="A33" s="17" t="inlineStr">
@@ -10158,13 +10260,13 @@
           <t>A twin-size inflatable airbed measuring 99 x 191 x 25 cm, built with Fiber-Tech internal construction using polyester fibres for comfort, vinyl sides and base, and a water-resistant flocked top surface with an anti-deflation valve. It supports a maximum weight of 136 kg and packs down compactly when deflated.</t>
         </is>
       </c>
-      <c r="D33" s="33" t="inlineStr"/>
-      <c r="E33" s="33" t="inlineStr">
+      <c r="D33" s="36" t="inlineStr"/>
+      <c r="E33" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-11</t>
         </is>
       </c>
-      <c r="F33" s="33" t="inlineStr">
+      <c r="F33" s="36" t="inlineStr">
         <is>
           <t>Airbed / lounger</t>
         </is>
@@ -10174,71 +10276,71 @@
           <t>considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H33" s="33" t="inlineStr">
+      <c r="H33" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I33" s="33" t="inlineStr">
+      <c r="I33" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J33" s="33" t="inlineStr">
+      <c r="J33" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K33" s="33" t="inlineStr">
+      <c r="K33" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L33" s="33" t="inlineStr">
+      <c r="L33" s="36" t="inlineStr">
         <is>
           <t>GEN-BED-2443</t>
         </is>
       </c>
-      <c r="M33" s="34" t="inlineStr">
+      <c r="M33" s="37" t="inlineStr">
         <is>
           <t>6941057412443</t>
         </is>
       </c>
-      <c r="N33" s="35" t="inlineStr"/>
-      <c r="O33" s="35" t="inlineStr"/>
-      <c r="P33" s="35" t="inlineStr"/>
-      <c r="Q33" s="33" t="inlineStr">
+      <c r="N33" s="38" t="inlineStr"/>
+      <c r="O33" s="38" t="inlineStr"/>
+      <c r="P33" s="38" t="inlineStr"/>
+      <c r="Q33" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R33" s="33" t="inlineStr">
+      <c r="R33" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S33" s="33" t="inlineStr">
+      <c r="S33" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T33" s="33" t="inlineStr">
+      <c r="T33" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U33" s="33" t="inlineStr"/>
-      <c r="V33" s="33" t="inlineStr">
+      <c r="U33" s="36" t="inlineStr"/>
+      <c r="V33" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W33" s="33" t="inlineStr">
+      <c r="W33" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X33" s="33" t="inlineStr">
+      <c r="X33" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10248,7 +10350,7 @@
           <t>https://www.ecoperation.com/media/catalog/product/cache/b76cf1d99a7811daa83ba86e6ad91c89/6/4/64757.jpg</t>
         </is>
       </c>
-      <c r="Z33" s="33" t="inlineStr">
+      <c r="Z33" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10258,7 +10360,7 @@
           <t>Twin Dura-Beam Classic Downy Airbed 99x191x25 cm</t>
         </is>
       </c>
-      <c r="AB33" s="33" t="inlineStr">
+      <c r="AB33" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10270,18 +10372,18 @@
           <t>Inflatable Beds and Mattresses</t>
         </is>
       </c>
-      <c r="AF33" s="33" t="inlineStr"/>
-      <c r="AG33" s="33" t="inlineStr">
+      <c r="AF33" s="36" t="inlineStr"/>
+      <c r="AG33" s="36" t="inlineStr">
         <is>
           <t>99.0cm</t>
         </is>
       </c>
-      <c r="AH33" s="33" t="inlineStr">
+      <c r="AH33" s="36" t="inlineStr">
         <is>
           <t>191.0cm</t>
         </is>
       </c>
-      <c r="AI33" s="33" t="inlineStr">
+      <c r="AI33" s="36" t="inlineStr">
         <is>
           <t>25.0cm</t>
         </is>
@@ -10303,17 +10405,17 @@
           <t>A plastic chlorine dosing lock from Steinbach, designed exclusively for use with long-term chlorine tablets, with a 1.5-inch connection fitting. It measures 37 cm in length, 22.5 cm in width, and 15 cm in height, making it a sturdy inline dosing unit for pool water treatment systems.</t>
         </is>
       </c>
-      <c r="D34" s="33" t="inlineStr">
+      <c r="D34" s="36" t="inlineStr">
         <is>
           <t>Steinbach</t>
         </is>
       </c>
-      <c r="E34" s="33" t="inlineStr">
+      <c r="E34" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F34" s="33" t="inlineStr">
+      <c r="F34" s="36" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -10323,71 +10425,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H34" s="33" t="inlineStr">
+      <c r="H34" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I34" s="33" t="inlineStr">
+      <c r="I34" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J34" s="33" t="inlineStr">
+      <c r="J34" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K34" s="33" t="inlineStr">
+      <c r="K34" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L34" s="33" t="inlineStr">
+      <c r="L34" s="36" t="inlineStr">
         <is>
           <t>STE-CHM-0307</t>
         </is>
       </c>
-      <c r="M34" s="34" t="inlineStr">
+      <c r="M34" s="37" t="inlineStr">
         <is>
           <t>9008748790307</t>
         </is>
       </c>
-      <c r="N34" s="35" t="inlineStr"/>
-      <c r="O34" s="35" t="inlineStr"/>
-      <c r="P34" s="35" t="inlineStr"/>
-      <c r="Q34" s="33" t="inlineStr">
+      <c r="N34" s="38" t="inlineStr"/>
+      <c r="O34" s="38" t="inlineStr"/>
+      <c r="P34" s="38" t="inlineStr"/>
+      <c r="Q34" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R34" s="33" t="inlineStr">
+      <c r="R34" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S34" s="33" t="inlineStr">
+      <c r="S34" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T34" s="33" t="inlineStr">
+      <c r="T34" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U34" s="33" t="inlineStr"/>
-      <c r="V34" s="33" t="inlineStr">
+      <c r="U34" s="36" t="inlineStr"/>
+      <c r="V34" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W34" s="33" t="inlineStr">
+      <c r="W34" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X34" s="33" t="inlineStr">
+      <c r="X34" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10397,7 +10499,7 @@
           <t>https://i.ebayimg.com/images/g/CrUAAeSwkOdqeaRR/s-l400.jpg</t>
         </is>
       </c>
-      <c r="Z34" s="33" t="inlineStr">
+      <c r="Z34" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10407,7 +10509,7 @@
           <t>STEINBACH Chlorine dosing lock, only for chlorine long-term tablets, plastic, connection 1.5 inch in</t>
         </is>
       </c>
-      <c r="AB34" s="33" t="inlineStr">
+      <c r="AB34" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10419,18 +10521,18 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF34" s="33" t="inlineStr"/>
-      <c r="AG34" s="33" t="inlineStr">
+      <c r="AF34" s="36" t="inlineStr"/>
+      <c r="AG34" s="36" t="inlineStr">
         <is>
           <t>22.5cm</t>
         </is>
       </c>
-      <c r="AH34" s="33" t="inlineStr">
+      <c r="AH34" s="36" t="inlineStr">
         <is>
           <t>37.0cm</t>
         </is>
       </c>
-      <c r="AI34" s="33" t="inlineStr">
+      <c r="AI34" s="36" t="inlineStr">
         <is>
           <t>15.0cm</t>
         </is>
@@ -10452,17 +10554,17 @@
           <t>A filter cleaning system for hot tub and pool cartridge filters, designed to remove debris and residue efficiently while keeping water usage to a minimum. A practical tool for extending the life of your filter without wasting a drop more than necessary.</t>
         </is>
       </c>
-      <c r="D35" s="33" t="inlineStr">
+      <c r="D35" s="36" t="inlineStr">
         <is>
           <t>Estelle</t>
         </is>
       </c>
-      <c r="E35" s="33" t="inlineStr">
+      <c r="E35" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F35" s="33" t="inlineStr">
+      <c r="F35" s="36" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -10472,71 +10574,71 @@
           <t>filters, spa-hot-tub, cleaning, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H35" s="33" t="inlineStr">
+      <c r="H35" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I35" s="33" t="inlineStr">
+      <c r="I35" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J35" s="33" t="inlineStr">
+      <c r="J35" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K35" s="33" t="inlineStr">
+      <c r="K35" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L35" s="33" t="inlineStr">
+      <c r="L35" s="36" t="inlineStr">
         <is>
           <t>EST-FIL-3669</t>
         </is>
       </c>
-      <c r="M35" s="34" t="inlineStr">
+      <c r="M35" s="37" t="inlineStr">
         <is>
           <t>8711842033669</t>
         </is>
       </c>
-      <c r="N35" s="35" t="inlineStr"/>
-      <c r="O35" s="35" t="inlineStr"/>
-      <c r="P35" s="35" t="inlineStr"/>
-      <c r="Q35" s="33" t="inlineStr">
+      <c r="N35" s="38" t="inlineStr"/>
+      <c r="O35" s="38" t="inlineStr"/>
+      <c r="P35" s="38" t="inlineStr"/>
+      <c r="Q35" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R35" s="33" t="inlineStr">
+      <c r="R35" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S35" s="33" t="inlineStr">
+      <c r="S35" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T35" s="33" t="inlineStr">
+      <c r="T35" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U35" s="33" t="inlineStr"/>
-      <c r="V35" s="33" t="inlineStr">
+      <c r="U35" s="36" t="inlineStr"/>
+      <c r="V35" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W35" s="33" t="inlineStr">
+      <c r="W35" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X35" s="33" t="inlineStr">
+      <c r="X35" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10546,7 +10648,7 @@
           <t>https://i.ebayimg.com/images/g/0e0AAOSweaplqO77/s-l400.jpg</t>
         </is>
       </c>
-      <c r="Z35" s="33" t="inlineStr">
+      <c r="Z35" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10556,7 +10658,7 @@
           <t>Estelle Filter Cleaning System Hot tubs Cartridge Filters Cleaner Spa Amazing!</t>
         </is>
       </c>
-      <c r="AB35" s="33" t="inlineStr">
+      <c r="AB35" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10568,10 +10670,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF35" s="33" t="inlineStr"/>
-      <c r="AG35" s="33" t="inlineStr"/>
-      <c r="AH35" s="33" t="inlineStr"/>
-      <c r="AI35" s="33" t="inlineStr"/>
+      <c r="AF35" s="36" t="inlineStr"/>
+      <c r="AG35" s="36" t="inlineStr"/>
+      <c r="AH35" s="36" t="inlineStr"/>
+      <c r="AI35" s="36" t="inlineStr"/>
     </row>
     <row r="36" ht="62" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
@@ -10589,17 +10691,17 @@
           <t>A compact handy scrub brush for pool maintenance, measuring 15 x 9 x 8 cm, suited to scrubbing pool surfaces and hard-to-reach areas. Small enough to manoeuvre easily, and ready to tackle whatever the waterline throws at it.</t>
         </is>
       </c>
-      <c r="D36" s="33" t="inlineStr">
+      <c r="D36" s="36" t="inlineStr">
         <is>
           <t>WAYS</t>
         </is>
       </c>
-      <c r="E36" s="33" t="inlineStr">
+      <c r="E36" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F36" s="33" t="inlineStr">
+      <c r="F36" s="36" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -10609,79 +10711,79 @@
           <t>pool, cleaning, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H36" s="33" t="inlineStr">
+      <c r="H36" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I36" s="33" t="inlineStr">
+      <c r="I36" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J36" s="33" t="inlineStr">
+      <c r="J36" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K36" s="33" t="inlineStr">
+      <c r="K36" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L36" s="33" t="inlineStr">
+      <c r="L36" s="36" t="inlineStr">
         <is>
           <t>WAY-CLN-2219</t>
         </is>
       </c>
-      <c r="M36" s="34" t="inlineStr">
+      <c r="M36" s="37" t="inlineStr">
         <is>
           <t>8720299182219</t>
         </is>
       </c>
-      <c r="N36" s="35" t="inlineStr"/>
-      <c r="O36" s="35" t="inlineStr"/>
-      <c r="P36" s="35" t="inlineStr"/>
-      <c r="Q36" s="33" t="inlineStr">
+      <c r="N36" s="38" t="inlineStr"/>
+      <c r="O36" s="38" t="inlineStr"/>
+      <c r="P36" s="38" t="inlineStr"/>
+      <c r="Q36" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R36" s="33" t="inlineStr">
+      <c r="R36" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S36" s="33" t="inlineStr">
+      <c r="S36" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T36" s="33" t="inlineStr">
+      <c r="T36" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U36" s="33" t="inlineStr"/>
-      <c r="V36" s="33" t="inlineStr">
+      <c r="U36" s="36" t="inlineStr"/>
+      <c r="V36" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W36" s="33" t="inlineStr">
+      <c r="W36" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X36" s="33" t="inlineStr">
+      <c r="X36" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y36" s="17" t="inlineStr"/>
-      <c r="Z36" s="33" t="inlineStr"/>
+      <c r="Z36" s="36" t="inlineStr"/>
       <c r="AA36" s="17" t="inlineStr"/>
-      <c r="AB36" s="33" t="inlineStr">
+      <c r="AB36" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10693,18 +10795,18 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF36" s="33" t="inlineStr"/>
-      <c r="AG36" s="33" t="inlineStr">
+      <c r="AF36" s="36" t="inlineStr"/>
+      <c r="AG36" s="36" t="inlineStr">
         <is>
           <t>8.0cm</t>
         </is>
       </c>
-      <c r="AH36" s="33" t="inlineStr">
+      <c r="AH36" s="36" t="inlineStr">
         <is>
           <t>15.0cm</t>
         </is>
       </c>
-      <c r="AI36" s="33" t="inlineStr">
+      <c r="AI36" s="36" t="inlineStr">
         <is>
           <t>9.0cm</t>
         </is>
@@ -10726,17 +10828,17 @@
           <t>An inflatable PVC headrest pillow for the Intex inflatable spa (model 28506), measuring 24 x 19 x 6 cm and weighing 0.22 kg, designed to support the head and neck comfortably during use. It attaches to the spa rim and can also be filled with water for added stability.</t>
         </is>
       </c>
-      <c r="D37" s="33" t="inlineStr">
+      <c r="D37" s="36" t="inlineStr">
         <is>
           <t>Intex</t>
         </is>
       </c>
-      <c r="E37" s="33" t="inlineStr">
+      <c r="E37" s="36" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F37" s="33" t="inlineStr">
+      <c r="F37" s="36" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -10746,75 +10848,75 @@
           <t>spa-hot-tub, accessories, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H37" s="33" t="inlineStr">
+      <c r="H37" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I37" s="33" t="inlineStr">
+      <c r="I37" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J37" s="33" t="inlineStr">
+      <c r="J37" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K37" s="33" t="inlineStr">
+      <c r="K37" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L37" s="33" t="inlineStr">
+      <c r="L37" s="36" t="inlineStr">
         <is>
           <t>INT-SPA-6075</t>
         </is>
       </c>
-      <c r="M37" s="34" t="inlineStr">
+      <c r="M37" s="37" t="inlineStr">
         <is>
           <t>6941057426075</t>
         </is>
       </c>
-      <c r="N37" s="35" t="inlineStr"/>
-      <c r="O37" s="35" t="inlineStr"/>
-      <c r="P37" s="35" t="inlineStr"/>
-      <c r="Q37" s="33" t="inlineStr">
+      <c r="N37" s="38" t="inlineStr"/>
+      <c r="O37" s="38" t="inlineStr"/>
+      <c r="P37" s="38" t="inlineStr"/>
+      <c r="Q37" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R37" s="33" t="inlineStr">
+      <c r="R37" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S37" s="33" t="inlineStr">
+      <c r="S37" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T37" s="33" t="inlineStr">
+      <c r="T37" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U37" s="33" t="inlineStr">
+      <c r="U37" s="36" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="V37" s="33" t="inlineStr">
+      <c r="V37" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W37" s="33" t="inlineStr">
+      <c r="W37" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X37" s="33" t="inlineStr">
+      <c r="X37" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10824,7 +10926,7 @@
           <t>https://content2.rozetka.com.ua/goods/images/big/570260745.jpg</t>
         </is>
       </c>
-      <c r="Z37" s="33" t="inlineStr">
+      <c r="Z37" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10834,7 +10936,7 @@
           <t>Headrest Pillow for INTEX Inflatable SPA 28506</t>
         </is>
       </c>
-      <c r="AB37" s="33" t="inlineStr">
+      <c r="AB37" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10846,18 +10948,18 @@
           <t>Intex Pure Spa Accessories</t>
         </is>
       </c>
-      <c r="AF37" s="33" t="inlineStr"/>
-      <c r="AG37" s="33" t="inlineStr">
+      <c r="AF37" s="36" t="inlineStr"/>
+      <c r="AG37" s="36" t="inlineStr">
         <is>
           <t>19.0cm</t>
         </is>
       </c>
-      <c r="AH37" s="33" t="inlineStr">
+      <c r="AH37" s="36" t="inlineStr">
         <is>
           <t>24.0cm</t>
         </is>
       </c>
-      <c r="AI37" s="33" t="inlineStr">
+      <c r="AI37" s="36" t="inlineStr">
         <is>
           <t>6.0cm</t>
         </is>
@@ -10879,13 +10981,13 @@
           <t>A DPD Pool test kit for active-oxygen pools, containing 20 DPD No. 4 reagent tablets for measuring active oxygen levels and 20 phenol red tablets for measuring pH. Results are read immediately after the tablet dissolves, with an ideal active oxygen range of 3.0 to 8.0 mg/l and a target pH of 7.0 to 7.4.</t>
         </is>
       </c>
-      <c r="D38" s="33" t="inlineStr"/>
-      <c r="E38" s="33" t="inlineStr">
+      <c r="D38" s="36" t="inlineStr"/>
+      <c r="E38" s="36" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F38" s="33" t="inlineStr">
+      <c r="F38" s="36" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -10895,71 +10997,71 @@
           <t>water-treatment, test-measure, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H38" s="33" t="inlineStr">
+      <c r="H38" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I38" s="33" t="inlineStr">
+      <c r="I38" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J38" s="33" t="inlineStr">
+      <c r="J38" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K38" s="33" t="inlineStr">
+      <c r="K38" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L38" s="33" t="inlineStr">
+      <c r="L38" s="36" t="inlineStr">
         <is>
           <t>GEN-TST-1347</t>
         </is>
       </c>
-      <c r="M38" s="34" t="inlineStr">
+      <c r="M38" s="37" t="inlineStr">
         <is>
           <t>4250463121347</t>
         </is>
       </c>
-      <c r="N38" s="35" t="inlineStr"/>
-      <c r="O38" s="35" t="inlineStr"/>
-      <c r="P38" s="35" t="inlineStr"/>
-      <c r="Q38" s="33" t="inlineStr">
+      <c r="N38" s="38" t="inlineStr"/>
+      <c r="O38" s="38" t="inlineStr"/>
+      <c r="P38" s="38" t="inlineStr"/>
+      <c r="Q38" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R38" s="33" t="inlineStr">
+      <c r="R38" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S38" s="33" t="inlineStr">
+      <c r="S38" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T38" s="33" t="inlineStr">
+      <c r="T38" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U38" s="33" t="inlineStr"/>
-      <c r="V38" s="33" t="inlineStr">
+      <c r="U38" s="36" t="inlineStr"/>
+      <c r="V38" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W38" s="33" t="inlineStr">
+      <c r="W38" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X38" s="33" t="inlineStr">
+      <c r="X38" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10969,7 +11071,7 @@
           <t>https://media.carrefour.fr/medias/8f94161f683b4e589024a5b5ebaa6873/p_200x200/cad3db6a00ef414a804b9226119bae96_image.jpg</t>
         </is>
       </c>
-      <c r="Z38" s="33" t="inlineStr">
+      <c r="Z38" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10979,7 +11081,7 @@
           <t>Active Oxygen Test Kit x1</t>
         </is>
       </c>
-      <c r="AB38" s="33" t="inlineStr">
+      <c r="AB38" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10991,10 +11093,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF38" s="33" t="inlineStr"/>
-      <c r="AG38" s="33" t="inlineStr"/>
-      <c r="AH38" s="33" t="inlineStr"/>
-      <c r="AI38" s="33" t="inlineStr"/>
+      <c r="AF38" s="36" t="inlineStr"/>
+      <c r="AG38" s="36" t="inlineStr"/>
+      <c r="AH38" s="36" t="inlineStr"/>
+      <c r="AI38" s="36" t="inlineStr"/>
     </row>
     <row r="39" ht="62" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
@@ -11012,17 +11114,17 @@
           <t>A pack of 2 replacement filter cartridges compatible with Intex Type H pool and spa pumps, made by Darlly. Straightforward to swap out, they keep the water moving clean without any complications.</t>
         </is>
       </c>
-      <c r="D39" s="33" t="inlineStr">
+      <c r="D39" s="36" t="inlineStr">
         <is>
           <t>Intex</t>
         </is>
       </c>
-      <c r="E39" s="33" t="inlineStr">
+      <c r="E39" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F39" s="33" t="inlineStr">
+      <c r="F39" s="36" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -11032,71 +11134,71 @@
           <t>filters, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H39" s="33" t="inlineStr">
+      <c r="H39" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I39" s="33" t="inlineStr">
+      <c r="I39" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J39" s="33" t="inlineStr">
+      <c r="J39" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K39" s="33" t="inlineStr">
+      <c r="K39" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L39" s="33" t="inlineStr">
+      <c r="L39" s="36" t="inlineStr">
         <is>
           <t>INT-FIL-2895</t>
         </is>
       </c>
-      <c r="M39" s="34" t="inlineStr">
+      <c r="M39" s="37" t="inlineStr">
         <is>
           <t>700175992895</t>
         </is>
       </c>
-      <c r="N39" s="35" t="inlineStr"/>
-      <c r="O39" s="35" t="inlineStr"/>
-      <c r="P39" s="35" t="inlineStr"/>
-      <c r="Q39" s="33" t="inlineStr">
+      <c r="N39" s="38" t="inlineStr"/>
+      <c r="O39" s="38" t="inlineStr"/>
+      <c r="P39" s="38" t="inlineStr"/>
+      <c r="Q39" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R39" s="33" t="inlineStr">
+      <c r="R39" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S39" s="33" t="inlineStr">
+      <c r="S39" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T39" s="33" t="inlineStr">
+      <c r="T39" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U39" s="33" t="inlineStr"/>
-      <c r="V39" s="33" t="inlineStr">
+      <c r="U39" s="36" t="inlineStr"/>
+      <c r="V39" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W39" s="33" t="inlineStr">
+      <c r="W39" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X39" s="33" t="inlineStr">
+      <c r="X39" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -11106,7 +11208,7 @@
           <t>https://a.allegroimg.com/original/11923c/a79785a04d36aa54f0d87384f038/Filtracni-kartuse-Intex-D-3BTZ0023-SC828</t>
         </is>
       </c>
-      <c r="Z39" s="33" t="inlineStr">
+      <c r="Z39" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -11116,7 +11218,7 @@
           <t>Darlly Filter Cartridge Pack of 2 Filter Cartridges Compatible with Intex Type H</t>
         </is>
       </c>
-      <c r="AB39" s="33" t="inlineStr">
+      <c r="AB39" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -11128,10 +11230,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF39" s="33" t="inlineStr"/>
-      <c r="AG39" s="33" t="inlineStr"/>
-      <c r="AH39" s="33" t="inlineStr"/>
-      <c r="AI39" s="33" t="inlineStr"/>
+      <c r="AF39" s="36" t="inlineStr"/>
+      <c r="AG39" s="36" t="inlineStr"/>
+      <c r="AH39" s="36" t="inlineStr"/>
+      <c r="AI39" s="36" t="inlineStr"/>
     </row>
     <row r="40" ht="62" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
@@ -11149,17 +11251,17 @@
           <t>A Darlly replacement spa filter cartridge with dimensions of 22 cm diameter by 27 cm height, compatible with SC713 and C-8465 references. A reliable like-for-like swap to keep your spa filtration running smoothly.</t>
         </is>
       </c>
-      <c r="D40" s="33" t="inlineStr">
+      <c r="D40" s="36" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E40" s="33" t="inlineStr">
+      <c r="E40" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F40" s="33" t="inlineStr">
+      <c r="F40" s="36" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -11169,71 +11271,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H40" s="33" t="inlineStr">
+      <c r="H40" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I40" s="33" t="inlineStr">
+      <c r="I40" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J40" s="33" t="inlineStr">
+      <c r="J40" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K40" s="33" t="inlineStr">
+      <c r="K40" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L40" s="33" t="inlineStr">
+      <c r="L40" s="36" t="inlineStr">
         <is>
           <t>DAR-FIL-1744</t>
         </is>
       </c>
-      <c r="M40" s="34" t="inlineStr">
+      <c r="M40" s="37" t="inlineStr">
         <is>
           <t>700175991744</t>
         </is>
       </c>
-      <c r="N40" s="35" t="inlineStr"/>
-      <c r="O40" s="35" t="inlineStr"/>
-      <c r="P40" s="35" t="inlineStr"/>
-      <c r="Q40" s="33" t="inlineStr">
+      <c r="N40" s="38" t="inlineStr"/>
+      <c r="O40" s="38" t="inlineStr"/>
+      <c r="P40" s="38" t="inlineStr"/>
+      <c r="Q40" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R40" s="33" t="inlineStr">
+      <c r="R40" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S40" s="33" t="inlineStr">
+      <c r="S40" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T40" s="33" t="inlineStr">
+      <c r="T40" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U40" s="33" t="inlineStr"/>
-      <c r="V40" s="33" t="inlineStr">
+      <c r="U40" s="36" t="inlineStr"/>
+      <c r="V40" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W40" s="33" t="inlineStr">
+      <c r="W40" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X40" s="33" t="inlineStr">
+      <c r="X40" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -11243,7 +11345,7 @@
           <t>https://images.barcodelookup.com/142259/1422591231-1.jpg</t>
         </is>
       </c>
-      <c r="Z40" s="33" t="inlineStr">
+      <c r="Z40" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -11253,7 +11355,7 @@
           <t>Spa Replacement Filter Ø 22 cm x 27 cm SC713, C-8465 - Darlly</t>
         </is>
       </c>
-      <c r="AB40" s="33" t="inlineStr">
+      <c r="AB40" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -11265,14 +11367,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF40" s="33" t="inlineStr"/>
-      <c r="AG40" s="33" t="inlineStr"/>
-      <c r="AH40" s="33" t="inlineStr">
+      <c r="AF40" s="36" t="inlineStr"/>
+      <c r="AG40" s="36" t="inlineStr"/>
+      <c r="AH40" s="36" t="inlineStr">
         <is>
           <t>22.0cm</t>
         </is>
       </c>
-      <c r="AI40" s="33" t="inlineStr">
+      <c r="AI40" s="36" t="inlineStr">
         <is>
           <t>27.0cm</t>
         </is>
@@ -11294,17 +11396,17 @@
           <t>A 1 kg pack of 20g multitabs for swimming pools, offering a 5-in-1 treatment that combines multiple water care functions in a single slow-dissolving tablet. Convenient all-in-one dosing that keeps pool maintenance simple.</t>
         </is>
       </c>
-      <c r="D41" s="33" t="inlineStr">
+      <c r="D41" s="36" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E41" s="33" t="inlineStr">
+      <c r="E41" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F41" s="33" t="inlineStr">
+      <c r="F41" s="36" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -11314,75 +11416,75 @@
           <t>pool, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H41" s="33" t="inlineStr">
+      <c r="H41" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I41" s="33" t="inlineStr">
+      <c r="I41" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J41" s="33" t="inlineStr">
+      <c r="J41" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K41" s="33" t="inlineStr">
+      <c r="K41" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L41" s="33" t="inlineStr">
+      <c r="L41" s="36" t="inlineStr">
         <is>
           <t>HFE-CHM-8430</t>
         </is>
       </c>
-      <c r="M41" s="34" t="inlineStr">
+      <c r="M41" s="37" t="inlineStr">
         <is>
           <t>4250463108430</t>
         </is>
       </c>
-      <c r="N41" s="35" t="inlineStr"/>
-      <c r="O41" s="35" t="inlineStr"/>
-      <c r="P41" s="35" t="inlineStr"/>
-      <c r="Q41" s="33" t="inlineStr">
+      <c r="N41" s="38" t="inlineStr"/>
+      <c r="O41" s="38" t="inlineStr"/>
+      <c r="P41" s="38" t="inlineStr"/>
+      <c r="Q41" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R41" s="33" t="inlineStr">
+      <c r="R41" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S41" s="33" t="inlineStr">
+      <c r="S41" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T41" s="33" t="inlineStr">
+      <c r="T41" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U41" s="33" t="inlineStr">
+      <c r="U41" s="36" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="V41" s="33" t="inlineStr">
+      <c r="V41" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W41" s="33" t="inlineStr">
+      <c r="W41" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X41" s="33" t="inlineStr">
+      <c r="X41" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -11392,7 +11494,7 @@
           <t>https://images.barcodelookup.com/17422/174228560-1.jpg</t>
         </is>
       </c>
-      <c r="Z41" s="33" t="inlineStr">
+      <c r="Z41" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -11402,7 +11504,7 @@
           <t>1 x 1 kg BAYZID® 20g 5-in-1 Multitabs for Pools - HÖFER CHEMIE</t>
         </is>
       </c>
-      <c r="AB41" s="33" t="inlineStr">
+      <c r="AB41" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -11414,10 +11516,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF41" s="33" t="inlineStr"/>
-      <c r="AG41" s="33" t="inlineStr"/>
-      <c r="AH41" s="33" t="inlineStr"/>
-      <c r="AI41" s="33" t="inlineStr"/>
+      <c r="AF41" s="36" t="inlineStr"/>
+      <c r="AG41" s="36" t="inlineStr"/>
+      <c r="AH41" s="36" t="inlineStr"/>
+      <c r="AI41" s="36" t="inlineStr"/>
     </row>
     <row r="42" ht="76" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
@@ -11435,17 +11537,17 @@
           <t>A ready-to-use alkaline spray cleaner for removing grease and dirt marks at the waterline of pools and for cleaning skimmers. The spray bottle makes application straightforward, and it can be used on a filled pool on all alkali-resistant surfaces.</t>
         </is>
       </c>
-      <c r="D42" s="33" t="inlineStr">
+      <c r="D42" s="36" t="inlineStr">
         <is>
           <t>Bayrol</t>
         </is>
       </c>
-      <c r="E42" s="33" t="inlineStr">
+      <c r="E42" s="36" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F42" s="33" t="inlineStr">
+      <c r="F42" s="36" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -11455,75 +11557,75 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H42" s="33" t="inlineStr">
+      <c r="H42" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I42" s="33" t="inlineStr">
+      <c r="I42" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J42" s="33" t="inlineStr">
+      <c r="J42" s="36" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K42" s="33" t="inlineStr">
+      <c r="K42" s="36" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L42" s="33" t="inlineStr">
+      <c r="L42" s="36" t="inlineStr">
         <is>
           <t>BAY-CLN-4134</t>
         </is>
       </c>
-      <c r="M42" s="34" t="inlineStr">
+      <c r="M42" s="37" t="inlineStr">
         <is>
           <t>4008367154134</t>
         </is>
       </c>
-      <c r="N42" s="35" t="inlineStr"/>
-      <c r="O42" s="35" t="inlineStr"/>
-      <c r="P42" s="35" t="inlineStr"/>
-      <c r="Q42" s="33" t="inlineStr">
+      <c r="N42" s="38" t="inlineStr"/>
+      <c r="O42" s="38" t="inlineStr"/>
+      <c r="P42" s="38" t="inlineStr"/>
+      <c r="Q42" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R42" s="33" t="inlineStr">
+      <c r="R42" s="36" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S42" s="33" t="inlineStr">
+      <c r="S42" s="36" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T42" s="33" t="inlineStr">
+      <c r="T42" s="36" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U42" s="33" t="inlineStr">
+      <c r="U42" s="36" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="V42" s="33" t="inlineStr">
+      <c r="V42" s="36" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W42" s="33" t="inlineStr">
+      <c r="W42" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X42" s="33" t="inlineStr">
+      <c r="X42" s="36" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -11533,7 +11635,7 @@
           <t>https://www.north-spa.de/wp-content/uploads/2023/02/Produktbild-1-Bayrol-Randfix-07-l-4008367154134.jpg</t>
         </is>
       </c>
-      <c r="Z42" s="33" t="inlineStr">
+      <c r="Z42" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -11543,7 +11645,7 @@
           <t>Bayrol Randfix 0,7 l</t>
         </is>
       </c>
-      <c r="AB42" s="33" t="inlineStr">
+      <c r="AB42" s="36" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -11555,10 +11657,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF42" s="33" t="inlineStr"/>
-      <c r="AG42" s="33" t="inlineStr"/>
-      <c r="AH42" s="33" t="inlineStr"/>
-      <c r="AI42" s="33" t="inlineStr"/>
+      <c r="AF42" s="36" t="inlineStr"/>
+      <c r="AG42" s="36" t="inlineStr"/>
+      <c r="AH42" s="36" t="inlineStr"/>
+      <c r="AI42" s="36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11718,4 +11820,146 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="96" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="39" t="inlineStr">
+        <is>
+          <t>How to read this sheet</t>
+        </is>
+      </c>
+      <c r="B1" s="40" t="inlineStr"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="17" t="inlineStr"/>
+      <c r="B2" s="17" t="inlineStr"/>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="41" t="inlineStr">
+        <is>
+          <t>Each FIELD is judged on its own evidence.</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>A row is not one colour. The photo, the description and the ingredients are verified separately, so a green photo can sit beside a yellow description. That is the design, not a mistake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="17" t="inlineStr"/>
+      <c r="B4" s="17" t="inlineStr"/>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>GREEN — verified</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>The barcode (or a brand article code) was found LITERALLY at the source: in the page text, its structured data, or the image filename. Never a name match, never a guess.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>YELLOW — review this</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>We have something, but it was not confirmed by one of those methods. It is probably right. Check it before it goes live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="44" t="inlineStr">
+        <is>
+          <t>RED — nothing</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>We found nothing for this field. It needs sourcing by hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="45" t="inlineStr">
+        <is>
+          <t>GREY — not applicable</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>The field does not apply, e.g. ingredients on a product that is not edible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="17" t="inlineStr"/>
+      <c r="B9" s="17" t="inlineStr"/>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="41" t="inlineStr">
+        <is>
+          <t>Status column</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>The worst field in the row. READY = all green. REVIEW = something is yellow. HOLD = something is missing. A REVIEW row can still have a perfectly verified photo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="17" t="inlineStr"/>
+      <c r="B11" s="17" t="inlineStr"/>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="41" t="inlineStr">
+        <is>
+          <t>Confirmed by</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>How many independent websites printed this barcode. More sources is stronger evidence, though one literal confirmation is already enough to be green.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="17" t="inlineStr"/>
+      <c r="B13" s="17" t="inlineStr"/>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="41" t="inlineStr">
+        <is>
+          <t>Tabs</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Curation = review here. Shopify import = the same products in Shopify's import schema, editable. Needs re-scan = scanned codes that carry no product barcode at all.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/projects/splashstore/docs/splashstore-scan-curation-260816.xlsx
+++ b/projects/splashstore/docs/splashstore-scan-curation-260816.xlsx
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -170,15 +170,6 @@
     <xf numFmtId="49" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -277,30 +268,14 @@
 Three sources agreeing is stronger evidence than one, though both are green.</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>Colour applies to THIS FIELD ONLY, and is judged separately from the photo.
-GREEN = written from the barcode-confirmed page for this exact product.
-YELLOW = written from a name-matched page, so it may describe a variant.
-RED = no description.
-A yellow description beside a green image is normal: the photo was proven by the barcode, the wording was not.</t>
-      </text>
-    </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>Colour applies to THIS FIELD ONLY, and is judged separately from the photo.
 GREEN = written from the barcode-confirmed page for this exact product.
 YELLOW = written from a name-matched page, so it may describe a variant.
 RED = no description.
-A yellow description beside a green image is normal: the photo was proven by the barcode, the wording was not.</t>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
-      <text>
-        <t>Colour applies to THIS FIELD ONLY.
-GREEN = the barcode was found literally on the page the photo came from.
-YELLOW = the right product, but the photo needs a look (crop, multipack, unclear).
-RED = no usable photo was found.</t>
+A yellow description beside a green image is normal: the photo was proven by the barcode, the wording was not.
+The cell names the page the wording came from, or says 'generic (from name)' when there was no page at all.</t>
       </text>
     </comment>
     <comment ref="P1" authorId="0" shapeId="0">
@@ -308,7 +283,8 @@
         <t>Colour applies to THIS FIELD ONLY.
 GREEN = the barcode was found literally on the page the photo came from.
 YELLOW = the right product, but the photo needs a look (crop, multipack, unclear).
-RED = no usable photo was found.</t>
+RED = no usable photo was found.
+The cell names the site the photo came from. Compare it with Description Source: a different site there means the two fields were proven separately.</t>
       </text>
     </comment>
     <comment ref="R1" authorId="0" shapeId="0">
@@ -1634,20 +1610,20 @@
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="56" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="56" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="56" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="28" customWidth="1" min="16" max="16"/>
+    <col width="56" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
     <col width="3" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
@@ -1753,7 +1729,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="244" customHeight="1">
+    <row r="2" ht="132" customHeight="1">
       <c r="A2" s="2" t="n"/>
       <c r="B2" s="5" t="inlineStr">
         <is>
@@ -1792,7 +1768,7 @@
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: spa-components.com</t>
         </is>
       </c>
       <c r="J2" s="18" t="inlineStr">
@@ -1811,7 +1787,7 @@
       </c>
       <c r="P2" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: spa-components.com</t>
         </is>
       </c>
       <c r="Q2" s="20" t="n"/>
@@ -1822,7 +1798,7 @@
       </c>
       <c r="S2" s="18" t="n"/>
     </row>
-    <row r="3" ht="258" customHeight="1">
+    <row r="3" ht="132" customHeight="1">
       <c r="A3" s="2" t="n"/>
       <c r="B3" s="5" t="inlineStr">
         <is>
@@ -1857,7 +1833,7 @@
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: bestwaystore.de</t>
         </is>
       </c>
       <c r="J3" s="18" t="inlineStr">
@@ -1880,7 +1856,7 @@
       </c>
       <c r="P3" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: bestwaystore.de</t>
         </is>
       </c>
       <c r="Q3" s="20" t="n"/>
@@ -1891,7 +1867,7 @@
       </c>
       <c r="S3" s="18" t="n"/>
     </row>
-    <row r="4" ht="272" customHeight="1">
+    <row r="4" ht="132" customHeight="1">
       <c r="A4" s="2" t="n"/>
       <c r="B4" s="5" t="inlineStr">
         <is>
@@ -1930,7 +1906,7 @@
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: pools.shop</t>
         </is>
       </c>
       <c r="J4" s="18" t="inlineStr">
@@ -1949,7 +1925,7 @@
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: pools.shop</t>
         </is>
       </c>
       <c r="Q4" s="20" t="n"/>
@@ -2001,7 +1977,7 @@
       </c>
       <c r="S5" s="18" t="n"/>
     </row>
-    <row r="6" ht="230" customHeight="1">
+    <row r="6" ht="132" customHeight="1">
       <c r="A6" s="2" t="n"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -2040,7 +2016,7 @@
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: barcodelookup.com</t>
         </is>
       </c>
       <c r="J6" s="18" t="inlineStr">
@@ -2070,7 +2046,7 @@
       </c>
       <c r="S6" s="18" t="n"/>
     </row>
-    <row r="7" ht="258" customHeight="1">
+    <row r="7" ht="132" customHeight="1">
       <c r="A7" s="2" t="n"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -2105,7 +2081,7 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: bestwaystore.de</t>
         </is>
       </c>
       <c r="J7" s="18" t="inlineStr">
@@ -2128,7 +2104,7 @@
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: bestwaystore.de</t>
         </is>
       </c>
       <c r="Q7" s="20" t="n"/>
@@ -2139,7 +2115,7 @@
       </c>
       <c r="S7" s="18" t="n"/>
     </row>
-    <row r="8" ht="216" customHeight="1">
+    <row r="8" ht="132" customHeight="1">
       <c r="A8" s="12" t="n"/>
       <c r="B8" s="13" t="inlineStr">
         <is>
@@ -2178,7 +2154,7 @@
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: barcodelookup.com</t>
         </is>
       </c>
       <c r="J8" s="18" t="inlineStr">
@@ -2208,7 +2184,7 @@
       </c>
       <c r="S8" s="18" t="n"/>
     </row>
-    <row r="9" ht="320" customHeight="1">
+    <row r="9" ht="132" customHeight="1">
       <c r="A9" s="12" t="n"/>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -2277,7 +2253,7 @@
       </c>
       <c r="S9" s="18" t="n"/>
     </row>
-    <row r="10" ht="300" customHeight="1">
+    <row r="10" ht="132" customHeight="1">
       <c r="A10" s="2" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -2312,7 +2288,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: intex.fr</t>
         </is>
       </c>
       <c r="J10" s="18" t="inlineStr">
@@ -2339,7 +2315,7 @@
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: intex.fr</t>
         </is>
       </c>
       <c r="Q10" s="20" t="n"/>
@@ -2350,7 +2326,7 @@
       </c>
       <c r="S10" s="18" t="n"/>
     </row>
-    <row r="11" ht="230" customHeight="1">
+    <row r="11" ht="132" customHeight="1">
       <c r="A11" s="2" t="n"/>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -2389,7 +2365,7 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: barcodelookup.com</t>
         </is>
       </c>
       <c r="J11" s="18" t="inlineStr">
@@ -2421,7 +2397,7 @@
       </c>
       <c r="S11" s="18" t="n"/>
     </row>
-    <row r="12" ht="202" customHeight="1">
+    <row r="12" ht="132" customHeight="1">
       <c r="A12" s="2" t="n"/>
       <c r="B12" s="13" t="inlineStr">
         <is>
@@ -2479,7 +2455,7 @@
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: north-spa.de</t>
         </is>
       </c>
       <c r="Q12" s="20" t="n"/>
@@ -2490,7 +2466,7 @@
       </c>
       <c r="S12" s="18" t="n"/>
     </row>
-    <row r="13" ht="230" customHeight="1">
+    <row r="13" ht="132" customHeight="1">
       <c r="A13" s="2" t="n"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -2525,7 +2501,7 @@
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: intex.fr</t>
         </is>
       </c>
       <c r="J13" s="18" t="inlineStr">
@@ -2544,7 +2520,7 @@
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: intex.fr</t>
         </is>
       </c>
       <c r="Q13" s="20" t="n"/>
@@ -2555,7 +2531,7 @@
       </c>
       <c r="S13" s="18" t="n"/>
     </row>
-    <row r="14" ht="202" customHeight="1">
+    <row r="14" ht="132" customHeight="1">
       <c r="A14" s="2" t="n"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -2594,7 +2570,7 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: barcodelookup.com</t>
         </is>
       </c>
       <c r="J14" s="18" t="inlineStr">
@@ -2624,7 +2600,7 @@
       </c>
       <c r="S14" s="18" t="n"/>
     </row>
-    <row r="15" ht="216" customHeight="1">
+    <row r="15" ht="132" customHeight="1">
       <c r="A15" s="2" t="n"/>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -2682,7 +2658,7 @@
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: spabalancer.ch</t>
         </is>
       </c>
       <c r="Q15" s="20" t="n"/>
@@ -2734,7 +2710,7 @@
       </c>
       <c r="S16" s="18" t="n"/>
     </row>
-    <row r="17" ht="202" customHeight="1">
+    <row r="17" ht="62" customHeight="1">
       <c r="A17" s="9" t="n"/>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -2799,7 +2775,7 @@
       </c>
       <c r="S17" s="18" t="n"/>
     </row>
-    <row r="18" ht="216" customHeight="1">
+    <row r="18" ht="132" customHeight="1">
       <c r="A18" s="2" t="n"/>
       <c r="B18" s="13" t="inlineStr">
         <is>
@@ -2857,7 +2833,7 @@
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: poolpowershop.de</t>
         </is>
       </c>
       <c r="Q18" s="20" t="n"/>
@@ -2868,7 +2844,7 @@
       </c>
       <c r="S18" s="18" t="n"/>
     </row>
-    <row r="19" ht="202" customHeight="1">
+    <row r="19" ht="132" customHeight="1">
       <c r="A19" s="2" t="n"/>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -2907,7 +2883,7 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: barcodelookup.com</t>
         </is>
       </c>
       <c r="J19" s="18" t="inlineStr">
@@ -2937,7 +2913,7 @@
       </c>
       <c r="S19" s="18" t="n"/>
     </row>
-    <row r="20" ht="272" customHeight="1">
+    <row r="20" ht="132" customHeight="1">
       <c r="A20" s="2" t="n"/>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -2976,7 +2952,7 @@
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: mangas.com.cy</t>
         </is>
       </c>
       <c r="J20" s="18" t="inlineStr">
@@ -2995,7 +2971,7 @@
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: mangas.com.cy</t>
         </is>
       </c>
       <c r="Q20" s="20" t="n"/>
@@ -3006,7 +2982,7 @@
       </c>
       <c r="S20" s="18" t="n"/>
     </row>
-    <row r="21" ht="320" customHeight="1">
+    <row r="21" ht="132" customHeight="1">
       <c r="A21" s="2" t="n"/>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -3045,7 +3021,7 @@
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: poolservices.cy</t>
         </is>
       </c>
       <c r="J21" s="18" t="inlineStr">
@@ -3064,7 +3040,7 @@
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: poolservices.cy</t>
         </is>
       </c>
       <c r="Q21" s="20" t="n"/>
@@ -3075,7 +3051,7 @@
       </c>
       <c r="S21" s="18" t="n"/>
     </row>
-    <row r="22" ht="188" customHeight="1">
+    <row r="22" ht="132" customHeight="1">
       <c r="A22" s="2" t="n"/>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -3114,7 +3090,7 @@
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: mangas.com.cy</t>
         </is>
       </c>
       <c r="J22" s="18" t="inlineStr">
@@ -3133,7 +3109,7 @@
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: mangas.com.cy</t>
         </is>
       </c>
       <c r="Q22" s="20" t="n"/>
@@ -3144,7 +3120,7 @@
       </c>
       <c r="S22" s="18" t="n"/>
     </row>
-    <row r="23" ht="174" customHeight="1">
+    <row r="23" ht="132" customHeight="1">
       <c r="A23" s="2" t="n"/>
       <c r="B23" s="13" t="inlineStr">
         <is>
@@ -3202,7 +3178,7 @@
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: hoefer-shop.com</t>
         </is>
       </c>
       <c r="Q23" s="20" t="n"/>
@@ -3213,7 +3189,7 @@
       </c>
       <c r="S23" s="18" t="n"/>
     </row>
-    <row r="24" ht="202" customHeight="1">
+    <row r="24" ht="132" customHeight="1">
       <c r="A24" s="2" t="n"/>
       <c r="B24" s="13" t="inlineStr">
         <is>
@@ -3271,7 +3247,7 @@
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: hoefer-shop.com</t>
         </is>
       </c>
       <c r="Q24" s="20" t="n"/>
@@ -3282,7 +3258,7 @@
       </c>
       <c r="S24" s="18" t="n"/>
     </row>
-    <row r="25" ht="202" customHeight="1">
+    <row r="25" ht="62" customHeight="1">
       <c r="A25" s="9" t="n"/>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -3349,7 +3325,7 @@
       </c>
       <c r="S25" s="18" t="n"/>
     </row>
-    <row r="26" ht="202" customHeight="1">
+    <row r="26" ht="132" customHeight="1">
       <c r="A26" s="2" t="n"/>
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -3388,7 +3364,7 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: barcodelookup.com</t>
         </is>
       </c>
       <c r="J26" s="18" t="inlineStr">
@@ -3418,7 +3394,7 @@
       </c>
       <c r="S26" s="18" t="n"/>
     </row>
-    <row r="27" ht="314" customHeight="1">
+    <row r="27" ht="132" customHeight="1">
       <c r="A27" s="2" t="n"/>
       <c r="B27" s="5" t="inlineStr">
         <is>
@@ -3453,7 +3429,7 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: piscinarium.com</t>
         </is>
       </c>
       <c r="J27" s="18" t="inlineStr">
@@ -3472,7 +3448,7 @@
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: piscinarium.com</t>
         </is>
       </c>
       <c r="Q27" s="20" t="n"/>
@@ -3483,7 +3459,7 @@
       </c>
       <c r="S27" s="18" t="n"/>
     </row>
-    <row r="28" ht="216" customHeight="1">
+    <row r="28" ht="62" customHeight="1">
       <c r="A28" s="9" t="n"/>
       <c r="B28" s="10" t="inlineStr">
         <is>
@@ -3544,7 +3520,7 @@
       </c>
       <c r="S28" s="18" t="n"/>
     </row>
-    <row r="29" ht="230" customHeight="1">
+    <row r="29" ht="62" customHeight="1">
       <c r="A29" s="9" t="n"/>
       <c r="B29" s="10" t="inlineStr">
         <is>
@@ -3609,7 +3585,7 @@
       </c>
       <c r="S29" s="18" t="n"/>
     </row>
-    <row r="30" ht="300" customHeight="1">
+    <row r="30" ht="132" customHeight="1">
       <c r="A30" s="2" t="n"/>
       <c r="B30" s="5" t="inlineStr">
         <is>
@@ -3648,7 +3624,7 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: cdiscount.com</t>
         </is>
       </c>
       <c r="J30" s="18" t="inlineStr">
@@ -3667,7 +3643,7 @@
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: cdiscount.com</t>
         </is>
       </c>
       <c r="Q30" s="20" t="n"/>
@@ -3678,7 +3654,7 @@
       </c>
       <c r="S30" s="18" t="n"/>
     </row>
-    <row r="31" ht="230" customHeight="1">
+    <row r="31" ht="132" customHeight="1">
       <c r="A31" s="2" t="n"/>
       <c r="B31" s="5" t="inlineStr">
         <is>
@@ -3713,7 +3689,7 @@
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: altruan.com</t>
         </is>
       </c>
       <c r="J31" s="18" t="inlineStr">
@@ -3734,7 +3710,7 @@
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: altruan.com</t>
         </is>
       </c>
       <c r="Q31" s="20" t="inlineStr">
@@ -3749,7 +3725,7 @@
       </c>
       <c r="S31" s="18" t="n"/>
     </row>
-    <row r="32" ht="272" customHeight="1">
+    <row r="32" ht="132" customHeight="1">
       <c r="A32" s="2" t="n"/>
       <c r="B32" s="13" t="inlineStr">
         <is>
@@ -3818,7 +3794,7 @@
       </c>
       <c r="S32" s="18" t="n"/>
     </row>
-    <row r="33" ht="244" customHeight="1">
+    <row r="33" ht="132" customHeight="1">
       <c r="A33" s="2" t="n"/>
       <c r="B33" s="5" t="inlineStr">
         <is>
@@ -3853,7 +3829,7 @@
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: barcodelookup.com</t>
         </is>
       </c>
       <c r="J33" s="18" t="inlineStr">
@@ -3883,7 +3859,7 @@
       </c>
       <c r="S33" s="18" t="n"/>
     </row>
-    <row r="34" ht="174" customHeight="1">
+    <row r="34" ht="132" customHeight="1">
       <c r="A34" s="2" t="n"/>
       <c r="B34" s="5" t="inlineStr">
         <is>
@@ -3918,7 +3894,7 @@
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: barcodelookup.com</t>
         </is>
       </c>
       <c r="J34" s="18" t="inlineStr">
@@ -3948,7 +3924,7 @@
       </c>
       <c r="S34" s="18" t="n"/>
     </row>
-    <row r="35" ht="320" customHeight="1">
+    <row r="35" ht="132" customHeight="1">
       <c r="A35" s="2" t="n"/>
       <c r="B35" s="5" t="inlineStr">
         <is>
@@ -3983,7 +3959,7 @@
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: ecoperation.com</t>
         </is>
       </c>
       <c r="J35" s="18" t="inlineStr">
@@ -4008,7 +3984,7 @@
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: ecoperation.com</t>
         </is>
       </c>
       <c r="Q35" s="20" t="n"/>
@@ -4019,7 +3995,7 @@
       </c>
       <c r="S35" s="18" t="n"/>
     </row>
-    <row r="36" ht="300" customHeight="1">
+    <row r="36" ht="132" customHeight="1">
       <c r="A36" s="2" t="n"/>
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -4058,7 +4034,7 @@
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: ebay.de</t>
         </is>
       </c>
       <c r="J36" s="18" t="inlineStr">
@@ -4083,7 +4059,7 @@
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: ebay.de</t>
         </is>
       </c>
       <c r="Q36" s="20" t="n"/>
@@ -4094,7 +4070,7 @@
       </c>
       <c r="S36" s="18" t="n"/>
     </row>
-    <row r="37" ht="272" customHeight="1">
+    <row r="37" ht="132" customHeight="1">
       <c r="A37" s="2" t="n"/>
       <c r="B37" s="5" t="inlineStr">
         <is>
@@ -4133,7 +4109,7 @@
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: ebay.com</t>
         </is>
       </c>
       <c r="J37" s="18" t="inlineStr">
@@ -4152,7 +4128,7 @@
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: ebay.com</t>
         </is>
       </c>
       <c r="Q37" s="20" t="n"/>
@@ -4163,7 +4139,7 @@
       </c>
       <c r="S37" s="18" t="n"/>
     </row>
-    <row r="38" ht="230" customHeight="1">
+    <row r="38" ht="62" customHeight="1">
       <c r="A38" s="9" t="n"/>
       <c r="B38" s="10" t="inlineStr">
         <is>
@@ -4234,7 +4210,7 @@
       </c>
       <c r="S38" s="18" t="n"/>
     </row>
-    <row r="39" ht="286" customHeight="1">
+    <row r="39" ht="132" customHeight="1">
       <c r="A39" s="2" t="n"/>
       <c r="B39" s="5" t="inlineStr">
         <is>
@@ -4273,7 +4249,7 @@
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: rozetka.pl</t>
         </is>
       </c>
       <c r="J39" s="18" t="inlineStr">
@@ -4300,7 +4276,7 @@
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: rozetka.pl</t>
         </is>
       </c>
       <c r="Q39" s="20" t="n"/>
@@ -4311,7 +4287,7 @@
       </c>
       <c r="S39" s="18" t="n"/>
     </row>
-    <row r="40" ht="314" customHeight="1">
+    <row r="40" ht="132" customHeight="1">
       <c r="A40" s="2" t="n"/>
       <c r="B40" s="5" t="inlineStr">
         <is>
@@ -4346,7 +4322,7 @@
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: carrefour.fr</t>
         </is>
       </c>
       <c r="J40" s="18" t="inlineStr">
@@ -4365,7 +4341,7 @@
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: carrefour.fr</t>
         </is>
       </c>
       <c r="Q40" s="20" t="n"/>
@@ -4376,7 +4352,7 @@
       </c>
       <c r="S40" s="18" t="n"/>
     </row>
-    <row r="41" ht="202" customHeight="1">
+    <row r="41" ht="132" customHeight="1">
       <c r="A41" s="2" t="n"/>
       <c r="B41" s="13" t="inlineStr">
         <is>
@@ -4434,7 +4410,7 @@
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: allegro.cz</t>
         </is>
       </c>
       <c r="Q41" s="20" t="n"/>
@@ -4445,7 +4421,7 @@
       </c>
       <c r="S41" s="18" t="n"/>
     </row>
-    <row r="42" ht="230" customHeight="1">
+    <row r="42" ht="132" customHeight="1">
       <c r="A42" s="2" t="n"/>
       <c r="B42" s="5" t="inlineStr">
         <is>
@@ -4484,7 +4460,7 @@
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: barcodelookup.com</t>
         </is>
       </c>
       <c r="J42" s="18" t="inlineStr">
@@ -4518,7 +4494,7 @@
       </c>
       <c r="S42" s="18" t="n"/>
     </row>
-    <row r="43" ht="230" customHeight="1">
+    <row r="43" ht="132" customHeight="1">
       <c r="A43" s="2" t="n"/>
       <c r="B43" s="5" t="inlineStr">
         <is>
@@ -4557,7 +4533,7 @@
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: barcodelookup.com</t>
         </is>
       </c>
       <c r="J43" s="18" t="inlineStr">
@@ -4589,7 +4565,7 @@
       </c>
       <c r="S43" s="18" t="n"/>
     </row>
-    <row r="44" ht="258" customHeight="1">
+    <row r="44" ht="132" customHeight="1">
       <c r="A44" s="2" t="n"/>
       <c r="B44" s="5" t="inlineStr">
         <is>
@@ -4628,7 +4604,7 @@
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>Verified — product page</t>
+          <t>Verified — product page: north-spa.de</t>
         </is>
       </c>
       <c r="J44" s="18" t="inlineStr">
@@ -4649,7 +4625,7 @@
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>Verified — barcode</t>
+          <t>Verified — barcode: north-spa.de</t>
         </is>
       </c>
       <c r="Q44" s="20" t="n"/>
@@ -5050,17 +5026,17 @@
           <t>A cartridge filter for hot tubs and swim spas, measuring 26.0 cm outer diameter, 13.0 cm bottom part, and 3.8 cm inner thread. Compatible with Darlly SC779 and 40372 codes, it captures dirt, grease, and fine particles to keep water clean.</t>
         </is>
       </c>
-      <c r="D2" s="28" t="inlineStr">
+      <c r="D2" s="23" t="inlineStr">
         <is>
           <t>Rising Dragon</t>
         </is>
       </c>
-      <c r="E2" s="28" t="inlineStr">
+      <c r="E2" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F2" s="28" t="inlineStr">
+      <c r="F2" s="23" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5070,71 +5046,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H2" s="28" t="inlineStr">
+      <c r="H2" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I2" s="28" t="inlineStr">
+      <c r="I2" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J2" s="28" t="inlineStr">
+      <c r="J2" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K2" s="28" t="inlineStr">
+      <c r="K2" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L2" s="28" t="inlineStr">
+      <c r="L2" s="23" t="inlineStr">
         <is>
           <t>RIS-FIL-2406</t>
         </is>
       </c>
-      <c r="M2" s="29" t="inlineStr">
+      <c r="M2" s="24" t="inlineStr">
         <is>
           <t>700175992406</t>
         </is>
       </c>
-      <c r="N2" s="30" t="inlineStr"/>
-      <c r="O2" s="30" t="inlineStr"/>
-      <c r="P2" s="30" t="inlineStr"/>
-      <c r="Q2" s="28" t="inlineStr">
+      <c r="N2" s="25" t="inlineStr"/>
+      <c r="O2" s="25" t="inlineStr"/>
+      <c r="P2" s="25" t="inlineStr"/>
+      <c r="Q2" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R2" s="28" t="inlineStr">
+      <c r="R2" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S2" s="28" t="inlineStr">
+      <c r="S2" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T2" s="28" t="inlineStr">
+      <c r="T2" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U2" s="28" t="inlineStr"/>
-      <c r="V2" s="28" t="inlineStr">
+      <c r="U2" s="23" t="inlineStr"/>
+      <c r="V2" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W2" s="28" t="inlineStr">
+      <c r="W2" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X2" s="28" t="inlineStr">
+      <c r="X2" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5144,7 +5120,7 @@
           <t>https://www.spa-components.com/user/shop/big/1473-1_filter-cartridge-sc779-rising-dragon-plastics--eago-whirlpools.jpg?ff=1&amp;x=1024&amp;y=768&amp;q=85&amp;ts=6720c4a0&amp;sg=161563f2</t>
         </is>
       </c>
-      <c r="Z2" s="28" t="inlineStr">
+      <c r="Z2" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5154,7 +5130,7 @@
           <t>Filter Cartridge SC779 - Rising Dragon Plastics, EAGO Whirlpools - Spa Components</t>
         </is>
       </c>
-      <c r="AB2" s="28" t="inlineStr">
+      <c r="AB2" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5166,10 +5142,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF2" s="28" t="inlineStr"/>
-      <c r="AG2" s="28" t="inlineStr"/>
-      <c r="AH2" s="28" t="inlineStr"/>
-      <c r="AI2" s="28" t="inlineStr"/>
+      <c r="AF2" s="23" t="inlineStr"/>
+      <c r="AG2" s="23" t="inlineStr"/>
+      <c r="AH2" s="23" t="inlineStr"/>
+      <c r="AI2" s="23" t="inlineStr"/>
     </row>
     <row r="3" ht="62" customHeight="1">
       <c r="A3" s="18" t="inlineStr">
@@ -5187,13 +5163,13 @@
           <t>A twin pack of Size II replacement filter cartridges measuring 10.6 x 13.6 cm, designed for compatible pool and spa filtration systems. The fine lamellar structure delivers thorough water cleaning and the cartridges are easy to rinse clean.</t>
         </is>
       </c>
-      <c r="D3" s="28" t="inlineStr"/>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr"/>
+      <c r="E3" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F3" s="28" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5203,71 +5179,71 @@
           <t>filters, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H3" s="28" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I3" s="28" t="inlineStr">
+      <c r="I3" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J3" s="28" t="inlineStr">
+      <c r="J3" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K3" s="28" t="inlineStr">
+      <c r="K3" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L3" s="28" t="inlineStr">
+      <c r="L3" s="23" t="inlineStr">
         <is>
           <t>GEN-FIL-3615</t>
         </is>
       </c>
-      <c r="M3" s="29" t="inlineStr">
+      <c r="M3" s="24" t="inlineStr">
         <is>
           <t>6941607353615</t>
         </is>
       </c>
-      <c r="N3" s="30" t="inlineStr"/>
-      <c r="O3" s="30" t="inlineStr"/>
-      <c r="P3" s="30" t="inlineStr"/>
-      <c r="Q3" s="28" t="inlineStr">
+      <c r="N3" s="25" t="inlineStr"/>
+      <c r="O3" s="25" t="inlineStr"/>
+      <c r="P3" s="25" t="inlineStr"/>
+      <c r="Q3" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R3" s="28" t="inlineStr">
+      <c r="R3" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S3" s="28" t="inlineStr">
+      <c r="S3" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T3" s="28" t="inlineStr">
+      <c r="T3" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U3" s="28" t="inlineStr"/>
-      <c r="V3" s="28" t="inlineStr">
+      <c r="U3" s="23" t="inlineStr"/>
+      <c r="V3" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W3" s="28" t="inlineStr">
+      <c r="W3" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X3" s="28" t="inlineStr">
+      <c r="X3" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5277,7 +5253,7 @@
           <t>https://www.bestwaystore.de/media/c6/f8/ba/1756384660/6941607353615-main-jpg.jpg?ts=1756384660</t>
         </is>
       </c>
-      <c r="Z3" s="28" t="inlineStr">
+      <c r="Z3" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5287,7 +5263,7 @@
           <t>Filter cartridge Size II double pack, 10.6 x 13.6 cm | 58094_26</t>
         </is>
       </c>
-      <c r="AB3" s="28" t="inlineStr">
+      <c r="AB3" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5299,14 +5275,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF3" s="28" t="inlineStr"/>
-      <c r="AG3" s="28" t="inlineStr"/>
-      <c r="AH3" s="28" t="inlineStr">
+      <c r="AF3" s="23" t="inlineStr"/>
+      <c r="AG3" s="23" t="inlineStr"/>
+      <c r="AH3" s="23" t="inlineStr">
         <is>
           <t>10.6cm</t>
         </is>
       </c>
-      <c r="AI3" s="28" t="inlineStr">
+      <c r="AI3" s="23" t="inlineStr">
         <is>
           <t>13.6cm</t>
         </is>
@@ -5328,17 +5304,17 @@
           <t>A single Flowclear Size 3 replacement filter cartridge for compatible Bestway pool filtration systems, featuring a fine lamellar structure that traps deposits and dirt effectively. Easy to clean and straightforward to swap out when routine maintenance is due.</t>
         </is>
       </c>
-      <c r="D4" s="28" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>Bestway</t>
         </is>
       </c>
-      <c r="E4" s="28" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F4" s="28" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5348,71 +5324,71 @@
           <t>filters, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H4" s="28" t="inlineStr">
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I4" s="28" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J4" s="28" t="inlineStr">
+      <c r="J4" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K4" s="28" t="inlineStr">
+      <c r="K4" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L4" s="28" t="inlineStr">
+      <c r="L4" s="23" t="inlineStr">
         <is>
           <t>BES-FIL-3592</t>
         </is>
       </c>
-      <c r="M4" s="29" t="inlineStr">
+      <c r="M4" s="24" t="inlineStr">
         <is>
           <t>6941607353592</t>
         </is>
       </c>
-      <c r="N4" s="30" t="inlineStr"/>
-      <c r="O4" s="30" t="inlineStr"/>
-      <c r="P4" s="30" t="inlineStr"/>
-      <c r="Q4" s="28" t="inlineStr">
+      <c r="N4" s="25" t="inlineStr"/>
+      <c r="O4" s="25" t="inlineStr"/>
+      <c r="P4" s="25" t="inlineStr"/>
+      <c r="Q4" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R4" s="28" t="inlineStr">
+      <c r="R4" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S4" s="28" t="inlineStr">
+      <c r="S4" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T4" s="28" t="inlineStr">
+      <c r="T4" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U4" s="28" t="inlineStr"/>
-      <c r="V4" s="28" t="inlineStr">
+      <c r="U4" s="23" t="inlineStr"/>
+      <c r="V4" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W4" s="28" t="inlineStr">
+      <c r="W4" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X4" s="28" t="inlineStr">
+      <c r="X4" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5422,7 +5398,7 @@
           <t>https://ap.nice-cdn.com/upload/image/product/large/default/bestway-flowclear-filter-cartridge-size-3-1-item-638140-en.jpg</t>
         </is>
       </c>
-      <c r="Z4" s="28" t="inlineStr">
+      <c r="Z4" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5432,7 +5408,7 @@
           <t>Bestway Flowclear™ Filter Cartridge Size 3, 1 item</t>
         </is>
       </c>
-      <c r="AB4" s="28" t="inlineStr">
+      <c r="AB4" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5444,10 +5420,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF4" s="28" t="inlineStr"/>
-      <c r="AG4" s="28" t="inlineStr"/>
-      <c r="AH4" s="28" t="inlineStr"/>
-      <c r="AI4" s="28" t="inlineStr"/>
+      <c r="AF4" s="23" t="inlineStr"/>
+      <c r="AG4" s="23" t="inlineStr"/>
+      <c r="AH4" s="23" t="inlineStr"/>
+      <c r="AI4" s="23" t="inlineStr"/>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
@@ -5465,17 +5441,17 @@
           <t>A two-pack of compatible hot tub and spa cartridge filters corresponding to Unicel C-4335, Pleatco PRB35-IN, and Filbur FC-2385 references. A handy spare-pair to keep on hand so your tub is never without a fresh filter.</t>
         </is>
       </c>
-      <c r="D5" s="28" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E5" s="28" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F5" s="28" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5485,71 +5461,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H5" s="28" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I5" s="28" t="inlineStr">
+      <c r="I5" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J5" s="28" t="inlineStr">
+      <c r="J5" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K5" s="28" t="inlineStr">
+      <c r="K5" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L5" s="28" t="inlineStr">
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t>DAR-FIL-1669</t>
         </is>
       </c>
-      <c r="M5" s="29" t="inlineStr">
+      <c r="M5" s="24" t="inlineStr">
         <is>
           <t>700175991669</t>
         </is>
       </c>
-      <c r="N5" s="30" t="inlineStr"/>
-      <c r="O5" s="30" t="inlineStr"/>
-      <c r="P5" s="30" t="inlineStr"/>
-      <c r="Q5" s="28" t="inlineStr">
+      <c r="N5" s="25" t="inlineStr"/>
+      <c r="O5" s="25" t="inlineStr"/>
+      <c r="P5" s="25" t="inlineStr"/>
+      <c r="Q5" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R5" s="28" t="inlineStr">
+      <c r="R5" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S5" s="28" t="inlineStr">
+      <c r="S5" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T5" s="28" t="inlineStr">
+      <c r="T5" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U5" s="28" t="inlineStr"/>
-      <c r="V5" s="28" t="inlineStr">
+      <c r="U5" s="23" t="inlineStr"/>
+      <c r="V5" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W5" s="28" t="inlineStr">
+      <c r="W5" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X5" s="28" t="inlineStr">
+      <c r="X5" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5559,7 +5535,7 @@
           <t>https://images.barcodelookup.com/29361/293617958-1.jpg</t>
         </is>
       </c>
-      <c r="Z5" s="28" t="inlineStr">
+      <c r="Z5" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5569,7 +5545,7 @@
           <t>Darlly Hot Tub Spa Filter SC705 40353 Compatible with Unicel C-4335 PRB35-IN Filbur FC-2385 2 Pack</t>
         </is>
       </c>
-      <c r="AB5" s="28" t="inlineStr">
+      <c r="AB5" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5581,10 +5557,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF5" s="28" t="inlineStr"/>
-      <c r="AG5" s="28" t="inlineStr"/>
-      <c r="AH5" s="28" t="inlineStr"/>
-      <c r="AI5" s="28" t="inlineStr"/>
+      <c r="AF5" s="23" t="inlineStr"/>
+      <c r="AG5" s="23" t="inlineStr"/>
+      <c r="AH5" s="23" t="inlineStr"/>
+      <c r="AI5" s="23" t="inlineStr"/>
     </row>
     <row r="6" ht="62" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
@@ -5602,13 +5578,13 @@
           <t>A single Size IV replacement filter cartridge measuring 14.2 x 25.4 cm, compatible with Bestway filter pump 58391 (9,463 l/h). Its deep-fold, fine-structure media delivers thorough water cleaning and can be rinsed clean with minimal effort.</t>
         </is>
       </c>
-      <c r="D6" s="28" t="inlineStr"/>
-      <c r="E6" s="28" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr"/>
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F6" s="28" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5618,71 +5594,71 @@
           <t>filters, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H6" s="28" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I6" s="28" t="inlineStr">
+      <c r="I6" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J6" s="28" t="inlineStr">
+      <c r="J6" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K6" s="28" t="inlineStr">
+      <c r="K6" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L6" s="28" t="inlineStr">
+      <c r="L6" s="23" t="inlineStr">
         <is>
           <t>GEN-FIL-3622</t>
         </is>
       </c>
-      <c r="M6" s="29" t="inlineStr">
+      <c r="M6" s="24" t="inlineStr">
         <is>
           <t>6941607353622</t>
         </is>
       </c>
-      <c r="N6" s="30" t="inlineStr"/>
-      <c r="O6" s="30" t="inlineStr"/>
-      <c r="P6" s="30" t="inlineStr"/>
-      <c r="Q6" s="28" t="inlineStr">
+      <c r="N6" s="25" t="inlineStr"/>
+      <c r="O6" s="25" t="inlineStr"/>
+      <c r="P6" s="25" t="inlineStr"/>
+      <c r="Q6" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R6" s="28" t="inlineStr">
+      <c r="R6" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S6" s="28" t="inlineStr">
+      <c r="S6" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T6" s="28" t="inlineStr">
+      <c r="T6" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U6" s="28" t="inlineStr"/>
-      <c r="V6" s="28" t="inlineStr">
+      <c r="U6" s="23" t="inlineStr"/>
+      <c r="V6" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W6" s="28" t="inlineStr">
+      <c r="W6" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X6" s="28" t="inlineStr">
+      <c r="X6" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5692,7 +5668,7 @@
           <t>https://www.bestwaystore.de/media/53/6c/e9/1756384676/6941607353622-main-jpg.jpg?ts=1756384676</t>
         </is>
       </c>
-      <c r="Z6" s="28" t="inlineStr">
+      <c r="Z6" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5702,7 +5678,7 @@
           <t>Filter cartridge Size IV 14.2 x 25.4 cm | 58095_26</t>
         </is>
       </c>
-      <c r="AB6" s="28" t="inlineStr">
+      <c r="AB6" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5714,14 +5690,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF6" s="28" t="inlineStr"/>
-      <c r="AG6" s="28" t="inlineStr"/>
-      <c r="AH6" s="28" t="inlineStr">
+      <c r="AF6" s="23" t="inlineStr"/>
+      <c r="AG6" s="23" t="inlineStr"/>
+      <c r="AH6" s="23" t="inlineStr">
         <is>
           <t>14.2cm</t>
         </is>
       </c>
-      <c r="AI6" s="28" t="inlineStr">
+      <c r="AI6" s="23" t="inlineStr">
         <is>
           <t>25.4cm</t>
         </is>
@@ -5743,17 +5719,17 @@
           <t>A pair of Darlly spa filter cartridges in the SC726 reference, also cross-referenced as Unicel C-4401 and Pleatco PRB17.5SF PR. Buying in pairs means a fresh replacement is always ready when it is time to swap.</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E7" s="28" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F7" s="28" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5763,71 +5739,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H7" s="28" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I7" s="28" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J7" s="28" t="inlineStr">
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K7" s="28" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L7" s="28" t="inlineStr">
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t>DAR-FIL-1874</t>
         </is>
       </c>
-      <c r="M7" s="29" t="inlineStr">
+      <c r="M7" s="24" t="inlineStr">
         <is>
           <t>700175991874</t>
         </is>
       </c>
-      <c r="N7" s="30" t="inlineStr"/>
-      <c r="O7" s="30" t="inlineStr"/>
-      <c r="P7" s="30" t="inlineStr"/>
-      <c r="Q7" s="28" t="inlineStr">
+      <c r="N7" s="25" t="inlineStr"/>
+      <c r="O7" s="25" t="inlineStr"/>
+      <c r="P7" s="25" t="inlineStr"/>
+      <c r="Q7" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R7" s="28" t="inlineStr">
+      <c r="R7" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S7" s="28" t="inlineStr">
+      <c r="S7" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T7" s="28" t="inlineStr">
+      <c r="T7" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U7" s="28" t="inlineStr"/>
-      <c r="V7" s="28" t="inlineStr">
+      <c r="U7" s="23" t="inlineStr"/>
+      <c r="V7" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W7" s="28" t="inlineStr">
+      <c r="W7" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X7" s="28" t="inlineStr">
+      <c r="X7" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5837,7 +5813,7 @@
           <t>https://images.barcodelookup.com/4378/43786454-1.jpg</t>
         </is>
       </c>
-      <c r="Z7" s="28" t="inlineStr">
+      <c r="Z7" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5847,7 +5823,7 @@
           <t>Darlly Spa Filter C-4401, PRB17.5SF PR, SC726 (Pair)</t>
         </is>
       </c>
-      <c r="AB7" s="28" t="inlineStr">
+      <c r="AB7" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5859,10 +5835,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF7" s="28" t="inlineStr"/>
-      <c r="AG7" s="28" t="inlineStr"/>
-      <c r="AH7" s="28" t="inlineStr"/>
-      <c r="AI7" s="28" t="inlineStr"/>
+      <c r="AF7" s="23" t="inlineStr"/>
+      <c r="AG7" s="23" t="inlineStr"/>
+      <c r="AH7" s="23" t="inlineStr"/>
+      <c r="AI7" s="23" t="inlineStr"/>
     </row>
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
@@ -5880,17 +5856,17 @@
           <t>A replacement spa filter cartridge compatible with Arctic, Beachcomber, Canadian, Hydropool and Jacuzzi spas, sold under cross-reference codes including Unicel C-4950, Pleatco PRB50-IN and Darlly 40506. It keeps hot tub water clean by trapping debris and particles as water cycles through the filtration system.</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5900,71 +5876,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H8" s="28" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I8" s="28" t="inlineStr">
+      <c r="I8" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J8" s="28" t="inlineStr">
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K8" s="28" t="inlineStr">
+      <c r="K8" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L8" s="28" t="inlineStr">
+      <c r="L8" s="23" t="inlineStr">
         <is>
           <t>DAR-FIL-1676</t>
         </is>
       </c>
-      <c r="M8" s="29" t="inlineStr">
+      <c r="M8" s="24" t="inlineStr">
         <is>
           <t>700175991676</t>
         </is>
       </c>
-      <c r="N8" s="30" t="inlineStr"/>
-      <c r="O8" s="30" t="inlineStr"/>
-      <c r="P8" s="30" t="inlineStr"/>
-      <c r="Q8" s="28" t="inlineStr">
+      <c r="N8" s="25" t="inlineStr"/>
+      <c r="O8" s="25" t="inlineStr"/>
+      <c r="P8" s="25" t="inlineStr"/>
+      <c r="Q8" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R8" s="28" t="inlineStr">
+      <c r="R8" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S8" s="28" t="inlineStr">
+      <c r="S8" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T8" s="28" t="inlineStr">
+      <c r="T8" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U8" s="28" t="inlineStr"/>
-      <c r="V8" s="28" t="inlineStr">
+      <c r="U8" s="23" t="inlineStr"/>
+      <c r="V8" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W8" s="28" t="inlineStr">
+      <c r="W8" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X8" s="28" t="inlineStr">
+      <c r="X8" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5974,7 +5950,7 @@
           <t>https://images.barcodelookup.com/4469/44699532-1.jpg</t>
         </is>
       </c>
-      <c r="Z8" s="28" t="inlineStr">
+      <c r="Z8" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5984,7 +5960,7 @@
           <t>Hot Tub Filter Unicel C4950 / C-4950 50' Spa Cartridge Pleatco PRB501N Darlly 40506 for Arctic, Beachcomber, Canadian,…</t>
         </is>
       </c>
-      <c r="AB8" s="28" t="inlineStr">
+      <c r="AB8" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5996,10 +5972,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF8" s="28" t="inlineStr"/>
-      <c r="AG8" s="28" t="inlineStr"/>
-      <c r="AH8" s="28" t="inlineStr"/>
-      <c r="AI8" s="28" t="inlineStr"/>
+      <c r="AF8" s="23" t="inlineStr"/>
+      <c r="AG8" s="23" t="inlineStr"/>
+      <c r="AH8" s="23" t="inlineStr"/>
+      <c r="AI8" s="23" t="inlineStr"/>
     </row>
     <row r="9" ht="76" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
@@ -6017,13 +5993,13 @@
           <t>A square inflatable hot tub for up to four people, with an overall outer diameter of 2.45 m and a structure measuring 1.75 x 1.75 x 0.71 m, built from high-resistance polyester for good rigidity and durability. The packaged weight is 64.92 kg, so you will want a helper on delivery day.</t>
         </is>
       </c>
-      <c r="D9" s="28" t="inlineStr"/>
-      <c r="E9" s="28" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr"/>
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F9" s="28" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -6033,75 +6009,75 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H9" s="28" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I9" s="28" t="inlineStr">
+      <c r="I9" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J9" s="28" t="inlineStr">
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K9" s="28" t="inlineStr">
+      <c r="K9" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L9" s="28" t="inlineStr">
+      <c r="L9" s="23" t="inlineStr">
         <is>
           <t>GEN-SPA-3395</t>
         </is>
       </c>
-      <c r="M9" s="29" t="inlineStr">
+      <c r="M9" s="24" t="inlineStr">
         <is>
           <t>6941057423395</t>
         </is>
       </c>
-      <c r="N9" s="30" t="inlineStr"/>
-      <c r="O9" s="30" t="inlineStr"/>
-      <c r="P9" s="30" t="inlineStr"/>
-      <c r="Q9" s="28" t="inlineStr">
+      <c r="N9" s="25" t="inlineStr"/>
+      <c r="O9" s="25" t="inlineStr"/>
+      <c r="P9" s="25" t="inlineStr"/>
+      <c r="Q9" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R9" s="28" t="inlineStr">
+      <c r="R9" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S9" s="28" t="inlineStr">
+      <c r="S9" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T9" s="28" t="inlineStr">
+      <c r="T9" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U9" s="28" t="inlineStr">
+      <c r="U9" s="23" t="inlineStr">
         <is>
           <t>64920</t>
         </is>
       </c>
-      <c r="V9" s="28" t="inlineStr">
+      <c r="V9" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W9" s="28" t="inlineStr">
+      <c r="W9" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X9" s="28" t="inlineStr">
+      <c r="X9" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6111,7 +6087,7 @@
           <t>https://media.intex.fr/7743-large_default_x2/28464ex-spa-gonflable-calacatta-4-places.jpg</t>
         </is>
       </c>
-      <c r="Z9" s="28" t="inlineStr">
+      <c r="Z9" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6121,7 +6097,7 @@
           <t>Calacatta 4-person Inflatable Spa</t>
         </is>
       </c>
-      <c r="AB9" s="28" t="inlineStr">
+      <c r="AB9" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6133,18 +6109,18 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF9" s="28" t="inlineStr"/>
-      <c r="AG9" s="28" t="inlineStr">
+      <c r="AF9" s="23" t="inlineStr"/>
+      <c r="AG9" s="23" t="inlineStr">
         <is>
           <t>175.0cm</t>
         </is>
       </c>
-      <c r="AH9" s="28" t="inlineStr">
+      <c r="AH9" s="23" t="inlineStr">
         <is>
           <t>175.0cm</t>
         </is>
       </c>
-      <c r="AI9" s="28" t="inlineStr">
+      <c r="AI9" s="23" t="inlineStr">
         <is>
           <t>71.0cm</t>
         </is>
@@ -6166,17 +6142,17 @@
           <t>A 3.0 kg tub of hth stabiliser granules for outdoor swimming pools, used to protect chlorine from UV degradation and extend its effectiveness. A reliable way to get more mileage from your sanitiser on sunny days.</t>
         </is>
       </c>
-      <c r="D10" s="28" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E10" s="28" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F10" s="28" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -6186,75 +6162,75 @@
           <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H10" s="28" t="inlineStr">
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I10" s="28" t="inlineStr">
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J10" s="28" t="inlineStr">
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K10" s="28" t="inlineStr">
+      <c r="K10" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L10" s="28" t="inlineStr">
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t>HTH-CHM-5716</t>
         </is>
       </c>
-      <c r="M10" s="29" t="inlineStr">
+      <c r="M10" s="24" t="inlineStr">
         <is>
           <t>3521686005716</t>
         </is>
       </c>
-      <c r="N10" s="30" t="inlineStr"/>
-      <c r="O10" s="30" t="inlineStr"/>
-      <c r="P10" s="30" t="inlineStr"/>
-      <c r="Q10" s="28" t="inlineStr">
+      <c r="N10" s="25" t="inlineStr"/>
+      <c r="O10" s="25" t="inlineStr"/>
+      <c r="P10" s="25" t="inlineStr"/>
+      <c r="Q10" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R10" s="28" t="inlineStr">
+      <c r="R10" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S10" s="28" t="inlineStr">
+      <c r="S10" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T10" s="28" t="inlineStr">
+      <c r="T10" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U10" s="28" t="inlineStr">
+      <c r="U10" s="23" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="V10" s="28" t="inlineStr">
+      <c r="V10" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W10" s="28" t="inlineStr">
+      <c r="W10" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X10" s="28" t="inlineStr">
+      <c r="X10" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6264,7 +6240,7 @@
           <t>https://images.barcodelookup.com/12027/120276177-1.jpg</t>
         </is>
       </c>
-      <c r="Z10" s="28" t="inlineStr">
+      <c r="Z10" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6274,7 +6250,7 @@
           <t>Hth Stabilizer Granulat 3,0 Kg</t>
         </is>
       </c>
-      <c r="AB10" s="28" t="inlineStr">
+      <c r="AB10" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6286,10 +6262,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF10" s="28" t="inlineStr"/>
-      <c r="AG10" s="28" t="inlineStr"/>
-      <c r="AH10" s="28" t="inlineStr"/>
-      <c r="AI10" s="28" t="inlineStr"/>
+      <c r="AF10" s="23" t="inlineStr"/>
+      <c r="AG10" s="23" t="inlineStr"/>
+      <c r="AH10" s="23" t="inlineStr"/>
+      <c r="AI10" s="23" t="inlineStr"/>
     </row>
     <row r="11" ht="62" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -6307,17 +6283,17 @@
           <t>A 1-litre bottle of hth Spa Antikalk, formulated to prevent and remove limescale in spa and hot tub water. Keeping scale under control helps protect internal components and maintain water clarity.</t>
         </is>
       </c>
-      <c r="D11" s="28" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E11" s="28" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F11" s="28" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -6327,71 +6303,71 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H11" s="28" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I11" s="28" t="inlineStr">
+      <c r="I11" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J11" s="28" t="inlineStr">
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K11" s="28" t="inlineStr">
+      <c r="K11" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L11" s="28" t="inlineStr">
+      <c r="L11" s="23" t="inlineStr">
         <is>
           <t>HTH-SPA-0194</t>
         </is>
       </c>
-      <c r="M11" s="29" t="inlineStr">
+      <c r="M11" s="24" t="inlineStr">
         <is>
           <t>3521684700194</t>
         </is>
       </c>
-      <c r="N11" s="30" t="inlineStr"/>
-      <c r="O11" s="30" t="inlineStr"/>
-      <c r="P11" s="30" t="inlineStr"/>
-      <c r="Q11" s="28" t="inlineStr">
+      <c r="N11" s="25" t="inlineStr"/>
+      <c r="O11" s="25" t="inlineStr"/>
+      <c r="P11" s="25" t="inlineStr"/>
+      <c r="Q11" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R11" s="28" t="inlineStr">
+      <c r="R11" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S11" s="28" t="inlineStr">
+      <c r="S11" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T11" s="28" t="inlineStr">
+      <c r="T11" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U11" s="28" t="inlineStr"/>
-      <c r="V11" s="28" t="inlineStr">
+      <c r="U11" s="23" t="inlineStr"/>
+      <c r="V11" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W11" s="28" t="inlineStr">
+      <c r="W11" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X11" s="28" t="inlineStr">
+      <c r="X11" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6401,7 +6377,7 @@
           <t>https://www.north-spa.de/wp-content/uploads/2025/02/Produktbild-1-hth-SPA-ANTIKALK-1-l-3521684700194-360x360.jpg</t>
         </is>
       </c>
-      <c r="Z11" s="28" t="inlineStr">
+      <c r="Z11" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6411,7 +6387,7 @@
           <t>1 l - hth® Spa ANTIKALK</t>
         </is>
       </c>
-      <c r="AB11" s="28" t="inlineStr">
+      <c r="AB11" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6423,10 +6399,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF11" s="28" t="inlineStr"/>
-      <c r="AG11" s="28" t="inlineStr"/>
-      <c r="AH11" s="28" t="inlineStr"/>
-      <c r="AI11" s="28" t="inlineStr"/>
+      <c r="AF11" s="23" t="inlineStr"/>
+      <c r="AG11" s="23" t="inlineStr"/>
+      <c r="AH11" s="23" t="inlineStr"/>
+      <c r="AI11" s="23" t="inlineStr"/>
     </row>
     <row r="12" ht="62" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
@@ -6444,13 +6420,13 @@
           <t>A round, olive-green inflatable spa designed to seat up to eight people comfortably, with a maximum water temperature of 40°C. Five accessories are included in the box, so there is plenty to get started with straight away.</t>
         </is>
       </c>
-      <c r="D12" s="28" t="inlineStr"/>
-      <c r="E12" s="28" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr"/>
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F12" s="28" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -6460,71 +6436,71 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H12" s="28" t="inlineStr">
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I12" s="28" t="inlineStr">
+      <c r="I12" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J12" s="28" t="inlineStr">
+      <c r="J12" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K12" s="28" t="inlineStr">
+      <c r="K12" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L12" s="28" t="inlineStr">
+      <c r="L12" s="23" t="inlineStr">
         <is>
           <t>GEN-SPA-9274</t>
         </is>
       </c>
-      <c r="M12" s="29" t="inlineStr">
+      <c r="M12" s="24" t="inlineStr">
         <is>
           <t>6941057429274</t>
         </is>
       </c>
-      <c r="N12" s="30" t="inlineStr"/>
-      <c r="O12" s="30" t="inlineStr"/>
-      <c r="P12" s="30" t="inlineStr"/>
-      <c r="Q12" s="28" t="inlineStr">
+      <c r="N12" s="25" t="inlineStr"/>
+      <c r="O12" s="25" t="inlineStr"/>
+      <c r="P12" s="25" t="inlineStr"/>
+      <c r="Q12" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R12" s="28" t="inlineStr">
+      <c r="R12" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S12" s="28" t="inlineStr">
+      <c r="S12" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T12" s="28" t="inlineStr">
+      <c r="T12" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U12" s="28" t="inlineStr"/>
-      <c r="V12" s="28" t="inlineStr">
+      <c r="U12" s="23" t="inlineStr"/>
+      <c r="V12" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W12" s="28" t="inlineStr">
+      <c r="W12" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X12" s="28" t="inlineStr">
+      <c r="X12" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6534,7 +6510,7 @@
           <t>https://media.intex.fr/11990-large_default_x2/28412np-spa-gonflable-olive-8-places.jpg</t>
         </is>
       </c>
-      <c r="Z12" s="28" t="inlineStr">
+      <c r="Z12" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6544,7 +6520,7 @@
           <t>Olive 8-person Inflatable Spa</t>
         </is>
       </c>
-      <c r="AB12" s="28" t="inlineStr">
+      <c r="AB12" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6556,10 +6532,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF12" s="28" t="inlineStr"/>
-      <c r="AG12" s="28" t="inlineStr"/>
-      <c r="AH12" s="28" t="inlineStr"/>
-      <c r="AI12" s="28" t="inlineStr"/>
+      <c r="AF12" s="23" t="inlineStr"/>
+      <c r="AG12" s="23" t="inlineStr"/>
+      <c r="AH12" s="23" t="inlineStr"/>
+      <c r="AI12" s="23" t="inlineStr"/>
     </row>
     <row r="13" ht="62" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
@@ -6577,17 +6553,17 @@
           <t>A Darlly SC750 replacement cartridge filter compatible with Arctic, Fonteyn, Rota, and Strong Spa hot tubs, among others. A straightforward like-for-like swap to keep your spa water flowing clean.</t>
         </is>
       </c>
-      <c r="D13" s="28" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E13" s="28" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F13" s="28" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6597,71 +6573,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H13" s="28" t="inlineStr">
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I13" s="28" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J13" s="28" t="inlineStr">
+      <c r="J13" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K13" s="28" t="inlineStr">
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L13" s="28" t="inlineStr">
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t>DAR-FIL-2116</t>
         </is>
       </c>
-      <c r="M13" s="29" t="inlineStr">
+      <c r="M13" s="24" t="inlineStr">
         <is>
           <t>700175992116</t>
         </is>
       </c>
-      <c r="N13" s="30" t="inlineStr"/>
-      <c r="O13" s="30" t="inlineStr"/>
-      <c r="P13" s="30" t="inlineStr"/>
-      <c r="Q13" s="28" t="inlineStr">
+      <c r="N13" s="25" t="inlineStr"/>
+      <c r="O13" s="25" t="inlineStr"/>
+      <c r="P13" s="25" t="inlineStr"/>
+      <c r="Q13" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R13" s="28" t="inlineStr">
+      <c r="R13" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S13" s="28" t="inlineStr">
+      <c r="S13" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T13" s="28" t="inlineStr">
+      <c r="T13" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U13" s="28" t="inlineStr"/>
-      <c r="V13" s="28" t="inlineStr">
+      <c r="U13" s="23" t="inlineStr"/>
+      <c r="V13" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W13" s="28" t="inlineStr">
+      <c r="W13" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X13" s="28" t="inlineStr">
+      <c r="X13" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6671,7 +6647,7 @@
           <t>https://images.barcodelookup.com/29338/293384728-1.jpg</t>
         </is>
       </c>
-      <c r="Z13" s="28" t="inlineStr">
+      <c r="Z13" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6681,7 +6657,7 @@
           <t>SC750 Filter Replacement Filter Lamellar Filter Arctic Fonteyn Rota Strong Spa - Darlly</t>
         </is>
       </c>
-      <c r="AB13" s="28" t="inlineStr">
+      <c r="AB13" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6693,10 +6669,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF13" s="28" t="inlineStr"/>
-      <c r="AG13" s="28" t="inlineStr"/>
-      <c r="AH13" s="28" t="inlineStr"/>
-      <c r="AI13" s="28" t="inlineStr"/>
+      <c r="AF13" s="23" t="inlineStr"/>
+      <c r="AG13" s="23" t="inlineStr"/>
+      <c r="AH13" s="23" t="inlineStr"/>
+      <c r="AI13" s="23" t="inlineStr"/>
     </row>
     <row r="14" ht="62" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
@@ -6714,17 +6690,17 @@
           <t>SpaBalancer Clean and Refresh is a spa water treatment product supplied with a sprayer for easy application. It is designed to keep spa water fresh and clean as part of a regular maintenance routine.</t>
         </is>
       </c>
-      <c r="D14" s="28" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>SpaBalancer</t>
         </is>
       </c>
-      <c r="E14" s="28" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F14" s="28" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -6734,71 +6710,71 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H14" s="28" t="inlineStr">
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I14" s="28" t="inlineStr">
+      <c r="I14" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J14" s="28" t="inlineStr">
+      <c r="J14" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K14" s="28" t="inlineStr">
+      <c r="K14" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L14" s="28" t="inlineStr">
+      <c r="L14" s="23" t="inlineStr">
         <is>
           <t>SPA-CLN-0117</t>
         </is>
       </c>
-      <c r="M14" s="29" t="inlineStr">
+      <c r="M14" s="24" t="inlineStr">
         <is>
           <t>4260374980117</t>
         </is>
       </c>
-      <c r="N14" s="30" t="inlineStr"/>
-      <c r="O14" s="30" t="inlineStr"/>
-      <c r="P14" s="30" t="inlineStr"/>
-      <c r="Q14" s="28" t="inlineStr">
+      <c r="N14" s="25" t="inlineStr"/>
+      <c r="O14" s="25" t="inlineStr"/>
+      <c r="P14" s="25" t="inlineStr"/>
+      <c r="Q14" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R14" s="28" t="inlineStr">
+      <c r="R14" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S14" s="28" t="inlineStr">
+      <c r="S14" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T14" s="28" t="inlineStr">
+      <c r="T14" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U14" s="28" t="inlineStr"/>
-      <c r="V14" s="28" t="inlineStr">
+      <c r="U14" s="23" t="inlineStr"/>
+      <c r="V14" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W14" s="28" t="inlineStr">
+      <c r="W14" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X14" s="28" t="inlineStr">
+      <c r="X14" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6808,7 +6784,7 @@
           <t>https://www.spabalancer.ch/media/ae/20/d2/1728651174/sb111_clean-refresh_freigestellt.png?ts=1777362921</t>
         </is>
       </c>
-      <c r="Z14" s="28" t="inlineStr">
+      <c r="Z14" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6818,7 +6794,7 @@
           <t>SpaBalancer Clean &amp; Refresh (+ sprayer)</t>
         </is>
       </c>
-      <c r="AB14" s="28" t="inlineStr">
+      <c r="AB14" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6830,10 +6806,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF14" s="28" t="inlineStr"/>
-      <c r="AG14" s="28" t="inlineStr"/>
-      <c r="AH14" s="28" t="inlineStr"/>
-      <c r="AI14" s="28" t="inlineStr"/>
+      <c r="AF14" s="23" t="inlineStr"/>
+      <c r="AG14" s="23" t="inlineStr"/>
+      <c r="AH14" s="23" t="inlineStr"/>
+      <c r="AI14" s="23" t="inlineStr"/>
     </row>
     <row r="15" ht="62" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
@@ -6851,17 +6827,17 @@
           <t>A pack of 500 DPD 1 reagent tablets for use with the Water-ID photometer, measuring free chlorine levels in pool or spa water. Having a full pack to hand means you will not run short mid-season.</t>
         </is>
       </c>
-      <c r="D15" s="28" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>Water-i.d.</t>
         </is>
       </c>
-      <c r="E15" s="28" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F15" s="28" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -6871,79 +6847,79 @@
           <t>test-measure, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H15" s="28" t="inlineStr">
+      <c r="H15" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I15" s="28" t="inlineStr">
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J15" s="28" t="inlineStr">
+      <c r="J15" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K15" s="28" t="inlineStr">
+      <c r="K15" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L15" s="28" t="inlineStr">
+      <c r="L15" s="23" t="inlineStr">
         <is>
           <t>WAT-TST-1702</t>
         </is>
       </c>
-      <c r="M15" s="29" t="inlineStr">
+      <c r="M15" s="24" t="inlineStr">
         <is>
           <t>4260431461702</t>
         </is>
       </c>
-      <c r="N15" s="30" t="inlineStr"/>
-      <c r="O15" s="30" t="inlineStr"/>
-      <c r="P15" s="30" t="inlineStr"/>
-      <c r="Q15" s="28" t="inlineStr">
+      <c r="N15" s="25" t="inlineStr"/>
+      <c r="O15" s="25" t="inlineStr"/>
+      <c r="P15" s="25" t="inlineStr"/>
+      <c r="Q15" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R15" s="28" t="inlineStr">
+      <c r="R15" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S15" s="28" t="inlineStr">
+      <c r="S15" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T15" s="28" t="inlineStr">
+      <c r="T15" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U15" s="28" t="inlineStr"/>
-      <c r="V15" s="28" t="inlineStr">
+      <c r="U15" s="23" t="inlineStr"/>
+      <c r="V15" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W15" s="28" t="inlineStr">
+      <c r="W15" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X15" s="28" t="inlineStr">
+      <c r="X15" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y15" s="18" t="inlineStr"/>
-      <c r="Z15" s="28" t="inlineStr"/>
+      <c r="Z15" s="23" t="inlineStr"/>
       <c r="AA15" s="18" t="inlineStr"/>
-      <c r="AB15" s="28" t="inlineStr">
+      <c r="AB15" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6955,10 +6931,10 @@
           <t>Pool Accessories</t>
         </is>
       </c>
-      <c r="AF15" s="28" t="inlineStr"/>
-      <c r="AG15" s="28" t="inlineStr"/>
-      <c r="AH15" s="28" t="inlineStr"/>
-      <c r="AI15" s="28" t="inlineStr"/>
+      <c r="AF15" s="23" t="inlineStr"/>
+      <c r="AG15" s="23" t="inlineStr"/>
+      <c r="AH15" s="23" t="inlineStr"/>
+      <c r="AI15" s="23" t="inlineStr"/>
     </row>
     <row r="16" ht="62" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
@@ -6976,17 +6952,17 @@
           <t>A pack of 500 Phenol Red reagent tablets compatible with the Water-ID photometer, used for measuring pH levels in pool or spa water. Accurate pH readings are the foundation of balanced, comfortable water.</t>
         </is>
       </c>
-      <c r="D16" s="28" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>Water-i.d.</t>
         </is>
       </c>
-      <c r="E16" s="28" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F16" s="28" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -6996,71 +6972,71 @@
           <t>test-measure, add-on, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H16" s="28" t="inlineStr">
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I16" s="28" t="inlineStr">
+      <c r="I16" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J16" s="28" t="inlineStr">
+      <c r="J16" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K16" s="28" t="inlineStr">
+      <c r="K16" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L16" s="28" t="inlineStr">
+      <c r="L16" s="23" t="inlineStr">
         <is>
           <t>WAT-TST-1801</t>
         </is>
       </c>
-      <c r="M16" s="29" t="inlineStr">
+      <c r="M16" s="24" t="inlineStr">
         <is>
           <t>4260431461801</t>
         </is>
       </c>
-      <c r="N16" s="30" t="inlineStr"/>
-      <c r="O16" s="30" t="inlineStr"/>
-      <c r="P16" s="30" t="inlineStr"/>
-      <c r="Q16" s="28" t="inlineStr">
+      <c r="N16" s="25" t="inlineStr"/>
+      <c r="O16" s="25" t="inlineStr"/>
+      <c r="P16" s="25" t="inlineStr"/>
+      <c r="Q16" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R16" s="28" t="inlineStr">
+      <c r="R16" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S16" s="28" t="inlineStr">
+      <c r="S16" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T16" s="28" t="inlineStr">
+      <c r="T16" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U16" s="28" t="inlineStr"/>
-      <c r="V16" s="28" t="inlineStr">
+      <c r="U16" s="23" t="inlineStr"/>
+      <c r="V16" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W16" s="28" t="inlineStr">
+      <c r="W16" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X16" s="28" t="inlineStr">
+      <c r="X16" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7070,7 +7046,7 @@
           <t>https://www.poolpowershop.de/media/46/63/13/1743521499/phenol-red-testtabletten-fuer-poollab-500-stk.jpg</t>
         </is>
       </c>
-      <c r="Z16" s="28" t="inlineStr">
+      <c r="Z16" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7080,7 +7056,7 @@
           <t>WATER-I.D. Water-ID Reagenzien Phenol Red Photometer 500</t>
         </is>
       </c>
-      <c r="AB16" s="28" t="inlineStr">
+      <c r="AB16" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7092,10 +7068,10 @@
           <t>Pool Accessories</t>
         </is>
       </c>
-      <c r="AF16" s="28" t="inlineStr"/>
-      <c r="AG16" s="28" t="inlineStr"/>
-      <c r="AH16" s="28" t="inlineStr"/>
-      <c r="AI16" s="28" t="inlineStr"/>
+      <c r="AF16" s="23" t="inlineStr"/>
+      <c r="AG16" s="23" t="inlineStr"/>
+      <c r="AH16" s="23" t="inlineStr"/>
+      <c r="AI16" s="23" t="inlineStr"/>
     </row>
     <row r="17" ht="62" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
@@ -7113,17 +7089,17 @@
           <t>An alkaline edge and surround cleaner in a 1-litre bottle, formulated to be gentle on pool liners, foils, and plastic surfaces. It tackles waterline grime without harming the materials it touches.</t>
         </is>
       </c>
-      <c r="D17" s="28" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>Cristal</t>
         </is>
       </c>
-      <c r="E17" s="28" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F17" s="28" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -7133,71 +7109,71 @@
           <t>pool, water-treatment, cleaning, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H17" s="28" t="inlineStr">
+      <c r="H17" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I17" s="28" t="inlineStr">
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J17" s="28" t="inlineStr">
+      <c r="J17" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K17" s="28" t="inlineStr">
+      <c r="K17" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L17" s="28" t="inlineStr">
+      <c r="L17" s="23" t="inlineStr">
         <is>
           <t>CRI-CHM-5212</t>
         </is>
       </c>
-      <c r="M17" s="29" t="inlineStr">
+      <c r="M17" s="24" t="inlineStr">
         <is>
           <t>4002369155212</t>
         </is>
       </c>
-      <c r="N17" s="30" t="inlineStr"/>
-      <c r="O17" s="30" t="inlineStr"/>
-      <c r="P17" s="30" t="inlineStr"/>
-      <c r="Q17" s="28" t="inlineStr">
+      <c r="N17" s="25" t="inlineStr"/>
+      <c r="O17" s="25" t="inlineStr"/>
+      <c r="P17" s="25" t="inlineStr"/>
+      <c r="Q17" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R17" s="28" t="inlineStr">
+      <c r="R17" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S17" s="28" t="inlineStr">
+      <c r="S17" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T17" s="28" t="inlineStr">
+      <c r="T17" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U17" s="28" t="inlineStr"/>
-      <c r="V17" s="28" t="inlineStr">
+      <c r="U17" s="23" t="inlineStr"/>
+      <c r="V17" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W17" s="28" t="inlineStr">
+      <c r="W17" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X17" s="28" t="inlineStr">
+      <c r="X17" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7207,7 +7183,7 @@
           <t>https://images.barcodelookup.com/21057/210579756-1.jpg</t>
         </is>
       </c>
-      <c r="Z17" s="28" t="inlineStr">
+      <c r="Z17" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7217,7 +7193,7 @@
           <t>Cristal Poolpflege CRISTAL Alkaline Edge Cleaner 1,0 l, (Gentle on Materials, for Liners, Plastic Surfaces</t>
         </is>
       </c>
-      <c r="AB17" s="28" t="inlineStr">
+      <c r="AB17" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7229,10 +7205,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF17" s="28" t="inlineStr"/>
-      <c r="AG17" s="28" t="inlineStr"/>
-      <c r="AH17" s="28" t="inlineStr"/>
-      <c r="AI17" s="28" t="inlineStr"/>
+      <c r="AF17" s="23" t="inlineStr"/>
+      <c r="AG17" s="23" t="inlineStr"/>
+      <c r="AH17" s="23" t="inlineStr"/>
+      <c r="AI17" s="23" t="inlineStr"/>
     </row>
     <row r="18" ht="76" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
@@ -7250,17 +7226,17 @@
           <t>A 1-litre pool surface cleaner formulated to remove sunscreen oils and greasy residues from the water surface, designed specifically for warm Mediterranean climates and heavy swimming loads. It keeps the waterline and surface clear without harming pool materials.</t>
         </is>
       </c>
-      <c r="D18" s="28" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F18" s="28" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -7270,71 +7246,71 @@
           <t>pool, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H18" s="28" t="inlineStr">
+      <c r="H18" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I18" s="28" t="inlineStr">
+      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J18" s="28" t="inlineStr">
+      <c r="J18" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K18" s="28" t="inlineStr">
+      <c r="K18" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L18" s="28" t="inlineStr">
+      <c r="L18" s="23" t="inlineStr">
         <is>
           <t>AQU-CLN-0223</t>
         </is>
       </c>
-      <c r="M18" s="29" t="inlineStr">
+      <c r="M18" s="24" t="inlineStr">
         <is>
           <t>5292638000223</t>
         </is>
       </c>
-      <c r="N18" s="30" t="inlineStr"/>
-      <c r="O18" s="30" t="inlineStr"/>
-      <c r="P18" s="30" t="inlineStr"/>
-      <c r="Q18" s="28" t="inlineStr">
+      <c r="N18" s="25" t="inlineStr"/>
+      <c r="O18" s="25" t="inlineStr"/>
+      <c r="P18" s="25" t="inlineStr"/>
+      <c r="Q18" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R18" s="28" t="inlineStr">
+      <c r="R18" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S18" s="28" t="inlineStr">
+      <c r="S18" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T18" s="28" t="inlineStr">
+      <c r="T18" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U18" s="28" t="inlineStr"/>
-      <c r="V18" s="28" t="inlineStr">
+      <c r="U18" s="23" t="inlineStr"/>
+      <c r="V18" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W18" s="28" t="inlineStr">
+      <c r="W18" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X18" s="28" t="inlineStr">
+      <c r="X18" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7344,7 +7320,7 @@
           <t>http://mangas.com.cy/media/products/5292638000223.jpg</t>
         </is>
       </c>
-      <c r="Z18" s="28" t="inlineStr">
+      <c r="Z18" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7354,7 +7330,7 @@
           <t>AQUALITY Pool Cleaner for Greasy Residues 1L</t>
         </is>
       </c>
-      <c r="AB18" s="28" t="inlineStr">
+      <c r="AB18" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7366,10 +7342,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF18" s="28" t="inlineStr"/>
-      <c r="AG18" s="28" t="inlineStr"/>
-      <c r="AH18" s="28" t="inlineStr"/>
-      <c r="AI18" s="28" t="inlineStr"/>
+      <c r="AF18" s="23" t="inlineStr"/>
+      <c r="AG18" s="23" t="inlineStr"/>
+      <c r="AH18" s="23" t="inlineStr"/>
+      <c r="AI18" s="23" t="inlineStr"/>
     </row>
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="18" t="inlineStr">
@@ -7387,17 +7363,17 @@
           <t>California Clear Blue is a super-concentrated, pH-neutral pool clarifier in a 1-litre bottle, using a cationic polymer formula to bind microscopic particles such as dust, pollen, and oils into larger clusters your filter can catch. Non-toxic and biodegradable, it is safe for sand, zeolite, and glass filtration media.</t>
         </is>
       </c>
-      <c r="D19" s="28" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E19" s="28" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F19" s="28" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -7407,71 +7383,71 @@
           <t>pool, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H19" s="28" t="inlineStr">
+      <c r="H19" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I19" s="28" t="inlineStr">
+      <c r="I19" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J19" s="28" t="inlineStr">
+      <c r="J19" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K19" s="28" t="inlineStr">
+      <c r="K19" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L19" s="28" t="inlineStr">
+      <c r="L19" s="23" t="inlineStr">
         <is>
           <t>AQU-CHM-0070</t>
         </is>
       </c>
-      <c r="M19" s="29" t="inlineStr">
+      <c r="M19" s="24" t="inlineStr">
         <is>
           <t>5292638000070</t>
         </is>
       </c>
-      <c r="N19" s="30" t="inlineStr"/>
-      <c r="O19" s="30" t="inlineStr"/>
-      <c r="P19" s="30" t="inlineStr"/>
-      <c r="Q19" s="28" t="inlineStr">
+      <c r="N19" s="25" t="inlineStr"/>
+      <c r="O19" s="25" t="inlineStr"/>
+      <c r="P19" s="25" t="inlineStr"/>
+      <c r="Q19" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R19" s="28" t="inlineStr">
+      <c r="R19" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S19" s="28" t="inlineStr">
+      <c r="S19" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T19" s="28" t="inlineStr">
+      <c r="T19" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U19" s="28" t="inlineStr"/>
-      <c r="V19" s="28" t="inlineStr">
+      <c r="U19" s="23" t="inlineStr"/>
+      <c r="V19" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W19" s="28" t="inlineStr">
+      <c r="W19" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X19" s="28" t="inlineStr">
+      <c r="X19" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7481,7 +7457,7 @@
           <t>https://poolservices.cy/storage/2026/05/California-Clear-Blue-1L-Aquality-2.jpeg</t>
         </is>
       </c>
-      <c r="Z19" s="28" t="inlineStr">
+      <c r="Z19" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7491,7 +7467,7 @@
           <t>Pool Clarifier California Clear Blue Aquality 1L</t>
         </is>
       </c>
-      <c r="AB19" s="28" t="inlineStr">
+      <c r="AB19" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7503,10 +7479,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF19" s="28" t="inlineStr"/>
-      <c r="AG19" s="28" t="inlineStr"/>
-      <c r="AH19" s="28" t="inlineStr"/>
-      <c r="AI19" s="28" t="inlineStr"/>
+      <c r="AF19" s="23" t="inlineStr"/>
+      <c r="AG19" s="23" t="inlineStr"/>
+      <c r="AH19" s="23" t="inlineStr"/>
+      <c r="AI19" s="23" t="inlineStr"/>
     </row>
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="18" t="inlineStr">
@@ -7524,17 +7500,17 @@
           <t>A 1-litre tile and vinyl cleaner for pools, designed to clean pool tile surfaces and vinyl liners. It makes light work of the tidying up that keeps a pool looking its best.</t>
         </is>
       </c>
-      <c r="D20" s="28" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E20" s="28" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F20" s="28" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -7544,71 +7520,71 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H20" s="28" t="inlineStr">
+      <c r="H20" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I20" s="28" t="inlineStr">
+      <c r="I20" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J20" s="28" t="inlineStr">
+      <c r="J20" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K20" s="28" t="inlineStr">
+      <c r="K20" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L20" s="28" t="inlineStr">
+      <c r="L20" s="23" t="inlineStr">
         <is>
           <t>AQU-CLN-0162</t>
         </is>
       </c>
-      <c r="M20" s="29" t="inlineStr">
+      <c r="M20" s="24" t="inlineStr">
         <is>
           <t>5292638000162</t>
         </is>
       </c>
-      <c r="N20" s="30" t="inlineStr"/>
-      <c r="O20" s="30" t="inlineStr"/>
-      <c r="P20" s="30" t="inlineStr"/>
-      <c r="Q20" s="28" t="inlineStr">
+      <c r="N20" s="25" t="inlineStr"/>
+      <c r="O20" s="25" t="inlineStr"/>
+      <c r="P20" s="25" t="inlineStr"/>
+      <c r="Q20" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R20" s="28" t="inlineStr">
+      <c r="R20" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S20" s="28" t="inlineStr">
+      <c r="S20" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T20" s="28" t="inlineStr">
+      <c r="T20" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U20" s="28" t="inlineStr"/>
-      <c r="V20" s="28" t="inlineStr">
+      <c r="U20" s="23" t="inlineStr"/>
+      <c r="V20" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W20" s="28" t="inlineStr">
+      <c r="W20" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X20" s="28" t="inlineStr">
+      <c r="X20" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7618,7 +7594,7 @@
           <t>http://mangas.com.cy/media/products/5292638000162.jpg</t>
         </is>
       </c>
-      <c r="Z20" s="28" t="inlineStr">
+      <c r="Z20" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7628,7 +7604,7 @@
           <t>AQUALITY Magic tile 4 vinyl cleaner 1L</t>
         </is>
       </c>
-      <c r="AB20" s="28" t="inlineStr">
+      <c r="AB20" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7640,10 +7616,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF20" s="28" t="inlineStr"/>
-      <c r="AG20" s="28" t="inlineStr"/>
-      <c r="AH20" s="28" t="inlineStr"/>
-      <c r="AI20" s="28" t="inlineStr"/>
+      <c r="AF20" s="23" t="inlineStr"/>
+      <c r="AG20" s="23" t="inlineStr"/>
+      <c r="AH20" s="23" t="inlineStr"/>
+      <c r="AI20" s="23" t="inlineStr"/>
     </row>
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
@@ -7661,17 +7637,17 @@
           <t>A 1-litre spa and pool water clarifier from Bayzid, formulated to clear cloudy or turbid water. A handy bottle to reach for whenever the water loses its sparkle.</t>
         </is>
       </c>
-      <c r="D21" s="28" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F21" s="28" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -7681,71 +7657,71 @@
           <t>spa-hot-tub, pool, water-treatment, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H21" s="28" t="inlineStr">
+      <c r="H21" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I21" s="28" t="inlineStr">
+      <c r="I21" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J21" s="28" t="inlineStr">
+      <c r="J21" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K21" s="28" t="inlineStr">
+      <c r="K21" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L21" s="28" t="inlineStr">
+      <c r="L21" s="23" t="inlineStr">
         <is>
           <t>HFE-SPA-7202</t>
         </is>
       </c>
-      <c r="M21" s="29" t="inlineStr">
+      <c r="M21" s="24" t="inlineStr">
         <is>
           <t>4250463127202</t>
         </is>
       </c>
-      <c r="N21" s="30" t="inlineStr"/>
-      <c r="O21" s="30" t="inlineStr"/>
-      <c r="P21" s="30" t="inlineStr"/>
-      <c r="Q21" s="28" t="inlineStr">
+      <c r="N21" s="25" t="inlineStr"/>
+      <c r="O21" s="25" t="inlineStr"/>
+      <c r="P21" s="25" t="inlineStr"/>
+      <c r="Q21" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R21" s="28" t="inlineStr">
+      <c r="R21" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S21" s="28" t="inlineStr">
+      <c r="S21" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T21" s="28" t="inlineStr">
+      <c r="T21" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U21" s="28" t="inlineStr"/>
-      <c r="V21" s="28" t="inlineStr">
+      <c r="U21" s="23" t="inlineStr"/>
+      <c r="V21" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W21" s="28" t="inlineStr">
+      <c r="W21" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X21" s="28" t="inlineStr">
+      <c r="X21" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7755,7 +7731,7 @@
           <t>https://hoefer-shop.com/cdn/shop/files/1x1L-BAYZID-Spa-Poolclear-v1-RS_1.jpg?v=1785600487&amp;width=800</t>
         </is>
       </c>
-      <c r="Z21" s="28" t="inlineStr">
+      <c r="Z21" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7765,7 +7741,7 @@
           <t>Höfer Chemie GmbH Pool Care 1 L BAYZID® SPA Poolclear Turbidity Remover</t>
         </is>
       </c>
-      <c r="AB21" s="28" t="inlineStr">
+      <c r="AB21" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7777,10 +7753,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF21" s="28" t="inlineStr"/>
-      <c r="AG21" s="28" t="inlineStr"/>
-      <c r="AH21" s="28" t="inlineStr"/>
-      <c r="AI21" s="28" t="inlineStr"/>
+      <c r="AF21" s="23" t="inlineStr"/>
+      <c r="AG21" s="23" t="inlineStr"/>
+      <c r="AH21" s="23" t="inlineStr"/>
+      <c r="AI21" s="23" t="inlineStr"/>
     </row>
     <row r="22" ht="62" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
@@ -7798,17 +7774,17 @@
           <t>A 1-litre bottle of hydrogen peroxide at 11.9% concentration, suitable for disinfection and water treatment applications. A straightforward chemical solution that keeps things clean without fuss.</t>
         </is>
       </c>
-      <c r="D22" s="28" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E22" s="28" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F22" s="28" t="inlineStr">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -7818,71 +7794,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H22" s="28" t="inlineStr">
+      <c r="H22" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I22" s="28" t="inlineStr">
+      <c r="I22" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J22" s="28" t="inlineStr">
+      <c r="J22" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K22" s="28" t="inlineStr">
+      <c r="K22" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L22" s="28" t="inlineStr">
+      <c r="L22" s="23" t="inlineStr">
         <is>
           <t>HFE-CHM-6788</t>
         </is>
       </c>
-      <c r="M22" s="29" t="inlineStr">
+      <c r="M22" s="24" t="inlineStr">
         <is>
           <t>4250463106788</t>
         </is>
       </c>
-      <c r="N22" s="30" t="inlineStr"/>
-      <c r="O22" s="30" t="inlineStr"/>
-      <c r="P22" s="30" t="inlineStr"/>
-      <c r="Q22" s="28" t="inlineStr">
+      <c r="N22" s="25" t="inlineStr"/>
+      <c r="O22" s="25" t="inlineStr"/>
+      <c r="P22" s="25" t="inlineStr"/>
+      <c r="Q22" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R22" s="28" t="inlineStr">
+      <c r="R22" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S22" s="28" t="inlineStr">
+      <c r="S22" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T22" s="28" t="inlineStr">
+      <c r="T22" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U22" s="28" t="inlineStr"/>
-      <c r="V22" s="28" t="inlineStr">
+      <c r="U22" s="23" t="inlineStr"/>
+      <c r="V22" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W22" s="28" t="inlineStr">
+      <c r="W22" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X22" s="28" t="inlineStr">
+      <c r="X22" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7892,7 +7868,7 @@
           <t>https://hoefer-shop.com/cdn/shop/files/1x1L-Wasserstoffperoxid-Flasche-hinten-26.jpg?v=1783777627&amp;width=1000</t>
         </is>
       </c>
-      <c r="Z22" s="28" t="inlineStr">
+      <c r="Z22" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7902,7 +7878,7 @@
           <t>HÖFER CHEMIE GMBH 1 l Hydrogen Peroxide 11,9%</t>
         </is>
       </c>
-      <c r="AB22" s="28" t="inlineStr">
+      <c r="AB22" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7914,10 +7890,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF22" s="28" t="inlineStr"/>
-      <c r="AG22" s="28" t="inlineStr"/>
-      <c r="AH22" s="28" t="inlineStr"/>
-      <c r="AI22" s="28" t="inlineStr"/>
+      <c r="AF22" s="23" t="inlineStr"/>
+      <c r="AG22" s="23" t="inlineStr"/>
+      <c r="AH22" s="23" t="inlineStr"/>
+      <c r="AI22" s="23" t="inlineStr"/>
     </row>
     <row r="23" ht="62" customHeight="1">
       <c r="A23" s="18" t="inlineStr">
@@ -7935,17 +7911,17 @@
           <t>A 4.5 kg pack of chlorine stabilizer for swimming pools, used to protect chlorine from UV degradation and extend its effectiveness in the water. Steady chemistry for a pool that earns its keep.</t>
         </is>
       </c>
-      <c r="D23" s="28" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>AstralPool</t>
         </is>
       </c>
-      <c r="E23" s="28" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F23" s="28" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -7955,83 +7931,83 @@
           <t>water-treatment, repeat-purchase, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H23" s="28" t="inlineStr">
+      <c r="H23" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I23" s="28" t="inlineStr">
+      <c r="I23" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J23" s="28" t="inlineStr">
+      <c r="J23" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K23" s="28" t="inlineStr">
+      <c r="K23" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L23" s="28" t="inlineStr">
+      <c r="L23" s="23" t="inlineStr">
         <is>
           <t>AST-CHM-0626</t>
         </is>
       </c>
-      <c r="M23" s="29" t="inlineStr">
+      <c r="M23" s="24" t="inlineStr">
         <is>
           <t>8432611960626</t>
         </is>
       </c>
-      <c r="N23" s="30" t="inlineStr"/>
-      <c r="O23" s="30" t="inlineStr"/>
-      <c r="P23" s="30" t="inlineStr"/>
-      <c r="Q23" s="28" t="inlineStr">
+      <c r="N23" s="25" t="inlineStr"/>
+      <c r="O23" s="25" t="inlineStr"/>
+      <c r="P23" s="25" t="inlineStr"/>
+      <c r="Q23" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R23" s="28" t="inlineStr">
+      <c r="R23" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S23" s="28" t="inlineStr">
+      <c r="S23" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T23" s="28" t="inlineStr">
+      <c r="T23" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U23" s="28" t="inlineStr">
+      <c r="U23" s="23" t="inlineStr">
         <is>
           <t>4500</t>
         </is>
       </c>
-      <c r="V23" s="28" t="inlineStr">
+      <c r="V23" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W23" s="28" t="inlineStr">
+      <c r="W23" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X23" s="28" t="inlineStr">
+      <c r="X23" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y23" s="18" t="inlineStr"/>
-      <c r="Z23" s="28" t="inlineStr"/>
+      <c r="Z23" s="23" t="inlineStr"/>
       <c r="AA23" s="18" t="inlineStr"/>
-      <c r="AB23" s="28" t="inlineStr">
+      <c r="AB23" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8043,10 +8019,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF23" s="28" t="inlineStr"/>
-      <c r="AG23" s="28" t="inlineStr"/>
-      <c r="AH23" s="28" t="inlineStr"/>
-      <c r="AI23" s="28" t="inlineStr"/>
+      <c r="AF23" s="23" t="inlineStr"/>
+      <c r="AG23" s="23" t="inlineStr"/>
+      <c r="AH23" s="23" t="inlineStr"/>
+      <c r="AI23" s="23" t="inlineStr"/>
     </row>
     <row r="24" ht="62" customHeight="1">
       <c r="A24" s="18" t="inlineStr">
@@ -8064,17 +8040,17 @@
           <t>UltraShock is a pool and spa shock treatment from SpaBalancer, designed to rapidly oxidise contaminants and restore water clarity. A quick reset for water that needs a little more persuasion.</t>
         </is>
       </c>
-      <c r="D24" s="28" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>SpaBalancer</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F24" s="28" t="inlineStr">
+      <c r="F24" s="23" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8084,71 +8060,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H24" s="28" t="inlineStr">
+      <c r="H24" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I24" s="28" t="inlineStr">
+      <c r="I24" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J24" s="28" t="inlineStr">
+      <c r="J24" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K24" s="28" t="inlineStr">
+      <c r="K24" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L24" s="28" t="inlineStr">
+      <c r="L24" s="23" t="inlineStr">
         <is>
           <t>SPA-CHM-0025</t>
         </is>
       </c>
-      <c r="M24" s="29" t="inlineStr">
+      <c r="M24" s="24" t="inlineStr">
         <is>
           <t>4260374980025</t>
         </is>
       </c>
-      <c r="N24" s="30" t="inlineStr"/>
-      <c r="O24" s="30" t="inlineStr"/>
-      <c r="P24" s="30" t="inlineStr"/>
-      <c r="Q24" s="28" t="inlineStr">
+      <c r="N24" s="25" t="inlineStr"/>
+      <c r="O24" s="25" t="inlineStr"/>
+      <c r="P24" s="25" t="inlineStr"/>
+      <c r="Q24" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R24" s="28" t="inlineStr">
+      <c r="R24" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S24" s="28" t="inlineStr">
+      <c r="S24" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T24" s="28" t="inlineStr">
+      <c r="T24" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U24" s="28" t="inlineStr"/>
-      <c r="V24" s="28" t="inlineStr">
+      <c r="U24" s="23" t="inlineStr"/>
+      <c r="V24" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W24" s="28" t="inlineStr">
+      <c r="W24" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X24" s="28" t="inlineStr">
+      <c r="X24" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8158,7 +8134,7 @@
           <t>https://images.barcodelookup.com/16704/167043133-1.jpg</t>
         </is>
       </c>
-      <c r="Z24" s="28" t="inlineStr">
+      <c r="Z24" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8168,7 +8144,7 @@
           <t>SpaBalancer UltraShock</t>
         </is>
       </c>
-      <c r="AB24" s="28" t="inlineStr">
+      <c r="AB24" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8180,10 +8156,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF24" s="28" t="inlineStr"/>
-      <c r="AG24" s="28" t="inlineStr"/>
-      <c r="AH24" s="28" t="inlineStr"/>
-      <c r="AI24" s="28" t="inlineStr"/>
+      <c r="AF24" s="23" t="inlineStr"/>
+      <c r="AG24" s="23" t="inlineStr"/>
+      <c r="AH24" s="23" t="inlineStr"/>
+      <c r="AI24" s="23" t="inlineStr"/>
     </row>
     <row r="25" ht="76" customHeight="1">
       <c r="A25" s="18" t="inlineStr">
@@ -8201,13 +8177,13 @@
           <t>A patented foam rubber eraser for cleaning pool surfaces, particularly suited to waterline stains on liner and vitreous ceramic finishes, and it works without detergents or chemicals. Each box contains 3 sponges, which harden when wet to scrub effectively while remaining soft and flexible in use.</t>
         </is>
       </c>
-      <c r="D25" s="28" t="inlineStr"/>
-      <c r="E25" s="28" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr"/>
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F25" s="28" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8217,71 +8193,71 @@
           <t>pool, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H25" s="28" t="inlineStr">
+      <c r="H25" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I25" s="28" t="inlineStr">
+      <c r="I25" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J25" s="28" t="inlineStr">
+      <c r="J25" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K25" s="28" t="inlineStr">
+      <c r="K25" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L25" s="28" t="inlineStr">
+      <c r="L25" s="23" t="inlineStr">
         <is>
           <t>GEN-CLN-0062</t>
         </is>
       </c>
-      <c r="M25" s="29" t="inlineStr">
+      <c r="M25" s="24" t="inlineStr">
         <is>
           <t>3760015880062</t>
         </is>
       </c>
-      <c r="N25" s="30" t="inlineStr"/>
-      <c r="O25" s="30" t="inlineStr"/>
-      <c r="P25" s="30" t="inlineStr"/>
-      <c r="Q25" s="28" t="inlineStr">
+      <c r="N25" s="25" t="inlineStr"/>
+      <c r="O25" s="25" t="inlineStr"/>
+      <c r="P25" s="25" t="inlineStr"/>
+      <c r="Q25" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R25" s="28" t="inlineStr">
+      <c r="R25" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S25" s="28" t="inlineStr">
+      <c r="S25" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T25" s="28" t="inlineStr">
+      <c r="T25" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U25" s="28" t="inlineStr"/>
-      <c r="V25" s="28" t="inlineStr">
+      <c r="U25" s="23" t="inlineStr"/>
+      <c r="V25" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W25" s="28" t="inlineStr">
+      <c r="W25" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X25" s="28" t="inlineStr">
+      <c r="X25" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8291,7 +8267,7 @@
           <t>https://www.piscinarium.com/2908-thickbox_default/pool-gom-magic-rubber-eraser.jpg</t>
         </is>
       </c>
-      <c r="Z25" s="28" t="inlineStr">
+      <c r="Z25" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8301,7 +8277,7 @@
           <t>Pool'Gom Magic Rubber Eraser</t>
         </is>
       </c>
-      <c r="AB25" s="28" t="inlineStr">
+      <c r="AB25" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8313,10 +8289,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF25" s="28" t="inlineStr"/>
-      <c r="AG25" s="28" t="inlineStr"/>
-      <c r="AH25" s="28" t="inlineStr"/>
-      <c r="AI25" s="28" t="inlineStr"/>
+      <c r="AF25" s="23" t="inlineStr"/>
+      <c r="AG25" s="23" t="inlineStr"/>
+      <c r="AH25" s="23" t="inlineStr"/>
+      <c r="AI25" s="23" t="inlineStr"/>
     </row>
     <row r="26" ht="62" customHeight="1">
       <c r="A26" s="18" t="inlineStr">
@@ -8334,13 +8310,13 @@
           <t>Spa Industries Europe appears to be a brand or supplier name rather than a specific product, so no product details can be confirmed. For accurate information, please check the full product listing.</t>
         </is>
       </c>
-      <c r="D26" s="28" t="inlineStr"/>
-      <c r="E26" s="28" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr"/>
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F26" s="28" t="inlineStr">
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -8350,79 +8326,79 @@
           <t>spa-hot-tub, considered-purchase, multi-source-confirmed, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H26" s="28" t="inlineStr">
+      <c r="H26" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I26" s="28" t="inlineStr">
+      <c r="I26" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J26" s="28" t="inlineStr">
+      <c r="J26" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K26" s="28" t="inlineStr">
+      <c r="K26" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L26" s="28" t="inlineStr">
+      <c r="L26" s="23" t="inlineStr">
         <is>
           <t>GEN-SPA-1968</t>
         </is>
       </c>
-      <c r="M26" s="29" t="inlineStr">
+      <c r="M26" s="24" t="inlineStr">
         <is>
           <t>5425021871968</t>
         </is>
       </c>
-      <c r="N26" s="30" t="inlineStr"/>
-      <c r="O26" s="30" t="inlineStr"/>
-      <c r="P26" s="30" t="inlineStr"/>
-      <c r="Q26" s="28" t="inlineStr">
+      <c r="N26" s="25" t="inlineStr"/>
+      <c r="O26" s="25" t="inlineStr"/>
+      <c r="P26" s="25" t="inlineStr"/>
+      <c r="Q26" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R26" s="28" t="inlineStr">
+      <c r="R26" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S26" s="28" t="inlineStr">
+      <c r="S26" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T26" s="28" t="inlineStr">
+      <c r="T26" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U26" s="28" t="inlineStr"/>
-      <c r="V26" s="28" t="inlineStr">
+      <c r="U26" s="23" t="inlineStr"/>
+      <c r="V26" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W26" s="28" t="inlineStr">
+      <c r="W26" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X26" s="28" t="inlineStr">
+      <c r="X26" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y26" s="18" t="inlineStr"/>
-      <c r="Z26" s="28" t="inlineStr"/>
+      <c r="Z26" s="23" t="inlineStr"/>
       <c r="AA26" s="18" t="inlineStr"/>
-      <c r="AB26" s="28" t="inlineStr">
+      <c r="AB26" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8434,10 +8410,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF26" s="28" t="inlineStr"/>
-      <c r="AG26" s="28" t="inlineStr"/>
-      <c r="AH26" s="28" t="inlineStr"/>
-      <c r="AI26" s="28" t="inlineStr"/>
+      <c r="AF26" s="23" t="inlineStr"/>
+      <c r="AG26" s="23" t="inlineStr"/>
+      <c r="AH26" s="23" t="inlineStr"/>
+      <c r="AI26" s="23" t="inlineStr"/>
     </row>
     <row r="27" ht="62" customHeight="1">
       <c r="A27" s="18" t="inlineStr">
@@ -8455,17 +8431,17 @@
           <t>A 1-litre high-concentrate sauna cleaner with eucalyptus fragrance, formulated as a deep-cleaning base cleaner for sauna surfaces. The concentrated formula means a little goes a long way, with a fresh scent to match.</t>
         </is>
       </c>
-      <c r="D27" s="28" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E27" s="28" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F27" s="28" t="inlineStr">
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8475,79 +8451,79 @@
           <t>cleaning, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H27" s="28" t="inlineStr">
+      <c r="H27" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I27" s="28" t="inlineStr">
+      <c r="I27" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J27" s="28" t="inlineStr">
+      <c r="J27" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K27" s="28" t="inlineStr">
+      <c r="K27" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L27" s="28" t="inlineStr">
+      <c r="L27" s="23" t="inlineStr">
         <is>
           <t>HFE-CLN-7004</t>
         </is>
       </c>
-      <c r="M27" s="29" t="inlineStr">
+      <c r="M27" s="24" t="inlineStr">
         <is>
           <t>4250463127004</t>
         </is>
       </c>
-      <c r="N27" s="30" t="inlineStr"/>
-      <c r="O27" s="30" t="inlineStr"/>
-      <c r="P27" s="30" t="inlineStr"/>
-      <c r="Q27" s="28" t="inlineStr">
+      <c r="N27" s="25" t="inlineStr"/>
+      <c r="O27" s="25" t="inlineStr"/>
+      <c r="P27" s="25" t="inlineStr"/>
+      <c r="Q27" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R27" s="28" t="inlineStr">
+      <c r="R27" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S27" s="28" t="inlineStr">
+      <c r="S27" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T27" s="28" t="inlineStr">
+      <c r="T27" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U27" s="28" t="inlineStr"/>
-      <c r="V27" s="28" t="inlineStr">
+      <c r="U27" s="23" t="inlineStr"/>
+      <c r="V27" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W27" s="28" t="inlineStr">
+      <c r="W27" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X27" s="28" t="inlineStr">
+      <c r="X27" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y27" s="18" t="inlineStr"/>
-      <c r="Z27" s="28" t="inlineStr"/>
+      <c r="Z27" s="23" t="inlineStr"/>
       <c r="AA27" s="18" t="inlineStr"/>
-      <c r="AB27" s="28" t="inlineStr">
+      <c r="AB27" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8559,10 +8535,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF27" s="28" t="inlineStr"/>
-      <c r="AG27" s="28" t="inlineStr"/>
-      <c r="AH27" s="28" t="inlineStr"/>
-      <c r="AI27" s="28" t="inlineStr"/>
+      <c r="AF27" s="23" t="inlineStr"/>
+      <c r="AG27" s="23" t="inlineStr"/>
+      <c r="AH27" s="23" t="inlineStr"/>
+      <c r="AI27" s="23" t="inlineStr"/>
     </row>
     <row r="28" ht="76" customHeight="1">
       <c r="A28" s="18" t="inlineStr">
@@ -8580,17 +8556,17 @@
           <t>This HTH spa cleaner removes mineral deposits such as limescale and rust, and cleans and polishes aluminium, chrome, stainless steel, and enamel surfaces with a pleasant pine fragrance. It has a high concentration of active ingredients and is recommended for periodic maintenance cleaning.</t>
         </is>
       </c>
-      <c r="D28" s="28" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E28" s="28" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F28" s="28" t="inlineStr">
+      <c r="F28" s="23" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8600,71 +8576,71 @@
           <t>spa-hot-tub, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H28" s="28" t="inlineStr">
+      <c r="H28" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I28" s="28" t="inlineStr">
+      <c r="I28" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J28" s="28" t="inlineStr">
+      <c r="J28" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K28" s="28" t="inlineStr">
+      <c r="K28" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L28" s="28" t="inlineStr">
+      <c r="L28" s="23" t="inlineStr">
         <is>
           <t>HTH-CLN-0178</t>
         </is>
       </c>
-      <c r="M28" s="29" t="inlineStr">
+      <c r="M28" s="24" t="inlineStr">
         <is>
           <t>3521686010178</t>
         </is>
       </c>
-      <c r="N28" s="30" t="inlineStr"/>
-      <c r="O28" s="30" t="inlineStr"/>
-      <c r="P28" s="30" t="inlineStr"/>
-      <c r="Q28" s="28" t="inlineStr">
+      <c r="N28" s="25" t="inlineStr"/>
+      <c r="O28" s="25" t="inlineStr"/>
+      <c r="P28" s="25" t="inlineStr"/>
+      <c r="Q28" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R28" s="28" t="inlineStr">
+      <c r="R28" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S28" s="28" t="inlineStr">
+      <c r="S28" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T28" s="28" t="inlineStr">
+      <c r="T28" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U28" s="28" t="inlineStr"/>
-      <c r="V28" s="28" t="inlineStr">
+      <c r="U28" s="23" t="inlineStr"/>
+      <c r="V28" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W28" s="28" t="inlineStr">
+      <c r="W28" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X28" s="28" t="inlineStr">
+      <c r="X28" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8674,7 +8650,7 @@
           <t>https://www.cdiscount.com/pdt2/0/5/1/1/700x700/auc2009356289051/rw/hth-spa-nettoyant-spa-3521686010178.jpg</t>
         </is>
       </c>
-      <c r="Z28" s="28" t="inlineStr">
+      <c r="Z28" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8684,7 +8660,7 @@
           <t>HTH Spa Spa Cleaner</t>
         </is>
       </c>
-      <c r="AB28" s="28" t="inlineStr">
+      <c r="AB28" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8696,10 +8672,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF28" s="28" t="inlineStr"/>
-      <c r="AG28" s="28" t="inlineStr"/>
-      <c r="AH28" s="28" t="inlineStr"/>
-      <c r="AI28" s="28" t="inlineStr"/>
+      <c r="AF28" s="23" t="inlineStr"/>
+      <c r="AG28" s="23" t="inlineStr"/>
+      <c r="AH28" s="23" t="inlineStr"/>
+      <c r="AI28" s="23" t="inlineStr"/>
     </row>
     <row r="29" ht="62" customHeight="1">
       <c r="A29" s="18" t="inlineStr">
@@ -8717,13 +8693,13 @@
           <t>A 25 kg sack of pure boiling salt (minimum 99.6% NaCl) without an anti-caking agent, meeting EN 973 Type A standard and suitable for use in pool salt electrolysis systems. Not intended for human consumption or animal feed.</t>
         </is>
       </c>
-      <c r="D29" s="28" t="inlineStr"/>
-      <c r="E29" s="28" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr"/>
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F29" s="28" t="inlineStr">
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>Pool salt</t>
         </is>
@@ -8733,75 +8709,75 @@
           <t>pool, salt, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H29" s="28" t="inlineStr">
+      <c r="H29" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I29" s="28" t="inlineStr">
+      <c r="I29" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J29" s="28" t="inlineStr">
+      <c r="J29" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K29" s="28" t="inlineStr">
+      <c r="K29" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L29" s="28" t="inlineStr">
+      <c r="L29" s="23" t="inlineStr">
         <is>
           <t>GEN-SLT-6110</t>
         </is>
       </c>
-      <c r="M29" s="29" t="inlineStr">
+      <c r="M29" s="24" t="inlineStr">
         <is>
           <t>9001880976110</t>
         </is>
       </c>
-      <c r="N29" s="30" t="inlineStr"/>
-      <c r="O29" s="30" t="inlineStr"/>
-      <c r="P29" s="30" t="inlineStr"/>
-      <c r="Q29" s="28" t="inlineStr">
+      <c r="N29" s="25" t="inlineStr"/>
+      <c r="O29" s="25" t="inlineStr"/>
+      <c r="P29" s="25" t="inlineStr"/>
+      <c r="Q29" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R29" s="28" t="inlineStr">
+      <c r="R29" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S29" s="28" t="inlineStr">
+      <c r="S29" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T29" s="28" t="inlineStr">
+      <c r="T29" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U29" s="28" t="inlineStr">
+      <c r="U29" s="23" t="inlineStr">
         <is>
           <t>25000</t>
         </is>
       </c>
-      <c r="V29" s="28" t="inlineStr">
+      <c r="V29" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W29" s="28" t="inlineStr">
+      <c r="W29" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X29" s="28" t="inlineStr">
+      <c r="X29" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8811,7 +8787,7 @@
           <t>http://altruan.com/cdn/shop/files/SalinenPoolSalz25kgSack.png?v=1778597596</t>
         </is>
       </c>
-      <c r="Z29" s="28" t="inlineStr">
+      <c r="Z29" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8821,7 +8797,7 @@
           <t>Saline pool salt pure boiling salt without separating agent | Sack (25 kg)</t>
         </is>
       </c>
-      <c r="AB29" s="28" t="inlineStr">
+      <c r="AB29" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8833,14 +8809,14 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF29" s="28" t="inlineStr">
+      <c r="AF29" s="23" t="inlineStr">
         <is>
           <t>Composition: Siedesalz (min. 99.6% NaCl) 100%; Separant/sodium ferrocyanide 4.0–12.0 mg/kg | Grain: &gt;0.63 mm approx. 20%, 0.2–0.63 mm approx. 75%, &lt;0.2 mm approx. 5% | Moisture: &lt;0.08%</t>
         </is>
       </c>
-      <c r="AG29" s="28" t="inlineStr"/>
-      <c r="AH29" s="28" t="inlineStr"/>
-      <c r="AI29" s="28" t="inlineStr"/>
+      <c r="AG29" s="23" t="inlineStr"/>
+      <c r="AH29" s="23" t="inlineStr"/>
+      <c r="AI29" s="23" t="inlineStr"/>
     </row>
     <row r="30" ht="76" customHeight="1">
       <c r="A30" s="18" t="inlineStr">
@@ -8858,17 +8834,17 @@
           <t>A cordless robotic pool cleaner that scrubs both floors and walls automatically, using WavePath navigation to map and cover the pool efficiently. Built-in high-performance filtration and smart control make it a hands-off solution for keeping pool water clear.</t>
         </is>
       </c>
-      <c r="D30" s="28" t="inlineStr">
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>Aiper</t>
         </is>
       </c>
-      <c r="E30" s="28" t="inlineStr">
+      <c r="E30" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F30" s="28" t="inlineStr">
+      <c r="F30" s="23" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -8878,71 +8854,71 @@
           <t>pool, cleaning, robot-cleaner, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H30" s="28" t="inlineStr">
+      <c r="H30" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I30" s="28" t="inlineStr">
+      <c r="I30" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J30" s="28" t="inlineStr">
+      <c r="J30" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K30" s="28" t="inlineStr">
+      <c r="K30" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L30" s="28" t="inlineStr">
+      <c r="L30" s="23" t="inlineStr">
         <is>
           <t>AIP-ROB-4940</t>
         </is>
       </c>
-      <c r="M30" s="29" t="inlineStr">
+      <c r="M30" s="24" t="inlineStr">
         <is>
           <t>6977676344940</t>
         </is>
       </c>
-      <c r="N30" s="30" t="inlineStr"/>
-      <c r="O30" s="30" t="inlineStr"/>
-      <c r="P30" s="30" t="inlineStr"/>
-      <c r="Q30" s="28" t="inlineStr">
+      <c r="N30" s="25" t="inlineStr"/>
+      <c r="O30" s="25" t="inlineStr"/>
+      <c r="P30" s="25" t="inlineStr"/>
+      <c r="Q30" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R30" s="28" t="inlineStr">
+      <c r="R30" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S30" s="28" t="inlineStr">
+      <c r="S30" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T30" s="28" t="inlineStr">
+      <c r="T30" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U30" s="28" t="inlineStr"/>
-      <c r="V30" s="28" t="inlineStr">
+      <c r="U30" s="23" t="inlineStr"/>
+      <c r="V30" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W30" s="28" t="inlineStr">
+      <c r="W30" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X30" s="28" t="inlineStr">
+      <c r="X30" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8952,7 +8928,7 @@
           <t>https://images.barcodelookup.com/176692/1766920801-1.jpg</t>
         </is>
       </c>
-      <c r="Z30" s="28" t="inlineStr">
+      <c r="Z30" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8962,7 +8938,7 @@
           <t>AIPER Scuba S3 Cordless Pool Robot, Automatic Floor and Wall Cleaning, WavePath™ Navigation, High-Performance Filtration…</t>
         </is>
       </c>
-      <c r="AB30" s="28" t="inlineStr">
+      <c r="AB30" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8974,10 +8950,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF30" s="28" t="inlineStr"/>
-      <c r="AG30" s="28" t="inlineStr"/>
-      <c r="AH30" s="28" t="inlineStr"/>
-      <c r="AI30" s="28" t="inlineStr"/>
+      <c r="AF30" s="23" t="inlineStr"/>
+      <c r="AG30" s="23" t="inlineStr"/>
+      <c r="AH30" s="23" t="inlineStr"/>
+      <c r="AI30" s="23" t="inlineStr"/>
     </row>
     <row r="31" ht="62" customHeight="1">
       <c r="A31" s="18" t="inlineStr">
@@ -8995,13 +8971,13 @@
           <t>The Scuba L1 EU is a pool cleaning device, though no further specific details about its features, dimensions, or mechanism are available from the product name alone. Buyers should refer to the full product listing for specifications.</t>
         </is>
       </c>
-      <c r="D31" s="28" t="inlineStr"/>
-      <c r="E31" s="28" t="inlineStr">
+      <c r="D31" s="23" t="inlineStr"/>
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F31" s="28" t="inlineStr">
+      <c r="F31" s="23" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9011,71 +8987,71 @@
           <t>robot-cleaner, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H31" s="28" t="inlineStr">
+      <c r="H31" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I31" s="28" t="inlineStr">
+      <c r="I31" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J31" s="28" t="inlineStr">
+      <c r="J31" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K31" s="28" t="inlineStr">
+      <c r="K31" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L31" s="28" t="inlineStr">
+      <c r="L31" s="23" t="inlineStr">
         <is>
           <t>GEN-ROB-5137</t>
         </is>
       </c>
-      <c r="M31" s="29" t="inlineStr">
+      <c r="M31" s="24" t="inlineStr">
         <is>
           <t>6975140315137</t>
         </is>
       </c>
-      <c r="N31" s="30" t="inlineStr"/>
-      <c r="O31" s="30" t="inlineStr"/>
-      <c r="P31" s="30" t="inlineStr"/>
-      <c r="Q31" s="28" t="inlineStr">
+      <c r="N31" s="25" t="inlineStr"/>
+      <c r="O31" s="25" t="inlineStr"/>
+      <c r="P31" s="25" t="inlineStr"/>
+      <c r="Q31" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R31" s="28" t="inlineStr">
+      <c r="R31" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S31" s="28" t="inlineStr">
+      <c r="S31" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T31" s="28" t="inlineStr">
+      <c r="T31" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U31" s="28" t="inlineStr"/>
-      <c r="V31" s="28" t="inlineStr">
+      <c r="U31" s="23" t="inlineStr"/>
+      <c r="V31" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W31" s="28" t="inlineStr">
+      <c r="W31" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X31" s="28" t="inlineStr">
+      <c r="X31" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9085,7 +9061,7 @@
           <t>https://images.barcodelookup.com/124722/1247228758-1.jpg</t>
         </is>
       </c>
-      <c r="Z31" s="28" t="inlineStr">
+      <c r="Z31" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9095,7 +9071,7 @@
           <t>Scuba L1 - EU</t>
         </is>
       </c>
-      <c r="AB31" s="28" t="inlineStr">
+      <c r="AB31" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9107,10 +9083,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF31" s="28" t="inlineStr"/>
-      <c r="AG31" s="28" t="inlineStr"/>
-      <c r="AH31" s="28" t="inlineStr"/>
-      <c r="AI31" s="28" t="inlineStr"/>
+      <c r="AF31" s="23" t="inlineStr"/>
+      <c r="AG31" s="23" t="inlineStr"/>
+      <c r="AH31" s="23" t="inlineStr"/>
+      <c r="AI31" s="23" t="inlineStr"/>
     </row>
     <row r="32" ht="48" customHeight="1">
       <c r="A32" s="18" t="inlineStr">
@@ -9128,13 +9104,13 @@
           <t>The Gre Pools RBR120 is a 51W robotic pool cleaner designed for automatic pool floor cleaning. A reliable workhorse that takes the scrubbing off your hands.</t>
         </is>
       </c>
-      <c r="D32" s="28" t="inlineStr"/>
-      <c r="E32" s="28" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr"/>
+      <c r="E32" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F32" s="28" t="inlineStr">
+      <c r="F32" s="23" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9144,71 +9120,71 @@
           <t>robot-cleaner, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H32" s="28" t="inlineStr">
+      <c r="H32" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I32" s="28" t="inlineStr">
+      <c r="I32" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J32" s="28" t="inlineStr">
+      <c r="J32" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K32" s="28" t="inlineStr">
+      <c r="K32" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L32" s="28" t="inlineStr">
+      <c r="L32" s="23" t="inlineStr">
         <is>
           <t>GEN-ROB-8500</t>
         </is>
       </c>
-      <c r="M32" s="29" t="inlineStr">
+      <c r="M32" s="24" t="inlineStr">
         <is>
           <t>8412081308500</t>
         </is>
       </c>
-      <c r="N32" s="30" t="inlineStr"/>
-      <c r="O32" s="30" t="inlineStr"/>
-      <c r="P32" s="30" t="inlineStr"/>
-      <c r="Q32" s="28" t="inlineStr">
+      <c r="N32" s="25" t="inlineStr"/>
+      <c r="O32" s="25" t="inlineStr"/>
+      <c r="P32" s="25" t="inlineStr"/>
+      <c r="Q32" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R32" s="28" t="inlineStr">
+      <c r="R32" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S32" s="28" t="inlineStr">
+      <c r="S32" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T32" s="28" t="inlineStr">
+      <c r="T32" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U32" s="28" t="inlineStr"/>
-      <c r="V32" s="28" t="inlineStr">
+      <c r="U32" s="23" t="inlineStr"/>
+      <c r="V32" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W32" s="28" t="inlineStr">
+      <c r="W32" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X32" s="28" t="inlineStr">
+      <c r="X32" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9218,7 +9194,7 @@
           <t>https://images.barcodelookup.com/124726/1247268298-1.jpg</t>
         </is>
       </c>
-      <c r="Z32" s="28" t="inlineStr">
+      <c r="Z32" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9228,7 +9204,7 @@
           <t>Battery Powered Robot WET RUNNER XPERT</t>
         </is>
       </c>
-      <c r="AB32" s="28" t="inlineStr">
+      <c r="AB32" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9240,10 +9216,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF32" s="28" t="inlineStr"/>
-      <c r="AG32" s="28" t="inlineStr"/>
-      <c r="AH32" s="28" t="inlineStr"/>
-      <c r="AI32" s="28" t="inlineStr"/>
+      <c r="AF32" s="23" t="inlineStr"/>
+      <c r="AG32" s="23" t="inlineStr"/>
+      <c r="AH32" s="23" t="inlineStr"/>
+      <c r="AI32" s="23" t="inlineStr"/>
     </row>
     <row r="33" ht="90" customHeight="1">
       <c r="A33" s="18" t="inlineStr">
@@ -9261,13 +9237,13 @@
           <t>A twin-size inflatable airbed measuring 99 x 191 x 25 cm, built with Fiber-Tech internal construction using polyester fibres for comfort, vinyl sides and base, and a water-resistant flocked top surface with an anti-deflation valve. It supports a maximum weight of 136 kg and packs down compactly when deflated.</t>
         </is>
       </c>
-      <c r="D33" s="28" t="inlineStr"/>
-      <c r="E33" s="28" t="inlineStr">
+      <c r="D33" s="23" t="inlineStr"/>
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-11</t>
         </is>
       </c>
-      <c r="F33" s="28" t="inlineStr">
+      <c r="F33" s="23" t="inlineStr">
         <is>
           <t>Airbed / lounger</t>
         </is>
@@ -9277,71 +9253,71 @@
           <t>considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H33" s="28" t="inlineStr">
+      <c r="H33" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I33" s="28" t="inlineStr">
+      <c r="I33" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J33" s="28" t="inlineStr">
+      <c r="J33" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K33" s="28" t="inlineStr">
+      <c r="K33" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L33" s="28" t="inlineStr">
+      <c r="L33" s="23" t="inlineStr">
         <is>
           <t>GEN-BED-2443</t>
         </is>
       </c>
-      <c r="M33" s="29" t="inlineStr">
+      <c r="M33" s="24" t="inlineStr">
         <is>
           <t>6941057412443</t>
         </is>
       </c>
-      <c r="N33" s="30" t="inlineStr"/>
-      <c r="O33" s="30" t="inlineStr"/>
-      <c r="P33" s="30" t="inlineStr"/>
-      <c r="Q33" s="28" t="inlineStr">
+      <c r="N33" s="25" t="inlineStr"/>
+      <c r="O33" s="25" t="inlineStr"/>
+      <c r="P33" s="25" t="inlineStr"/>
+      <c r="Q33" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R33" s="28" t="inlineStr">
+      <c r="R33" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S33" s="28" t="inlineStr">
+      <c r="S33" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T33" s="28" t="inlineStr">
+      <c r="T33" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U33" s="28" t="inlineStr"/>
-      <c r="V33" s="28" t="inlineStr">
+      <c r="U33" s="23" t="inlineStr"/>
+      <c r="V33" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W33" s="28" t="inlineStr">
+      <c r="W33" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X33" s="28" t="inlineStr">
+      <c r="X33" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9351,7 +9327,7 @@
           <t>https://www.ecoperation.com/media/catalog/product/cache/b76cf1d99a7811daa83ba86e6ad91c89/6/4/64757.jpg</t>
         </is>
       </c>
-      <c r="Z33" s="28" t="inlineStr">
+      <c r="Z33" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9361,7 +9337,7 @@
           <t>Twin Dura-Beam Classic Downy Airbed 99x191x25 cm</t>
         </is>
       </c>
-      <c r="AB33" s="28" t="inlineStr">
+      <c r="AB33" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9373,18 +9349,18 @@
           <t>Inflatable Beds and Mattresses</t>
         </is>
       </c>
-      <c r="AF33" s="28" t="inlineStr"/>
-      <c r="AG33" s="28" t="inlineStr">
+      <c r="AF33" s="23" t="inlineStr"/>
+      <c r="AG33" s="23" t="inlineStr">
         <is>
           <t>99.0cm</t>
         </is>
       </c>
-      <c r="AH33" s="28" t="inlineStr">
+      <c r="AH33" s="23" t="inlineStr">
         <is>
           <t>191.0cm</t>
         </is>
       </c>
-      <c r="AI33" s="28" t="inlineStr">
+      <c r="AI33" s="23" t="inlineStr">
         <is>
           <t>25.0cm</t>
         </is>
@@ -9406,17 +9382,17 @@
           <t>A plastic chlorine dosing lock from Steinbach, designed exclusively for use with long-term chlorine tablets, with a 1.5-inch connection fitting. It measures 37 cm in length, 22.5 cm in width, and 15 cm in height, making it a sturdy inline dosing unit for pool water treatment systems.</t>
         </is>
       </c>
-      <c r="D34" s="28" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>Steinbach</t>
         </is>
       </c>
-      <c r="E34" s="28" t="inlineStr">
+      <c r="E34" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F34" s="28" t="inlineStr">
+      <c r="F34" s="23" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -9426,71 +9402,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H34" s="28" t="inlineStr">
+      <c r="H34" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I34" s="28" t="inlineStr">
+      <c r="I34" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J34" s="28" t="inlineStr">
+      <c r="J34" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K34" s="28" t="inlineStr">
+      <c r="K34" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L34" s="28" t="inlineStr">
+      <c r="L34" s="23" t="inlineStr">
         <is>
           <t>STE-CHM-0307</t>
         </is>
       </c>
-      <c r="M34" s="29" t="inlineStr">
+      <c r="M34" s="24" t="inlineStr">
         <is>
           <t>9008748790307</t>
         </is>
       </c>
-      <c r="N34" s="30" t="inlineStr"/>
-      <c r="O34" s="30" t="inlineStr"/>
-      <c r="P34" s="30" t="inlineStr"/>
-      <c r="Q34" s="28" t="inlineStr">
+      <c r="N34" s="25" t="inlineStr"/>
+      <c r="O34" s="25" t="inlineStr"/>
+      <c r="P34" s="25" t="inlineStr"/>
+      <c r="Q34" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R34" s="28" t="inlineStr">
+      <c r="R34" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S34" s="28" t="inlineStr">
+      <c r="S34" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T34" s="28" t="inlineStr">
+      <c r="T34" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U34" s="28" t="inlineStr"/>
-      <c r="V34" s="28" t="inlineStr">
+      <c r="U34" s="23" t="inlineStr"/>
+      <c r="V34" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W34" s="28" t="inlineStr">
+      <c r="W34" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X34" s="28" t="inlineStr">
+      <c r="X34" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9500,7 +9476,7 @@
           <t>https://i.ebayimg.com/images/g/CrUAAeSwkOdqeaRR/s-l400.jpg</t>
         </is>
       </c>
-      <c r="Z34" s="28" t="inlineStr">
+      <c r="Z34" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9510,7 +9486,7 @@
           <t>STEINBACH Chlorine dosing lock, only for chlorine long-term tablets, plastic, connection 1.5 inch in</t>
         </is>
       </c>
-      <c r="AB34" s="28" t="inlineStr">
+      <c r="AB34" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9522,18 +9498,18 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF34" s="28" t="inlineStr"/>
-      <c r="AG34" s="28" t="inlineStr">
+      <c r="AF34" s="23" t="inlineStr"/>
+      <c r="AG34" s="23" t="inlineStr">
         <is>
           <t>22.5cm</t>
         </is>
       </c>
-      <c r="AH34" s="28" t="inlineStr">
+      <c r="AH34" s="23" t="inlineStr">
         <is>
           <t>37.0cm</t>
         </is>
       </c>
-      <c r="AI34" s="28" t="inlineStr">
+      <c r="AI34" s="23" t="inlineStr">
         <is>
           <t>15.0cm</t>
         </is>
@@ -9555,17 +9531,17 @@
           <t>A filter cleaning system for hot tub and pool cartridge filters, designed to remove debris and residue efficiently while keeping water usage to a minimum. A practical tool for extending the life of your filter without wasting a drop more than necessary.</t>
         </is>
       </c>
-      <c r="D35" s="28" t="inlineStr">
+      <c r="D35" s="23" t="inlineStr">
         <is>
           <t>Estelle</t>
         </is>
       </c>
-      <c r="E35" s="28" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F35" s="28" t="inlineStr">
+      <c r="F35" s="23" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -9575,71 +9551,71 @@
           <t>filters, spa-hot-tub, cleaning, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H35" s="28" t="inlineStr">
+      <c r="H35" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I35" s="28" t="inlineStr">
+      <c r="I35" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J35" s="28" t="inlineStr">
+      <c r="J35" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K35" s="28" t="inlineStr">
+      <c r="K35" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L35" s="28" t="inlineStr">
+      <c r="L35" s="23" t="inlineStr">
         <is>
           <t>EST-FIL-3669</t>
         </is>
       </c>
-      <c r="M35" s="29" t="inlineStr">
+      <c r="M35" s="24" t="inlineStr">
         <is>
           <t>8711842033669</t>
         </is>
       </c>
-      <c r="N35" s="30" t="inlineStr"/>
-      <c r="O35" s="30" t="inlineStr"/>
-      <c r="P35" s="30" t="inlineStr"/>
-      <c r="Q35" s="28" t="inlineStr">
+      <c r="N35" s="25" t="inlineStr"/>
+      <c r="O35" s="25" t="inlineStr"/>
+      <c r="P35" s="25" t="inlineStr"/>
+      <c r="Q35" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R35" s="28" t="inlineStr">
+      <c r="R35" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S35" s="28" t="inlineStr">
+      <c r="S35" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T35" s="28" t="inlineStr">
+      <c r="T35" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U35" s="28" t="inlineStr"/>
-      <c r="V35" s="28" t="inlineStr">
+      <c r="U35" s="23" t="inlineStr"/>
+      <c r="V35" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W35" s="28" t="inlineStr">
+      <c r="W35" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X35" s="28" t="inlineStr">
+      <c r="X35" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9649,7 +9625,7 @@
           <t>https://i.ebayimg.com/images/g/0e0AAOSweaplqO77/s-l400.jpg</t>
         </is>
       </c>
-      <c r="Z35" s="28" t="inlineStr">
+      <c r="Z35" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9659,7 +9635,7 @@
           <t>Estelle Filter Cleaning System Hot tubs Cartridge Filters Cleaner Spa Amazing!</t>
         </is>
       </c>
-      <c r="AB35" s="28" t="inlineStr">
+      <c r="AB35" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9671,10 +9647,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF35" s="28" t="inlineStr"/>
-      <c r="AG35" s="28" t="inlineStr"/>
-      <c r="AH35" s="28" t="inlineStr"/>
-      <c r="AI35" s="28" t="inlineStr"/>
+      <c r="AF35" s="23" t="inlineStr"/>
+      <c r="AG35" s="23" t="inlineStr"/>
+      <c r="AH35" s="23" t="inlineStr"/>
+      <c r="AI35" s="23" t="inlineStr"/>
     </row>
     <row r="36" ht="62" customHeight="1">
       <c r="A36" s="18" t="inlineStr">
@@ -9692,17 +9668,17 @@
           <t>A compact handy scrub brush for pool maintenance, measuring 15 x 9 x 8 cm, suited to scrubbing pool surfaces and hard-to-reach areas. Small enough to manoeuvre easily, and ready to tackle whatever the waterline throws at it.</t>
         </is>
       </c>
-      <c r="D36" s="28" t="inlineStr">
+      <c r="D36" s="23" t="inlineStr">
         <is>
           <t>WAYS</t>
         </is>
       </c>
-      <c r="E36" s="28" t="inlineStr">
+      <c r="E36" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F36" s="28" t="inlineStr">
+      <c r="F36" s="23" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -9712,79 +9688,79 @@
           <t>pool, cleaning, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H36" s="28" t="inlineStr">
+      <c r="H36" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I36" s="28" t="inlineStr">
+      <c r="I36" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J36" s="28" t="inlineStr">
+      <c r="J36" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K36" s="28" t="inlineStr">
+      <c r="K36" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L36" s="28" t="inlineStr">
+      <c r="L36" s="23" t="inlineStr">
         <is>
           <t>WAY-CLN-2219</t>
         </is>
       </c>
-      <c r="M36" s="29" t="inlineStr">
+      <c r="M36" s="24" t="inlineStr">
         <is>
           <t>8720299182219</t>
         </is>
       </c>
-      <c r="N36" s="30" t="inlineStr"/>
-      <c r="O36" s="30" t="inlineStr"/>
-      <c r="P36" s="30" t="inlineStr"/>
-      <c r="Q36" s="28" t="inlineStr">
+      <c r="N36" s="25" t="inlineStr"/>
+      <c r="O36" s="25" t="inlineStr"/>
+      <c r="P36" s="25" t="inlineStr"/>
+      <c r="Q36" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R36" s="28" t="inlineStr">
+      <c r="R36" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S36" s="28" t="inlineStr">
+      <c r="S36" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T36" s="28" t="inlineStr">
+      <c r="T36" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U36" s="28" t="inlineStr"/>
-      <c r="V36" s="28" t="inlineStr">
+      <c r="U36" s="23" t="inlineStr"/>
+      <c r="V36" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W36" s="28" t="inlineStr">
+      <c r="W36" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X36" s="28" t="inlineStr">
+      <c r="X36" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y36" s="18" t="inlineStr"/>
-      <c r="Z36" s="28" t="inlineStr"/>
+      <c r="Z36" s="23" t="inlineStr"/>
       <c r="AA36" s="18" t="inlineStr"/>
-      <c r="AB36" s="28" t="inlineStr">
+      <c r="AB36" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9796,18 +9772,18 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF36" s="28" t="inlineStr"/>
-      <c r="AG36" s="28" t="inlineStr">
+      <c r="AF36" s="23" t="inlineStr"/>
+      <c r="AG36" s="23" t="inlineStr">
         <is>
           <t>8.0cm</t>
         </is>
       </c>
-      <c r="AH36" s="28" t="inlineStr">
+      <c r="AH36" s="23" t="inlineStr">
         <is>
           <t>15.0cm</t>
         </is>
       </c>
-      <c r="AI36" s="28" t="inlineStr">
+      <c r="AI36" s="23" t="inlineStr">
         <is>
           <t>9.0cm</t>
         </is>
@@ -9829,17 +9805,17 @@
           <t>An inflatable PVC headrest pillow for the Intex inflatable spa (model 28506), measuring 24 x 19 x 6 cm and weighing 0.22 kg, designed to support the head and neck comfortably during use. It attaches to the spa rim and can also be filled with water for added stability.</t>
         </is>
       </c>
-      <c r="D37" s="28" t="inlineStr">
+      <c r="D37" s="23" t="inlineStr">
         <is>
           <t>Intex</t>
         </is>
       </c>
-      <c r="E37" s="28" t="inlineStr">
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F37" s="28" t="inlineStr">
+      <c r="F37" s="23" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -9849,75 +9825,75 @@
           <t>spa-hot-tub, accessories, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H37" s="28" t="inlineStr">
+      <c r="H37" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I37" s="28" t="inlineStr">
+      <c r="I37" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J37" s="28" t="inlineStr">
+      <c r="J37" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K37" s="28" t="inlineStr">
+      <c r="K37" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L37" s="28" t="inlineStr">
+      <c r="L37" s="23" t="inlineStr">
         <is>
           <t>INT-SPA-6075</t>
         </is>
       </c>
-      <c r="M37" s="29" t="inlineStr">
+      <c r="M37" s="24" t="inlineStr">
         <is>
           <t>6941057426075</t>
         </is>
       </c>
-      <c r="N37" s="30" t="inlineStr"/>
-      <c r="O37" s="30" t="inlineStr"/>
-      <c r="P37" s="30" t="inlineStr"/>
-      <c r="Q37" s="28" t="inlineStr">
+      <c r="N37" s="25" t="inlineStr"/>
+      <c r="O37" s="25" t="inlineStr"/>
+      <c r="P37" s="25" t="inlineStr"/>
+      <c r="Q37" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R37" s="28" t="inlineStr">
+      <c r="R37" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S37" s="28" t="inlineStr">
+      <c r="S37" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T37" s="28" t="inlineStr">
+      <c r="T37" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U37" s="28" t="inlineStr">
+      <c r="U37" s="23" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="V37" s="28" t="inlineStr">
+      <c r="V37" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W37" s="28" t="inlineStr">
+      <c r="W37" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X37" s="28" t="inlineStr">
+      <c r="X37" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9927,7 +9903,7 @@
           <t>https://content2.rozetka.com.ua/goods/images/big/570260745.jpg</t>
         </is>
       </c>
-      <c r="Z37" s="28" t="inlineStr">
+      <c r="Z37" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9937,7 +9913,7 @@
           <t>Headrest Pillow for INTEX Inflatable SPA 28506</t>
         </is>
       </c>
-      <c r="AB37" s="28" t="inlineStr">
+      <c r="AB37" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9949,18 +9925,18 @@
           <t>Intex Pure Spa Accessories</t>
         </is>
       </c>
-      <c r="AF37" s="28" t="inlineStr"/>
-      <c r="AG37" s="28" t="inlineStr">
+      <c r="AF37" s="23" t="inlineStr"/>
+      <c r="AG37" s="23" t="inlineStr">
         <is>
           <t>19.0cm</t>
         </is>
       </c>
-      <c r="AH37" s="28" t="inlineStr">
+      <c r="AH37" s="23" t="inlineStr">
         <is>
           <t>24.0cm</t>
         </is>
       </c>
-      <c r="AI37" s="28" t="inlineStr">
+      <c r="AI37" s="23" t="inlineStr">
         <is>
           <t>6.0cm</t>
         </is>
@@ -9982,13 +9958,13 @@
           <t>A DPD Pool test kit for active-oxygen pools, containing 20 DPD No. 4 reagent tablets for measuring active oxygen levels and 20 phenol red tablets for measuring pH. Results are read immediately after the tablet dissolves, with an ideal active oxygen range of 3.0 to 8.0 mg/l and a target pH of 7.0 to 7.4.</t>
         </is>
       </c>
-      <c r="D38" s="28" t="inlineStr"/>
-      <c r="E38" s="28" t="inlineStr">
+      <c r="D38" s="23" t="inlineStr"/>
+      <c r="E38" s="23" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F38" s="28" t="inlineStr">
+      <c r="F38" s="23" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -9998,71 +9974,71 @@
           <t>water-treatment, test-measure, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H38" s="28" t="inlineStr">
+      <c r="H38" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I38" s="28" t="inlineStr">
+      <c r="I38" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J38" s="28" t="inlineStr">
+      <c r="J38" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K38" s="28" t="inlineStr">
+      <c r="K38" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L38" s="28" t="inlineStr">
+      <c r="L38" s="23" t="inlineStr">
         <is>
           <t>GEN-TST-1347</t>
         </is>
       </c>
-      <c r="M38" s="29" t="inlineStr">
+      <c r="M38" s="24" t="inlineStr">
         <is>
           <t>4250463121347</t>
         </is>
       </c>
-      <c r="N38" s="30" t="inlineStr"/>
-      <c r="O38" s="30" t="inlineStr"/>
-      <c r="P38" s="30" t="inlineStr"/>
-      <c r="Q38" s="28" t="inlineStr">
+      <c r="N38" s="25" t="inlineStr"/>
+      <c r="O38" s="25" t="inlineStr"/>
+      <c r="P38" s="25" t="inlineStr"/>
+      <c r="Q38" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R38" s="28" t="inlineStr">
+      <c r="R38" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S38" s="28" t="inlineStr">
+      <c r="S38" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T38" s="28" t="inlineStr">
+      <c r="T38" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U38" s="28" t="inlineStr"/>
-      <c r="V38" s="28" t="inlineStr">
+      <c r="U38" s="23" t="inlineStr"/>
+      <c r="V38" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W38" s="28" t="inlineStr">
+      <c r="W38" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X38" s="28" t="inlineStr">
+      <c r="X38" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10072,7 +10048,7 @@
           <t>https://media.carrefour.fr/medias/8f94161f683b4e589024a5b5ebaa6873/p_200x200/cad3db6a00ef414a804b9226119bae96_image.jpg</t>
         </is>
       </c>
-      <c r="Z38" s="28" t="inlineStr">
+      <c r="Z38" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10082,7 +10058,7 @@
           <t>Active Oxygen Test Kit x1</t>
         </is>
       </c>
-      <c r="AB38" s="28" t="inlineStr">
+      <c r="AB38" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10094,10 +10070,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF38" s="28" t="inlineStr"/>
-      <c r="AG38" s="28" t="inlineStr"/>
-      <c r="AH38" s="28" t="inlineStr"/>
-      <c r="AI38" s="28" t="inlineStr"/>
+      <c r="AF38" s="23" t="inlineStr"/>
+      <c r="AG38" s="23" t="inlineStr"/>
+      <c r="AH38" s="23" t="inlineStr"/>
+      <c r="AI38" s="23" t="inlineStr"/>
     </row>
     <row r="39" ht="62" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
@@ -10115,17 +10091,17 @@
           <t>A pack of 2 replacement filter cartridges compatible with Intex Type H pool and spa pumps, made by Darlly. Straightforward to swap out, they keep the water moving clean without any complications.</t>
         </is>
       </c>
-      <c r="D39" s="28" t="inlineStr">
+      <c r="D39" s="23" t="inlineStr">
         <is>
           <t>Intex</t>
         </is>
       </c>
-      <c r="E39" s="28" t="inlineStr">
+      <c r="E39" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F39" s="28" t="inlineStr">
+      <c r="F39" s="23" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -10135,71 +10111,71 @@
           <t>filters, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H39" s="28" t="inlineStr">
+      <c r="H39" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I39" s="28" t="inlineStr">
+      <c r="I39" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J39" s="28" t="inlineStr">
+      <c r="J39" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K39" s="28" t="inlineStr">
+      <c r="K39" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L39" s="28" t="inlineStr">
+      <c r="L39" s="23" t="inlineStr">
         <is>
           <t>INT-FIL-2895</t>
         </is>
       </c>
-      <c r="M39" s="29" t="inlineStr">
+      <c r="M39" s="24" t="inlineStr">
         <is>
           <t>700175992895</t>
         </is>
       </c>
-      <c r="N39" s="30" t="inlineStr"/>
-      <c r="O39" s="30" t="inlineStr"/>
-      <c r="P39" s="30" t="inlineStr"/>
-      <c r="Q39" s="28" t="inlineStr">
+      <c r="N39" s="25" t="inlineStr"/>
+      <c r="O39" s="25" t="inlineStr"/>
+      <c r="P39" s="25" t="inlineStr"/>
+      <c r="Q39" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R39" s="28" t="inlineStr">
+      <c r="R39" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S39" s="28" t="inlineStr">
+      <c r="S39" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T39" s="28" t="inlineStr">
+      <c r="T39" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U39" s="28" t="inlineStr"/>
-      <c r="V39" s="28" t="inlineStr">
+      <c r="U39" s="23" t="inlineStr"/>
+      <c r="V39" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W39" s="28" t="inlineStr">
+      <c r="W39" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X39" s="28" t="inlineStr">
+      <c r="X39" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10209,7 +10185,7 @@
           <t>https://a.allegroimg.com/original/11923c/a79785a04d36aa54f0d87384f038/Filtracni-kartuse-Intex-D-3BTZ0023-SC828</t>
         </is>
       </c>
-      <c r="Z39" s="28" t="inlineStr">
+      <c r="Z39" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10219,7 +10195,7 @@
           <t>Darlly Filter Cartridge Pack of 2 Filter Cartridges Compatible with Intex Type H</t>
         </is>
       </c>
-      <c r="AB39" s="28" t="inlineStr">
+      <c r="AB39" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10231,10 +10207,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF39" s="28" t="inlineStr"/>
-      <c r="AG39" s="28" t="inlineStr"/>
-      <c r="AH39" s="28" t="inlineStr"/>
-      <c r="AI39" s="28" t="inlineStr"/>
+      <c r="AF39" s="23" t="inlineStr"/>
+      <c r="AG39" s="23" t="inlineStr"/>
+      <c r="AH39" s="23" t="inlineStr"/>
+      <c r="AI39" s="23" t="inlineStr"/>
     </row>
     <row r="40" ht="62" customHeight="1">
       <c r="A40" s="18" t="inlineStr">
@@ -10252,17 +10228,17 @@
           <t>A Darlly replacement spa filter cartridge with dimensions of 22 cm diameter by 27 cm height, compatible with SC713 and C-8465 references. A reliable like-for-like swap to keep your spa filtration running smoothly.</t>
         </is>
       </c>
-      <c r="D40" s="28" t="inlineStr">
+      <c r="D40" s="23" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E40" s="28" t="inlineStr">
+      <c r="E40" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F40" s="28" t="inlineStr">
+      <c r="F40" s="23" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -10272,71 +10248,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H40" s="28" t="inlineStr">
+      <c r="H40" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I40" s="28" t="inlineStr">
+      <c r="I40" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J40" s="28" t="inlineStr">
+      <c r="J40" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K40" s="28" t="inlineStr">
+      <c r="K40" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L40" s="28" t="inlineStr">
+      <c r="L40" s="23" t="inlineStr">
         <is>
           <t>DAR-FIL-1744</t>
         </is>
       </c>
-      <c r="M40" s="29" t="inlineStr">
+      <c r="M40" s="24" t="inlineStr">
         <is>
           <t>700175991744</t>
         </is>
       </c>
-      <c r="N40" s="30" t="inlineStr"/>
-      <c r="O40" s="30" t="inlineStr"/>
-      <c r="P40" s="30" t="inlineStr"/>
-      <c r="Q40" s="28" t="inlineStr">
+      <c r="N40" s="25" t="inlineStr"/>
+      <c r="O40" s="25" t="inlineStr"/>
+      <c r="P40" s="25" t="inlineStr"/>
+      <c r="Q40" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R40" s="28" t="inlineStr">
+      <c r="R40" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S40" s="28" t="inlineStr">
+      <c r="S40" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T40" s="28" t="inlineStr">
+      <c r="T40" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U40" s="28" t="inlineStr"/>
-      <c r="V40" s="28" t="inlineStr">
+      <c r="U40" s="23" t="inlineStr"/>
+      <c r="V40" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W40" s="28" t="inlineStr">
+      <c r="W40" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X40" s="28" t="inlineStr">
+      <c r="X40" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10346,7 +10322,7 @@
           <t>https://images.barcodelookup.com/142259/1422591231-1.jpg</t>
         </is>
       </c>
-      <c r="Z40" s="28" t="inlineStr">
+      <c r="Z40" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10356,7 +10332,7 @@
           <t>Spa Replacement Filter Ø 22 cm x 27 cm SC713, C-8465 - Darlly</t>
         </is>
       </c>
-      <c r="AB40" s="28" t="inlineStr">
+      <c r="AB40" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10368,14 +10344,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF40" s="28" t="inlineStr"/>
-      <c r="AG40" s="28" t="inlineStr"/>
-      <c r="AH40" s="28" t="inlineStr">
+      <c r="AF40" s="23" t="inlineStr"/>
+      <c r="AG40" s="23" t="inlineStr"/>
+      <c r="AH40" s="23" t="inlineStr">
         <is>
           <t>22.0cm</t>
         </is>
       </c>
-      <c r="AI40" s="28" t="inlineStr">
+      <c r="AI40" s="23" t="inlineStr">
         <is>
           <t>27.0cm</t>
         </is>
@@ -10397,17 +10373,17 @@
           <t>A 1 kg pack of 20g multitabs for swimming pools, offering a 5-in-1 treatment that combines multiple water care functions in a single slow-dissolving tablet. Convenient all-in-one dosing that keeps pool maintenance simple.</t>
         </is>
       </c>
-      <c r="D41" s="28" t="inlineStr">
+      <c r="D41" s="23" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E41" s="28" t="inlineStr">
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F41" s="28" t="inlineStr">
+      <c r="F41" s="23" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -10417,75 +10393,75 @@
           <t>pool, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H41" s="28" t="inlineStr">
+      <c r="H41" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I41" s="28" t="inlineStr">
+      <c r="I41" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J41" s="28" t="inlineStr">
+      <c r="J41" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K41" s="28" t="inlineStr">
+      <c r="K41" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L41" s="28" t="inlineStr">
+      <c r="L41" s="23" t="inlineStr">
         <is>
           <t>HFE-CHM-8430</t>
         </is>
       </c>
-      <c r="M41" s="29" t="inlineStr">
+      <c r="M41" s="24" t="inlineStr">
         <is>
           <t>4250463108430</t>
         </is>
       </c>
-      <c r="N41" s="30" t="inlineStr"/>
-      <c r="O41" s="30" t="inlineStr"/>
-      <c r="P41" s="30" t="inlineStr"/>
-      <c r="Q41" s="28" t="inlineStr">
+      <c r="N41" s="25" t="inlineStr"/>
+      <c r="O41" s="25" t="inlineStr"/>
+      <c r="P41" s="25" t="inlineStr"/>
+      <c r="Q41" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R41" s="28" t="inlineStr">
+      <c r="R41" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S41" s="28" t="inlineStr">
+      <c r="S41" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T41" s="28" t="inlineStr">
+      <c r="T41" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U41" s="28" t="inlineStr">
+      <c r="U41" s="23" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="V41" s="28" t="inlineStr">
+      <c r="V41" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W41" s="28" t="inlineStr">
+      <c r="W41" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X41" s="28" t="inlineStr">
+      <c r="X41" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10495,7 +10471,7 @@
           <t>https://images.barcodelookup.com/17422/174228560-1.jpg</t>
         </is>
       </c>
-      <c r="Z41" s="28" t="inlineStr">
+      <c r="Z41" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10505,7 +10481,7 @@
           <t>1 x 1 kg BAYZID® 20g 5-in-1 Multitabs for Pools - HÖFER CHEMIE</t>
         </is>
       </c>
-      <c r="AB41" s="28" t="inlineStr">
+      <c r="AB41" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10517,10 +10493,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF41" s="28" t="inlineStr"/>
-      <c r="AG41" s="28" t="inlineStr"/>
-      <c r="AH41" s="28" t="inlineStr"/>
-      <c r="AI41" s="28" t="inlineStr"/>
+      <c r="AF41" s="23" t="inlineStr"/>
+      <c r="AG41" s="23" t="inlineStr"/>
+      <c r="AH41" s="23" t="inlineStr"/>
+      <c r="AI41" s="23" t="inlineStr"/>
     </row>
     <row r="42" ht="76" customHeight="1">
       <c r="A42" s="18" t="inlineStr">
@@ -10538,17 +10514,17 @@
           <t>A ready-to-use alkaline spray cleaner for removing grease and dirt marks at the waterline of pools and for cleaning skimmers. The spray bottle makes application straightforward, and it can be used on a filled pool on all alkali-resistant surfaces.</t>
         </is>
       </c>
-      <c r="D42" s="28" t="inlineStr">
+      <c r="D42" s="23" t="inlineStr">
         <is>
           <t>Bayrol</t>
         </is>
       </c>
-      <c r="E42" s="28" t="inlineStr">
+      <c r="E42" s="23" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F42" s="28" t="inlineStr">
+      <c r="F42" s="23" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -10558,75 +10534,75 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H42" s="28" t="inlineStr">
+      <c r="H42" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I42" s="28" t="inlineStr">
+      <c r="I42" s="23" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J42" s="28" t="inlineStr">
+      <c r="J42" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K42" s="28" t="inlineStr">
+      <c r="K42" s="23" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L42" s="28" t="inlineStr">
+      <c r="L42" s="23" t="inlineStr">
         <is>
           <t>BAY-CLN-4134</t>
         </is>
       </c>
-      <c r="M42" s="29" t="inlineStr">
+      <c r="M42" s="24" t="inlineStr">
         <is>
           <t>4008367154134</t>
         </is>
       </c>
-      <c r="N42" s="30" t="inlineStr"/>
-      <c r="O42" s="30" t="inlineStr"/>
-      <c r="P42" s="30" t="inlineStr"/>
-      <c r="Q42" s="28" t="inlineStr">
+      <c r="N42" s="25" t="inlineStr"/>
+      <c r="O42" s="25" t="inlineStr"/>
+      <c r="P42" s="25" t="inlineStr"/>
+      <c r="Q42" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R42" s="28" t="inlineStr">
+      <c r="R42" s="23" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S42" s="28" t="inlineStr">
+      <c r="S42" s="23" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T42" s="28" t="inlineStr">
+      <c r="T42" s="23" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U42" s="28" t="inlineStr">
+      <c r="U42" s="23" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="V42" s="28" t="inlineStr">
+      <c r="V42" s="23" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W42" s="28" t="inlineStr">
+      <c r="W42" s="23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X42" s="28" t="inlineStr">
+      <c r="X42" s="23" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10636,7 +10612,7 @@
           <t>https://www.north-spa.de/wp-content/uploads/2023/02/Produktbild-1-Bayrol-Randfix-07-l-4008367154134.jpg</t>
         </is>
       </c>
-      <c r="Z42" s="28" t="inlineStr">
+      <c r="Z42" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10646,7 +10622,7 @@
           <t>Bayrol Randfix 0,7 l</t>
         </is>
       </c>
-      <c r="AB42" s="28" t="inlineStr">
+      <c r="AB42" s="23" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10658,10 +10634,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF42" s="28" t="inlineStr"/>
-      <c r="AG42" s="28" t="inlineStr"/>
-      <c r="AH42" s="28" t="inlineStr"/>
-      <c r="AI42" s="28" t="inlineStr"/>
+      <c r="AF42" s="23" t="inlineStr"/>
+      <c r="AG42" s="23" t="inlineStr"/>
+      <c r="AH42" s="23" t="inlineStr"/>
+      <c r="AI42" s="23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projects/splashstore/docs/splashstore-scan-curation-260816.xlsx
+++ b/projects/splashstore/docs/splashstore-scan-curation-260816.xlsx
@@ -2262,7 +2262,7 @@
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>Calacatta 4-person Inflatable Spa</t>
+          <t>Calacatta 4-person inflatable spa</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>Olive 8-person Inflatable Spa</t>
+          <t>Olive 8-person inflatable spa</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>SC750 Filter Replacement Filter Lamellar Filter Arctic Fonteyn Rota Strong Spa - Darlly</t>
+          <t>SC750 Filter replacement filter lamellar filter Arctic Fonteyn Rota Strong Spa - Darlly</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>Cristal Poolpflege CRISTAL Alkaline Edge Cleaner 1,0 l, (Gentle on Materials, for Liners, Plastic Surfaces</t>
+          <t>Cristal Poolpflege CRISTAL edge cleaner alkaline 1,0 l, (material-safe, for liners, plastic</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>AQUALITY Pool Cleaner for Greasy Residues 1L</t>
+          <t>AQUALITY Pool cleaner for greasy residue 1L</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>Höfer Chemie GmbH Pool Care 1 L BAYZID® SPA Poolclear Turbidity Remover</t>
+          <t>Höfer Chemie GmbH pool care 1 L BAYZID® SPA Poolclear turbidity remover</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>HÖFER CHEMIE GMBH 1 l Hydrogen Peroxide 11,9%</t>
+          <t>HÖFER CHEMIE GMBH 1 l hydrogen peroxide 11,9%</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>Astralpool Water Care Astralpool Chlorine Stabilizer 4,5 kg</t>
+          <t>Astralpool water care Astralpool Chlorine Stabilizer 4,5 kg</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>Höfer Chemie GmbH 1 L Sauna Cleaner with Eucalyptus Scent - High-Concentrate Deep Cleaner</t>
+          <t>Höfer Chemie GmbH 1 L sauna cleaner with eucalyptus scent - high-concentrate heavy-duty cleaner</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>HTH Spa Spa Cleaner</t>
+          <t>HTH Spa spa cleaner</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>AIPER Scuba S3 Cordless Pool Robot, Automatic Floor and Wall Cleaning, WavePath™ Navigation, High-Performance Filtration and Smart Control</t>
+          <t>AIPER Scuba S3 cordless pool robot, automatic floor and wall cleaning, WavePath™ navigation, high-performance filtration and smart control</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>WAYS - Pool Maintenance - Scrub Brush - 15 x 9 x 8 cm - Handy scrub</t>
+          <t>WAYS - Pool maintenance - Scrub brush - 15 x 9 x 8 cm - Handy scrub</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>Headrest Pillow for INTEX Inflatable SPA 28506</t>
+          <t>Pillow for inflatable SPA INTEX 28506</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>Active Oxygen Test Kit x1</t>
+          <t>Active oxygen test kit x1</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>Darlly Filter Cartridge Pack of 2 Filter Cartridges Compatible with Intex Type H</t>
+          <t>Darlly filter cartridge pack of 2 filter cartridges compatible with Intex type H</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>Spa Replacement Filter Ø 22 cm x 27 cm SC713, C-8465 - Darlly</t>
+          <t>Spa replacement filter Ø 22 cm x 27 cm SC713, C-8465 - Darlly</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>1 x 1 kg BAYZID® 20g 5-in-1 Multitabs for Pools - HÖFER CHEMIE</t>
+          <t>1 x 1 kg BAYZID® multitabs 20g 5in1 for pools - HöFER CHEMIE</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>Calacatta 4-person Inflatable Spa</t>
+          <t>Calacatta 4-person inflatable spa</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="AA9" s="18" t="inlineStr">
         <is>
-          <t>Calacatta 4-person Inflatable Spa</t>
+          <t>Calacatta 4-person inflatable spa</t>
         </is>
       </c>
       <c r="AB9" s="23" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>Olive 8-person Inflatable Spa</t>
+          <t>Olive 8-person inflatable spa</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="AA12" s="18" t="inlineStr">
         <is>
-          <t>Olive 8-person Inflatable Spa</t>
+          <t>Olive 8-person inflatable spa</t>
         </is>
       </c>
       <c r="AB12" s="23" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>SC750 Filter Replacement Filter Lamellar Filter Arctic Fonteyn Rota Strong Spa - Darlly</t>
+          <t>SC750 Filter replacement filter lamellar filter Arctic Fonteyn Rota Strong Spa - Darlly</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="AA13" s="18" t="inlineStr">
         <is>
-          <t>SC750 Filter Replacement Filter Lamellar Filter Arctic Fonteyn Rota Strong Spa - Darlly</t>
+          <t>SC750 Filter replacement filter lamellar filter Arctic Fonteyn Rota Strong Spa - Darlly</t>
         </is>
       </c>
       <c r="AB13" s="23" t="inlineStr">
@@ -7076,12 +7076,12 @@
     <row r="17" ht="62" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>cristal-poolpflege-cristal-alkaline-edge-cleaner-1-0-l-gentle-on-materials-for-l</t>
+          <t>cristal-poolpflege-cristal-edge-cleaner-alkaline-1-0-l-material-safe-for-liners-</t>
         </is>
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
-          <t>Cristal Poolpflege CRISTAL Alkaline Edge Cleaner 1,0 l, (Gentle on Materials, for Liners, Plastic Surfaces</t>
+          <t>Cristal Poolpflege CRISTAL edge cleaner alkaline 1,0 l, (material-safe, for liners, plastic</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="AA17" s="18" t="inlineStr">
         <is>
-          <t>Cristal Poolpflege CRISTAL Alkaline Edge Cleaner 1,0 l, (Gentle on Materials, for Liners, Plastic Surfaces</t>
+          <t>Cristal Poolpflege CRISTAL edge cleaner alkaline 1,0 l, (material-safe, for liners, plastic</t>
         </is>
       </c>
       <c r="AB17" s="23" t="inlineStr">
@@ -7213,12 +7213,12 @@
     <row r="18" ht="76" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>aquality-pool-cleaner-for-greasy-residues-1l</t>
+          <t>aquality-pool-cleaner-for-greasy-residue-1l</t>
         </is>
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>AQUALITY Pool Cleaner for Greasy Residues 1L</t>
+          <t>AQUALITY Pool cleaner for greasy residue 1L</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="AA18" s="18" t="inlineStr">
         <is>
-          <t>AQUALITY Pool Cleaner for Greasy Residues 1L</t>
+          <t>AQUALITY Pool cleaner for greasy residue 1L</t>
         </is>
       </c>
       <c r="AB18" s="23" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>Höfer Chemie GmbH Pool Care 1 L BAYZID® SPA Poolclear Turbidity Remover</t>
+          <t>Höfer Chemie GmbH pool care 1 L BAYZID® SPA Poolclear turbidity remover</t>
         </is>
       </c>
       <c r="C21" s="18" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AA21" s="18" t="inlineStr">
         <is>
-          <t>Höfer Chemie GmbH Pool Care 1 L BAYZID® SPA Poolclear Turbidity Remover</t>
+          <t>Höfer Chemie GmbH pool care 1 L BAYZID® SPA Poolclear turbidity remover</t>
         </is>
       </c>
       <c r="AB21" s="23" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>HÖFER CHEMIE GMBH 1 l Hydrogen Peroxide 11,9%</t>
+          <t>HÖFER CHEMIE GMBH 1 l hydrogen peroxide 11,9%</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="AA22" s="18" t="inlineStr">
         <is>
-          <t>HÖFER CHEMIE GMBH 1 l Hydrogen Peroxide 11,9%</t>
+          <t>HÖFER CHEMIE GMBH 1 l hydrogen peroxide 11,9%</t>
         </is>
       </c>
       <c r="AB22" s="23" t="inlineStr">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t>Astralpool Water Care Astralpool Chlorine Stabilizer 4,5 kg</t>
+          <t>Astralpool water care Astralpool Chlorine Stabilizer 4,5 kg</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
@@ -8418,12 +8418,12 @@
     <row r="27" ht="62" customHeight="1">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>hofer-chemie-gmbh-1-l-sauna-cleaner-with-eucalyptus-scent-high-concentrate-deep-</t>
+          <t>hofer-chemie-gmbh-1-l-sauna-cleaner-with-eucalyptus-scent-high-concentrate-heavy</t>
         </is>
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>Höfer Chemie GmbH 1 L Sauna Cleaner with Eucalyptus Scent - High-Concentrate Deep Cleaner</t>
+          <t>Höfer Chemie GmbH 1 L sauna cleaner with eucalyptus scent - high-concentrate heavy-duty cleaner</t>
         </is>
       </c>
       <c r="C27" s="18" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>HTH Spa Spa Cleaner</t>
+          <t>HTH Spa spa cleaner</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="AA28" s="18" t="inlineStr">
         <is>
-          <t>HTH Spa Spa Cleaner</t>
+          <t>HTH Spa spa cleaner</t>
         </is>
       </c>
       <c r="AB28" s="23" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>AIPER Scuba S3 Cordless Pool Robot, Automatic Floor and Wall Cleaning, WavePath™ Navigation, High-Performance Filtration and Smart Control</t>
+          <t>AIPER Scuba S3 cordless pool robot, automatic floor and wall cleaning, WavePath™ navigation, high-performance filtration and smart control</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AA30" s="18" t="inlineStr">
         <is>
-          <t>AIPER Scuba S3 Cordless Pool Robot, Automatic Floor and Wall Cleaning, WavePath™ Navigation, High-Performance Filtration…</t>
+          <t>AIPER Scuba S3 cordless pool robot, automatic floor and wall cleaning, WavePath™ navigation, high-performance filtration…</t>
         </is>
       </c>
       <c r="AB30" s="23" t="inlineStr">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>WAYS - Pool Maintenance - Scrub Brush - 15 x 9 x 8 cm - Handy scrub</t>
+          <t>WAYS - Pool maintenance - Scrub brush - 15 x 9 x 8 cm - Handy scrub</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
@@ -9792,12 +9792,12 @@
     <row r="37" ht="76" customHeight="1">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>headrest-pillow-for-intex-inflatable-spa-28506</t>
+          <t>pillow-for-inflatable-spa-intex-28506</t>
         </is>
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>Headrest Pillow for INTEX Inflatable SPA 28506</t>
+          <t>Pillow for inflatable SPA INTEX 28506</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="AA37" s="18" t="inlineStr">
         <is>
-          <t>Headrest Pillow for INTEX Inflatable SPA 28506</t>
+          <t>Pillow for inflatable SPA INTEX 28506</t>
         </is>
       </c>
       <c r="AB37" s="23" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Active Oxygen Test Kit x1</t>
+          <t>Active oxygen test kit x1</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="AA38" s="18" t="inlineStr">
         <is>
-          <t>Active Oxygen Test Kit x1</t>
+          <t>Active oxygen test kit x1</t>
         </is>
       </c>
       <c r="AB38" s="23" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>Darlly Filter Cartridge Pack of 2 Filter Cartridges Compatible with Intex Type H</t>
+          <t>Darlly filter cartridge pack of 2 filter cartridges compatible with Intex type H</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="AA39" s="18" t="inlineStr">
         <is>
-          <t>Darlly Filter Cartridge Pack of 2 Filter Cartridges Compatible with Intex Type H</t>
+          <t>Darlly filter cartridge pack of 2 filter cartridges compatible with Intex type H</t>
         </is>
       </c>
       <c r="AB39" s="23" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Spa Replacement Filter Ø 22 cm x 27 cm SC713, C-8465 - Darlly</t>
+          <t>Spa replacement filter Ø 22 cm x 27 cm SC713, C-8465 - Darlly</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="AA40" s="18" t="inlineStr">
         <is>
-          <t>Spa Replacement Filter Ø 22 cm x 27 cm SC713, C-8465 - Darlly</t>
+          <t>Spa replacement filter Ø 22 cm x 27 cm SC713, C-8465 - Darlly</t>
         </is>
       </c>
       <c r="AB40" s="23" t="inlineStr">
@@ -10360,12 +10360,12 @@
     <row r="41" ht="62" customHeight="1">
       <c r="A41" s="18" t="inlineStr">
         <is>
-          <t>1-x-1-kg-bayzid-20g-5-in-1-multitabs-for-pools-hofer-chemie</t>
+          <t>1-x-1-kg-bayzid-multitabs-20g-5in1-for-pools-hofer-chemie</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>1 x 1 kg BAYZID® 20g 5-in-1 Multitabs for Pools - HÖFER CHEMIE</t>
+          <t>1 x 1 kg BAYZID® multitabs 20g 5in1 for pools - HöFER CHEMIE</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="AA41" s="18" t="inlineStr">
         <is>
-          <t>1 x 1 kg BAYZID® 20g 5-in-1 Multitabs for Pools - HÖFER CHEMIE</t>
+          <t>1 x 1 kg BAYZID® multitabs 20g 5in1 for pools - HöFER CHEMIE</t>
         </is>
       </c>
       <c r="AB41" s="23" t="inlineStr">

--- a/projects/splashstore/docs/splashstore-scan-curation-260816.xlsx
+++ b/projects/splashstore/docs/splashstore-scan-curation-260816.xlsx
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -176,6 +176,15 @@
     <xf numFmtId="49" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -274,6 +283,16 @@
 Three sources agreeing is stronger evidence than one, though both are green.</t>
       </text>
     </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Colour applies to THIS FIELD ONLY, and is judged separately from the photo.
+GREEN = written from the barcode-confirmed page for this exact product.
+YELLOW = written from a name-matched page, so it may describe a variant.
+RED = no description.
+A yellow description beside a green image is normal: the photo was proven by the barcode, the wording was not.
+The cell names the page the wording came from, or says 'generic (from name)' when there was no page at all.</t>
+      </text>
+    </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>Colour applies to THIS FIELD ONLY, and is judged separately from the photo.
@@ -282,6 +301,15 @@
 RED = no description.
 A yellow description beside a green image is normal: the photo was proven by the barcode, the wording was not.
 The cell names the page the wording came from, or says 'generic (from name)' when there was no page at all.</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>Colour applies to THIS FIELD ONLY.
+GREEN = the barcode was found literally on the page the photo came from.
+YELLOW = the right product, but the photo needs a look (crop, multipack, unclear).
+RED = no usable photo was found.
+The cell names the site the photo came from. Compare it with Description Source: a different site there means the two fields were proven separately.</t>
       </text>
     </comment>
     <comment ref="P1" authorId="0" shapeId="0">
@@ -302,11 +330,39 @@
 RED = missing on an edible product.</t>
       </text>
     </comment>
+    <comment ref="P5" authorId="0" shapeId="0">
+      <text>
+        <t>No source anywhere confirmed this barcode, so the product has no name — and with no name there is nothing to search an image with.
+Identify it by hand: check the packaging, or search the code on the brand's own site.</t>
+      </text>
+    </comment>
+    <comment ref="P16" authorId="0" shapeId="0">
+      <text>
+        <t>No source anywhere confirmed this barcode, so the product has no name — and with no name there is nothing to search an image with.
+Identify it by hand: check the packaging, or search the code on the brand's own site.</t>
+      </text>
+    </comment>
+    <comment ref="N17" authorId="0" shapeId="0">
+      <text>
+        <t>A photo WAS found and checked against this product's confirmed name.
+The image AI judged it a different product, so it was not used:
+0.85: The image shows a WATER-I.D. DPD No.1 RAPID product with 50 tablets (I; 0.92: The image shows DPD No. 3 tablets, but the claimed product is DPD No. 
+This one wants photographing in the garage, not more searching.</t>
+      </text>
+    </comment>
     <comment ref="P17" authorId="0" shapeId="0">
       <text>
         <t>A photo WAS found and checked against this product's confirmed name.
 The image AI judged it a different product, so it was not used:
 0.85: The image shows a WATER-I.D. DPD No.1 RAPID product with 50 tablets (I; 0.92: The image shows DPD No. 3 tablets, but the claimed product is DPD No. 
+This one wants photographing in the garage, not more searching.</t>
+      </text>
+    </comment>
+    <comment ref="N28" authorId="0" shapeId="0">
+      <text>
+        <t>A photo WAS found and checked against this product's confirmed name.
+The image AI judged it a different product, so it was not used:
+0.85: The image shows a 'Big Sir' spa by Signature Spas, not a product from 
 This one wants photographing in the garage, not more searching.</t>
       </text>
     </comment>
@@ -318,12 +374,32 @@
 This one wants photographing in the garage, not more searching.</t>
       </text>
     </comment>
+    <comment ref="N29" authorId="0" shapeId="0">
+      <text>
+        <t>A photo WAS found and checked against this product's confirmed name.
+The image AI judged it a different product, so it was not used:
+0.97: The image shows a 3D animated purple dinosaur/dragon cartoon character
+This one wants photographing in the garage, not more searching.</t>
+      </text>
+    </comment>
     <comment ref="P29" authorId="0" shapeId="0">
       <text>
         <t>A photo WAS found and checked against this product's confirmed name.
 The image AI judged it a different product, so it was not used:
 0.97: The image shows a 3D animated purple dinosaur/dragon cartoon character
 This one wants photographing in the garage, not more searching.</t>
+      </text>
+    </comment>
+    <comment ref="P38" authorId="0" shapeId="0">
+      <text>
+        <t>The product IS identified from its barcode, but no usable photo was found by any source we search: the barcode databases, the barcode directories, an image search on the confirmed name, and eBay.
+Nothing left to try automatically. Photograph it in the garage.</t>
+      </text>
+    </comment>
+    <comment ref="P45" authorId="0" shapeId="0">
+      <text>
+        <t>No source anywhere confirmed this barcode, so the product has no name — and with no name there is nothing to search an image with.
+Identify it by hand: check the packaging, or search the code on the brand's own site.</t>
       </text>
     </comment>
   </commentList>
@@ -1668,20 +1744,20 @@
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="56" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="56" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="56" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="36" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="28" customWidth="1" min="18" max="18"/>
+    <col width="56" customWidth="1" min="19" max="19"/>
     <col width="3" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
@@ -1787,7 +1863,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="132" customHeight="1">
+    <row r="2" ht="244" customHeight="1">
       <c r="A2" s="2" t="n"/>
       <c r="B2" s="5" t="inlineStr">
         <is>
@@ -1856,7 +1932,7 @@
       </c>
       <c r="S2" s="19" t="n"/>
     </row>
-    <row r="3" ht="132" customHeight="1">
+    <row r="3" ht="258" customHeight="1">
       <c r="A3" s="2" t="n"/>
       <c r="B3" s="5" t="inlineStr">
         <is>
@@ -1925,7 +2001,7 @@
       </c>
       <c r="S3" s="19" t="n"/>
     </row>
-    <row r="4" ht="132" customHeight="1">
+    <row r="4" ht="272" customHeight="1">
       <c r="A4" s="2" t="n"/>
       <c r="B4" s="5" t="inlineStr">
         <is>
@@ -2035,7 +2111,7 @@
       </c>
       <c r="S5" s="19" t="n"/>
     </row>
-    <row r="6" ht="132" customHeight="1">
+    <row r="6" ht="230" customHeight="1">
       <c r="A6" s="2" t="n"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -2104,7 +2180,7 @@
       </c>
       <c r="S6" s="19" t="n"/>
     </row>
-    <row r="7" ht="132" customHeight="1">
+    <row r="7" ht="258" customHeight="1">
       <c r="A7" s="2" t="n"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -2173,7 +2249,7 @@
       </c>
       <c r="S7" s="19" t="n"/>
     </row>
-    <row r="8" ht="132" customHeight="1">
+    <row r="8" ht="216" customHeight="1">
       <c r="A8" s="12" t="n"/>
       <c r="B8" s="13" t="inlineStr">
         <is>
@@ -2242,7 +2318,7 @@
       </c>
       <c r="S8" s="19" t="n"/>
     </row>
-    <row r="9" ht="132" customHeight="1">
+    <row r="9" ht="320" customHeight="1">
       <c r="A9" s="12" t="n"/>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -2311,7 +2387,7 @@
       </c>
       <c r="S9" s="19" t="n"/>
     </row>
-    <row r="10" ht="132" customHeight="1">
+    <row r="10" ht="300" customHeight="1">
       <c r="A10" s="2" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -2384,7 +2460,7 @@
       </c>
       <c r="S10" s="19" t="n"/>
     </row>
-    <row r="11" ht="132" customHeight="1">
+    <row r="11" ht="230" customHeight="1">
       <c r="A11" s="2" t="n"/>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -2455,7 +2531,7 @@
       </c>
       <c r="S11" s="19" t="n"/>
     </row>
-    <row r="12" ht="132" customHeight="1">
+    <row r="12" ht="202" customHeight="1">
       <c r="A12" s="2" t="n"/>
       <c r="B12" s="13" t="inlineStr">
         <is>
@@ -2524,7 +2600,7 @@
       </c>
       <c r="S12" s="19" t="n"/>
     </row>
-    <row r="13" ht="132" customHeight="1">
+    <row r="13" ht="230" customHeight="1">
       <c r="A13" s="2" t="n"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -2589,7 +2665,7 @@
       </c>
       <c r="S13" s="19" t="n"/>
     </row>
-    <row r="14" ht="132" customHeight="1">
+    <row r="14" ht="202" customHeight="1">
       <c r="A14" s="2" t="n"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -2658,7 +2734,7 @@
       </c>
       <c r="S14" s="19" t="n"/>
     </row>
-    <row r="15" ht="132" customHeight="1">
+    <row r="15" ht="216" customHeight="1">
       <c r="A15" s="2" t="n"/>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -2768,7 +2844,7 @@
       </c>
       <c r="S16" s="19" t="n"/>
     </row>
-    <row r="17" ht="62" customHeight="1">
+    <row r="17" ht="202" customHeight="1">
       <c r="A17" s="9" t="n"/>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -2837,7 +2913,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="132" customHeight="1">
+    <row r="18" ht="216" customHeight="1">
       <c r="A18" s="2" t="n"/>
       <c r="B18" s="13" t="inlineStr">
         <is>
@@ -2906,7 +2982,7 @@
       </c>
       <c r="S18" s="19" t="n"/>
     </row>
-    <row r="19" ht="132" customHeight="1">
+    <row r="19" ht="202" customHeight="1">
       <c r="A19" s="2" t="n"/>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -2975,7 +3051,7 @@
       </c>
       <c r="S19" s="19" t="n"/>
     </row>
-    <row r="20" ht="132" customHeight="1">
+    <row r="20" ht="272" customHeight="1">
       <c r="A20" s="2" t="n"/>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -3044,7 +3120,7 @@
       </c>
       <c r="S20" s="19" t="n"/>
     </row>
-    <row r="21" ht="132" customHeight="1">
+    <row r="21" ht="320" customHeight="1">
       <c r="A21" s="2" t="n"/>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -3113,7 +3189,7 @@
       </c>
       <c r="S21" s="19" t="n"/>
     </row>
-    <row r="22" ht="132" customHeight="1">
+    <row r="22" ht="188" customHeight="1">
       <c r="A22" s="2" t="n"/>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -3182,7 +3258,7 @@
       </c>
       <c r="S22" s="19" t="n"/>
     </row>
-    <row r="23" ht="132" customHeight="1">
+    <row r="23" ht="174" customHeight="1">
       <c r="A23" s="2" t="n"/>
       <c r="B23" s="13" t="inlineStr">
         <is>
@@ -3251,7 +3327,7 @@
       </c>
       <c r="S23" s="19" t="n"/>
     </row>
-    <row r="24" ht="132" customHeight="1">
+    <row r="24" ht="202" customHeight="1">
       <c r="A24" s="2" t="n"/>
       <c r="B24" s="13" t="inlineStr">
         <is>
@@ -3320,7 +3396,7 @@
       </c>
       <c r="S24" s="19" t="n"/>
     </row>
-    <row r="25" ht="132" customHeight="1">
+    <row r="25" ht="202" customHeight="1">
       <c r="A25" s="12" t="n"/>
       <c r="B25" s="13" t="inlineStr">
         <is>
@@ -3391,7 +3467,7 @@
       </c>
       <c r="S25" s="19" t="n"/>
     </row>
-    <row r="26" ht="132" customHeight="1">
+    <row r="26" ht="202" customHeight="1">
       <c r="A26" s="2" t="n"/>
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -3460,7 +3536,7 @@
       </c>
       <c r="S26" s="19" t="n"/>
     </row>
-    <row r="27" ht="132" customHeight="1">
+    <row r="27" ht="314" customHeight="1">
       <c r="A27" s="2" t="n"/>
       <c r="B27" s="5" t="inlineStr">
         <is>
@@ -3525,7 +3601,7 @@
       </c>
       <c r="S27" s="19" t="n"/>
     </row>
-    <row r="28" ht="62" customHeight="1">
+    <row r="28" ht="216" customHeight="1">
       <c r="A28" s="9" t="n"/>
       <c r="B28" s="10" t="inlineStr">
         <is>
@@ -3590,7 +3666,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="62" customHeight="1">
+    <row r="29" ht="230" customHeight="1">
       <c r="A29" s="9" t="n"/>
       <c r="B29" s="10" t="inlineStr">
         <is>
@@ -3659,7 +3735,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="132" customHeight="1">
+    <row r="30" ht="300" customHeight="1">
       <c r="A30" s="2" t="n"/>
       <c r="B30" s="5" t="inlineStr">
         <is>
@@ -3728,7 +3804,7 @@
       </c>
       <c r="S30" s="19" t="n"/>
     </row>
-    <row r="31" ht="132" customHeight="1">
+    <row r="31" ht="230" customHeight="1">
       <c r="A31" s="2" t="n"/>
       <c r="B31" s="5" t="inlineStr">
         <is>
@@ -3799,7 +3875,7 @@
       </c>
       <c r="S31" s="19" t="n"/>
     </row>
-    <row r="32" ht="132" customHeight="1">
+    <row r="32" ht="272" customHeight="1">
       <c r="A32" s="2" t="n"/>
       <c r="B32" s="13" t="inlineStr">
         <is>
@@ -3868,7 +3944,7 @@
       </c>
       <c r="S32" s="19" t="n"/>
     </row>
-    <row r="33" ht="132" customHeight="1">
+    <row r="33" ht="244" customHeight="1">
       <c r="A33" s="2" t="n"/>
       <c r="B33" s="5" t="inlineStr">
         <is>
@@ -3933,7 +4009,7 @@
       </c>
       <c r="S33" s="19" t="n"/>
     </row>
-    <row r="34" ht="132" customHeight="1">
+    <row r="34" ht="174" customHeight="1">
       <c r="A34" s="2" t="n"/>
       <c r="B34" s="5" t="inlineStr">
         <is>
@@ -3998,7 +4074,7 @@
       </c>
       <c r="S34" s="19" t="n"/>
     </row>
-    <row r="35" ht="132" customHeight="1">
+    <row r="35" ht="320" customHeight="1">
       <c r="A35" s="2" t="n"/>
       <c r="B35" s="5" t="inlineStr">
         <is>
@@ -4069,7 +4145,7 @@
       </c>
       <c r="S35" s="19" t="n"/>
     </row>
-    <row r="36" ht="132" customHeight="1">
+    <row r="36" ht="300" customHeight="1">
       <c r="A36" s="2" t="n"/>
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -4144,7 +4220,7 @@
       </c>
       <c r="S36" s="19" t="n"/>
     </row>
-    <row r="37" ht="132" customHeight="1">
+    <row r="37" ht="272" customHeight="1">
       <c r="A37" s="2" t="n"/>
       <c r="B37" s="5" t="inlineStr">
         <is>
@@ -4213,7 +4289,7 @@
       </c>
       <c r="S37" s="19" t="n"/>
     </row>
-    <row r="38" ht="62" customHeight="1">
+    <row r="38" ht="230" customHeight="1">
       <c r="A38" s="9" t="n"/>
       <c r="B38" s="10" t="inlineStr">
         <is>
@@ -4284,7 +4360,7 @@
       </c>
       <c r="S38" s="19" t="n"/>
     </row>
-    <row r="39" ht="132" customHeight="1">
+    <row r="39" ht="286" customHeight="1">
       <c r="A39" s="2" t="n"/>
       <c r="B39" s="5" t="inlineStr">
         <is>
@@ -4361,7 +4437,7 @@
       </c>
       <c r="S39" s="19" t="n"/>
     </row>
-    <row r="40" ht="132" customHeight="1">
+    <row r="40" ht="314" customHeight="1">
       <c r="A40" s="2" t="n"/>
       <c r="B40" s="5" t="inlineStr">
         <is>
@@ -4426,7 +4502,7 @@
       </c>
       <c r="S40" s="19" t="n"/>
     </row>
-    <row r="41" ht="132" customHeight="1">
+    <row r="41" ht="202" customHeight="1">
       <c r="A41" s="2" t="n"/>
       <c r="B41" s="13" t="inlineStr">
         <is>
@@ -4495,7 +4571,7 @@
       </c>
       <c r="S41" s="19" t="n"/>
     </row>
-    <row r="42" ht="132" customHeight="1">
+    <row r="42" ht="230" customHeight="1">
       <c r="A42" s="2" t="n"/>
       <c r="B42" s="5" t="inlineStr">
         <is>
@@ -4568,7 +4644,7 @@
       </c>
       <c r="S42" s="19" t="n"/>
     </row>
-    <row r="43" ht="132" customHeight="1">
+    <row r="43" ht="230" customHeight="1">
       <c r="A43" s="2" t="n"/>
       <c r="B43" s="5" t="inlineStr">
         <is>
@@ -4639,7 +4715,7 @@
       </c>
       <c r="S43" s="19" t="n"/>
     </row>
-    <row r="44" ht="132" customHeight="1">
+    <row r="44" ht="258" customHeight="1">
       <c r="A44" s="2" t="n"/>
       <c r="B44" s="5" t="inlineStr">
         <is>
@@ -5105,17 +5181,17 @@
           <t>A cartridge filter for hot tubs and swim spas, measuring 26.0 cm outer diameter, 13.0 cm bottom part, and 3.8 cm inner thread. Compatible with Darlly SC779 and 40372 codes, it captures dirt, grease, and fine particles to keep water clean.</t>
         </is>
       </c>
-      <c r="D2" s="25" t="inlineStr">
+      <c r="D2" s="30" t="inlineStr">
         <is>
           <t>Rising Dragon</t>
         </is>
       </c>
-      <c r="E2" s="25" t="inlineStr">
+      <c r="E2" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F2" s="25" t="inlineStr">
+      <c r="F2" s="30" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5125,71 +5201,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H2" s="25" t="inlineStr">
+      <c r="H2" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I2" s="25" t="inlineStr">
+      <c r="I2" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J2" s="25" t="inlineStr">
+      <c r="J2" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K2" s="25" t="inlineStr">
+      <c r="K2" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L2" s="25" t="inlineStr">
+      <c r="L2" s="30" t="inlineStr">
         <is>
           <t>RIS-FIL-2406</t>
         </is>
       </c>
-      <c r="M2" s="26" t="inlineStr">
+      <c r="M2" s="31" t="inlineStr">
         <is>
           <t>700175992406</t>
         </is>
       </c>
-      <c r="N2" s="27" t="inlineStr"/>
-      <c r="O2" s="27" t="inlineStr"/>
-      <c r="P2" s="27" t="inlineStr"/>
-      <c r="Q2" s="25" t="inlineStr">
+      <c r="N2" s="32" t="inlineStr"/>
+      <c r="O2" s="32" t="inlineStr"/>
+      <c r="P2" s="32" t="inlineStr"/>
+      <c r="Q2" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R2" s="25" t="inlineStr">
+      <c r="R2" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S2" s="25" t="inlineStr">
+      <c r="S2" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T2" s="25" t="inlineStr">
+      <c r="T2" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U2" s="25" t="inlineStr"/>
-      <c r="V2" s="25" t="inlineStr">
+      <c r="U2" s="30" t="inlineStr"/>
+      <c r="V2" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W2" s="25" t="inlineStr">
+      <c r="W2" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X2" s="25" t="inlineStr">
+      <c r="X2" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5199,7 +5275,7 @@
           <t>https://www.spa-components.com/user/shop/big/1473-1_filter-cartridge-sc779-rising-dragon-plastics--eago-whirlpools.jpg?ff=1&amp;x=1024&amp;y=768&amp;q=85&amp;ts=6720c4a0&amp;sg=161563f2</t>
         </is>
       </c>
-      <c r="Z2" s="25" t="inlineStr">
+      <c r="Z2" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5209,7 +5285,7 @@
           <t>Filter Cartridge SC779 - Rising Dragon Plastics, EAGO Whirlpools - Spa Components</t>
         </is>
       </c>
-      <c r="AB2" s="25" t="inlineStr">
+      <c r="AB2" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5221,10 +5297,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF2" s="25" t="inlineStr"/>
-      <c r="AG2" s="25" t="inlineStr"/>
-      <c r="AH2" s="25" t="inlineStr"/>
-      <c r="AI2" s="25" t="inlineStr"/>
+      <c r="AF2" s="30" t="inlineStr"/>
+      <c r="AG2" s="30" t="inlineStr"/>
+      <c r="AH2" s="30" t="inlineStr"/>
+      <c r="AI2" s="30" t="inlineStr"/>
     </row>
     <row r="3" ht="62" customHeight="1">
       <c r="A3" s="19" t="inlineStr">
@@ -5242,13 +5318,13 @@
           <t>A twin pack of Size II replacement filter cartridges measuring 10.6 x 13.6 cm, designed for compatible pool and spa filtration systems. The fine lamellar structure delivers thorough water cleaning and the cartridges are easy to rinse clean.</t>
         </is>
       </c>
-      <c r="D3" s="25" t="inlineStr"/>
-      <c r="E3" s="25" t="inlineStr">
+      <c r="D3" s="30" t="inlineStr"/>
+      <c r="E3" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F3" s="25" t="inlineStr">
+      <c r="F3" s="30" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5258,71 +5334,71 @@
           <t>filters, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H3" s="25" t="inlineStr">
+      <c r="H3" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I3" s="25" t="inlineStr">
+      <c r="I3" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J3" s="25" t="inlineStr">
+      <c r="J3" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K3" s="25" t="inlineStr">
+      <c r="K3" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L3" s="25" t="inlineStr">
+      <c r="L3" s="30" t="inlineStr">
         <is>
           <t>GEN-FIL-3615</t>
         </is>
       </c>
-      <c r="M3" s="26" t="inlineStr">
+      <c r="M3" s="31" t="inlineStr">
         <is>
           <t>6941607353615</t>
         </is>
       </c>
-      <c r="N3" s="27" t="inlineStr"/>
-      <c r="O3" s="27" t="inlineStr"/>
-      <c r="P3" s="27" t="inlineStr"/>
-      <c r="Q3" s="25" t="inlineStr">
+      <c r="N3" s="32" t="inlineStr"/>
+      <c r="O3" s="32" t="inlineStr"/>
+      <c r="P3" s="32" t="inlineStr"/>
+      <c r="Q3" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R3" s="25" t="inlineStr">
+      <c r="R3" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S3" s="25" t="inlineStr">
+      <c r="S3" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T3" s="25" t="inlineStr">
+      <c r="T3" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U3" s="25" t="inlineStr"/>
-      <c r="V3" s="25" t="inlineStr">
+      <c r="U3" s="30" t="inlineStr"/>
+      <c r="V3" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W3" s="25" t="inlineStr">
+      <c r="W3" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X3" s="25" t="inlineStr">
+      <c r="X3" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5332,7 +5408,7 @@
           <t>https://www.bestwaystore.de/media/c6/f8/ba/1756384660/6941607353615-main-jpg.jpg?ts=1756384660</t>
         </is>
       </c>
-      <c r="Z3" s="25" t="inlineStr">
+      <c r="Z3" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5342,7 +5418,7 @@
           <t>Filter cartridge Size II double pack, 10.6 x 13.6 cm | 58094_26</t>
         </is>
       </c>
-      <c r="AB3" s="25" t="inlineStr">
+      <c r="AB3" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5354,14 +5430,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF3" s="25" t="inlineStr"/>
-      <c r="AG3" s="25" t="inlineStr"/>
-      <c r="AH3" s="25" t="inlineStr">
+      <c r="AF3" s="30" t="inlineStr"/>
+      <c r="AG3" s="30" t="inlineStr"/>
+      <c r="AH3" s="30" t="inlineStr">
         <is>
           <t>10.6cm</t>
         </is>
       </c>
-      <c r="AI3" s="25" t="inlineStr">
+      <c r="AI3" s="30" t="inlineStr">
         <is>
           <t>13.6cm</t>
         </is>
@@ -5383,17 +5459,17 @@
           <t>A single Flowclear Size 3 replacement filter cartridge for compatible Bestway pool filtration systems, featuring a fine lamellar structure that traps deposits and dirt effectively. Easy to clean and straightforward to swap out when routine maintenance is due.</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>Bestway</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F4" s="25" t="inlineStr">
+      <c r="F4" s="30" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5403,71 +5479,71 @@
           <t>filters, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H4" s="25" t="inlineStr">
+      <c r="H4" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J4" s="25" t="inlineStr">
+      <c r="J4" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L4" s="25" t="inlineStr">
+      <c r="L4" s="30" t="inlineStr">
         <is>
           <t>BES-FIL-3592</t>
         </is>
       </c>
-      <c r="M4" s="26" t="inlineStr">
+      <c r="M4" s="31" t="inlineStr">
         <is>
           <t>6941607353592</t>
         </is>
       </c>
-      <c r="N4" s="27" t="inlineStr"/>
-      <c r="O4" s="27" t="inlineStr"/>
-      <c r="P4" s="27" t="inlineStr"/>
-      <c r="Q4" s="25" t="inlineStr">
+      <c r="N4" s="32" t="inlineStr"/>
+      <c r="O4" s="32" t="inlineStr"/>
+      <c r="P4" s="32" t="inlineStr"/>
+      <c r="Q4" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R4" s="25" t="inlineStr">
+      <c r="R4" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S4" s="25" t="inlineStr">
+      <c r="S4" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T4" s="25" t="inlineStr">
+      <c r="T4" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U4" s="25" t="inlineStr"/>
-      <c r="V4" s="25" t="inlineStr">
+      <c r="U4" s="30" t="inlineStr"/>
+      <c r="V4" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W4" s="25" t="inlineStr">
+      <c r="W4" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X4" s="25" t="inlineStr">
+      <c r="X4" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5477,7 +5553,7 @@
           <t>https://ap.nice-cdn.com/upload/image/product/large/default/bestway-flowclear-filter-cartridge-size-3-1-item-638140-en.jpg</t>
         </is>
       </c>
-      <c r="Z4" s="25" t="inlineStr">
+      <c r="Z4" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5487,7 +5563,7 @@
           <t>Bestway Flowclear™ Filter Cartridge Size 3, 1 item</t>
         </is>
       </c>
-      <c r="AB4" s="25" t="inlineStr">
+      <c r="AB4" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5499,10 +5575,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF4" s="25" t="inlineStr"/>
-      <c r="AG4" s="25" t="inlineStr"/>
-      <c r="AH4" s="25" t="inlineStr"/>
-      <c r="AI4" s="25" t="inlineStr"/>
+      <c r="AF4" s="30" t="inlineStr"/>
+      <c r="AG4" s="30" t="inlineStr"/>
+      <c r="AH4" s="30" t="inlineStr"/>
+      <c r="AI4" s="30" t="inlineStr"/>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
@@ -5520,17 +5596,17 @@
           <t>A two-pack of compatible hot tub and spa cartridge filters corresponding to Unicel C-4335, Pleatco PRB35-IN, and Filbur FC-2385 references. A handy spare-pair to keep on hand so your tub is never without a fresh filter.</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="30" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="30" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5540,71 +5616,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="J5" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="K5" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L5" s="25" t="inlineStr">
+      <c r="L5" s="30" t="inlineStr">
         <is>
           <t>DAR-FIL-1669</t>
         </is>
       </c>
-      <c r="M5" s="26" t="inlineStr">
+      <c r="M5" s="31" t="inlineStr">
         <is>
           <t>700175991669</t>
         </is>
       </c>
-      <c r="N5" s="27" t="inlineStr"/>
-      <c r="O5" s="27" t="inlineStr"/>
-      <c r="P5" s="27" t="inlineStr"/>
-      <c r="Q5" s="25" t="inlineStr">
+      <c r="N5" s="32" t="inlineStr"/>
+      <c r="O5" s="32" t="inlineStr"/>
+      <c r="P5" s="32" t="inlineStr"/>
+      <c r="Q5" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R5" s="25" t="inlineStr">
+      <c r="R5" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S5" s="25" t="inlineStr">
+      <c r="S5" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T5" s="25" t="inlineStr">
+      <c r="T5" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U5" s="25" t="inlineStr"/>
-      <c r="V5" s="25" t="inlineStr">
+      <c r="U5" s="30" t="inlineStr"/>
+      <c r="V5" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W5" s="25" t="inlineStr">
+      <c r="W5" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X5" s="25" t="inlineStr">
+      <c r="X5" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5614,7 +5690,7 @@
           <t>https://images.barcodelookup.com/29361/293617958-1.jpg</t>
         </is>
       </c>
-      <c r="Z5" s="25" t="inlineStr">
+      <c r="Z5" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5624,7 +5700,7 @@
           <t>Darlly Hot Tub Spa Filter SC705 40353 Compatible with Unicel C-4335 PRB35-IN Filbur FC-2385 2 Pack</t>
         </is>
       </c>
-      <c r="AB5" s="25" t="inlineStr">
+      <c r="AB5" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5636,10 +5712,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF5" s="25" t="inlineStr"/>
-      <c r="AG5" s="25" t="inlineStr"/>
-      <c r="AH5" s="25" t="inlineStr"/>
-      <c r="AI5" s="25" t="inlineStr"/>
+      <c r="AF5" s="30" t="inlineStr"/>
+      <c r="AG5" s="30" t="inlineStr"/>
+      <c r="AH5" s="30" t="inlineStr"/>
+      <c r="AI5" s="30" t="inlineStr"/>
     </row>
     <row r="6" ht="62" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -5657,13 +5733,13 @@
           <t>A single Size IV replacement filter cartridge measuring 14.2 x 25.4 cm, compatible with Bestway filter pump 58391 (9,463 l/h). Its deep-fold, fine-structure media delivers thorough water cleaning and can be rinsed clean with minimal effort.</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr"/>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr"/>
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F6" s="25" t="inlineStr">
+      <c r="F6" s="30" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5673,71 +5749,71 @@
           <t>filters, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H6" s="25" t="inlineStr">
+      <c r="H6" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I6" s="25" t="inlineStr">
+      <c r="I6" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J6" s="25" t="inlineStr">
+      <c r="J6" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K6" s="25" t="inlineStr">
+      <c r="K6" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L6" s="25" t="inlineStr">
+      <c r="L6" s="30" t="inlineStr">
         <is>
           <t>GEN-FIL-3622</t>
         </is>
       </c>
-      <c r="M6" s="26" t="inlineStr">
+      <c r="M6" s="31" t="inlineStr">
         <is>
           <t>6941607353622</t>
         </is>
       </c>
-      <c r="N6" s="27" t="inlineStr"/>
-      <c r="O6" s="27" t="inlineStr"/>
-      <c r="P6" s="27" t="inlineStr"/>
-      <c r="Q6" s="25" t="inlineStr">
+      <c r="N6" s="32" t="inlineStr"/>
+      <c r="O6" s="32" t="inlineStr"/>
+      <c r="P6" s="32" t="inlineStr"/>
+      <c r="Q6" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R6" s="25" t="inlineStr">
+      <c r="R6" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S6" s="25" t="inlineStr">
+      <c r="S6" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T6" s="25" t="inlineStr">
+      <c r="T6" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U6" s="25" t="inlineStr"/>
-      <c r="V6" s="25" t="inlineStr">
+      <c r="U6" s="30" t="inlineStr"/>
+      <c r="V6" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W6" s="25" t="inlineStr">
+      <c r="W6" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X6" s="25" t="inlineStr">
+      <c r="X6" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5747,7 +5823,7 @@
           <t>https://www.bestwaystore.de/media/53/6c/e9/1756384676/6941607353622-main-jpg.jpg?ts=1756384676</t>
         </is>
       </c>
-      <c r="Z6" s="25" t="inlineStr">
+      <c r="Z6" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5757,7 +5833,7 @@
           <t>Filter cartridge Size IV 14.2 x 25.4 cm | 58095_26</t>
         </is>
       </c>
-      <c r="AB6" s="25" t="inlineStr">
+      <c r="AB6" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5769,14 +5845,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF6" s="25" t="inlineStr"/>
-      <c r="AG6" s="25" t="inlineStr"/>
-      <c r="AH6" s="25" t="inlineStr">
+      <c r="AF6" s="30" t="inlineStr"/>
+      <c r="AG6" s="30" t="inlineStr"/>
+      <c r="AH6" s="30" t="inlineStr">
         <is>
           <t>14.2cm</t>
         </is>
       </c>
-      <c r="AI6" s="25" t="inlineStr">
+      <c r="AI6" s="30" t="inlineStr">
         <is>
           <t>25.4cm</t>
         </is>
@@ -5798,17 +5874,17 @@
           <t>A pair of Darlly spa filter cartridges in the SC726 reference, also cross-referenced as Unicel C-4401 and Pleatco PRB17.5SF PR. Buying in pairs means a fresh replacement is always ready when it is time to swap.</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F7" s="25" t="inlineStr">
+      <c r="F7" s="30" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5818,71 +5894,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H7" s="25" t="inlineStr">
+      <c r="H7" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="I7" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J7" s="25" t="inlineStr">
+      <c r="J7" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K7" s="25" t="inlineStr">
+      <c r="K7" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L7" s="25" t="inlineStr">
+      <c r="L7" s="30" t="inlineStr">
         <is>
           <t>DAR-FIL-1874</t>
         </is>
       </c>
-      <c r="M7" s="26" t="inlineStr">
+      <c r="M7" s="31" t="inlineStr">
         <is>
           <t>700175991874</t>
         </is>
       </c>
-      <c r="N7" s="27" t="inlineStr"/>
-      <c r="O7" s="27" t="inlineStr"/>
-      <c r="P7" s="27" t="inlineStr"/>
-      <c r="Q7" s="25" t="inlineStr">
+      <c r="N7" s="32" t="inlineStr"/>
+      <c r="O7" s="32" t="inlineStr"/>
+      <c r="P7" s="32" t="inlineStr"/>
+      <c r="Q7" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R7" s="25" t="inlineStr">
+      <c r="R7" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S7" s="25" t="inlineStr">
+      <c r="S7" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T7" s="25" t="inlineStr">
+      <c r="T7" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U7" s="25" t="inlineStr"/>
-      <c r="V7" s="25" t="inlineStr">
+      <c r="U7" s="30" t="inlineStr"/>
+      <c r="V7" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W7" s="25" t="inlineStr">
+      <c r="W7" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X7" s="25" t="inlineStr">
+      <c r="X7" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5892,7 +5968,7 @@
           <t>https://images.barcodelookup.com/4378/43786454-1.jpg</t>
         </is>
       </c>
-      <c r="Z7" s="25" t="inlineStr">
+      <c r="Z7" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5902,7 +5978,7 @@
           <t>Darlly Spa Filter C-4401, PRB17.5SF PR, SC726 (Pair)</t>
         </is>
       </c>
-      <c r="AB7" s="25" t="inlineStr">
+      <c r="AB7" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5914,10 +5990,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF7" s="25" t="inlineStr"/>
-      <c r="AG7" s="25" t="inlineStr"/>
-      <c r="AH7" s="25" t="inlineStr"/>
-      <c r="AI7" s="25" t="inlineStr"/>
+      <c r="AF7" s="30" t="inlineStr"/>
+      <c r="AG7" s="30" t="inlineStr"/>
+      <c r="AH7" s="30" t="inlineStr"/>
+      <c r="AI7" s="30" t="inlineStr"/>
     </row>
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -5935,17 +6011,17 @@
           <t>A replacement spa filter cartridge compatible with Arctic, Beachcomber, Canadian, Hydropool and Jacuzzi spas, sold under cross-reference codes including Unicel C-4950, Pleatco PRB50-IN and Darlly 40506. It keeps hot tub water clean by trapping debris and particles as water cycles through the filtration system.</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F8" s="25" t="inlineStr">
+      <c r="F8" s="30" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5955,71 +6031,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H8" s="25" t="inlineStr">
+      <c r="H8" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I8" s="25" t="inlineStr">
+      <c r="I8" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J8" s="25" t="inlineStr">
+      <c r="J8" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K8" s="25" t="inlineStr">
+      <c r="K8" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L8" s="25" t="inlineStr">
+      <c r="L8" s="30" t="inlineStr">
         <is>
           <t>DAR-FIL-1676</t>
         </is>
       </c>
-      <c r="M8" s="26" t="inlineStr">
+      <c r="M8" s="31" t="inlineStr">
         <is>
           <t>700175991676</t>
         </is>
       </c>
-      <c r="N8" s="27" t="inlineStr"/>
-      <c r="O8" s="27" t="inlineStr"/>
-      <c r="P8" s="27" t="inlineStr"/>
-      <c r="Q8" s="25" t="inlineStr">
+      <c r="N8" s="32" t="inlineStr"/>
+      <c r="O8" s="32" t="inlineStr"/>
+      <c r="P8" s="32" t="inlineStr"/>
+      <c r="Q8" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R8" s="25" t="inlineStr">
+      <c r="R8" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S8" s="25" t="inlineStr">
+      <c r="S8" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T8" s="25" t="inlineStr">
+      <c r="T8" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U8" s="25" t="inlineStr"/>
-      <c r="V8" s="25" t="inlineStr">
+      <c r="U8" s="30" t="inlineStr"/>
+      <c r="V8" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W8" s="25" t="inlineStr">
+      <c r="W8" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X8" s="25" t="inlineStr">
+      <c r="X8" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6029,7 +6105,7 @@
           <t>https://images.barcodelookup.com/4469/44699532-1.jpg</t>
         </is>
       </c>
-      <c r="Z8" s="25" t="inlineStr">
+      <c r="Z8" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6039,7 +6115,7 @@
           <t>Hot Tub Filter Unicel C4950 / C-4950 50' Spa Cartridge Pleatco PRB501N Darlly 40506 for Arctic, Beachcomber, Canadian,…</t>
         </is>
       </c>
-      <c r="AB8" s="25" t="inlineStr">
+      <c r="AB8" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6051,10 +6127,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF8" s="25" t="inlineStr"/>
-      <c r="AG8" s="25" t="inlineStr"/>
-      <c r="AH8" s="25" t="inlineStr"/>
-      <c r="AI8" s="25" t="inlineStr"/>
+      <c r="AF8" s="30" t="inlineStr"/>
+      <c r="AG8" s="30" t="inlineStr"/>
+      <c r="AH8" s="30" t="inlineStr"/>
+      <c r="AI8" s="30" t="inlineStr"/>
     </row>
     <row r="9" ht="76" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -6072,13 +6148,13 @@
           <t>A square inflatable hot tub for up to four people, with an overall outer diameter of 2.45 m and a structure measuring 1.75 x 1.75 x 0.71 m, built from high-resistance polyester for good rigidity and durability. The packaged weight is 64.92 kg, so you will want a helper on delivery day.</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr"/>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="D9" s="30" t="inlineStr"/>
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F9" s="25" t="inlineStr">
+      <c r="F9" s="30" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -6088,75 +6164,75 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H9" s="25" t="inlineStr">
+      <c r="H9" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I9" s="25" t="inlineStr">
+      <c r="I9" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J9" s="25" t="inlineStr">
+      <c r="J9" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K9" s="25" t="inlineStr">
+      <c r="K9" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L9" s="25" t="inlineStr">
+      <c r="L9" s="30" t="inlineStr">
         <is>
           <t>GEN-SPA-3395</t>
         </is>
       </c>
-      <c r="M9" s="26" t="inlineStr">
+      <c r="M9" s="31" t="inlineStr">
         <is>
           <t>6941057423395</t>
         </is>
       </c>
-      <c r="N9" s="27" t="inlineStr"/>
-      <c r="O9" s="27" t="inlineStr"/>
-      <c r="P9" s="27" t="inlineStr"/>
-      <c r="Q9" s="25" t="inlineStr">
+      <c r="N9" s="32" t="inlineStr"/>
+      <c r="O9" s="32" t="inlineStr"/>
+      <c r="P9" s="32" t="inlineStr"/>
+      <c r="Q9" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R9" s="25" t="inlineStr">
+      <c r="R9" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S9" s="25" t="inlineStr">
+      <c r="S9" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T9" s="25" t="inlineStr">
+      <c r="T9" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U9" s="25" t="inlineStr">
+      <c r="U9" s="30" t="inlineStr">
         <is>
           <t>64920</t>
         </is>
       </c>
-      <c r="V9" s="25" t="inlineStr">
+      <c r="V9" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W9" s="25" t="inlineStr">
+      <c r="W9" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X9" s="25" t="inlineStr">
+      <c r="X9" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6166,7 +6242,7 @@
           <t>https://media.intex.fr/7743-large_default_x2/28464ex-spa-gonflable-calacatta-4-places.jpg</t>
         </is>
       </c>
-      <c r="Z9" s="25" t="inlineStr">
+      <c r="Z9" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6176,7 +6252,7 @@
           <t>Calacatta 4-person inflatable spa</t>
         </is>
       </c>
-      <c r="AB9" s="25" t="inlineStr">
+      <c r="AB9" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6188,18 +6264,18 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF9" s="25" t="inlineStr"/>
-      <c r="AG9" s="25" t="inlineStr">
+      <c r="AF9" s="30" t="inlineStr"/>
+      <c r="AG9" s="30" t="inlineStr">
         <is>
           <t>175.0cm</t>
         </is>
       </c>
-      <c r="AH9" s="25" t="inlineStr">
+      <c r="AH9" s="30" t="inlineStr">
         <is>
           <t>175.0cm</t>
         </is>
       </c>
-      <c r="AI9" s="25" t="inlineStr">
+      <c r="AI9" s="30" t="inlineStr">
         <is>
           <t>71.0cm</t>
         </is>
@@ -6221,17 +6297,17 @@
           <t>A 3.0 kg tub of hth stabiliser granules for outdoor swimming pools, used to protect chlorine from UV degradation and extend its effectiveness. A reliable way to get more mileage from your sanitiser on sunny days.</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="30" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F10" s="25" t="inlineStr">
+      <c r="F10" s="30" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -6241,75 +6317,75 @@
           <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H10" s="25" t="inlineStr">
+      <c r="H10" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I10" s="25" t="inlineStr">
+      <c r="I10" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J10" s="25" t="inlineStr">
+      <c r="J10" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K10" s="25" t="inlineStr">
+      <c r="K10" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L10" s="25" t="inlineStr">
+      <c r="L10" s="30" t="inlineStr">
         <is>
           <t>HTH-CHM-5716</t>
         </is>
       </c>
-      <c r="M10" s="26" t="inlineStr">
+      <c r="M10" s="31" t="inlineStr">
         <is>
           <t>3521686005716</t>
         </is>
       </c>
-      <c r="N10" s="27" t="inlineStr"/>
-      <c r="O10" s="27" t="inlineStr"/>
-      <c r="P10" s="27" t="inlineStr"/>
-      <c r="Q10" s="25" t="inlineStr">
+      <c r="N10" s="32" t="inlineStr"/>
+      <c r="O10" s="32" t="inlineStr"/>
+      <c r="P10" s="32" t="inlineStr"/>
+      <c r="Q10" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R10" s="25" t="inlineStr">
+      <c r="R10" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S10" s="25" t="inlineStr">
+      <c r="S10" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T10" s="25" t="inlineStr">
+      <c r="T10" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U10" s="25" t="inlineStr">
+      <c r="U10" s="30" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="V10" s="25" t="inlineStr">
+      <c r="V10" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W10" s="25" t="inlineStr">
+      <c r="W10" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X10" s="25" t="inlineStr">
+      <c r="X10" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6319,7 +6395,7 @@
           <t>https://images.barcodelookup.com/12027/120276177-1.jpg</t>
         </is>
       </c>
-      <c r="Z10" s="25" t="inlineStr">
+      <c r="Z10" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6329,7 +6405,7 @@
           <t>Hth Stabilizer Granulat 3,0 Kg</t>
         </is>
       </c>
-      <c r="AB10" s="25" t="inlineStr">
+      <c r="AB10" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6341,10 +6417,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF10" s="25" t="inlineStr"/>
-      <c r="AG10" s="25" t="inlineStr"/>
-      <c r="AH10" s="25" t="inlineStr"/>
-      <c r="AI10" s="25" t="inlineStr"/>
+      <c r="AF10" s="30" t="inlineStr"/>
+      <c r="AG10" s="30" t="inlineStr"/>
+      <c r="AH10" s="30" t="inlineStr"/>
+      <c r="AI10" s="30" t="inlineStr"/>
     </row>
     <row r="11" ht="62" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -6362,17 +6438,17 @@
           <t>A 1-litre bottle of hth Spa Antikalk, formulated to prevent and remove limescale in spa and hot tub water. Keeping scale under control helps protect internal components and maintain water clarity.</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -6382,71 +6458,71 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H11" s="25" t="inlineStr">
+      <c r="H11" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I11" s="25" t="inlineStr">
+      <c r="I11" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J11" s="25" t="inlineStr">
+      <c r="J11" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K11" s="25" t="inlineStr">
+      <c r="K11" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L11" s="25" t="inlineStr">
+      <c r="L11" s="30" t="inlineStr">
         <is>
           <t>HTH-SPA-0194</t>
         </is>
       </c>
-      <c r="M11" s="26" t="inlineStr">
+      <c r="M11" s="31" t="inlineStr">
         <is>
           <t>3521684700194</t>
         </is>
       </c>
-      <c r="N11" s="27" t="inlineStr"/>
-      <c r="O11" s="27" t="inlineStr"/>
-      <c r="P11" s="27" t="inlineStr"/>
-      <c r="Q11" s="25" t="inlineStr">
+      <c r="N11" s="32" t="inlineStr"/>
+      <c r="O11" s="32" t="inlineStr"/>
+      <c r="P11" s="32" t="inlineStr"/>
+      <c r="Q11" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R11" s="25" t="inlineStr">
+      <c r="R11" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S11" s="25" t="inlineStr">
+      <c r="S11" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T11" s="25" t="inlineStr">
+      <c r="T11" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U11" s="25" t="inlineStr"/>
-      <c r="V11" s="25" t="inlineStr">
+      <c r="U11" s="30" t="inlineStr"/>
+      <c r="V11" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W11" s="25" t="inlineStr">
+      <c r="W11" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X11" s="25" t="inlineStr">
+      <c r="X11" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6456,7 +6532,7 @@
           <t>https://www.north-spa.de/wp-content/uploads/2025/02/Produktbild-1-hth-SPA-ANTIKALK-1-l-3521684700194-360x360.jpg</t>
         </is>
       </c>
-      <c r="Z11" s="25" t="inlineStr">
+      <c r="Z11" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6466,7 +6542,7 @@
           <t>1 l - hth® Spa ANTIKALK</t>
         </is>
       </c>
-      <c r="AB11" s="25" t="inlineStr">
+      <c r="AB11" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6478,10 +6554,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF11" s="25" t="inlineStr"/>
-      <c r="AG11" s="25" t="inlineStr"/>
-      <c r="AH11" s="25" t="inlineStr"/>
-      <c r="AI11" s="25" t="inlineStr"/>
+      <c r="AF11" s="30" t="inlineStr"/>
+      <c r="AG11" s="30" t="inlineStr"/>
+      <c r="AH11" s="30" t="inlineStr"/>
+      <c r="AI11" s="30" t="inlineStr"/>
     </row>
     <row r="12" ht="62" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -6499,13 +6575,13 @@
           <t>A round, olive-green inflatable spa designed to seat up to eight people comfortably, with a maximum water temperature of 40°C. Five accessories are included in the box, so there is plenty to get started with straight away.</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr"/>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="D12" s="30" t="inlineStr"/>
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F12" s="25" t="inlineStr">
+      <c r="F12" s="30" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -6515,71 +6591,71 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H12" s="25" t="inlineStr">
+      <c r="H12" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I12" s="25" t="inlineStr">
+      <c r="I12" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J12" s="25" t="inlineStr">
+      <c r="J12" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K12" s="25" t="inlineStr">
+      <c r="K12" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L12" s="25" t="inlineStr">
+      <c r="L12" s="30" t="inlineStr">
         <is>
           <t>GEN-SPA-9274</t>
         </is>
       </c>
-      <c r="M12" s="26" t="inlineStr">
+      <c r="M12" s="31" t="inlineStr">
         <is>
           <t>6941057429274</t>
         </is>
       </c>
-      <c r="N12" s="27" t="inlineStr"/>
-      <c r="O12" s="27" t="inlineStr"/>
-      <c r="P12" s="27" t="inlineStr"/>
-      <c r="Q12" s="25" t="inlineStr">
+      <c r="N12" s="32" t="inlineStr"/>
+      <c r="O12" s="32" t="inlineStr"/>
+      <c r="P12" s="32" t="inlineStr"/>
+      <c r="Q12" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R12" s="25" t="inlineStr">
+      <c r="R12" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S12" s="25" t="inlineStr">
+      <c r="S12" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T12" s="25" t="inlineStr">
+      <c r="T12" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U12" s="25" t="inlineStr"/>
-      <c r="V12" s="25" t="inlineStr">
+      <c r="U12" s="30" t="inlineStr"/>
+      <c r="V12" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W12" s="25" t="inlineStr">
+      <c r="W12" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X12" s="25" t="inlineStr">
+      <c r="X12" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6589,7 +6665,7 @@
           <t>https://media.intex.fr/11990-large_default_x2/28412np-spa-gonflable-olive-8-places.jpg</t>
         </is>
       </c>
-      <c r="Z12" s="25" t="inlineStr">
+      <c r="Z12" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6599,7 +6675,7 @@
           <t>Olive 8-person inflatable spa</t>
         </is>
       </c>
-      <c r="AB12" s="25" t="inlineStr">
+      <c r="AB12" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6611,10 +6687,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF12" s="25" t="inlineStr"/>
-      <c r="AG12" s="25" t="inlineStr"/>
-      <c r="AH12" s="25" t="inlineStr"/>
-      <c r="AI12" s="25" t="inlineStr"/>
+      <c r="AF12" s="30" t="inlineStr"/>
+      <c r="AG12" s="30" t="inlineStr"/>
+      <c r="AH12" s="30" t="inlineStr"/>
+      <c r="AI12" s="30" t="inlineStr"/>
     </row>
     <row r="13" ht="62" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -6632,17 +6708,17 @@
           <t>A Darlly SC750 replacement cartridge filter compatible with Arctic, Fonteyn, Rota, and Strong Spa hot tubs, among others. A straightforward like-for-like swap to keep your spa water flowing clean.</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F13" s="25" t="inlineStr">
+      <c r="F13" s="30" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6652,71 +6728,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H13" s="25" t="inlineStr">
+      <c r="H13" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I13" s="25" t="inlineStr">
+      <c r="I13" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J13" s="25" t="inlineStr">
+      <c r="J13" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K13" s="25" t="inlineStr">
+      <c r="K13" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L13" s="25" t="inlineStr">
+      <c r="L13" s="30" t="inlineStr">
         <is>
           <t>DAR-FIL-2116</t>
         </is>
       </c>
-      <c r="M13" s="26" t="inlineStr">
+      <c r="M13" s="31" t="inlineStr">
         <is>
           <t>700175992116</t>
         </is>
       </c>
-      <c r="N13" s="27" t="inlineStr"/>
-      <c r="O13" s="27" t="inlineStr"/>
-      <c r="P13" s="27" t="inlineStr"/>
-      <c r="Q13" s="25" t="inlineStr">
+      <c r="N13" s="32" t="inlineStr"/>
+      <c r="O13" s="32" t="inlineStr"/>
+      <c r="P13" s="32" t="inlineStr"/>
+      <c r="Q13" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R13" s="25" t="inlineStr">
+      <c r="R13" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S13" s="25" t="inlineStr">
+      <c r="S13" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T13" s="25" t="inlineStr">
+      <c r="T13" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U13" s="25" t="inlineStr"/>
-      <c r="V13" s="25" t="inlineStr">
+      <c r="U13" s="30" t="inlineStr"/>
+      <c r="V13" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W13" s="25" t="inlineStr">
+      <c r="W13" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X13" s="25" t="inlineStr">
+      <c r="X13" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6726,7 +6802,7 @@
           <t>https://images.barcodelookup.com/29338/293384728-1.jpg</t>
         </is>
       </c>
-      <c r="Z13" s="25" t="inlineStr">
+      <c r="Z13" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6736,7 +6812,7 @@
           <t>SC750 Filter replacement filter lamellar filter Arctic Fonteyn Rota Strong Spa - Darlly</t>
         </is>
       </c>
-      <c r="AB13" s="25" t="inlineStr">
+      <c r="AB13" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6748,10 +6824,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF13" s="25" t="inlineStr"/>
-      <c r="AG13" s="25" t="inlineStr"/>
-      <c r="AH13" s="25" t="inlineStr"/>
-      <c r="AI13" s="25" t="inlineStr"/>
+      <c r="AF13" s="30" t="inlineStr"/>
+      <c r="AG13" s="30" t="inlineStr"/>
+      <c r="AH13" s="30" t="inlineStr"/>
+      <c r="AI13" s="30" t="inlineStr"/>
     </row>
     <row r="14" ht="62" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -6769,17 +6845,17 @@
           <t>SpaBalancer Clean and Refresh is a spa water treatment product supplied with a sprayer for easy application. It is designed to keep spa water fresh and clean as part of a regular maintenance routine.</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="30" t="inlineStr">
         <is>
           <t>SpaBalancer</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F14" s="25" t="inlineStr">
+      <c r="F14" s="30" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -6789,71 +6865,71 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H14" s="25" t="inlineStr">
+      <c r="H14" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I14" s="25" t="inlineStr">
+      <c r="I14" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J14" s="25" t="inlineStr">
+      <c r="J14" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K14" s="25" t="inlineStr">
+      <c r="K14" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L14" s="25" t="inlineStr">
+      <c r="L14" s="30" t="inlineStr">
         <is>
           <t>SPA-CLN-0117</t>
         </is>
       </c>
-      <c r="M14" s="26" t="inlineStr">
+      <c r="M14" s="31" t="inlineStr">
         <is>
           <t>4260374980117</t>
         </is>
       </c>
-      <c r="N14" s="27" t="inlineStr"/>
-      <c r="O14" s="27" t="inlineStr"/>
-      <c r="P14" s="27" t="inlineStr"/>
-      <c r="Q14" s="25" t="inlineStr">
+      <c r="N14" s="32" t="inlineStr"/>
+      <c r="O14" s="32" t="inlineStr"/>
+      <c r="P14" s="32" t="inlineStr"/>
+      <c r="Q14" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R14" s="25" t="inlineStr">
+      <c r="R14" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S14" s="25" t="inlineStr">
+      <c r="S14" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T14" s="25" t="inlineStr">
+      <c r="T14" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U14" s="25" t="inlineStr"/>
-      <c r="V14" s="25" t="inlineStr">
+      <c r="U14" s="30" t="inlineStr"/>
+      <c r="V14" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W14" s="25" t="inlineStr">
+      <c r="W14" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X14" s="25" t="inlineStr">
+      <c r="X14" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6863,7 +6939,7 @@
           <t>https://www.spabalancer.ch/media/ae/20/d2/1728651174/sb111_clean-refresh_freigestellt.png?ts=1777362921</t>
         </is>
       </c>
-      <c r="Z14" s="25" t="inlineStr">
+      <c r="Z14" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6873,7 +6949,7 @@
           <t>SpaBalancer Clean &amp; Refresh (+ sprayer)</t>
         </is>
       </c>
-      <c r="AB14" s="25" t="inlineStr">
+      <c r="AB14" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6885,10 +6961,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF14" s="25" t="inlineStr"/>
-      <c r="AG14" s="25" t="inlineStr"/>
-      <c r="AH14" s="25" t="inlineStr"/>
-      <c r="AI14" s="25" t="inlineStr"/>
+      <c r="AF14" s="30" t="inlineStr"/>
+      <c r="AG14" s="30" t="inlineStr"/>
+      <c r="AH14" s="30" t="inlineStr"/>
+      <c r="AI14" s="30" t="inlineStr"/>
     </row>
     <row r="15" ht="62" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -6906,17 +6982,17 @@
           <t>A pack of 500 DPD 1 reagent tablets for use with the Water-ID photometer, measuring free chlorine levels in pool or spa water. Having a full pack to hand means you will not run short mid-season.</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="D15" s="30" t="inlineStr">
         <is>
           <t>Water-i.d.</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F15" s="25" t="inlineStr">
+      <c r="F15" s="30" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -6926,79 +7002,79 @@
           <t>test-measure, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H15" s="25" t="inlineStr">
+      <c r="H15" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I15" s="25" t="inlineStr">
+      <c r="I15" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J15" s="25" t="inlineStr">
+      <c r="J15" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K15" s="25" t="inlineStr">
+      <c r="K15" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L15" s="25" t="inlineStr">
+      <c r="L15" s="30" t="inlineStr">
         <is>
           <t>WAT-TST-1702</t>
         </is>
       </c>
-      <c r="M15" s="26" t="inlineStr">
+      <c r="M15" s="31" t="inlineStr">
         <is>
           <t>4260431461702</t>
         </is>
       </c>
-      <c r="N15" s="27" t="inlineStr"/>
-      <c r="O15" s="27" t="inlineStr"/>
-      <c r="P15" s="27" t="inlineStr"/>
-      <c r="Q15" s="25" t="inlineStr">
+      <c r="N15" s="32" t="inlineStr"/>
+      <c r="O15" s="32" t="inlineStr"/>
+      <c r="P15" s="32" t="inlineStr"/>
+      <c r="Q15" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R15" s="25" t="inlineStr">
+      <c r="R15" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S15" s="25" t="inlineStr">
+      <c r="S15" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T15" s="25" t="inlineStr">
+      <c r="T15" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U15" s="25" t="inlineStr"/>
-      <c r="V15" s="25" t="inlineStr">
+      <c r="U15" s="30" t="inlineStr"/>
+      <c r="V15" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W15" s="25" t="inlineStr">
+      <c r="W15" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X15" s="25" t="inlineStr">
+      <c r="X15" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y15" s="19" t="inlineStr"/>
-      <c r="Z15" s="25" t="inlineStr"/>
+      <c r="Z15" s="30" t="inlineStr"/>
       <c r="AA15" s="19" t="inlineStr"/>
-      <c r="AB15" s="25" t="inlineStr">
+      <c r="AB15" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7010,10 +7086,10 @@
           <t>Pool Accessories</t>
         </is>
       </c>
-      <c r="AF15" s="25" t="inlineStr"/>
-      <c r="AG15" s="25" t="inlineStr"/>
-      <c r="AH15" s="25" t="inlineStr"/>
-      <c r="AI15" s="25" t="inlineStr"/>
+      <c r="AF15" s="30" t="inlineStr"/>
+      <c r="AG15" s="30" t="inlineStr"/>
+      <c r="AH15" s="30" t="inlineStr"/>
+      <c r="AI15" s="30" t="inlineStr"/>
     </row>
     <row r="16" ht="62" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -7031,17 +7107,17 @@
           <t>A pack of 500 Phenol Red reagent tablets compatible with the Water-ID photometer, used for measuring pH levels in pool or spa water. Accurate pH readings are the foundation of balanced, comfortable water.</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="30" t="inlineStr">
         <is>
           <t>Water-i.d.</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="30" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F16" s="25" t="inlineStr">
+      <c r="F16" s="30" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -7051,71 +7127,71 @@
           <t>test-measure, add-on, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H16" s="25" t="inlineStr">
+      <c r="H16" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I16" s="25" t="inlineStr">
+      <c r="I16" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J16" s="25" t="inlineStr">
+      <c r="J16" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K16" s="25" t="inlineStr">
+      <c r="K16" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L16" s="25" t="inlineStr">
+      <c r="L16" s="30" t="inlineStr">
         <is>
           <t>WAT-TST-1801</t>
         </is>
       </c>
-      <c r="M16" s="26" t="inlineStr">
+      <c r="M16" s="31" t="inlineStr">
         <is>
           <t>4260431461801</t>
         </is>
       </c>
-      <c r="N16" s="27" t="inlineStr"/>
-      <c r="O16" s="27" t="inlineStr"/>
-      <c r="P16" s="27" t="inlineStr"/>
-      <c r="Q16" s="25" t="inlineStr">
+      <c r="N16" s="32" t="inlineStr"/>
+      <c r="O16" s="32" t="inlineStr"/>
+      <c r="P16" s="32" t="inlineStr"/>
+      <c r="Q16" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R16" s="25" t="inlineStr">
+      <c r="R16" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S16" s="25" t="inlineStr">
+      <c r="S16" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T16" s="25" t="inlineStr">
+      <c r="T16" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U16" s="25" t="inlineStr"/>
-      <c r="V16" s="25" t="inlineStr">
+      <c r="U16" s="30" t="inlineStr"/>
+      <c r="V16" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W16" s="25" t="inlineStr">
+      <c r="W16" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X16" s="25" t="inlineStr">
+      <c r="X16" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7125,7 +7201,7 @@
           <t>https://www.poolpowershop.de/media/46/63/13/1743521499/phenol-red-testtabletten-fuer-poollab-500-stk.jpg</t>
         </is>
       </c>
-      <c r="Z16" s="25" t="inlineStr">
+      <c r="Z16" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7135,7 +7211,7 @@
           <t>WATER-I.D. Water-ID Reagenzien Phenol Red Photometer 500</t>
         </is>
       </c>
-      <c r="AB16" s="25" t="inlineStr">
+      <c r="AB16" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7147,10 +7223,10 @@
           <t>Pool Accessories</t>
         </is>
       </c>
-      <c r="AF16" s="25" t="inlineStr"/>
-      <c r="AG16" s="25" t="inlineStr"/>
-      <c r="AH16" s="25" t="inlineStr"/>
-      <c r="AI16" s="25" t="inlineStr"/>
+      <c r="AF16" s="30" t="inlineStr"/>
+      <c r="AG16" s="30" t="inlineStr"/>
+      <c r="AH16" s="30" t="inlineStr"/>
+      <c r="AI16" s="30" t="inlineStr"/>
     </row>
     <row r="17" ht="62" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -7168,17 +7244,17 @@
           <t>An alkaline edge and surround cleaner in a 1-litre bottle, formulated to be gentle on pool liners, foils, and plastic surfaces. It tackles waterline grime without harming the materials it touches.</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D17" s="30" t="inlineStr">
         <is>
           <t>Cristal</t>
         </is>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E17" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F17" s="25" t="inlineStr">
+      <c r="F17" s="30" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -7188,71 +7264,71 @@
           <t>pool, water-treatment, cleaning, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H17" s="25" t="inlineStr">
+      <c r="H17" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I17" s="25" t="inlineStr">
+      <c r="I17" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J17" s="25" t="inlineStr">
+      <c r="J17" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K17" s="25" t="inlineStr">
+      <c r="K17" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L17" s="25" t="inlineStr">
+      <c r="L17" s="30" t="inlineStr">
         <is>
           <t>CRI-CHM-5212</t>
         </is>
       </c>
-      <c r="M17" s="26" t="inlineStr">
+      <c r="M17" s="31" t="inlineStr">
         <is>
           <t>4002369155212</t>
         </is>
       </c>
-      <c r="N17" s="27" t="inlineStr"/>
-      <c r="O17" s="27" t="inlineStr"/>
-      <c r="P17" s="27" t="inlineStr"/>
-      <c r="Q17" s="25" t="inlineStr">
+      <c r="N17" s="32" t="inlineStr"/>
+      <c r="O17" s="32" t="inlineStr"/>
+      <c r="P17" s="32" t="inlineStr"/>
+      <c r="Q17" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R17" s="25" t="inlineStr">
+      <c r="R17" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S17" s="25" t="inlineStr">
+      <c r="S17" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T17" s="25" t="inlineStr">
+      <c r="T17" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U17" s="25" t="inlineStr"/>
-      <c r="V17" s="25" t="inlineStr">
+      <c r="U17" s="30" t="inlineStr"/>
+      <c r="V17" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W17" s="25" t="inlineStr">
+      <c r="W17" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X17" s="25" t="inlineStr">
+      <c r="X17" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7262,7 +7338,7 @@
           <t>https://images.barcodelookup.com/21057/210579756-1.jpg</t>
         </is>
       </c>
-      <c r="Z17" s="25" t="inlineStr">
+      <c r="Z17" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7272,7 +7348,7 @@
           <t>Cristal Poolpflege CRISTAL edge cleaner alkaline 1,0 l, (material-safe, for liners, plastic</t>
         </is>
       </c>
-      <c r="AB17" s="25" t="inlineStr">
+      <c r="AB17" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7284,10 +7360,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF17" s="25" t="inlineStr"/>
-      <c r="AG17" s="25" t="inlineStr"/>
-      <c r="AH17" s="25" t="inlineStr"/>
-      <c r="AI17" s="25" t="inlineStr"/>
+      <c r="AF17" s="30" t="inlineStr"/>
+      <c r="AG17" s="30" t="inlineStr"/>
+      <c r="AH17" s="30" t="inlineStr"/>
+      <c r="AI17" s="30" t="inlineStr"/>
     </row>
     <row r="18" ht="76" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -7305,17 +7381,17 @@
           <t>A 1-litre pool surface cleaner formulated to remove sunscreen oils and greasy residues from the water surface, designed specifically for warm Mediterranean climates and heavy swimming loads. It keeps the waterline and surface clear without harming pool materials.</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D18" s="30" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E18" s="25" t="inlineStr">
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F18" s="25" t="inlineStr">
+      <c r="F18" s="30" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -7325,71 +7401,71 @@
           <t>pool, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H18" s="25" t="inlineStr">
+      <c r="H18" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I18" s="25" t="inlineStr">
+      <c r="I18" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J18" s="25" t="inlineStr">
+      <c r="J18" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K18" s="25" t="inlineStr">
+      <c r="K18" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L18" s="25" t="inlineStr">
+      <c r="L18" s="30" t="inlineStr">
         <is>
           <t>AQU-CLN-0223</t>
         </is>
       </c>
-      <c r="M18" s="26" t="inlineStr">
+      <c r="M18" s="31" t="inlineStr">
         <is>
           <t>5292638000223</t>
         </is>
       </c>
-      <c r="N18" s="27" t="inlineStr"/>
-      <c r="O18" s="27" t="inlineStr"/>
-      <c r="P18" s="27" t="inlineStr"/>
-      <c r="Q18" s="25" t="inlineStr">
+      <c r="N18" s="32" t="inlineStr"/>
+      <c r="O18" s="32" t="inlineStr"/>
+      <c r="P18" s="32" t="inlineStr"/>
+      <c r="Q18" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R18" s="25" t="inlineStr">
+      <c r="R18" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S18" s="25" t="inlineStr">
+      <c r="S18" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T18" s="25" t="inlineStr">
+      <c r="T18" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U18" s="25" t="inlineStr"/>
-      <c r="V18" s="25" t="inlineStr">
+      <c r="U18" s="30" t="inlineStr"/>
+      <c r="V18" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W18" s="25" t="inlineStr">
+      <c r="W18" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X18" s="25" t="inlineStr">
+      <c r="X18" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7399,7 +7475,7 @@
           <t>http://mangas.com.cy/media/products/5292638000223.jpg</t>
         </is>
       </c>
-      <c r="Z18" s="25" t="inlineStr">
+      <c r="Z18" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7409,7 +7485,7 @@
           <t>AQUALITY Pool cleaner for greasy residue 1L</t>
         </is>
       </c>
-      <c r="AB18" s="25" t="inlineStr">
+      <c r="AB18" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7421,10 +7497,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF18" s="25" t="inlineStr"/>
-      <c r="AG18" s="25" t="inlineStr"/>
-      <c r="AH18" s="25" t="inlineStr"/>
-      <c r="AI18" s="25" t="inlineStr"/>
+      <c r="AF18" s="30" t="inlineStr"/>
+      <c r="AG18" s="30" t="inlineStr"/>
+      <c r="AH18" s="30" t="inlineStr"/>
+      <c r="AI18" s="30" t="inlineStr"/>
     </row>
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
@@ -7442,17 +7518,17 @@
           <t>California Clear Blue is a super-concentrated, pH-neutral pool clarifier in a 1-litre bottle, using a cationic polymer formula to bind microscopic particles such as dust, pollen, and oils into larger clusters your filter can catch. Non-toxic and biodegradable, it is safe for sand, zeolite, and glass filtration media.</t>
         </is>
       </c>
-      <c r="D19" s="25" t="inlineStr">
+      <c r="D19" s="30" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E19" s="25" t="inlineStr">
+      <c r="E19" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F19" s="25" t="inlineStr">
+      <c r="F19" s="30" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -7462,71 +7538,71 @@
           <t>pool, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H19" s="25" t="inlineStr">
+      <c r="H19" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I19" s="25" t="inlineStr">
+      <c r="I19" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J19" s="25" t="inlineStr">
+      <c r="J19" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K19" s="25" t="inlineStr">
+      <c r="K19" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L19" s="25" t="inlineStr">
+      <c r="L19" s="30" t="inlineStr">
         <is>
           <t>AQU-CHM-0070</t>
         </is>
       </c>
-      <c r="M19" s="26" t="inlineStr">
+      <c r="M19" s="31" t="inlineStr">
         <is>
           <t>5292638000070</t>
         </is>
       </c>
-      <c r="N19" s="27" t="inlineStr"/>
-      <c r="O19" s="27" t="inlineStr"/>
-      <c r="P19" s="27" t="inlineStr"/>
-      <c r="Q19" s="25" t="inlineStr">
+      <c r="N19" s="32" t="inlineStr"/>
+      <c r="O19" s="32" t="inlineStr"/>
+      <c r="P19" s="32" t="inlineStr"/>
+      <c r="Q19" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R19" s="25" t="inlineStr">
+      <c r="R19" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S19" s="25" t="inlineStr">
+      <c r="S19" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T19" s="25" t="inlineStr">
+      <c r="T19" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U19" s="25" t="inlineStr"/>
-      <c r="V19" s="25" t="inlineStr">
+      <c r="U19" s="30" t="inlineStr"/>
+      <c r="V19" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W19" s="25" t="inlineStr">
+      <c r="W19" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X19" s="25" t="inlineStr">
+      <c r="X19" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7536,7 +7612,7 @@
           <t>https://poolservices.cy/storage/2026/05/California-Clear-Blue-1L-Aquality-2.jpeg</t>
         </is>
       </c>
-      <c r="Z19" s="25" t="inlineStr">
+      <c r="Z19" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7546,7 +7622,7 @@
           <t>Pool Clarifier California Clear Blue Aquality 1L</t>
         </is>
       </c>
-      <c r="AB19" s="25" t="inlineStr">
+      <c r="AB19" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7558,10 +7634,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF19" s="25" t="inlineStr"/>
-      <c r="AG19" s="25" t="inlineStr"/>
-      <c r="AH19" s="25" t="inlineStr"/>
-      <c r="AI19" s="25" t="inlineStr"/>
+      <c r="AF19" s="30" t="inlineStr"/>
+      <c r="AG19" s="30" t="inlineStr"/>
+      <c r="AH19" s="30" t="inlineStr"/>
+      <c r="AI19" s="30" t="inlineStr"/>
     </row>
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -7579,17 +7655,17 @@
           <t>A 1-litre tile and vinyl cleaner for pools, designed to clean pool tile surfaces and vinyl liners. It makes light work of the tidying up that keeps a pool looking its best.</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D20" s="30" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E20" s="25" t="inlineStr">
+      <c r="E20" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F20" s="25" t="inlineStr">
+      <c r="F20" s="30" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -7599,71 +7675,71 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H20" s="25" t="inlineStr">
+      <c r="H20" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I20" s="25" t="inlineStr">
+      <c r="I20" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J20" s="25" t="inlineStr">
+      <c r="J20" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K20" s="25" t="inlineStr">
+      <c r="K20" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L20" s="25" t="inlineStr">
+      <c r="L20" s="30" t="inlineStr">
         <is>
           <t>AQU-CLN-0162</t>
         </is>
       </c>
-      <c r="M20" s="26" t="inlineStr">
+      <c r="M20" s="31" t="inlineStr">
         <is>
           <t>5292638000162</t>
         </is>
       </c>
-      <c r="N20" s="27" t="inlineStr"/>
-      <c r="O20" s="27" t="inlineStr"/>
-      <c r="P20" s="27" t="inlineStr"/>
-      <c r="Q20" s="25" t="inlineStr">
+      <c r="N20" s="32" t="inlineStr"/>
+      <c r="O20" s="32" t="inlineStr"/>
+      <c r="P20" s="32" t="inlineStr"/>
+      <c r="Q20" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R20" s="25" t="inlineStr">
+      <c r="R20" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S20" s="25" t="inlineStr">
+      <c r="S20" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T20" s="25" t="inlineStr">
+      <c r="T20" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U20" s="25" t="inlineStr"/>
-      <c r="V20" s="25" t="inlineStr">
+      <c r="U20" s="30" t="inlineStr"/>
+      <c r="V20" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W20" s="25" t="inlineStr">
+      <c r="W20" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X20" s="25" t="inlineStr">
+      <c r="X20" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7673,7 +7749,7 @@
           <t>http://mangas.com.cy/media/products/5292638000162.jpg</t>
         </is>
       </c>
-      <c r="Z20" s="25" t="inlineStr">
+      <c r="Z20" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7683,7 +7759,7 @@
           <t>AQUALITY Magic tile 4 vinyl cleaner 1L</t>
         </is>
       </c>
-      <c r="AB20" s="25" t="inlineStr">
+      <c r="AB20" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7695,10 +7771,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF20" s="25" t="inlineStr"/>
-      <c r="AG20" s="25" t="inlineStr"/>
-      <c r="AH20" s="25" t="inlineStr"/>
-      <c r="AI20" s="25" t="inlineStr"/>
+      <c r="AF20" s="30" t="inlineStr"/>
+      <c r="AG20" s="30" t="inlineStr"/>
+      <c r="AH20" s="30" t="inlineStr"/>
+      <c r="AI20" s="30" t="inlineStr"/>
     </row>
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
@@ -7716,17 +7792,17 @@
           <t>A 1-litre spa and pool water clarifier from Bayzid, formulated to clear cloudy or turbid water. A handy bottle to reach for whenever the water loses its sparkle.</t>
         </is>
       </c>
-      <c r="D21" s="25" t="inlineStr">
+      <c r="D21" s="30" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E21" s="25" t="inlineStr">
+      <c r="E21" s="30" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F21" s="25" t="inlineStr">
+      <c r="F21" s="30" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -7736,71 +7812,71 @@
           <t>spa-hot-tub, pool, water-treatment, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H21" s="25" t="inlineStr">
+      <c r="H21" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I21" s="25" t="inlineStr">
+      <c r="I21" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J21" s="25" t="inlineStr">
+      <c r="J21" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K21" s="25" t="inlineStr">
+      <c r="K21" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L21" s="25" t="inlineStr">
+      <c r="L21" s="30" t="inlineStr">
         <is>
           <t>HFE-SPA-7202</t>
         </is>
       </c>
-      <c r="M21" s="26" t="inlineStr">
+      <c r="M21" s="31" t="inlineStr">
         <is>
           <t>4250463127202</t>
         </is>
       </c>
-      <c r="N21" s="27" t="inlineStr"/>
-      <c r="O21" s="27" t="inlineStr"/>
-      <c r="P21" s="27" t="inlineStr"/>
-      <c r="Q21" s="25" t="inlineStr">
+      <c r="N21" s="32" t="inlineStr"/>
+      <c r="O21" s="32" t="inlineStr"/>
+      <c r="P21" s="32" t="inlineStr"/>
+      <c r="Q21" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R21" s="25" t="inlineStr">
+      <c r="R21" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S21" s="25" t="inlineStr">
+      <c r="S21" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T21" s="25" t="inlineStr">
+      <c r="T21" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U21" s="25" t="inlineStr"/>
-      <c r="V21" s="25" t="inlineStr">
+      <c r="U21" s="30" t="inlineStr"/>
+      <c r="V21" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W21" s="25" t="inlineStr">
+      <c r="W21" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X21" s="25" t="inlineStr">
+      <c r="X21" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7810,7 +7886,7 @@
           <t>https://hoefer-shop.com/cdn/shop/files/1x1L-BAYZID-Spa-Poolclear-v1-RS_1.jpg?v=1785600487&amp;width=800</t>
         </is>
       </c>
-      <c r="Z21" s="25" t="inlineStr">
+      <c r="Z21" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7820,7 +7896,7 @@
           <t>Höfer Chemie GmbH pool care 1 L BAYZID® SPA Poolclear turbidity remover</t>
         </is>
       </c>
-      <c r="AB21" s="25" t="inlineStr">
+      <c r="AB21" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7832,10 +7908,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF21" s="25" t="inlineStr"/>
-      <c r="AG21" s="25" t="inlineStr"/>
-      <c r="AH21" s="25" t="inlineStr"/>
-      <c r="AI21" s="25" t="inlineStr"/>
+      <c r="AF21" s="30" t="inlineStr"/>
+      <c r="AG21" s="30" t="inlineStr"/>
+      <c r="AH21" s="30" t="inlineStr"/>
+      <c r="AI21" s="30" t="inlineStr"/>
     </row>
     <row r="22" ht="62" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
@@ -7853,17 +7929,17 @@
           <t>A 1-litre bottle of hydrogen peroxide at 11.9% concentration, suitable for disinfection and water treatment applications. A straightforward chemical solution that keeps things clean without fuss.</t>
         </is>
       </c>
-      <c r="D22" s="25" t="inlineStr">
+      <c r="D22" s="30" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E22" s="25" t="inlineStr">
+      <c r="E22" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F22" s="25" t="inlineStr">
+      <c r="F22" s="30" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -7873,71 +7949,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H22" s="25" t="inlineStr">
+      <c r="H22" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I22" s="25" t="inlineStr">
+      <c r="I22" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J22" s="25" t="inlineStr">
+      <c r="J22" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K22" s="25" t="inlineStr">
+      <c r="K22" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L22" s="25" t="inlineStr">
+      <c r="L22" s="30" t="inlineStr">
         <is>
           <t>HFE-CHM-6788</t>
         </is>
       </c>
-      <c r="M22" s="26" t="inlineStr">
+      <c r="M22" s="31" t="inlineStr">
         <is>
           <t>4250463106788</t>
         </is>
       </c>
-      <c r="N22" s="27" t="inlineStr"/>
-      <c r="O22" s="27" t="inlineStr"/>
-      <c r="P22" s="27" t="inlineStr"/>
-      <c r="Q22" s="25" t="inlineStr">
+      <c r="N22" s="32" t="inlineStr"/>
+      <c r="O22" s="32" t="inlineStr"/>
+      <c r="P22" s="32" t="inlineStr"/>
+      <c r="Q22" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R22" s="25" t="inlineStr">
+      <c r="R22" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S22" s="25" t="inlineStr">
+      <c r="S22" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T22" s="25" t="inlineStr">
+      <c r="T22" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U22" s="25" t="inlineStr"/>
-      <c r="V22" s="25" t="inlineStr">
+      <c r="U22" s="30" t="inlineStr"/>
+      <c r="V22" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W22" s="25" t="inlineStr">
+      <c r="W22" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X22" s="25" t="inlineStr">
+      <c r="X22" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7947,7 +8023,7 @@
           <t>https://hoefer-shop.com/cdn/shop/files/1x1L-Wasserstoffperoxid-Flasche-hinten-26.jpg?v=1783777627&amp;width=1000</t>
         </is>
       </c>
-      <c r="Z22" s="25" t="inlineStr">
+      <c r="Z22" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7957,7 +8033,7 @@
           <t>HÖFER CHEMIE GMBH 1 l hydrogen peroxide 11,9%</t>
         </is>
       </c>
-      <c r="AB22" s="25" t="inlineStr">
+      <c r="AB22" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7969,10 +8045,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF22" s="25" t="inlineStr"/>
-      <c r="AG22" s="25" t="inlineStr"/>
-      <c r="AH22" s="25" t="inlineStr"/>
-      <c r="AI22" s="25" t="inlineStr"/>
+      <c r="AF22" s="30" t="inlineStr"/>
+      <c r="AG22" s="30" t="inlineStr"/>
+      <c r="AH22" s="30" t="inlineStr"/>
+      <c r="AI22" s="30" t="inlineStr"/>
     </row>
     <row r="23" ht="62" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
@@ -7990,17 +8066,17 @@
           <t>A 4.5 kg pack of chlorine stabilizer for swimming pools, used to protect chlorine from UV degradation and extend its effectiveness in the water. Steady chemistry for a pool that earns its keep.</t>
         </is>
       </c>
-      <c r="D23" s="25" t="inlineStr">
+      <c r="D23" s="30" t="inlineStr">
         <is>
           <t>AstralPool</t>
         </is>
       </c>
-      <c r="E23" s="25" t="inlineStr">
+      <c r="E23" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F23" s="25" t="inlineStr">
+      <c r="F23" s="30" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8010,75 +8086,75 @@
           <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H23" s="25" t="inlineStr">
+      <c r="H23" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I23" s="25" t="inlineStr">
+      <c r="I23" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J23" s="25" t="inlineStr">
+      <c r="J23" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K23" s="25" t="inlineStr">
+      <c r="K23" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L23" s="25" t="inlineStr">
+      <c r="L23" s="30" t="inlineStr">
         <is>
           <t>AST-CHM-0626</t>
         </is>
       </c>
-      <c r="M23" s="26" t="inlineStr">
+      <c r="M23" s="31" t="inlineStr">
         <is>
           <t>8432611960626</t>
         </is>
       </c>
-      <c r="N23" s="27" t="inlineStr"/>
-      <c r="O23" s="27" t="inlineStr"/>
-      <c r="P23" s="27" t="inlineStr"/>
-      <c r="Q23" s="25" t="inlineStr">
+      <c r="N23" s="32" t="inlineStr"/>
+      <c r="O23" s="32" t="inlineStr"/>
+      <c r="P23" s="32" t="inlineStr"/>
+      <c r="Q23" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R23" s="25" t="inlineStr">
+      <c r="R23" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S23" s="25" t="inlineStr">
+      <c r="S23" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T23" s="25" t="inlineStr">
+      <c r="T23" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U23" s="25" t="inlineStr">
+      <c r="U23" s="30" t="inlineStr">
         <is>
           <t>4500</t>
         </is>
       </c>
-      <c r="V23" s="25" t="inlineStr">
+      <c r="V23" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W23" s="25" t="inlineStr">
+      <c r="W23" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X23" s="25" t="inlineStr">
+      <c r="X23" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8088,7 +8164,7 @@
           <t>https://yokando.com/img/p/2/8/2/9/3/28293.jpg</t>
         </is>
       </c>
-      <c r="Z23" s="25" t="inlineStr">
+      <c r="Z23" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8098,7 +8174,7 @@
           <t>Astralpool water care Astralpool Chlorine Stabilizer 4,5 kg</t>
         </is>
       </c>
-      <c r="AB23" s="25" t="inlineStr">
+      <c r="AB23" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8110,10 +8186,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF23" s="25" t="inlineStr"/>
-      <c r="AG23" s="25" t="inlineStr"/>
-      <c r="AH23" s="25" t="inlineStr"/>
-      <c r="AI23" s="25" t="inlineStr"/>
+      <c r="AF23" s="30" t="inlineStr"/>
+      <c r="AG23" s="30" t="inlineStr"/>
+      <c r="AH23" s="30" t="inlineStr"/>
+      <c r="AI23" s="30" t="inlineStr"/>
     </row>
     <row r="24" ht="62" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
@@ -8131,17 +8207,17 @@
           <t>UltraShock is a pool and spa shock treatment from SpaBalancer, designed to rapidly oxidise contaminants and restore water clarity. A quick reset for water that needs a little more persuasion.</t>
         </is>
       </c>
-      <c r="D24" s="25" t="inlineStr">
+      <c r="D24" s="30" t="inlineStr">
         <is>
           <t>SpaBalancer</t>
         </is>
       </c>
-      <c r="E24" s="25" t="inlineStr">
+      <c r="E24" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F24" s="25" t="inlineStr">
+      <c r="F24" s="30" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8151,71 +8227,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H24" s="25" t="inlineStr">
+      <c r="H24" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I24" s="25" t="inlineStr">
+      <c r="I24" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J24" s="25" t="inlineStr">
+      <c r="J24" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K24" s="25" t="inlineStr">
+      <c r="K24" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L24" s="25" t="inlineStr">
+      <c r="L24" s="30" t="inlineStr">
         <is>
           <t>SPA-CHM-0025</t>
         </is>
       </c>
-      <c r="M24" s="26" t="inlineStr">
+      <c r="M24" s="31" t="inlineStr">
         <is>
           <t>4260374980025</t>
         </is>
       </c>
-      <c r="N24" s="27" t="inlineStr"/>
-      <c r="O24" s="27" t="inlineStr"/>
-      <c r="P24" s="27" t="inlineStr"/>
-      <c r="Q24" s="25" t="inlineStr">
+      <c r="N24" s="32" t="inlineStr"/>
+      <c r="O24" s="32" t="inlineStr"/>
+      <c r="P24" s="32" t="inlineStr"/>
+      <c r="Q24" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R24" s="25" t="inlineStr">
+      <c r="R24" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S24" s="25" t="inlineStr">
+      <c r="S24" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T24" s="25" t="inlineStr">
+      <c r="T24" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U24" s="25" t="inlineStr"/>
-      <c r="V24" s="25" t="inlineStr">
+      <c r="U24" s="30" t="inlineStr"/>
+      <c r="V24" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W24" s="25" t="inlineStr">
+      <c r="W24" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X24" s="25" t="inlineStr">
+      <c r="X24" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8225,7 +8301,7 @@
           <t>https://images.barcodelookup.com/16704/167043133-1.jpg</t>
         </is>
       </c>
-      <c r="Z24" s="25" t="inlineStr">
+      <c r="Z24" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8235,7 +8311,7 @@
           <t>SpaBalancer UltraShock</t>
         </is>
       </c>
-      <c r="AB24" s="25" t="inlineStr">
+      <c r="AB24" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8247,10 +8323,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF24" s="25" t="inlineStr"/>
-      <c r="AG24" s="25" t="inlineStr"/>
-      <c r="AH24" s="25" t="inlineStr"/>
-      <c r="AI24" s="25" t="inlineStr"/>
+      <c r="AF24" s="30" t="inlineStr"/>
+      <c r="AG24" s="30" t="inlineStr"/>
+      <c r="AH24" s="30" t="inlineStr"/>
+      <c r="AI24" s="30" t="inlineStr"/>
     </row>
     <row r="25" ht="76" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
@@ -8268,13 +8344,13 @@
           <t>A patented foam rubber eraser for cleaning pool surfaces, particularly suited to waterline stains on liner and vitreous ceramic finishes, and it works without detergents or chemicals. Each box contains 3 sponges, which harden when wet to scrub effectively while remaining soft and flexible in use.</t>
         </is>
       </c>
-      <c r="D25" s="25" t="inlineStr"/>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="D25" s="30" t="inlineStr"/>
+      <c r="E25" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F25" s="25" t="inlineStr">
+      <c r="F25" s="30" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8284,71 +8360,71 @@
           <t>pool, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H25" s="25" t="inlineStr">
+      <c r="H25" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I25" s="25" t="inlineStr">
+      <c r="I25" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J25" s="25" t="inlineStr">
+      <c r="J25" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K25" s="25" t="inlineStr">
+      <c r="K25" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L25" s="25" t="inlineStr">
+      <c r="L25" s="30" t="inlineStr">
         <is>
           <t>GEN-CLN-0062</t>
         </is>
       </c>
-      <c r="M25" s="26" t="inlineStr">
+      <c r="M25" s="31" t="inlineStr">
         <is>
           <t>3760015880062</t>
         </is>
       </c>
-      <c r="N25" s="27" t="inlineStr"/>
-      <c r="O25" s="27" t="inlineStr"/>
-      <c r="P25" s="27" t="inlineStr"/>
-      <c r="Q25" s="25" t="inlineStr">
+      <c r="N25" s="32" t="inlineStr"/>
+      <c r="O25" s="32" t="inlineStr"/>
+      <c r="P25" s="32" t="inlineStr"/>
+      <c r="Q25" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R25" s="25" t="inlineStr">
+      <c r="R25" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S25" s="25" t="inlineStr">
+      <c r="S25" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T25" s="25" t="inlineStr">
+      <c r="T25" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U25" s="25" t="inlineStr"/>
-      <c r="V25" s="25" t="inlineStr">
+      <c r="U25" s="30" t="inlineStr"/>
+      <c r="V25" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W25" s="25" t="inlineStr">
+      <c r="W25" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X25" s="25" t="inlineStr">
+      <c r="X25" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8358,7 +8434,7 @@
           <t>https://www.piscinarium.com/2908-thickbox_default/pool-gom-magic-rubber-eraser.jpg</t>
         </is>
       </c>
-      <c r="Z25" s="25" t="inlineStr">
+      <c r="Z25" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8368,7 +8444,7 @@
           <t>Pool'Gom Magic Rubber Eraser</t>
         </is>
       </c>
-      <c r="AB25" s="25" t="inlineStr">
+      <c r="AB25" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8380,10 +8456,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF25" s="25" t="inlineStr"/>
-      <c r="AG25" s="25" t="inlineStr"/>
-      <c r="AH25" s="25" t="inlineStr"/>
-      <c r="AI25" s="25" t="inlineStr"/>
+      <c r="AF25" s="30" t="inlineStr"/>
+      <c r="AG25" s="30" t="inlineStr"/>
+      <c r="AH25" s="30" t="inlineStr"/>
+      <c r="AI25" s="30" t="inlineStr"/>
     </row>
     <row r="26" ht="62" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
@@ -8401,13 +8477,13 @@
           <t>Spa Industries Europe appears to be a brand or supplier name rather than a specific product, so no product details can be confirmed. For accurate information, please check the full product listing.</t>
         </is>
       </c>
-      <c r="D26" s="25" t="inlineStr"/>
-      <c r="E26" s="25" t="inlineStr">
+      <c r="D26" s="30" t="inlineStr"/>
+      <c r="E26" s="30" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F26" s="25" t="inlineStr">
+      <c r="F26" s="30" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -8417,79 +8493,79 @@
           <t>spa-hot-tub, considered-purchase, multi-source-confirmed, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H26" s="25" t="inlineStr">
+      <c r="H26" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I26" s="25" t="inlineStr">
+      <c r="I26" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J26" s="25" t="inlineStr">
+      <c r="J26" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K26" s="25" t="inlineStr">
+      <c r="K26" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L26" s="25" t="inlineStr">
+      <c r="L26" s="30" t="inlineStr">
         <is>
           <t>GEN-SPA-1968</t>
         </is>
       </c>
-      <c r="M26" s="26" t="inlineStr">
+      <c r="M26" s="31" t="inlineStr">
         <is>
           <t>5425021871968</t>
         </is>
       </c>
-      <c r="N26" s="27" t="inlineStr"/>
-      <c r="O26" s="27" t="inlineStr"/>
-      <c r="P26" s="27" t="inlineStr"/>
-      <c r="Q26" s="25" t="inlineStr">
+      <c r="N26" s="32" t="inlineStr"/>
+      <c r="O26" s="32" t="inlineStr"/>
+      <c r="P26" s="32" t="inlineStr"/>
+      <c r="Q26" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R26" s="25" t="inlineStr">
+      <c r="R26" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S26" s="25" t="inlineStr">
+      <c r="S26" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T26" s="25" t="inlineStr">
+      <c r="T26" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U26" s="25" t="inlineStr"/>
-      <c r="V26" s="25" t="inlineStr">
+      <c r="U26" s="30" t="inlineStr"/>
+      <c r="V26" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W26" s="25" t="inlineStr">
+      <c r="W26" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X26" s="25" t="inlineStr">
+      <c r="X26" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y26" s="19" t="inlineStr"/>
-      <c r="Z26" s="25" t="inlineStr"/>
+      <c r="Z26" s="30" t="inlineStr"/>
       <c r="AA26" s="19" t="inlineStr"/>
-      <c r="AB26" s="25" t="inlineStr">
+      <c r="AB26" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8501,10 +8577,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF26" s="25" t="inlineStr"/>
-      <c r="AG26" s="25" t="inlineStr"/>
-      <c r="AH26" s="25" t="inlineStr"/>
-      <c r="AI26" s="25" t="inlineStr"/>
+      <c r="AF26" s="30" t="inlineStr"/>
+      <c r="AG26" s="30" t="inlineStr"/>
+      <c r="AH26" s="30" t="inlineStr"/>
+      <c r="AI26" s="30" t="inlineStr"/>
     </row>
     <row r="27" ht="62" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
@@ -8522,17 +8598,17 @@
           <t>A 1-litre high-concentrate sauna cleaner with eucalyptus fragrance, formulated as a deep-cleaning base cleaner for sauna surfaces. The concentrated formula means a little goes a long way, with a fresh scent to match.</t>
         </is>
       </c>
-      <c r="D27" s="25" t="inlineStr">
+      <c r="D27" s="30" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E27" s="25" t="inlineStr">
+      <c r="E27" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F27" s="25" t="inlineStr">
+      <c r="F27" s="30" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8542,79 +8618,79 @@
           <t>cleaning, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H27" s="25" t="inlineStr">
+      <c r="H27" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I27" s="25" t="inlineStr">
+      <c r="I27" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J27" s="25" t="inlineStr">
+      <c r="J27" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K27" s="25" t="inlineStr">
+      <c r="K27" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L27" s="25" t="inlineStr">
+      <c r="L27" s="30" t="inlineStr">
         <is>
           <t>HFE-CLN-7004</t>
         </is>
       </c>
-      <c r="M27" s="26" t="inlineStr">
+      <c r="M27" s="31" t="inlineStr">
         <is>
           <t>4250463127004</t>
         </is>
       </c>
-      <c r="N27" s="27" t="inlineStr"/>
-      <c r="O27" s="27" t="inlineStr"/>
-      <c r="P27" s="27" t="inlineStr"/>
-      <c r="Q27" s="25" t="inlineStr">
+      <c r="N27" s="32" t="inlineStr"/>
+      <c r="O27" s="32" t="inlineStr"/>
+      <c r="P27" s="32" t="inlineStr"/>
+      <c r="Q27" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R27" s="25" t="inlineStr">
+      <c r="R27" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S27" s="25" t="inlineStr">
+      <c r="S27" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T27" s="25" t="inlineStr">
+      <c r="T27" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U27" s="25" t="inlineStr"/>
-      <c r="V27" s="25" t="inlineStr">
+      <c r="U27" s="30" t="inlineStr"/>
+      <c r="V27" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W27" s="25" t="inlineStr">
+      <c r="W27" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X27" s="25" t="inlineStr">
+      <c r="X27" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y27" s="19" t="inlineStr"/>
-      <c r="Z27" s="25" t="inlineStr"/>
+      <c r="Z27" s="30" t="inlineStr"/>
       <c r="AA27" s="19" t="inlineStr"/>
-      <c r="AB27" s="25" t="inlineStr">
+      <c r="AB27" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8626,10 +8702,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF27" s="25" t="inlineStr"/>
-      <c r="AG27" s="25" t="inlineStr"/>
-      <c r="AH27" s="25" t="inlineStr"/>
-      <c r="AI27" s="25" t="inlineStr"/>
+      <c r="AF27" s="30" t="inlineStr"/>
+      <c r="AG27" s="30" t="inlineStr"/>
+      <c r="AH27" s="30" t="inlineStr"/>
+      <c r="AI27" s="30" t="inlineStr"/>
     </row>
     <row r="28" ht="76" customHeight="1">
       <c r="A28" s="19" t="inlineStr">
@@ -8647,17 +8723,17 @@
           <t>This HTH spa cleaner removes mineral deposits such as limescale and rust, and cleans and polishes aluminium, chrome, stainless steel, and enamel surfaces with a pleasant pine fragrance. It has a high concentration of active ingredients and is recommended for periodic maintenance cleaning.</t>
         </is>
       </c>
-      <c r="D28" s="25" t="inlineStr">
+      <c r="D28" s="30" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E28" s="25" t="inlineStr">
+      <c r="E28" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F28" s="25" t="inlineStr">
+      <c r="F28" s="30" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8667,71 +8743,71 @@
           <t>spa-hot-tub, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H28" s="25" t="inlineStr">
+      <c r="H28" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I28" s="25" t="inlineStr">
+      <c r="I28" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J28" s="25" t="inlineStr">
+      <c r="J28" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K28" s="25" t="inlineStr">
+      <c r="K28" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L28" s="25" t="inlineStr">
+      <c r="L28" s="30" t="inlineStr">
         <is>
           <t>HTH-CLN-0178</t>
         </is>
       </c>
-      <c r="M28" s="26" t="inlineStr">
+      <c r="M28" s="31" t="inlineStr">
         <is>
           <t>3521686010178</t>
         </is>
       </c>
-      <c r="N28" s="27" t="inlineStr"/>
-      <c r="O28" s="27" t="inlineStr"/>
-      <c r="P28" s="27" t="inlineStr"/>
-      <c r="Q28" s="25" t="inlineStr">
+      <c r="N28" s="32" t="inlineStr"/>
+      <c r="O28" s="32" t="inlineStr"/>
+      <c r="P28" s="32" t="inlineStr"/>
+      <c r="Q28" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R28" s="25" t="inlineStr">
+      <c r="R28" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S28" s="25" t="inlineStr">
+      <c r="S28" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T28" s="25" t="inlineStr">
+      <c r="T28" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U28" s="25" t="inlineStr"/>
-      <c r="V28" s="25" t="inlineStr">
+      <c r="U28" s="30" t="inlineStr"/>
+      <c r="V28" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W28" s="25" t="inlineStr">
+      <c r="W28" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X28" s="25" t="inlineStr">
+      <c r="X28" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8741,7 +8817,7 @@
           <t>https://www.cdiscount.com/pdt2/0/5/1/1/700x700/auc2009356289051/rw/hth-spa-nettoyant-spa-3521686010178.jpg</t>
         </is>
       </c>
-      <c r="Z28" s="25" t="inlineStr">
+      <c r="Z28" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8751,7 +8827,7 @@
           <t>HTH Spa spa cleaner</t>
         </is>
       </c>
-      <c r="AB28" s="25" t="inlineStr">
+      <c r="AB28" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8763,10 +8839,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF28" s="25" t="inlineStr"/>
-      <c r="AG28" s="25" t="inlineStr"/>
-      <c r="AH28" s="25" t="inlineStr"/>
-      <c r="AI28" s="25" t="inlineStr"/>
+      <c r="AF28" s="30" t="inlineStr"/>
+      <c r="AG28" s="30" t="inlineStr"/>
+      <c r="AH28" s="30" t="inlineStr"/>
+      <c r="AI28" s="30" t="inlineStr"/>
     </row>
     <row r="29" ht="62" customHeight="1">
       <c r="A29" s="19" t="inlineStr">
@@ -8784,13 +8860,13 @@
           <t>A 25 kg sack of pure boiling salt (minimum 99.6% NaCl) without an anti-caking agent, meeting EN 973 Type A standard and suitable for use in pool salt electrolysis systems. Not intended for human consumption or animal feed.</t>
         </is>
       </c>
-      <c r="D29" s="25" t="inlineStr"/>
-      <c r="E29" s="25" t="inlineStr">
+      <c r="D29" s="30" t="inlineStr"/>
+      <c r="E29" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F29" s="25" t="inlineStr">
+      <c r="F29" s="30" t="inlineStr">
         <is>
           <t>Pool salt</t>
         </is>
@@ -8800,75 +8876,75 @@
           <t>pool, salt, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H29" s="25" t="inlineStr">
+      <c r="H29" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I29" s="25" t="inlineStr">
+      <c r="I29" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J29" s="25" t="inlineStr">
+      <c r="J29" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K29" s="25" t="inlineStr">
+      <c r="K29" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L29" s="25" t="inlineStr">
+      <c r="L29" s="30" t="inlineStr">
         <is>
           <t>GEN-SLT-6110</t>
         </is>
       </c>
-      <c r="M29" s="26" t="inlineStr">
+      <c r="M29" s="31" t="inlineStr">
         <is>
           <t>9001880976110</t>
         </is>
       </c>
-      <c r="N29" s="27" t="inlineStr"/>
-      <c r="O29" s="27" t="inlineStr"/>
-      <c r="P29" s="27" t="inlineStr"/>
-      <c r="Q29" s="25" t="inlineStr">
+      <c r="N29" s="32" t="inlineStr"/>
+      <c r="O29" s="32" t="inlineStr"/>
+      <c r="P29" s="32" t="inlineStr"/>
+      <c r="Q29" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R29" s="25" t="inlineStr">
+      <c r="R29" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S29" s="25" t="inlineStr">
+      <c r="S29" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T29" s="25" t="inlineStr">
+      <c r="T29" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U29" s="25" t="inlineStr">
+      <c r="U29" s="30" t="inlineStr">
         <is>
           <t>25000</t>
         </is>
       </c>
-      <c r="V29" s="25" t="inlineStr">
+      <c r="V29" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W29" s="25" t="inlineStr">
+      <c r="W29" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X29" s="25" t="inlineStr">
+      <c r="X29" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8878,7 +8954,7 @@
           <t>http://altruan.com/cdn/shop/files/SalinenPoolSalz25kgSack.png?v=1778597596</t>
         </is>
       </c>
-      <c r="Z29" s="25" t="inlineStr">
+      <c r="Z29" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8888,7 +8964,7 @@
           <t>Saline pool salt pure boiling salt without separating agent | Sack (25 kg)</t>
         </is>
       </c>
-      <c r="AB29" s="25" t="inlineStr">
+      <c r="AB29" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8900,14 +8976,14 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF29" s="25" t="inlineStr">
+      <c r="AF29" s="30" t="inlineStr">
         <is>
           <t>Composition: Siedesalz (min. 99.6% NaCl) 100%; Separant/sodium ferrocyanide 4.0–12.0 mg/kg | Grain: &gt;0.63 mm approx. 20%, 0.2–0.63 mm approx. 75%, &lt;0.2 mm approx. 5% | Moisture: &lt;0.08%</t>
         </is>
       </c>
-      <c r="AG29" s="25" t="inlineStr"/>
-      <c r="AH29" s="25" t="inlineStr"/>
-      <c r="AI29" s="25" t="inlineStr"/>
+      <c r="AG29" s="30" t="inlineStr"/>
+      <c r="AH29" s="30" t="inlineStr"/>
+      <c r="AI29" s="30" t="inlineStr"/>
     </row>
     <row r="30" ht="76" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
@@ -8925,17 +9001,17 @@
           <t>A cordless robotic pool cleaner that scrubs both floors and walls automatically, using WavePath navigation to map and cover the pool efficiently. Built-in high-performance filtration and smart control make it a hands-off solution for keeping pool water clear.</t>
         </is>
       </c>
-      <c r="D30" s="25" t="inlineStr">
+      <c r="D30" s="30" t="inlineStr">
         <is>
           <t>Aiper</t>
         </is>
       </c>
-      <c r="E30" s="25" t="inlineStr">
+      <c r="E30" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F30" s="25" t="inlineStr">
+      <c r="F30" s="30" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -8945,71 +9021,71 @@
           <t>pool, cleaning, robot-cleaner, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H30" s="25" t="inlineStr">
+      <c r="H30" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I30" s="25" t="inlineStr">
+      <c r="I30" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J30" s="25" t="inlineStr">
+      <c r="J30" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K30" s="25" t="inlineStr">
+      <c r="K30" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L30" s="25" t="inlineStr">
+      <c r="L30" s="30" t="inlineStr">
         <is>
           <t>AIP-ROB-4940</t>
         </is>
       </c>
-      <c r="M30" s="26" t="inlineStr">
+      <c r="M30" s="31" t="inlineStr">
         <is>
           <t>6977676344940</t>
         </is>
       </c>
-      <c r="N30" s="27" t="inlineStr"/>
-      <c r="O30" s="27" t="inlineStr"/>
-      <c r="P30" s="27" t="inlineStr"/>
-      <c r="Q30" s="25" t="inlineStr">
+      <c r="N30" s="32" t="inlineStr"/>
+      <c r="O30" s="32" t="inlineStr"/>
+      <c r="P30" s="32" t="inlineStr"/>
+      <c r="Q30" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R30" s="25" t="inlineStr">
+      <c r="R30" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S30" s="25" t="inlineStr">
+      <c r="S30" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T30" s="25" t="inlineStr">
+      <c r="T30" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U30" s="25" t="inlineStr"/>
-      <c r="V30" s="25" t="inlineStr">
+      <c r="U30" s="30" t="inlineStr"/>
+      <c r="V30" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W30" s="25" t="inlineStr">
+      <c r="W30" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X30" s="25" t="inlineStr">
+      <c r="X30" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9019,7 +9095,7 @@
           <t>https://images.barcodelookup.com/176692/1766920801-1.jpg</t>
         </is>
       </c>
-      <c r="Z30" s="25" t="inlineStr">
+      <c r="Z30" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9029,7 +9105,7 @@
           <t>AIPER Scuba S3 cordless pool robot, automatic floor and wall cleaning, WavePath™ navigation, high-performance filtration…</t>
         </is>
       </c>
-      <c r="AB30" s="25" t="inlineStr">
+      <c r="AB30" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9041,10 +9117,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF30" s="25" t="inlineStr"/>
-      <c r="AG30" s="25" t="inlineStr"/>
-      <c r="AH30" s="25" t="inlineStr"/>
-      <c r="AI30" s="25" t="inlineStr"/>
+      <c r="AF30" s="30" t="inlineStr"/>
+      <c r="AG30" s="30" t="inlineStr"/>
+      <c r="AH30" s="30" t="inlineStr"/>
+      <c r="AI30" s="30" t="inlineStr"/>
     </row>
     <row r="31" ht="62" customHeight="1">
       <c r="A31" s="19" t="inlineStr">
@@ -9062,13 +9138,13 @@
           <t>The Scuba L1 EU is a pool cleaning device, though no further specific details about its features, dimensions, or mechanism are available from the product name alone. Buyers should refer to the full product listing for specifications.</t>
         </is>
       </c>
-      <c r="D31" s="25" t="inlineStr"/>
-      <c r="E31" s="25" t="inlineStr">
+      <c r="D31" s="30" t="inlineStr"/>
+      <c r="E31" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F31" s="25" t="inlineStr">
+      <c r="F31" s="30" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9078,71 +9154,71 @@
           <t>robot-cleaner, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H31" s="25" t="inlineStr">
+      <c r="H31" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I31" s="25" t="inlineStr">
+      <c r="I31" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J31" s="25" t="inlineStr">
+      <c r="J31" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K31" s="25" t="inlineStr">
+      <c r="K31" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L31" s="25" t="inlineStr">
+      <c r="L31" s="30" t="inlineStr">
         <is>
           <t>GEN-ROB-5137</t>
         </is>
       </c>
-      <c r="M31" s="26" t="inlineStr">
+      <c r="M31" s="31" t="inlineStr">
         <is>
           <t>6975140315137</t>
         </is>
       </c>
-      <c r="N31" s="27" t="inlineStr"/>
-      <c r="O31" s="27" t="inlineStr"/>
-      <c r="P31" s="27" t="inlineStr"/>
-      <c r="Q31" s="25" t="inlineStr">
+      <c r="N31" s="32" t="inlineStr"/>
+      <c r="O31" s="32" t="inlineStr"/>
+      <c r="P31" s="32" t="inlineStr"/>
+      <c r="Q31" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R31" s="25" t="inlineStr">
+      <c r="R31" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S31" s="25" t="inlineStr">
+      <c r="S31" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T31" s="25" t="inlineStr">
+      <c r="T31" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U31" s="25" t="inlineStr"/>
-      <c r="V31" s="25" t="inlineStr">
+      <c r="U31" s="30" t="inlineStr"/>
+      <c r="V31" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W31" s="25" t="inlineStr">
+      <c r="W31" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X31" s="25" t="inlineStr">
+      <c r="X31" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9152,7 +9228,7 @@
           <t>https://images.barcodelookup.com/124722/1247228758-1.jpg</t>
         </is>
       </c>
-      <c r="Z31" s="25" t="inlineStr">
+      <c r="Z31" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9162,7 +9238,7 @@
           <t>Scuba L1 - EU</t>
         </is>
       </c>
-      <c r="AB31" s="25" t="inlineStr">
+      <c r="AB31" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9174,10 +9250,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF31" s="25" t="inlineStr"/>
-      <c r="AG31" s="25" t="inlineStr"/>
-      <c r="AH31" s="25" t="inlineStr"/>
-      <c r="AI31" s="25" t="inlineStr"/>
+      <c r="AF31" s="30" t="inlineStr"/>
+      <c r="AG31" s="30" t="inlineStr"/>
+      <c r="AH31" s="30" t="inlineStr"/>
+      <c r="AI31" s="30" t="inlineStr"/>
     </row>
     <row r="32" ht="48" customHeight="1">
       <c r="A32" s="19" t="inlineStr">
@@ -9195,13 +9271,13 @@
           <t>The Gre Pools RBR120 is a 51W robotic pool cleaner designed for automatic pool floor cleaning. A reliable workhorse that takes the scrubbing off your hands.</t>
         </is>
       </c>
-      <c r="D32" s="25" t="inlineStr"/>
-      <c r="E32" s="25" t="inlineStr">
+      <c r="D32" s="30" t="inlineStr"/>
+      <c r="E32" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F32" s="25" t="inlineStr">
+      <c r="F32" s="30" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9211,71 +9287,71 @@
           <t>robot-cleaner, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H32" s="25" t="inlineStr">
+      <c r="H32" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I32" s="25" t="inlineStr">
+      <c r="I32" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J32" s="25" t="inlineStr">
+      <c r="J32" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K32" s="25" t="inlineStr">
+      <c r="K32" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L32" s="25" t="inlineStr">
+      <c r="L32" s="30" t="inlineStr">
         <is>
           <t>GEN-ROB-8500</t>
         </is>
       </c>
-      <c r="M32" s="26" t="inlineStr">
+      <c r="M32" s="31" t="inlineStr">
         <is>
           <t>8412081308500</t>
         </is>
       </c>
-      <c r="N32" s="27" t="inlineStr"/>
-      <c r="O32" s="27" t="inlineStr"/>
-      <c r="P32" s="27" t="inlineStr"/>
-      <c r="Q32" s="25" t="inlineStr">
+      <c r="N32" s="32" t="inlineStr"/>
+      <c r="O32" s="32" t="inlineStr"/>
+      <c r="P32" s="32" t="inlineStr"/>
+      <c r="Q32" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R32" s="25" t="inlineStr">
+      <c r="R32" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S32" s="25" t="inlineStr">
+      <c r="S32" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T32" s="25" t="inlineStr">
+      <c r="T32" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U32" s="25" t="inlineStr"/>
-      <c r="V32" s="25" t="inlineStr">
+      <c r="U32" s="30" t="inlineStr"/>
+      <c r="V32" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W32" s="25" t="inlineStr">
+      <c r="W32" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X32" s="25" t="inlineStr">
+      <c r="X32" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9285,7 +9361,7 @@
           <t>https://images.barcodelookup.com/124726/1247268298-1.jpg</t>
         </is>
       </c>
-      <c r="Z32" s="25" t="inlineStr">
+      <c r="Z32" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9295,7 +9371,7 @@
           <t>Battery Powered Robot WET RUNNER XPERT</t>
         </is>
       </c>
-      <c r="AB32" s="25" t="inlineStr">
+      <c r="AB32" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9307,10 +9383,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF32" s="25" t="inlineStr"/>
-      <c r="AG32" s="25" t="inlineStr"/>
-      <c r="AH32" s="25" t="inlineStr"/>
-      <c r="AI32" s="25" t="inlineStr"/>
+      <c r="AF32" s="30" t="inlineStr"/>
+      <c r="AG32" s="30" t="inlineStr"/>
+      <c r="AH32" s="30" t="inlineStr"/>
+      <c r="AI32" s="30" t="inlineStr"/>
     </row>
     <row r="33" ht="90" customHeight="1">
       <c r="A33" s="19" t="inlineStr">
@@ -9328,13 +9404,13 @@
           <t>A twin-size inflatable airbed measuring 99 x 191 x 25 cm, built with Fiber-Tech internal construction using polyester fibres for comfort, vinyl sides and base, and a water-resistant flocked top surface with an anti-deflation valve. It supports a maximum weight of 136 kg and packs down compactly when deflated.</t>
         </is>
       </c>
-      <c r="D33" s="25" t="inlineStr"/>
-      <c r="E33" s="25" t="inlineStr">
+      <c r="D33" s="30" t="inlineStr"/>
+      <c r="E33" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-11</t>
         </is>
       </c>
-      <c r="F33" s="25" t="inlineStr">
+      <c r="F33" s="30" t="inlineStr">
         <is>
           <t>Airbed / lounger</t>
         </is>
@@ -9344,71 +9420,71 @@
           <t>considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H33" s="25" t="inlineStr">
+      <c r="H33" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I33" s="25" t="inlineStr">
+      <c r="I33" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J33" s="25" t="inlineStr">
+      <c r="J33" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K33" s="25" t="inlineStr">
+      <c r="K33" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L33" s="25" t="inlineStr">
+      <c r="L33" s="30" t="inlineStr">
         <is>
           <t>GEN-BED-2443</t>
         </is>
       </c>
-      <c r="M33" s="26" t="inlineStr">
+      <c r="M33" s="31" t="inlineStr">
         <is>
           <t>6941057412443</t>
         </is>
       </c>
-      <c r="N33" s="27" t="inlineStr"/>
-      <c r="O33" s="27" t="inlineStr"/>
-      <c r="P33" s="27" t="inlineStr"/>
-      <c r="Q33" s="25" t="inlineStr">
+      <c r="N33" s="32" t="inlineStr"/>
+      <c r="O33" s="32" t="inlineStr"/>
+      <c r="P33" s="32" t="inlineStr"/>
+      <c r="Q33" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R33" s="25" t="inlineStr">
+      <c r="R33" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S33" s="25" t="inlineStr">
+      <c r="S33" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T33" s="25" t="inlineStr">
+      <c r="T33" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U33" s="25" t="inlineStr"/>
-      <c r="V33" s="25" t="inlineStr">
+      <c r="U33" s="30" t="inlineStr"/>
+      <c r="V33" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W33" s="25" t="inlineStr">
+      <c r="W33" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X33" s="25" t="inlineStr">
+      <c r="X33" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9418,7 +9494,7 @@
           <t>https://www.ecoperation.com/media/catalog/product/cache/b76cf1d99a7811daa83ba86e6ad91c89/6/4/64757.jpg</t>
         </is>
       </c>
-      <c r="Z33" s="25" t="inlineStr">
+      <c r="Z33" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9428,7 +9504,7 @@
           <t>Twin Dura-Beam Classic Downy Airbed 99x191x25 cm</t>
         </is>
       </c>
-      <c r="AB33" s="25" t="inlineStr">
+      <c r="AB33" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9440,18 +9516,18 @@
           <t>Inflatable Beds and Mattresses</t>
         </is>
       </c>
-      <c r="AF33" s="25" t="inlineStr"/>
-      <c r="AG33" s="25" t="inlineStr">
+      <c r="AF33" s="30" t="inlineStr"/>
+      <c r="AG33" s="30" t="inlineStr">
         <is>
           <t>99.0cm</t>
         </is>
       </c>
-      <c r="AH33" s="25" t="inlineStr">
+      <c r="AH33" s="30" t="inlineStr">
         <is>
           <t>191.0cm</t>
         </is>
       </c>
-      <c r="AI33" s="25" t="inlineStr">
+      <c r="AI33" s="30" t="inlineStr">
         <is>
           <t>25.0cm</t>
         </is>
@@ -9473,17 +9549,17 @@
           <t>A plastic chlorine dosing lock from Steinbach, designed exclusively for use with long-term chlorine tablets, with a 1.5-inch connection fitting. It measures 37 cm in length, 22.5 cm in width, and 15 cm in height, making it a sturdy inline dosing unit for pool water treatment systems.</t>
         </is>
       </c>
-      <c r="D34" s="25" t="inlineStr">
+      <c r="D34" s="30" t="inlineStr">
         <is>
           <t>Steinbach</t>
         </is>
       </c>
-      <c r="E34" s="25" t="inlineStr">
+      <c r="E34" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F34" s="25" t="inlineStr">
+      <c r="F34" s="30" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -9493,71 +9569,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H34" s="25" t="inlineStr">
+      <c r="H34" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I34" s="25" t="inlineStr">
+      <c r="I34" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J34" s="25" t="inlineStr">
+      <c r="J34" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K34" s="25" t="inlineStr">
+      <c r="K34" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L34" s="25" t="inlineStr">
+      <c r="L34" s="30" t="inlineStr">
         <is>
           <t>STE-CHM-0307</t>
         </is>
       </c>
-      <c r="M34" s="26" t="inlineStr">
+      <c r="M34" s="31" t="inlineStr">
         <is>
           <t>9008748790307</t>
         </is>
       </c>
-      <c r="N34" s="27" t="inlineStr"/>
-      <c r="O34" s="27" t="inlineStr"/>
-      <c r="P34" s="27" t="inlineStr"/>
-      <c r="Q34" s="25" t="inlineStr">
+      <c r="N34" s="32" t="inlineStr"/>
+      <c r="O34" s="32" t="inlineStr"/>
+      <c r="P34" s="32" t="inlineStr"/>
+      <c r="Q34" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R34" s="25" t="inlineStr">
+      <c r="R34" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S34" s="25" t="inlineStr">
+      <c r="S34" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T34" s="25" t="inlineStr">
+      <c r="T34" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U34" s="25" t="inlineStr"/>
-      <c r="V34" s="25" t="inlineStr">
+      <c r="U34" s="30" t="inlineStr"/>
+      <c r="V34" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W34" s="25" t="inlineStr">
+      <c r="W34" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X34" s="25" t="inlineStr">
+      <c r="X34" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9567,7 +9643,7 @@
           <t>https://i.ebayimg.com/images/g/CrUAAeSwkOdqeaRR/s-l400.jpg</t>
         </is>
       </c>
-      <c r="Z34" s="25" t="inlineStr">
+      <c r="Z34" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9577,7 +9653,7 @@
           <t>STEINBACH Chlorine dosing lock, only for chlorine long-term tablets, plastic, connection 1.5 inch in</t>
         </is>
       </c>
-      <c r="AB34" s="25" t="inlineStr">
+      <c r="AB34" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9589,18 +9665,18 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF34" s="25" t="inlineStr"/>
-      <c r="AG34" s="25" t="inlineStr">
+      <c r="AF34" s="30" t="inlineStr"/>
+      <c r="AG34" s="30" t="inlineStr">
         <is>
           <t>22.5cm</t>
         </is>
       </c>
-      <c r="AH34" s="25" t="inlineStr">
+      <c r="AH34" s="30" t="inlineStr">
         <is>
           <t>37.0cm</t>
         </is>
       </c>
-      <c r="AI34" s="25" t="inlineStr">
+      <c r="AI34" s="30" t="inlineStr">
         <is>
           <t>15.0cm</t>
         </is>
@@ -9622,17 +9698,17 @@
           <t>A filter cleaning system for hot tub and pool cartridge filters, designed to remove debris and residue efficiently while keeping water usage to a minimum. A practical tool for extending the life of your filter without wasting a drop more than necessary.</t>
         </is>
       </c>
-      <c r="D35" s="25" t="inlineStr">
+      <c r="D35" s="30" t="inlineStr">
         <is>
           <t>Estelle</t>
         </is>
       </c>
-      <c r="E35" s="25" t="inlineStr">
+      <c r="E35" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F35" s="25" t="inlineStr">
+      <c r="F35" s="30" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -9642,71 +9718,71 @@
           <t>filters, spa-hot-tub, cleaning, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H35" s="25" t="inlineStr">
+      <c r="H35" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I35" s="25" t="inlineStr">
+      <c r="I35" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J35" s="25" t="inlineStr">
+      <c r="J35" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K35" s="25" t="inlineStr">
+      <c r="K35" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L35" s="25" t="inlineStr">
+      <c r="L35" s="30" t="inlineStr">
         <is>
           <t>EST-FIL-3669</t>
         </is>
       </c>
-      <c r="M35" s="26" t="inlineStr">
+      <c r="M35" s="31" t="inlineStr">
         <is>
           <t>8711842033669</t>
         </is>
       </c>
-      <c r="N35" s="27" t="inlineStr"/>
-      <c r="O35" s="27" t="inlineStr"/>
-      <c r="P35" s="27" t="inlineStr"/>
-      <c r="Q35" s="25" t="inlineStr">
+      <c r="N35" s="32" t="inlineStr"/>
+      <c r="O35" s="32" t="inlineStr"/>
+      <c r="P35" s="32" t="inlineStr"/>
+      <c r="Q35" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R35" s="25" t="inlineStr">
+      <c r="R35" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S35" s="25" t="inlineStr">
+      <c r="S35" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T35" s="25" t="inlineStr">
+      <c r="T35" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U35" s="25" t="inlineStr"/>
-      <c r="V35" s="25" t="inlineStr">
+      <c r="U35" s="30" t="inlineStr"/>
+      <c r="V35" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W35" s="25" t="inlineStr">
+      <c r="W35" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X35" s="25" t="inlineStr">
+      <c r="X35" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9716,7 +9792,7 @@
           <t>https://i.ebayimg.com/images/g/0e0AAOSweaplqO77/s-l400.jpg</t>
         </is>
       </c>
-      <c r="Z35" s="25" t="inlineStr">
+      <c r="Z35" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9726,7 +9802,7 @@
           <t>Estelle Filter Cleaning System Hot tubs Cartridge Filters Cleaner Spa Amazing!</t>
         </is>
       </c>
-      <c r="AB35" s="25" t="inlineStr">
+      <c r="AB35" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9738,10 +9814,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF35" s="25" t="inlineStr"/>
-      <c r="AG35" s="25" t="inlineStr"/>
-      <c r="AH35" s="25" t="inlineStr"/>
-      <c r="AI35" s="25" t="inlineStr"/>
+      <c r="AF35" s="30" t="inlineStr"/>
+      <c r="AG35" s="30" t="inlineStr"/>
+      <c r="AH35" s="30" t="inlineStr"/>
+      <c r="AI35" s="30" t="inlineStr"/>
     </row>
     <row r="36" ht="62" customHeight="1">
       <c r="A36" s="19" t="inlineStr">
@@ -9759,17 +9835,17 @@
           <t>A compact handy scrub brush for pool maintenance, measuring 15 x 9 x 8 cm, suited to scrubbing pool surfaces and hard-to-reach areas. Small enough to manoeuvre easily, and ready to tackle whatever the waterline throws at it.</t>
         </is>
       </c>
-      <c r="D36" s="25" t="inlineStr">
+      <c r="D36" s="30" t="inlineStr">
         <is>
           <t>WAYS</t>
         </is>
       </c>
-      <c r="E36" s="25" t="inlineStr">
+      <c r="E36" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F36" s="25" t="inlineStr">
+      <c r="F36" s="30" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -9779,79 +9855,79 @@
           <t>pool, cleaning, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H36" s="25" t="inlineStr">
+      <c r="H36" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I36" s="25" t="inlineStr">
+      <c r="I36" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J36" s="25" t="inlineStr">
+      <c r="J36" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K36" s="25" t="inlineStr">
+      <c r="K36" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L36" s="25" t="inlineStr">
+      <c r="L36" s="30" t="inlineStr">
         <is>
           <t>WAY-CLN-2219</t>
         </is>
       </c>
-      <c r="M36" s="26" t="inlineStr">
+      <c r="M36" s="31" t="inlineStr">
         <is>
           <t>8720299182219</t>
         </is>
       </c>
-      <c r="N36" s="27" t="inlineStr"/>
-      <c r="O36" s="27" t="inlineStr"/>
-      <c r="P36" s="27" t="inlineStr"/>
-      <c r="Q36" s="25" t="inlineStr">
+      <c r="N36" s="32" t="inlineStr"/>
+      <c r="O36" s="32" t="inlineStr"/>
+      <c r="P36" s="32" t="inlineStr"/>
+      <c r="Q36" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R36" s="25" t="inlineStr">
+      <c r="R36" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S36" s="25" t="inlineStr">
+      <c r="S36" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T36" s="25" t="inlineStr">
+      <c r="T36" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U36" s="25" t="inlineStr"/>
-      <c r="V36" s="25" t="inlineStr">
+      <c r="U36" s="30" t="inlineStr"/>
+      <c r="V36" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W36" s="25" t="inlineStr">
+      <c r="W36" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X36" s="25" t="inlineStr">
+      <c r="X36" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y36" s="19" t="inlineStr"/>
-      <c r="Z36" s="25" t="inlineStr"/>
+      <c r="Z36" s="30" t="inlineStr"/>
       <c r="AA36" s="19" t="inlineStr"/>
-      <c r="AB36" s="25" t="inlineStr">
+      <c r="AB36" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9863,18 +9939,18 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF36" s="25" t="inlineStr"/>
-      <c r="AG36" s="25" t="inlineStr">
+      <c r="AF36" s="30" t="inlineStr"/>
+      <c r="AG36" s="30" t="inlineStr">
         <is>
           <t>8.0cm</t>
         </is>
       </c>
-      <c r="AH36" s="25" t="inlineStr">
+      <c r="AH36" s="30" t="inlineStr">
         <is>
           <t>15.0cm</t>
         </is>
       </c>
-      <c r="AI36" s="25" t="inlineStr">
+      <c r="AI36" s="30" t="inlineStr">
         <is>
           <t>9.0cm</t>
         </is>
@@ -9896,17 +9972,17 @@
           <t>An inflatable PVC headrest pillow for the Intex inflatable spa (model 28506), measuring 24 x 19 x 6 cm and weighing 0.22 kg, designed to support the head and neck comfortably during use. It attaches to the spa rim and can also be filled with water for added stability.</t>
         </is>
       </c>
-      <c r="D37" s="25" t="inlineStr">
+      <c r="D37" s="30" t="inlineStr">
         <is>
           <t>Intex</t>
         </is>
       </c>
-      <c r="E37" s="25" t="inlineStr">
+      <c r="E37" s="30" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F37" s="25" t="inlineStr">
+      <c r="F37" s="30" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -9916,75 +9992,75 @@
           <t>spa-hot-tub, accessories, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H37" s="25" t="inlineStr">
+      <c r="H37" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I37" s="25" t="inlineStr">
+      <c r="I37" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J37" s="25" t="inlineStr">
+      <c r="J37" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K37" s="25" t="inlineStr">
+      <c r="K37" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L37" s="25" t="inlineStr">
+      <c r="L37" s="30" t="inlineStr">
         <is>
           <t>INT-SPA-6075</t>
         </is>
       </c>
-      <c r="M37" s="26" t="inlineStr">
+      <c r="M37" s="31" t="inlineStr">
         <is>
           <t>6941057426075</t>
         </is>
       </c>
-      <c r="N37" s="27" t="inlineStr"/>
-      <c r="O37" s="27" t="inlineStr"/>
-      <c r="P37" s="27" t="inlineStr"/>
-      <c r="Q37" s="25" t="inlineStr">
+      <c r="N37" s="32" t="inlineStr"/>
+      <c r="O37" s="32" t="inlineStr"/>
+      <c r="P37" s="32" t="inlineStr"/>
+      <c r="Q37" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R37" s="25" t="inlineStr">
+      <c r="R37" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S37" s="25" t="inlineStr">
+      <c r="S37" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T37" s="25" t="inlineStr">
+      <c r="T37" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U37" s="25" t="inlineStr">
+      <c r="U37" s="30" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="V37" s="25" t="inlineStr">
+      <c r="V37" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W37" s="25" t="inlineStr">
+      <c r="W37" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X37" s="25" t="inlineStr">
+      <c r="X37" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9994,7 +10070,7 @@
           <t>https://content2.rozetka.com.ua/goods/images/big/570260745.jpg</t>
         </is>
       </c>
-      <c r="Z37" s="25" t="inlineStr">
+      <c r="Z37" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10004,7 +10080,7 @@
           <t>Pillow for inflatable SPA INTEX 28506</t>
         </is>
       </c>
-      <c r="AB37" s="25" t="inlineStr">
+      <c r="AB37" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10016,18 +10092,18 @@
           <t>Intex Pure Spa Accessories</t>
         </is>
       </c>
-      <c r="AF37" s="25" t="inlineStr"/>
-      <c r="AG37" s="25" t="inlineStr">
+      <c r="AF37" s="30" t="inlineStr"/>
+      <c r="AG37" s="30" t="inlineStr">
         <is>
           <t>19.0cm</t>
         </is>
       </c>
-      <c r="AH37" s="25" t="inlineStr">
+      <c r="AH37" s="30" t="inlineStr">
         <is>
           <t>24.0cm</t>
         </is>
       </c>
-      <c r="AI37" s="25" t="inlineStr">
+      <c r="AI37" s="30" t="inlineStr">
         <is>
           <t>6.0cm</t>
         </is>
@@ -10049,13 +10125,13 @@
           <t>A DPD Pool test kit for active-oxygen pools, containing 20 DPD No. 4 reagent tablets for measuring active oxygen levels and 20 phenol red tablets for measuring pH. Results are read immediately after the tablet dissolves, with an ideal active oxygen range of 3.0 to 8.0 mg/l and a target pH of 7.0 to 7.4.</t>
         </is>
       </c>
-      <c r="D38" s="25" t="inlineStr"/>
-      <c r="E38" s="25" t="inlineStr">
+      <c r="D38" s="30" t="inlineStr"/>
+      <c r="E38" s="30" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F38" s="25" t="inlineStr">
+      <c r="F38" s="30" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -10065,71 +10141,71 @@
           <t>water-treatment, test-measure, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H38" s="25" t="inlineStr">
+      <c r="H38" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I38" s="25" t="inlineStr">
+      <c r="I38" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J38" s="25" t="inlineStr">
+      <c r="J38" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K38" s="25" t="inlineStr">
+      <c r="K38" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L38" s="25" t="inlineStr">
+      <c r="L38" s="30" t="inlineStr">
         <is>
           <t>GEN-TST-1347</t>
         </is>
       </c>
-      <c r="M38" s="26" t="inlineStr">
+      <c r="M38" s="31" t="inlineStr">
         <is>
           <t>4250463121347</t>
         </is>
       </c>
-      <c r="N38" s="27" t="inlineStr"/>
-      <c r="O38" s="27" t="inlineStr"/>
-      <c r="P38" s="27" t="inlineStr"/>
-      <c r="Q38" s="25" t="inlineStr">
+      <c r="N38" s="32" t="inlineStr"/>
+      <c r="O38" s="32" t="inlineStr"/>
+      <c r="P38" s="32" t="inlineStr"/>
+      <c r="Q38" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R38" s="25" t="inlineStr">
+      <c r="R38" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S38" s="25" t="inlineStr">
+      <c r="S38" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T38" s="25" t="inlineStr">
+      <c r="T38" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U38" s="25" t="inlineStr"/>
-      <c r="V38" s="25" t="inlineStr">
+      <c r="U38" s="30" t="inlineStr"/>
+      <c r="V38" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W38" s="25" t="inlineStr">
+      <c r="W38" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X38" s="25" t="inlineStr">
+      <c r="X38" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10139,7 +10215,7 @@
           <t>https://media.carrefour.fr/medias/8f94161f683b4e589024a5b5ebaa6873/p_200x200/cad3db6a00ef414a804b9226119bae96_image.jpg</t>
         </is>
       </c>
-      <c r="Z38" s="25" t="inlineStr">
+      <c r="Z38" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10149,7 +10225,7 @@
           <t>Active oxygen test kit x1</t>
         </is>
       </c>
-      <c r="AB38" s="25" t="inlineStr">
+      <c r="AB38" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10161,10 +10237,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF38" s="25" t="inlineStr"/>
-      <c r="AG38" s="25" t="inlineStr"/>
-      <c r="AH38" s="25" t="inlineStr"/>
-      <c r="AI38" s="25" t="inlineStr"/>
+      <c r="AF38" s="30" t="inlineStr"/>
+      <c r="AG38" s="30" t="inlineStr"/>
+      <c r="AH38" s="30" t="inlineStr"/>
+      <c r="AI38" s="30" t="inlineStr"/>
     </row>
     <row r="39" ht="62" customHeight="1">
       <c r="A39" s="19" t="inlineStr">
@@ -10182,17 +10258,17 @@
           <t>A pack of 2 replacement filter cartridges compatible with Intex Type H pool and spa pumps, made by Darlly. Straightforward to swap out, they keep the water moving clean without any complications.</t>
         </is>
       </c>
-      <c r="D39" s="25" t="inlineStr">
+      <c r="D39" s="30" t="inlineStr">
         <is>
           <t>Intex</t>
         </is>
       </c>
-      <c r="E39" s="25" t="inlineStr">
+      <c r="E39" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F39" s="25" t="inlineStr">
+      <c r="F39" s="30" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -10202,71 +10278,71 @@
           <t>filters, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H39" s="25" t="inlineStr">
+      <c r="H39" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I39" s="25" t="inlineStr">
+      <c r="I39" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J39" s="25" t="inlineStr">
+      <c r="J39" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K39" s="25" t="inlineStr">
+      <c r="K39" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L39" s="25" t="inlineStr">
+      <c r="L39" s="30" t="inlineStr">
         <is>
           <t>INT-FIL-2895</t>
         </is>
       </c>
-      <c r="M39" s="26" t="inlineStr">
+      <c r="M39" s="31" t="inlineStr">
         <is>
           <t>700175992895</t>
         </is>
       </c>
-      <c r="N39" s="27" t="inlineStr"/>
-      <c r="O39" s="27" t="inlineStr"/>
-      <c r="P39" s="27" t="inlineStr"/>
-      <c r="Q39" s="25" t="inlineStr">
+      <c r="N39" s="32" t="inlineStr"/>
+      <c r="O39" s="32" t="inlineStr"/>
+      <c r="P39" s="32" t="inlineStr"/>
+      <c r="Q39" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R39" s="25" t="inlineStr">
+      <c r="R39" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S39" s="25" t="inlineStr">
+      <c r="S39" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T39" s="25" t="inlineStr">
+      <c r="T39" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U39" s="25" t="inlineStr"/>
-      <c r="V39" s="25" t="inlineStr">
+      <c r="U39" s="30" t="inlineStr"/>
+      <c r="V39" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W39" s="25" t="inlineStr">
+      <c r="W39" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X39" s="25" t="inlineStr">
+      <c r="X39" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10276,7 +10352,7 @@
           <t>https://a.allegroimg.com/original/11923c/a79785a04d36aa54f0d87384f038/Filtracni-kartuse-Intex-D-3BTZ0023-SC828</t>
         </is>
       </c>
-      <c r="Z39" s="25" t="inlineStr">
+      <c r="Z39" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10286,7 +10362,7 @@
           <t>Darlly filter cartridge pack of 2 filter cartridges compatible with Intex type H</t>
         </is>
       </c>
-      <c r="AB39" s="25" t="inlineStr">
+      <c r="AB39" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10298,10 +10374,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF39" s="25" t="inlineStr"/>
-      <c r="AG39" s="25" t="inlineStr"/>
-      <c r="AH39" s="25" t="inlineStr"/>
-      <c r="AI39" s="25" t="inlineStr"/>
+      <c r="AF39" s="30" t="inlineStr"/>
+      <c r="AG39" s="30" t="inlineStr"/>
+      <c r="AH39" s="30" t="inlineStr"/>
+      <c r="AI39" s="30" t="inlineStr"/>
     </row>
     <row r="40" ht="62" customHeight="1">
       <c r="A40" s="19" t="inlineStr">
@@ -10319,17 +10395,17 @@
           <t>A Darlly replacement spa filter cartridge with dimensions of 22 cm diameter by 27 cm height, compatible with SC713 and C-8465 references. A reliable like-for-like swap to keep your spa filtration running smoothly.</t>
         </is>
       </c>
-      <c r="D40" s="25" t="inlineStr">
+      <c r="D40" s="30" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E40" s="25" t="inlineStr">
+      <c r="E40" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F40" s="25" t="inlineStr">
+      <c r="F40" s="30" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -10339,71 +10415,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H40" s="25" t="inlineStr">
+      <c r="H40" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I40" s="25" t="inlineStr">
+      <c r="I40" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J40" s="25" t="inlineStr">
+      <c r="J40" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K40" s="25" t="inlineStr">
+      <c r="K40" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L40" s="25" t="inlineStr">
+      <c r="L40" s="30" t="inlineStr">
         <is>
           <t>DAR-FIL-1744</t>
         </is>
       </c>
-      <c r="M40" s="26" t="inlineStr">
+      <c r="M40" s="31" t="inlineStr">
         <is>
           <t>700175991744</t>
         </is>
       </c>
-      <c r="N40" s="27" t="inlineStr"/>
-      <c r="O40" s="27" t="inlineStr"/>
-      <c r="P40" s="27" t="inlineStr"/>
-      <c r="Q40" s="25" t="inlineStr">
+      <c r="N40" s="32" t="inlineStr"/>
+      <c r="O40" s="32" t="inlineStr"/>
+      <c r="P40" s="32" t="inlineStr"/>
+      <c r="Q40" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R40" s="25" t="inlineStr">
+      <c r="R40" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S40" s="25" t="inlineStr">
+      <c r="S40" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T40" s="25" t="inlineStr">
+      <c r="T40" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U40" s="25" t="inlineStr"/>
-      <c r="V40" s="25" t="inlineStr">
+      <c r="U40" s="30" t="inlineStr"/>
+      <c r="V40" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W40" s="25" t="inlineStr">
+      <c r="W40" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X40" s="25" t="inlineStr">
+      <c r="X40" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10413,7 +10489,7 @@
           <t>https://images.barcodelookup.com/142259/1422591231-1.jpg</t>
         </is>
       </c>
-      <c r="Z40" s="25" t="inlineStr">
+      <c r="Z40" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10423,7 +10499,7 @@
           <t>Spa replacement filter Ø 22 cm x 27 cm SC713, C-8465 - Darlly</t>
         </is>
       </c>
-      <c r="AB40" s="25" t="inlineStr">
+      <c r="AB40" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10435,14 +10511,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF40" s="25" t="inlineStr"/>
-      <c r="AG40" s="25" t="inlineStr"/>
-      <c r="AH40" s="25" t="inlineStr">
+      <c r="AF40" s="30" t="inlineStr"/>
+      <c r="AG40" s="30" t="inlineStr"/>
+      <c r="AH40" s="30" t="inlineStr">
         <is>
           <t>22.0cm</t>
         </is>
       </c>
-      <c r="AI40" s="25" t="inlineStr">
+      <c r="AI40" s="30" t="inlineStr">
         <is>
           <t>27.0cm</t>
         </is>
@@ -10464,17 +10540,17 @@
           <t>A 1 kg pack of 20g multitabs for swimming pools, offering a 5-in-1 treatment that combines multiple water care functions in a single slow-dissolving tablet. Convenient all-in-one dosing that keeps pool maintenance simple.</t>
         </is>
       </c>
-      <c r="D41" s="25" t="inlineStr">
+      <c r="D41" s="30" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E41" s="25" t="inlineStr">
+      <c r="E41" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F41" s="25" t="inlineStr">
+      <c r="F41" s="30" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -10484,75 +10560,75 @@
           <t>pool, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H41" s="25" t="inlineStr">
+      <c r="H41" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I41" s="25" t="inlineStr">
+      <c r="I41" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J41" s="25" t="inlineStr">
+      <c r="J41" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K41" s="25" t="inlineStr">
+      <c r="K41" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L41" s="25" t="inlineStr">
+      <c r="L41" s="30" t="inlineStr">
         <is>
           <t>HFE-CHM-8430</t>
         </is>
       </c>
-      <c r="M41" s="26" t="inlineStr">
+      <c r="M41" s="31" t="inlineStr">
         <is>
           <t>4250463108430</t>
         </is>
       </c>
-      <c r="N41" s="27" t="inlineStr"/>
-      <c r="O41" s="27" t="inlineStr"/>
-      <c r="P41" s="27" t="inlineStr"/>
-      <c r="Q41" s="25" t="inlineStr">
+      <c r="N41" s="32" t="inlineStr"/>
+      <c r="O41" s="32" t="inlineStr"/>
+      <c r="P41" s="32" t="inlineStr"/>
+      <c r="Q41" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R41" s="25" t="inlineStr">
+      <c r="R41" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S41" s="25" t="inlineStr">
+      <c r="S41" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T41" s="25" t="inlineStr">
+      <c r="T41" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U41" s="25" t="inlineStr">
+      <c r="U41" s="30" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="V41" s="25" t="inlineStr">
+      <c r="V41" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W41" s="25" t="inlineStr">
+      <c r="W41" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X41" s="25" t="inlineStr">
+      <c r="X41" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10562,7 +10638,7 @@
           <t>https://images.barcodelookup.com/17422/174228560-1.jpg</t>
         </is>
       </c>
-      <c r="Z41" s="25" t="inlineStr">
+      <c r="Z41" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10572,7 +10648,7 @@
           <t>1 x 1 kg BAYZID® multitabs 20g 5in1 for pools - HöFER CHEMIE</t>
         </is>
       </c>
-      <c r="AB41" s="25" t="inlineStr">
+      <c r="AB41" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10584,10 +10660,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF41" s="25" t="inlineStr"/>
-      <c r="AG41" s="25" t="inlineStr"/>
-      <c r="AH41" s="25" t="inlineStr"/>
-      <c r="AI41" s="25" t="inlineStr"/>
+      <c r="AF41" s="30" t="inlineStr"/>
+      <c r="AG41" s="30" t="inlineStr"/>
+      <c r="AH41" s="30" t="inlineStr"/>
+      <c r="AI41" s="30" t="inlineStr"/>
     </row>
     <row r="42" ht="76" customHeight="1">
       <c r="A42" s="19" t="inlineStr">
@@ -10605,17 +10681,17 @@
           <t>A ready-to-use alkaline spray cleaner for removing grease and dirt marks at the waterline of pools and for cleaning skimmers. The spray bottle makes application straightforward, and it can be used on a filled pool on all alkali-resistant surfaces.</t>
         </is>
       </c>
-      <c r="D42" s="25" t="inlineStr">
+      <c r="D42" s="30" t="inlineStr">
         <is>
           <t>Bayrol</t>
         </is>
       </c>
-      <c r="E42" s="25" t="inlineStr">
+      <c r="E42" s="30" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F42" s="25" t="inlineStr">
+      <c r="F42" s="30" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -10625,75 +10701,75 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H42" s="25" t="inlineStr">
+      <c r="H42" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I42" s="25" t="inlineStr">
+      <c r="I42" s="30" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J42" s="25" t="inlineStr">
+      <c r="J42" s="30" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K42" s="25" t="inlineStr">
+      <c r="K42" s="30" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L42" s="25" t="inlineStr">
+      <c r="L42" s="30" t="inlineStr">
         <is>
           <t>BAY-CLN-4134</t>
         </is>
       </c>
-      <c r="M42" s="26" t="inlineStr">
+      <c r="M42" s="31" t="inlineStr">
         <is>
           <t>4008367154134</t>
         </is>
       </c>
-      <c r="N42" s="27" t="inlineStr"/>
-      <c r="O42" s="27" t="inlineStr"/>
-      <c r="P42" s="27" t="inlineStr"/>
-      <c r="Q42" s="25" t="inlineStr">
+      <c r="N42" s="32" t="inlineStr"/>
+      <c r="O42" s="32" t="inlineStr"/>
+      <c r="P42" s="32" t="inlineStr"/>
+      <c r="Q42" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R42" s="25" t="inlineStr">
+      <c r="R42" s="30" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S42" s="25" t="inlineStr">
+      <c r="S42" s="30" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T42" s="25" t="inlineStr">
+      <c r="T42" s="30" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U42" s="25" t="inlineStr">
+      <c r="U42" s="30" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="V42" s="25" t="inlineStr">
+      <c r="V42" s="30" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W42" s="25" t="inlineStr">
+      <c r="W42" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X42" s="25" t="inlineStr">
+      <c r="X42" s="30" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10703,7 +10779,7 @@
           <t>https://www.north-spa.de/wp-content/uploads/2023/02/Produktbild-1-Bayrol-Randfix-07-l-4008367154134.jpg</t>
         </is>
       </c>
-      <c r="Z42" s="25" t="inlineStr">
+      <c r="Z42" s="30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10713,7 +10789,7 @@
           <t>Bayrol Randfix 0,7 l</t>
         </is>
       </c>
-      <c r="AB42" s="25" t="inlineStr">
+      <c r="AB42" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10725,10 +10801,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF42" s="25" t="inlineStr"/>
-      <c r="AG42" s="25" t="inlineStr"/>
-      <c r="AH42" s="25" t="inlineStr"/>
-      <c r="AI42" s="25" t="inlineStr"/>
+      <c r="AF42" s="30" t="inlineStr"/>
+      <c r="AG42" s="30" t="inlineStr"/>
+      <c r="AH42" s="30" t="inlineStr"/>
+      <c r="AI42" s="30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projects/splashstore/docs/splashstore-scan-curation-260816.xlsx
+++ b/projects/splashstore/docs/splashstore-scan-curation-260816.xlsx
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -175,6 +175,12 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -330,7 +336,19 @@
 RED = missing on an edible product.</t>
       </text>
     </comment>
+    <comment ref="N5" authorId="0" shapeId="0">
+      <text>
+        <t>No source anywhere confirmed this barcode, so the product has no name — and with no name there is nothing to search an image with.
+Identify it by hand: check the packaging, or search the code on the brand's own site.</t>
+      </text>
+    </comment>
     <comment ref="P5" authorId="0" shapeId="0">
+      <text>
+        <t>No source anywhere confirmed this barcode, so the product has no name — and with no name there is nothing to search an image with.
+Identify it by hand: check the packaging, or search the code on the brand's own site.</t>
+      </text>
+    </comment>
+    <comment ref="N16" authorId="0" shapeId="0">
       <text>
         <t>No source anywhere confirmed this barcode, so the product has no name — and with no name there is nothing to search an image with.
 Identify it by hand: check the packaging, or search the code on the brand's own site.</t>
@@ -390,10 +408,22 @@
 This one wants photographing in the garage, not more searching.</t>
       </text>
     </comment>
+    <comment ref="N38" authorId="0" shapeId="0">
+      <text>
+        <t>The product IS identified from its barcode, but no usable photo was found by any source we search: the barcode databases, the barcode directories, an image search on the confirmed name, and eBay.
+Nothing left to try automatically. Photograph it in the garage.</t>
+      </text>
+    </comment>
     <comment ref="P38" authorId="0" shapeId="0">
       <text>
         <t>The product IS identified from its barcode, but no usable photo was found by any source we search: the barcode databases, the barcode directories, an image search on the confirmed name, and eBay.
 Nothing left to try automatically. Photograph it in the garage.</t>
+      </text>
+    </comment>
+    <comment ref="N45" authorId="0" shapeId="0">
+      <text>
+        <t>No source anywhere confirmed this barcode, so the product has no name — and with no name there is nothing to search an image with.
+Identify it by hand: check the packaging, or search the code on the brand's own site.</t>
       </text>
     </comment>
     <comment ref="P45" authorId="0" shapeId="0">
@@ -1740,24 +1770,24 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.14285714285714" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="56" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="56" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
     <col width="3" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
@@ -1863,7 +1893,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="244" customHeight="1">
+    <row r="2" ht="132" customHeight="1">
       <c r="A2" s="2" t="n"/>
       <c r="B2" s="5" t="inlineStr">
         <is>
@@ -1900,7 +1930,7 @@
           <t>A cartridge filter for hot tubs and swim spas, measuring 26.0 cm outer diameter, 13.0 cm bottom part, and 3.8 cm inner thread. Compatible with Darlly SC779 and 40372 codes, it captures dirt, grease, and fine particles to keep water clean.</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: spa-components.com</t>
         </is>
@@ -1919,20 +1949,20 @@
           <t>https://www.spa-components.com/user/shop/big/1473-1_filter-cartridge-sc779-rising-dragon-plastics--eago-whirlpools.jpg?ff=1&amp;x=1024&amp;y=768&amp;q=85&amp;ts=6720c4a0&amp;sg=161563f2</t>
         </is>
       </c>
-      <c r="P2" s="7" t="inlineStr">
+      <c r="P2" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: spa-components.com</t>
         </is>
       </c>
       <c r="Q2" s="21" t="n"/>
-      <c r="R2" s="8" t="inlineStr">
+      <c r="R2" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S2" s="19" t="n"/>
     </row>
-    <row r="3" ht="258" customHeight="1">
+    <row r="3" ht="132" customHeight="1">
       <c r="A3" s="2" t="n"/>
       <c r="B3" s="5" t="inlineStr">
         <is>
@@ -1965,7 +1995,7 @@
           <t>A twin pack of Size II replacement filter cartridges measuring 10.6 x 13.6 cm, designed for compatible pool and spa filtration systems. The fine lamellar structure delivers thorough water cleaning and the cartridges are easy to rinse clean.</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: bestwaystore.de</t>
         </is>
@@ -1988,20 +2018,20 @@
           <t>https://www.bestwaystore.de/media/c6/f8/ba/1756384660/6941607353615-main-jpg.jpg?ts=1756384660</t>
         </is>
       </c>
-      <c r="P3" s="7" t="inlineStr">
+      <c r="P3" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: bestwaystore.de</t>
         </is>
       </c>
       <c r="Q3" s="21" t="n"/>
-      <c r="R3" s="8" t="inlineStr">
+      <c r="R3" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S3" s="19" t="n"/>
     </row>
-    <row r="4" ht="272" customHeight="1">
+    <row r="4" ht="132" customHeight="1">
       <c r="A4" s="2" t="n"/>
       <c r="B4" s="5" t="inlineStr">
         <is>
@@ -2038,7 +2068,7 @@
           <t>A single Flowclear Size 3 replacement filter cartridge for compatible Bestway pool filtration systems, featuring a fine lamellar structure that traps deposits and dirt effectively. Easy to clean and straightforward to swap out when routine maintenance is due.</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: pools.shop</t>
         </is>
@@ -2057,20 +2087,20 @@
           <t>https://ap.nice-cdn.com/upload/image/product/large/default/bestway-flowclear-filter-cartridge-size-3-1-item-638140-en.jpg</t>
         </is>
       </c>
-      <c r="P4" s="7" t="inlineStr">
+      <c r="P4" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: pools.shop</t>
         </is>
       </c>
       <c r="Q4" s="21" t="n"/>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="R4" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S4" s="19" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="9" t="n"/>
       <c r="B5" s="10" t="inlineStr">
         <is>
@@ -2087,7 +2117,7 @@
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="22" t="n"/>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t>Blank — missing</t>
         </is>
@@ -2098,20 +2128,20 @@
       <c r="M5" s="4" t="n"/>
       <c r="N5" s="4" t="n"/>
       <c r="O5" s="11" t="n"/>
-      <c r="P5" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
+      <c r="P5" s="22" t="inlineStr">
+        <is>
+          <t>Blank — not identified, cannot search</t>
         </is>
       </c>
       <c r="Q5" s="21" t="n"/>
-      <c r="R5" s="8" t="inlineStr">
+      <c r="R5" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S5" s="19" t="n"/>
     </row>
-    <row r="6" ht="230" customHeight="1">
+    <row r="6" ht="132" customHeight="1">
       <c r="A6" s="2" t="n"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -2148,7 +2178,7 @@
           <t>A two-pack of compatible hot tub and spa cartridge filters corresponding to Unicel C-4335, Pleatco PRB35-IN, and Filbur FC-2385 references. A handy spare-pair to keep on hand so your tub is never without a fresh filter.</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -2167,20 +2197,20 @@
           <t>https://images.barcodelookup.com/29361/293617958-1.jpg</t>
         </is>
       </c>
-      <c r="P6" s="7" t="inlineStr">
+      <c r="P6" s="30" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
       <c r="Q6" s="21" t="n"/>
-      <c r="R6" s="8" t="inlineStr">
+      <c r="R6" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S6" s="19" t="n"/>
     </row>
-    <row r="7" ht="258" customHeight="1">
+    <row r="7" ht="132" customHeight="1">
       <c r="A7" s="2" t="n"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -2213,7 +2243,7 @@
           <t>A single Size IV replacement filter cartridge measuring 14.2 x 25.4 cm, compatible with Bestway filter pump 58391 (9,463 l/h). Its deep-fold, fine-structure media delivers thorough water cleaning and can be rinsed clean with minimal effort.</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: bestwaystore.de</t>
         </is>
@@ -2236,20 +2266,20 @@
           <t>https://www.bestwaystore.de/media/53/6c/e9/1756384676/6941607353622-main-jpg.jpg?ts=1756384676</t>
         </is>
       </c>
-      <c r="P7" s="7" t="inlineStr">
+      <c r="P7" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: bestwaystore.de</t>
         </is>
       </c>
       <c r="Q7" s="21" t="n"/>
-      <c r="R7" s="8" t="inlineStr">
+      <c r="R7" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S7" s="19" t="n"/>
     </row>
-    <row r="8" ht="216" customHeight="1">
+    <row r="8" ht="132" customHeight="1">
       <c r="A8" s="12" t="n"/>
       <c r="B8" s="13" t="inlineStr">
         <is>
@@ -2286,7 +2316,7 @@
           <t>A pair of Darlly spa filter cartridges in the SC726 reference, also cross-referenced as Unicel C-4401 and Pleatco PRB17.5SF PR. Buying in pairs means a fresh replacement is always ready when it is time to swap.</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -2305,20 +2335,20 @@
           <t>https://images.barcodelookup.com/4378/43786454-1.jpg</t>
         </is>
       </c>
-      <c r="P8" s="14" t="inlineStr">
+      <c r="P8" s="31" t="inlineStr">
         <is>
           <t>Likely — Barcode Lookup (barcode) (unclear)</t>
         </is>
       </c>
       <c r="Q8" s="21" t="n"/>
-      <c r="R8" s="8" t="inlineStr">
+      <c r="R8" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S8" s="19" t="n"/>
     </row>
-    <row r="9" ht="320" customHeight="1">
+    <row r="9" ht="132" customHeight="1">
       <c r="A9" s="12" t="n"/>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -2355,7 +2385,7 @@
           <t>A replacement spa filter cartridge compatible with Arctic, Beachcomber, Canadian, Hydropool and Jacuzzi spas, sold under cross-reference codes including Unicel C-4950, Pleatco PRB50-IN and Darlly 40506. It keeps hot tub water clean by trapping debris and particles as water cycles through the filtration system.</t>
         </is>
       </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="I9" s="23" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -2374,20 +2404,20 @@
           <t>https://images.barcodelookup.com/4469/44699532-1.jpg</t>
         </is>
       </c>
-      <c r="P9" s="14" t="inlineStr">
+      <c r="P9" s="31" t="inlineStr">
         <is>
           <t>Likely — Barcode Lookup (barcode) (unclear)</t>
         </is>
       </c>
       <c r="Q9" s="21" t="n"/>
-      <c r="R9" s="8" t="inlineStr">
+      <c r="R9" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S9" s="19" t="n"/>
     </row>
-    <row r="10" ht="300" customHeight="1">
+    <row r="10" ht="132" customHeight="1">
       <c r="A10" s="2" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -2420,7 +2450,7 @@
           <t>A square inflatable hot tub for up to four people, with an overall outer diameter of 2.45 m and a structure measuring 1.75 x 1.75 x 0.71 m, built from high-resistance polyester for good rigidity and durability. The packaged weight is 64.92 kg, so you will want a helper on delivery day.</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: intex.fr</t>
         </is>
@@ -2447,20 +2477,20 @@
           <t>https://media.intex.fr/7743-large_default_x2/28464ex-spa-gonflable-calacatta-4-places.jpg</t>
         </is>
       </c>
-      <c r="P10" s="7" t="inlineStr">
+      <c r="P10" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: intex.fr</t>
         </is>
       </c>
       <c r="Q10" s="21" t="n"/>
-      <c r="R10" s="8" t="inlineStr">
+      <c r="R10" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S10" s="19" t="n"/>
     </row>
-    <row r="11" ht="230" customHeight="1">
+    <row r="11" ht="132" customHeight="1">
       <c r="A11" s="2" t="n"/>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -2497,7 +2527,7 @@
           <t>A 3.0 kg tub of hth stabiliser granules for outdoor swimming pools, used to protect chlorine from UV degradation and extend its effectiveness. A reliable way to get more mileage from your sanitiser on sunny days.</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -2518,20 +2548,20 @@
           <t>https://images.barcodelookup.com/12027/120276177-1.jpg</t>
         </is>
       </c>
-      <c r="P11" s="7" t="inlineStr">
+      <c r="P11" s="30" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
       <c r="Q11" s="21" t="n"/>
-      <c r="R11" s="8" t="inlineStr">
+      <c r="R11" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S11" s="19" t="n"/>
     </row>
-    <row r="12" ht="202" customHeight="1">
+    <row r="12" ht="132" customHeight="1">
       <c r="A12" s="2" t="n"/>
       <c r="B12" s="13" t="inlineStr">
         <is>
@@ -2568,7 +2598,7 @@
           <t>A 1-litre bottle of hth Spa Antikalk, formulated to prevent and remove limescale in spa and hot tub water. Keeping scale under control helps protect internal components and maintain water clarity.</t>
         </is>
       </c>
-      <c r="I12" s="15" t="inlineStr">
+      <c r="I12" s="23" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -2587,20 +2617,20 @@
           <t>https://www.north-spa.de/wp-content/uploads/2025/02/Produktbild-1-hth-SPA-ANTIKALK-1-l-3521684700194-360x360.jpg</t>
         </is>
       </c>
-      <c r="P12" s="7" t="inlineStr">
+      <c r="P12" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: north-spa.de</t>
         </is>
       </c>
       <c r="Q12" s="21" t="n"/>
-      <c r="R12" s="8" t="inlineStr">
+      <c r="R12" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S12" s="19" t="n"/>
     </row>
-    <row r="13" ht="230" customHeight="1">
+    <row r="13" ht="132" customHeight="1">
       <c r="A13" s="2" t="n"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -2633,7 +2663,7 @@
           <t>A round, olive-green inflatable spa designed to seat up to eight people comfortably, with a maximum water temperature of 40°C. Five accessories are included in the box, so there is plenty to get started with straight away.</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: intex.fr</t>
         </is>
@@ -2652,20 +2682,20 @@
           <t>https://media.intex.fr/11990-large_default_x2/28412np-spa-gonflable-olive-8-places.jpg</t>
         </is>
       </c>
-      <c r="P13" s="7" t="inlineStr">
+      <c r="P13" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: intex.fr</t>
         </is>
       </c>
       <c r="Q13" s="21" t="n"/>
-      <c r="R13" s="8" t="inlineStr">
+      <c r="R13" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S13" s="19" t="n"/>
     </row>
-    <row r="14" ht="202" customHeight="1">
+    <row r="14" ht="132" customHeight="1">
       <c r="A14" s="2" t="n"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -2702,7 +2732,7 @@
           <t>A Darlly SC750 replacement cartridge filter compatible with Arctic, Fonteyn, Rota, and Strong Spa hot tubs, among others. A straightforward like-for-like swap to keep your spa water flowing clean.</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -2721,20 +2751,20 @@
           <t>https://images.barcodelookup.com/29338/293384728-1.jpg</t>
         </is>
       </c>
-      <c r="P14" s="7" t="inlineStr">
+      <c r="P14" s="30" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
       <c r="Q14" s="21" t="n"/>
-      <c r="R14" s="8" t="inlineStr">
+      <c r="R14" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S14" s="19" t="n"/>
     </row>
-    <row r="15" ht="216" customHeight="1">
+    <row r="15" ht="132" customHeight="1">
       <c r="A15" s="2" t="n"/>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -2771,7 +2801,7 @@
           <t>SpaBalancer Clean and Refresh is a spa water treatment product supplied with a sprayer for easy application. It is designed to keep spa water fresh and clean as part of a regular maintenance routine.</t>
         </is>
       </c>
-      <c r="I15" s="15" t="inlineStr">
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -2790,20 +2820,20 @@
           <t>https://www.spabalancer.ch/media/ae/20/d2/1728651174/sb111_clean-refresh_freigestellt.png?ts=1777362921</t>
         </is>
       </c>
-      <c r="P15" s="7" t="inlineStr">
+      <c r="P15" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: spabalancer.ch</t>
         </is>
       </c>
       <c r="Q15" s="21" t="n"/>
-      <c r="R15" s="8" t="inlineStr">
+      <c r="R15" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S15" s="19" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="34" customHeight="1">
       <c r="A16" s="9" t="n"/>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -2820,7 +2850,7 @@
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="22" t="n"/>
-      <c r="I16" s="11" t="inlineStr">
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>Blank — missing</t>
         </is>
@@ -2831,20 +2861,20 @@
       <c r="M16" s="4" t="n"/>
       <c r="N16" s="4" t="n"/>
       <c r="O16" s="11" t="n"/>
-      <c r="P16" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
+      <c r="P16" s="22" t="inlineStr">
+        <is>
+          <t>Blank — not identified, cannot search</t>
         </is>
       </c>
       <c r="Q16" s="21" t="n"/>
-      <c r="R16" s="8" t="inlineStr">
+      <c r="R16" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S16" s="19" t="n"/>
     </row>
-    <row r="17" ht="202" customHeight="1">
+    <row r="17" ht="62" customHeight="1">
       <c r="A17" s="9" t="n"/>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -2881,7 +2911,7 @@
           <t>A pack of 500 DPD 1 reagent tablets for use with the Water-ID photometer, measuring free chlorine levels in pool or spa water. Having a full pack to hand means you will not run short mid-season.</t>
         </is>
       </c>
-      <c r="I17" s="15" t="inlineStr">
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -2896,13 +2926,13 @@
       <c r="M17" s="4" t="n"/>
       <c r="N17" s="4" t="n"/>
       <c r="O17" s="11" t="n"/>
-      <c r="P17" s="11" t="inlineStr">
-        <is>
-          <t>Blank — checked, not the product</t>
+      <c r="P17" s="22" t="inlineStr">
+        <is>
+          <t>Blank — found one, wrong product</t>
         </is>
       </c>
       <c r="Q17" s="21" t="n"/>
-      <c r="R17" s="8" t="inlineStr">
+      <c r="R17" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -2913,7 +2943,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="216" customHeight="1">
+    <row r="18" ht="132" customHeight="1">
       <c r="A18" s="2" t="n"/>
       <c r="B18" s="13" t="inlineStr">
         <is>
@@ -2950,7 +2980,7 @@
           <t>A pack of 500 Phenol Red reagent tablets compatible with the Water-ID photometer, used for measuring pH levels in pool or spa water. Accurate pH readings are the foundation of balanced, comfortable water.</t>
         </is>
       </c>
-      <c r="I18" s="15" t="inlineStr">
+      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -2969,20 +2999,20 @@
           <t>https://www.poolpowershop.de/media/46/63/13/1743521499/phenol-red-testtabletten-fuer-poollab-500-stk.jpg</t>
         </is>
       </c>
-      <c r="P18" s="7" t="inlineStr">
+      <c r="P18" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: poolpowershop.de</t>
         </is>
       </c>
       <c r="Q18" s="21" t="n"/>
-      <c r="R18" s="8" t="inlineStr">
+      <c r="R18" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S18" s="19" t="n"/>
     </row>
-    <row r="19" ht="202" customHeight="1">
+    <row r="19" ht="132" customHeight="1">
       <c r="A19" s="2" t="n"/>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -3019,7 +3049,7 @@
           <t>An alkaline edge and surround cleaner in a 1-litre bottle, formulated to be gentle on pool liners, foils, and plastic surfaces. It tackles waterline grime without harming the materials it touches.</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -3038,20 +3068,20 @@
           <t>https://images.barcodelookup.com/21057/210579756-1.jpg</t>
         </is>
       </c>
-      <c r="P19" s="7" t="inlineStr">
+      <c r="P19" s="30" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
       <c r="Q19" s="21" t="n"/>
-      <c r="R19" s="8" t="inlineStr">
+      <c r="R19" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S19" s="19" t="n"/>
     </row>
-    <row r="20" ht="272" customHeight="1">
+    <row r="20" ht="132" customHeight="1">
       <c r="A20" s="2" t="n"/>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -3088,7 +3118,7 @@
           <t>A 1-litre pool surface cleaner formulated to remove sunscreen oils and greasy residues from the water surface, designed specifically for warm Mediterranean climates and heavy swimming loads. It keeps the waterline and surface clear without harming pool materials.</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: mangas.com.cy</t>
         </is>
@@ -3107,20 +3137,20 @@
           <t>http://mangas.com.cy/media/products/5292638000223.jpg</t>
         </is>
       </c>
-      <c r="P20" s="7" t="inlineStr">
+      <c r="P20" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: mangas.com.cy</t>
         </is>
       </c>
       <c r="Q20" s="21" t="n"/>
-      <c r="R20" s="8" t="inlineStr">
+      <c r="R20" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S20" s="19" t="n"/>
     </row>
-    <row r="21" ht="320" customHeight="1">
+    <row r="21" ht="132" customHeight="1">
       <c r="A21" s="2" t="n"/>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -3157,7 +3187,7 @@
           <t>California Clear Blue is a super-concentrated, pH-neutral pool clarifier in a 1-litre bottle, using a cationic polymer formula to bind microscopic particles such as dust, pollen, and oils into larger clusters your filter can catch. Non-toxic and biodegradable, it is safe for sand, zeolite, and glass filtration media.</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: poolservices.cy</t>
         </is>
@@ -3176,20 +3206,20 @@
           <t>https://poolservices.cy/storage/2026/05/California-Clear-Blue-1L-Aquality-2.jpeg</t>
         </is>
       </c>
-      <c r="P21" s="7" t="inlineStr">
+      <c r="P21" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: poolservices.cy</t>
         </is>
       </c>
       <c r="Q21" s="21" t="n"/>
-      <c r="R21" s="8" t="inlineStr">
+      <c r="R21" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S21" s="19" t="n"/>
     </row>
-    <row r="22" ht="188" customHeight="1">
+    <row r="22" ht="132" customHeight="1">
       <c r="A22" s="2" t="n"/>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -3226,7 +3256,7 @@
           <t>A 1-litre tile and vinyl cleaner for pools, designed to clean pool tile surfaces and vinyl liners. It makes light work of the tidying up that keeps a pool looking its best.</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I22" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: mangas.com.cy</t>
         </is>
@@ -3245,20 +3275,20 @@
           <t>http://mangas.com.cy/media/products/5292638000162.jpg</t>
         </is>
       </c>
-      <c r="P22" s="7" t="inlineStr">
+      <c r="P22" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: mangas.com.cy</t>
         </is>
       </c>
       <c r="Q22" s="21" t="n"/>
-      <c r="R22" s="8" t="inlineStr">
+      <c r="R22" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S22" s="19" t="n"/>
     </row>
-    <row r="23" ht="174" customHeight="1">
+    <row r="23" ht="132" customHeight="1">
       <c r="A23" s="2" t="n"/>
       <c r="B23" s="13" t="inlineStr">
         <is>
@@ -3295,7 +3325,7 @@
           <t>A 1-litre spa and pool water clarifier from Bayzid, formulated to clear cloudy or turbid water. A handy bottle to reach for whenever the water loses its sparkle.</t>
         </is>
       </c>
-      <c r="I23" s="15" t="inlineStr">
+      <c r="I23" s="23" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -3314,20 +3344,20 @@
           <t>https://hoefer-shop.com/cdn/shop/files/1x1L-BAYZID-Spa-Poolclear-v1-RS_1.jpg?v=1785600487&amp;width=800</t>
         </is>
       </c>
-      <c r="P23" s="7" t="inlineStr">
+      <c r="P23" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: hoefer-shop.com</t>
         </is>
       </c>
       <c r="Q23" s="21" t="n"/>
-      <c r="R23" s="8" t="inlineStr">
+      <c r="R23" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S23" s="19" t="n"/>
     </row>
-    <row r="24" ht="202" customHeight="1">
+    <row r="24" ht="132" customHeight="1">
       <c r="A24" s="2" t="n"/>
       <c r="B24" s="13" t="inlineStr">
         <is>
@@ -3364,7 +3394,7 @@
           <t>A 1-litre bottle of hydrogen peroxide at 11.9% concentration, suitable for disinfection and water treatment applications. A straightforward chemical solution that keeps things clean without fuss.</t>
         </is>
       </c>
-      <c r="I24" s="15" t="inlineStr">
+      <c r="I24" s="23" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -3383,20 +3413,20 @@
           <t>https://hoefer-shop.com/cdn/shop/files/1x1L-Wasserstoffperoxid-Flasche-hinten-26.jpg?v=1783777627&amp;width=1000</t>
         </is>
       </c>
-      <c r="P24" s="7" t="inlineStr">
+      <c r="P24" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: hoefer-shop.com</t>
         </is>
       </c>
       <c r="Q24" s="21" t="n"/>
-      <c r="R24" s="8" t="inlineStr">
+      <c r="R24" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S24" s="19" t="n"/>
     </row>
-    <row r="25" ht="202" customHeight="1">
+    <row r="25" ht="132" customHeight="1">
       <c r="A25" s="12" t="n"/>
       <c r="B25" s="13" t="inlineStr">
         <is>
@@ -3433,7 +3463,7 @@
           <t>A 4.5 kg pack of chlorine stabilizer for swimming pools, used to protect chlorine from UV degradation and extend its effectiveness in the water. Steady chemistry for a pool that earns its keep.</t>
         </is>
       </c>
-      <c r="I25" s="15" t="inlineStr">
+      <c r="I25" s="23" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -3454,20 +3484,20 @@
           <t>https://yokando.com/img/p/2/8/2/9/3/28293.jpg</t>
         </is>
       </c>
-      <c r="P25" s="14" t="inlineStr">
+      <c r="P25" s="31" t="inlineStr">
         <is>
           <t>Likely — image match: yokando.com</t>
         </is>
       </c>
       <c r="Q25" s="21" t="n"/>
-      <c r="R25" s="8" t="inlineStr">
+      <c r="R25" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S25" s="19" t="n"/>
     </row>
-    <row r="26" ht="202" customHeight="1">
+    <row r="26" ht="132" customHeight="1">
       <c r="A26" s="2" t="n"/>
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -3504,7 +3534,7 @@
           <t>UltraShock is a pool and spa shock treatment from SpaBalancer, designed to rapidly oxidise contaminants and restore water clarity. A quick reset for water that needs a little more persuasion.</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I26" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -3523,20 +3553,20 @@
           <t>https://images.barcodelookup.com/16704/167043133-1.jpg</t>
         </is>
       </c>
-      <c r="P26" s="7" t="inlineStr">
+      <c r="P26" s="30" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
       <c r="Q26" s="21" t="n"/>
-      <c r="R26" s="8" t="inlineStr">
+      <c r="R26" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S26" s="19" t="n"/>
     </row>
-    <row r="27" ht="314" customHeight="1">
+    <row r="27" ht="132" customHeight="1">
       <c r="A27" s="2" t="n"/>
       <c r="B27" s="5" t="inlineStr">
         <is>
@@ -3569,7 +3599,7 @@
           <t>A patented foam rubber eraser for cleaning pool surfaces, particularly suited to waterline stains on liner and vitreous ceramic finishes, and it works without detergents or chemicals. Each box contains 3 sponges, which harden when wet to scrub effectively while remaining soft and flexible in use.</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: piscinarium.com</t>
         </is>
@@ -3588,20 +3618,20 @@
           <t>https://www.piscinarium.com/2908-thickbox_default/pool-gom-magic-rubber-eraser.jpg</t>
         </is>
       </c>
-      <c r="P27" s="7" t="inlineStr">
+      <c r="P27" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: piscinarium.com</t>
         </is>
       </c>
       <c r="Q27" s="21" t="n"/>
-      <c r="R27" s="8" t="inlineStr">
+      <c r="R27" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S27" s="19" t="n"/>
     </row>
-    <row r="28" ht="216" customHeight="1">
+    <row r="28" ht="62" customHeight="1">
       <c r="A28" s="9" t="n"/>
       <c r="B28" s="10" t="inlineStr">
         <is>
@@ -3634,7 +3664,7 @@
           <t>Spa Industries Europe appears to be a brand or supplier name rather than a specific product, so no product details can be confirmed. For accurate information, please check the full product listing.</t>
         </is>
       </c>
-      <c r="I28" s="15" t="inlineStr">
+      <c r="I28" s="23" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -3649,13 +3679,13 @@
       <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="n"/>
       <c r="O28" s="11" t="n"/>
-      <c r="P28" s="11" t="inlineStr">
-        <is>
-          <t>Blank — checked, not the product</t>
+      <c r="P28" s="22" t="inlineStr">
+        <is>
+          <t>Blank — found one, wrong product</t>
         </is>
       </c>
       <c r="Q28" s="21" t="n"/>
-      <c r="R28" s="8" t="inlineStr">
+      <c r="R28" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -3666,7 +3696,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="230" customHeight="1">
+    <row r="29" ht="62" customHeight="1">
       <c r="A29" s="9" t="n"/>
       <c r="B29" s="10" t="inlineStr">
         <is>
@@ -3703,7 +3733,7 @@
           <t>A 1-litre high-concentrate sauna cleaner with eucalyptus fragrance, formulated as a deep-cleaning base cleaner for sauna surfaces. The concentrated formula means a little goes a long way, with a fresh scent to match.</t>
         </is>
       </c>
-      <c r="I29" s="15" t="inlineStr">
+      <c r="I29" s="23" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -3718,13 +3748,13 @@
       <c r="M29" s="4" t="n"/>
       <c r="N29" s="4" t="n"/>
       <c r="O29" s="11" t="n"/>
-      <c r="P29" s="11" t="inlineStr">
-        <is>
-          <t>Blank — checked, not the product</t>
+      <c r="P29" s="22" t="inlineStr">
+        <is>
+          <t>Blank — found one, wrong product</t>
         </is>
       </c>
       <c r="Q29" s="21" t="n"/>
-      <c r="R29" s="8" t="inlineStr">
+      <c r="R29" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -3735,7 +3765,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="300" customHeight="1">
+    <row r="30" ht="132" customHeight="1">
       <c r="A30" s="2" t="n"/>
       <c r="B30" s="5" t="inlineStr">
         <is>
@@ -3772,7 +3802,7 @@
           <t>This HTH spa cleaner removes mineral deposits such as limescale and rust, and cleans and polishes aluminium, chrome, stainless steel, and enamel surfaces with a pleasant pine fragrance. It has a high concentration of active ingredients and is recommended for periodic maintenance cleaning.</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I30" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: cdiscount.com</t>
         </is>
@@ -3791,20 +3821,20 @@
           <t>https://www.cdiscount.com/pdt2/0/5/1/1/700x700/auc2009356289051/rw/hth-spa-nettoyant-spa-3521686010178.jpg</t>
         </is>
       </c>
-      <c r="P30" s="7" t="inlineStr">
+      <c r="P30" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: cdiscount.com</t>
         </is>
       </c>
       <c r="Q30" s="21" t="n"/>
-      <c r="R30" s="8" t="inlineStr">
+      <c r="R30" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S30" s="19" t="n"/>
     </row>
-    <row r="31" ht="230" customHeight="1">
+    <row r="31" ht="132" customHeight="1">
       <c r="A31" s="2" t="n"/>
       <c r="B31" s="5" t="inlineStr">
         <is>
@@ -3837,7 +3867,7 @@
           <t>A 25 kg sack of pure boiling salt (minimum 99.6% NaCl) without an anti-caking agent, meeting EN 973 Type A standard and suitable for use in pool salt electrolysis systems. Not intended for human consumption or animal feed.</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I31" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: altruan.com</t>
         </is>
@@ -3858,7 +3888,7 @@
           <t>http://altruan.com/cdn/shop/files/SalinenPoolSalz25kgSack.png?v=1778597596</t>
         </is>
       </c>
-      <c r="P31" s="7" t="inlineStr">
+      <c r="P31" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: altruan.com</t>
         </is>
@@ -3868,14 +3898,14 @@
           <t>Composition: Siedesalz (min. 99.6% NaCl) 100%; Separant/sodium ferrocyanide 4.0–12.0 mg/kg | Grain: &gt;0.63 mm approx. 20%, 0.2–0.63 mm approx. 75%, &lt;0.2 mm approx. 5% | Moisture: &lt;0.08%</t>
         </is>
       </c>
-      <c r="R31" s="8" t="inlineStr">
+      <c r="R31" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S31" s="19" t="n"/>
     </row>
-    <row r="32" ht="272" customHeight="1">
+    <row r="32" ht="132" customHeight="1">
       <c r="A32" s="2" t="n"/>
       <c r="B32" s="13" t="inlineStr">
         <is>
@@ -3912,7 +3942,7 @@
           <t>A cordless robotic pool cleaner that scrubs both floors and walls automatically, using WavePath navigation to map and cover the pool efficiently. Built-in high-performance filtration and smart control make it a hands-off solution for keeping pool water clear.</t>
         </is>
       </c>
-      <c r="I32" s="15" t="inlineStr">
+      <c r="I32" s="23" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -3931,20 +3961,20 @@
           <t>https://images.barcodelookup.com/176692/1766920801-1.jpg</t>
         </is>
       </c>
-      <c r="P32" s="7" t="inlineStr">
+      <c r="P32" s="30" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
       <c r="Q32" s="21" t="n"/>
-      <c r="R32" s="8" t="inlineStr">
+      <c r="R32" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S32" s="19" t="n"/>
     </row>
-    <row r="33" ht="244" customHeight="1">
+    <row r="33" ht="132" customHeight="1">
       <c r="A33" s="2" t="n"/>
       <c r="B33" s="5" t="inlineStr">
         <is>
@@ -3977,7 +4007,7 @@
           <t>The Scuba L1 EU is a pool cleaning device, though no further specific details about its features, dimensions, or mechanism are available from the product name alone. Buyers should refer to the full product listing for specifications.</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -3996,20 +4026,20 @@
           <t>https://images.barcodelookup.com/124722/1247228758-1.jpg</t>
         </is>
       </c>
-      <c r="P33" s="7" t="inlineStr">
+      <c r="P33" s="30" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
       <c r="Q33" s="21" t="n"/>
-      <c r="R33" s="8" t="inlineStr">
+      <c r="R33" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S33" s="19" t="n"/>
     </row>
-    <row r="34" ht="174" customHeight="1">
+    <row r="34" ht="132" customHeight="1">
       <c r="A34" s="2" t="n"/>
       <c r="B34" s="5" t="inlineStr">
         <is>
@@ -4042,7 +4072,7 @@
           <t>The Gre Pools RBR120 is a 51W robotic pool cleaner designed for automatic pool floor cleaning. A reliable workhorse that takes the scrubbing off your hands.</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -4061,20 +4091,20 @@
           <t>https://images.barcodelookup.com/124726/1247268298-1.jpg</t>
         </is>
       </c>
-      <c r="P34" s="7" t="inlineStr">
+      <c r="P34" s="30" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
       <c r="Q34" s="21" t="n"/>
-      <c r="R34" s="8" t="inlineStr">
+      <c r="R34" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S34" s="19" t="n"/>
     </row>
-    <row r="35" ht="320" customHeight="1">
+    <row r="35" ht="132" customHeight="1">
       <c r="A35" s="2" t="n"/>
       <c r="B35" s="5" t="inlineStr">
         <is>
@@ -4107,7 +4137,7 @@
           <t>A twin-size inflatable airbed measuring 99 x 191 x 25 cm, built with Fiber-Tech internal construction using polyester fibres for comfort, vinyl sides and base, and a water-resistant flocked top surface with an anti-deflation valve. It supports a maximum weight of 136 kg and packs down compactly when deflated.</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="I35" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: ecoperation.com</t>
         </is>
@@ -4132,20 +4162,20 @@
           <t>https://www.ecoperation.com/media/catalog/product/cache/b76cf1d99a7811daa83ba86e6ad91c89/6/4/64757.jpg</t>
         </is>
       </c>
-      <c r="P35" s="7" t="inlineStr">
+      <c r="P35" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: ecoperation.com</t>
         </is>
       </c>
       <c r="Q35" s="21" t="n"/>
-      <c r="R35" s="8" t="inlineStr">
+      <c r="R35" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S35" s="19" t="n"/>
     </row>
-    <row r="36" ht="300" customHeight="1">
+    <row r="36" ht="132" customHeight="1">
       <c r="A36" s="2" t="n"/>
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -4182,7 +4212,7 @@
           <t>A plastic chlorine dosing lock from Steinbach, designed exclusively for use with long-term chlorine tablets, with a 1.5-inch connection fitting. It measures 37 cm in length, 22.5 cm in width, and 15 cm in height, making it a sturdy inline dosing unit for pool water treatment systems.</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="I36" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: ebay.de</t>
         </is>
@@ -4207,20 +4237,20 @@
           <t>https://i.ebayimg.com/images/g/CrUAAeSwkOdqeaRR/s-l400.jpg</t>
         </is>
       </c>
-      <c r="P36" s="7" t="inlineStr">
+      <c r="P36" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: ebay.de</t>
         </is>
       </c>
       <c r="Q36" s="21" t="n"/>
-      <c r="R36" s="8" t="inlineStr">
+      <c r="R36" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S36" s="19" t="n"/>
     </row>
-    <row r="37" ht="272" customHeight="1">
+    <row r="37" ht="132" customHeight="1">
       <c r="A37" s="2" t="n"/>
       <c r="B37" s="5" t="inlineStr">
         <is>
@@ -4257,7 +4287,7 @@
           <t>A filter cleaning system for hot tub and pool cartridge filters, designed to remove debris and residue efficiently while keeping water usage to a minimum. A practical tool for extending the life of your filter without wasting a drop more than necessary.</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="I37" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: ebay.com</t>
         </is>
@@ -4276,20 +4306,20 @@
           <t>https://i.ebayimg.com/images/g/0e0AAOSweaplqO77/s-l400.jpg</t>
         </is>
       </c>
-      <c r="P37" s="7" t="inlineStr">
+      <c r="P37" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: ebay.com</t>
         </is>
       </c>
       <c r="Q37" s="21" t="n"/>
-      <c r="R37" s="8" t="inlineStr">
+      <c r="R37" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S37" s="19" t="n"/>
     </row>
-    <row r="38" ht="230" customHeight="1">
+    <row r="38" ht="62" customHeight="1">
       <c r="A38" s="9" t="n"/>
       <c r="B38" s="10" t="inlineStr">
         <is>
@@ -4326,7 +4356,7 @@
           <t>A compact handy scrub brush for pool maintenance, measuring 15 x 9 x 8 cm, suited to scrubbing pool surfaces and hard-to-reach areas. Small enough to manoeuvre easily, and ready to tackle whatever the waterline throws at it.</t>
         </is>
       </c>
-      <c r="I38" s="15" t="inlineStr">
+      <c r="I38" s="23" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -4347,20 +4377,20 @@
       </c>
       <c r="N38" s="4" t="n"/>
       <c r="O38" s="11" t="n"/>
-      <c r="P38" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
+      <c r="P38" s="22" t="inlineStr">
+        <is>
+          <t>Blank — searched, none found</t>
         </is>
       </c>
       <c r="Q38" s="21" t="n"/>
-      <c r="R38" s="8" t="inlineStr">
+      <c r="R38" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S38" s="19" t="n"/>
     </row>
-    <row r="39" ht="286" customHeight="1">
+    <row r="39" ht="132" customHeight="1">
       <c r="A39" s="2" t="n"/>
       <c r="B39" s="5" t="inlineStr">
         <is>
@@ -4397,7 +4427,7 @@
           <t>An inflatable PVC headrest pillow for the Intex inflatable spa (model 28506), measuring 24 x 19 x 6 cm and weighing 0.22 kg, designed to support the head and neck comfortably during use. It attaches to the spa rim and can also be filled with water for added stability.</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="I39" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: rozetka.pl</t>
         </is>
@@ -4424,20 +4454,20 @@
           <t>https://content2.rozetka.com.ua/goods/images/big/570260745.jpg</t>
         </is>
       </c>
-      <c r="P39" s="7" t="inlineStr">
+      <c r="P39" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: rozetka.pl</t>
         </is>
       </c>
       <c r="Q39" s="21" t="n"/>
-      <c r="R39" s="8" t="inlineStr">
+      <c r="R39" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S39" s="19" t="n"/>
     </row>
-    <row r="40" ht="314" customHeight="1">
+    <row r="40" ht="132" customHeight="1">
       <c r="A40" s="2" t="n"/>
       <c r="B40" s="5" t="inlineStr">
         <is>
@@ -4470,7 +4500,7 @@
           <t>A DPD Pool test kit for active-oxygen pools, containing 20 DPD No. 4 reagent tablets for measuring active oxygen levels and 20 phenol red tablets for measuring pH. Results are read immediately after the tablet dissolves, with an ideal active oxygen range of 3.0 to 8.0 mg/l and a target pH of 7.0 to 7.4.</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="I40" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: carrefour.fr</t>
         </is>
@@ -4489,20 +4519,20 @@
           <t>https://media.carrefour.fr/medias/8f94161f683b4e589024a5b5ebaa6873/p_200x200/cad3db6a00ef414a804b9226119bae96_image.jpg</t>
         </is>
       </c>
-      <c r="P40" s="7" t="inlineStr">
+      <c r="P40" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: carrefour.fr</t>
         </is>
       </c>
       <c r="Q40" s="21" t="n"/>
-      <c r="R40" s="8" t="inlineStr">
+      <c r="R40" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S40" s="19" t="n"/>
     </row>
-    <row r="41" ht="202" customHeight="1">
+    <row r="41" ht="132" customHeight="1">
       <c r="A41" s="2" t="n"/>
       <c r="B41" s="13" t="inlineStr">
         <is>
@@ -4539,7 +4569,7 @@
           <t>A pack of 2 replacement filter cartridges compatible with Intex Type H pool and spa pumps, made by Darlly. Straightforward to swap out, they keep the water moving clean without any complications.</t>
         </is>
       </c>
-      <c r="I41" s="15" t="inlineStr">
+      <c r="I41" s="23" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -4558,20 +4588,20 @@
           <t>https://a.allegroimg.com/original/11923c/a79785a04d36aa54f0d87384f038/Filtracni-kartuse-Intex-D-3BTZ0023-SC828</t>
         </is>
       </c>
-      <c r="P41" s="7" t="inlineStr">
+      <c r="P41" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: allegro.cz</t>
         </is>
       </c>
       <c r="Q41" s="21" t="n"/>
-      <c r="R41" s="8" t="inlineStr">
+      <c r="R41" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S41" s="19" t="n"/>
     </row>
-    <row r="42" ht="230" customHeight="1">
+    <row r="42" ht="132" customHeight="1">
       <c r="A42" s="2" t="n"/>
       <c r="B42" s="5" t="inlineStr">
         <is>
@@ -4608,7 +4638,7 @@
           <t>A Darlly replacement spa filter cartridge with dimensions of 22 cm diameter by 27 cm height, compatible with SC713 and C-8465 references. A reliable like-for-like swap to keep your spa filtration running smoothly.</t>
         </is>
       </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="I42" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -4631,20 +4661,20 @@
           <t>https://images.barcodelookup.com/142259/1422591231-1.jpg</t>
         </is>
       </c>
-      <c r="P42" s="7" t="inlineStr">
+      <c r="P42" s="30" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
       <c r="Q42" s="21" t="n"/>
-      <c r="R42" s="8" t="inlineStr">
+      <c r="R42" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S42" s="19" t="n"/>
     </row>
-    <row r="43" ht="230" customHeight="1">
+    <row r="43" ht="132" customHeight="1">
       <c r="A43" s="2" t="n"/>
       <c r="B43" s="5" t="inlineStr">
         <is>
@@ -4681,7 +4711,7 @@
           <t>A 1 kg pack of 20g multitabs for swimming pools, offering a 5-in-1 treatment that combines multiple water care functions in a single slow-dissolving tablet. Convenient all-in-one dosing that keeps pool maintenance simple.</t>
         </is>
       </c>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="I43" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -4702,20 +4732,20 @@
           <t>https://images.barcodelookup.com/17422/174228560-1.jpg</t>
         </is>
       </c>
-      <c r="P43" s="7" t="inlineStr">
+      <c r="P43" s="30" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
       <c r="Q43" s="21" t="n"/>
-      <c r="R43" s="8" t="inlineStr">
+      <c r="R43" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S43" s="19" t="n"/>
     </row>
-    <row r="44" ht="258" customHeight="1">
+    <row r="44" ht="132" customHeight="1">
       <c r="A44" s="2" t="n"/>
       <c r="B44" s="5" t="inlineStr">
         <is>
@@ -4752,7 +4782,7 @@
           <t>A ready-to-use alkaline spray cleaner for removing grease and dirt marks at the waterline of pools and for cleaning skimmers. The spray bottle makes application straightforward, and it can be used on a filled pool on all alkali-resistant surfaces.</t>
         </is>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="I44" s="30" t="inlineStr">
         <is>
           <t>Verified — product page: north-spa.de</t>
         </is>
@@ -4773,20 +4803,20 @@
           <t>https://www.north-spa.de/wp-content/uploads/2023/02/Produktbild-1-Bayrol-Randfix-07-l-4008367154134.jpg</t>
         </is>
       </c>
-      <c r="P44" s="7" t="inlineStr">
+      <c r="P44" s="30" t="inlineStr">
         <is>
           <t>Verified — barcode: north-spa.de</t>
         </is>
       </c>
       <c r="Q44" s="21" t="n"/>
-      <c r="R44" s="8" t="inlineStr">
+      <c r="R44" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
       <c r="S44" s="19" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" ht="34" customHeight="1">
       <c r="A45" s="9" t="n"/>
       <c r="B45" s="10" t="inlineStr">
         <is>
@@ -4803,7 +4833,7 @@
       <c r="F45" s="3" t="n"/>
       <c r="G45" s="3" t="n"/>
       <c r="H45" s="22" t="n"/>
-      <c r="I45" s="11" t="inlineStr">
+      <c r="I45" s="22" t="inlineStr">
         <is>
           <t>Blank — missing</t>
         </is>
@@ -4814,13 +4844,13 @@
       <c r="M45" s="4" t="n"/>
       <c r="N45" s="4" t="n"/>
       <c r="O45" s="11" t="n"/>
-      <c r="P45" s="11" t="inlineStr">
-        <is>
-          <t>Blank — no image</t>
+      <c r="P45" s="22" t="inlineStr">
+        <is>
+          <t>Blank — not identified, cannot search</t>
         </is>
       </c>
       <c r="Q45" s="21" t="n"/>
-      <c r="R45" s="8" t="inlineStr">
+      <c r="R45" s="21" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -5181,17 +5211,17 @@
           <t>A cartridge filter for hot tubs and swim spas, measuring 26.0 cm outer diameter, 13.0 cm bottom part, and 3.8 cm inner thread. Compatible with Darlly SC779 and 40372 codes, it captures dirt, grease, and fine particles to keep water clean.</t>
         </is>
       </c>
-      <c r="D2" s="30" t="inlineStr">
+      <c r="D2" s="32" t="inlineStr">
         <is>
           <t>Rising Dragon</t>
         </is>
       </c>
-      <c r="E2" s="30" t="inlineStr">
+      <c r="E2" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F2" s="30" t="inlineStr">
+      <c r="F2" s="32" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5201,71 +5231,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H2" s="30" t="inlineStr">
+      <c r="H2" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I2" s="30" t="inlineStr">
+      <c r="I2" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J2" s="30" t="inlineStr">
+      <c r="J2" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K2" s="30" t="inlineStr">
+      <c r="K2" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L2" s="30" t="inlineStr">
+      <c r="L2" s="32" t="inlineStr">
         <is>
           <t>RIS-FIL-2406</t>
         </is>
       </c>
-      <c r="M2" s="31" t="inlineStr">
+      <c r="M2" s="33" t="inlineStr">
         <is>
           <t>700175992406</t>
         </is>
       </c>
-      <c r="N2" s="32" t="inlineStr"/>
-      <c r="O2" s="32" t="inlineStr"/>
-      <c r="P2" s="32" t="inlineStr"/>
-      <c r="Q2" s="30" t="inlineStr">
+      <c r="N2" s="34" t="inlineStr"/>
+      <c r="O2" s="34" t="inlineStr"/>
+      <c r="P2" s="34" t="inlineStr"/>
+      <c r="Q2" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R2" s="30" t="inlineStr">
+      <c r="R2" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S2" s="30" t="inlineStr">
+      <c r="S2" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T2" s="30" t="inlineStr">
+      <c r="T2" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U2" s="30" t="inlineStr"/>
-      <c r="V2" s="30" t="inlineStr">
+      <c r="U2" s="32" t="inlineStr"/>
+      <c r="V2" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W2" s="30" t="inlineStr">
+      <c r="W2" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X2" s="30" t="inlineStr">
+      <c r="X2" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5275,7 +5305,7 @@
           <t>https://www.spa-components.com/user/shop/big/1473-1_filter-cartridge-sc779-rising-dragon-plastics--eago-whirlpools.jpg?ff=1&amp;x=1024&amp;y=768&amp;q=85&amp;ts=6720c4a0&amp;sg=161563f2</t>
         </is>
       </c>
-      <c r="Z2" s="30" t="inlineStr">
+      <c r="Z2" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5285,7 +5315,7 @@
           <t>Filter Cartridge SC779 - Rising Dragon Plastics, EAGO Whirlpools - Spa Components</t>
         </is>
       </c>
-      <c r="AB2" s="30" t="inlineStr">
+      <c r="AB2" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5297,10 +5327,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF2" s="30" t="inlineStr"/>
-      <c r="AG2" s="30" t="inlineStr"/>
-      <c r="AH2" s="30" t="inlineStr"/>
-      <c r="AI2" s="30" t="inlineStr"/>
+      <c r="AF2" s="32" t="inlineStr"/>
+      <c r="AG2" s="32" t="inlineStr"/>
+      <c r="AH2" s="32" t="inlineStr"/>
+      <c r="AI2" s="32" t="inlineStr"/>
     </row>
     <row r="3" ht="62" customHeight="1">
       <c r="A3" s="19" t="inlineStr">
@@ -5318,13 +5348,13 @@
           <t>A twin pack of Size II replacement filter cartridges measuring 10.6 x 13.6 cm, designed for compatible pool and spa filtration systems. The fine lamellar structure delivers thorough water cleaning and the cartridges are easy to rinse clean.</t>
         </is>
       </c>
-      <c r="D3" s="30" t="inlineStr"/>
-      <c r="E3" s="30" t="inlineStr">
+      <c r="D3" s="32" t="inlineStr"/>
+      <c r="E3" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F3" s="30" t="inlineStr">
+      <c r="F3" s="32" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5334,71 +5364,71 @@
           <t>filters, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H3" s="30" t="inlineStr">
+      <c r="H3" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I3" s="30" t="inlineStr">
+      <c r="I3" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J3" s="30" t="inlineStr">
+      <c r="J3" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K3" s="30" t="inlineStr">
+      <c r="K3" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L3" s="30" t="inlineStr">
+      <c r="L3" s="32" t="inlineStr">
         <is>
           <t>GEN-FIL-3615</t>
         </is>
       </c>
-      <c r="M3" s="31" t="inlineStr">
+      <c r="M3" s="33" t="inlineStr">
         <is>
           <t>6941607353615</t>
         </is>
       </c>
-      <c r="N3" s="32" t="inlineStr"/>
-      <c r="O3" s="32" t="inlineStr"/>
-      <c r="P3" s="32" t="inlineStr"/>
-      <c r="Q3" s="30" t="inlineStr">
+      <c r="N3" s="34" t="inlineStr"/>
+      <c r="O3" s="34" t="inlineStr"/>
+      <c r="P3" s="34" t="inlineStr"/>
+      <c r="Q3" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R3" s="30" t="inlineStr">
+      <c r="R3" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S3" s="30" t="inlineStr">
+      <c r="S3" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T3" s="30" t="inlineStr">
+      <c r="T3" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U3" s="30" t="inlineStr"/>
-      <c r="V3" s="30" t="inlineStr">
+      <c r="U3" s="32" t="inlineStr"/>
+      <c r="V3" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W3" s="30" t="inlineStr">
+      <c r="W3" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X3" s="30" t="inlineStr">
+      <c r="X3" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5408,7 +5438,7 @@
           <t>https://www.bestwaystore.de/media/c6/f8/ba/1756384660/6941607353615-main-jpg.jpg?ts=1756384660</t>
         </is>
       </c>
-      <c r="Z3" s="30" t="inlineStr">
+      <c r="Z3" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5418,7 +5448,7 @@
           <t>Filter cartridge Size II double pack, 10.6 x 13.6 cm | 58094_26</t>
         </is>
       </c>
-      <c r="AB3" s="30" t="inlineStr">
+      <c r="AB3" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5430,14 +5460,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF3" s="30" t="inlineStr"/>
-      <c r="AG3" s="30" t="inlineStr"/>
-      <c r="AH3" s="30" t="inlineStr">
+      <c r="AF3" s="32" t="inlineStr"/>
+      <c r="AG3" s="32" t="inlineStr"/>
+      <c r="AH3" s="32" t="inlineStr">
         <is>
           <t>10.6cm</t>
         </is>
       </c>
-      <c r="AI3" s="30" t="inlineStr">
+      <c r="AI3" s="32" t="inlineStr">
         <is>
           <t>13.6cm</t>
         </is>
@@ -5459,17 +5489,17 @@
           <t>A single Flowclear Size 3 replacement filter cartridge for compatible Bestway pool filtration systems, featuring a fine lamellar structure that traps deposits and dirt effectively. Easy to clean and straightforward to swap out when routine maintenance is due.</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>Bestway</t>
         </is>
       </c>
-      <c r="E4" s="30" t="inlineStr">
+      <c r="E4" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F4" s="30" t="inlineStr">
+      <c r="F4" s="32" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5479,71 +5509,71 @@
           <t>filters, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H4" s="30" t="inlineStr">
+      <c r="H4" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I4" s="30" t="inlineStr">
+      <c r="I4" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J4" s="30" t="inlineStr">
+      <c r="J4" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K4" s="30" t="inlineStr">
+      <c r="K4" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L4" s="30" t="inlineStr">
+      <c r="L4" s="32" t="inlineStr">
         <is>
           <t>BES-FIL-3592</t>
         </is>
       </c>
-      <c r="M4" s="31" t="inlineStr">
+      <c r="M4" s="33" t="inlineStr">
         <is>
           <t>6941607353592</t>
         </is>
       </c>
-      <c r="N4" s="32" t="inlineStr"/>
-      <c r="O4" s="32" t="inlineStr"/>
-      <c r="P4" s="32" t="inlineStr"/>
-      <c r="Q4" s="30" t="inlineStr">
+      <c r="N4" s="34" t="inlineStr"/>
+      <c r="O4" s="34" t="inlineStr"/>
+      <c r="P4" s="34" t="inlineStr"/>
+      <c r="Q4" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R4" s="30" t="inlineStr">
+      <c r="R4" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S4" s="30" t="inlineStr">
+      <c r="S4" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T4" s="30" t="inlineStr">
+      <c r="T4" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U4" s="30" t="inlineStr"/>
-      <c r="V4" s="30" t="inlineStr">
+      <c r="U4" s="32" t="inlineStr"/>
+      <c r="V4" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W4" s="30" t="inlineStr">
+      <c r="W4" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X4" s="30" t="inlineStr">
+      <c r="X4" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5553,7 +5583,7 @@
           <t>https://ap.nice-cdn.com/upload/image/product/large/default/bestway-flowclear-filter-cartridge-size-3-1-item-638140-en.jpg</t>
         </is>
       </c>
-      <c r="Z4" s="30" t="inlineStr">
+      <c r="Z4" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5563,7 +5593,7 @@
           <t>Bestway Flowclear™ Filter Cartridge Size 3, 1 item</t>
         </is>
       </c>
-      <c r="AB4" s="30" t="inlineStr">
+      <c r="AB4" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5575,10 +5605,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF4" s="30" t="inlineStr"/>
-      <c r="AG4" s="30" t="inlineStr"/>
-      <c r="AH4" s="30" t="inlineStr"/>
-      <c r="AI4" s="30" t="inlineStr"/>
+      <c r="AF4" s="32" t="inlineStr"/>
+      <c r="AG4" s="32" t="inlineStr"/>
+      <c r="AH4" s="32" t="inlineStr"/>
+      <c r="AI4" s="32" t="inlineStr"/>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
@@ -5596,17 +5626,17 @@
           <t>A two-pack of compatible hot tub and spa cartridge filters corresponding to Unicel C-4335, Pleatco PRB35-IN, and Filbur FC-2385 references. A handy spare-pair to keep on hand so your tub is never without a fresh filter.</t>
         </is>
       </c>
-      <c r="D5" s="30" t="inlineStr">
+      <c r="D5" s="32" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E5" s="30" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F5" s="30" t="inlineStr">
+      <c r="F5" s="32" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5616,71 +5646,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H5" s="30" t="inlineStr">
+      <c r="H5" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I5" s="30" t="inlineStr">
+      <c r="I5" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J5" s="30" t="inlineStr">
+      <c r="J5" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K5" s="30" t="inlineStr">
+      <c r="K5" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L5" s="30" t="inlineStr">
+      <c r="L5" s="32" t="inlineStr">
         <is>
           <t>DAR-FIL-1669</t>
         </is>
       </c>
-      <c r="M5" s="31" t="inlineStr">
+      <c r="M5" s="33" t="inlineStr">
         <is>
           <t>700175991669</t>
         </is>
       </c>
-      <c r="N5" s="32" t="inlineStr"/>
-      <c r="O5" s="32" t="inlineStr"/>
-      <c r="P5" s="32" t="inlineStr"/>
-      <c r="Q5" s="30" t="inlineStr">
+      <c r="N5" s="34" t="inlineStr"/>
+      <c r="O5" s="34" t="inlineStr"/>
+      <c r="P5" s="34" t="inlineStr"/>
+      <c r="Q5" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R5" s="30" t="inlineStr">
+      <c r="R5" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S5" s="30" t="inlineStr">
+      <c r="S5" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T5" s="30" t="inlineStr">
+      <c r="T5" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U5" s="30" t="inlineStr"/>
-      <c r="V5" s="30" t="inlineStr">
+      <c r="U5" s="32" t="inlineStr"/>
+      <c r="V5" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W5" s="30" t="inlineStr">
+      <c r="W5" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X5" s="30" t="inlineStr">
+      <c r="X5" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5690,7 +5720,7 @@
           <t>https://images.barcodelookup.com/29361/293617958-1.jpg</t>
         </is>
       </c>
-      <c r="Z5" s="30" t="inlineStr">
+      <c r="Z5" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5700,7 +5730,7 @@
           <t>Darlly Hot Tub Spa Filter SC705 40353 Compatible with Unicel C-4335 PRB35-IN Filbur FC-2385 2 Pack</t>
         </is>
       </c>
-      <c r="AB5" s="30" t="inlineStr">
+      <c r="AB5" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5712,10 +5742,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF5" s="30" t="inlineStr"/>
-      <c r="AG5" s="30" t="inlineStr"/>
-      <c r="AH5" s="30" t="inlineStr"/>
-      <c r="AI5" s="30" t="inlineStr"/>
+      <c r="AF5" s="32" t="inlineStr"/>
+      <c r="AG5" s="32" t="inlineStr"/>
+      <c r="AH5" s="32" t="inlineStr"/>
+      <c r="AI5" s="32" t="inlineStr"/>
     </row>
     <row r="6" ht="62" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -5733,13 +5763,13 @@
           <t>A single Size IV replacement filter cartridge measuring 14.2 x 25.4 cm, compatible with Bestway filter pump 58391 (9,463 l/h). Its deep-fold, fine-structure media delivers thorough water cleaning and can be rinsed clean with minimal effort.</t>
         </is>
       </c>
-      <c r="D6" s="30" t="inlineStr"/>
-      <c r="E6" s="30" t="inlineStr">
+      <c r="D6" s="32" t="inlineStr"/>
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F6" s="30" t="inlineStr">
+      <c r="F6" s="32" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5749,71 +5779,71 @@
           <t>filters, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H6" s="30" t="inlineStr">
+      <c r="H6" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I6" s="30" t="inlineStr">
+      <c r="I6" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J6" s="30" t="inlineStr">
+      <c r="J6" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K6" s="30" t="inlineStr">
+      <c r="K6" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L6" s="30" t="inlineStr">
+      <c r="L6" s="32" t="inlineStr">
         <is>
           <t>GEN-FIL-3622</t>
         </is>
       </c>
-      <c r="M6" s="31" t="inlineStr">
+      <c r="M6" s="33" t="inlineStr">
         <is>
           <t>6941607353622</t>
         </is>
       </c>
-      <c r="N6" s="32" t="inlineStr"/>
-      <c r="O6" s="32" t="inlineStr"/>
-      <c r="P6" s="32" t="inlineStr"/>
-      <c r="Q6" s="30" t="inlineStr">
+      <c r="N6" s="34" t="inlineStr"/>
+      <c r="O6" s="34" t="inlineStr"/>
+      <c r="P6" s="34" t="inlineStr"/>
+      <c r="Q6" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R6" s="30" t="inlineStr">
+      <c r="R6" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S6" s="30" t="inlineStr">
+      <c r="S6" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T6" s="30" t="inlineStr">
+      <c r="T6" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U6" s="30" t="inlineStr"/>
-      <c r="V6" s="30" t="inlineStr">
+      <c r="U6" s="32" t="inlineStr"/>
+      <c r="V6" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W6" s="30" t="inlineStr">
+      <c r="W6" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X6" s="30" t="inlineStr">
+      <c r="X6" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5823,7 +5853,7 @@
           <t>https://www.bestwaystore.de/media/53/6c/e9/1756384676/6941607353622-main-jpg.jpg?ts=1756384676</t>
         </is>
       </c>
-      <c r="Z6" s="30" t="inlineStr">
+      <c r="Z6" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5833,7 +5863,7 @@
           <t>Filter cartridge Size IV 14.2 x 25.4 cm | 58095_26</t>
         </is>
       </c>
-      <c r="AB6" s="30" t="inlineStr">
+      <c r="AB6" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5845,14 +5875,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF6" s="30" t="inlineStr"/>
-      <c r="AG6" s="30" t="inlineStr"/>
-      <c r="AH6" s="30" t="inlineStr">
+      <c r="AF6" s="32" t="inlineStr"/>
+      <c r="AG6" s="32" t="inlineStr"/>
+      <c r="AH6" s="32" t="inlineStr">
         <is>
           <t>14.2cm</t>
         </is>
       </c>
-      <c r="AI6" s="30" t="inlineStr">
+      <c r="AI6" s="32" t="inlineStr">
         <is>
           <t>25.4cm</t>
         </is>
@@ -5874,17 +5904,17 @@
           <t>A pair of Darlly spa filter cartridges in the SC726 reference, also cross-referenced as Unicel C-4401 and Pleatco PRB17.5SF PR. Buying in pairs means a fresh replacement is always ready when it is time to swap.</t>
         </is>
       </c>
-      <c r="D7" s="30" t="inlineStr">
+      <c r="D7" s="32" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E7" s="30" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F7" s="30" t="inlineStr">
+      <c r="F7" s="32" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5894,71 +5924,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H7" s="30" t="inlineStr">
+      <c r="H7" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I7" s="30" t="inlineStr">
+      <c r="I7" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J7" s="30" t="inlineStr">
+      <c r="J7" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K7" s="30" t="inlineStr">
+      <c r="K7" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L7" s="30" t="inlineStr">
+      <c r="L7" s="32" t="inlineStr">
         <is>
           <t>DAR-FIL-1874</t>
         </is>
       </c>
-      <c r="M7" s="31" t="inlineStr">
+      <c r="M7" s="33" t="inlineStr">
         <is>
           <t>700175991874</t>
         </is>
       </c>
-      <c r="N7" s="32" t="inlineStr"/>
-      <c r="O7" s="32" t="inlineStr"/>
-      <c r="P7" s="32" t="inlineStr"/>
-      <c r="Q7" s="30" t="inlineStr">
+      <c r="N7" s="34" t="inlineStr"/>
+      <c r="O7" s="34" t="inlineStr"/>
+      <c r="P7" s="34" t="inlineStr"/>
+      <c r="Q7" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R7" s="30" t="inlineStr">
+      <c r="R7" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S7" s="30" t="inlineStr">
+      <c r="S7" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T7" s="30" t="inlineStr">
+      <c r="T7" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U7" s="30" t="inlineStr"/>
-      <c r="V7" s="30" t="inlineStr">
+      <c r="U7" s="32" t="inlineStr"/>
+      <c r="V7" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W7" s="30" t="inlineStr">
+      <c r="W7" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X7" s="30" t="inlineStr">
+      <c r="X7" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5968,7 +5998,7 @@
           <t>https://images.barcodelookup.com/4378/43786454-1.jpg</t>
         </is>
       </c>
-      <c r="Z7" s="30" t="inlineStr">
+      <c r="Z7" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5978,7 +6008,7 @@
           <t>Darlly Spa Filter C-4401, PRB17.5SF PR, SC726 (Pair)</t>
         </is>
       </c>
-      <c r="AB7" s="30" t="inlineStr">
+      <c r="AB7" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5990,10 +6020,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF7" s="30" t="inlineStr"/>
-      <c r="AG7" s="30" t="inlineStr"/>
-      <c r="AH7" s="30" t="inlineStr"/>
-      <c r="AI7" s="30" t="inlineStr"/>
+      <c r="AF7" s="32" t="inlineStr"/>
+      <c r="AG7" s="32" t="inlineStr"/>
+      <c r="AH7" s="32" t="inlineStr"/>
+      <c r="AI7" s="32" t="inlineStr"/>
     </row>
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -6011,17 +6041,17 @@
           <t>A replacement spa filter cartridge compatible with Arctic, Beachcomber, Canadian, Hydropool and Jacuzzi spas, sold under cross-reference codes including Unicel C-4950, Pleatco PRB50-IN and Darlly 40506. It keeps hot tub water clean by trapping debris and particles as water cycles through the filtration system.</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="D8" s="32" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F8" s="30" t="inlineStr">
+      <c r="F8" s="32" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6031,71 +6061,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H8" s="30" t="inlineStr">
+      <c r="H8" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I8" s="30" t="inlineStr">
+      <c r="I8" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J8" s="30" t="inlineStr">
+      <c r="J8" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K8" s="30" t="inlineStr">
+      <c r="K8" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L8" s="30" t="inlineStr">
+      <c r="L8" s="32" t="inlineStr">
         <is>
           <t>DAR-FIL-1676</t>
         </is>
       </c>
-      <c r="M8" s="31" t="inlineStr">
+      <c r="M8" s="33" t="inlineStr">
         <is>
           <t>700175991676</t>
         </is>
       </c>
-      <c r="N8" s="32" t="inlineStr"/>
-      <c r="O8" s="32" t="inlineStr"/>
-      <c r="P8" s="32" t="inlineStr"/>
-      <c r="Q8" s="30" t="inlineStr">
+      <c r="N8" s="34" t="inlineStr"/>
+      <c r="O8" s="34" t="inlineStr"/>
+      <c r="P8" s="34" t="inlineStr"/>
+      <c r="Q8" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R8" s="30" t="inlineStr">
+      <c r="R8" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S8" s="30" t="inlineStr">
+      <c r="S8" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T8" s="30" t="inlineStr">
+      <c r="T8" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U8" s="30" t="inlineStr"/>
-      <c r="V8" s="30" t="inlineStr">
+      <c r="U8" s="32" t="inlineStr"/>
+      <c r="V8" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W8" s="30" t="inlineStr">
+      <c r="W8" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X8" s="30" t="inlineStr">
+      <c r="X8" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6105,7 +6135,7 @@
           <t>https://images.barcodelookup.com/4469/44699532-1.jpg</t>
         </is>
       </c>
-      <c r="Z8" s="30" t="inlineStr">
+      <c r="Z8" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6115,7 +6145,7 @@
           <t>Hot Tub Filter Unicel C4950 / C-4950 50' Spa Cartridge Pleatco PRB501N Darlly 40506 for Arctic, Beachcomber, Canadian,…</t>
         </is>
       </c>
-      <c r="AB8" s="30" t="inlineStr">
+      <c r="AB8" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6127,10 +6157,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF8" s="30" t="inlineStr"/>
-      <c r="AG8" s="30" t="inlineStr"/>
-      <c r="AH8" s="30" t="inlineStr"/>
-      <c r="AI8" s="30" t="inlineStr"/>
+      <c r="AF8" s="32" t="inlineStr"/>
+      <c r="AG8" s="32" t="inlineStr"/>
+      <c r="AH8" s="32" t="inlineStr"/>
+      <c r="AI8" s="32" t="inlineStr"/>
     </row>
     <row r="9" ht="76" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -6148,13 +6178,13 @@
           <t>A square inflatable hot tub for up to four people, with an overall outer diameter of 2.45 m and a structure measuring 1.75 x 1.75 x 0.71 m, built from high-resistance polyester for good rigidity and durability. The packaged weight is 64.92 kg, so you will want a helper on delivery day.</t>
         </is>
       </c>
-      <c r="D9" s="30" t="inlineStr"/>
-      <c r="E9" s="30" t="inlineStr">
+      <c r="D9" s="32" t="inlineStr"/>
+      <c r="E9" s="32" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F9" s="30" t="inlineStr">
+      <c r="F9" s="32" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -6164,75 +6194,75 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H9" s="30" t="inlineStr">
+      <c r="H9" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I9" s="30" t="inlineStr">
+      <c r="I9" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J9" s="30" t="inlineStr">
+      <c r="J9" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K9" s="30" t="inlineStr">
+      <c r="K9" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L9" s="30" t="inlineStr">
+      <c r="L9" s="32" t="inlineStr">
         <is>
           <t>GEN-SPA-3395</t>
         </is>
       </c>
-      <c r="M9" s="31" t="inlineStr">
+      <c r="M9" s="33" t="inlineStr">
         <is>
           <t>6941057423395</t>
         </is>
       </c>
-      <c r="N9" s="32" t="inlineStr"/>
-      <c r="O9" s="32" t="inlineStr"/>
-      <c r="P9" s="32" t="inlineStr"/>
-      <c r="Q9" s="30" t="inlineStr">
+      <c r="N9" s="34" t="inlineStr"/>
+      <c r="O9" s="34" t="inlineStr"/>
+      <c r="P9" s="34" t="inlineStr"/>
+      <c r="Q9" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R9" s="30" t="inlineStr">
+      <c r="R9" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S9" s="30" t="inlineStr">
+      <c r="S9" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T9" s="30" t="inlineStr">
+      <c r="T9" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U9" s="30" t="inlineStr">
+      <c r="U9" s="32" t="inlineStr">
         <is>
           <t>64920</t>
         </is>
       </c>
-      <c r="V9" s="30" t="inlineStr">
+      <c r="V9" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W9" s="30" t="inlineStr">
+      <c r="W9" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X9" s="30" t="inlineStr">
+      <c r="X9" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6242,7 +6272,7 @@
           <t>https://media.intex.fr/7743-large_default_x2/28464ex-spa-gonflable-calacatta-4-places.jpg</t>
         </is>
       </c>
-      <c r="Z9" s="30" t="inlineStr">
+      <c r="Z9" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6252,7 +6282,7 @@
           <t>Calacatta 4-person inflatable spa</t>
         </is>
       </c>
-      <c r="AB9" s="30" t="inlineStr">
+      <c r="AB9" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6264,18 +6294,18 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF9" s="30" t="inlineStr"/>
-      <c r="AG9" s="30" t="inlineStr">
+      <c r="AF9" s="32" t="inlineStr"/>
+      <c r="AG9" s="32" t="inlineStr">
         <is>
           <t>175.0cm</t>
         </is>
       </c>
-      <c r="AH9" s="30" t="inlineStr">
+      <c r="AH9" s="32" t="inlineStr">
         <is>
           <t>175.0cm</t>
         </is>
       </c>
-      <c r="AI9" s="30" t="inlineStr">
+      <c r="AI9" s="32" t="inlineStr">
         <is>
           <t>71.0cm</t>
         </is>
@@ -6297,17 +6327,17 @@
           <t>A 3.0 kg tub of hth stabiliser granules for outdoor swimming pools, used to protect chlorine from UV degradation and extend its effectiveness. A reliable way to get more mileage from your sanitiser on sunny days.</t>
         </is>
       </c>
-      <c r="D10" s="30" t="inlineStr">
+      <c r="D10" s="32" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E10" s="30" t="inlineStr">
+      <c r="E10" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F10" s="30" t="inlineStr">
+      <c r="F10" s="32" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -6317,75 +6347,75 @@
           <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H10" s="30" t="inlineStr">
+      <c r="H10" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I10" s="30" t="inlineStr">
+      <c r="I10" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J10" s="30" t="inlineStr">
+      <c r="J10" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K10" s="30" t="inlineStr">
+      <c r="K10" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L10" s="30" t="inlineStr">
+      <c r="L10" s="32" t="inlineStr">
         <is>
           <t>HTH-CHM-5716</t>
         </is>
       </c>
-      <c r="M10" s="31" t="inlineStr">
+      <c r="M10" s="33" t="inlineStr">
         <is>
           <t>3521686005716</t>
         </is>
       </c>
-      <c r="N10" s="32" t="inlineStr"/>
-      <c r="O10" s="32" t="inlineStr"/>
-      <c r="P10" s="32" t="inlineStr"/>
-      <c r="Q10" s="30" t="inlineStr">
+      <c r="N10" s="34" t="inlineStr"/>
+      <c r="O10" s="34" t="inlineStr"/>
+      <c r="P10" s="34" t="inlineStr"/>
+      <c r="Q10" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R10" s="30" t="inlineStr">
+      <c r="R10" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S10" s="30" t="inlineStr">
+      <c r="S10" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T10" s="30" t="inlineStr">
+      <c r="T10" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U10" s="30" t="inlineStr">
+      <c r="U10" s="32" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="V10" s="30" t="inlineStr">
+      <c r="V10" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W10" s="30" t="inlineStr">
+      <c r="W10" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X10" s="30" t="inlineStr">
+      <c r="X10" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6395,7 +6425,7 @@
           <t>https://images.barcodelookup.com/12027/120276177-1.jpg</t>
         </is>
       </c>
-      <c r="Z10" s="30" t="inlineStr">
+      <c r="Z10" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6405,7 +6435,7 @@
           <t>Hth Stabilizer Granulat 3,0 Kg</t>
         </is>
       </c>
-      <c r="AB10" s="30" t="inlineStr">
+      <c r="AB10" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6417,10 +6447,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF10" s="30" t="inlineStr"/>
-      <c r="AG10" s="30" t="inlineStr"/>
-      <c r="AH10" s="30" t="inlineStr"/>
-      <c r="AI10" s="30" t="inlineStr"/>
+      <c r="AF10" s="32" t="inlineStr"/>
+      <c r="AG10" s="32" t="inlineStr"/>
+      <c r="AH10" s="32" t="inlineStr"/>
+      <c r="AI10" s="32" t="inlineStr"/>
     </row>
     <row r="11" ht="62" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -6438,17 +6468,17 @@
           <t>A 1-litre bottle of hth Spa Antikalk, formulated to prevent and remove limescale in spa and hot tub water. Keeping scale under control helps protect internal components and maintain water clarity.</t>
         </is>
       </c>
-      <c r="D11" s="30" t="inlineStr">
+      <c r="D11" s="32" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E11" s="30" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F11" s="30" t="inlineStr">
+      <c r="F11" s="32" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -6458,71 +6488,71 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H11" s="30" t="inlineStr">
+      <c r="H11" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I11" s="30" t="inlineStr">
+      <c r="I11" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J11" s="30" t="inlineStr">
+      <c r="J11" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K11" s="30" t="inlineStr">
+      <c r="K11" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L11" s="30" t="inlineStr">
+      <c r="L11" s="32" t="inlineStr">
         <is>
           <t>HTH-SPA-0194</t>
         </is>
       </c>
-      <c r="M11" s="31" t="inlineStr">
+      <c r="M11" s="33" t="inlineStr">
         <is>
           <t>3521684700194</t>
         </is>
       </c>
-      <c r="N11" s="32" t="inlineStr"/>
-      <c r="O11" s="32" t="inlineStr"/>
-      <c r="P11" s="32" t="inlineStr"/>
-      <c r="Q11" s="30" t="inlineStr">
+      <c r="N11" s="34" t="inlineStr"/>
+      <c r="O11" s="34" t="inlineStr"/>
+      <c r="P11" s="34" t="inlineStr"/>
+      <c r="Q11" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R11" s="30" t="inlineStr">
+      <c r="R11" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S11" s="30" t="inlineStr">
+      <c r="S11" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T11" s="30" t="inlineStr">
+      <c r="T11" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U11" s="30" t="inlineStr"/>
-      <c r="V11" s="30" t="inlineStr">
+      <c r="U11" s="32" t="inlineStr"/>
+      <c r="V11" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W11" s="30" t="inlineStr">
+      <c r="W11" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X11" s="30" t="inlineStr">
+      <c r="X11" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6532,7 +6562,7 @@
           <t>https://www.north-spa.de/wp-content/uploads/2025/02/Produktbild-1-hth-SPA-ANTIKALK-1-l-3521684700194-360x360.jpg</t>
         </is>
       </c>
-      <c r="Z11" s="30" t="inlineStr">
+      <c r="Z11" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6542,7 +6572,7 @@
           <t>1 l - hth® Spa ANTIKALK</t>
         </is>
       </c>
-      <c r="AB11" s="30" t="inlineStr">
+      <c r="AB11" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6554,10 +6584,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF11" s="30" t="inlineStr"/>
-      <c r="AG11" s="30" t="inlineStr"/>
-      <c r="AH11" s="30" t="inlineStr"/>
-      <c r="AI11" s="30" t="inlineStr"/>
+      <c r="AF11" s="32" t="inlineStr"/>
+      <c r="AG11" s="32" t="inlineStr"/>
+      <c r="AH11" s="32" t="inlineStr"/>
+      <c r="AI11" s="32" t="inlineStr"/>
     </row>
     <row r="12" ht="62" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -6575,13 +6605,13 @@
           <t>A round, olive-green inflatable spa designed to seat up to eight people comfortably, with a maximum water temperature of 40°C. Five accessories are included in the box, so there is plenty to get started with straight away.</t>
         </is>
       </c>
-      <c r="D12" s="30" t="inlineStr"/>
-      <c r="E12" s="30" t="inlineStr">
+      <c r="D12" s="32" t="inlineStr"/>
+      <c r="E12" s="32" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F12" s="30" t="inlineStr">
+      <c r="F12" s="32" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -6591,71 +6621,71 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H12" s="30" t="inlineStr">
+      <c r="H12" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I12" s="30" t="inlineStr">
+      <c r="I12" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J12" s="30" t="inlineStr">
+      <c r="J12" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K12" s="30" t="inlineStr">
+      <c r="K12" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L12" s="30" t="inlineStr">
+      <c r="L12" s="32" t="inlineStr">
         <is>
           <t>GEN-SPA-9274</t>
         </is>
       </c>
-      <c r="M12" s="31" t="inlineStr">
+      <c r="M12" s="33" t="inlineStr">
         <is>
           <t>6941057429274</t>
         </is>
       </c>
-      <c r="N12" s="32" t="inlineStr"/>
-      <c r="O12" s="32" t="inlineStr"/>
-      <c r="P12" s="32" t="inlineStr"/>
-      <c r="Q12" s="30" t="inlineStr">
+      <c r="N12" s="34" t="inlineStr"/>
+      <c r="O12" s="34" t="inlineStr"/>
+      <c r="P12" s="34" t="inlineStr"/>
+      <c r="Q12" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R12" s="30" t="inlineStr">
+      <c r="R12" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S12" s="30" t="inlineStr">
+      <c r="S12" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T12" s="30" t="inlineStr">
+      <c r="T12" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U12" s="30" t="inlineStr"/>
-      <c r="V12" s="30" t="inlineStr">
+      <c r="U12" s="32" t="inlineStr"/>
+      <c r="V12" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W12" s="30" t="inlineStr">
+      <c r="W12" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X12" s="30" t="inlineStr">
+      <c r="X12" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6665,7 +6695,7 @@
           <t>https://media.intex.fr/11990-large_default_x2/28412np-spa-gonflable-olive-8-places.jpg</t>
         </is>
       </c>
-      <c r="Z12" s="30" t="inlineStr">
+      <c r="Z12" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6675,7 +6705,7 @@
           <t>Olive 8-person inflatable spa</t>
         </is>
       </c>
-      <c r="AB12" s="30" t="inlineStr">
+      <c r="AB12" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6687,10 +6717,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF12" s="30" t="inlineStr"/>
-      <c r="AG12" s="30" t="inlineStr"/>
-      <c r="AH12" s="30" t="inlineStr"/>
-      <c r="AI12" s="30" t="inlineStr"/>
+      <c r="AF12" s="32" t="inlineStr"/>
+      <c r="AG12" s="32" t="inlineStr"/>
+      <c r="AH12" s="32" t="inlineStr"/>
+      <c r="AI12" s="32" t="inlineStr"/>
     </row>
     <row r="13" ht="62" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -6708,17 +6738,17 @@
           <t>A Darlly SC750 replacement cartridge filter compatible with Arctic, Fonteyn, Rota, and Strong Spa hot tubs, among others. A straightforward like-for-like swap to keep your spa water flowing clean.</t>
         </is>
       </c>
-      <c r="D13" s="30" t="inlineStr">
+      <c r="D13" s="32" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E13" s="30" t="inlineStr">
+      <c r="E13" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F13" s="30" t="inlineStr">
+      <c r="F13" s="32" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6728,71 +6758,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H13" s="30" t="inlineStr">
+      <c r="H13" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I13" s="30" t="inlineStr">
+      <c r="I13" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J13" s="30" t="inlineStr">
+      <c r="J13" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K13" s="30" t="inlineStr">
+      <c r="K13" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L13" s="30" t="inlineStr">
+      <c r="L13" s="32" t="inlineStr">
         <is>
           <t>DAR-FIL-2116</t>
         </is>
       </c>
-      <c r="M13" s="31" t="inlineStr">
+      <c r="M13" s="33" t="inlineStr">
         <is>
           <t>700175992116</t>
         </is>
       </c>
-      <c r="N13" s="32" t="inlineStr"/>
-      <c r="O13" s="32" t="inlineStr"/>
-      <c r="P13" s="32" t="inlineStr"/>
-      <c r="Q13" s="30" t="inlineStr">
+      <c r="N13" s="34" t="inlineStr"/>
+      <c r="O13" s="34" t="inlineStr"/>
+      <c r="P13" s="34" t="inlineStr"/>
+      <c r="Q13" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R13" s="30" t="inlineStr">
+      <c r="R13" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S13" s="30" t="inlineStr">
+      <c r="S13" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T13" s="30" t="inlineStr">
+      <c r="T13" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U13" s="30" t="inlineStr"/>
-      <c r="V13" s="30" t="inlineStr">
+      <c r="U13" s="32" t="inlineStr"/>
+      <c r="V13" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W13" s="30" t="inlineStr">
+      <c r="W13" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X13" s="30" t="inlineStr">
+      <c r="X13" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6802,7 +6832,7 @@
           <t>https://images.barcodelookup.com/29338/293384728-1.jpg</t>
         </is>
       </c>
-      <c r="Z13" s="30" t="inlineStr">
+      <c r="Z13" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6812,7 +6842,7 @@
           <t>SC750 Filter replacement filter lamellar filter Arctic Fonteyn Rota Strong Spa - Darlly</t>
         </is>
       </c>
-      <c r="AB13" s="30" t="inlineStr">
+      <c r="AB13" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6824,10 +6854,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF13" s="30" t="inlineStr"/>
-      <c r="AG13" s="30" t="inlineStr"/>
-      <c r="AH13" s="30" t="inlineStr"/>
-      <c r="AI13" s="30" t="inlineStr"/>
+      <c r="AF13" s="32" t="inlineStr"/>
+      <c r="AG13" s="32" t="inlineStr"/>
+      <c r="AH13" s="32" t="inlineStr"/>
+      <c r="AI13" s="32" t="inlineStr"/>
     </row>
     <row r="14" ht="62" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -6845,17 +6875,17 @@
           <t>SpaBalancer Clean and Refresh is a spa water treatment product supplied with a sprayer for easy application. It is designed to keep spa water fresh and clean as part of a regular maintenance routine.</t>
         </is>
       </c>
-      <c r="D14" s="30" t="inlineStr">
+      <c r="D14" s="32" t="inlineStr">
         <is>
           <t>SpaBalancer</t>
         </is>
       </c>
-      <c r="E14" s="30" t="inlineStr">
+      <c r="E14" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F14" s="30" t="inlineStr">
+      <c r="F14" s="32" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -6865,71 +6895,71 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H14" s="30" t="inlineStr">
+      <c r="H14" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I14" s="30" t="inlineStr">
+      <c r="I14" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J14" s="30" t="inlineStr">
+      <c r="J14" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K14" s="30" t="inlineStr">
+      <c r="K14" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L14" s="30" t="inlineStr">
+      <c r="L14" s="32" t="inlineStr">
         <is>
           <t>SPA-CLN-0117</t>
         </is>
       </c>
-      <c r="M14" s="31" t="inlineStr">
+      <c r="M14" s="33" t="inlineStr">
         <is>
           <t>4260374980117</t>
         </is>
       </c>
-      <c r="N14" s="32" t="inlineStr"/>
-      <c r="O14" s="32" t="inlineStr"/>
-      <c r="P14" s="32" t="inlineStr"/>
-      <c r="Q14" s="30" t="inlineStr">
+      <c r="N14" s="34" t="inlineStr"/>
+      <c r="O14" s="34" t="inlineStr"/>
+      <c r="P14" s="34" t="inlineStr"/>
+      <c r="Q14" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R14" s="30" t="inlineStr">
+      <c r="R14" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S14" s="30" t="inlineStr">
+      <c r="S14" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T14" s="30" t="inlineStr">
+      <c r="T14" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U14" s="30" t="inlineStr"/>
-      <c r="V14" s="30" t="inlineStr">
+      <c r="U14" s="32" t="inlineStr"/>
+      <c r="V14" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W14" s="30" t="inlineStr">
+      <c r="W14" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X14" s="30" t="inlineStr">
+      <c r="X14" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6939,7 +6969,7 @@
           <t>https://www.spabalancer.ch/media/ae/20/d2/1728651174/sb111_clean-refresh_freigestellt.png?ts=1777362921</t>
         </is>
       </c>
-      <c r="Z14" s="30" t="inlineStr">
+      <c r="Z14" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6949,7 +6979,7 @@
           <t>SpaBalancer Clean &amp; Refresh (+ sprayer)</t>
         </is>
       </c>
-      <c r="AB14" s="30" t="inlineStr">
+      <c r="AB14" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6961,10 +6991,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF14" s="30" t="inlineStr"/>
-      <c r="AG14" s="30" t="inlineStr"/>
-      <c r="AH14" s="30" t="inlineStr"/>
-      <c r="AI14" s="30" t="inlineStr"/>
+      <c r="AF14" s="32" t="inlineStr"/>
+      <c r="AG14" s="32" t="inlineStr"/>
+      <c r="AH14" s="32" t="inlineStr"/>
+      <c r="AI14" s="32" t="inlineStr"/>
     </row>
     <row r="15" ht="62" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -6982,17 +7012,17 @@
           <t>A pack of 500 DPD 1 reagent tablets for use with the Water-ID photometer, measuring free chlorine levels in pool or spa water. Having a full pack to hand means you will not run short mid-season.</t>
         </is>
       </c>
-      <c r="D15" s="30" t="inlineStr">
+      <c r="D15" s="32" t="inlineStr">
         <is>
           <t>Water-i.d.</t>
         </is>
       </c>
-      <c r="E15" s="30" t="inlineStr">
+      <c r="E15" s="32" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F15" s="30" t="inlineStr">
+      <c r="F15" s="32" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -7002,79 +7032,79 @@
           <t>test-measure, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H15" s="30" t="inlineStr">
+      <c r="H15" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I15" s="30" t="inlineStr">
+      <c r="I15" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J15" s="30" t="inlineStr">
+      <c r="J15" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K15" s="30" t="inlineStr">
+      <c r="K15" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L15" s="30" t="inlineStr">
+      <c r="L15" s="32" t="inlineStr">
         <is>
           <t>WAT-TST-1702</t>
         </is>
       </c>
-      <c r="M15" s="31" t="inlineStr">
+      <c r="M15" s="33" t="inlineStr">
         <is>
           <t>4260431461702</t>
         </is>
       </c>
-      <c r="N15" s="32" t="inlineStr"/>
-      <c r="O15" s="32" t="inlineStr"/>
-      <c r="P15" s="32" t="inlineStr"/>
-      <c r="Q15" s="30" t="inlineStr">
+      <c r="N15" s="34" t="inlineStr"/>
+      <c r="O15" s="34" t="inlineStr"/>
+      <c r="P15" s="34" t="inlineStr"/>
+      <c r="Q15" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R15" s="30" t="inlineStr">
+      <c r="R15" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S15" s="30" t="inlineStr">
+      <c r="S15" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T15" s="30" t="inlineStr">
+      <c r="T15" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U15" s="30" t="inlineStr"/>
-      <c r="V15" s="30" t="inlineStr">
+      <c r="U15" s="32" t="inlineStr"/>
+      <c r="V15" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W15" s="30" t="inlineStr">
+      <c r="W15" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X15" s="30" t="inlineStr">
+      <c r="X15" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y15" s="19" t="inlineStr"/>
-      <c r="Z15" s="30" t="inlineStr"/>
+      <c r="Z15" s="32" t="inlineStr"/>
       <c r="AA15" s="19" t="inlineStr"/>
-      <c r="AB15" s="30" t="inlineStr">
+      <c r="AB15" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7086,10 +7116,10 @@
           <t>Pool Accessories</t>
         </is>
       </c>
-      <c r="AF15" s="30" t="inlineStr"/>
-      <c r="AG15" s="30" t="inlineStr"/>
-      <c r="AH15" s="30" t="inlineStr"/>
-      <c r="AI15" s="30" t="inlineStr"/>
+      <c r="AF15" s="32" t="inlineStr"/>
+      <c r="AG15" s="32" t="inlineStr"/>
+      <c r="AH15" s="32" t="inlineStr"/>
+      <c r="AI15" s="32" t="inlineStr"/>
     </row>
     <row r="16" ht="62" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -7107,17 +7137,17 @@
           <t>A pack of 500 Phenol Red reagent tablets compatible with the Water-ID photometer, used for measuring pH levels in pool or spa water. Accurate pH readings are the foundation of balanced, comfortable water.</t>
         </is>
       </c>
-      <c r="D16" s="30" t="inlineStr">
+      <c r="D16" s="32" t="inlineStr">
         <is>
           <t>Water-i.d.</t>
         </is>
       </c>
-      <c r="E16" s="30" t="inlineStr">
+      <c r="E16" s="32" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F16" s="30" t="inlineStr">
+      <c r="F16" s="32" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -7127,71 +7157,71 @@
           <t>test-measure, add-on, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H16" s="30" t="inlineStr">
+      <c r="H16" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I16" s="30" t="inlineStr">
+      <c r="I16" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J16" s="30" t="inlineStr">
+      <c r="J16" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K16" s="30" t="inlineStr">
+      <c r="K16" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L16" s="30" t="inlineStr">
+      <c r="L16" s="32" t="inlineStr">
         <is>
           <t>WAT-TST-1801</t>
         </is>
       </c>
-      <c r="M16" s="31" t="inlineStr">
+      <c r="M16" s="33" t="inlineStr">
         <is>
           <t>4260431461801</t>
         </is>
       </c>
-      <c r="N16" s="32" t="inlineStr"/>
-      <c r="O16" s="32" t="inlineStr"/>
-      <c r="P16" s="32" t="inlineStr"/>
-      <c r="Q16" s="30" t="inlineStr">
+      <c r="N16" s="34" t="inlineStr"/>
+      <c r="O16" s="34" t="inlineStr"/>
+      <c r="P16" s="34" t="inlineStr"/>
+      <c r="Q16" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R16" s="30" t="inlineStr">
+      <c r="R16" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S16" s="30" t="inlineStr">
+      <c r="S16" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T16" s="30" t="inlineStr">
+      <c r="T16" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U16" s="30" t="inlineStr"/>
-      <c r="V16" s="30" t="inlineStr">
+      <c r="U16" s="32" t="inlineStr"/>
+      <c r="V16" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W16" s="30" t="inlineStr">
+      <c r="W16" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X16" s="30" t="inlineStr">
+      <c r="X16" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7201,7 +7231,7 @@
           <t>https://www.poolpowershop.de/media/46/63/13/1743521499/phenol-red-testtabletten-fuer-poollab-500-stk.jpg</t>
         </is>
       </c>
-      <c r="Z16" s="30" t="inlineStr">
+      <c r="Z16" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7211,7 +7241,7 @@
           <t>WATER-I.D. Water-ID Reagenzien Phenol Red Photometer 500</t>
         </is>
       </c>
-      <c r="AB16" s="30" t="inlineStr">
+      <c r="AB16" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7223,10 +7253,10 @@
           <t>Pool Accessories</t>
         </is>
       </c>
-      <c r="AF16" s="30" t="inlineStr"/>
-      <c r="AG16" s="30" t="inlineStr"/>
-      <c r="AH16" s="30" t="inlineStr"/>
-      <c r="AI16" s="30" t="inlineStr"/>
+      <c r="AF16" s="32" t="inlineStr"/>
+      <c r="AG16" s="32" t="inlineStr"/>
+      <c r="AH16" s="32" t="inlineStr"/>
+      <c r="AI16" s="32" t="inlineStr"/>
     </row>
     <row r="17" ht="62" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -7244,17 +7274,17 @@
           <t>An alkaline edge and surround cleaner in a 1-litre bottle, formulated to be gentle on pool liners, foils, and plastic surfaces. It tackles waterline grime without harming the materials it touches.</t>
         </is>
       </c>
-      <c r="D17" s="30" t="inlineStr">
+      <c r="D17" s="32" t="inlineStr">
         <is>
           <t>Cristal</t>
         </is>
       </c>
-      <c r="E17" s="30" t="inlineStr">
+      <c r="E17" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F17" s="30" t="inlineStr">
+      <c r="F17" s="32" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -7264,71 +7294,71 @@
           <t>pool, water-treatment, cleaning, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H17" s="30" t="inlineStr">
+      <c r="H17" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I17" s="30" t="inlineStr">
+      <c r="I17" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J17" s="30" t="inlineStr">
+      <c r="J17" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K17" s="30" t="inlineStr">
+      <c r="K17" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L17" s="30" t="inlineStr">
+      <c r="L17" s="32" t="inlineStr">
         <is>
           <t>CRI-CHM-5212</t>
         </is>
       </c>
-      <c r="M17" s="31" t="inlineStr">
+      <c r="M17" s="33" t="inlineStr">
         <is>
           <t>4002369155212</t>
         </is>
       </c>
-      <c r="N17" s="32" t="inlineStr"/>
-      <c r="O17" s="32" t="inlineStr"/>
-      <c r="P17" s="32" t="inlineStr"/>
-      <c r="Q17" s="30" t="inlineStr">
+      <c r="N17" s="34" t="inlineStr"/>
+      <c r="O17" s="34" t="inlineStr"/>
+      <c r="P17" s="34" t="inlineStr"/>
+      <c r="Q17" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R17" s="30" t="inlineStr">
+      <c r="R17" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S17" s="30" t="inlineStr">
+      <c r="S17" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T17" s="30" t="inlineStr">
+      <c r="T17" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U17" s="30" t="inlineStr"/>
-      <c r="V17" s="30" t="inlineStr">
+      <c r="U17" s="32" t="inlineStr"/>
+      <c r="V17" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W17" s="30" t="inlineStr">
+      <c r="W17" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X17" s="30" t="inlineStr">
+      <c r="X17" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7338,7 +7368,7 @@
           <t>https://images.barcodelookup.com/21057/210579756-1.jpg</t>
         </is>
       </c>
-      <c r="Z17" s="30" t="inlineStr">
+      <c r="Z17" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7348,7 +7378,7 @@
           <t>Cristal Poolpflege CRISTAL edge cleaner alkaline 1,0 l, (material-safe, for liners, plastic</t>
         </is>
       </c>
-      <c r="AB17" s="30" t="inlineStr">
+      <c r="AB17" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7360,10 +7390,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF17" s="30" t="inlineStr"/>
-      <c r="AG17" s="30" t="inlineStr"/>
-      <c r="AH17" s="30" t="inlineStr"/>
-      <c r="AI17" s="30" t="inlineStr"/>
+      <c r="AF17" s="32" t="inlineStr"/>
+      <c r="AG17" s="32" t="inlineStr"/>
+      <c r="AH17" s="32" t="inlineStr"/>
+      <c r="AI17" s="32" t="inlineStr"/>
     </row>
     <row r="18" ht="76" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -7381,17 +7411,17 @@
           <t>A 1-litre pool surface cleaner formulated to remove sunscreen oils and greasy residues from the water surface, designed specifically for warm Mediterranean climates and heavy swimming loads. It keeps the waterline and surface clear without harming pool materials.</t>
         </is>
       </c>
-      <c r="D18" s="30" t="inlineStr">
+      <c r="D18" s="32" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E18" s="30" t="inlineStr">
+      <c r="E18" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F18" s="30" t="inlineStr">
+      <c r="F18" s="32" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -7401,71 +7431,71 @@
           <t>pool, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H18" s="30" t="inlineStr">
+      <c r="H18" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I18" s="30" t="inlineStr">
+      <c r="I18" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J18" s="30" t="inlineStr">
+      <c r="J18" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K18" s="30" t="inlineStr">
+      <c r="K18" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L18" s="30" t="inlineStr">
+      <c r="L18" s="32" t="inlineStr">
         <is>
           <t>AQU-CLN-0223</t>
         </is>
       </c>
-      <c r="M18" s="31" t="inlineStr">
+      <c r="M18" s="33" t="inlineStr">
         <is>
           <t>5292638000223</t>
         </is>
       </c>
-      <c r="N18" s="32" t="inlineStr"/>
-      <c r="O18" s="32" t="inlineStr"/>
-      <c r="P18" s="32" t="inlineStr"/>
-      <c r="Q18" s="30" t="inlineStr">
+      <c r="N18" s="34" t="inlineStr"/>
+      <c r="O18" s="34" t="inlineStr"/>
+      <c r="P18" s="34" t="inlineStr"/>
+      <c r="Q18" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R18" s="30" t="inlineStr">
+      <c r="R18" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S18" s="30" t="inlineStr">
+      <c r="S18" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T18" s="30" t="inlineStr">
+      <c r="T18" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U18" s="30" t="inlineStr"/>
-      <c r="V18" s="30" t="inlineStr">
+      <c r="U18" s="32" t="inlineStr"/>
+      <c r="V18" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W18" s="30" t="inlineStr">
+      <c r="W18" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X18" s="30" t="inlineStr">
+      <c r="X18" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7475,7 +7505,7 @@
           <t>http://mangas.com.cy/media/products/5292638000223.jpg</t>
         </is>
       </c>
-      <c r="Z18" s="30" t="inlineStr">
+      <c r="Z18" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7485,7 +7515,7 @@
           <t>AQUALITY Pool cleaner for greasy residue 1L</t>
         </is>
       </c>
-      <c r="AB18" s="30" t="inlineStr">
+      <c r="AB18" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7497,10 +7527,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF18" s="30" t="inlineStr"/>
-      <c r="AG18" s="30" t="inlineStr"/>
-      <c r="AH18" s="30" t="inlineStr"/>
-      <c r="AI18" s="30" t="inlineStr"/>
+      <c r="AF18" s="32" t="inlineStr"/>
+      <c r="AG18" s="32" t="inlineStr"/>
+      <c r="AH18" s="32" t="inlineStr"/>
+      <c r="AI18" s="32" t="inlineStr"/>
     </row>
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
@@ -7518,17 +7548,17 @@
           <t>California Clear Blue is a super-concentrated, pH-neutral pool clarifier in a 1-litre bottle, using a cationic polymer formula to bind microscopic particles such as dust, pollen, and oils into larger clusters your filter can catch. Non-toxic and biodegradable, it is safe for sand, zeolite, and glass filtration media.</t>
         </is>
       </c>
-      <c r="D19" s="30" t="inlineStr">
+      <c r="D19" s="32" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E19" s="30" t="inlineStr">
+      <c r="E19" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F19" s="30" t="inlineStr">
+      <c r="F19" s="32" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -7538,71 +7568,71 @@
           <t>pool, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H19" s="30" t="inlineStr">
+      <c r="H19" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I19" s="30" t="inlineStr">
+      <c r="I19" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J19" s="30" t="inlineStr">
+      <c r="J19" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K19" s="30" t="inlineStr">
+      <c r="K19" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L19" s="30" t="inlineStr">
+      <c r="L19" s="32" t="inlineStr">
         <is>
           <t>AQU-CHM-0070</t>
         </is>
       </c>
-      <c r="M19" s="31" t="inlineStr">
+      <c r="M19" s="33" t="inlineStr">
         <is>
           <t>5292638000070</t>
         </is>
       </c>
-      <c r="N19" s="32" t="inlineStr"/>
-      <c r="O19" s="32" t="inlineStr"/>
-      <c r="P19" s="32" t="inlineStr"/>
-      <c r="Q19" s="30" t="inlineStr">
+      <c r="N19" s="34" t="inlineStr"/>
+      <c r="O19" s="34" t="inlineStr"/>
+      <c r="P19" s="34" t="inlineStr"/>
+      <c r="Q19" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R19" s="30" t="inlineStr">
+      <c r="R19" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S19" s="30" t="inlineStr">
+      <c r="S19" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T19" s="30" t="inlineStr">
+      <c r="T19" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U19" s="30" t="inlineStr"/>
-      <c r="V19" s="30" t="inlineStr">
+      <c r="U19" s="32" t="inlineStr"/>
+      <c r="V19" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W19" s="30" t="inlineStr">
+      <c r="W19" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X19" s="30" t="inlineStr">
+      <c r="X19" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7612,7 +7642,7 @@
           <t>https://poolservices.cy/storage/2026/05/California-Clear-Blue-1L-Aquality-2.jpeg</t>
         </is>
       </c>
-      <c r="Z19" s="30" t="inlineStr">
+      <c r="Z19" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7622,7 +7652,7 @@
           <t>Pool Clarifier California Clear Blue Aquality 1L</t>
         </is>
       </c>
-      <c r="AB19" s="30" t="inlineStr">
+      <c r="AB19" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7634,10 +7664,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF19" s="30" t="inlineStr"/>
-      <c r="AG19" s="30" t="inlineStr"/>
-      <c r="AH19" s="30" t="inlineStr"/>
-      <c r="AI19" s="30" t="inlineStr"/>
+      <c r="AF19" s="32" t="inlineStr"/>
+      <c r="AG19" s="32" t="inlineStr"/>
+      <c r="AH19" s="32" t="inlineStr"/>
+      <c r="AI19" s="32" t="inlineStr"/>
     </row>
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -7655,17 +7685,17 @@
           <t>A 1-litre tile and vinyl cleaner for pools, designed to clean pool tile surfaces and vinyl liners. It makes light work of the tidying up that keeps a pool looking its best.</t>
         </is>
       </c>
-      <c r="D20" s="30" t="inlineStr">
+      <c r="D20" s="32" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E20" s="30" t="inlineStr">
+      <c r="E20" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F20" s="30" t="inlineStr">
+      <c r="F20" s="32" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -7675,71 +7705,71 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H20" s="30" t="inlineStr">
+      <c r="H20" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I20" s="30" t="inlineStr">
+      <c r="I20" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J20" s="30" t="inlineStr">
+      <c r="J20" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K20" s="30" t="inlineStr">
+      <c r="K20" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L20" s="30" t="inlineStr">
+      <c r="L20" s="32" t="inlineStr">
         <is>
           <t>AQU-CLN-0162</t>
         </is>
       </c>
-      <c r="M20" s="31" t="inlineStr">
+      <c r="M20" s="33" t="inlineStr">
         <is>
           <t>5292638000162</t>
         </is>
       </c>
-      <c r="N20" s="32" t="inlineStr"/>
-      <c r="O20" s="32" t="inlineStr"/>
-      <c r="P20" s="32" t="inlineStr"/>
-      <c r="Q20" s="30" t="inlineStr">
+      <c r="N20" s="34" t="inlineStr"/>
+      <c r="O20" s="34" t="inlineStr"/>
+      <c r="P20" s="34" t="inlineStr"/>
+      <c r="Q20" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R20" s="30" t="inlineStr">
+      <c r="R20" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S20" s="30" t="inlineStr">
+      <c r="S20" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T20" s="30" t="inlineStr">
+      <c r="T20" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U20" s="30" t="inlineStr"/>
-      <c r="V20" s="30" t="inlineStr">
+      <c r="U20" s="32" t="inlineStr"/>
+      <c r="V20" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W20" s="30" t="inlineStr">
+      <c r="W20" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X20" s="30" t="inlineStr">
+      <c r="X20" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7749,7 +7779,7 @@
           <t>http://mangas.com.cy/media/products/5292638000162.jpg</t>
         </is>
       </c>
-      <c r="Z20" s="30" t="inlineStr">
+      <c r="Z20" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7759,7 +7789,7 @@
           <t>AQUALITY Magic tile 4 vinyl cleaner 1L</t>
         </is>
       </c>
-      <c r="AB20" s="30" t="inlineStr">
+      <c r="AB20" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7771,10 +7801,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF20" s="30" t="inlineStr"/>
-      <c r="AG20" s="30" t="inlineStr"/>
-      <c r="AH20" s="30" t="inlineStr"/>
-      <c r="AI20" s="30" t="inlineStr"/>
+      <c r="AF20" s="32" t="inlineStr"/>
+      <c r="AG20" s="32" t="inlineStr"/>
+      <c r="AH20" s="32" t="inlineStr"/>
+      <c r="AI20" s="32" t="inlineStr"/>
     </row>
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
@@ -7792,17 +7822,17 @@
           <t>A 1-litre spa and pool water clarifier from Bayzid, formulated to clear cloudy or turbid water. A handy bottle to reach for whenever the water loses its sparkle.</t>
         </is>
       </c>
-      <c r="D21" s="30" t="inlineStr">
+      <c r="D21" s="32" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E21" s="30" t="inlineStr">
+      <c r="E21" s="32" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F21" s="30" t="inlineStr">
+      <c r="F21" s="32" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -7812,71 +7842,71 @@
           <t>spa-hot-tub, pool, water-treatment, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H21" s="30" t="inlineStr">
+      <c r="H21" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I21" s="30" t="inlineStr">
+      <c r="I21" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J21" s="30" t="inlineStr">
+      <c r="J21" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K21" s="30" t="inlineStr">
+      <c r="K21" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L21" s="30" t="inlineStr">
+      <c r="L21" s="32" t="inlineStr">
         <is>
           <t>HFE-SPA-7202</t>
         </is>
       </c>
-      <c r="M21" s="31" t="inlineStr">
+      <c r="M21" s="33" t="inlineStr">
         <is>
           <t>4250463127202</t>
         </is>
       </c>
-      <c r="N21" s="32" t="inlineStr"/>
-      <c r="O21" s="32" t="inlineStr"/>
-      <c r="P21" s="32" t="inlineStr"/>
-      <c r="Q21" s="30" t="inlineStr">
+      <c r="N21" s="34" t="inlineStr"/>
+      <c r="O21" s="34" t="inlineStr"/>
+      <c r="P21" s="34" t="inlineStr"/>
+      <c r="Q21" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R21" s="30" t="inlineStr">
+      <c r="R21" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S21" s="30" t="inlineStr">
+      <c r="S21" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T21" s="30" t="inlineStr">
+      <c r="T21" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U21" s="30" t="inlineStr"/>
-      <c r="V21" s="30" t="inlineStr">
+      <c r="U21" s="32" t="inlineStr"/>
+      <c r="V21" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W21" s="30" t="inlineStr">
+      <c r="W21" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X21" s="30" t="inlineStr">
+      <c r="X21" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7886,7 +7916,7 @@
           <t>https://hoefer-shop.com/cdn/shop/files/1x1L-BAYZID-Spa-Poolclear-v1-RS_1.jpg?v=1785600487&amp;width=800</t>
         </is>
       </c>
-      <c r="Z21" s="30" t="inlineStr">
+      <c r="Z21" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7896,7 +7926,7 @@
           <t>Höfer Chemie GmbH pool care 1 L BAYZID® SPA Poolclear turbidity remover</t>
         </is>
       </c>
-      <c r="AB21" s="30" t="inlineStr">
+      <c r="AB21" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7908,10 +7938,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF21" s="30" t="inlineStr"/>
-      <c r="AG21" s="30" t="inlineStr"/>
-      <c r="AH21" s="30" t="inlineStr"/>
-      <c r="AI21" s="30" t="inlineStr"/>
+      <c r="AF21" s="32" t="inlineStr"/>
+      <c r="AG21" s="32" t="inlineStr"/>
+      <c r="AH21" s="32" t="inlineStr"/>
+      <c r="AI21" s="32" t="inlineStr"/>
     </row>
     <row r="22" ht="62" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
@@ -7929,17 +7959,17 @@
           <t>A 1-litre bottle of hydrogen peroxide at 11.9% concentration, suitable for disinfection and water treatment applications. A straightforward chemical solution that keeps things clean without fuss.</t>
         </is>
       </c>
-      <c r="D22" s="30" t="inlineStr">
+      <c r="D22" s="32" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E22" s="30" t="inlineStr">
+      <c r="E22" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F22" s="30" t="inlineStr">
+      <c r="F22" s="32" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -7949,71 +7979,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H22" s="30" t="inlineStr">
+      <c r="H22" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I22" s="30" t="inlineStr">
+      <c r="I22" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J22" s="30" t="inlineStr">
+      <c r="J22" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K22" s="30" t="inlineStr">
+      <c r="K22" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L22" s="30" t="inlineStr">
+      <c r="L22" s="32" t="inlineStr">
         <is>
           <t>HFE-CHM-6788</t>
         </is>
       </c>
-      <c r="M22" s="31" t="inlineStr">
+      <c r="M22" s="33" t="inlineStr">
         <is>
           <t>4250463106788</t>
         </is>
       </c>
-      <c r="N22" s="32" t="inlineStr"/>
-      <c r="O22" s="32" t="inlineStr"/>
-      <c r="P22" s="32" t="inlineStr"/>
-      <c r="Q22" s="30" t="inlineStr">
+      <c r="N22" s="34" t="inlineStr"/>
+      <c r="O22" s="34" t="inlineStr"/>
+      <c r="P22" s="34" t="inlineStr"/>
+      <c r="Q22" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R22" s="30" t="inlineStr">
+      <c r="R22" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S22" s="30" t="inlineStr">
+      <c r="S22" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T22" s="30" t="inlineStr">
+      <c r="T22" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U22" s="30" t="inlineStr"/>
-      <c r="V22" s="30" t="inlineStr">
+      <c r="U22" s="32" t="inlineStr"/>
+      <c r="V22" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W22" s="30" t="inlineStr">
+      <c r="W22" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X22" s="30" t="inlineStr">
+      <c r="X22" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8023,7 +8053,7 @@
           <t>https://hoefer-shop.com/cdn/shop/files/1x1L-Wasserstoffperoxid-Flasche-hinten-26.jpg?v=1783777627&amp;width=1000</t>
         </is>
       </c>
-      <c r="Z22" s="30" t="inlineStr">
+      <c r="Z22" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8033,7 +8063,7 @@
           <t>HÖFER CHEMIE GMBH 1 l hydrogen peroxide 11,9%</t>
         </is>
       </c>
-      <c r="AB22" s="30" t="inlineStr">
+      <c r="AB22" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8045,10 +8075,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF22" s="30" t="inlineStr"/>
-      <c r="AG22" s="30" t="inlineStr"/>
-      <c r="AH22" s="30" t="inlineStr"/>
-      <c r="AI22" s="30" t="inlineStr"/>
+      <c r="AF22" s="32" t="inlineStr"/>
+      <c r="AG22" s="32" t="inlineStr"/>
+      <c r="AH22" s="32" t="inlineStr"/>
+      <c r="AI22" s="32" t="inlineStr"/>
     </row>
     <row r="23" ht="62" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
@@ -8066,17 +8096,17 @@
           <t>A 4.5 kg pack of chlorine stabilizer for swimming pools, used to protect chlorine from UV degradation and extend its effectiveness in the water. Steady chemistry for a pool that earns its keep.</t>
         </is>
       </c>
-      <c r="D23" s="30" t="inlineStr">
+      <c r="D23" s="32" t="inlineStr">
         <is>
           <t>AstralPool</t>
         </is>
       </c>
-      <c r="E23" s="30" t="inlineStr">
+      <c r="E23" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F23" s="30" t="inlineStr">
+      <c r="F23" s="32" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8086,75 +8116,75 @@
           <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H23" s="30" t="inlineStr">
+      <c r="H23" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I23" s="30" t="inlineStr">
+      <c r="I23" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J23" s="30" t="inlineStr">
+      <c r="J23" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K23" s="30" t="inlineStr">
+      <c r="K23" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L23" s="30" t="inlineStr">
+      <c r="L23" s="32" t="inlineStr">
         <is>
           <t>AST-CHM-0626</t>
         </is>
       </c>
-      <c r="M23" s="31" t="inlineStr">
+      <c r="M23" s="33" t="inlineStr">
         <is>
           <t>8432611960626</t>
         </is>
       </c>
-      <c r="N23" s="32" t="inlineStr"/>
-      <c r="O23" s="32" t="inlineStr"/>
-      <c r="P23" s="32" t="inlineStr"/>
-      <c r="Q23" s="30" t="inlineStr">
+      <c r="N23" s="34" t="inlineStr"/>
+      <c r="O23" s="34" t="inlineStr"/>
+      <c r="P23" s="34" t="inlineStr"/>
+      <c r="Q23" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R23" s="30" t="inlineStr">
+      <c r="R23" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S23" s="30" t="inlineStr">
+      <c r="S23" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T23" s="30" t="inlineStr">
+      <c r="T23" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U23" s="30" t="inlineStr">
+      <c r="U23" s="32" t="inlineStr">
         <is>
           <t>4500</t>
         </is>
       </c>
-      <c r="V23" s="30" t="inlineStr">
+      <c r="V23" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W23" s="30" t="inlineStr">
+      <c r="W23" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X23" s="30" t="inlineStr">
+      <c r="X23" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8164,7 +8194,7 @@
           <t>https://yokando.com/img/p/2/8/2/9/3/28293.jpg</t>
         </is>
       </c>
-      <c r="Z23" s="30" t="inlineStr">
+      <c r="Z23" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8174,7 +8204,7 @@
           <t>Astralpool water care Astralpool Chlorine Stabilizer 4,5 kg</t>
         </is>
       </c>
-      <c r="AB23" s="30" t="inlineStr">
+      <c r="AB23" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8186,10 +8216,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF23" s="30" t="inlineStr"/>
-      <c r="AG23" s="30" t="inlineStr"/>
-      <c r="AH23" s="30" t="inlineStr"/>
-      <c r="AI23" s="30" t="inlineStr"/>
+      <c r="AF23" s="32" t="inlineStr"/>
+      <c r="AG23" s="32" t="inlineStr"/>
+      <c r="AH23" s="32" t="inlineStr"/>
+      <c r="AI23" s="32" t="inlineStr"/>
     </row>
     <row r="24" ht="62" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
@@ -8207,17 +8237,17 @@
           <t>UltraShock is a pool and spa shock treatment from SpaBalancer, designed to rapidly oxidise contaminants and restore water clarity. A quick reset for water that needs a little more persuasion.</t>
         </is>
       </c>
-      <c r="D24" s="30" t="inlineStr">
+      <c r="D24" s="32" t="inlineStr">
         <is>
           <t>SpaBalancer</t>
         </is>
       </c>
-      <c r="E24" s="30" t="inlineStr">
+      <c r="E24" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F24" s="30" t="inlineStr">
+      <c r="F24" s="32" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8227,71 +8257,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H24" s="30" t="inlineStr">
+      <c r="H24" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I24" s="30" t="inlineStr">
+      <c r="I24" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J24" s="30" t="inlineStr">
+      <c r="J24" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K24" s="30" t="inlineStr">
+      <c r="K24" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L24" s="30" t="inlineStr">
+      <c r="L24" s="32" t="inlineStr">
         <is>
           <t>SPA-CHM-0025</t>
         </is>
       </c>
-      <c r="M24" s="31" t="inlineStr">
+      <c r="M24" s="33" t="inlineStr">
         <is>
           <t>4260374980025</t>
         </is>
       </c>
-      <c r="N24" s="32" t="inlineStr"/>
-      <c r="O24" s="32" t="inlineStr"/>
-      <c r="P24" s="32" t="inlineStr"/>
-      <c r="Q24" s="30" t="inlineStr">
+      <c r="N24" s="34" t="inlineStr"/>
+      <c r="O24" s="34" t="inlineStr"/>
+      <c r="P24" s="34" t="inlineStr"/>
+      <c r="Q24" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R24" s="30" t="inlineStr">
+      <c r="R24" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S24" s="30" t="inlineStr">
+      <c r="S24" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T24" s="30" t="inlineStr">
+      <c r="T24" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U24" s="30" t="inlineStr"/>
-      <c r="V24" s="30" t="inlineStr">
+      <c r="U24" s="32" t="inlineStr"/>
+      <c r="V24" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W24" s="30" t="inlineStr">
+      <c r="W24" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X24" s="30" t="inlineStr">
+      <c r="X24" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8301,7 +8331,7 @@
           <t>https://images.barcodelookup.com/16704/167043133-1.jpg</t>
         </is>
       </c>
-      <c r="Z24" s="30" t="inlineStr">
+      <c r="Z24" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8311,7 +8341,7 @@
           <t>SpaBalancer UltraShock</t>
         </is>
       </c>
-      <c r="AB24" s="30" t="inlineStr">
+      <c r="AB24" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8323,10 +8353,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF24" s="30" t="inlineStr"/>
-      <c r="AG24" s="30" t="inlineStr"/>
-      <c r="AH24" s="30" t="inlineStr"/>
-      <c r="AI24" s="30" t="inlineStr"/>
+      <c r="AF24" s="32" t="inlineStr"/>
+      <c r="AG24" s="32" t="inlineStr"/>
+      <c r="AH24" s="32" t="inlineStr"/>
+      <c r="AI24" s="32" t="inlineStr"/>
     </row>
     <row r="25" ht="76" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
@@ -8344,13 +8374,13 @@
           <t>A patented foam rubber eraser for cleaning pool surfaces, particularly suited to waterline stains on liner and vitreous ceramic finishes, and it works without detergents or chemicals. Each box contains 3 sponges, which harden when wet to scrub effectively while remaining soft and flexible in use.</t>
         </is>
       </c>
-      <c r="D25" s="30" t="inlineStr"/>
-      <c r="E25" s="30" t="inlineStr">
+      <c r="D25" s="32" t="inlineStr"/>
+      <c r="E25" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F25" s="30" t="inlineStr">
+      <c r="F25" s="32" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8360,71 +8390,71 @@
           <t>pool, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H25" s="30" t="inlineStr">
+      <c r="H25" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I25" s="30" t="inlineStr">
+      <c r="I25" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J25" s="30" t="inlineStr">
+      <c r="J25" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K25" s="30" t="inlineStr">
+      <c r="K25" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L25" s="30" t="inlineStr">
+      <c r="L25" s="32" t="inlineStr">
         <is>
           <t>GEN-CLN-0062</t>
         </is>
       </c>
-      <c r="M25" s="31" t="inlineStr">
+      <c r="M25" s="33" t="inlineStr">
         <is>
           <t>3760015880062</t>
         </is>
       </c>
-      <c r="N25" s="32" t="inlineStr"/>
-      <c r="O25" s="32" t="inlineStr"/>
-      <c r="P25" s="32" t="inlineStr"/>
-      <c r="Q25" s="30" t="inlineStr">
+      <c r="N25" s="34" t="inlineStr"/>
+      <c r="O25" s="34" t="inlineStr"/>
+      <c r="P25" s="34" t="inlineStr"/>
+      <c r="Q25" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R25" s="30" t="inlineStr">
+      <c r="R25" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S25" s="30" t="inlineStr">
+      <c r="S25" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T25" s="30" t="inlineStr">
+      <c r="T25" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U25" s="30" t="inlineStr"/>
-      <c r="V25" s="30" t="inlineStr">
+      <c r="U25" s="32" t="inlineStr"/>
+      <c r="V25" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W25" s="30" t="inlineStr">
+      <c r="W25" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X25" s="30" t="inlineStr">
+      <c r="X25" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8434,7 +8464,7 @@
           <t>https://www.piscinarium.com/2908-thickbox_default/pool-gom-magic-rubber-eraser.jpg</t>
         </is>
       </c>
-      <c r="Z25" s="30" t="inlineStr">
+      <c r="Z25" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8444,7 +8474,7 @@
           <t>Pool'Gom Magic Rubber Eraser</t>
         </is>
       </c>
-      <c r="AB25" s="30" t="inlineStr">
+      <c r="AB25" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8456,10 +8486,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF25" s="30" t="inlineStr"/>
-      <c r="AG25" s="30" t="inlineStr"/>
-      <c r="AH25" s="30" t="inlineStr"/>
-      <c r="AI25" s="30" t="inlineStr"/>
+      <c r="AF25" s="32" t="inlineStr"/>
+      <c r="AG25" s="32" t="inlineStr"/>
+      <c r="AH25" s="32" t="inlineStr"/>
+      <c r="AI25" s="32" t="inlineStr"/>
     </row>
     <row r="26" ht="62" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
@@ -8477,13 +8507,13 @@
           <t>Spa Industries Europe appears to be a brand or supplier name rather than a specific product, so no product details can be confirmed. For accurate information, please check the full product listing.</t>
         </is>
       </c>
-      <c r="D26" s="30" t="inlineStr"/>
-      <c r="E26" s="30" t="inlineStr">
+      <c r="D26" s="32" t="inlineStr"/>
+      <c r="E26" s="32" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F26" s="30" t="inlineStr">
+      <c r="F26" s="32" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -8493,79 +8523,79 @@
           <t>spa-hot-tub, considered-purchase, multi-source-confirmed, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H26" s="30" t="inlineStr">
+      <c r="H26" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I26" s="30" t="inlineStr">
+      <c r="I26" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J26" s="30" t="inlineStr">
+      <c r="J26" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K26" s="30" t="inlineStr">
+      <c r="K26" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L26" s="30" t="inlineStr">
+      <c r="L26" s="32" t="inlineStr">
         <is>
           <t>GEN-SPA-1968</t>
         </is>
       </c>
-      <c r="M26" s="31" t="inlineStr">
+      <c r="M26" s="33" t="inlineStr">
         <is>
           <t>5425021871968</t>
         </is>
       </c>
-      <c r="N26" s="32" t="inlineStr"/>
-      <c r="O26" s="32" t="inlineStr"/>
-      <c r="P26" s="32" t="inlineStr"/>
-      <c r="Q26" s="30" t="inlineStr">
+      <c r="N26" s="34" t="inlineStr"/>
+      <c r="O26" s="34" t="inlineStr"/>
+      <c r="P26" s="34" t="inlineStr"/>
+      <c r="Q26" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R26" s="30" t="inlineStr">
+      <c r="R26" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S26" s="30" t="inlineStr">
+      <c r="S26" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T26" s="30" t="inlineStr">
+      <c r="T26" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U26" s="30" t="inlineStr"/>
-      <c r="V26" s="30" t="inlineStr">
+      <c r="U26" s="32" t="inlineStr"/>
+      <c r="V26" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W26" s="30" t="inlineStr">
+      <c r="W26" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X26" s="30" t="inlineStr">
+      <c r="X26" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y26" s="19" t="inlineStr"/>
-      <c r="Z26" s="30" t="inlineStr"/>
+      <c r="Z26" s="32" t="inlineStr"/>
       <c r="AA26" s="19" t="inlineStr"/>
-      <c r="AB26" s="30" t="inlineStr">
+      <c r="AB26" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8577,10 +8607,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF26" s="30" t="inlineStr"/>
-      <c r="AG26" s="30" t="inlineStr"/>
-      <c r="AH26" s="30" t="inlineStr"/>
-      <c r="AI26" s="30" t="inlineStr"/>
+      <c r="AF26" s="32" t="inlineStr"/>
+      <c r="AG26" s="32" t="inlineStr"/>
+      <c r="AH26" s="32" t="inlineStr"/>
+      <c r="AI26" s="32" t="inlineStr"/>
     </row>
     <row r="27" ht="62" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
@@ -8598,17 +8628,17 @@
           <t>A 1-litre high-concentrate sauna cleaner with eucalyptus fragrance, formulated as a deep-cleaning base cleaner for sauna surfaces. The concentrated formula means a little goes a long way, with a fresh scent to match.</t>
         </is>
       </c>
-      <c r="D27" s="30" t="inlineStr">
+      <c r="D27" s="32" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E27" s="30" t="inlineStr">
+      <c r="E27" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F27" s="30" t="inlineStr">
+      <c r="F27" s="32" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8618,79 +8648,79 @@
           <t>cleaning, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H27" s="30" t="inlineStr">
+      <c r="H27" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I27" s="30" t="inlineStr">
+      <c r="I27" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J27" s="30" t="inlineStr">
+      <c r="J27" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K27" s="30" t="inlineStr">
+      <c r="K27" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L27" s="30" t="inlineStr">
+      <c r="L27" s="32" t="inlineStr">
         <is>
           <t>HFE-CLN-7004</t>
         </is>
       </c>
-      <c r="M27" s="31" t="inlineStr">
+      <c r="M27" s="33" t="inlineStr">
         <is>
           <t>4250463127004</t>
         </is>
       </c>
-      <c r="N27" s="32" t="inlineStr"/>
-      <c r="O27" s="32" t="inlineStr"/>
-      <c r="P27" s="32" t="inlineStr"/>
-      <c r="Q27" s="30" t="inlineStr">
+      <c r="N27" s="34" t="inlineStr"/>
+      <c r="O27" s="34" t="inlineStr"/>
+      <c r="P27" s="34" t="inlineStr"/>
+      <c r="Q27" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R27" s="30" t="inlineStr">
+      <c r="R27" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S27" s="30" t="inlineStr">
+      <c r="S27" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T27" s="30" t="inlineStr">
+      <c r="T27" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U27" s="30" t="inlineStr"/>
-      <c r="V27" s="30" t="inlineStr">
+      <c r="U27" s="32" t="inlineStr"/>
+      <c r="V27" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W27" s="30" t="inlineStr">
+      <c r="W27" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X27" s="30" t="inlineStr">
+      <c r="X27" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y27" s="19" t="inlineStr"/>
-      <c r="Z27" s="30" t="inlineStr"/>
+      <c r="Z27" s="32" t="inlineStr"/>
       <c r="AA27" s="19" t="inlineStr"/>
-      <c r="AB27" s="30" t="inlineStr">
+      <c r="AB27" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8702,10 +8732,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF27" s="30" t="inlineStr"/>
-      <c r="AG27" s="30" t="inlineStr"/>
-      <c r="AH27" s="30" t="inlineStr"/>
-      <c r="AI27" s="30" t="inlineStr"/>
+      <c r="AF27" s="32" t="inlineStr"/>
+      <c r="AG27" s="32" t="inlineStr"/>
+      <c r="AH27" s="32" t="inlineStr"/>
+      <c r="AI27" s="32" t="inlineStr"/>
     </row>
     <row r="28" ht="76" customHeight="1">
       <c r="A28" s="19" t="inlineStr">
@@ -8723,17 +8753,17 @@
           <t>This HTH spa cleaner removes mineral deposits such as limescale and rust, and cleans and polishes aluminium, chrome, stainless steel, and enamel surfaces with a pleasant pine fragrance. It has a high concentration of active ingredients and is recommended for periodic maintenance cleaning.</t>
         </is>
       </c>
-      <c r="D28" s="30" t="inlineStr">
+      <c r="D28" s="32" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E28" s="30" t="inlineStr">
+      <c r="E28" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F28" s="30" t="inlineStr">
+      <c r="F28" s="32" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8743,71 +8773,71 @@
           <t>spa-hot-tub, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H28" s="30" t="inlineStr">
+      <c r="H28" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I28" s="30" t="inlineStr">
+      <c r="I28" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J28" s="30" t="inlineStr">
+      <c r="J28" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K28" s="30" t="inlineStr">
+      <c r="K28" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L28" s="30" t="inlineStr">
+      <c r="L28" s="32" t="inlineStr">
         <is>
           <t>HTH-CLN-0178</t>
         </is>
       </c>
-      <c r="M28" s="31" t="inlineStr">
+      <c r="M28" s="33" t="inlineStr">
         <is>
           <t>3521686010178</t>
         </is>
       </c>
-      <c r="N28" s="32" t="inlineStr"/>
-      <c r="O28" s="32" t="inlineStr"/>
-      <c r="P28" s="32" t="inlineStr"/>
-      <c r="Q28" s="30" t="inlineStr">
+      <c r="N28" s="34" t="inlineStr"/>
+      <c r="O28" s="34" t="inlineStr"/>
+      <c r="P28" s="34" t="inlineStr"/>
+      <c r="Q28" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R28" s="30" t="inlineStr">
+      <c r="R28" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S28" s="30" t="inlineStr">
+      <c r="S28" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T28" s="30" t="inlineStr">
+      <c r="T28" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U28" s="30" t="inlineStr"/>
-      <c r="V28" s="30" t="inlineStr">
+      <c r="U28" s="32" t="inlineStr"/>
+      <c r="V28" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W28" s="30" t="inlineStr">
+      <c r="W28" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X28" s="30" t="inlineStr">
+      <c r="X28" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8817,7 +8847,7 @@
           <t>https://www.cdiscount.com/pdt2/0/5/1/1/700x700/auc2009356289051/rw/hth-spa-nettoyant-spa-3521686010178.jpg</t>
         </is>
       </c>
-      <c r="Z28" s="30" t="inlineStr">
+      <c r="Z28" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8827,7 +8857,7 @@
           <t>HTH Spa spa cleaner</t>
         </is>
       </c>
-      <c r="AB28" s="30" t="inlineStr">
+      <c r="AB28" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8839,10 +8869,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF28" s="30" t="inlineStr"/>
-      <c r="AG28" s="30" t="inlineStr"/>
-      <c r="AH28" s="30" t="inlineStr"/>
-      <c r="AI28" s="30" t="inlineStr"/>
+      <c r="AF28" s="32" t="inlineStr"/>
+      <c r="AG28" s="32" t="inlineStr"/>
+      <c r="AH28" s="32" t="inlineStr"/>
+      <c r="AI28" s="32" t="inlineStr"/>
     </row>
     <row r="29" ht="62" customHeight="1">
       <c r="A29" s="19" t="inlineStr">
@@ -8860,13 +8890,13 @@
           <t>A 25 kg sack of pure boiling salt (minimum 99.6% NaCl) without an anti-caking agent, meeting EN 973 Type A standard and suitable for use in pool salt electrolysis systems. Not intended for human consumption or animal feed.</t>
         </is>
       </c>
-      <c r="D29" s="30" t="inlineStr"/>
-      <c r="E29" s="30" t="inlineStr">
+      <c r="D29" s="32" t="inlineStr"/>
+      <c r="E29" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F29" s="30" t="inlineStr">
+      <c r="F29" s="32" t="inlineStr">
         <is>
           <t>Pool salt</t>
         </is>
@@ -8876,75 +8906,75 @@
           <t>pool, salt, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H29" s="30" t="inlineStr">
+      <c r="H29" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I29" s="30" t="inlineStr">
+      <c r="I29" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J29" s="30" t="inlineStr">
+      <c r="J29" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K29" s="30" t="inlineStr">
+      <c r="K29" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L29" s="30" t="inlineStr">
+      <c r="L29" s="32" t="inlineStr">
         <is>
           <t>GEN-SLT-6110</t>
         </is>
       </c>
-      <c r="M29" s="31" t="inlineStr">
+      <c r="M29" s="33" t="inlineStr">
         <is>
           <t>9001880976110</t>
         </is>
       </c>
-      <c r="N29" s="32" t="inlineStr"/>
-      <c r="O29" s="32" t="inlineStr"/>
-      <c r="P29" s="32" t="inlineStr"/>
-      <c r="Q29" s="30" t="inlineStr">
+      <c r="N29" s="34" t="inlineStr"/>
+      <c r="O29" s="34" t="inlineStr"/>
+      <c r="P29" s="34" t="inlineStr"/>
+      <c r="Q29" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R29" s="30" t="inlineStr">
+      <c r="R29" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S29" s="30" t="inlineStr">
+      <c r="S29" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T29" s="30" t="inlineStr">
+      <c r="T29" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U29" s="30" t="inlineStr">
+      <c r="U29" s="32" t="inlineStr">
         <is>
           <t>25000</t>
         </is>
       </c>
-      <c r="V29" s="30" t="inlineStr">
+      <c r="V29" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W29" s="30" t="inlineStr">
+      <c r="W29" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X29" s="30" t="inlineStr">
+      <c r="X29" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8954,7 +8984,7 @@
           <t>http://altruan.com/cdn/shop/files/SalinenPoolSalz25kgSack.png?v=1778597596</t>
         </is>
       </c>
-      <c r="Z29" s="30" t="inlineStr">
+      <c r="Z29" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8964,7 +8994,7 @@
           <t>Saline pool salt pure boiling salt without separating agent | Sack (25 kg)</t>
         </is>
       </c>
-      <c r="AB29" s="30" t="inlineStr">
+      <c r="AB29" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8976,14 +9006,14 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF29" s="30" t="inlineStr">
+      <c r="AF29" s="32" t="inlineStr">
         <is>
           <t>Composition: Siedesalz (min. 99.6% NaCl) 100%; Separant/sodium ferrocyanide 4.0–12.0 mg/kg | Grain: &gt;0.63 mm approx. 20%, 0.2–0.63 mm approx. 75%, &lt;0.2 mm approx. 5% | Moisture: &lt;0.08%</t>
         </is>
       </c>
-      <c r="AG29" s="30" t="inlineStr"/>
-      <c r="AH29" s="30" t="inlineStr"/>
-      <c r="AI29" s="30" t="inlineStr"/>
+      <c r="AG29" s="32" t="inlineStr"/>
+      <c r="AH29" s="32" t="inlineStr"/>
+      <c r="AI29" s="32" t="inlineStr"/>
     </row>
     <row r="30" ht="76" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
@@ -9001,17 +9031,17 @@
           <t>A cordless robotic pool cleaner that scrubs both floors and walls automatically, using WavePath navigation to map and cover the pool efficiently. Built-in high-performance filtration and smart control make it a hands-off solution for keeping pool water clear.</t>
         </is>
       </c>
-      <c r="D30" s="30" t="inlineStr">
+      <c r="D30" s="32" t="inlineStr">
         <is>
           <t>Aiper</t>
         </is>
       </c>
-      <c r="E30" s="30" t="inlineStr">
+      <c r="E30" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F30" s="30" t="inlineStr">
+      <c r="F30" s="32" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9021,71 +9051,71 @@
           <t>pool, cleaning, robot-cleaner, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H30" s="30" t="inlineStr">
+      <c r="H30" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I30" s="30" t="inlineStr">
+      <c r="I30" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J30" s="30" t="inlineStr">
+      <c r="J30" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K30" s="30" t="inlineStr">
+      <c r="K30" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L30" s="30" t="inlineStr">
+      <c r="L30" s="32" t="inlineStr">
         <is>
           <t>AIP-ROB-4940</t>
         </is>
       </c>
-      <c r="M30" s="31" t="inlineStr">
+      <c r="M30" s="33" t="inlineStr">
         <is>
           <t>6977676344940</t>
         </is>
       </c>
-      <c r="N30" s="32" t="inlineStr"/>
-      <c r="O30" s="32" t="inlineStr"/>
-      <c r="P30" s="32" t="inlineStr"/>
-      <c r="Q30" s="30" t="inlineStr">
+      <c r="N30" s="34" t="inlineStr"/>
+      <c r="O30" s="34" t="inlineStr"/>
+      <c r="P30" s="34" t="inlineStr"/>
+      <c r="Q30" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R30" s="30" t="inlineStr">
+      <c r="R30" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S30" s="30" t="inlineStr">
+      <c r="S30" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T30" s="30" t="inlineStr">
+      <c r="T30" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U30" s="30" t="inlineStr"/>
-      <c r="V30" s="30" t="inlineStr">
+      <c r="U30" s="32" t="inlineStr"/>
+      <c r="V30" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W30" s="30" t="inlineStr">
+      <c r="W30" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X30" s="30" t="inlineStr">
+      <c r="X30" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9095,7 +9125,7 @@
           <t>https://images.barcodelookup.com/176692/1766920801-1.jpg</t>
         </is>
       </c>
-      <c r="Z30" s="30" t="inlineStr">
+      <c r="Z30" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9105,7 +9135,7 @@
           <t>AIPER Scuba S3 cordless pool robot, automatic floor and wall cleaning, WavePath™ navigation, high-performance filtration…</t>
         </is>
       </c>
-      <c r="AB30" s="30" t="inlineStr">
+      <c r="AB30" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9117,10 +9147,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF30" s="30" t="inlineStr"/>
-      <c r="AG30" s="30" t="inlineStr"/>
-      <c r="AH30" s="30" t="inlineStr"/>
-      <c r="AI30" s="30" t="inlineStr"/>
+      <c r="AF30" s="32" t="inlineStr"/>
+      <c r="AG30" s="32" t="inlineStr"/>
+      <c r="AH30" s="32" t="inlineStr"/>
+      <c r="AI30" s="32" t="inlineStr"/>
     </row>
     <row r="31" ht="62" customHeight="1">
       <c r="A31" s="19" t="inlineStr">
@@ -9138,13 +9168,13 @@
           <t>The Scuba L1 EU is a pool cleaning device, though no further specific details about its features, dimensions, or mechanism are available from the product name alone. Buyers should refer to the full product listing for specifications.</t>
         </is>
       </c>
-      <c r="D31" s="30" t="inlineStr"/>
-      <c r="E31" s="30" t="inlineStr">
+      <c r="D31" s="32" t="inlineStr"/>
+      <c r="E31" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F31" s="30" t="inlineStr">
+      <c r="F31" s="32" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9154,71 +9184,71 @@
           <t>robot-cleaner, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H31" s="30" t="inlineStr">
+      <c r="H31" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I31" s="30" t="inlineStr">
+      <c r="I31" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J31" s="30" t="inlineStr">
+      <c r="J31" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K31" s="30" t="inlineStr">
+      <c r="K31" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L31" s="30" t="inlineStr">
+      <c r="L31" s="32" t="inlineStr">
         <is>
           <t>GEN-ROB-5137</t>
         </is>
       </c>
-      <c r="M31" s="31" t="inlineStr">
+      <c r="M31" s="33" t="inlineStr">
         <is>
           <t>6975140315137</t>
         </is>
       </c>
-      <c r="N31" s="32" t="inlineStr"/>
-      <c r="O31" s="32" t="inlineStr"/>
-      <c r="P31" s="32" t="inlineStr"/>
-      <c r="Q31" s="30" t="inlineStr">
+      <c r="N31" s="34" t="inlineStr"/>
+      <c r="O31" s="34" t="inlineStr"/>
+      <c r="P31" s="34" t="inlineStr"/>
+      <c r="Q31" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R31" s="30" t="inlineStr">
+      <c r="R31" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S31" s="30" t="inlineStr">
+      <c r="S31" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T31" s="30" t="inlineStr">
+      <c r="T31" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U31" s="30" t="inlineStr"/>
-      <c r="V31" s="30" t="inlineStr">
+      <c r="U31" s="32" t="inlineStr"/>
+      <c r="V31" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W31" s="30" t="inlineStr">
+      <c r="W31" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X31" s="30" t="inlineStr">
+      <c r="X31" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9228,7 +9258,7 @@
           <t>https://images.barcodelookup.com/124722/1247228758-1.jpg</t>
         </is>
       </c>
-      <c r="Z31" s="30" t="inlineStr">
+      <c r="Z31" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9238,7 +9268,7 @@
           <t>Scuba L1 - EU</t>
         </is>
       </c>
-      <c r="AB31" s="30" t="inlineStr">
+      <c r="AB31" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9250,10 +9280,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF31" s="30" t="inlineStr"/>
-      <c r="AG31" s="30" t="inlineStr"/>
-      <c r="AH31" s="30" t="inlineStr"/>
-      <c r="AI31" s="30" t="inlineStr"/>
+      <c r="AF31" s="32" t="inlineStr"/>
+      <c r="AG31" s="32" t="inlineStr"/>
+      <c r="AH31" s="32" t="inlineStr"/>
+      <c r="AI31" s="32" t="inlineStr"/>
     </row>
     <row r="32" ht="48" customHeight="1">
       <c r="A32" s="19" t="inlineStr">
@@ -9271,13 +9301,13 @@
           <t>The Gre Pools RBR120 is a 51W robotic pool cleaner designed for automatic pool floor cleaning. A reliable workhorse that takes the scrubbing off your hands.</t>
         </is>
       </c>
-      <c r="D32" s="30" t="inlineStr"/>
-      <c r="E32" s="30" t="inlineStr">
+      <c r="D32" s="32" t="inlineStr"/>
+      <c r="E32" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F32" s="30" t="inlineStr">
+      <c r="F32" s="32" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9287,71 +9317,71 @@
           <t>robot-cleaner, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H32" s="30" t="inlineStr">
+      <c r="H32" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I32" s="30" t="inlineStr">
+      <c r="I32" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J32" s="30" t="inlineStr">
+      <c r="J32" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K32" s="30" t="inlineStr">
+      <c r="K32" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L32" s="30" t="inlineStr">
+      <c r="L32" s="32" t="inlineStr">
         <is>
           <t>GEN-ROB-8500</t>
         </is>
       </c>
-      <c r="M32" s="31" t="inlineStr">
+      <c r="M32" s="33" t="inlineStr">
         <is>
           <t>8412081308500</t>
         </is>
       </c>
-      <c r="N32" s="32" t="inlineStr"/>
-      <c r="O32" s="32" t="inlineStr"/>
-      <c r="P32" s="32" t="inlineStr"/>
-      <c r="Q32" s="30" t="inlineStr">
+      <c r="N32" s="34" t="inlineStr"/>
+      <c r="O32" s="34" t="inlineStr"/>
+      <c r="P32" s="34" t="inlineStr"/>
+      <c r="Q32" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R32" s="30" t="inlineStr">
+      <c r="R32" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S32" s="30" t="inlineStr">
+      <c r="S32" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T32" s="30" t="inlineStr">
+      <c r="T32" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U32" s="30" t="inlineStr"/>
-      <c r="V32" s="30" t="inlineStr">
+      <c r="U32" s="32" t="inlineStr"/>
+      <c r="V32" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W32" s="30" t="inlineStr">
+      <c r="W32" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X32" s="30" t="inlineStr">
+      <c r="X32" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9361,7 +9391,7 @@
           <t>https://images.barcodelookup.com/124726/1247268298-1.jpg</t>
         </is>
       </c>
-      <c r="Z32" s="30" t="inlineStr">
+      <c r="Z32" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9371,7 +9401,7 @@
           <t>Battery Powered Robot WET RUNNER XPERT</t>
         </is>
       </c>
-      <c r="AB32" s="30" t="inlineStr">
+      <c r="AB32" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9383,10 +9413,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF32" s="30" t="inlineStr"/>
-      <c r="AG32" s="30" t="inlineStr"/>
-      <c r="AH32" s="30" t="inlineStr"/>
-      <c r="AI32" s="30" t="inlineStr"/>
+      <c r="AF32" s="32" t="inlineStr"/>
+      <c r="AG32" s="32" t="inlineStr"/>
+      <c r="AH32" s="32" t="inlineStr"/>
+      <c r="AI32" s="32" t="inlineStr"/>
     </row>
     <row r="33" ht="90" customHeight="1">
       <c r="A33" s="19" t="inlineStr">
@@ -9404,13 +9434,13 @@
           <t>A twin-size inflatable airbed measuring 99 x 191 x 25 cm, built with Fiber-Tech internal construction using polyester fibres for comfort, vinyl sides and base, and a water-resistant flocked top surface with an anti-deflation valve. It supports a maximum weight of 136 kg and packs down compactly when deflated.</t>
         </is>
       </c>
-      <c r="D33" s="30" t="inlineStr"/>
-      <c r="E33" s="30" t="inlineStr">
+      <c r="D33" s="32" t="inlineStr"/>
+      <c r="E33" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-11</t>
         </is>
       </c>
-      <c r="F33" s="30" t="inlineStr">
+      <c r="F33" s="32" t="inlineStr">
         <is>
           <t>Airbed / lounger</t>
         </is>
@@ -9420,71 +9450,71 @@
           <t>considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H33" s="30" t="inlineStr">
+      <c r="H33" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I33" s="30" t="inlineStr">
+      <c r="I33" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J33" s="30" t="inlineStr">
+      <c r="J33" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K33" s="30" t="inlineStr">
+      <c r="K33" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L33" s="30" t="inlineStr">
+      <c r="L33" s="32" t="inlineStr">
         <is>
           <t>GEN-BED-2443</t>
         </is>
       </c>
-      <c r="M33" s="31" t="inlineStr">
+      <c r="M33" s="33" t="inlineStr">
         <is>
           <t>6941057412443</t>
         </is>
       </c>
-      <c r="N33" s="32" t="inlineStr"/>
-      <c r="O33" s="32" t="inlineStr"/>
-      <c r="P33" s="32" t="inlineStr"/>
-      <c r="Q33" s="30" t="inlineStr">
+      <c r="N33" s="34" t="inlineStr"/>
+      <c r="O33" s="34" t="inlineStr"/>
+      <c r="P33" s="34" t="inlineStr"/>
+      <c r="Q33" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R33" s="30" t="inlineStr">
+      <c r="R33" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S33" s="30" t="inlineStr">
+      <c r="S33" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T33" s="30" t="inlineStr">
+      <c r="T33" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U33" s="30" t="inlineStr"/>
-      <c r="V33" s="30" t="inlineStr">
+      <c r="U33" s="32" t="inlineStr"/>
+      <c r="V33" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W33" s="30" t="inlineStr">
+      <c r="W33" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X33" s="30" t="inlineStr">
+      <c r="X33" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9494,7 +9524,7 @@
           <t>https://www.ecoperation.com/media/catalog/product/cache/b76cf1d99a7811daa83ba86e6ad91c89/6/4/64757.jpg</t>
         </is>
       </c>
-      <c r="Z33" s="30" t="inlineStr">
+      <c r="Z33" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9504,7 +9534,7 @@
           <t>Twin Dura-Beam Classic Downy Airbed 99x191x25 cm</t>
         </is>
       </c>
-      <c r="AB33" s="30" t="inlineStr">
+      <c r="AB33" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9516,18 +9546,18 @@
           <t>Inflatable Beds and Mattresses</t>
         </is>
       </c>
-      <c r="AF33" s="30" t="inlineStr"/>
-      <c r="AG33" s="30" t="inlineStr">
+      <c r="AF33" s="32" t="inlineStr"/>
+      <c r="AG33" s="32" t="inlineStr">
         <is>
           <t>99.0cm</t>
         </is>
       </c>
-      <c r="AH33" s="30" t="inlineStr">
+      <c r="AH33" s="32" t="inlineStr">
         <is>
           <t>191.0cm</t>
         </is>
       </c>
-      <c r="AI33" s="30" t="inlineStr">
+      <c r="AI33" s="32" t="inlineStr">
         <is>
           <t>25.0cm</t>
         </is>
@@ -9549,17 +9579,17 @@
           <t>A plastic chlorine dosing lock from Steinbach, designed exclusively for use with long-term chlorine tablets, with a 1.5-inch connection fitting. It measures 37 cm in length, 22.5 cm in width, and 15 cm in height, making it a sturdy inline dosing unit for pool water treatment systems.</t>
         </is>
       </c>
-      <c r="D34" s="30" t="inlineStr">
+      <c r="D34" s="32" t="inlineStr">
         <is>
           <t>Steinbach</t>
         </is>
       </c>
-      <c r="E34" s="30" t="inlineStr">
+      <c r="E34" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F34" s="30" t="inlineStr">
+      <c r="F34" s="32" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -9569,71 +9599,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H34" s="30" t="inlineStr">
+      <c r="H34" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I34" s="30" t="inlineStr">
+      <c r="I34" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J34" s="30" t="inlineStr">
+      <c r="J34" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K34" s="30" t="inlineStr">
+      <c r="K34" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L34" s="30" t="inlineStr">
+      <c r="L34" s="32" t="inlineStr">
         <is>
           <t>STE-CHM-0307</t>
         </is>
       </c>
-      <c r="M34" s="31" t="inlineStr">
+      <c r="M34" s="33" t="inlineStr">
         <is>
           <t>9008748790307</t>
         </is>
       </c>
-      <c r="N34" s="32" t="inlineStr"/>
-      <c r="O34" s="32" t="inlineStr"/>
-      <c r="P34" s="32" t="inlineStr"/>
-      <c r="Q34" s="30" t="inlineStr">
+      <c r="N34" s="34" t="inlineStr"/>
+      <c r="O34" s="34" t="inlineStr"/>
+      <c r="P34" s="34" t="inlineStr"/>
+      <c r="Q34" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R34" s="30" t="inlineStr">
+      <c r="R34" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S34" s="30" t="inlineStr">
+      <c r="S34" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T34" s="30" t="inlineStr">
+      <c r="T34" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U34" s="30" t="inlineStr"/>
-      <c r="V34" s="30" t="inlineStr">
+      <c r="U34" s="32" t="inlineStr"/>
+      <c r="V34" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W34" s="30" t="inlineStr">
+      <c r="W34" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X34" s="30" t="inlineStr">
+      <c r="X34" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9643,7 +9673,7 @@
           <t>https://i.ebayimg.com/images/g/CrUAAeSwkOdqeaRR/s-l400.jpg</t>
         </is>
       </c>
-      <c r="Z34" s="30" t="inlineStr">
+      <c r="Z34" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9653,7 +9683,7 @@
           <t>STEINBACH Chlorine dosing lock, only for chlorine long-term tablets, plastic, connection 1.5 inch in</t>
         </is>
       </c>
-      <c r="AB34" s="30" t="inlineStr">
+      <c r="AB34" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9665,18 +9695,18 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF34" s="30" t="inlineStr"/>
-      <c r="AG34" s="30" t="inlineStr">
+      <c r="AF34" s="32" t="inlineStr"/>
+      <c r="AG34" s="32" t="inlineStr">
         <is>
           <t>22.5cm</t>
         </is>
       </c>
-      <c r="AH34" s="30" t="inlineStr">
+      <c r="AH34" s="32" t="inlineStr">
         <is>
           <t>37.0cm</t>
         </is>
       </c>
-      <c r="AI34" s="30" t="inlineStr">
+      <c r="AI34" s="32" t="inlineStr">
         <is>
           <t>15.0cm</t>
         </is>
@@ -9698,17 +9728,17 @@
           <t>A filter cleaning system for hot tub and pool cartridge filters, designed to remove debris and residue efficiently while keeping water usage to a minimum. A practical tool for extending the life of your filter without wasting a drop more than necessary.</t>
         </is>
       </c>
-      <c r="D35" s="30" t="inlineStr">
+      <c r="D35" s="32" t="inlineStr">
         <is>
           <t>Estelle</t>
         </is>
       </c>
-      <c r="E35" s="30" t="inlineStr">
+      <c r="E35" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F35" s="30" t="inlineStr">
+      <c r="F35" s="32" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -9718,71 +9748,71 @@
           <t>filters, spa-hot-tub, cleaning, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H35" s="30" t="inlineStr">
+      <c r="H35" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I35" s="30" t="inlineStr">
+      <c r="I35" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J35" s="30" t="inlineStr">
+      <c r="J35" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K35" s="30" t="inlineStr">
+      <c r="K35" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L35" s="30" t="inlineStr">
+      <c r="L35" s="32" t="inlineStr">
         <is>
           <t>EST-FIL-3669</t>
         </is>
       </c>
-      <c r="M35" s="31" t="inlineStr">
+      <c r="M35" s="33" t="inlineStr">
         <is>
           <t>8711842033669</t>
         </is>
       </c>
-      <c r="N35" s="32" t="inlineStr"/>
-      <c r="O35" s="32" t="inlineStr"/>
-      <c r="P35" s="32" t="inlineStr"/>
-      <c r="Q35" s="30" t="inlineStr">
+      <c r="N35" s="34" t="inlineStr"/>
+      <c r="O35" s="34" t="inlineStr"/>
+      <c r="P35" s="34" t="inlineStr"/>
+      <c r="Q35" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R35" s="30" t="inlineStr">
+      <c r="R35" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S35" s="30" t="inlineStr">
+      <c r="S35" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T35" s="30" t="inlineStr">
+      <c r="T35" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U35" s="30" t="inlineStr"/>
-      <c r="V35" s="30" t="inlineStr">
+      <c r="U35" s="32" t="inlineStr"/>
+      <c r="V35" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W35" s="30" t="inlineStr">
+      <c r="W35" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X35" s="30" t="inlineStr">
+      <c r="X35" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9792,7 +9822,7 @@
           <t>https://i.ebayimg.com/images/g/0e0AAOSweaplqO77/s-l400.jpg</t>
         </is>
       </c>
-      <c r="Z35" s="30" t="inlineStr">
+      <c r="Z35" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9802,7 +9832,7 @@
           <t>Estelle Filter Cleaning System Hot tubs Cartridge Filters Cleaner Spa Amazing!</t>
         </is>
       </c>
-      <c r="AB35" s="30" t="inlineStr">
+      <c r="AB35" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9814,10 +9844,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF35" s="30" t="inlineStr"/>
-      <c r="AG35" s="30" t="inlineStr"/>
-      <c r="AH35" s="30" t="inlineStr"/>
-      <c r="AI35" s="30" t="inlineStr"/>
+      <c r="AF35" s="32" t="inlineStr"/>
+      <c r="AG35" s="32" t="inlineStr"/>
+      <c r="AH35" s="32" t="inlineStr"/>
+      <c r="AI35" s="32" t="inlineStr"/>
     </row>
     <row r="36" ht="62" customHeight="1">
       <c r="A36" s="19" t="inlineStr">
@@ -9835,17 +9865,17 @@
           <t>A compact handy scrub brush for pool maintenance, measuring 15 x 9 x 8 cm, suited to scrubbing pool surfaces and hard-to-reach areas. Small enough to manoeuvre easily, and ready to tackle whatever the waterline throws at it.</t>
         </is>
       </c>
-      <c r="D36" s="30" t="inlineStr">
+      <c r="D36" s="32" t="inlineStr">
         <is>
           <t>WAYS</t>
         </is>
       </c>
-      <c r="E36" s="30" t="inlineStr">
+      <c r="E36" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F36" s="30" t="inlineStr">
+      <c r="F36" s="32" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -9855,79 +9885,79 @@
           <t>pool, cleaning, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H36" s="30" t="inlineStr">
+      <c r="H36" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I36" s="30" t="inlineStr">
+      <c r="I36" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J36" s="30" t="inlineStr">
+      <c r="J36" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K36" s="30" t="inlineStr">
+      <c r="K36" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L36" s="30" t="inlineStr">
+      <c r="L36" s="32" t="inlineStr">
         <is>
           <t>WAY-CLN-2219</t>
         </is>
       </c>
-      <c r="M36" s="31" t="inlineStr">
+      <c r="M36" s="33" t="inlineStr">
         <is>
           <t>8720299182219</t>
         </is>
       </c>
-      <c r="N36" s="32" t="inlineStr"/>
-      <c r="O36" s="32" t="inlineStr"/>
-      <c r="P36" s="32" t="inlineStr"/>
-      <c r="Q36" s="30" t="inlineStr">
+      <c r="N36" s="34" t="inlineStr"/>
+      <c r="O36" s="34" t="inlineStr"/>
+      <c r="P36" s="34" t="inlineStr"/>
+      <c r="Q36" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R36" s="30" t="inlineStr">
+      <c r="R36" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S36" s="30" t="inlineStr">
+      <c r="S36" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T36" s="30" t="inlineStr">
+      <c r="T36" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U36" s="30" t="inlineStr"/>
-      <c r="V36" s="30" t="inlineStr">
+      <c r="U36" s="32" t="inlineStr"/>
+      <c r="V36" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W36" s="30" t="inlineStr">
+      <c r="W36" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X36" s="30" t="inlineStr">
+      <c r="X36" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y36" s="19" t="inlineStr"/>
-      <c r="Z36" s="30" t="inlineStr"/>
+      <c r="Z36" s="32" t="inlineStr"/>
       <c r="AA36" s="19" t="inlineStr"/>
-      <c r="AB36" s="30" t="inlineStr">
+      <c r="AB36" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9939,18 +9969,18 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF36" s="30" t="inlineStr"/>
-      <c r="AG36" s="30" t="inlineStr">
+      <c r="AF36" s="32" t="inlineStr"/>
+      <c r="AG36" s="32" t="inlineStr">
         <is>
           <t>8.0cm</t>
         </is>
       </c>
-      <c r="AH36" s="30" t="inlineStr">
+      <c r="AH36" s="32" t="inlineStr">
         <is>
           <t>15.0cm</t>
         </is>
       </c>
-      <c r="AI36" s="30" t="inlineStr">
+      <c r="AI36" s="32" t="inlineStr">
         <is>
           <t>9.0cm</t>
         </is>
@@ -9972,17 +10002,17 @@
           <t>An inflatable PVC headrest pillow for the Intex inflatable spa (model 28506), measuring 24 x 19 x 6 cm and weighing 0.22 kg, designed to support the head and neck comfortably during use. It attaches to the spa rim and can also be filled with water for added stability.</t>
         </is>
       </c>
-      <c r="D37" s="30" t="inlineStr">
+      <c r="D37" s="32" t="inlineStr">
         <is>
           <t>Intex</t>
         </is>
       </c>
-      <c r="E37" s="30" t="inlineStr">
+      <c r="E37" s="32" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F37" s="30" t="inlineStr">
+      <c r="F37" s="32" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -9992,75 +10022,75 @@
           <t>spa-hot-tub, accessories, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H37" s="30" t="inlineStr">
+      <c r="H37" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I37" s="30" t="inlineStr">
+      <c r="I37" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J37" s="30" t="inlineStr">
+      <c r="J37" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K37" s="30" t="inlineStr">
+      <c r="K37" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L37" s="30" t="inlineStr">
+      <c r="L37" s="32" t="inlineStr">
         <is>
           <t>INT-SPA-6075</t>
         </is>
       </c>
-      <c r="M37" s="31" t="inlineStr">
+      <c r="M37" s="33" t="inlineStr">
         <is>
           <t>6941057426075</t>
         </is>
       </c>
-      <c r="N37" s="32" t="inlineStr"/>
-      <c r="O37" s="32" t="inlineStr"/>
-      <c r="P37" s="32" t="inlineStr"/>
-      <c r="Q37" s="30" t="inlineStr">
+      <c r="N37" s="34" t="inlineStr"/>
+      <c r="O37" s="34" t="inlineStr"/>
+      <c r="P37" s="34" t="inlineStr"/>
+      <c r="Q37" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R37" s="30" t="inlineStr">
+      <c r="R37" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S37" s="30" t="inlineStr">
+      <c r="S37" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T37" s="30" t="inlineStr">
+      <c r="T37" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U37" s="30" t="inlineStr">
+      <c r="U37" s="32" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="V37" s="30" t="inlineStr">
+      <c r="V37" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W37" s="30" t="inlineStr">
+      <c r="W37" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X37" s="30" t="inlineStr">
+      <c r="X37" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10070,7 +10100,7 @@
           <t>https://content2.rozetka.com.ua/goods/images/big/570260745.jpg</t>
         </is>
       </c>
-      <c r="Z37" s="30" t="inlineStr">
+      <c r="Z37" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10080,7 +10110,7 @@
           <t>Pillow for inflatable SPA INTEX 28506</t>
         </is>
       </c>
-      <c r="AB37" s="30" t="inlineStr">
+      <c r="AB37" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10092,18 +10122,18 @@
           <t>Intex Pure Spa Accessories</t>
         </is>
       </c>
-      <c r="AF37" s="30" t="inlineStr"/>
-      <c r="AG37" s="30" t="inlineStr">
+      <c r="AF37" s="32" t="inlineStr"/>
+      <c r="AG37" s="32" t="inlineStr">
         <is>
           <t>19.0cm</t>
         </is>
       </c>
-      <c r="AH37" s="30" t="inlineStr">
+      <c r="AH37" s="32" t="inlineStr">
         <is>
           <t>24.0cm</t>
         </is>
       </c>
-      <c r="AI37" s="30" t="inlineStr">
+      <c r="AI37" s="32" t="inlineStr">
         <is>
           <t>6.0cm</t>
         </is>
@@ -10125,13 +10155,13 @@
           <t>A DPD Pool test kit for active-oxygen pools, containing 20 DPD No. 4 reagent tablets for measuring active oxygen levels and 20 phenol red tablets for measuring pH. Results are read immediately after the tablet dissolves, with an ideal active oxygen range of 3.0 to 8.0 mg/l and a target pH of 7.0 to 7.4.</t>
         </is>
       </c>
-      <c r="D38" s="30" t="inlineStr"/>
-      <c r="E38" s="30" t="inlineStr">
+      <c r="D38" s="32" t="inlineStr"/>
+      <c r="E38" s="32" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F38" s="30" t="inlineStr">
+      <c r="F38" s="32" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -10141,71 +10171,71 @@
           <t>water-treatment, test-measure, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H38" s="30" t="inlineStr">
+      <c r="H38" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I38" s="30" t="inlineStr">
+      <c r="I38" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J38" s="30" t="inlineStr">
+      <c r="J38" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K38" s="30" t="inlineStr">
+      <c r="K38" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L38" s="30" t="inlineStr">
+      <c r="L38" s="32" t="inlineStr">
         <is>
           <t>GEN-TST-1347</t>
         </is>
       </c>
-      <c r="M38" s="31" t="inlineStr">
+      <c r="M38" s="33" t="inlineStr">
         <is>
           <t>4250463121347</t>
         </is>
       </c>
-      <c r="N38" s="32" t="inlineStr"/>
-      <c r="O38" s="32" t="inlineStr"/>
-      <c r="P38" s="32" t="inlineStr"/>
-      <c r="Q38" s="30" t="inlineStr">
+      <c r="N38" s="34" t="inlineStr"/>
+      <c r="O38" s="34" t="inlineStr"/>
+      <c r="P38" s="34" t="inlineStr"/>
+      <c r="Q38" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R38" s="30" t="inlineStr">
+      <c r="R38" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S38" s="30" t="inlineStr">
+      <c r="S38" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T38" s="30" t="inlineStr">
+      <c r="T38" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U38" s="30" t="inlineStr"/>
-      <c r="V38" s="30" t="inlineStr">
+      <c r="U38" s="32" t="inlineStr"/>
+      <c r="V38" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W38" s="30" t="inlineStr">
+      <c r="W38" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X38" s="30" t="inlineStr">
+      <c r="X38" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10215,7 +10245,7 @@
           <t>https://media.carrefour.fr/medias/8f94161f683b4e589024a5b5ebaa6873/p_200x200/cad3db6a00ef414a804b9226119bae96_image.jpg</t>
         </is>
       </c>
-      <c r="Z38" s="30" t="inlineStr">
+      <c r="Z38" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10225,7 +10255,7 @@
           <t>Active oxygen test kit x1</t>
         </is>
       </c>
-      <c r="AB38" s="30" t="inlineStr">
+      <c r="AB38" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10237,10 +10267,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF38" s="30" t="inlineStr"/>
-      <c r="AG38" s="30" t="inlineStr"/>
-      <c r="AH38" s="30" t="inlineStr"/>
-      <c r="AI38" s="30" t="inlineStr"/>
+      <c r="AF38" s="32" t="inlineStr"/>
+      <c r="AG38" s="32" t="inlineStr"/>
+      <c r="AH38" s="32" t="inlineStr"/>
+      <c r="AI38" s="32" t="inlineStr"/>
     </row>
     <row r="39" ht="62" customHeight="1">
       <c r="A39" s="19" t="inlineStr">
@@ -10258,17 +10288,17 @@
           <t>A pack of 2 replacement filter cartridges compatible with Intex Type H pool and spa pumps, made by Darlly. Straightforward to swap out, they keep the water moving clean without any complications.</t>
         </is>
       </c>
-      <c r="D39" s="30" t="inlineStr">
+      <c r="D39" s="32" t="inlineStr">
         <is>
           <t>Intex</t>
         </is>
       </c>
-      <c r="E39" s="30" t="inlineStr">
+      <c r="E39" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F39" s="30" t="inlineStr">
+      <c r="F39" s="32" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -10278,71 +10308,71 @@
           <t>filters, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H39" s="30" t="inlineStr">
+      <c r="H39" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I39" s="30" t="inlineStr">
+      <c r="I39" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J39" s="30" t="inlineStr">
+      <c r="J39" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K39" s="30" t="inlineStr">
+      <c r="K39" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L39" s="30" t="inlineStr">
+      <c r="L39" s="32" t="inlineStr">
         <is>
           <t>INT-FIL-2895</t>
         </is>
       </c>
-      <c r="M39" s="31" t="inlineStr">
+      <c r="M39" s="33" t="inlineStr">
         <is>
           <t>700175992895</t>
         </is>
       </c>
-      <c r="N39" s="32" t="inlineStr"/>
-      <c r="O39" s="32" t="inlineStr"/>
-      <c r="P39" s="32" t="inlineStr"/>
-      <c r="Q39" s="30" t="inlineStr">
+      <c r="N39" s="34" t="inlineStr"/>
+      <c r="O39" s="34" t="inlineStr"/>
+      <c r="P39" s="34" t="inlineStr"/>
+      <c r="Q39" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R39" s="30" t="inlineStr">
+      <c r="R39" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S39" s="30" t="inlineStr">
+      <c r="S39" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T39" s="30" t="inlineStr">
+      <c r="T39" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U39" s="30" t="inlineStr"/>
-      <c r="V39" s="30" t="inlineStr">
+      <c r="U39" s="32" t="inlineStr"/>
+      <c r="V39" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W39" s="30" t="inlineStr">
+      <c r="W39" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X39" s="30" t="inlineStr">
+      <c r="X39" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10352,7 +10382,7 @@
           <t>https://a.allegroimg.com/original/11923c/a79785a04d36aa54f0d87384f038/Filtracni-kartuse-Intex-D-3BTZ0023-SC828</t>
         </is>
       </c>
-      <c r="Z39" s="30" t="inlineStr">
+      <c r="Z39" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10362,7 +10392,7 @@
           <t>Darlly filter cartridge pack of 2 filter cartridges compatible with Intex type H</t>
         </is>
       </c>
-      <c r="AB39" s="30" t="inlineStr">
+      <c r="AB39" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10374,10 +10404,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF39" s="30" t="inlineStr"/>
-      <c r="AG39" s="30" t="inlineStr"/>
-      <c r="AH39" s="30" t="inlineStr"/>
-      <c r="AI39" s="30" t="inlineStr"/>
+      <c r="AF39" s="32" t="inlineStr"/>
+      <c r="AG39" s="32" t="inlineStr"/>
+      <c r="AH39" s="32" t="inlineStr"/>
+      <c r="AI39" s="32" t="inlineStr"/>
     </row>
     <row r="40" ht="62" customHeight="1">
       <c r="A40" s="19" t="inlineStr">
@@ -10395,17 +10425,17 @@
           <t>A Darlly replacement spa filter cartridge with dimensions of 22 cm diameter by 27 cm height, compatible with SC713 and C-8465 references. A reliable like-for-like swap to keep your spa filtration running smoothly.</t>
         </is>
       </c>
-      <c r="D40" s="30" t="inlineStr">
+      <c r="D40" s="32" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E40" s="30" t="inlineStr">
+      <c r="E40" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F40" s="30" t="inlineStr">
+      <c r="F40" s="32" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -10415,71 +10445,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H40" s="30" t="inlineStr">
+      <c r="H40" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I40" s="30" t="inlineStr">
+      <c r="I40" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J40" s="30" t="inlineStr">
+      <c r="J40" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K40" s="30" t="inlineStr">
+      <c r="K40" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L40" s="30" t="inlineStr">
+      <c r="L40" s="32" t="inlineStr">
         <is>
           <t>DAR-FIL-1744</t>
         </is>
       </c>
-      <c r="M40" s="31" t="inlineStr">
+      <c r="M40" s="33" t="inlineStr">
         <is>
           <t>700175991744</t>
         </is>
       </c>
-      <c r="N40" s="32" t="inlineStr"/>
-      <c r="O40" s="32" t="inlineStr"/>
-      <c r="P40" s="32" t="inlineStr"/>
-      <c r="Q40" s="30" t="inlineStr">
+      <c r="N40" s="34" t="inlineStr"/>
+      <c r="O40" s="34" t="inlineStr"/>
+      <c r="P40" s="34" t="inlineStr"/>
+      <c r="Q40" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R40" s="30" t="inlineStr">
+      <c r="R40" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S40" s="30" t="inlineStr">
+      <c r="S40" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T40" s="30" t="inlineStr">
+      <c r="T40" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U40" s="30" t="inlineStr"/>
-      <c r="V40" s="30" t="inlineStr">
+      <c r="U40" s="32" t="inlineStr"/>
+      <c r="V40" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W40" s="30" t="inlineStr">
+      <c r="W40" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X40" s="30" t="inlineStr">
+      <c r="X40" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10489,7 +10519,7 @@
           <t>https://images.barcodelookup.com/142259/1422591231-1.jpg</t>
         </is>
       </c>
-      <c r="Z40" s="30" t="inlineStr">
+      <c r="Z40" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10499,7 +10529,7 @@
           <t>Spa replacement filter Ø 22 cm x 27 cm SC713, C-8465 - Darlly</t>
         </is>
       </c>
-      <c r="AB40" s="30" t="inlineStr">
+      <c r="AB40" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10511,14 +10541,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF40" s="30" t="inlineStr"/>
-      <c r="AG40" s="30" t="inlineStr"/>
-      <c r="AH40" s="30" t="inlineStr">
+      <c r="AF40" s="32" t="inlineStr"/>
+      <c r="AG40" s="32" t="inlineStr"/>
+      <c r="AH40" s="32" t="inlineStr">
         <is>
           <t>22.0cm</t>
         </is>
       </c>
-      <c r="AI40" s="30" t="inlineStr">
+      <c r="AI40" s="32" t="inlineStr">
         <is>
           <t>27.0cm</t>
         </is>
@@ -10540,17 +10570,17 @@
           <t>A 1 kg pack of 20g multitabs for swimming pools, offering a 5-in-1 treatment that combines multiple water care functions in a single slow-dissolving tablet. Convenient all-in-one dosing that keeps pool maintenance simple.</t>
         </is>
       </c>
-      <c r="D41" s="30" t="inlineStr">
+      <c r="D41" s="32" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E41" s="30" t="inlineStr">
+      <c r="E41" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F41" s="30" t="inlineStr">
+      <c r="F41" s="32" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -10560,75 +10590,75 @@
           <t>pool, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H41" s="30" t="inlineStr">
+      <c r="H41" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I41" s="30" t="inlineStr">
+      <c r="I41" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J41" s="30" t="inlineStr">
+      <c r="J41" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K41" s="30" t="inlineStr">
+      <c r="K41" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L41" s="30" t="inlineStr">
+      <c r="L41" s="32" t="inlineStr">
         <is>
           <t>HFE-CHM-8430</t>
         </is>
       </c>
-      <c r="M41" s="31" t="inlineStr">
+      <c r="M41" s="33" t="inlineStr">
         <is>
           <t>4250463108430</t>
         </is>
       </c>
-      <c r="N41" s="32" t="inlineStr"/>
-      <c r="O41" s="32" t="inlineStr"/>
-      <c r="P41" s="32" t="inlineStr"/>
-      <c r="Q41" s="30" t="inlineStr">
+      <c r="N41" s="34" t="inlineStr"/>
+      <c r="O41" s="34" t="inlineStr"/>
+      <c r="P41" s="34" t="inlineStr"/>
+      <c r="Q41" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R41" s="30" t="inlineStr">
+      <c r="R41" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S41" s="30" t="inlineStr">
+      <c r="S41" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T41" s="30" t="inlineStr">
+      <c r="T41" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U41" s="30" t="inlineStr">
+      <c r="U41" s="32" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="V41" s="30" t="inlineStr">
+      <c r="V41" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W41" s="30" t="inlineStr">
+      <c r="W41" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X41" s="30" t="inlineStr">
+      <c r="X41" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10638,7 +10668,7 @@
           <t>https://images.barcodelookup.com/17422/174228560-1.jpg</t>
         </is>
       </c>
-      <c r="Z41" s="30" t="inlineStr">
+      <c r="Z41" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10648,7 +10678,7 @@
           <t>1 x 1 kg BAYZID® multitabs 20g 5in1 for pools - HöFER CHEMIE</t>
         </is>
       </c>
-      <c r="AB41" s="30" t="inlineStr">
+      <c r="AB41" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10660,10 +10690,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF41" s="30" t="inlineStr"/>
-      <c r="AG41" s="30" t="inlineStr"/>
-      <c r="AH41" s="30" t="inlineStr"/>
-      <c r="AI41" s="30" t="inlineStr"/>
+      <c r="AF41" s="32" t="inlineStr"/>
+      <c r="AG41" s="32" t="inlineStr"/>
+      <c r="AH41" s="32" t="inlineStr"/>
+      <c r="AI41" s="32" t="inlineStr"/>
     </row>
     <row r="42" ht="76" customHeight="1">
       <c r="A42" s="19" t="inlineStr">
@@ -10681,17 +10711,17 @@
           <t>A ready-to-use alkaline spray cleaner for removing grease and dirt marks at the waterline of pools and for cleaning skimmers. The spray bottle makes application straightforward, and it can be used on a filled pool on all alkali-resistant surfaces.</t>
         </is>
       </c>
-      <c r="D42" s="30" t="inlineStr">
+      <c r="D42" s="32" t="inlineStr">
         <is>
           <t>Bayrol</t>
         </is>
       </c>
-      <c r="E42" s="30" t="inlineStr">
+      <c r="E42" s="32" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F42" s="30" t="inlineStr">
+      <c r="F42" s="32" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -10701,75 +10731,75 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H42" s="30" t="inlineStr">
+      <c r="H42" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I42" s="30" t="inlineStr">
+      <c r="I42" s="32" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J42" s="30" t="inlineStr">
+      <c r="J42" s="32" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K42" s="30" t="inlineStr">
+      <c r="K42" s="32" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L42" s="30" t="inlineStr">
+      <c r="L42" s="32" t="inlineStr">
         <is>
           <t>BAY-CLN-4134</t>
         </is>
       </c>
-      <c r="M42" s="31" t="inlineStr">
+      <c r="M42" s="33" t="inlineStr">
         <is>
           <t>4008367154134</t>
         </is>
       </c>
-      <c r="N42" s="32" t="inlineStr"/>
-      <c r="O42" s="32" t="inlineStr"/>
-      <c r="P42" s="32" t="inlineStr"/>
-      <c r="Q42" s="30" t="inlineStr">
+      <c r="N42" s="34" t="inlineStr"/>
+      <c r="O42" s="34" t="inlineStr"/>
+      <c r="P42" s="34" t="inlineStr"/>
+      <c r="Q42" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R42" s="30" t="inlineStr">
+      <c r="R42" s="32" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S42" s="30" t="inlineStr">
+      <c r="S42" s="32" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T42" s="30" t="inlineStr">
+      <c r="T42" s="32" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U42" s="30" t="inlineStr">
+      <c r="U42" s="32" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="V42" s="30" t="inlineStr">
+      <c r="V42" s="32" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W42" s="30" t="inlineStr">
+      <c r="W42" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X42" s="30" t="inlineStr">
+      <c r="X42" s="32" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10779,7 +10809,7 @@
           <t>https://www.north-spa.de/wp-content/uploads/2023/02/Produktbild-1-Bayrol-Randfix-07-l-4008367154134.jpg</t>
         </is>
       </c>
-      <c r="Z42" s="30" t="inlineStr">
+      <c r="Z42" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10789,7 +10819,7 @@
           <t>Bayrol Randfix 0,7 l</t>
         </is>
       </c>
-      <c r="AB42" s="30" t="inlineStr">
+      <c r="AB42" s="32" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10801,10 +10831,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF42" s="30" t="inlineStr"/>
-      <c r="AG42" s="30" t="inlineStr"/>
-      <c r="AH42" s="30" t="inlineStr"/>
-      <c r="AI42" s="30" t="inlineStr"/>
+      <c r="AF42" s="32" t="inlineStr"/>
+      <c r="AG42" s="32" t="inlineStr"/>
+      <c r="AH42" s="32" t="inlineStr"/>
+      <c r="AI42" s="32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projects/splashstore/docs/splashstore-scan-curation-260816.xlsx
+++ b/projects/splashstore/docs/splashstore-scan-curation-260816.xlsx
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -152,10 +152,16 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -176,21 +182,6 @@
     <xf numFmtId="49" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -289,16 +280,6 @@
 Three sources agreeing is stronger evidence than one, though both are green.</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>Colour applies to THIS FIELD ONLY, and is judged separately from the photo.
-GREEN = written from the barcode-confirmed page for this exact product.
-YELLOW = written from a name-matched page, so it may describe a variant.
-RED = no description.
-A yellow description beside a green image is normal: the photo was proven by the barcode, the wording was not.
-The cell names the page the wording came from, or says 'generic (from name)' when there was no page at all.</t>
-      </text>
-    </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>Colour applies to THIS FIELD ONLY, and is judged separately from the photo.
@@ -307,15 +288,6 @@
 RED = no description.
 A yellow description beside a green image is normal: the photo was proven by the barcode, the wording was not.
 The cell names the page the wording came from, or says 'generic (from name)' when there was no page at all.</t>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
-      <text>
-        <t>Colour applies to THIS FIELD ONLY.
-GREEN = the barcode was found literally on the page the photo came from.
-YELLOW = the right product, but the photo needs a look (crop, multipack, unclear).
-RED = no usable photo was found.
-The cell names the site the photo came from. Compare it with Description Source: a different site there means the two fields were proven separately.</t>
       </text>
     </comment>
     <comment ref="P1" authorId="0" shapeId="0">
@@ -336,19 +308,7 @@
 RED = missing on an edible product.</t>
       </text>
     </comment>
-    <comment ref="N5" authorId="0" shapeId="0">
-      <text>
-        <t>No source anywhere confirmed this barcode, so the product has no name — and with no name there is nothing to search an image with.
-Identify it by hand: check the packaging, or search the code on the brand's own site.</t>
-      </text>
-    </comment>
     <comment ref="P5" authorId="0" shapeId="0">
-      <text>
-        <t>No source anywhere confirmed this barcode, so the product has no name — and with no name there is nothing to search an image with.
-Identify it by hand: check the packaging, or search the code on the brand's own site.</t>
-      </text>
-    </comment>
-    <comment ref="N16" authorId="0" shapeId="0">
       <text>
         <t>No source anywhere confirmed this barcode, so the product has no name — and with no name there is nothing to search an image with.
 Identify it by hand: check the packaging, or search the code on the brand's own site.</t>
@@ -360,27 +320,11 @@
 Identify it by hand: check the packaging, or search the code on the brand's own site.</t>
       </text>
     </comment>
-    <comment ref="N17" authorId="0" shapeId="0">
-      <text>
-        <t>A photo WAS found and checked against this product's confirmed name.
-The image AI judged it a different product, so it was not used:
-0.85: The image shows a WATER-I.D. DPD No.1 RAPID product with 50 tablets (I; 0.92: The image shows DPD No. 3 tablets, but the claimed product is DPD No. 
-This one wants photographing in the garage, not more searching.</t>
-      </text>
-    </comment>
     <comment ref="P17" authorId="0" shapeId="0">
       <text>
         <t>A photo WAS found and checked against this product's confirmed name.
 The image AI judged it a different product, so it was not used:
 0.85: The image shows a WATER-I.D. DPD No.1 RAPID product with 50 tablets (I; 0.92: The image shows DPD No. 3 tablets, but the claimed product is DPD No. 
-This one wants photographing in the garage, not more searching.</t>
-      </text>
-    </comment>
-    <comment ref="N28" authorId="0" shapeId="0">
-      <text>
-        <t>A photo WAS found and checked against this product's confirmed name.
-The image AI judged it a different product, so it was not used:
-0.85: The image shows a 'Big Sir' spa by Signature Spas, not a product from 
 This one wants photographing in the garage, not more searching.</t>
       </text>
     </comment>
@@ -392,14 +336,6 @@
 This one wants photographing in the garage, not more searching.</t>
       </text>
     </comment>
-    <comment ref="N29" authorId="0" shapeId="0">
-      <text>
-        <t>A photo WAS found and checked against this product's confirmed name.
-The image AI judged it a different product, so it was not used:
-0.97: The image shows a 3D animated purple dinosaur/dragon cartoon character
-This one wants photographing in the garage, not more searching.</t>
-      </text>
-    </comment>
     <comment ref="P29" authorId="0" shapeId="0">
       <text>
         <t>A photo WAS found and checked against this product's confirmed name.
@@ -408,22 +344,10 @@
 This one wants photographing in the garage, not more searching.</t>
       </text>
     </comment>
-    <comment ref="N38" authorId="0" shapeId="0">
-      <text>
-        <t>The product IS identified from its barcode, but no usable photo was found by any source we search: the barcode databases, the barcode directories, an image search on the confirmed name, and eBay.
-Nothing left to try automatically. Photograph it in the garage.</t>
-      </text>
-    </comment>
     <comment ref="P38" authorId="0" shapeId="0">
       <text>
         <t>The product IS identified from its barcode, but no usable photo was found by any source we search: the barcode databases, the barcode directories, an image search on the confirmed name, and eBay.
 Nothing left to try automatically. Photograph it in the garage.</t>
-      </text>
-    </comment>
-    <comment ref="N45" authorId="0" shapeId="0">
-      <text>
-        <t>No source anywhere confirmed this barcode, so the product has no name — and with no name there is nothing to search an image with.
-Identify it by hand: check the packaging, or search the code on the brand's own site.</t>
       </text>
     </comment>
     <comment ref="P45" authorId="0" shapeId="0">
@@ -1930,7 +1854,7 @@
           <t>A cartridge filter for hot tubs and swim spas, measuring 26.0 cm outer diameter, 13.0 cm bottom part, and 3.8 cm inner thread. Compatible with Darlly SC779 and 40372 codes, it captures dirt, grease, and fine particles to keep water clean.</t>
         </is>
       </c>
-      <c r="I2" s="30" t="inlineStr">
+      <c r="I2" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: spa-components.com</t>
         </is>
@@ -1949,13 +1873,13 @@
           <t>https://www.spa-components.com/user/shop/big/1473-1_filter-cartridge-sc779-rising-dragon-plastics--eago-whirlpools.jpg?ff=1&amp;x=1024&amp;y=768&amp;q=85&amp;ts=6720c4a0&amp;sg=161563f2</t>
         </is>
       </c>
-      <c r="P2" s="30" t="inlineStr">
+      <c r="P2" s="21" t="inlineStr">
         <is>
           <t>Verified — barcode: spa-components.com</t>
         </is>
       </c>
-      <c r="Q2" s="21" t="n"/>
-      <c r="R2" s="21" t="inlineStr">
+      <c r="Q2" s="22" t="n"/>
+      <c r="R2" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -1995,7 +1919,7 @@
           <t>A twin pack of Size II replacement filter cartridges measuring 10.6 x 13.6 cm, designed for compatible pool and spa filtration systems. The fine lamellar structure delivers thorough water cleaning and the cartridges are easy to rinse clean.</t>
         </is>
       </c>
-      <c r="I3" s="30" t="inlineStr">
+      <c r="I3" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: bestwaystore.de</t>
         </is>
@@ -2018,13 +1942,13 @@
           <t>https://www.bestwaystore.de/media/c6/f8/ba/1756384660/6941607353615-main-jpg.jpg?ts=1756384660</t>
         </is>
       </c>
-      <c r="P3" s="30" t="inlineStr">
-        <is>
-          <t>Verified — barcode: bestwaystore.de</t>
-        </is>
-      </c>
-      <c r="Q3" s="21" t="n"/>
-      <c r="R3" s="21" t="inlineStr">
+      <c r="P3" s="21" t="inlineStr">
+        <is>
+          <t>Verified — 2 sources (barcode): bestwaystore.de</t>
+        </is>
+      </c>
+      <c r="Q3" s="22" t="n"/>
+      <c r="R3" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -2068,7 +1992,7 @@
           <t>A single Flowclear Size 3 replacement filter cartridge for compatible Bestway pool filtration systems, featuring a fine lamellar structure that traps deposits and dirt effectively. Easy to clean and straightforward to swap out when routine maintenance is due.</t>
         </is>
       </c>
-      <c r="I4" s="30" t="inlineStr">
+      <c r="I4" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: pools.shop</t>
         </is>
@@ -2087,13 +2011,13 @@
           <t>https://ap.nice-cdn.com/upload/image/product/large/default/bestway-flowclear-filter-cartridge-size-3-1-item-638140-en.jpg</t>
         </is>
       </c>
-      <c r="P4" s="30" t="inlineStr">
-        <is>
-          <t>Verified — barcode: pools.shop</t>
-        </is>
-      </c>
-      <c r="Q4" s="21" t="n"/>
-      <c r="R4" s="21" t="inlineStr">
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t>Verified — 2 sources (barcode): pools.shop</t>
+        </is>
+      </c>
+      <c r="Q4" s="22" t="n"/>
+      <c r="R4" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -2116,8 +2040,8 @@
       <c r="E5" s="19" t="inlineStr"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
-      <c r="H5" s="22" t="n"/>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="H5" s="23" t="n"/>
+      <c r="I5" s="23" t="inlineStr">
         <is>
           <t>Blank — missing</t>
         </is>
@@ -2128,13 +2052,13 @@
       <c r="M5" s="4" t="n"/>
       <c r="N5" s="4" t="n"/>
       <c r="O5" s="11" t="n"/>
-      <c r="P5" s="22" t="inlineStr">
+      <c r="P5" s="23" t="inlineStr">
         <is>
           <t>Blank — not identified, cannot search</t>
         </is>
       </c>
-      <c r="Q5" s="21" t="n"/>
-      <c r="R5" s="21" t="inlineStr">
+      <c r="Q5" s="22" t="n"/>
+      <c r="R5" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -2178,7 +2102,7 @@
           <t>A two-pack of compatible hot tub and spa cartridge filters corresponding to Unicel C-4335, Pleatco PRB35-IN, and Filbur FC-2385 references. A handy spare-pair to keep on hand so your tub is never without a fresh filter.</t>
         </is>
       </c>
-      <c r="I6" s="30" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -2197,13 +2121,13 @@
           <t>https://images.barcodelookup.com/29361/293617958-1.jpg</t>
         </is>
       </c>
-      <c r="P6" s="30" t="inlineStr">
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="Q6" s="21" t="n"/>
-      <c r="R6" s="21" t="inlineStr">
+      <c r="Q6" s="22" t="n"/>
+      <c r="R6" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -2243,7 +2167,7 @@
           <t>A single Size IV replacement filter cartridge measuring 14.2 x 25.4 cm, compatible with Bestway filter pump 58391 (9,463 l/h). Its deep-fold, fine-structure media delivers thorough water cleaning and can be rinsed clean with minimal effort.</t>
         </is>
       </c>
-      <c r="I7" s="30" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: bestwaystore.de</t>
         </is>
@@ -2266,13 +2190,13 @@
           <t>https://www.bestwaystore.de/media/53/6c/e9/1756384676/6941607353622-main-jpg.jpg?ts=1756384676</t>
         </is>
       </c>
-      <c r="P7" s="30" t="inlineStr">
-        <is>
-          <t>Verified — barcode: bestwaystore.de</t>
-        </is>
-      </c>
-      <c r="Q7" s="21" t="n"/>
-      <c r="R7" s="21" t="inlineStr">
+      <c r="P7" s="21" t="inlineStr">
+        <is>
+          <t>Verified — 2 sources (barcode): bestwaystore.de</t>
+        </is>
+      </c>
+      <c r="Q7" s="22" t="n"/>
+      <c r="R7" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -2316,7 +2240,7 @@
           <t>A pair of Darlly spa filter cartridges in the SC726 reference, also cross-referenced as Unicel C-4401 and Pleatco PRB17.5SF PR. Buying in pairs means a fresh replacement is always ready when it is time to swap.</t>
         </is>
       </c>
-      <c r="I8" s="30" t="inlineStr">
+      <c r="I8" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -2335,13 +2259,13 @@
           <t>https://images.barcodelookup.com/4378/43786454-1.jpg</t>
         </is>
       </c>
-      <c r="P8" s="31" t="inlineStr">
+      <c r="P8" s="24" t="inlineStr">
         <is>
           <t>Likely — Barcode Lookup (barcode) (unclear)</t>
         </is>
       </c>
-      <c r="Q8" s="21" t="n"/>
-      <c r="R8" s="21" t="inlineStr">
+      <c r="Q8" s="22" t="n"/>
+      <c r="R8" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -2380,12 +2304,12 @@
           <t>Filter cartridge</t>
         </is>
       </c>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="H9" s="25" t="inlineStr">
         <is>
           <t>A replacement spa filter cartridge compatible with Arctic, Beachcomber, Canadian, Hydropool and Jacuzzi spas, sold under cross-reference codes including Unicel C-4950, Pleatco PRB50-IN and Darlly 40506. It keeps hot tub water clean by trapping debris and particles as water cycles through the filtration system.</t>
         </is>
       </c>
-      <c r="I9" s="23" t="inlineStr">
+      <c r="I9" s="25" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -2404,13 +2328,13 @@
           <t>https://images.barcodelookup.com/4469/44699532-1.jpg</t>
         </is>
       </c>
-      <c r="P9" s="31" t="inlineStr">
+      <c r="P9" s="24" t="inlineStr">
         <is>
           <t>Likely — Barcode Lookup (barcode) (unclear)</t>
         </is>
       </c>
-      <c r="Q9" s="21" t="n"/>
-      <c r="R9" s="21" t="inlineStr">
+      <c r="Q9" s="22" t="n"/>
+      <c r="R9" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -2450,7 +2374,7 @@
           <t>A square inflatable hot tub for up to four people, with an overall outer diameter of 2.45 m and a structure measuring 1.75 x 1.75 x 0.71 m, built from high-resistance polyester for good rigidity and durability. The packaged weight is 64.92 kg, so you will want a helper on delivery day.</t>
         </is>
       </c>
-      <c r="I10" s="30" t="inlineStr">
+      <c r="I10" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: intex.fr</t>
         </is>
@@ -2477,13 +2401,13 @@
           <t>https://media.intex.fr/7743-large_default_x2/28464ex-spa-gonflable-calacatta-4-places.jpg</t>
         </is>
       </c>
-      <c r="P10" s="30" t="inlineStr">
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t>Verified — barcode: intex.fr</t>
         </is>
       </c>
-      <c r="Q10" s="21" t="n"/>
-      <c r="R10" s="21" t="inlineStr">
+      <c r="Q10" s="22" t="n"/>
+      <c r="R10" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -2527,7 +2451,7 @@
           <t>A 3.0 kg tub of hth stabiliser granules for outdoor swimming pools, used to protect chlorine from UV degradation and extend its effectiveness. A reliable way to get more mileage from your sanitiser on sunny days.</t>
         </is>
       </c>
-      <c r="I11" s="30" t="inlineStr">
+      <c r="I11" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -2548,13 +2472,13 @@
           <t>https://images.barcodelookup.com/12027/120276177-1.jpg</t>
         </is>
       </c>
-      <c r="P11" s="30" t="inlineStr">
+      <c r="P11" s="21" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="Q11" s="21" t="n"/>
-      <c r="R11" s="21" t="inlineStr">
+      <c r="Q11" s="22" t="n"/>
+      <c r="R11" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -2593,12 +2517,12 @@
           <t>Inflatable spa</t>
         </is>
       </c>
-      <c r="H12" s="23" t="inlineStr">
+      <c r="H12" s="25" t="inlineStr">
         <is>
           <t>A 1-litre bottle of hth Spa Antikalk, formulated to prevent and remove limescale in spa and hot tub water. Keeping scale under control helps protect internal components and maintain water clarity.</t>
         </is>
       </c>
-      <c r="I12" s="23" t="inlineStr">
+      <c r="I12" s="25" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -2617,13 +2541,13 @@
           <t>https://www.north-spa.de/wp-content/uploads/2025/02/Produktbild-1-hth-SPA-ANTIKALK-1-l-3521684700194-360x360.jpg</t>
         </is>
       </c>
-      <c r="P12" s="30" t="inlineStr">
+      <c r="P12" s="21" t="inlineStr">
         <is>
           <t>Verified — barcode: north-spa.de</t>
         </is>
       </c>
-      <c r="Q12" s="21" t="n"/>
-      <c r="R12" s="21" t="inlineStr">
+      <c r="Q12" s="22" t="n"/>
+      <c r="R12" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -2663,7 +2587,7 @@
           <t>A round, olive-green inflatable spa designed to seat up to eight people comfortably, with a maximum water temperature of 40°C. Five accessories are included in the box, so there is plenty to get started with straight away.</t>
         </is>
       </c>
-      <c r="I13" s="30" t="inlineStr">
+      <c r="I13" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: intex.fr</t>
         </is>
@@ -2682,13 +2606,13 @@
           <t>https://media.intex.fr/11990-large_default_x2/28412np-spa-gonflable-olive-8-places.jpg</t>
         </is>
       </c>
-      <c r="P13" s="30" t="inlineStr">
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t>Verified — barcode: intex.fr</t>
         </is>
       </c>
-      <c r="Q13" s="21" t="n"/>
-      <c r="R13" s="21" t="inlineStr">
+      <c r="Q13" s="22" t="n"/>
+      <c r="R13" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -2732,7 +2656,7 @@
           <t>A Darlly SC750 replacement cartridge filter compatible with Arctic, Fonteyn, Rota, and Strong Spa hot tubs, among others. A straightforward like-for-like swap to keep your spa water flowing clean.</t>
         </is>
       </c>
-      <c r="I14" s="30" t="inlineStr">
+      <c r="I14" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -2751,13 +2675,13 @@
           <t>https://images.barcodelookup.com/29338/293384728-1.jpg</t>
         </is>
       </c>
-      <c r="P14" s="30" t="inlineStr">
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="Q14" s="21" t="n"/>
-      <c r="R14" s="21" t="inlineStr">
+      <c r="Q14" s="22" t="n"/>
+      <c r="R14" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -2796,12 +2720,12 @@
           <t>Pool cleaning product</t>
         </is>
       </c>
-      <c r="H15" s="23" t="inlineStr">
+      <c r="H15" s="25" t="inlineStr">
         <is>
           <t>SpaBalancer Clean and Refresh is a spa water treatment product supplied with a sprayer for easy application. It is designed to keep spa water fresh and clean as part of a regular maintenance routine.</t>
         </is>
       </c>
-      <c r="I15" s="23" t="inlineStr">
+      <c r="I15" s="25" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -2820,13 +2744,13 @@
           <t>https://www.spabalancer.ch/media/ae/20/d2/1728651174/sb111_clean-refresh_freigestellt.png?ts=1777362921</t>
         </is>
       </c>
-      <c r="P15" s="30" t="inlineStr">
+      <c r="P15" s="21" t="inlineStr">
         <is>
           <t>Verified — barcode: spabalancer.ch</t>
         </is>
       </c>
-      <c r="Q15" s="21" t="n"/>
-      <c r="R15" s="21" t="inlineStr">
+      <c r="Q15" s="22" t="n"/>
+      <c r="R15" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -2849,8 +2773,8 @@
       <c r="E16" s="19" t="inlineStr"/>
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="3" t="n"/>
-      <c r="H16" s="22" t="n"/>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="H16" s="23" t="n"/>
+      <c r="I16" s="23" t="inlineStr">
         <is>
           <t>Blank — missing</t>
         </is>
@@ -2861,13 +2785,13 @@
       <c r="M16" s="4" t="n"/>
       <c r="N16" s="4" t="n"/>
       <c r="O16" s="11" t="n"/>
-      <c r="P16" s="22" t="inlineStr">
+      <c r="P16" s="23" t="inlineStr">
         <is>
           <t>Blank — not identified, cannot search</t>
         </is>
       </c>
-      <c r="Q16" s="21" t="n"/>
-      <c r="R16" s="21" t="inlineStr">
+      <c r="Q16" s="22" t="n"/>
+      <c r="R16" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -2906,12 +2830,12 @@
           <t>Water test kit</t>
         </is>
       </c>
-      <c r="H17" s="23" t="inlineStr">
+      <c r="H17" s="25" t="inlineStr">
         <is>
           <t>A pack of 500 DPD 1 reagent tablets for use with the Water-ID photometer, measuring free chlorine levels in pool or spa water. Having a full pack to hand means you will not run short mid-season.</t>
         </is>
       </c>
-      <c r="I17" s="23" t="inlineStr">
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -2926,18 +2850,18 @@
       <c r="M17" s="4" t="n"/>
       <c r="N17" s="4" t="n"/>
       <c r="O17" s="11" t="n"/>
-      <c r="P17" s="22" t="inlineStr">
+      <c r="P17" s="23" t="inlineStr">
         <is>
           <t>Blank — found one, wrong product</t>
         </is>
       </c>
-      <c r="Q17" s="21" t="n"/>
-      <c r="R17" s="21" t="inlineStr">
+      <c r="Q17" s="22" t="n"/>
+      <c r="R17" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="S17" s="24" t="inlineStr">
+      <c r="S17" s="26" t="inlineStr">
         <is>
           <t>Water-ID DPD No.1 Rapid Tablets</t>
         </is>
@@ -2975,12 +2899,12 @@
           <t>Water test kit</t>
         </is>
       </c>
-      <c r="H18" s="23" t="inlineStr">
+      <c r="H18" s="25" t="inlineStr">
         <is>
           <t>A pack of 500 Phenol Red reagent tablets compatible with the Water-ID photometer, used for measuring pH levels in pool or spa water. Accurate pH readings are the foundation of balanced, comfortable water.</t>
         </is>
       </c>
-      <c r="I18" s="23" t="inlineStr">
+      <c r="I18" s="25" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -2999,13 +2923,13 @@
           <t>https://www.poolpowershop.de/media/46/63/13/1743521499/phenol-red-testtabletten-fuer-poollab-500-stk.jpg</t>
         </is>
       </c>
-      <c r="P18" s="30" t="inlineStr">
+      <c r="P18" s="21" t="inlineStr">
         <is>
           <t>Verified — barcode: poolpowershop.de</t>
         </is>
       </c>
-      <c r="Q18" s="21" t="n"/>
-      <c r="R18" s="21" t="inlineStr">
+      <c r="Q18" s="22" t="n"/>
+      <c r="R18" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -3049,7 +2973,7 @@
           <t>An alkaline edge and surround cleaner in a 1-litre bottle, formulated to be gentle on pool liners, foils, and plastic surfaces. It tackles waterline grime without harming the materials it touches.</t>
         </is>
       </c>
-      <c r="I19" s="30" t="inlineStr">
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -3068,13 +2992,13 @@
           <t>https://images.barcodelookup.com/21057/210579756-1.jpg</t>
         </is>
       </c>
-      <c r="P19" s="30" t="inlineStr">
+      <c r="P19" s="21" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="Q19" s="21" t="n"/>
-      <c r="R19" s="21" t="inlineStr">
+      <c r="Q19" s="22" t="n"/>
+      <c r="R19" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -3118,7 +3042,7 @@
           <t>A 1-litre pool surface cleaner formulated to remove sunscreen oils and greasy residues from the water surface, designed specifically for warm Mediterranean climates and heavy swimming loads. It keeps the waterline and surface clear without harming pool materials.</t>
         </is>
       </c>
-      <c r="I20" s="30" t="inlineStr">
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: mangas.com.cy</t>
         </is>
@@ -3137,13 +3061,13 @@
           <t>http://mangas.com.cy/media/products/5292638000223.jpg</t>
         </is>
       </c>
-      <c r="P20" s="30" t="inlineStr">
+      <c r="P20" s="21" t="inlineStr">
         <is>
           <t>Verified — barcode: mangas.com.cy</t>
         </is>
       </c>
-      <c r="Q20" s="21" t="n"/>
-      <c r="R20" s="21" t="inlineStr">
+      <c r="Q20" s="22" t="n"/>
+      <c r="R20" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -3187,7 +3111,7 @@
           <t>California Clear Blue is a super-concentrated, pH-neutral pool clarifier in a 1-litre bottle, using a cationic polymer formula to bind microscopic particles such as dust, pollen, and oils into larger clusters your filter can catch. Non-toxic and biodegradable, it is safe for sand, zeolite, and glass filtration media.</t>
         </is>
       </c>
-      <c r="I21" s="30" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: poolservices.cy</t>
         </is>
@@ -3206,13 +3130,13 @@
           <t>https://poolservices.cy/storage/2026/05/California-Clear-Blue-1L-Aquality-2.jpeg</t>
         </is>
       </c>
-      <c r="P21" s="30" t="inlineStr">
+      <c r="P21" s="21" t="inlineStr">
         <is>
           <t>Verified — barcode: poolservices.cy</t>
         </is>
       </c>
-      <c r="Q21" s="21" t="n"/>
-      <c r="R21" s="21" t="inlineStr">
+      <c r="Q21" s="22" t="n"/>
+      <c r="R21" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -3256,7 +3180,7 @@
           <t>A 1-litre tile and vinyl cleaner for pools, designed to clean pool tile surfaces and vinyl liners. It makes light work of the tidying up that keeps a pool looking its best.</t>
         </is>
       </c>
-      <c r="I22" s="30" t="inlineStr">
+      <c r="I22" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: mangas.com.cy</t>
         </is>
@@ -3275,13 +3199,13 @@
           <t>http://mangas.com.cy/media/products/5292638000162.jpg</t>
         </is>
       </c>
-      <c r="P22" s="30" t="inlineStr">
+      <c r="P22" s="21" t="inlineStr">
         <is>
           <t>Verified — barcode: mangas.com.cy</t>
         </is>
       </c>
-      <c r="Q22" s="21" t="n"/>
-      <c r="R22" s="21" t="inlineStr">
+      <c r="Q22" s="22" t="n"/>
+      <c r="R22" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -3320,12 +3244,12 @@
           <t>Inflatable spa</t>
         </is>
       </c>
-      <c r="H23" s="23" t="inlineStr">
+      <c r="H23" s="25" t="inlineStr">
         <is>
           <t>A 1-litre spa and pool water clarifier from Bayzid, formulated to clear cloudy or turbid water. A handy bottle to reach for whenever the water loses its sparkle.</t>
         </is>
       </c>
-      <c r="I23" s="23" t="inlineStr">
+      <c r="I23" s="25" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -3344,13 +3268,13 @@
           <t>https://hoefer-shop.com/cdn/shop/files/1x1L-BAYZID-Spa-Poolclear-v1-RS_1.jpg?v=1785600487&amp;width=800</t>
         </is>
       </c>
-      <c r="P23" s="30" t="inlineStr">
+      <c r="P23" s="21" t="inlineStr">
         <is>
           <t>Verified — barcode: hoefer-shop.com</t>
         </is>
       </c>
-      <c r="Q23" s="21" t="n"/>
-      <c r="R23" s="21" t="inlineStr">
+      <c r="Q23" s="22" t="n"/>
+      <c r="R23" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -3389,12 +3313,12 @@
           <t>Pool chemical</t>
         </is>
       </c>
-      <c r="H24" s="23" t="inlineStr">
+      <c r="H24" s="25" t="inlineStr">
         <is>
           <t>A 1-litre bottle of hydrogen peroxide at 11.9% concentration, suitable for disinfection and water treatment applications. A straightforward chemical solution that keeps things clean without fuss.</t>
         </is>
       </c>
-      <c r="I24" s="23" t="inlineStr">
+      <c r="I24" s="25" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -3413,13 +3337,13 @@
           <t>https://hoefer-shop.com/cdn/shop/files/1x1L-Wasserstoffperoxid-Flasche-hinten-26.jpg?v=1783777627&amp;width=1000</t>
         </is>
       </c>
-      <c r="P24" s="30" t="inlineStr">
+      <c r="P24" s="21" t="inlineStr">
         <is>
           <t>Verified — barcode: hoefer-shop.com</t>
         </is>
       </c>
-      <c r="Q24" s="21" t="n"/>
-      <c r="R24" s="21" t="inlineStr">
+      <c r="Q24" s="22" t="n"/>
+      <c r="R24" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -3458,12 +3382,12 @@
           <t>Pool chemical</t>
         </is>
       </c>
-      <c r="H25" s="23" t="inlineStr">
+      <c r="H25" s="25" t="inlineStr">
         <is>
           <t>A 4.5 kg pack of chlorine stabilizer for swimming pools, used to protect chlorine from UV degradation and extend its effectiveness in the water. Steady chemistry for a pool that earns its keep.</t>
         </is>
       </c>
-      <c r="I25" s="23" t="inlineStr">
+      <c r="I25" s="25" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -3484,13 +3408,13 @@
           <t>https://yokando.com/img/p/2/8/2/9/3/28293.jpg</t>
         </is>
       </c>
-      <c r="P25" s="31" t="inlineStr">
+      <c r="P25" s="24" t="inlineStr">
         <is>
           <t>Likely — image match: yokando.com</t>
         </is>
       </c>
-      <c r="Q25" s="21" t="n"/>
-      <c r="R25" s="21" t="inlineStr">
+      <c r="Q25" s="22" t="n"/>
+      <c r="R25" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -3534,7 +3458,7 @@
           <t>UltraShock is a pool and spa shock treatment from SpaBalancer, designed to rapidly oxidise contaminants and restore water clarity. A quick reset for water that needs a little more persuasion.</t>
         </is>
       </c>
-      <c r="I26" s="30" t="inlineStr">
+      <c r="I26" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -3553,13 +3477,13 @@
           <t>https://images.barcodelookup.com/16704/167043133-1.jpg</t>
         </is>
       </c>
-      <c r="P26" s="30" t="inlineStr">
+      <c r="P26" s="21" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="Q26" s="21" t="n"/>
-      <c r="R26" s="21" t="inlineStr">
+      <c r="Q26" s="22" t="n"/>
+      <c r="R26" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -3599,7 +3523,7 @@
           <t>A patented foam rubber eraser for cleaning pool surfaces, particularly suited to waterline stains on liner and vitreous ceramic finishes, and it works without detergents or chemicals. Each box contains 3 sponges, which harden when wet to scrub effectively while remaining soft and flexible in use.</t>
         </is>
       </c>
-      <c r="I27" s="30" t="inlineStr">
+      <c r="I27" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: piscinarium.com</t>
         </is>
@@ -3618,13 +3542,13 @@
           <t>https://www.piscinarium.com/2908-thickbox_default/pool-gom-magic-rubber-eraser.jpg</t>
         </is>
       </c>
-      <c r="P27" s="30" t="inlineStr">
+      <c r="P27" s="21" t="inlineStr">
         <is>
           <t>Verified — barcode: piscinarium.com</t>
         </is>
       </c>
-      <c r="Q27" s="21" t="n"/>
-      <c r="R27" s="21" t="inlineStr">
+      <c r="Q27" s="22" t="n"/>
+      <c r="R27" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -3659,12 +3583,12 @@
           <t>Inflatable spa</t>
         </is>
       </c>
-      <c r="H28" s="23" t="inlineStr">
+      <c r="H28" s="25" t="inlineStr">
         <is>
           <t>Spa Industries Europe appears to be a brand or supplier name rather than a specific product, so no product details can be confirmed. For accurate information, please check the full product listing.</t>
         </is>
       </c>
-      <c r="I28" s="23" t="inlineStr">
+      <c r="I28" s="25" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -3679,18 +3603,18 @@
       <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="n"/>
       <c r="O28" s="11" t="n"/>
-      <c r="P28" s="22" t="inlineStr">
+      <c r="P28" s="23" t="inlineStr">
         <is>
           <t>Blank — found one, wrong product</t>
         </is>
       </c>
-      <c r="Q28" s="21" t="n"/>
-      <c r="R28" s="21" t="inlineStr">
+      <c r="Q28" s="22" t="n"/>
+      <c r="R28" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="S28" s="24" t="inlineStr">
+      <c r="S28" s="26" t="inlineStr">
         <is>
           <t>Spa Industries Europe | Gouda</t>
         </is>
@@ -3728,12 +3652,12 @@
           <t>Pool cleaning product</t>
         </is>
       </c>
-      <c r="H29" s="23" t="inlineStr">
+      <c r="H29" s="25" t="inlineStr">
         <is>
           <t>A 1-litre high-concentrate sauna cleaner with eucalyptus fragrance, formulated as a deep-cleaning base cleaner for sauna surfaces. The concentrated formula means a little goes a long way, with a fresh scent to match.</t>
         </is>
       </c>
-      <c r="I29" s="23" t="inlineStr">
+      <c r="I29" s="25" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -3748,18 +3672,18 @@
       <c r="M29" s="4" t="n"/>
       <c r="N29" s="4" t="n"/>
       <c r="O29" s="11" t="n"/>
-      <c r="P29" s="22" t="inlineStr">
+      <c r="P29" s="23" t="inlineStr">
         <is>
           <t>Blank — found one, wrong product</t>
         </is>
       </c>
-      <c r="Q29" s="21" t="n"/>
-      <c r="R29" s="21" t="inlineStr">
+      <c r="Q29" s="22" t="n"/>
+      <c r="R29" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
       </c>
-      <c r="S29" s="24" t="inlineStr">
+      <c r="S29" s="26" t="inlineStr">
         <is>
           <t>Deutschland Card Winni / Aixsponza</t>
         </is>
@@ -3802,7 +3726,7 @@
           <t>This HTH spa cleaner removes mineral deposits such as limescale and rust, and cleans and polishes aluminium, chrome, stainless steel, and enamel surfaces with a pleasant pine fragrance. It has a high concentration of active ingredients and is recommended for periodic maintenance cleaning.</t>
         </is>
       </c>
-      <c r="I30" s="30" t="inlineStr">
+      <c r="I30" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: cdiscount.com</t>
         </is>
@@ -3821,13 +3745,13 @@
           <t>https://www.cdiscount.com/pdt2/0/5/1/1/700x700/auc2009356289051/rw/hth-spa-nettoyant-spa-3521686010178.jpg</t>
         </is>
       </c>
-      <c r="P30" s="30" t="inlineStr">
+      <c r="P30" s="21" t="inlineStr">
         <is>
           <t>Verified — barcode: cdiscount.com</t>
         </is>
       </c>
-      <c r="Q30" s="21" t="n"/>
-      <c r="R30" s="21" t="inlineStr">
+      <c r="Q30" s="22" t="n"/>
+      <c r="R30" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -3867,7 +3791,7 @@
           <t>A 25 kg sack of pure boiling salt (minimum 99.6% NaCl) without an anti-caking agent, meeting EN 973 Type A standard and suitable for use in pool salt electrolysis systems. Not intended for human consumption or animal feed.</t>
         </is>
       </c>
-      <c r="I31" s="30" t="inlineStr">
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: altruan.com</t>
         </is>
@@ -3888,17 +3812,17 @@
           <t>http://altruan.com/cdn/shop/files/SalinenPoolSalz25kgSack.png?v=1778597596</t>
         </is>
       </c>
-      <c r="P31" s="30" t="inlineStr">
+      <c r="P31" s="21" t="inlineStr">
         <is>
           <t>Verified — barcode: altruan.com</t>
         </is>
       </c>
-      <c r="Q31" s="21" t="inlineStr">
+      <c r="Q31" s="22" t="inlineStr">
         <is>
           <t>Composition: Siedesalz (min. 99.6% NaCl) 100%; Separant/sodium ferrocyanide 4.0–12.0 mg/kg | Grain: &gt;0.63 mm approx. 20%, 0.2–0.63 mm approx. 75%, &lt;0.2 mm approx. 5% | Moisture: &lt;0.08%</t>
         </is>
       </c>
-      <c r="R31" s="21" t="inlineStr">
+      <c r="R31" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -3937,12 +3861,12 @@
           <t>Pool robot cleaner</t>
         </is>
       </c>
-      <c r="H32" s="23" t="inlineStr">
+      <c r="H32" s="25" t="inlineStr">
         <is>
           <t>A cordless robotic pool cleaner that scrubs both floors and walls automatically, using WavePath navigation to map and cover the pool efficiently. Built-in high-performance filtration and smart control make it a hands-off solution for keeping pool water clear.</t>
         </is>
       </c>
-      <c r="I32" s="23" t="inlineStr">
+      <c r="I32" s="25" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -3961,13 +3885,13 @@
           <t>https://images.barcodelookup.com/176692/1766920801-1.jpg</t>
         </is>
       </c>
-      <c r="P32" s="30" t="inlineStr">
+      <c r="P32" s="21" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="Q32" s="21" t="n"/>
-      <c r="R32" s="21" t="inlineStr">
+      <c r="Q32" s="22" t="n"/>
+      <c r="R32" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -4007,7 +3931,7 @@
           <t>The Scuba L1 EU is a pool cleaning device, though no further specific details about its features, dimensions, or mechanism are available from the product name alone. Buyers should refer to the full product listing for specifications.</t>
         </is>
       </c>
-      <c r="I33" s="30" t="inlineStr">
+      <c r="I33" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -4026,13 +3950,13 @@
           <t>https://images.barcodelookup.com/124722/1247228758-1.jpg</t>
         </is>
       </c>
-      <c r="P33" s="30" t="inlineStr">
+      <c r="P33" s="21" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="Q33" s="21" t="n"/>
-      <c r="R33" s="21" t="inlineStr">
+      <c r="Q33" s="22" t="n"/>
+      <c r="R33" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -4072,7 +3996,7 @@
           <t>The Gre Pools RBR120 is a 51W robotic pool cleaner designed for automatic pool floor cleaning. A reliable workhorse that takes the scrubbing off your hands.</t>
         </is>
       </c>
-      <c r="I34" s="30" t="inlineStr">
+      <c r="I34" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -4091,13 +4015,13 @@
           <t>https://images.barcodelookup.com/124726/1247268298-1.jpg</t>
         </is>
       </c>
-      <c r="P34" s="30" t="inlineStr">
+      <c r="P34" s="21" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="Q34" s="21" t="n"/>
-      <c r="R34" s="21" t="inlineStr">
+      <c r="Q34" s="22" t="n"/>
+      <c r="R34" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -4137,7 +4061,7 @@
           <t>A twin-size inflatable airbed measuring 99 x 191 x 25 cm, built with Fiber-Tech internal construction using polyester fibres for comfort, vinyl sides and base, and a water-resistant flocked top surface with an anti-deflation valve. It supports a maximum weight of 136 kg and packs down compactly when deflated.</t>
         </is>
       </c>
-      <c r="I35" s="30" t="inlineStr">
+      <c r="I35" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: ecoperation.com</t>
         </is>
@@ -4162,13 +4086,13 @@
           <t>https://www.ecoperation.com/media/catalog/product/cache/b76cf1d99a7811daa83ba86e6ad91c89/6/4/64757.jpg</t>
         </is>
       </c>
-      <c r="P35" s="30" t="inlineStr">
+      <c r="P35" s="21" t="inlineStr">
         <is>
           <t>Verified — barcode: ecoperation.com</t>
         </is>
       </c>
-      <c r="Q35" s="21" t="n"/>
-      <c r="R35" s="21" t="inlineStr">
+      <c r="Q35" s="22" t="n"/>
+      <c r="R35" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -4212,7 +4136,7 @@
           <t>A plastic chlorine dosing lock from Steinbach, designed exclusively for use with long-term chlorine tablets, with a 1.5-inch connection fitting. It measures 37 cm in length, 22.5 cm in width, and 15 cm in height, making it a sturdy inline dosing unit for pool water treatment systems.</t>
         </is>
       </c>
-      <c r="I36" s="30" t="inlineStr">
+      <c r="I36" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: ebay.de</t>
         </is>
@@ -4237,13 +4161,13 @@
           <t>https://i.ebayimg.com/images/g/CrUAAeSwkOdqeaRR/s-l400.jpg</t>
         </is>
       </c>
-      <c r="P36" s="30" t="inlineStr">
+      <c r="P36" s="21" t="inlineStr">
         <is>
           <t>Verified — barcode: ebay.de</t>
         </is>
       </c>
-      <c r="Q36" s="21" t="n"/>
-      <c r="R36" s="21" t="inlineStr">
+      <c r="Q36" s="22" t="n"/>
+      <c r="R36" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -4287,7 +4211,7 @@
           <t>A filter cleaning system for hot tub and pool cartridge filters, designed to remove debris and residue efficiently while keeping water usage to a minimum. A practical tool for extending the life of your filter without wasting a drop more than necessary.</t>
         </is>
       </c>
-      <c r="I37" s="30" t="inlineStr">
+      <c r="I37" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: ebay.com</t>
         </is>
@@ -4306,13 +4230,13 @@
           <t>https://i.ebayimg.com/images/g/0e0AAOSweaplqO77/s-l400.jpg</t>
         </is>
       </c>
-      <c r="P37" s="30" t="inlineStr">
+      <c r="P37" s="21" t="inlineStr">
         <is>
           <t>Verified — barcode: ebay.com</t>
         </is>
       </c>
-      <c r="Q37" s="21" t="n"/>
-      <c r="R37" s="21" t="inlineStr">
+      <c r="Q37" s="22" t="n"/>
+      <c r="R37" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -4351,12 +4275,12 @@
           <t>Pool cleaning product</t>
         </is>
       </c>
-      <c r="H38" s="23" t="inlineStr">
+      <c r="H38" s="25" t="inlineStr">
         <is>
           <t>A compact handy scrub brush for pool maintenance, measuring 15 x 9 x 8 cm, suited to scrubbing pool surfaces and hard-to-reach areas. Small enough to manoeuvre easily, and ready to tackle whatever the waterline throws at it.</t>
         </is>
       </c>
-      <c r="I38" s="23" t="inlineStr">
+      <c r="I38" s="25" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -4377,13 +4301,13 @@
       </c>
       <c r="N38" s="4" t="n"/>
       <c r="O38" s="11" t="n"/>
-      <c r="P38" s="22" t="inlineStr">
+      <c r="P38" s="23" t="inlineStr">
         <is>
           <t>Blank — searched, none found</t>
         </is>
       </c>
-      <c r="Q38" s="21" t="n"/>
-      <c r="R38" s="21" t="inlineStr">
+      <c r="Q38" s="22" t="n"/>
+      <c r="R38" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -4427,7 +4351,7 @@
           <t>An inflatable PVC headrest pillow for the Intex inflatable spa (model 28506), measuring 24 x 19 x 6 cm and weighing 0.22 kg, designed to support the head and neck comfortably during use. It attaches to the spa rim and can also be filled with water for added stability.</t>
         </is>
       </c>
-      <c r="I39" s="30" t="inlineStr">
+      <c r="I39" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: rozetka.pl</t>
         </is>
@@ -4454,13 +4378,13 @@
           <t>https://content2.rozetka.com.ua/goods/images/big/570260745.jpg</t>
         </is>
       </c>
-      <c r="P39" s="30" t="inlineStr">
+      <c r="P39" s="21" t="inlineStr">
         <is>
           <t>Verified — barcode: rozetka.pl</t>
         </is>
       </c>
-      <c r="Q39" s="21" t="n"/>
-      <c r="R39" s="21" t="inlineStr">
+      <c r="Q39" s="22" t="n"/>
+      <c r="R39" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -4500,7 +4424,7 @@
           <t>A DPD Pool test kit for active-oxygen pools, containing 20 DPD No. 4 reagent tablets for measuring active oxygen levels and 20 phenol red tablets for measuring pH. Results are read immediately after the tablet dissolves, with an ideal active oxygen range of 3.0 to 8.0 mg/l and a target pH of 7.0 to 7.4.</t>
         </is>
       </c>
-      <c r="I40" s="30" t="inlineStr">
+      <c r="I40" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: carrefour.fr</t>
         </is>
@@ -4519,13 +4443,13 @@
           <t>https://media.carrefour.fr/medias/8f94161f683b4e589024a5b5ebaa6873/p_200x200/cad3db6a00ef414a804b9226119bae96_image.jpg</t>
         </is>
       </c>
-      <c r="P40" s="30" t="inlineStr">
+      <c r="P40" s="21" t="inlineStr">
         <is>
           <t>Verified — barcode: carrefour.fr</t>
         </is>
       </c>
-      <c r="Q40" s="21" t="n"/>
-      <c r="R40" s="21" t="inlineStr">
+      <c r="Q40" s="22" t="n"/>
+      <c r="R40" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -4564,12 +4488,12 @@
           <t>Filter cartridge</t>
         </is>
       </c>
-      <c r="H41" s="23" t="inlineStr">
+      <c r="H41" s="25" t="inlineStr">
         <is>
           <t>A pack of 2 replacement filter cartridges compatible with Intex Type H pool and spa pumps, made by Darlly. Straightforward to swap out, they keep the water moving clean without any complications.</t>
         </is>
       </c>
-      <c r="I41" s="23" t="inlineStr">
+      <c r="I41" s="25" t="inlineStr">
         <is>
           <t>Likely — generic (from name)</t>
         </is>
@@ -4588,13 +4512,13 @@
           <t>https://a.allegroimg.com/original/11923c/a79785a04d36aa54f0d87384f038/Filtracni-kartuse-Intex-D-3BTZ0023-SC828</t>
         </is>
       </c>
-      <c r="P41" s="30" t="inlineStr">
+      <c r="P41" s="21" t="inlineStr">
         <is>
           <t>Verified — barcode: allegro.cz</t>
         </is>
       </c>
-      <c r="Q41" s="21" t="n"/>
-      <c r="R41" s="21" t="inlineStr">
+      <c r="Q41" s="22" t="n"/>
+      <c r="R41" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -4638,7 +4562,7 @@
           <t>A Darlly replacement spa filter cartridge with dimensions of 22 cm diameter by 27 cm height, compatible with SC713 and C-8465 references. A reliable like-for-like swap to keep your spa filtration running smoothly.</t>
         </is>
       </c>
-      <c r="I42" s="30" t="inlineStr">
+      <c r="I42" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -4661,13 +4585,13 @@
           <t>https://images.barcodelookup.com/142259/1422591231-1.jpg</t>
         </is>
       </c>
-      <c r="P42" s="30" t="inlineStr">
+      <c r="P42" s="21" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="Q42" s="21" t="n"/>
-      <c r="R42" s="21" t="inlineStr">
+      <c r="Q42" s="22" t="n"/>
+      <c r="R42" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -4711,7 +4635,7 @@
           <t>A 1 kg pack of 20g multitabs for swimming pools, offering a 5-in-1 treatment that combines multiple water care functions in a single slow-dissolving tablet. Convenient all-in-one dosing that keeps pool maintenance simple.</t>
         </is>
       </c>
-      <c r="I43" s="30" t="inlineStr">
+      <c r="I43" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -4732,13 +4656,13 @@
           <t>https://images.barcodelookup.com/17422/174228560-1.jpg</t>
         </is>
       </c>
-      <c r="P43" s="30" t="inlineStr">
+      <c r="P43" s="21" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
       </c>
-      <c r="Q43" s="21" t="n"/>
-      <c r="R43" s="21" t="inlineStr">
+      <c r="Q43" s="22" t="n"/>
+      <c r="R43" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -4782,7 +4706,7 @@
           <t>A ready-to-use alkaline spray cleaner for removing grease and dirt marks at the waterline of pools and for cleaning skimmers. The spray bottle makes application straightforward, and it can be used on a filled pool on all alkali-resistant surfaces.</t>
         </is>
       </c>
-      <c r="I44" s="30" t="inlineStr">
+      <c r="I44" s="21" t="inlineStr">
         <is>
           <t>Verified — product page: north-spa.de</t>
         </is>
@@ -4803,13 +4727,13 @@
           <t>https://www.north-spa.de/wp-content/uploads/2023/02/Produktbild-1-Bayrol-Randfix-07-l-4008367154134.jpg</t>
         </is>
       </c>
-      <c r="P44" s="30" t="inlineStr">
+      <c r="P44" s="21" t="inlineStr">
         <is>
           <t>Verified — barcode: north-spa.de</t>
         </is>
       </c>
-      <c r="Q44" s="21" t="n"/>
-      <c r="R44" s="21" t="inlineStr">
+      <c r="Q44" s="22" t="n"/>
+      <c r="R44" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -4832,8 +4756,8 @@
       <c r="E45" s="19" t="inlineStr"/>
       <c r="F45" s="3" t="n"/>
       <c r="G45" s="3" t="n"/>
-      <c r="H45" s="22" t="n"/>
-      <c r="I45" s="22" t="inlineStr">
+      <c r="H45" s="23" t="n"/>
+      <c r="I45" s="23" t="inlineStr">
         <is>
           <t>Blank — missing</t>
         </is>
@@ -4844,13 +4768,13 @@
       <c r="M45" s="4" t="n"/>
       <c r="N45" s="4" t="n"/>
       <c r="O45" s="11" t="n"/>
-      <c r="P45" s="22" t="inlineStr">
+      <c r="P45" s="23" t="inlineStr">
         <is>
           <t>Blank — not identified, cannot search</t>
         </is>
       </c>
-      <c r="Q45" s="21" t="n"/>
-      <c r="R45" s="21" t="inlineStr">
+      <c r="Q45" s="22" t="n"/>
+      <c r="R45" s="22" t="inlineStr">
         <is>
           <t>N/A (not edible)</t>
         </is>
@@ -5211,17 +5135,17 @@
           <t>A cartridge filter for hot tubs and swim spas, measuring 26.0 cm outer diameter, 13.0 cm bottom part, and 3.8 cm inner thread. Compatible with Darlly SC779 and 40372 codes, it captures dirt, grease, and fine particles to keep water clean.</t>
         </is>
       </c>
-      <c r="D2" s="32" t="inlineStr">
+      <c r="D2" s="27" t="inlineStr">
         <is>
           <t>Rising Dragon</t>
         </is>
       </c>
-      <c r="E2" s="32" t="inlineStr">
+      <c r="E2" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F2" s="32" t="inlineStr">
+      <c r="F2" s="27" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5231,71 +5155,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H2" s="32" t="inlineStr">
+      <c r="H2" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I2" s="32" t="inlineStr">
+      <c r="I2" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J2" s="32" t="inlineStr">
+      <c r="J2" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K2" s="32" t="inlineStr">
+      <c r="K2" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L2" s="32" t="inlineStr">
+      <c r="L2" s="27" t="inlineStr">
         <is>
           <t>RIS-FIL-2406</t>
         </is>
       </c>
-      <c r="M2" s="33" t="inlineStr">
+      <c r="M2" s="28" t="inlineStr">
         <is>
           <t>700175992406</t>
         </is>
       </c>
-      <c r="N2" s="34" t="inlineStr"/>
-      <c r="O2" s="34" t="inlineStr"/>
-      <c r="P2" s="34" t="inlineStr"/>
-      <c r="Q2" s="32" t="inlineStr">
+      <c r="N2" s="29" t="inlineStr"/>
+      <c r="O2" s="29" t="inlineStr"/>
+      <c r="P2" s="29" t="inlineStr"/>
+      <c r="Q2" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R2" s="32" t="inlineStr">
+      <c r="R2" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S2" s="32" t="inlineStr">
+      <c r="S2" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T2" s="32" t="inlineStr">
+      <c r="T2" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U2" s="32" t="inlineStr"/>
-      <c r="V2" s="32" t="inlineStr">
+      <c r="U2" s="27" t="inlineStr"/>
+      <c r="V2" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W2" s="32" t="inlineStr">
+      <c r="W2" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X2" s="32" t="inlineStr">
+      <c r="X2" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5305,7 +5229,7 @@
           <t>https://www.spa-components.com/user/shop/big/1473-1_filter-cartridge-sc779-rising-dragon-plastics--eago-whirlpools.jpg?ff=1&amp;x=1024&amp;y=768&amp;q=85&amp;ts=6720c4a0&amp;sg=161563f2</t>
         </is>
       </c>
-      <c r="Z2" s="32" t="inlineStr">
+      <c r="Z2" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5315,7 +5239,7 @@
           <t>Filter Cartridge SC779 - Rising Dragon Plastics, EAGO Whirlpools - Spa Components</t>
         </is>
       </c>
-      <c r="AB2" s="32" t="inlineStr">
+      <c r="AB2" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5327,10 +5251,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF2" s="32" t="inlineStr"/>
-      <c r="AG2" s="32" t="inlineStr"/>
-      <c r="AH2" s="32" t="inlineStr"/>
-      <c r="AI2" s="32" t="inlineStr"/>
+      <c r="AF2" s="27" t="inlineStr"/>
+      <c r="AG2" s="27" t="inlineStr"/>
+      <c r="AH2" s="27" t="inlineStr"/>
+      <c r="AI2" s="27" t="inlineStr"/>
     </row>
     <row r="3" ht="62" customHeight="1">
       <c r="A3" s="19" t="inlineStr">
@@ -5348,13 +5272,13 @@
           <t>A twin pack of Size II replacement filter cartridges measuring 10.6 x 13.6 cm, designed for compatible pool and spa filtration systems. The fine lamellar structure delivers thorough water cleaning and the cartridges are easy to rinse clean.</t>
         </is>
       </c>
-      <c r="D3" s="32" t="inlineStr"/>
-      <c r="E3" s="32" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr"/>
+      <c r="E3" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F3" s="32" t="inlineStr">
+      <c r="F3" s="27" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5364,71 +5288,71 @@
           <t>filters, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H3" s="32" t="inlineStr">
+      <c r="H3" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I3" s="32" t="inlineStr">
+      <c r="I3" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J3" s="32" t="inlineStr">
+      <c r="J3" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K3" s="32" t="inlineStr">
+      <c r="K3" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L3" s="32" t="inlineStr">
+      <c r="L3" s="27" t="inlineStr">
         <is>
           <t>GEN-FIL-3615</t>
         </is>
       </c>
-      <c r="M3" s="33" t="inlineStr">
+      <c r="M3" s="28" t="inlineStr">
         <is>
           <t>6941607353615</t>
         </is>
       </c>
-      <c r="N3" s="34" t="inlineStr"/>
-      <c r="O3" s="34" t="inlineStr"/>
-      <c r="P3" s="34" t="inlineStr"/>
-      <c r="Q3" s="32" t="inlineStr">
+      <c r="N3" s="29" t="inlineStr"/>
+      <c r="O3" s="29" t="inlineStr"/>
+      <c r="P3" s="29" t="inlineStr"/>
+      <c r="Q3" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R3" s="32" t="inlineStr">
+      <c r="R3" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S3" s="32" t="inlineStr">
+      <c r="S3" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T3" s="32" t="inlineStr">
+      <c r="T3" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U3" s="32" t="inlineStr"/>
-      <c r="V3" s="32" t="inlineStr">
+      <c r="U3" s="27" t="inlineStr"/>
+      <c r="V3" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W3" s="32" t="inlineStr">
+      <c r="W3" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X3" s="32" t="inlineStr">
+      <c r="X3" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5438,7 +5362,7 @@
           <t>https://www.bestwaystore.de/media/c6/f8/ba/1756384660/6941607353615-main-jpg.jpg?ts=1756384660</t>
         </is>
       </c>
-      <c r="Z3" s="32" t="inlineStr">
+      <c r="Z3" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5448,7 +5372,7 @@
           <t>Filter cartridge Size II double pack, 10.6 x 13.6 cm | 58094_26</t>
         </is>
       </c>
-      <c r="AB3" s="32" t="inlineStr">
+      <c r="AB3" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5460,14 +5384,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF3" s="32" t="inlineStr"/>
-      <c r="AG3" s="32" t="inlineStr"/>
-      <c r="AH3" s="32" t="inlineStr">
+      <c r="AF3" s="27" t="inlineStr"/>
+      <c r="AG3" s="27" t="inlineStr"/>
+      <c r="AH3" s="27" t="inlineStr">
         <is>
           <t>10.6cm</t>
         </is>
       </c>
-      <c r="AI3" s="32" t="inlineStr">
+      <c r="AI3" s="27" t="inlineStr">
         <is>
           <t>13.6cm</t>
         </is>
@@ -5489,17 +5413,17 @@
           <t>A single Flowclear Size 3 replacement filter cartridge for compatible Bestway pool filtration systems, featuring a fine lamellar structure that traps deposits and dirt effectively. Easy to clean and straightforward to swap out when routine maintenance is due.</t>
         </is>
       </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="D4" s="27" t="inlineStr">
         <is>
           <t>Bestway</t>
         </is>
       </c>
-      <c r="E4" s="32" t="inlineStr">
+      <c r="E4" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F4" s="32" t="inlineStr">
+      <c r="F4" s="27" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5509,71 +5433,71 @@
           <t>filters, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H4" s="32" t="inlineStr">
+      <c r="H4" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I4" s="32" t="inlineStr">
+      <c r="I4" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J4" s="32" t="inlineStr">
+      <c r="J4" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K4" s="32" t="inlineStr">
+      <c r="K4" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L4" s="32" t="inlineStr">
+      <c r="L4" s="27" t="inlineStr">
         <is>
           <t>BES-FIL-3592</t>
         </is>
       </c>
-      <c r="M4" s="33" t="inlineStr">
+      <c r="M4" s="28" t="inlineStr">
         <is>
           <t>6941607353592</t>
         </is>
       </c>
-      <c r="N4" s="34" t="inlineStr"/>
-      <c r="O4" s="34" t="inlineStr"/>
-      <c r="P4" s="34" t="inlineStr"/>
-      <c r="Q4" s="32" t="inlineStr">
+      <c r="N4" s="29" t="inlineStr"/>
+      <c r="O4" s="29" t="inlineStr"/>
+      <c r="P4" s="29" t="inlineStr"/>
+      <c r="Q4" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R4" s="32" t="inlineStr">
+      <c r="R4" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S4" s="32" t="inlineStr">
+      <c r="S4" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T4" s="32" t="inlineStr">
+      <c r="T4" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U4" s="32" t="inlineStr"/>
-      <c r="V4" s="32" t="inlineStr">
+      <c r="U4" s="27" t="inlineStr"/>
+      <c r="V4" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W4" s="32" t="inlineStr">
+      <c r="W4" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X4" s="32" t="inlineStr">
+      <c r="X4" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5583,7 +5507,7 @@
           <t>https://ap.nice-cdn.com/upload/image/product/large/default/bestway-flowclear-filter-cartridge-size-3-1-item-638140-en.jpg</t>
         </is>
       </c>
-      <c r="Z4" s="32" t="inlineStr">
+      <c r="Z4" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5593,7 +5517,7 @@
           <t>Bestway Flowclear™ Filter Cartridge Size 3, 1 item</t>
         </is>
       </c>
-      <c r="AB4" s="32" t="inlineStr">
+      <c r="AB4" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5605,10 +5529,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF4" s="32" t="inlineStr"/>
-      <c r="AG4" s="32" t="inlineStr"/>
-      <c r="AH4" s="32" t="inlineStr"/>
-      <c r="AI4" s="32" t="inlineStr"/>
+      <c r="AF4" s="27" t="inlineStr"/>
+      <c r="AG4" s="27" t="inlineStr"/>
+      <c r="AH4" s="27" t="inlineStr"/>
+      <c r="AI4" s="27" t="inlineStr"/>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
@@ -5626,17 +5550,17 @@
           <t>A two-pack of compatible hot tub and spa cartridge filters corresponding to Unicel C-4335, Pleatco PRB35-IN, and Filbur FC-2385 references. A handy spare-pair to keep on hand so your tub is never without a fresh filter.</t>
         </is>
       </c>
-      <c r="D5" s="32" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E5" s="32" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5646,71 +5570,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H5" s="32" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I5" s="32" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J5" s="32" t="inlineStr">
+      <c r="J5" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K5" s="32" t="inlineStr">
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L5" s="32" t="inlineStr">
+      <c r="L5" s="27" t="inlineStr">
         <is>
           <t>DAR-FIL-1669</t>
         </is>
       </c>
-      <c r="M5" s="33" t="inlineStr">
+      <c r="M5" s="28" t="inlineStr">
         <is>
           <t>700175991669</t>
         </is>
       </c>
-      <c r="N5" s="34" t="inlineStr"/>
-      <c r="O5" s="34" t="inlineStr"/>
-      <c r="P5" s="34" t="inlineStr"/>
-      <c r="Q5" s="32" t="inlineStr">
+      <c r="N5" s="29" t="inlineStr"/>
+      <c r="O5" s="29" t="inlineStr"/>
+      <c r="P5" s="29" t="inlineStr"/>
+      <c r="Q5" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R5" s="32" t="inlineStr">
+      <c r="R5" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S5" s="32" t="inlineStr">
+      <c r="S5" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T5" s="32" t="inlineStr">
+      <c r="T5" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U5" s="32" t="inlineStr"/>
-      <c r="V5" s="32" t="inlineStr">
+      <c r="U5" s="27" t="inlineStr"/>
+      <c r="V5" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W5" s="32" t="inlineStr">
+      <c r="W5" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X5" s="32" t="inlineStr">
+      <c r="X5" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5720,7 +5644,7 @@
           <t>https://images.barcodelookup.com/29361/293617958-1.jpg</t>
         </is>
       </c>
-      <c r="Z5" s="32" t="inlineStr">
+      <c r="Z5" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5730,7 +5654,7 @@
           <t>Darlly Hot Tub Spa Filter SC705 40353 Compatible with Unicel C-4335 PRB35-IN Filbur FC-2385 2 Pack</t>
         </is>
       </c>
-      <c r="AB5" s="32" t="inlineStr">
+      <c r="AB5" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5742,10 +5666,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF5" s="32" t="inlineStr"/>
-      <c r="AG5" s="32" t="inlineStr"/>
-      <c r="AH5" s="32" t="inlineStr"/>
-      <c r="AI5" s="32" t="inlineStr"/>
+      <c r="AF5" s="27" t="inlineStr"/>
+      <c r="AG5" s="27" t="inlineStr"/>
+      <c r="AH5" s="27" t="inlineStr"/>
+      <c r="AI5" s="27" t="inlineStr"/>
     </row>
     <row r="6" ht="62" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -5763,13 +5687,13 @@
           <t>A single Size IV replacement filter cartridge measuring 14.2 x 25.4 cm, compatible with Bestway filter pump 58391 (9,463 l/h). Its deep-fold, fine-structure media delivers thorough water cleaning and can be rinsed clean with minimal effort.</t>
         </is>
       </c>
-      <c r="D6" s="32" t="inlineStr"/>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr"/>
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" s="27" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5779,71 +5703,71 @@
           <t>filters, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H6" s="32" t="inlineStr">
+      <c r="H6" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I6" s="32" t="inlineStr">
+      <c r="I6" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J6" s="32" t="inlineStr">
+      <c r="J6" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K6" s="32" t="inlineStr">
+      <c r="K6" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L6" s="32" t="inlineStr">
+      <c r="L6" s="27" t="inlineStr">
         <is>
           <t>GEN-FIL-3622</t>
         </is>
       </c>
-      <c r="M6" s="33" t="inlineStr">
+      <c r="M6" s="28" t="inlineStr">
         <is>
           <t>6941607353622</t>
         </is>
       </c>
-      <c r="N6" s="34" t="inlineStr"/>
-      <c r="O6" s="34" t="inlineStr"/>
-      <c r="P6" s="34" t="inlineStr"/>
-      <c r="Q6" s="32" t="inlineStr">
+      <c r="N6" s="29" t="inlineStr"/>
+      <c r="O6" s="29" t="inlineStr"/>
+      <c r="P6" s="29" t="inlineStr"/>
+      <c r="Q6" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R6" s="32" t="inlineStr">
+      <c r="R6" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S6" s="32" t="inlineStr">
+      <c r="S6" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T6" s="32" t="inlineStr">
+      <c r="T6" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U6" s="32" t="inlineStr"/>
-      <c r="V6" s="32" t="inlineStr">
+      <c r="U6" s="27" t="inlineStr"/>
+      <c r="V6" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W6" s="32" t="inlineStr">
+      <c r="W6" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X6" s="32" t="inlineStr">
+      <c r="X6" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5853,7 +5777,7 @@
           <t>https://www.bestwaystore.de/media/53/6c/e9/1756384676/6941607353622-main-jpg.jpg?ts=1756384676</t>
         </is>
       </c>
-      <c r="Z6" s="32" t="inlineStr">
+      <c r="Z6" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5863,7 +5787,7 @@
           <t>Filter cartridge Size IV 14.2 x 25.4 cm | 58095_26</t>
         </is>
       </c>
-      <c r="AB6" s="32" t="inlineStr">
+      <c r="AB6" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5875,14 +5799,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF6" s="32" t="inlineStr"/>
-      <c r="AG6" s="32" t="inlineStr"/>
-      <c r="AH6" s="32" t="inlineStr">
+      <c r="AF6" s="27" t="inlineStr"/>
+      <c r="AG6" s="27" t="inlineStr"/>
+      <c r="AH6" s="27" t="inlineStr">
         <is>
           <t>14.2cm</t>
         </is>
       </c>
-      <c r="AI6" s="32" t="inlineStr">
+      <c r="AI6" s="27" t="inlineStr">
         <is>
           <t>25.4cm</t>
         </is>
@@ -5904,17 +5828,17 @@
           <t>A pair of Darlly spa filter cartridges in the SC726 reference, also cross-referenced as Unicel C-4401 and Pleatco PRB17.5SF PR. Buying in pairs means a fresh replacement is always ready when it is time to swap.</t>
         </is>
       </c>
-      <c r="D7" s="32" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E7" s="32" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F7" s="32" t="inlineStr">
+      <c r="F7" s="27" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5924,71 +5848,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H7" s="32" t="inlineStr">
+      <c r="H7" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I7" s="32" t="inlineStr">
+      <c r="I7" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J7" s="32" t="inlineStr">
+      <c r="J7" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K7" s="32" t="inlineStr">
+      <c r="K7" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L7" s="32" t="inlineStr">
+      <c r="L7" s="27" t="inlineStr">
         <is>
           <t>DAR-FIL-1874</t>
         </is>
       </c>
-      <c r="M7" s="33" t="inlineStr">
+      <c r="M7" s="28" t="inlineStr">
         <is>
           <t>700175991874</t>
         </is>
       </c>
-      <c r="N7" s="34" t="inlineStr"/>
-      <c r="O7" s="34" t="inlineStr"/>
-      <c r="P7" s="34" t="inlineStr"/>
-      <c r="Q7" s="32" t="inlineStr">
+      <c r="N7" s="29" t="inlineStr"/>
+      <c r="O7" s="29" t="inlineStr"/>
+      <c r="P7" s="29" t="inlineStr"/>
+      <c r="Q7" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R7" s="32" t="inlineStr">
+      <c r="R7" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S7" s="32" t="inlineStr">
+      <c r="S7" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T7" s="32" t="inlineStr">
+      <c r="T7" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U7" s="32" t="inlineStr"/>
-      <c r="V7" s="32" t="inlineStr">
+      <c r="U7" s="27" t="inlineStr"/>
+      <c r="V7" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W7" s="32" t="inlineStr">
+      <c r="W7" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X7" s="32" t="inlineStr">
+      <c r="X7" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5998,7 +5922,7 @@
           <t>https://images.barcodelookup.com/4378/43786454-1.jpg</t>
         </is>
       </c>
-      <c r="Z7" s="32" t="inlineStr">
+      <c r="Z7" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6008,7 +5932,7 @@
           <t>Darlly Spa Filter C-4401, PRB17.5SF PR, SC726 (Pair)</t>
         </is>
       </c>
-      <c r="AB7" s="32" t="inlineStr">
+      <c r="AB7" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6020,10 +5944,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF7" s="32" t="inlineStr"/>
-      <c r="AG7" s="32" t="inlineStr"/>
-      <c r="AH7" s="32" t="inlineStr"/>
-      <c r="AI7" s="32" t="inlineStr"/>
+      <c r="AF7" s="27" t="inlineStr"/>
+      <c r="AG7" s="27" t="inlineStr"/>
+      <c r="AH7" s="27" t="inlineStr"/>
+      <c r="AI7" s="27" t="inlineStr"/>
     </row>
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -6041,17 +5965,17 @@
           <t>A replacement spa filter cartridge compatible with Arctic, Beachcomber, Canadian, Hydropool and Jacuzzi spas, sold under cross-reference codes including Unicel C-4950, Pleatco PRB50-IN and Darlly 40506. It keeps hot tub water clean by trapping debris and particles as water cycles through the filtration system.</t>
         </is>
       </c>
-      <c r="D8" s="32" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E8" s="32" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F8" s="32" t="inlineStr">
+      <c r="F8" s="27" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6061,71 +5985,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H8" s="32" t="inlineStr">
+      <c r="H8" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I8" s="32" t="inlineStr">
+      <c r="I8" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J8" s="32" t="inlineStr">
+      <c r="J8" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K8" s="32" t="inlineStr">
+      <c r="K8" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L8" s="32" t="inlineStr">
+      <c r="L8" s="27" t="inlineStr">
         <is>
           <t>DAR-FIL-1676</t>
         </is>
       </c>
-      <c r="M8" s="33" t="inlineStr">
+      <c r="M8" s="28" t="inlineStr">
         <is>
           <t>700175991676</t>
         </is>
       </c>
-      <c r="N8" s="34" t="inlineStr"/>
-      <c r="O8" s="34" t="inlineStr"/>
-      <c r="P8" s="34" t="inlineStr"/>
-      <c r="Q8" s="32" t="inlineStr">
+      <c r="N8" s="29" t="inlineStr"/>
+      <c r="O8" s="29" t="inlineStr"/>
+      <c r="P8" s="29" t="inlineStr"/>
+      <c r="Q8" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R8" s="32" t="inlineStr">
+      <c r="R8" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S8" s="32" t="inlineStr">
+      <c r="S8" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T8" s="32" t="inlineStr">
+      <c r="T8" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U8" s="32" t="inlineStr"/>
-      <c r="V8" s="32" t="inlineStr">
+      <c r="U8" s="27" t="inlineStr"/>
+      <c r="V8" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W8" s="32" t="inlineStr">
+      <c r="W8" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X8" s="32" t="inlineStr">
+      <c r="X8" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6135,7 +6059,7 @@
           <t>https://images.barcodelookup.com/4469/44699532-1.jpg</t>
         </is>
       </c>
-      <c r="Z8" s="32" t="inlineStr">
+      <c r="Z8" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6145,7 +6069,7 @@
           <t>Hot Tub Filter Unicel C4950 / C-4950 50' Spa Cartridge Pleatco PRB501N Darlly 40506 for Arctic, Beachcomber, Canadian,…</t>
         </is>
       </c>
-      <c r="AB8" s="32" t="inlineStr">
+      <c r="AB8" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6157,10 +6081,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF8" s="32" t="inlineStr"/>
-      <c r="AG8" s="32" t="inlineStr"/>
-      <c r="AH8" s="32" t="inlineStr"/>
-      <c r="AI8" s="32" t="inlineStr"/>
+      <c r="AF8" s="27" t="inlineStr"/>
+      <c r="AG8" s="27" t="inlineStr"/>
+      <c r="AH8" s="27" t="inlineStr"/>
+      <c r="AI8" s="27" t="inlineStr"/>
     </row>
     <row r="9" ht="76" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -6178,13 +6102,13 @@
           <t>A square inflatable hot tub for up to four people, with an overall outer diameter of 2.45 m and a structure measuring 1.75 x 1.75 x 0.71 m, built from high-resistance polyester for good rigidity and durability. The packaged weight is 64.92 kg, so you will want a helper on delivery day.</t>
         </is>
       </c>
-      <c r="D9" s="32" t="inlineStr"/>
-      <c r="E9" s="32" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr"/>
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F9" s="32" t="inlineStr">
+      <c r="F9" s="27" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -6194,75 +6118,75 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H9" s="32" t="inlineStr">
+      <c r="H9" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I9" s="32" t="inlineStr">
+      <c r="I9" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J9" s="32" t="inlineStr">
+      <c r="J9" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K9" s="32" t="inlineStr">
+      <c r="K9" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L9" s="32" t="inlineStr">
+      <c r="L9" s="27" t="inlineStr">
         <is>
           <t>GEN-SPA-3395</t>
         </is>
       </c>
-      <c r="M9" s="33" t="inlineStr">
+      <c r="M9" s="28" t="inlineStr">
         <is>
           <t>6941057423395</t>
         </is>
       </c>
-      <c r="N9" s="34" t="inlineStr"/>
-      <c r="O9" s="34" t="inlineStr"/>
-      <c r="P9" s="34" t="inlineStr"/>
-      <c r="Q9" s="32" t="inlineStr">
+      <c r="N9" s="29" t="inlineStr"/>
+      <c r="O9" s="29" t="inlineStr"/>
+      <c r="P9" s="29" t="inlineStr"/>
+      <c r="Q9" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R9" s="32" t="inlineStr">
+      <c r="R9" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S9" s="32" t="inlineStr">
+      <c r="S9" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T9" s="32" t="inlineStr">
+      <c r="T9" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U9" s="32" t="inlineStr">
+      <c r="U9" s="27" t="inlineStr">
         <is>
           <t>64920</t>
         </is>
       </c>
-      <c r="V9" s="32" t="inlineStr">
+      <c r="V9" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W9" s="32" t="inlineStr">
+      <c r="W9" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X9" s="32" t="inlineStr">
+      <c r="X9" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6272,7 +6196,7 @@
           <t>https://media.intex.fr/7743-large_default_x2/28464ex-spa-gonflable-calacatta-4-places.jpg</t>
         </is>
       </c>
-      <c r="Z9" s="32" t="inlineStr">
+      <c r="Z9" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6282,7 +6206,7 @@
           <t>Calacatta 4-person inflatable spa</t>
         </is>
       </c>
-      <c r="AB9" s="32" t="inlineStr">
+      <c r="AB9" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6294,18 +6218,18 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF9" s="32" t="inlineStr"/>
-      <c r="AG9" s="32" t="inlineStr">
+      <c r="AF9" s="27" t="inlineStr"/>
+      <c r="AG9" s="27" t="inlineStr">
         <is>
           <t>175.0cm</t>
         </is>
       </c>
-      <c r="AH9" s="32" t="inlineStr">
+      <c r="AH9" s="27" t="inlineStr">
         <is>
           <t>175.0cm</t>
         </is>
       </c>
-      <c r="AI9" s="32" t="inlineStr">
+      <c r="AI9" s="27" t="inlineStr">
         <is>
           <t>71.0cm</t>
         </is>
@@ -6327,17 +6251,17 @@
           <t>A 3.0 kg tub of hth stabiliser granules for outdoor swimming pools, used to protect chlorine from UV degradation and extend its effectiveness. A reliable way to get more mileage from your sanitiser on sunny days.</t>
         </is>
       </c>
-      <c r="D10" s="32" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E10" s="32" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F10" s="32" t="inlineStr">
+      <c r="F10" s="27" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -6347,75 +6271,75 @@
           <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H10" s="32" t="inlineStr">
+      <c r="H10" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I10" s="32" t="inlineStr">
+      <c r="I10" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J10" s="32" t="inlineStr">
+      <c r="J10" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K10" s="32" t="inlineStr">
+      <c r="K10" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L10" s="32" t="inlineStr">
+      <c r="L10" s="27" t="inlineStr">
         <is>
           <t>HTH-CHM-5716</t>
         </is>
       </c>
-      <c r="M10" s="33" t="inlineStr">
+      <c r="M10" s="28" t="inlineStr">
         <is>
           <t>3521686005716</t>
         </is>
       </c>
-      <c r="N10" s="34" t="inlineStr"/>
-      <c r="O10" s="34" t="inlineStr"/>
-      <c r="P10" s="34" t="inlineStr"/>
-      <c r="Q10" s="32" t="inlineStr">
+      <c r="N10" s="29" t="inlineStr"/>
+      <c r="O10" s="29" t="inlineStr"/>
+      <c r="P10" s="29" t="inlineStr"/>
+      <c r="Q10" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R10" s="32" t="inlineStr">
+      <c r="R10" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S10" s="32" t="inlineStr">
+      <c r="S10" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T10" s="32" t="inlineStr">
+      <c r="T10" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U10" s="32" t="inlineStr">
+      <c r="U10" s="27" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="V10" s="32" t="inlineStr">
+      <c r="V10" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W10" s="32" t="inlineStr">
+      <c r="W10" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X10" s="32" t="inlineStr">
+      <c r="X10" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6425,7 +6349,7 @@
           <t>https://images.barcodelookup.com/12027/120276177-1.jpg</t>
         </is>
       </c>
-      <c r="Z10" s="32" t="inlineStr">
+      <c r="Z10" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6435,7 +6359,7 @@
           <t>Hth Stabilizer Granulat 3,0 Kg</t>
         </is>
       </c>
-      <c r="AB10" s="32" t="inlineStr">
+      <c r="AB10" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6447,10 +6371,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF10" s="32" t="inlineStr"/>
-      <c r="AG10" s="32" t="inlineStr"/>
-      <c r="AH10" s="32" t="inlineStr"/>
-      <c r="AI10" s="32" t="inlineStr"/>
+      <c r="AF10" s="27" t="inlineStr"/>
+      <c r="AG10" s="27" t="inlineStr"/>
+      <c r="AH10" s="27" t="inlineStr"/>
+      <c r="AI10" s="27" t="inlineStr"/>
     </row>
     <row r="11" ht="62" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -6468,17 +6392,17 @@
           <t>A 1-litre bottle of hth Spa Antikalk, formulated to prevent and remove limescale in spa and hot tub water. Keeping scale under control helps protect internal components and maintain water clarity.</t>
         </is>
       </c>
-      <c r="D11" s="32" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E11" s="32" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F11" s="32" t="inlineStr">
+      <c r="F11" s="27" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -6488,71 +6412,71 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H11" s="32" t="inlineStr">
+      <c r="H11" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I11" s="32" t="inlineStr">
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J11" s="32" t="inlineStr">
+      <c r="J11" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K11" s="32" t="inlineStr">
+      <c r="K11" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L11" s="32" t="inlineStr">
+      <c r="L11" s="27" t="inlineStr">
         <is>
           <t>HTH-SPA-0194</t>
         </is>
       </c>
-      <c r="M11" s="33" t="inlineStr">
+      <c r="M11" s="28" t="inlineStr">
         <is>
           <t>3521684700194</t>
         </is>
       </c>
-      <c r="N11" s="34" t="inlineStr"/>
-      <c r="O11" s="34" t="inlineStr"/>
-      <c r="P11" s="34" t="inlineStr"/>
-      <c r="Q11" s="32" t="inlineStr">
+      <c r="N11" s="29" t="inlineStr"/>
+      <c r="O11" s="29" t="inlineStr"/>
+      <c r="P11" s="29" t="inlineStr"/>
+      <c r="Q11" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R11" s="32" t="inlineStr">
+      <c r="R11" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S11" s="32" t="inlineStr">
+      <c r="S11" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T11" s="32" t="inlineStr">
+      <c r="T11" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U11" s="32" t="inlineStr"/>
-      <c r="V11" s="32" t="inlineStr">
+      <c r="U11" s="27" t="inlineStr"/>
+      <c r="V11" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W11" s="32" t="inlineStr">
+      <c r="W11" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X11" s="32" t="inlineStr">
+      <c r="X11" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6562,7 +6486,7 @@
           <t>https://www.north-spa.de/wp-content/uploads/2025/02/Produktbild-1-hth-SPA-ANTIKALK-1-l-3521684700194-360x360.jpg</t>
         </is>
       </c>
-      <c r="Z11" s="32" t="inlineStr">
+      <c r="Z11" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6572,7 +6496,7 @@
           <t>1 l - hth® Spa ANTIKALK</t>
         </is>
       </c>
-      <c r="AB11" s="32" t="inlineStr">
+      <c r="AB11" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6584,10 +6508,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF11" s="32" t="inlineStr"/>
-      <c r="AG11" s="32" t="inlineStr"/>
-      <c r="AH11" s="32" t="inlineStr"/>
-      <c r="AI11" s="32" t="inlineStr"/>
+      <c r="AF11" s="27" t="inlineStr"/>
+      <c r="AG11" s="27" t="inlineStr"/>
+      <c r="AH11" s="27" t="inlineStr"/>
+      <c r="AI11" s="27" t="inlineStr"/>
     </row>
     <row r="12" ht="62" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -6605,13 +6529,13 @@
           <t>A round, olive-green inflatable spa designed to seat up to eight people comfortably, with a maximum water temperature of 40°C. Five accessories are included in the box, so there is plenty to get started with straight away.</t>
         </is>
       </c>
-      <c r="D12" s="32" t="inlineStr"/>
-      <c r="E12" s="32" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr"/>
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F12" s="32" t="inlineStr">
+      <c r="F12" s="27" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -6621,71 +6545,71 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H12" s="32" t="inlineStr">
+      <c r="H12" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I12" s="32" t="inlineStr">
+      <c r="I12" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J12" s="32" t="inlineStr">
+      <c r="J12" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K12" s="32" t="inlineStr">
+      <c r="K12" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L12" s="32" t="inlineStr">
+      <c r="L12" s="27" t="inlineStr">
         <is>
           <t>GEN-SPA-9274</t>
         </is>
       </c>
-      <c r="M12" s="33" t="inlineStr">
+      <c r="M12" s="28" t="inlineStr">
         <is>
           <t>6941057429274</t>
         </is>
       </c>
-      <c r="N12" s="34" t="inlineStr"/>
-      <c r="O12" s="34" t="inlineStr"/>
-      <c r="P12" s="34" t="inlineStr"/>
-      <c r="Q12" s="32" t="inlineStr">
+      <c r="N12" s="29" t="inlineStr"/>
+      <c r="O12" s="29" t="inlineStr"/>
+      <c r="P12" s="29" t="inlineStr"/>
+      <c r="Q12" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R12" s="32" t="inlineStr">
+      <c r="R12" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S12" s="32" t="inlineStr">
+      <c r="S12" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T12" s="32" t="inlineStr">
+      <c r="T12" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U12" s="32" t="inlineStr"/>
-      <c r="V12" s="32" t="inlineStr">
+      <c r="U12" s="27" t="inlineStr"/>
+      <c r="V12" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W12" s="32" t="inlineStr">
+      <c r="W12" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X12" s="32" t="inlineStr">
+      <c r="X12" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6695,7 +6619,7 @@
           <t>https://media.intex.fr/11990-large_default_x2/28412np-spa-gonflable-olive-8-places.jpg</t>
         </is>
       </c>
-      <c r="Z12" s="32" t="inlineStr">
+      <c r="Z12" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6705,7 +6629,7 @@
           <t>Olive 8-person inflatable spa</t>
         </is>
       </c>
-      <c r="AB12" s="32" t="inlineStr">
+      <c r="AB12" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6717,10 +6641,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF12" s="32" t="inlineStr"/>
-      <c r="AG12" s="32" t="inlineStr"/>
-      <c r="AH12" s="32" t="inlineStr"/>
-      <c r="AI12" s="32" t="inlineStr"/>
+      <c r="AF12" s="27" t="inlineStr"/>
+      <c r="AG12" s="27" t="inlineStr"/>
+      <c r="AH12" s="27" t="inlineStr"/>
+      <c r="AI12" s="27" t="inlineStr"/>
     </row>
     <row r="13" ht="62" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -6738,17 +6662,17 @@
           <t>A Darlly SC750 replacement cartridge filter compatible with Arctic, Fonteyn, Rota, and Strong Spa hot tubs, among others. A straightforward like-for-like swap to keep your spa water flowing clean.</t>
         </is>
       </c>
-      <c r="D13" s="32" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E13" s="32" t="inlineStr">
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F13" s="32" t="inlineStr">
+      <c r="F13" s="27" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6758,71 +6682,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H13" s="32" t="inlineStr">
+      <c r="H13" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I13" s="32" t="inlineStr">
+      <c r="I13" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J13" s="32" t="inlineStr">
+      <c r="J13" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K13" s="32" t="inlineStr">
+      <c r="K13" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L13" s="32" t="inlineStr">
+      <c r="L13" s="27" t="inlineStr">
         <is>
           <t>DAR-FIL-2116</t>
         </is>
       </c>
-      <c r="M13" s="33" t="inlineStr">
+      <c r="M13" s="28" t="inlineStr">
         <is>
           <t>700175992116</t>
         </is>
       </c>
-      <c r="N13" s="34" t="inlineStr"/>
-      <c r="O13" s="34" t="inlineStr"/>
-      <c r="P13" s="34" t="inlineStr"/>
-      <c r="Q13" s="32" t="inlineStr">
+      <c r="N13" s="29" t="inlineStr"/>
+      <c r="O13" s="29" t="inlineStr"/>
+      <c r="P13" s="29" t="inlineStr"/>
+      <c r="Q13" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R13" s="32" t="inlineStr">
+      <c r="R13" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S13" s="32" t="inlineStr">
+      <c r="S13" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T13" s="32" t="inlineStr">
+      <c r="T13" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U13" s="32" t="inlineStr"/>
-      <c r="V13" s="32" t="inlineStr">
+      <c r="U13" s="27" t="inlineStr"/>
+      <c r="V13" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W13" s="32" t="inlineStr">
+      <c r="W13" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X13" s="32" t="inlineStr">
+      <c r="X13" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6832,7 +6756,7 @@
           <t>https://images.barcodelookup.com/29338/293384728-1.jpg</t>
         </is>
       </c>
-      <c r="Z13" s="32" t="inlineStr">
+      <c r="Z13" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6842,7 +6766,7 @@
           <t>SC750 Filter replacement filter lamellar filter Arctic Fonteyn Rota Strong Spa - Darlly</t>
         </is>
       </c>
-      <c r="AB13" s="32" t="inlineStr">
+      <c r="AB13" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6854,10 +6778,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF13" s="32" t="inlineStr"/>
-      <c r="AG13" s="32" t="inlineStr"/>
-      <c r="AH13" s="32" t="inlineStr"/>
-      <c r="AI13" s="32" t="inlineStr"/>
+      <c r="AF13" s="27" t="inlineStr"/>
+      <c r="AG13" s="27" t="inlineStr"/>
+      <c r="AH13" s="27" t="inlineStr"/>
+      <c r="AI13" s="27" t="inlineStr"/>
     </row>
     <row r="14" ht="62" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -6875,17 +6799,17 @@
           <t>SpaBalancer Clean and Refresh is a spa water treatment product supplied with a sprayer for easy application. It is designed to keep spa water fresh and clean as part of a regular maintenance routine.</t>
         </is>
       </c>
-      <c r="D14" s="32" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>SpaBalancer</t>
         </is>
       </c>
-      <c r="E14" s="32" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F14" s="32" t="inlineStr">
+      <c r="F14" s="27" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -6895,71 +6819,71 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H14" s="32" t="inlineStr">
+      <c r="H14" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I14" s="32" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J14" s="32" t="inlineStr">
+      <c r="J14" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K14" s="32" t="inlineStr">
+      <c r="K14" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L14" s="32" t="inlineStr">
+      <c r="L14" s="27" t="inlineStr">
         <is>
           <t>SPA-CLN-0117</t>
         </is>
       </c>
-      <c r="M14" s="33" t="inlineStr">
+      <c r="M14" s="28" t="inlineStr">
         <is>
           <t>4260374980117</t>
         </is>
       </c>
-      <c r="N14" s="34" t="inlineStr"/>
-      <c r="O14" s="34" t="inlineStr"/>
-      <c r="P14" s="34" t="inlineStr"/>
-      <c r="Q14" s="32" t="inlineStr">
+      <c r="N14" s="29" t="inlineStr"/>
+      <c r="O14" s="29" t="inlineStr"/>
+      <c r="P14" s="29" t="inlineStr"/>
+      <c r="Q14" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R14" s="32" t="inlineStr">
+      <c r="R14" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S14" s="32" t="inlineStr">
+      <c r="S14" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T14" s="32" t="inlineStr">
+      <c r="T14" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U14" s="32" t="inlineStr"/>
-      <c r="V14" s="32" t="inlineStr">
+      <c r="U14" s="27" t="inlineStr"/>
+      <c r="V14" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W14" s="32" t="inlineStr">
+      <c r="W14" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X14" s="32" t="inlineStr">
+      <c r="X14" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6969,7 +6893,7 @@
           <t>https://www.spabalancer.ch/media/ae/20/d2/1728651174/sb111_clean-refresh_freigestellt.png?ts=1777362921</t>
         </is>
       </c>
-      <c r="Z14" s="32" t="inlineStr">
+      <c r="Z14" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6979,7 +6903,7 @@
           <t>SpaBalancer Clean &amp; Refresh (+ sprayer)</t>
         </is>
       </c>
-      <c r="AB14" s="32" t="inlineStr">
+      <c r="AB14" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6991,10 +6915,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF14" s="32" t="inlineStr"/>
-      <c r="AG14" s="32" t="inlineStr"/>
-      <c r="AH14" s="32" t="inlineStr"/>
-      <c r="AI14" s="32" t="inlineStr"/>
+      <c r="AF14" s="27" t="inlineStr"/>
+      <c r="AG14" s="27" t="inlineStr"/>
+      <c r="AH14" s="27" t="inlineStr"/>
+      <c r="AI14" s="27" t="inlineStr"/>
     </row>
     <row r="15" ht="62" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -7012,17 +6936,17 @@
           <t>A pack of 500 DPD 1 reagent tablets for use with the Water-ID photometer, measuring free chlorine levels in pool or spa water. Having a full pack to hand means you will not run short mid-season.</t>
         </is>
       </c>
-      <c r="D15" s="32" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Water-i.d.</t>
         </is>
       </c>
-      <c r="E15" s="32" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F15" s="32" t="inlineStr">
+      <c r="F15" s="27" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -7032,79 +6956,79 @@
           <t>test-measure, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H15" s="32" t="inlineStr">
+      <c r="H15" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I15" s="32" t="inlineStr">
+      <c r="I15" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J15" s="32" t="inlineStr">
+      <c r="J15" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K15" s="32" t="inlineStr">
+      <c r="K15" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L15" s="32" t="inlineStr">
+      <c r="L15" s="27" t="inlineStr">
         <is>
           <t>WAT-TST-1702</t>
         </is>
       </c>
-      <c r="M15" s="33" t="inlineStr">
+      <c r="M15" s="28" t="inlineStr">
         <is>
           <t>4260431461702</t>
         </is>
       </c>
-      <c r="N15" s="34" t="inlineStr"/>
-      <c r="O15" s="34" t="inlineStr"/>
-      <c r="P15" s="34" t="inlineStr"/>
-      <c r="Q15" s="32" t="inlineStr">
+      <c r="N15" s="29" t="inlineStr"/>
+      <c r="O15" s="29" t="inlineStr"/>
+      <c r="P15" s="29" t="inlineStr"/>
+      <c r="Q15" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R15" s="32" t="inlineStr">
+      <c r="R15" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S15" s="32" t="inlineStr">
+      <c r="S15" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T15" s="32" t="inlineStr">
+      <c r="T15" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U15" s="32" t="inlineStr"/>
-      <c r="V15" s="32" t="inlineStr">
+      <c r="U15" s="27" t="inlineStr"/>
+      <c r="V15" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W15" s="32" t="inlineStr">
+      <c r="W15" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X15" s="32" t="inlineStr">
+      <c r="X15" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y15" s="19" t="inlineStr"/>
-      <c r="Z15" s="32" t="inlineStr"/>
+      <c r="Z15" s="27" t="inlineStr"/>
       <c r="AA15" s="19" t="inlineStr"/>
-      <c r="AB15" s="32" t="inlineStr">
+      <c r="AB15" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7116,10 +7040,10 @@
           <t>Pool Accessories</t>
         </is>
       </c>
-      <c r="AF15" s="32" t="inlineStr"/>
-      <c r="AG15" s="32" t="inlineStr"/>
-      <c r="AH15" s="32" t="inlineStr"/>
-      <c r="AI15" s="32" t="inlineStr"/>
+      <c r="AF15" s="27" t="inlineStr"/>
+      <c r="AG15" s="27" t="inlineStr"/>
+      <c r="AH15" s="27" t="inlineStr"/>
+      <c r="AI15" s="27" t="inlineStr"/>
     </row>
     <row r="16" ht="62" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -7137,17 +7061,17 @@
           <t>A pack of 500 Phenol Red reagent tablets compatible with the Water-ID photometer, used for measuring pH levels in pool or spa water. Accurate pH readings are the foundation of balanced, comfortable water.</t>
         </is>
       </c>
-      <c r="D16" s="32" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>Water-i.d.</t>
         </is>
       </c>
-      <c r="E16" s="32" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F16" s="32" t="inlineStr">
+      <c r="F16" s="27" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -7157,71 +7081,71 @@
           <t>test-measure, add-on, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H16" s="32" t="inlineStr">
+      <c r="H16" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I16" s="32" t="inlineStr">
+      <c r="I16" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J16" s="32" t="inlineStr">
+      <c r="J16" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K16" s="32" t="inlineStr">
+      <c r="K16" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L16" s="32" t="inlineStr">
+      <c r="L16" s="27" t="inlineStr">
         <is>
           <t>WAT-TST-1801</t>
         </is>
       </c>
-      <c r="M16" s="33" t="inlineStr">
+      <c r="M16" s="28" t="inlineStr">
         <is>
           <t>4260431461801</t>
         </is>
       </c>
-      <c r="N16" s="34" t="inlineStr"/>
-      <c r="O16" s="34" t="inlineStr"/>
-      <c r="P16" s="34" t="inlineStr"/>
-      <c r="Q16" s="32" t="inlineStr">
+      <c r="N16" s="29" t="inlineStr"/>
+      <c r="O16" s="29" t="inlineStr"/>
+      <c r="P16" s="29" t="inlineStr"/>
+      <c r="Q16" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R16" s="32" t="inlineStr">
+      <c r="R16" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S16" s="32" t="inlineStr">
+      <c r="S16" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T16" s="32" t="inlineStr">
+      <c r="T16" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U16" s="32" t="inlineStr"/>
-      <c r="V16" s="32" t="inlineStr">
+      <c r="U16" s="27" t="inlineStr"/>
+      <c r="V16" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W16" s="32" t="inlineStr">
+      <c r="W16" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X16" s="32" t="inlineStr">
+      <c r="X16" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7231,7 +7155,7 @@
           <t>https://www.poolpowershop.de/media/46/63/13/1743521499/phenol-red-testtabletten-fuer-poollab-500-stk.jpg</t>
         </is>
       </c>
-      <c r="Z16" s="32" t="inlineStr">
+      <c r="Z16" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7241,7 +7165,7 @@
           <t>WATER-I.D. Water-ID Reagenzien Phenol Red Photometer 500</t>
         </is>
       </c>
-      <c r="AB16" s="32" t="inlineStr">
+      <c r="AB16" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7253,10 +7177,10 @@
           <t>Pool Accessories</t>
         </is>
       </c>
-      <c r="AF16" s="32" t="inlineStr"/>
-      <c r="AG16" s="32" t="inlineStr"/>
-      <c r="AH16" s="32" t="inlineStr"/>
-      <c r="AI16" s="32" t="inlineStr"/>
+      <c r="AF16" s="27" t="inlineStr"/>
+      <c r="AG16" s="27" t="inlineStr"/>
+      <c r="AH16" s="27" t="inlineStr"/>
+      <c r="AI16" s="27" t="inlineStr"/>
     </row>
     <row r="17" ht="62" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -7274,17 +7198,17 @@
           <t>An alkaline edge and surround cleaner in a 1-litre bottle, formulated to be gentle on pool liners, foils, and plastic surfaces. It tackles waterline grime without harming the materials it touches.</t>
         </is>
       </c>
-      <c r="D17" s="32" t="inlineStr">
+      <c r="D17" s="27" t="inlineStr">
         <is>
           <t>Cristal</t>
         </is>
       </c>
-      <c r="E17" s="32" t="inlineStr">
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F17" s="32" t="inlineStr">
+      <c r="F17" s="27" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -7294,71 +7218,71 @@
           <t>pool, water-treatment, cleaning, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H17" s="32" t="inlineStr">
+      <c r="H17" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I17" s="32" t="inlineStr">
+      <c r="I17" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J17" s="32" t="inlineStr">
+      <c r="J17" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K17" s="32" t="inlineStr">
+      <c r="K17" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L17" s="32" t="inlineStr">
+      <c r="L17" s="27" t="inlineStr">
         <is>
           <t>CRI-CHM-5212</t>
         </is>
       </c>
-      <c r="M17" s="33" t="inlineStr">
+      <c r="M17" s="28" t="inlineStr">
         <is>
           <t>4002369155212</t>
         </is>
       </c>
-      <c r="N17" s="34" t="inlineStr"/>
-      <c r="O17" s="34" t="inlineStr"/>
-      <c r="P17" s="34" t="inlineStr"/>
-      <c r="Q17" s="32" t="inlineStr">
+      <c r="N17" s="29" t="inlineStr"/>
+      <c r="O17" s="29" t="inlineStr"/>
+      <c r="P17" s="29" t="inlineStr"/>
+      <c r="Q17" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R17" s="32" t="inlineStr">
+      <c r="R17" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S17" s="32" t="inlineStr">
+      <c r="S17" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T17" s="32" t="inlineStr">
+      <c r="T17" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U17" s="32" t="inlineStr"/>
-      <c r="V17" s="32" t="inlineStr">
+      <c r="U17" s="27" t="inlineStr"/>
+      <c r="V17" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W17" s="32" t="inlineStr">
+      <c r="W17" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X17" s="32" t="inlineStr">
+      <c r="X17" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7368,7 +7292,7 @@
           <t>https://images.barcodelookup.com/21057/210579756-1.jpg</t>
         </is>
       </c>
-      <c r="Z17" s="32" t="inlineStr">
+      <c r="Z17" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7378,7 +7302,7 @@
           <t>Cristal Poolpflege CRISTAL edge cleaner alkaline 1,0 l, (material-safe, for liners, plastic</t>
         </is>
       </c>
-      <c r="AB17" s="32" t="inlineStr">
+      <c r="AB17" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7390,10 +7314,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF17" s="32" t="inlineStr"/>
-      <c r="AG17" s="32" t="inlineStr"/>
-      <c r="AH17" s="32" t="inlineStr"/>
-      <c r="AI17" s="32" t="inlineStr"/>
+      <c r="AF17" s="27" t="inlineStr"/>
+      <c r="AG17" s="27" t="inlineStr"/>
+      <c r="AH17" s="27" t="inlineStr"/>
+      <c r="AI17" s="27" t="inlineStr"/>
     </row>
     <row r="18" ht="76" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -7411,17 +7335,17 @@
           <t>A 1-litre pool surface cleaner formulated to remove sunscreen oils and greasy residues from the water surface, designed specifically for warm Mediterranean climates and heavy swimming loads. It keeps the waterline and surface clear without harming pool materials.</t>
         </is>
       </c>
-      <c r="D18" s="32" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E18" s="32" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F18" s="32" t="inlineStr">
+      <c r="F18" s="27" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -7431,71 +7355,71 @@
           <t>pool, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H18" s="32" t="inlineStr">
+      <c r="H18" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I18" s="32" t="inlineStr">
+      <c r="I18" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J18" s="32" t="inlineStr">
+      <c r="J18" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K18" s="32" t="inlineStr">
+      <c r="K18" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L18" s="32" t="inlineStr">
+      <c r="L18" s="27" t="inlineStr">
         <is>
           <t>AQU-CLN-0223</t>
         </is>
       </c>
-      <c r="M18" s="33" t="inlineStr">
+      <c r="M18" s="28" t="inlineStr">
         <is>
           <t>5292638000223</t>
         </is>
       </c>
-      <c r="N18" s="34" t="inlineStr"/>
-      <c r="O18" s="34" t="inlineStr"/>
-      <c r="P18" s="34" t="inlineStr"/>
-      <c r="Q18" s="32" t="inlineStr">
+      <c r="N18" s="29" t="inlineStr"/>
+      <c r="O18" s="29" t="inlineStr"/>
+      <c r="P18" s="29" t="inlineStr"/>
+      <c r="Q18" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R18" s="32" t="inlineStr">
+      <c r="R18" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S18" s="32" t="inlineStr">
+      <c r="S18" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T18" s="32" t="inlineStr">
+      <c r="T18" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U18" s="32" t="inlineStr"/>
-      <c r="V18" s="32" t="inlineStr">
+      <c r="U18" s="27" t="inlineStr"/>
+      <c r="V18" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W18" s="32" t="inlineStr">
+      <c r="W18" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X18" s="32" t="inlineStr">
+      <c r="X18" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7505,7 +7429,7 @@
           <t>http://mangas.com.cy/media/products/5292638000223.jpg</t>
         </is>
       </c>
-      <c r="Z18" s="32" t="inlineStr">
+      <c r="Z18" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7515,7 +7439,7 @@
           <t>AQUALITY Pool cleaner for greasy residue 1L</t>
         </is>
       </c>
-      <c r="AB18" s="32" t="inlineStr">
+      <c r="AB18" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7527,10 +7451,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF18" s="32" t="inlineStr"/>
-      <c r="AG18" s="32" t="inlineStr"/>
-      <c r="AH18" s="32" t="inlineStr"/>
-      <c r="AI18" s="32" t="inlineStr"/>
+      <c r="AF18" s="27" t="inlineStr"/>
+      <c r="AG18" s="27" t="inlineStr"/>
+      <c r="AH18" s="27" t="inlineStr"/>
+      <c r="AI18" s="27" t="inlineStr"/>
     </row>
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
@@ -7548,17 +7472,17 @@
           <t>California Clear Blue is a super-concentrated, pH-neutral pool clarifier in a 1-litre bottle, using a cationic polymer formula to bind microscopic particles such as dust, pollen, and oils into larger clusters your filter can catch. Non-toxic and biodegradable, it is safe for sand, zeolite, and glass filtration media.</t>
         </is>
       </c>
-      <c r="D19" s="32" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E19" s="32" t="inlineStr">
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F19" s="32" t="inlineStr">
+      <c r="F19" s="27" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -7568,71 +7492,71 @@
           <t>pool, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H19" s="32" t="inlineStr">
+      <c r="H19" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I19" s="32" t="inlineStr">
+      <c r="I19" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J19" s="32" t="inlineStr">
+      <c r="J19" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K19" s="32" t="inlineStr">
+      <c r="K19" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L19" s="32" t="inlineStr">
+      <c r="L19" s="27" t="inlineStr">
         <is>
           <t>AQU-CHM-0070</t>
         </is>
       </c>
-      <c r="M19" s="33" t="inlineStr">
+      <c r="M19" s="28" t="inlineStr">
         <is>
           <t>5292638000070</t>
         </is>
       </c>
-      <c r="N19" s="34" t="inlineStr"/>
-      <c r="O19" s="34" t="inlineStr"/>
-      <c r="P19" s="34" t="inlineStr"/>
-      <c r="Q19" s="32" t="inlineStr">
+      <c r="N19" s="29" t="inlineStr"/>
+      <c r="O19" s="29" t="inlineStr"/>
+      <c r="P19" s="29" t="inlineStr"/>
+      <c r="Q19" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R19" s="32" t="inlineStr">
+      <c r="R19" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S19" s="32" t="inlineStr">
+      <c r="S19" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T19" s="32" t="inlineStr">
+      <c r="T19" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U19" s="32" t="inlineStr"/>
-      <c r="V19" s="32" t="inlineStr">
+      <c r="U19" s="27" t="inlineStr"/>
+      <c r="V19" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W19" s="32" t="inlineStr">
+      <c r="W19" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X19" s="32" t="inlineStr">
+      <c r="X19" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7642,7 +7566,7 @@
           <t>https://poolservices.cy/storage/2026/05/California-Clear-Blue-1L-Aquality-2.jpeg</t>
         </is>
       </c>
-      <c r="Z19" s="32" t="inlineStr">
+      <c r="Z19" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7652,7 +7576,7 @@
           <t>Pool Clarifier California Clear Blue Aquality 1L</t>
         </is>
       </c>
-      <c r="AB19" s="32" t="inlineStr">
+      <c r="AB19" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7664,10 +7588,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF19" s="32" t="inlineStr"/>
-      <c r="AG19" s="32" t="inlineStr"/>
-      <c r="AH19" s="32" t="inlineStr"/>
-      <c r="AI19" s="32" t="inlineStr"/>
+      <c r="AF19" s="27" t="inlineStr"/>
+      <c r="AG19" s="27" t="inlineStr"/>
+      <c r="AH19" s="27" t="inlineStr"/>
+      <c r="AI19" s="27" t="inlineStr"/>
     </row>
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -7685,17 +7609,17 @@
           <t>A 1-litre tile and vinyl cleaner for pools, designed to clean pool tile surfaces and vinyl liners. It makes light work of the tidying up that keeps a pool looking its best.</t>
         </is>
       </c>
-      <c r="D20" s="32" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E20" s="32" t="inlineStr">
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F20" s="32" t="inlineStr">
+      <c r="F20" s="27" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -7705,71 +7629,71 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H20" s="32" t="inlineStr">
+      <c r="H20" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I20" s="32" t="inlineStr">
+      <c r="I20" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J20" s="32" t="inlineStr">
+      <c r="J20" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K20" s="32" t="inlineStr">
+      <c r="K20" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L20" s="32" t="inlineStr">
+      <c r="L20" s="27" t="inlineStr">
         <is>
           <t>AQU-CLN-0162</t>
         </is>
       </c>
-      <c r="M20" s="33" t="inlineStr">
+      <c r="M20" s="28" t="inlineStr">
         <is>
           <t>5292638000162</t>
         </is>
       </c>
-      <c r="N20" s="34" t="inlineStr"/>
-      <c r="O20" s="34" t="inlineStr"/>
-      <c r="P20" s="34" t="inlineStr"/>
-      <c r="Q20" s="32" t="inlineStr">
+      <c r="N20" s="29" t="inlineStr"/>
+      <c r="O20" s="29" t="inlineStr"/>
+      <c r="P20" s="29" t="inlineStr"/>
+      <c r="Q20" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R20" s="32" t="inlineStr">
+      <c r="R20" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S20" s="32" t="inlineStr">
+      <c r="S20" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T20" s="32" t="inlineStr">
+      <c r="T20" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U20" s="32" t="inlineStr"/>
-      <c r="V20" s="32" t="inlineStr">
+      <c r="U20" s="27" t="inlineStr"/>
+      <c r="V20" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W20" s="32" t="inlineStr">
+      <c r="W20" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X20" s="32" t="inlineStr">
+      <c r="X20" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7779,7 +7703,7 @@
           <t>http://mangas.com.cy/media/products/5292638000162.jpg</t>
         </is>
       </c>
-      <c r="Z20" s="32" t="inlineStr">
+      <c r="Z20" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7789,7 +7713,7 @@
           <t>AQUALITY Magic tile 4 vinyl cleaner 1L</t>
         </is>
       </c>
-      <c r="AB20" s="32" t="inlineStr">
+      <c r="AB20" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7801,10 +7725,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF20" s="32" t="inlineStr"/>
-      <c r="AG20" s="32" t="inlineStr"/>
-      <c r="AH20" s="32" t="inlineStr"/>
-      <c r="AI20" s="32" t="inlineStr"/>
+      <c r="AF20" s="27" t="inlineStr"/>
+      <c r="AG20" s="27" t="inlineStr"/>
+      <c r="AH20" s="27" t="inlineStr"/>
+      <c r="AI20" s="27" t="inlineStr"/>
     </row>
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
@@ -7822,17 +7746,17 @@
           <t>A 1-litre spa and pool water clarifier from Bayzid, formulated to clear cloudy or turbid water. A handy bottle to reach for whenever the water loses its sparkle.</t>
         </is>
       </c>
-      <c r="D21" s="32" t="inlineStr">
+      <c r="D21" s="27" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E21" s="32" t="inlineStr">
+      <c r="E21" s="27" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F21" s="32" t="inlineStr">
+      <c r="F21" s="27" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -7842,71 +7766,71 @@
           <t>spa-hot-tub, pool, water-treatment, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H21" s="32" t="inlineStr">
+      <c r="H21" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I21" s="32" t="inlineStr">
+      <c r="I21" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J21" s="32" t="inlineStr">
+      <c r="J21" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K21" s="32" t="inlineStr">
+      <c r="K21" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L21" s="32" t="inlineStr">
+      <c r="L21" s="27" t="inlineStr">
         <is>
           <t>HFE-SPA-7202</t>
         </is>
       </c>
-      <c r="M21" s="33" t="inlineStr">
+      <c r="M21" s="28" t="inlineStr">
         <is>
           <t>4250463127202</t>
         </is>
       </c>
-      <c r="N21" s="34" t="inlineStr"/>
-      <c r="O21" s="34" t="inlineStr"/>
-      <c r="P21" s="34" t="inlineStr"/>
-      <c r="Q21" s="32" t="inlineStr">
+      <c r="N21" s="29" t="inlineStr"/>
+      <c r="O21" s="29" t="inlineStr"/>
+      <c r="P21" s="29" t="inlineStr"/>
+      <c r="Q21" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R21" s="32" t="inlineStr">
+      <c r="R21" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S21" s="32" t="inlineStr">
+      <c r="S21" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T21" s="32" t="inlineStr">
+      <c r="T21" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U21" s="32" t="inlineStr"/>
-      <c r="V21" s="32" t="inlineStr">
+      <c r="U21" s="27" t="inlineStr"/>
+      <c r="V21" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W21" s="32" t="inlineStr">
+      <c r="W21" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X21" s="32" t="inlineStr">
+      <c r="X21" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7916,7 +7840,7 @@
           <t>https://hoefer-shop.com/cdn/shop/files/1x1L-BAYZID-Spa-Poolclear-v1-RS_1.jpg?v=1785600487&amp;width=800</t>
         </is>
       </c>
-      <c r="Z21" s="32" t="inlineStr">
+      <c r="Z21" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7926,7 +7850,7 @@
           <t>Höfer Chemie GmbH pool care 1 L BAYZID® SPA Poolclear turbidity remover</t>
         </is>
       </c>
-      <c r="AB21" s="32" t="inlineStr">
+      <c r="AB21" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7938,10 +7862,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF21" s="32" t="inlineStr"/>
-      <c r="AG21" s="32" t="inlineStr"/>
-      <c r="AH21" s="32" t="inlineStr"/>
-      <c r="AI21" s="32" t="inlineStr"/>
+      <c r="AF21" s="27" t="inlineStr"/>
+      <c r="AG21" s="27" t="inlineStr"/>
+      <c r="AH21" s="27" t="inlineStr"/>
+      <c r="AI21" s="27" t="inlineStr"/>
     </row>
     <row r="22" ht="62" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
@@ -7959,17 +7883,17 @@
           <t>A 1-litre bottle of hydrogen peroxide at 11.9% concentration, suitable for disinfection and water treatment applications. A straightforward chemical solution that keeps things clean without fuss.</t>
         </is>
       </c>
-      <c r="D22" s="32" t="inlineStr">
+      <c r="D22" s="27" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E22" s="32" t="inlineStr">
+      <c r="E22" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F22" s="32" t="inlineStr">
+      <c r="F22" s="27" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -7979,71 +7903,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H22" s="32" t="inlineStr">
+      <c r="H22" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I22" s="32" t="inlineStr">
+      <c r="I22" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J22" s="32" t="inlineStr">
+      <c r="J22" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K22" s="32" t="inlineStr">
+      <c r="K22" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L22" s="32" t="inlineStr">
+      <c r="L22" s="27" t="inlineStr">
         <is>
           <t>HFE-CHM-6788</t>
         </is>
       </c>
-      <c r="M22" s="33" t="inlineStr">
+      <c r="M22" s="28" t="inlineStr">
         <is>
           <t>4250463106788</t>
         </is>
       </c>
-      <c r="N22" s="34" t="inlineStr"/>
-      <c r="O22" s="34" t="inlineStr"/>
-      <c r="P22" s="34" t="inlineStr"/>
-      <c r="Q22" s="32" t="inlineStr">
+      <c r="N22" s="29" t="inlineStr"/>
+      <c r="O22" s="29" t="inlineStr"/>
+      <c r="P22" s="29" t="inlineStr"/>
+      <c r="Q22" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R22" s="32" t="inlineStr">
+      <c r="R22" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S22" s="32" t="inlineStr">
+      <c r="S22" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T22" s="32" t="inlineStr">
+      <c r="T22" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U22" s="32" t="inlineStr"/>
-      <c r="V22" s="32" t="inlineStr">
+      <c r="U22" s="27" t="inlineStr"/>
+      <c r="V22" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W22" s="32" t="inlineStr">
+      <c r="W22" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X22" s="32" t="inlineStr">
+      <c r="X22" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8053,7 +7977,7 @@
           <t>https://hoefer-shop.com/cdn/shop/files/1x1L-Wasserstoffperoxid-Flasche-hinten-26.jpg?v=1783777627&amp;width=1000</t>
         </is>
       </c>
-      <c r="Z22" s="32" t="inlineStr">
+      <c r="Z22" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8063,7 +7987,7 @@
           <t>HÖFER CHEMIE GMBH 1 l hydrogen peroxide 11,9%</t>
         </is>
       </c>
-      <c r="AB22" s="32" t="inlineStr">
+      <c r="AB22" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8075,10 +7999,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF22" s="32" t="inlineStr"/>
-      <c r="AG22" s="32" t="inlineStr"/>
-      <c r="AH22" s="32" t="inlineStr"/>
-      <c r="AI22" s="32" t="inlineStr"/>
+      <c r="AF22" s="27" t="inlineStr"/>
+      <c r="AG22" s="27" t="inlineStr"/>
+      <c r="AH22" s="27" t="inlineStr"/>
+      <c r="AI22" s="27" t="inlineStr"/>
     </row>
     <row r="23" ht="62" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
@@ -8096,17 +8020,17 @@
           <t>A 4.5 kg pack of chlorine stabilizer for swimming pools, used to protect chlorine from UV degradation and extend its effectiveness in the water. Steady chemistry for a pool that earns its keep.</t>
         </is>
       </c>
-      <c r="D23" s="32" t="inlineStr">
+      <c r="D23" s="27" t="inlineStr">
         <is>
           <t>AstralPool</t>
         </is>
       </c>
-      <c r="E23" s="32" t="inlineStr">
+      <c r="E23" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F23" s="32" t="inlineStr">
+      <c r="F23" s="27" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8116,75 +8040,75 @@
           <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H23" s="32" t="inlineStr">
+      <c r="H23" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I23" s="32" t="inlineStr">
+      <c r="I23" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J23" s="32" t="inlineStr">
+      <c r="J23" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K23" s="32" t="inlineStr">
+      <c r="K23" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L23" s="32" t="inlineStr">
+      <c r="L23" s="27" t="inlineStr">
         <is>
           <t>AST-CHM-0626</t>
         </is>
       </c>
-      <c r="M23" s="33" t="inlineStr">
+      <c r="M23" s="28" t="inlineStr">
         <is>
           <t>8432611960626</t>
         </is>
       </c>
-      <c r="N23" s="34" t="inlineStr"/>
-      <c r="O23" s="34" t="inlineStr"/>
-      <c r="P23" s="34" t="inlineStr"/>
-      <c r="Q23" s="32" t="inlineStr">
+      <c r="N23" s="29" t="inlineStr"/>
+      <c r="O23" s="29" t="inlineStr"/>
+      <c r="P23" s="29" t="inlineStr"/>
+      <c r="Q23" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R23" s="32" t="inlineStr">
+      <c r="R23" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S23" s="32" t="inlineStr">
+      <c r="S23" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T23" s="32" t="inlineStr">
+      <c r="T23" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U23" s="32" t="inlineStr">
+      <c r="U23" s="27" t="inlineStr">
         <is>
           <t>4500</t>
         </is>
       </c>
-      <c r="V23" s="32" t="inlineStr">
+      <c r="V23" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W23" s="32" t="inlineStr">
+      <c r="W23" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X23" s="32" t="inlineStr">
+      <c r="X23" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8194,7 +8118,7 @@
           <t>https://yokando.com/img/p/2/8/2/9/3/28293.jpg</t>
         </is>
       </c>
-      <c r="Z23" s="32" t="inlineStr">
+      <c r="Z23" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8204,7 +8128,7 @@
           <t>Astralpool water care Astralpool Chlorine Stabilizer 4,5 kg</t>
         </is>
       </c>
-      <c r="AB23" s="32" t="inlineStr">
+      <c r="AB23" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8216,10 +8140,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF23" s="32" t="inlineStr"/>
-      <c r="AG23" s="32" t="inlineStr"/>
-      <c r="AH23" s="32" t="inlineStr"/>
-      <c r="AI23" s="32" t="inlineStr"/>
+      <c r="AF23" s="27" t="inlineStr"/>
+      <c r="AG23" s="27" t="inlineStr"/>
+      <c r="AH23" s="27" t="inlineStr"/>
+      <c r="AI23" s="27" t="inlineStr"/>
     </row>
     <row r="24" ht="62" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
@@ -8237,17 +8161,17 @@
           <t>UltraShock is a pool and spa shock treatment from SpaBalancer, designed to rapidly oxidise contaminants and restore water clarity. A quick reset for water that needs a little more persuasion.</t>
         </is>
       </c>
-      <c r="D24" s="32" t="inlineStr">
+      <c r="D24" s="27" t="inlineStr">
         <is>
           <t>SpaBalancer</t>
         </is>
       </c>
-      <c r="E24" s="32" t="inlineStr">
+      <c r="E24" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F24" s="32" t="inlineStr">
+      <c r="F24" s="27" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8257,71 +8181,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H24" s="32" t="inlineStr">
+      <c r="H24" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I24" s="32" t="inlineStr">
+      <c r="I24" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J24" s="32" t="inlineStr">
+      <c r="J24" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K24" s="32" t="inlineStr">
+      <c r="K24" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L24" s="32" t="inlineStr">
+      <c r="L24" s="27" t="inlineStr">
         <is>
           <t>SPA-CHM-0025</t>
         </is>
       </c>
-      <c r="M24" s="33" t="inlineStr">
+      <c r="M24" s="28" t="inlineStr">
         <is>
           <t>4260374980025</t>
         </is>
       </c>
-      <c r="N24" s="34" t="inlineStr"/>
-      <c r="O24" s="34" t="inlineStr"/>
-      <c r="P24" s="34" t="inlineStr"/>
-      <c r="Q24" s="32" t="inlineStr">
+      <c r="N24" s="29" t="inlineStr"/>
+      <c r="O24" s="29" t="inlineStr"/>
+      <c r="P24" s="29" t="inlineStr"/>
+      <c r="Q24" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R24" s="32" t="inlineStr">
+      <c r="R24" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S24" s="32" t="inlineStr">
+      <c r="S24" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T24" s="32" t="inlineStr">
+      <c r="T24" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U24" s="32" t="inlineStr"/>
-      <c r="V24" s="32" t="inlineStr">
+      <c r="U24" s="27" t="inlineStr"/>
+      <c r="V24" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W24" s="32" t="inlineStr">
+      <c r="W24" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X24" s="32" t="inlineStr">
+      <c r="X24" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8331,7 +8255,7 @@
           <t>https://images.barcodelookup.com/16704/167043133-1.jpg</t>
         </is>
       </c>
-      <c r="Z24" s="32" t="inlineStr">
+      <c r="Z24" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8341,7 +8265,7 @@
           <t>SpaBalancer UltraShock</t>
         </is>
       </c>
-      <c r="AB24" s="32" t="inlineStr">
+      <c r="AB24" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8353,10 +8277,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF24" s="32" t="inlineStr"/>
-      <c r="AG24" s="32" t="inlineStr"/>
-      <c r="AH24" s="32" t="inlineStr"/>
-      <c r="AI24" s="32" t="inlineStr"/>
+      <c r="AF24" s="27" t="inlineStr"/>
+      <c r="AG24" s="27" t="inlineStr"/>
+      <c r="AH24" s="27" t="inlineStr"/>
+      <c r="AI24" s="27" t="inlineStr"/>
     </row>
     <row r="25" ht="76" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
@@ -8374,13 +8298,13 @@
           <t>A patented foam rubber eraser for cleaning pool surfaces, particularly suited to waterline stains on liner and vitreous ceramic finishes, and it works without detergents or chemicals. Each box contains 3 sponges, which harden when wet to scrub effectively while remaining soft and flexible in use.</t>
         </is>
       </c>
-      <c r="D25" s="32" t="inlineStr"/>
-      <c r="E25" s="32" t="inlineStr">
+      <c r="D25" s="27" t="inlineStr"/>
+      <c r="E25" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F25" s="32" t="inlineStr">
+      <c r="F25" s="27" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8390,71 +8314,71 @@
           <t>pool, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H25" s="32" t="inlineStr">
+      <c r="H25" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I25" s="32" t="inlineStr">
+      <c r="I25" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J25" s="32" t="inlineStr">
+      <c r="J25" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K25" s="32" t="inlineStr">
+      <c r="K25" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L25" s="32" t="inlineStr">
+      <c r="L25" s="27" t="inlineStr">
         <is>
           <t>GEN-CLN-0062</t>
         </is>
       </c>
-      <c r="M25" s="33" t="inlineStr">
+      <c r="M25" s="28" t="inlineStr">
         <is>
           <t>3760015880062</t>
         </is>
       </c>
-      <c r="N25" s="34" t="inlineStr"/>
-      <c r="O25" s="34" t="inlineStr"/>
-      <c r="P25" s="34" t="inlineStr"/>
-      <c r="Q25" s="32" t="inlineStr">
+      <c r="N25" s="29" t="inlineStr"/>
+      <c r="O25" s="29" t="inlineStr"/>
+      <c r="P25" s="29" t="inlineStr"/>
+      <c r="Q25" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R25" s="32" t="inlineStr">
+      <c r="R25" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S25" s="32" t="inlineStr">
+      <c r="S25" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T25" s="32" t="inlineStr">
+      <c r="T25" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U25" s="32" t="inlineStr"/>
-      <c r="V25" s="32" t="inlineStr">
+      <c r="U25" s="27" t="inlineStr"/>
+      <c r="V25" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W25" s="32" t="inlineStr">
+      <c r="W25" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X25" s="32" t="inlineStr">
+      <c r="X25" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8464,7 +8388,7 @@
           <t>https://www.piscinarium.com/2908-thickbox_default/pool-gom-magic-rubber-eraser.jpg</t>
         </is>
       </c>
-      <c r="Z25" s="32" t="inlineStr">
+      <c r="Z25" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8474,7 +8398,7 @@
           <t>Pool'Gom Magic Rubber Eraser</t>
         </is>
       </c>
-      <c r="AB25" s="32" t="inlineStr">
+      <c r="AB25" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8486,10 +8410,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF25" s="32" t="inlineStr"/>
-      <c r="AG25" s="32" t="inlineStr"/>
-      <c r="AH25" s="32" t="inlineStr"/>
-      <c r="AI25" s="32" t="inlineStr"/>
+      <c r="AF25" s="27" t="inlineStr"/>
+      <c r="AG25" s="27" t="inlineStr"/>
+      <c r="AH25" s="27" t="inlineStr"/>
+      <c r="AI25" s="27" t="inlineStr"/>
     </row>
     <row r="26" ht="62" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
@@ -8507,13 +8431,13 @@
           <t>Spa Industries Europe appears to be a brand or supplier name rather than a specific product, so no product details can be confirmed. For accurate information, please check the full product listing.</t>
         </is>
       </c>
-      <c r="D26" s="32" t="inlineStr"/>
-      <c r="E26" s="32" t="inlineStr">
+      <c r="D26" s="27" t="inlineStr"/>
+      <c r="E26" s="27" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F26" s="32" t="inlineStr">
+      <c r="F26" s="27" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -8523,79 +8447,79 @@
           <t>spa-hot-tub, considered-purchase, multi-source-confirmed, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H26" s="32" t="inlineStr">
+      <c r="H26" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I26" s="32" t="inlineStr">
+      <c r="I26" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J26" s="32" t="inlineStr">
+      <c r="J26" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K26" s="32" t="inlineStr">
+      <c r="K26" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L26" s="32" t="inlineStr">
+      <c r="L26" s="27" t="inlineStr">
         <is>
           <t>GEN-SPA-1968</t>
         </is>
       </c>
-      <c r="M26" s="33" t="inlineStr">
+      <c r="M26" s="28" t="inlineStr">
         <is>
           <t>5425021871968</t>
         </is>
       </c>
-      <c r="N26" s="34" t="inlineStr"/>
-      <c r="O26" s="34" t="inlineStr"/>
-      <c r="P26" s="34" t="inlineStr"/>
-      <c r="Q26" s="32" t="inlineStr">
+      <c r="N26" s="29" t="inlineStr"/>
+      <c r="O26" s="29" t="inlineStr"/>
+      <c r="P26" s="29" t="inlineStr"/>
+      <c r="Q26" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R26" s="32" t="inlineStr">
+      <c r="R26" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S26" s="32" t="inlineStr">
+      <c r="S26" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T26" s="32" t="inlineStr">
+      <c r="T26" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U26" s="32" t="inlineStr"/>
-      <c r="V26" s="32" t="inlineStr">
+      <c r="U26" s="27" t="inlineStr"/>
+      <c r="V26" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W26" s="32" t="inlineStr">
+      <c r="W26" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X26" s="32" t="inlineStr">
+      <c r="X26" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y26" s="19" t="inlineStr"/>
-      <c r="Z26" s="32" t="inlineStr"/>
+      <c r="Z26" s="27" t="inlineStr"/>
       <c r="AA26" s="19" t="inlineStr"/>
-      <c r="AB26" s="32" t="inlineStr">
+      <c r="AB26" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8607,10 +8531,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF26" s="32" t="inlineStr"/>
-      <c r="AG26" s="32" t="inlineStr"/>
-      <c r="AH26" s="32" t="inlineStr"/>
-      <c r="AI26" s="32" t="inlineStr"/>
+      <c r="AF26" s="27" t="inlineStr"/>
+      <c r="AG26" s="27" t="inlineStr"/>
+      <c r="AH26" s="27" t="inlineStr"/>
+      <c r="AI26" s="27" t="inlineStr"/>
     </row>
     <row r="27" ht="62" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
@@ -8628,17 +8552,17 @@
           <t>A 1-litre high-concentrate sauna cleaner with eucalyptus fragrance, formulated as a deep-cleaning base cleaner for sauna surfaces. The concentrated formula means a little goes a long way, with a fresh scent to match.</t>
         </is>
       </c>
-      <c r="D27" s="32" t="inlineStr">
+      <c r="D27" s="27" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E27" s="32" t="inlineStr">
+      <c r="E27" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F27" s="32" t="inlineStr">
+      <c r="F27" s="27" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8648,79 +8572,79 @@
           <t>cleaning, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H27" s="32" t="inlineStr">
+      <c r="H27" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I27" s="32" t="inlineStr">
+      <c r="I27" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J27" s="32" t="inlineStr">
+      <c r="J27" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K27" s="32" t="inlineStr">
+      <c r="K27" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L27" s="32" t="inlineStr">
+      <c r="L27" s="27" t="inlineStr">
         <is>
           <t>HFE-CLN-7004</t>
         </is>
       </c>
-      <c r="M27" s="33" t="inlineStr">
+      <c r="M27" s="28" t="inlineStr">
         <is>
           <t>4250463127004</t>
         </is>
       </c>
-      <c r="N27" s="34" t="inlineStr"/>
-      <c r="O27" s="34" t="inlineStr"/>
-      <c r="P27" s="34" t="inlineStr"/>
-      <c r="Q27" s="32" t="inlineStr">
+      <c r="N27" s="29" t="inlineStr"/>
+      <c r="O27" s="29" t="inlineStr"/>
+      <c r="P27" s="29" t="inlineStr"/>
+      <c r="Q27" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R27" s="32" t="inlineStr">
+      <c r="R27" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S27" s="32" t="inlineStr">
+      <c r="S27" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T27" s="32" t="inlineStr">
+      <c r="T27" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U27" s="32" t="inlineStr"/>
-      <c r="V27" s="32" t="inlineStr">
+      <c r="U27" s="27" t="inlineStr"/>
+      <c r="V27" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W27" s="32" t="inlineStr">
+      <c r="W27" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X27" s="32" t="inlineStr">
+      <c r="X27" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y27" s="19" t="inlineStr"/>
-      <c r="Z27" s="32" t="inlineStr"/>
+      <c r="Z27" s="27" t="inlineStr"/>
       <c r="AA27" s="19" t="inlineStr"/>
-      <c r="AB27" s="32" t="inlineStr">
+      <c r="AB27" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8732,10 +8656,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF27" s="32" t="inlineStr"/>
-      <c r="AG27" s="32" t="inlineStr"/>
-      <c r="AH27" s="32" t="inlineStr"/>
-      <c r="AI27" s="32" t="inlineStr"/>
+      <c r="AF27" s="27" t="inlineStr"/>
+      <c r="AG27" s="27" t="inlineStr"/>
+      <c r="AH27" s="27" t="inlineStr"/>
+      <c r="AI27" s="27" t="inlineStr"/>
     </row>
     <row r="28" ht="76" customHeight="1">
       <c r="A28" s="19" t="inlineStr">
@@ -8753,17 +8677,17 @@
           <t>This HTH spa cleaner removes mineral deposits such as limescale and rust, and cleans and polishes aluminium, chrome, stainless steel, and enamel surfaces with a pleasant pine fragrance. It has a high concentration of active ingredients and is recommended for periodic maintenance cleaning.</t>
         </is>
       </c>
-      <c r="D28" s="32" t="inlineStr">
+      <c r="D28" s="27" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E28" s="32" t="inlineStr">
+      <c r="E28" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F28" s="32" t="inlineStr">
+      <c r="F28" s="27" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8773,71 +8697,71 @@
           <t>spa-hot-tub, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H28" s="32" t="inlineStr">
+      <c r="H28" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I28" s="32" t="inlineStr">
+      <c r="I28" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J28" s="32" t="inlineStr">
+      <c r="J28" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K28" s="32" t="inlineStr">
+      <c r="K28" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L28" s="32" t="inlineStr">
+      <c r="L28" s="27" t="inlineStr">
         <is>
           <t>HTH-CLN-0178</t>
         </is>
       </c>
-      <c r="M28" s="33" t="inlineStr">
+      <c r="M28" s="28" t="inlineStr">
         <is>
           <t>3521686010178</t>
         </is>
       </c>
-      <c r="N28" s="34" t="inlineStr"/>
-      <c r="O28" s="34" t="inlineStr"/>
-      <c r="P28" s="34" t="inlineStr"/>
-      <c r="Q28" s="32" t="inlineStr">
+      <c r="N28" s="29" t="inlineStr"/>
+      <c r="O28" s="29" t="inlineStr"/>
+      <c r="P28" s="29" t="inlineStr"/>
+      <c r="Q28" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R28" s="32" t="inlineStr">
+      <c r="R28" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S28" s="32" t="inlineStr">
+      <c r="S28" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T28" s="32" t="inlineStr">
+      <c r="T28" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U28" s="32" t="inlineStr"/>
-      <c r="V28" s="32" t="inlineStr">
+      <c r="U28" s="27" t="inlineStr"/>
+      <c r="V28" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W28" s="32" t="inlineStr">
+      <c r="W28" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X28" s="32" t="inlineStr">
+      <c r="X28" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8847,7 +8771,7 @@
           <t>https://www.cdiscount.com/pdt2/0/5/1/1/700x700/auc2009356289051/rw/hth-spa-nettoyant-spa-3521686010178.jpg</t>
         </is>
       </c>
-      <c r="Z28" s="32" t="inlineStr">
+      <c r="Z28" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8857,7 +8781,7 @@
           <t>HTH Spa spa cleaner</t>
         </is>
       </c>
-      <c r="AB28" s="32" t="inlineStr">
+      <c r="AB28" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8869,10 +8793,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF28" s="32" t="inlineStr"/>
-      <c r="AG28" s="32" t="inlineStr"/>
-      <c r="AH28" s="32" t="inlineStr"/>
-      <c r="AI28" s="32" t="inlineStr"/>
+      <c r="AF28" s="27" t="inlineStr"/>
+      <c r="AG28" s="27" t="inlineStr"/>
+      <c r="AH28" s="27" t="inlineStr"/>
+      <c r="AI28" s="27" t="inlineStr"/>
     </row>
     <row r="29" ht="62" customHeight="1">
       <c r="A29" s="19" t="inlineStr">
@@ -8890,13 +8814,13 @@
           <t>A 25 kg sack of pure boiling salt (minimum 99.6% NaCl) without an anti-caking agent, meeting EN 973 Type A standard and suitable for use in pool salt electrolysis systems. Not intended for human consumption or animal feed.</t>
         </is>
       </c>
-      <c r="D29" s="32" t="inlineStr"/>
-      <c r="E29" s="32" t="inlineStr">
+      <c r="D29" s="27" t="inlineStr"/>
+      <c r="E29" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F29" s="32" t="inlineStr">
+      <c r="F29" s="27" t="inlineStr">
         <is>
           <t>Pool salt</t>
         </is>
@@ -8906,75 +8830,75 @@
           <t>pool, salt, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H29" s="32" t="inlineStr">
+      <c r="H29" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I29" s="32" t="inlineStr">
+      <c r="I29" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J29" s="32" t="inlineStr">
+      <c r="J29" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K29" s="32" t="inlineStr">
+      <c r="K29" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L29" s="32" t="inlineStr">
+      <c r="L29" s="27" t="inlineStr">
         <is>
           <t>GEN-SLT-6110</t>
         </is>
       </c>
-      <c r="M29" s="33" t="inlineStr">
+      <c r="M29" s="28" t="inlineStr">
         <is>
           <t>9001880976110</t>
         </is>
       </c>
-      <c r="N29" s="34" t="inlineStr"/>
-      <c r="O29" s="34" t="inlineStr"/>
-      <c r="P29" s="34" t="inlineStr"/>
-      <c r="Q29" s="32" t="inlineStr">
+      <c r="N29" s="29" t="inlineStr"/>
+      <c r="O29" s="29" t="inlineStr"/>
+      <c r="P29" s="29" t="inlineStr"/>
+      <c r="Q29" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R29" s="32" t="inlineStr">
+      <c r="R29" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S29" s="32" t="inlineStr">
+      <c r="S29" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T29" s="32" t="inlineStr">
+      <c r="T29" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U29" s="32" t="inlineStr">
+      <c r="U29" s="27" t="inlineStr">
         <is>
           <t>25000</t>
         </is>
       </c>
-      <c r="V29" s="32" t="inlineStr">
+      <c r="V29" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W29" s="32" t="inlineStr">
+      <c r="W29" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X29" s="32" t="inlineStr">
+      <c r="X29" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8984,7 +8908,7 @@
           <t>http://altruan.com/cdn/shop/files/SalinenPoolSalz25kgSack.png?v=1778597596</t>
         </is>
       </c>
-      <c r="Z29" s="32" t="inlineStr">
+      <c r="Z29" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8994,7 +8918,7 @@
           <t>Saline pool salt pure boiling salt without separating agent | Sack (25 kg)</t>
         </is>
       </c>
-      <c r="AB29" s="32" t="inlineStr">
+      <c r="AB29" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9006,14 +8930,14 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF29" s="32" t="inlineStr">
+      <c r="AF29" s="27" t="inlineStr">
         <is>
           <t>Composition: Siedesalz (min. 99.6% NaCl) 100%; Separant/sodium ferrocyanide 4.0–12.0 mg/kg | Grain: &gt;0.63 mm approx. 20%, 0.2–0.63 mm approx. 75%, &lt;0.2 mm approx. 5% | Moisture: &lt;0.08%</t>
         </is>
       </c>
-      <c r="AG29" s="32" t="inlineStr"/>
-      <c r="AH29" s="32" t="inlineStr"/>
-      <c r="AI29" s="32" t="inlineStr"/>
+      <c r="AG29" s="27" t="inlineStr"/>
+      <c r="AH29" s="27" t="inlineStr"/>
+      <c r="AI29" s="27" t="inlineStr"/>
     </row>
     <row r="30" ht="76" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
@@ -9031,17 +8955,17 @@
           <t>A cordless robotic pool cleaner that scrubs both floors and walls automatically, using WavePath navigation to map and cover the pool efficiently. Built-in high-performance filtration and smart control make it a hands-off solution for keeping pool water clear.</t>
         </is>
       </c>
-      <c r="D30" s="32" t="inlineStr">
+      <c r="D30" s="27" t="inlineStr">
         <is>
           <t>Aiper</t>
         </is>
       </c>
-      <c r="E30" s="32" t="inlineStr">
+      <c r="E30" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F30" s="32" t="inlineStr">
+      <c r="F30" s="27" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9051,71 +8975,71 @@
           <t>pool, cleaning, robot-cleaner, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H30" s="32" t="inlineStr">
+      <c r="H30" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I30" s="32" t="inlineStr">
+      <c r="I30" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J30" s="32" t="inlineStr">
+      <c r="J30" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K30" s="32" t="inlineStr">
+      <c r="K30" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L30" s="32" t="inlineStr">
+      <c r="L30" s="27" t="inlineStr">
         <is>
           <t>AIP-ROB-4940</t>
         </is>
       </c>
-      <c r="M30" s="33" t="inlineStr">
+      <c r="M30" s="28" t="inlineStr">
         <is>
           <t>6977676344940</t>
         </is>
       </c>
-      <c r="N30" s="34" t="inlineStr"/>
-      <c r="O30" s="34" t="inlineStr"/>
-      <c r="P30" s="34" t="inlineStr"/>
-      <c r="Q30" s="32" t="inlineStr">
+      <c r="N30" s="29" t="inlineStr"/>
+      <c r="O30" s="29" t="inlineStr"/>
+      <c r="P30" s="29" t="inlineStr"/>
+      <c r="Q30" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R30" s="32" t="inlineStr">
+      <c r="R30" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S30" s="32" t="inlineStr">
+      <c r="S30" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T30" s="32" t="inlineStr">
+      <c r="T30" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U30" s="32" t="inlineStr"/>
-      <c r="V30" s="32" t="inlineStr">
+      <c r="U30" s="27" t="inlineStr"/>
+      <c r="V30" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W30" s="32" t="inlineStr">
+      <c r="W30" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X30" s="32" t="inlineStr">
+      <c r="X30" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9125,7 +9049,7 @@
           <t>https://images.barcodelookup.com/176692/1766920801-1.jpg</t>
         </is>
       </c>
-      <c r="Z30" s="32" t="inlineStr">
+      <c r="Z30" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9135,7 +9059,7 @@
           <t>AIPER Scuba S3 cordless pool robot, automatic floor and wall cleaning, WavePath™ navigation, high-performance filtration…</t>
         </is>
       </c>
-      <c r="AB30" s="32" t="inlineStr">
+      <c r="AB30" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9147,10 +9071,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF30" s="32" t="inlineStr"/>
-      <c r="AG30" s="32" t="inlineStr"/>
-      <c r="AH30" s="32" t="inlineStr"/>
-      <c r="AI30" s="32" t="inlineStr"/>
+      <c r="AF30" s="27" t="inlineStr"/>
+      <c r="AG30" s="27" t="inlineStr"/>
+      <c r="AH30" s="27" t="inlineStr"/>
+      <c r="AI30" s="27" t="inlineStr"/>
     </row>
     <row r="31" ht="62" customHeight="1">
       <c r="A31" s="19" t="inlineStr">
@@ -9168,13 +9092,13 @@
           <t>The Scuba L1 EU is a pool cleaning device, though no further specific details about its features, dimensions, or mechanism are available from the product name alone. Buyers should refer to the full product listing for specifications.</t>
         </is>
       </c>
-      <c r="D31" s="32" t="inlineStr"/>
-      <c r="E31" s="32" t="inlineStr">
+      <c r="D31" s="27" t="inlineStr"/>
+      <c r="E31" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F31" s="32" t="inlineStr">
+      <c r="F31" s="27" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9184,71 +9108,71 @@
           <t>robot-cleaner, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H31" s="32" t="inlineStr">
+      <c r="H31" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I31" s="32" t="inlineStr">
+      <c r="I31" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J31" s="32" t="inlineStr">
+      <c r="J31" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K31" s="32" t="inlineStr">
+      <c r="K31" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L31" s="32" t="inlineStr">
+      <c r="L31" s="27" t="inlineStr">
         <is>
           <t>GEN-ROB-5137</t>
         </is>
       </c>
-      <c r="M31" s="33" t="inlineStr">
+      <c r="M31" s="28" t="inlineStr">
         <is>
           <t>6975140315137</t>
         </is>
       </c>
-      <c r="N31" s="34" t="inlineStr"/>
-      <c r="O31" s="34" t="inlineStr"/>
-      <c r="P31" s="34" t="inlineStr"/>
-      <c r="Q31" s="32" t="inlineStr">
+      <c r="N31" s="29" t="inlineStr"/>
+      <c r="O31" s="29" t="inlineStr"/>
+      <c r="P31" s="29" t="inlineStr"/>
+      <c r="Q31" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R31" s="32" t="inlineStr">
+      <c r="R31" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S31" s="32" t="inlineStr">
+      <c r="S31" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T31" s="32" t="inlineStr">
+      <c r="T31" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U31" s="32" t="inlineStr"/>
-      <c r="V31" s="32" t="inlineStr">
+      <c r="U31" s="27" t="inlineStr"/>
+      <c r="V31" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W31" s="32" t="inlineStr">
+      <c r="W31" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X31" s="32" t="inlineStr">
+      <c r="X31" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9258,7 +9182,7 @@
           <t>https://images.barcodelookup.com/124722/1247228758-1.jpg</t>
         </is>
       </c>
-      <c r="Z31" s="32" t="inlineStr">
+      <c r="Z31" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9268,7 +9192,7 @@
           <t>Scuba L1 - EU</t>
         </is>
       </c>
-      <c r="AB31" s="32" t="inlineStr">
+      <c r="AB31" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9280,10 +9204,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF31" s="32" t="inlineStr"/>
-      <c r="AG31" s="32" t="inlineStr"/>
-      <c r="AH31" s="32" t="inlineStr"/>
-      <c r="AI31" s="32" t="inlineStr"/>
+      <c r="AF31" s="27" t="inlineStr"/>
+      <c r="AG31" s="27" t="inlineStr"/>
+      <c r="AH31" s="27" t="inlineStr"/>
+      <c r="AI31" s="27" t="inlineStr"/>
     </row>
     <row r="32" ht="48" customHeight="1">
       <c r="A32" s="19" t="inlineStr">
@@ -9301,13 +9225,13 @@
           <t>The Gre Pools RBR120 is a 51W robotic pool cleaner designed for automatic pool floor cleaning. A reliable workhorse that takes the scrubbing off your hands.</t>
         </is>
       </c>
-      <c r="D32" s="32" t="inlineStr"/>
-      <c r="E32" s="32" t="inlineStr">
+      <c r="D32" s="27" t="inlineStr"/>
+      <c r="E32" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F32" s="32" t="inlineStr">
+      <c r="F32" s="27" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9317,71 +9241,71 @@
           <t>robot-cleaner, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H32" s="32" t="inlineStr">
+      <c r="H32" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I32" s="32" t="inlineStr">
+      <c r="I32" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J32" s="32" t="inlineStr">
+      <c r="J32" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K32" s="32" t="inlineStr">
+      <c r="K32" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L32" s="32" t="inlineStr">
+      <c r="L32" s="27" t="inlineStr">
         <is>
           <t>GEN-ROB-8500</t>
         </is>
       </c>
-      <c r="M32" s="33" t="inlineStr">
+      <c r="M32" s="28" t="inlineStr">
         <is>
           <t>8412081308500</t>
         </is>
       </c>
-      <c r="N32" s="34" t="inlineStr"/>
-      <c r="O32" s="34" t="inlineStr"/>
-      <c r="P32" s="34" t="inlineStr"/>
-      <c r="Q32" s="32" t="inlineStr">
+      <c r="N32" s="29" t="inlineStr"/>
+      <c r="O32" s="29" t="inlineStr"/>
+      <c r="P32" s="29" t="inlineStr"/>
+      <c r="Q32" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R32" s="32" t="inlineStr">
+      <c r="R32" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S32" s="32" t="inlineStr">
+      <c r="S32" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T32" s="32" t="inlineStr">
+      <c r="T32" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U32" s="32" t="inlineStr"/>
-      <c r="V32" s="32" t="inlineStr">
+      <c r="U32" s="27" t="inlineStr"/>
+      <c r="V32" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W32" s="32" t="inlineStr">
+      <c r="W32" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X32" s="32" t="inlineStr">
+      <c r="X32" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9391,7 +9315,7 @@
           <t>https://images.barcodelookup.com/124726/1247268298-1.jpg</t>
         </is>
       </c>
-      <c r="Z32" s="32" t="inlineStr">
+      <c r="Z32" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9401,7 +9325,7 @@
           <t>Battery Powered Robot WET RUNNER XPERT</t>
         </is>
       </c>
-      <c r="AB32" s="32" t="inlineStr">
+      <c r="AB32" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9413,10 +9337,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF32" s="32" t="inlineStr"/>
-      <c r="AG32" s="32" t="inlineStr"/>
-      <c r="AH32" s="32" t="inlineStr"/>
-      <c r="AI32" s="32" t="inlineStr"/>
+      <c r="AF32" s="27" t="inlineStr"/>
+      <c r="AG32" s="27" t="inlineStr"/>
+      <c r="AH32" s="27" t="inlineStr"/>
+      <c r="AI32" s="27" t="inlineStr"/>
     </row>
     <row r="33" ht="90" customHeight="1">
       <c r="A33" s="19" t="inlineStr">
@@ -9434,13 +9358,13 @@
           <t>A twin-size inflatable airbed measuring 99 x 191 x 25 cm, built with Fiber-Tech internal construction using polyester fibres for comfort, vinyl sides and base, and a water-resistant flocked top surface with an anti-deflation valve. It supports a maximum weight of 136 kg and packs down compactly when deflated.</t>
         </is>
       </c>
-      <c r="D33" s="32" t="inlineStr"/>
-      <c r="E33" s="32" t="inlineStr">
+      <c r="D33" s="27" t="inlineStr"/>
+      <c r="E33" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-11</t>
         </is>
       </c>
-      <c r="F33" s="32" t="inlineStr">
+      <c r="F33" s="27" t="inlineStr">
         <is>
           <t>Airbed / lounger</t>
         </is>
@@ -9450,71 +9374,71 @@
           <t>considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H33" s="32" t="inlineStr">
+      <c r="H33" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I33" s="32" t="inlineStr">
+      <c r="I33" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J33" s="32" t="inlineStr">
+      <c r="J33" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K33" s="32" t="inlineStr">
+      <c r="K33" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L33" s="32" t="inlineStr">
+      <c r="L33" s="27" t="inlineStr">
         <is>
           <t>GEN-BED-2443</t>
         </is>
       </c>
-      <c r="M33" s="33" t="inlineStr">
+      <c r="M33" s="28" t="inlineStr">
         <is>
           <t>6941057412443</t>
         </is>
       </c>
-      <c r="N33" s="34" t="inlineStr"/>
-      <c r="O33" s="34" t="inlineStr"/>
-      <c r="P33" s="34" t="inlineStr"/>
-      <c r="Q33" s="32" t="inlineStr">
+      <c r="N33" s="29" t="inlineStr"/>
+      <c r="O33" s="29" t="inlineStr"/>
+      <c r="P33" s="29" t="inlineStr"/>
+      <c r="Q33" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R33" s="32" t="inlineStr">
+      <c r="R33" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S33" s="32" t="inlineStr">
+      <c r="S33" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T33" s="32" t="inlineStr">
+      <c r="T33" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U33" s="32" t="inlineStr"/>
-      <c r="V33" s="32" t="inlineStr">
+      <c r="U33" s="27" t="inlineStr"/>
+      <c r="V33" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W33" s="32" t="inlineStr">
+      <c r="W33" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X33" s="32" t="inlineStr">
+      <c r="X33" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9524,7 +9448,7 @@
           <t>https://www.ecoperation.com/media/catalog/product/cache/b76cf1d99a7811daa83ba86e6ad91c89/6/4/64757.jpg</t>
         </is>
       </c>
-      <c r="Z33" s="32" t="inlineStr">
+      <c r="Z33" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9534,7 +9458,7 @@
           <t>Twin Dura-Beam Classic Downy Airbed 99x191x25 cm</t>
         </is>
       </c>
-      <c r="AB33" s="32" t="inlineStr">
+      <c r="AB33" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9546,18 +9470,18 @@
           <t>Inflatable Beds and Mattresses</t>
         </is>
       </c>
-      <c r="AF33" s="32" t="inlineStr"/>
-      <c r="AG33" s="32" t="inlineStr">
+      <c r="AF33" s="27" t="inlineStr"/>
+      <c r="AG33" s="27" t="inlineStr">
         <is>
           <t>99.0cm</t>
         </is>
       </c>
-      <c r="AH33" s="32" t="inlineStr">
+      <c r="AH33" s="27" t="inlineStr">
         <is>
           <t>191.0cm</t>
         </is>
       </c>
-      <c r="AI33" s="32" t="inlineStr">
+      <c r="AI33" s="27" t="inlineStr">
         <is>
           <t>25.0cm</t>
         </is>
@@ -9579,17 +9503,17 @@
           <t>A plastic chlorine dosing lock from Steinbach, designed exclusively for use with long-term chlorine tablets, with a 1.5-inch connection fitting. It measures 37 cm in length, 22.5 cm in width, and 15 cm in height, making it a sturdy inline dosing unit for pool water treatment systems.</t>
         </is>
       </c>
-      <c r="D34" s="32" t="inlineStr">
+      <c r="D34" s="27" t="inlineStr">
         <is>
           <t>Steinbach</t>
         </is>
       </c>
-      <c r="E34" s="32" t="inlineStr">
+      <c r="E34" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F34" s="32" t="inlineStr">
+      <c r="F34" s="27" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -9599,71 +9523,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H34" s="32" t="inlineStr">
+      <c r="H34" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I34" s="32" t="inlineStr">
+      <c r="I34" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J34" s="32" t="inlineStr">
+      <c r="J34" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K34" s="32" t="inlineStr">
+      <c r="K34" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L34" s="32" t="inlineStr">
+      <c r="L34" s="27" t="inlineStr">
         <is>
           <t>STE-CHM-0307</t>
         </is>
       </c>
-      <c r="M34" s="33" t="inlineStr">
+      <c r="M34" s="28" t="inlineStr">
         <is>
           <t>9008748790307</t>
         </is>
       </c>
-      <c r="N34" s="34" t="inlineStr"/>
-      <c r="O34" s="34" t="inlineStr"/>
-      <c r="P34" s="34" t="inlineStr"/>
-      <c r="Q34" s="32" t="inlineStr">
+      <c r="N34" s="29" t="inlineStr"/>
+      <c r="O34" s="29" t="inlineStr"/>
+      <c r="P34" s="29" t="inlineStr"/>
+      <c r="Q34" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R34" s="32" t="inlineStr">
+      <c r="R34" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S34" s="32" t="inlineStr">
+      <c r="S34" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T34" s="32" t="inlineStr">
+      <c r="T34" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U34" s="32" t="inlineStr"/>
-      <c r="V34" s="32" t="inlineStr">
+      <c r="U34" s="27" t="inlineStr"/>
+      <c r="V34" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W34" s="32" t="inlineStr">
+      <c r="W34" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X34" s="32" t="inlineStr">
+      <c r="X34" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9673,7 +9597,7 @@
           <t>https://i.ebayimg.com/images/g/CrUAAeSwkOdqeaRR/s-l400.jpg</t>
         </is>
       </c>
-      <c r="Z34" s="32" t="inlineStr">
+      <c r="Z34" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9683,7 +9607,7 @@
           <t>STEINBACH Chlorine dosing lock, only for chlorine long-term tablets, plastic, connection 1.5 inch in</t>
         </is>
       </c>
-      <c r="AB34" s="32" t="inlineStr">
+      <c r="AB34" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9695,18 +9619,18 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF34" s="32" t="inlineStr"/>
-      <c r="AG34" s="32" t="inlineStr">
+      <c r="AF34" s="27" t="inlineStr"/>
+      <c r="AG34" s="27" t="inlineStr">
         <is>
           <t>22.5cm</t>
         </is>
       </c>
-      <c r="AH34" s="32" t="inlineStr">
+      <c r="AH34" s="27" t="inlineStr">
         <is>
           <t>37.0cm</t>
         </is>
       </c>
-      <c r="AI34" s="32" t="inlineStr">
+      <c r="AI34" s="27" t="inlineStr">
         <is>
           <t>15.0cm</t>
         </is>
@@ -9728,17 +9652,17 @@
           <t>A filter cleaning system for hot tub and pool cartridge filters, designed to remove debris and residue efficiently while keeping water usage to a minimum. A practical tool for extending the life of your filter without wasting a drop more than necessary.</t>
         </is>
       </c>
-      <c r="D35" s="32" t="inlineStr">
+      <c r="D35" s="27" t="inlineStr">
         <is>
           <t>Estelle</t>
         </is>
       </c>
-      <c r="E35" s="32" t="inlineStr">
+      <c r="E35" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F35" s="32" t="inlineStr">
+      <c r="F35" s="27" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -9748,71 +9672,71 @@
           <t>filters, spa-hot-tub, cleaning, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H35" s="32" t="inlineStr">
+      <c r="H35" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I35" s="32" t="inlineStr">
+      <c r="I35" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J35" s="32" t="inlineStr">
+      <c r="J35" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K35" s="32" t="inlineStr">
+      <c r="K35" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L35" s="32" t="inlineStr">
+      <c r="L35" s="27" t="inlineStr">
         <is>
           <t>EST-FIL-3669</t>
         </is>
       </c>
-      <c r="M35" s="33" t="inlineStr">
+      <c r="M35" s="28" t="inlineStr">
         <is>
           <t>8711842033669</t>
         </is>
       </c>
-      <c r="N35" s="34" t="inlineStr"/>
-      <c r="O35" s="34" t="inlineStr"/>
-      <c r="P35" s="34" t="inlineStr"/>
-      <c r="Q35" s="32" t="inlineStr">
+      <c r="N35" s="29" t="inlineStr"/>
+      <c r="O35" s="29" t="inlineStr"/>
+      <c r="P35" s="29" t="inlineStr"/>
+      <c r="Q35" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R35" s="32" t="inlineStr">
+      <c r="R35" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S35" s="32" t="inlineStr">
+      <c r="S35" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T35" s="32" t="inlineStr">
+      <c r="T35" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U35" s="32" t="inlineStr"/>
-      <c r="V35" s="32" t="inlineStr">
+      <c r="U35" s="27" t="inlineStr"/>
+      <c r="V35" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W35" s="32" t="inlineStr">
+      <c r="W35" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X35" s="32" t="inlineStr">
+      <c r="X35" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9822,7 +9746,7 @@
           <t>https://i.ebayimg.com/images/g/0e0AAOSweaplqO77/s-l400.jpg</t>
         </is>
       </c>
-      <c r="Z35" s="32" t="inlineStr">
+      <c r="Z35" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9832,7 +9756,7 @@
           <t>Estelle Filter Cleaning System Hot tubs Cartridge Filters Cleaner Spa Amazing!</t>
         </is>
       </c>
-      <c r="AB35" s="32" t="inlineStr">
+      <c r="AB35" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9844,10 +9768,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF35" s="32" t="inlineStr"/>
-      <c r="AG35" s="32" t="inlineStr"/>
-      <c r="AH35" s="32" t="inlineStr"/>
-      <c r="AI35" s="32" t="inlineStr"/>
+      <c r="AF35" s="27" t="inlineStr"/>
+      <c r="AG35" s="27" t="inlineStr"/>
+      <c r="AH35" s="27" t="inlineStr"/>
+      <c r="AI35" s="27" t="inlineStr"/>
     </row>
     <row r="36" ht="62" customHeight="1">
       <c r="A36" s="19" t="inlineStr">
@@ -9865,17 +9789,17 @@
           <t>A compact handy scrub brush for pool maintenance, measuring 15 x 9 x 8 cm, suited to scrubbing pool surfaces and hard-to-reach areas. Small enough to manoeuvre easily, and ready to tackle whatever the waterline throws at it.</t>
         </is>
       </c>
-      <c r="D36" s="32" t="inlineStr">
+      <c r="D36" s="27" t="inlineStr">
         <is>
           <t>WAYS</t>
         </is>
       </c>
-      <c r="E36" s="32" t="inlineStr">
+      <c r="E36" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F36" s="32" t="inlineStr">
+      <c r="F36" s="27" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -9885,79 +9809,79 @@
           <t>pool, cleaning, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H36" s="32" t="inlineStr">
+      <c r="H36" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I36" s="32" t="inlineStr">
+      <c r="I36" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J36" s="32" t="inlineStr">
+      <c r="J36" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K36" s="32" t="inlineStr">
+      <c r="K36" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L36" s="32" t="inlineStr">
+      <c r="L36" s="27" t="inlineStr">
         <is>
           <t>WAY-CLN-2219</t>
         </is>
       </c>
-      <c r="M36" s="33" t="inlineStr">
+      <c r="M36" s="28" t="inlineStr">
         <is>
           <t>8720299182219</t>
         </is>
       </c>
-      <c r="N36" s="34" t="inlineStr"/>
-      <c r="O36" s="34" t="inlineStr"/>
-      <c r="P36" s="34" t="inlineStr"/>
-      <c r="Q36" s="32" t="inlineStr">
+      <c r="N36" s="29" t="inlineStr"/>
+      <c r="O36" s="29" t="inlineStr"/>
+      <c r="P36" s="29" t="inlineStr"/>
+      <c r="Q36" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R36" s="32" t="inlineStr">
+      <c r="R36" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S36" s="32" t="inlineStr">
+      <c r="S36" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T36" s="32" t="inlineStr">
+      <c r="T36" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U36" s="32" t="inlineStr"/>
-      <c r="V36" s="32" t="inlineStr">
+      <c r="U36" s="27" t="inlineStr"/>
+      <c r="V36" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W36" s="32" t="inlineStr">
+      <c r="W36" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X36" s="32" t="inlineStr">
+      <c r="X36" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y36" s="19" t="inlineStr"/>
-      <c r="Z36" s="32" t="inlineStr"/>
+      <c r="Z36" s="27" t="inlineStr"/>
       <c r="AA36" s="19" t="inlineStr"/>
-      <c r="AB36" s="32" t="inlineStr">
+      <c r="AB36" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9969,18 +9893,18 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF36" s="32" t="inlineStr"/>
-      <c r="AG36" s="32" t="inlineStr">
+      <c r="AF36" s="27" t="inlineStr"/>
+      <c r="AG36" s="27" t="inlineStr">
         <is>
           <t>8.0cm</t>
         </is>
       </c>
-      <c r="AH36" s="32" t="inlineStr">
+      <c r="AH36" s="27" t="inlineStr">
         <is>
           <t>15.0cm</t>
         </is>
       </c>
-      <c r="AI36" s="32" t="inlineStr">
+      <c r="AI36" s="27" t="inlineStr">
         <is>
           <t>9.0cm</t>
         </is>
@@ -10002,17 +9926,17 @@
           <t>An inflatable PVC headrest pillow for the Intex inflatable spa (model 28506), measuring 24 x 19 x 6 cm and weighing 0.22 kg, designed to support the head and neck comfortably during use. It attaches to the spa rim and can also be filled with water for added stability.</t>
         </is>
       </c>
-      <c r="D37" s="32" t="inlineStr">
+      <c r="D37" s="27" t="inlineStr">
         <is>
           <t>Intex</t>
         </is>
       </c>
-      <c r="E37" s="32" t="inlineStr">
+      <c r="E37" s="27" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F37" s="32" t="inlineStr">
+      <c r="F37" s="27" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -10022,75 +9946,75 @@
           <t>spa-hot-tub, accessories, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H37" s="32" t="inlineStr">
+      <c r="H37" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I37" s="32" t="inlineStr">
+      <c r="I37" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J37" s="32" t="inlineStr">
+      <c r="J37" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K37" s="32" t="inlineStr">
+      <c r="K37" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L37" s="32" t="inlineStr">
+      <c r="L37" s="27" t="inlineStr">
         <is>
           <t>INT-SPA-6075</t>
         </is>
       </c>
-      <c r="M37" s="33" t="inlineStr">
+      <c r="M37" s="28" t="inlineStr">
         <is>
           <t>6941057426075</t>
         </is>
       </c>
-      <c r="N37" s="34" t="inlineStr"/>
-      <c r="O37" s="34" t="inlineStr"/>
-      <c r="P37" s="34" t="inlineStr"/>
-      <c r="Q37" s="32" t="inlineStr">
+      <c r="N37" s="29" t="inlineStr"/>
+      <c r="O37" s="29" t="inlineStr"/>
+      <c r="P37" s="29" t="inlineStr"/>
+      <c r="Q37" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R37" s="32" t="inlineStr">
+      <c r="R37" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S37" s="32" t="inlineStr">
+      <c r="S37" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T37" s="32" t="inlineStr">
+      <c r="T37" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U37" s="32" t="inlineStr">
+      <c r="U37" s="27" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="V37" s="32" t="inlineStr">
+      <c r="V37" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W37" s="32" t="inlineStr">
+      <c r="W37" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X37" s="32" t="inlineStr">
+      <c r="X37" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10100,7 +10024,7 @@
           <t>https://content2.rozetka.com.ua/goods/images/big/570260745.jpg</t>
         </is>
       </c>
-      <c r="Z37" s="32" t="inlineStr">
+      <c r="Z37" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10110,7 +10034,7 @@
           <t>Pillow for inflatable SPA INTEX 28506</t>
         </is>
       </c>
-      <c r="AB37" s="32" t="inlineStr">
+      <c r="AB37" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10122,18 +10046,18 @@
           <t>Intex Pure Spa Accessories</t>
         </is>
       </c>
-      <c r="AF37" s="32" t="inlineStr"/>
-      <c r="AG37" s="32" t="inlineStr">
+      <c r="AF37" s="27" t="inlineStr"/>
+      <c r="AG37" s="27" t="inlineStr">
         <is>
           <t>19.0cm</t>
         </is>
       </c>
-      <c r="AH37" s="32" t="inlineStr">
+      <c r="AH37" s="27" t="inlineStr">
         <is>
           <t>24.0cm</t>
         </is>
       </c>
-      <c r="AI37" s="32" t="inlineStr">
+      <c r="AI37" s="27" t="inlineStr">
         <is>
           <t>6.0cm</t>
         </is>
@@ -10155,13 +10079,13 @@
           <t>A DPD Pool test kit for active-oxygen pools, containing 20 DPD No. 4 reagent tablets for measuring active oxygen levels and 20 phenol red tablets for measuring pH. Results are read immediately after the tablet dissolves, with an ideal active oxygen range of 3.0 to 8.0 mg/l and a target pH of 7.0 to 7.4.</t>
         </is>
       </c>
-      <c r="D38" s="32" t="inlineStr"/>
-      <c r="E38" s="32" t="inlineStr">
+      <c r="D38" s="27" t="inlineStr"/>
+      <c r="E38" s="27" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F38" s="32" t="inlineStr">
+      <c r="F38" s="27" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -10171,71 +10095,71 @@
           <t>water-treatment, test-measure, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H38" s="32" t="inlineStr">
+      <c r="H38" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I38" s="32" t="inlineStr">
+      <c r="I38" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J38" s="32" t="inlineStr">
+      <c r="J38" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K38" s="32" t="inlineStr">
+      <c r="K38" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L38" s="32" t="inlineStr">
+      <c r="L38" s="27" t="inlineStr">
         <is>
           <t>GEN-TST-1347</t>
         </is>
       </c>
-      <c r="M38" s="33" t="inlineStr">
+      <c r="M38" s="28" t="inlineStr">
         <is>
           <t>4250463121347</t>
         </is>
       </c>
-      <c r="N38" s="34" t="inlineStr"/>
-      <c r="O38" s="34" t="inlineStr"/>
-      <c r="P38" s="34" t="inlineStr"/>
-      <c r="Q38" s="32" t="inlineStr">
+      <c r="N38" s="29" t="inlineStr"/>
+      <c r="O38" s="29" t="inlineStr"/>
+      <c r="P38" s="29" t="inlineStr"/>
+      <c r="Q38" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R38" s="32" t="inlineStr">
+      <c r="R38" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S38" s="32" t="inlineStr">
+      <c r="S38" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T38" s="32" t="inlineStr">
+      <c r="T38" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U38" s="32" t="inlineStr"/>
-      <c r="V38" s="32" t="inlineStr">
+      <c r="U38" s="27" t="inlineStr"/>
+      <c r="V38" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W38" s="32" t="inlineStr">
+      <c r="W38" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X38" s="32" t="inlineStr">
+      <c r="X38" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10245,7 +10169,7 @@
           <t>https://media.carrefour.fr/medias/8f94161f683b4e589024a5b5ebaa6873/p_200x200/cad3db6a00ef414a804b9226119bae96_image.jpg</t>
         </is>
       </c>
-      <c r="Z38" s="32" t="inlineStr">
+      <c r="Z38" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10255,7 +10179,7 @@
           <t>Active oxygen test kit x1</t>
         </is>
       </c>
-      <c r="AB38" s="32" t="inlineStr">
+      <c r="AB38" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10267,10 +10191,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF38" s="32" t="inlineStr"/>
-      <c r="AG38" s="32" t="inlineStr"/>
-      <c r="AH38" s="32" t="inlineStr"/>
-      <c r="AI38" s="32" t="inlineStr"/>
+      <c r="AF38" s="27" t="inlineStr"/>
+      <c r="AG38" s="27" t="inlineStr"/>
+      <c r="AH38" s="27" t="inlineStr"/>
+      <c r="AI38" s="27" t="inlineStr"/>
     </row>
     <row r="39" ht="62" customHeight="1">
       <c r="A39" s="19" t="inlineStr">
@@ -10288,17 +10212,17 @@
           <t>A pack of 2 replacement filter cartridges compatible with Intex Type H pool and spa pumps, made by Darlly. Straightforward to swap out, they keep the water moving clean without any complications.</t>
         </is>
       </c>
-      <c r="D39" s="32" t="inlineStr">
+      <c r="D39" s="27" t="inlineStr">
         <is>
           <t>Intex</t>
         </is>
       </c>
-      <c r="E39" s="32" t="inlineStr">
+      <c r="E39" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F39" s="32" t="inlineStr">
+      <c r="F39" s="27" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -10308,71 +10232,71 @@
           <t>filters, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H39" s="32" t="inlineStr">
+      <c r="H39" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I39" s="32" t="inlineStr">
+      <c r="I39" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J39" s="32" t="inlineStr">
+      <c r="J39" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K39" s="32" t="inlineStr">
+      <c r="K39" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L39" s="32" t="inlineStr">
+      <c r="L39" s="27" t="inlineStr">
         <is>
           <t>INT-FIL-2895</t>
         </is>
       </c>
-      <c r="M39" s="33" t="inlineStr">
+      <c r="M39" s="28" t="inlineStr">
         <is>
           <t>700175992895</t>
         </is>
       </c>
-      <c r="N39" s="34" t="inlineStr"/>
-      <c r="O39" s="34" t="inlineStr"/>
-      <c r="P39" s="34" t="inlineStr"/>
-      <c r="Q39" s="32" t="inlineStr">
+      <c r="N39" s="29" t="inlineStr"/>
+      <c r="O39" s="29" t="inlineStr"/>
+      <c r="P39" s="29" t="inlineStr"/>
+      <c r="Q39" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R39" s="32" t="inlineStr">
+      <c r="R39" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S39" s="32" t="inlineStr">
+      <c r="S39" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T39" s="32" t="inlineStr">
+      <c r="T39" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U39" s="32" t="inlineStr"/>
-      <c r="V39" s="32" t="inlineStr">
+      <c r="U39" s="27" t="inlineStr"/>
+      <c r="V39" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W39" s="32" t="inlineStr">
+      <c r="W39" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X39" s="32" t="inlineStr">
+      <c r="X39" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10382,7 +10306,7 @@
           <t>https://a.allegroimg.com/original/11923c/a79785a04d36aa54f0d87384f038/Filtracni-kartuse-Intex-D-3BTZ0023-SC828</t>
         </is>
       </c>
-      <c r="Z39" s="32" t="inlineStr">
+      <c r="Z39" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10392,7 +10316,7 @@
           <t>Darlly filter cartridge pack of 2 filter cartridges compatible with Intex type H</t>
         </is>
       </c>
-      <c r="AB39" s="32" t="inlineStr">
+      <c r="AB39" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10404,10 +10328,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF39" s="32" t="inlineStr"/>
-      <c r="AG39" s="32" t="inlineStr"/>
-      <c r="AH39" s="32" t="inlineStr"/>
-      <c r="AI39" s="32" t="inlineStr"/>
+      <c r="AF39" s="27" t="inlineStr"/>
+      <c r="AG39" s="27" t="inlineStr"/>
+      <c r="AH39" s="27" t="inlineStr"/>
+      <c r="AI39" s="27" t="inlineStr"/>
     </row>
     <row r="40" ht="62" customHeight="1">
       <c r="A40" s="19" t="inlineStr">
@@ -10425,17 +10349,17 @@
           <t>A Darlly replacement spa filter cartridge with dimensions of 22 cm diameter by 27 cm height, compatible with SC713 and C-8465 references. A reliable like-for-like swap to keep your spa filtration running smoothly.</t>
         </is>
       </c>
-      <c r="D40" s="32" t="inlineStr">
+      <c r="D40" s="27" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E40" s="32" t="inlineStr">
+      <c r="E40" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F40" s="32" t="inlineStr">
+      <c r="F40" s="27" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -10445,71 +10369,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H40" s="32" t="inlineStr">
+      <c r="H40" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I40" s="32" t="inlineStr">
+      <c r="I40" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J40" s="32" t="inlineStr">
+      <c r="J40" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K40" s="32" t="inlineStr">
+      <c r="K40" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L40" s="32" t="inlineStr">
+      <c r="L40" s="27" t="inlineStr">
         <is>
           <t>DAR-FIL-1744</t>
         </is>
       </c>
-      <c r="M40" s="33" t="inlineStr">
+      <c r="M40" s="28" t="inlineStr">
         <is>
           <t>700175991744</t>
         </is>
       </c>
-      <c r="N40" s="34" t="inlineStr"/>
-      <c r="O40" s="34" t="inlineStr"/>
-      <c r="P40" s="34" t="inlineStr"/>
-      <c r="Q40" s="32" t="inlineStr">
+      <c r="N40" s="29" t="inlineStr"/>
+      <c r="O40" s="29" t="inlineStr"/>
+      <c r="P40" s="29" t="inlineStr"/>
+      <c r="Q40" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R40" s="32" t="inlineStr">
+      <c r="R40" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S40" s="32" t="inlineStr">
+      <c r="S40" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T40" s="32" t="inlineStr">
+      <c r="T40" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U40" s="32" t="inlineStr"/>
-      <c r="V40" s="32" t="inlineStr">
+      <c r="U40" s="27" t="inlineStr"/>
+      <c r="V40" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W40" s="32" t="inlineStr">
+      <c r="W40" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X40" s="32" t="inlineStr">
+      <c r="X40" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10519,7 +10443,7 @@
           <t>https://images.barcodelookup.com/142259/1422591231-1.jpg</t>
         </is>
       </c>
-      <c r="Z40" s="32" t="inlineStr">
+      <c r="Z40" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10529,7 +10453,7 @@
           <t>Spa replacement filter Ø 22 cm x 27 cm SC713, C-8465 - Darlly</t>
         </is>
       </c>
-      <c r="AB40" s="32" t="inlineStr">
+      <c r="AB40" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10541,14 +10465,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF40" s="32" t="inlineStr"/>
-      <c r="AG40" s="32" t="inlineStr"/>
-      <c r="AH40" s="32" t="inlineStr">
+      <c r="AF40" s="27" t="inlineStr"/>
+      <c r="AG40" s="27" t="inlineStr"/>
+      <c r="AH40" s="27" t="inlineStr">
         <is>
           <t>22.0cm</t>
         </is>
       </c>
-      <c r="AI40" s="32" t="inlineStr">
+      <c r="AI40" s="27" t="inlineStr">
         <is>
           <t>27.0cm</t>
         </is>
@@ -10570,17 +10494,17 @@
           <t>A 1 kg pack of 20g multitabs for swimming pools, offering a 5-in-1 treatment that combines multiple water care functions in a single slow-dissolving tablet. Convenient all-in-one dosing that keeps pool maintenance simple.</t>
         </is>
       </c>
-      <c r="D41" s="32" t="inlineStr">
+      <c r="D41" s="27" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E41" s="32" t="inlineStr">
+      <c r="E41" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F41" s="32" t="inlineStr">
+      <c r="F41" s="27" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -10590,75 +10514,75 @@
           <t>pool, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H41" s="32" t="inlineStr">
+      <c r="H41" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I41" s="32" t="inlineStr">
+      <c r="I41" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J41" s="32" t="inlineStr">
+      <c r="J41" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K41" s="32" t="inlineStr">
+      <c r="K41" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L41" s="32" t="inlineStr">
+      <c r="L41" s="27" t="inlineStr">
         <is>
           <t>HFE-CHM-8430</t>
         </is>
       </c>
-      <c r="M41" s="33" t="inlineStr">
+      <c r="M41" s="28" t="inlineStr">
         <is>
           <t>4250463108430</t>
         </is>
       </c>
-      <c r="N41" s="34" t="inlineStr"/>
-      <c r="O41" s="34" t="inlineStr"/>
-      <c r="P41" s="34" t="inlineStr"/>
-      <c r="Q41" s="32" t="inlineStr">
+      <c r="N41" s="29" t="inlineStr"/>
+      <c r="O41" s="29" t="inlineStr"/>
+      <c r="P41" s="29" t="inlineStr"/>
+      <c r="Q41" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R41" s="32" t="inlineStr">
+      <c r="R41" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S41" s="32" t="inlineStr">
+      <c r="S41" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T41" s="32" t="inlineStr">
+      <c r="T41" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U41" s="32" t="inlineStr">
+      <c r="U41" s="27" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="V41" s="32" t="inlineStr">
+      <c r="V41" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W41" s="32" t="inlineStr">
+      <c r="W41" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X41" s="32" t="inlineStr">
+      <c r="X41" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10668,7 +10592,7 @@
           <t>https://images.barcodelookup.com/17422/174228560-1.jpg</t>
         </is>
       </c>
-      <c r="Z41" s="32" t="inlineStr">
+      <c r="Z41" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10678,7 +10602,7 @@
           <t>1 x 1 kg BAYZID® multitabs 20g 5in1 for pools - HöFER CHEMIE</t>
         </is>
       </c>
-      <c r="AB41" s="32" t="inlineStr">
+      <c r="AB41" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10690,10 +10614,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF41" s="32" t="inlineStr"/>
-      <c r="AG41" s="32" t="inlineStr"/>
-      <c r="AH41" s="32" t="inlineStr"/>
-      <c r="AI41" s="32" t="inlineStr"/>
+      <c r="AF41" s="27" t="inlineStr"/>
+      <c r="AG41" s="27" t="inlineStr"/>
+      <c r="AH41" s="27" t="inlineStr"/>
+      <c r="AI41" s="27" t="inlineStr"/>
     </row>
     <row r="42" ht="76" customHeight="1">
       <c r="A42" s="19" t="inlineStr">
@@ -10711,17 +10635,17 @@
           <t>A ready-to-use alkaline spray cleaner for removing grease and dirt marks at the waterline of pools and for cleaning skimmers. The spray bottle makes application straightforward, and it can be used on a filled pool on all alkali-resistant surfaces.</t>
         </is>
       </c>
-      <c r="D42" s="32" t="inlineStr">
+      <c r="D42" s="27" t="inlineStr">
         <is>
           <t>Bayrol</t>
         </is>
       </c>
-      <c r="E42" s="32" t="inlineStr">
+      <c r="E42" s="27" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F42" s="32" t="inlineStr">
+      <c r="F42" s="27" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -10731,75 +10655,75 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H42" s="32" t="inlineStr">
+      <c r="H42" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I42" s="32" t="inlineStr">
+      <c r="I42" s="27" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J42" s="32" t="inlineStr">
+      <c r="J42" s="27" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K42" s="32" t="inlineStr">
+      <c r="K42" s="27" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L42" s="32" t="inlineStr">
+      <c r="L42" s="27" t="inlineStr">
         <is>
           <t>BAY-CLN-4134</t>
         </is>
       </c>
-      <c r="M42" s="33" t="inlineStr">
+      <c r="M42" s="28" t="inlineStr">
         <is>
           <t>4008367154134</t>
         </is>
       </c>
-      <c r="N42" s="34" t="inlineStr"/>
-      <c r="O42" s="34" t="inlineStr"/>
-      <c r="P42" s="34" t="inlineStr"/>
-      <c r="Q42" s="32" t="inlineStr">
+      <c r="N42" s="29" t="inlineStr"/>
+      <c r="O42" s="29" t="inlineStr"/>
+      <c r="P42" s="29" t="inlineStr"/>
+      <c r="Q42" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R42" s="32" t="inlineStr">
+      <c r="R42" s="27" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S42" s="32" t="inlineStr">
+      <c r="S42" s="27" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T42" s="32" t="inlineStr">
+      <c r="T42" s="27" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U42" s="32" t="inlineStr">
+      <c r="U42" s="27" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="V42" s="32" t="inlineStr">
+      <c r="V42" s="27" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W42" s="32" t="inlineStr">
+      <c r="W42" s="27" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X42" s="32" t="inlineStr">
+      <c r="X42" s="27" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10809,7 +10733,7 @@
           <t>https://www.north-spa.de/wp-content/uploads/2023/02/Produktbild-1-Bayrol-Randfix-07-l-4008367154134.jpg</t>
         </is>
       </c>
-      <c r="Z42" s="32" t="inlineStr">
+      <c r="Z42" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10819,7 +10743,7 @@
           <t>Bayrol Randfix 0,7 l</t>
         </is>
       </c>
-      <c r="AB42" s="32" t="inlineStr">
+      <c r="AB42" s="27" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10831,10 +10755,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF42" s="32" t="inlineStr"/>
-      <c r="AG42" s="32" t="inlineStr"/>
-      <c r="AH42" s="32" t="inlineStr"/>
-      <c r="AI42" s="32" t="inlineStr"/>
+      <c r="AF42" s="27" t="inlineStr"/>
+      <c r="AG42" s="27" t="inlineStr"/>
+      <c r="AH42" s="27" t="inlineStr"/>
+      <c r="AI42" s="27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10873,119 +10797,119 @@
       </c>
     </row>
     <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="28" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>(21)28624(250)2610</t>
         </is>
       </c>
-      <c r="B2" s="29" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>GS1 serial capture (AI 21/250) — identifies one physical unit, carries no product code</t>
         </is>
       </c>
-      <c r="C2" s="29" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
         <is>
           <t>Re-scan the product's own EAN/UPC from the packaging, or enter it by hand.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>XLY41601182</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>supplier or model code, not a GTIN</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="C3" s="31" t="inlineStr">
         <is>
           <t>Re-scan the product's own EAN/UPC from the packaging, or enter it by hand.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>(21)68672(250)2510</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>GS1 serial capture (AI 21/250) — identifies one physical unit, carries no product code</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>Re-scan the product's own EAN/UPC from the packaging, or enter it by hand.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>XLY41601180</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>supplier or model code, not a GTIN</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t>Re-scan the product's own EAN/UPC from the packaging, or enter it by hand.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>(21)11371(250)2510</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>GS1 serial capture (AI 21/250) — identifies one physical unit, carries no product code</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>Re-scan the product's own EAN/UPC from the packaging, or enter it by hand.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>X0020RYMP3</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>supplier or model code, not a GTIN</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>Re-scan the product's own EAN/UPC from the packaging, or enter it by hand.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>05FT72001</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>supplier or model code, not a GTIN</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t>Re-scan the product's own EAN/UPC from the packaging, or enter it by hand.</t>
         </is>

--- a/projects/splashstore/docs/splashstore-scan-curation-260816.xlsx
+++ b/projects/splashstore/docs/splashstore-scan-curation-260816.xlsx
@@ -43,7 +43,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +95,11 @@
         <fgColor rgb="00E4DFEC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D08E"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -108,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -205,6 +210,21 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -317,6 +337,16 @@
 Three sources agreeing is stronger evidence than one, though both are green.</t>
       </text>
     </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Colour applies to THIS FIELD ONLY, and is judged separately from the photo.
+GREEN = written from the barcode-confirmed page for this exact product.
+YELLOW = written from a name-matched page, so it may describe a variant.
+RED = no description.
+A yellow description beside a green image is normal: the photo was proven by the barcode, the wording was not.
+The cell names the page the wording came from, or says 'generic (from name)' when there was no page at all.</t>
+      </text>
+    </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <t>Colour applies to THIS FIELD ONLY, and is judged separately from the photo.
@@ -335,6 +365,15 @@
 RED = no description.
 A yellow description beside a green image is normal: the photo was proven by the barcode, the wording was not.
 The cell names the page the wording came from, or says 'generic (from name)' when there was no page at all.</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Colour applies to THIS FIELD ONLY.
+GREEN = the barcode was found literally on the page the photo came from.
+YELLOW = the right product, but the photo needs a look (crop, multipack, unclear).
+RED = no usable photo was found.
+The cell names the site the photo came from. Compare it with Description Source: a different site there means the two fields were proven separately.</t>
       </text>
     </comment>
     <comment ref="N1" authorId="0" shapeId="0">
@@ -364,6 +403,17 @@
 RED = missing on an edible product.</t>
       </text>
     </comment>
+    <comment ref="L5" authorId="0" shapeId="0">
+      <text>
+        <t>No source anywhere confirmed this barcode, so the product has no name — and with no name there is nothing to search an image with.
+Identify it by hand: check the packaging, or search the code on the brand's own site.
+Avenues tried (4):
+- db: 5061066600127 -&gt; miss
+- barcode-image: 5061066600127 -&gt; 6 candidates
+- ean-web: 5061066600127 -&gt; 7 pages found
+- ebay: 5061066600127 -&gt; 0 listing(s)</t>
+      </text>
+    </comment>
     <comment ref="N5" authorId="0" shapeId="0">
       <text>
         <t>No source anywhere confirmed this barcode, so the product has no name — and with no name there is nothing to search an image with.
@@ -384,6 +434,17 @@
 - barcode-image: 5061066600127 -&gt; 6 candidates
 - ean-web: 5061066600127 -&gt; 7 pages found
 - ebay: 5061066600127 -&gt; 0 listing(s)</t>
+      </text>
+    </comment>
+    <comment ref="L16" authorId="0" shapeId="0">
+      <text>
+        <t>No source anywhere confirmed this barcode, so the product has no name — and with no name there is nothing to search an image with.
+Identify it by hand: check the packaging, or search the code on the brand's own site.
+Avenues tried (4):
+- db: 5292638000759 -&gt; miss
+- barcode-image: 5292638000759 -&gt; 6 candidates
+- ean-web: 5292638000759 -&gt; 7 pages found
+- ebay: 5292638000759 -&gt; 0 listing(s)</t>
       </text>
     </comment>
     <comment ref="N16" authorId="0" shapeId="0">
@@ -408,6 +469,11 @@
 - ebay: 5292638000759 -&gt; 0 listing(s)</t>
       </text>
     </comment>
+    <comment ref="L17" authorId="0" shapeId="0">
+      <text>
+        <t>The image AI judged this photo to be the SAME product line in a DIFFERENT pack size or count than this barcode's. Adopted as yellow by policy: a recognisable variant photo beats an empty cell, but verify the size before it goes live.</t>
+      </text>
+    </comment>
     <comment ref="N17" authorId="0" shapeId="0">
       <text>
         <t>The image AI judged this photo to be the SAME product line in a DIFFERENT pack size or count than this barcode's. Adopted as yellow by policy: a recognisable variant photo beats an empty cell, but verify the size before it goes live.</t>
@@ -416,6 +482,19 @@
     <comment ref="P17" authorId="0" shapeId="0">
       <text>
         <t>The image AI judged this photo to be the SAME product line in a DIFFERENT pack size or count than this barcode's. Adopted as yellow by policy: a recognisable variant photo beats an empty cell, but verify the size before it goes live.</t>
+      </text>
+    </comment>
+    <comment ref="L29" authorId="0" shapeId="0">
+      <text>
+        <t>A photo WAS found and checked against this product's confirmed name.
+The image AI judged it a different product, so it was not used:
+0.97: The image shows a 3D animated purple dinosaur/dragon cartoon character
+This one wants photographing in the garage, not more searching.
+Avenues tried (4):
+- db: 4250463127004 -&gt; miss
+- barcode-image: 4250463127004 -&gt; 6 candidates
+- ean-web: 4250463127004 -&gt; 7 pages found
+- name-ladder:full: Deutschland Card -&gt; 6 candidates</t>
       </text>
     </comment>
     <comment ref="N29" authorId="0" shapeId="0">
@@ -444,6 +523,20 @@
 - name-ladder:full: Deutschland Card -&gt; 6 candidates</t>
       </text>
     </comment>
+    <comment ref="L38" authorId="0" shapeId="0">
+      <text>
+        <t>The product IS identified from its barcode, but no usable photo was found by any source we search: the barcode databases, the barcode directories, an image search on the confirmed name, and eBay.
+Nothing left to try automatically. Photograph it in the garage.
+Avenues tried (7):
+- db: 8720299182219 -&gt; miss
+- barcode-image: 8720299182219 -&gt; 6 candidates
+- ean-web: 8720299182219 -&gt; 7 pages found
+- name-ladder:full: WAYS - Poolvedligeholdelse - Skrubebørste - 15 x 9 x 8 cm - Handy scrub -&gt; 6 candidates
+- name-ladder:simple: WAYS - Poolvedligeholdelse - Skrubebørste - - -&gt; 6 candidates
+- name-ladder:english: WAYS - Pool Maintenance - Scrub Brush - 15 x 9 x 8 cm - Handy scrub -&gt; 6 candidates
+- ebay: 8720299182219 -&gt; 0 listing(s)</t>
+      </text>
+    </comment>
     <comment ref="N38" authorId="0" shapeId="0">
       <text>
         <t>The product IS identified from its barcode, but no usable photo was found by any source we search: the barcode databases, the barcode directories, an image search on the confirmed name, and eBay.
@@ -470,6 +563,17 @@
 - name-ladder:simple: WAYS - Poolvedligeholdelse - Skrubebørste - - -&gt; 6 candidates
 - name-ladder:english: WAYS - Pool Maintenance - Scrub Brush - 15 x 9 x 8 cm - Handy scrub -&gt; 6 candidates
 - ebay: 8720299182219 -&gt; 0 listing(s)</t>
+      </text>
+    </comment>
+    <comment ref="L45" authorId="0" shapeId="0">
+      <text>
+        <t>No source anywhere confirmed this barcode, so the product has no name — and with no name there is nothing to search an image with.
+Identify it by hand: check the packaging, or search the code on the brand's own site.
+Avenues tried (4):
+- db: 9008748095532 -&gt; miss
+- barcode-image: 9008748095532 -&gt; 6 candidates
+- ean-web: 9008748095532 -&gt; 7 pages found
+- ebay: 9008748095532 -&gt; 0 listing(s)</t>
       </text>
     </comment>
     <comment ref="N45" authorId="0" shapeId="0">
@@ -2007,7 +2111,7 @@
       </c>
       <c r="T1" s="18" t="inlineStr">
         <is>
-          <t>Colours are per field, not per row. Green: the barcode was found literally at that source. Yellow: plausible, but not confirmed that way. Red: nothing. Grey: not applicable. Blue tints mark IDENTITY fields (barcode, who confirmed it) - a category, not a verdict. A green photo beside a yellow description is normal. Hover any header for detail.</t>
+          <t>Colours are per field, not per row. Green: the barcode was found literally at that source. Yellow: plausible, but not confirmed that way. Red: nothing. Grey: not applicable. Darker green: verified AND the cell links to the proving page. Blue tints mark IDENTITY fields (barcode, who confirmed it) - a category, not a verdict. A green photo beside a yellow description is normal. Hover any header for detail.</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2152,7 @@
           <t>A cartridge filter for hot tubs and swim spas, with a 26 cm outer diameter, 13 cm bottom section, and 3.8 cm inner thread. Compatible with Darlly SC779 / 40372 and a wide range of other brands, it traps dirt, grease, and fine particles to keep your water clean.</t>
         </is>
       </c>
-      <c r="I2" s="22" t="inlineStr">
+      <c r="I2" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: spa-components.com</t>
         </is>
@@ -2064,12 +2168,12 @@
       </c>
       <c r="M2" s="23" t="n"/>
       <c r="N2" s="23" t="n"/>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="O2" s="40" t="inlineStr">
         <is>
           <t>https://www.spa-components.com/user/shop/big/1473-1_filter-cartridge-sc779-rising-dragon-plastics--eago-whirlpools.jpg?ff=1&amp;x=1024&amp;y=768&amp;q=85&amp;ts=6720c4a0&amp;sg=161563f2</t>
         </is>
       </c>
-      <c r="P2" s="22" t="inlineStr">
+      <c r="P2" s="39" t="inlineStr">
         <is>
           <t>Verified — barcode: spa-components.com</t>
         </is>
@@ -2115,7 +2219,7 @@
           <t>A twin pack of Size II replacement filter cartridges measuring 10.6 x 13.6 cm, designed for compatible pool and spa filtration systems. The fine lamellar structure delivers thorough water cleaning and the cartridges are easy to rinse clean.</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: bestwaystore.de</t>
         </is>
@@ -2133,12 +2237,12 @@
         <v>13.6</v>
       </c>
       <c r="N3" s="23" t="n"/>
-      <c r="O3" s="7" t="inlineStr">
+      <c r="O3" s="40" t="inlineStr">
         <is>
           <t>https://www.bestwaystore.de/media/c6/f8/ba/1756384660/6941607353615-main-jpg.jpg?ts=1756384660</t>
         </is>
       </c>
-      <c r="P3" s="22" t="inlineStr">
+      <c r="P3" s="39" t="inlineStr">
         <is>
           <t>Verified — 2 sources (barcode): bestwaystore.de</t>
         </is>
@@ -2188,7 +2292,7 @@
           <t>A Size 3 replacement filter cartridge for Bestway Flowclear filtration systems, designed to remove deposits and dirt from pool water. Its fine lamellar structure makes it easy to clean and maintain.</t>
         </is>
       </c>
-      <c r="I4" s="22" t="inlineStr">
+      <c r="I4" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: pools.shop</t>
         </is>
@@ -2202,12 +2306,12 @@
       <c r="L4" s="23" t="n"/>
       <c r="M4" s="23" t="n"/>
       <c r="N4" s="23" t="n"/>
-      <c r="O4" s="7" t="inlineStr">
+      <c r="O4" s="40" t="inlineStr">
         <is>
           <t>https://ap.nice-cdn.com/upload/image/product/large/default/bestway-flowclear-filter-cartridge-size-3-1-item-638140-en.jpg</t>
         </is>
       </c>
-      <c r="P4" s="22" t="inlineStr">
+      <c r="P4" s="39" t="inlineStr">
         <is>
           <t>Verified — 2 sources (barcode): pools.shop</t>
         </is>
@@ -2298,7 +2402,7 @@
           <t>A hot tub and spa filter cartridge measuring 125 mm in diameter and 235 mm in length, with 54 mm openings at both ends. Sold as a 2-pack, it is compatible with Unicel C-4335, Pleatco PRB35-IN, Filbur FC-2385, and a long list of other manufacturer codes including Sundance Spas and Jacuzzi 6000-136.</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -2316,12 +2420,12 @@
         <v>23.5</v>
       </c>
       <c r="N6" s="23" t="n"/>
-      <c r="O6" s="7" t="inlineStr">
+      <c r="O6" s="40" t="inlineStr">
         <is>
           <t>https://images.barcodelookup.com/29361/293617958-1.jpg</t>
         </is>
       </c>
-      <c r="P6" s="22" t="inlineStr">
+      <c r="P6" s="39" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
@@ -2367,7 +2471,7 @@
           <t>A single Size IV replacement filter cartridge measuring 14.2 x 25.4 cm, compatible with Bestway filter pump 58391 (9,463 l/h). Its deep-fold, fine-structure media delivers thorough water cleaning and can be rinsed clean with minimal effort.</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I7" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: bestwaystore.de</t>
         </is>
@@ -2385,12 +2489,12 @@
         <v>25.4</v>
       </c>
       <c r="N7" s="23" t="n"/>
-      <c r="O7" s="7" t="inlineStr">
+      <c r="O7" s="40" t="inlineStr">
         <is>
           <t>https://www.bestwaystore.de/media/53/6c/e9/1756384676/6941607353622-main-jpg.jpg?ts=1756384676</t>
         </is>
       </c>
-      <c r="P7" s="22" t="inlineStr">
+      <c r="P7" s="39" t="inlineStr">
         <is>
           <t>Verified — 2 sources (barcode): bestwaystore.de</t>
         </is>
@@ -2440,7 +2544,7 @@
           <t>A pair of spa and whirlpool replacement filter cartridges, compatible with Unicel C-4401 and Pleatco PRB17.5SF PR (code SC726). Sold as a set of two, they suit a range of hot tub brands.</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I8" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -2574,7 +2678,7 @@
           <t>A square inflatable hot tub for up to four people, with an overall outer diameter of 2.45 m and a structure measuring 1.75 x 1.75 x 0.71 m, built from high-resistance polyester for good rigidity and durability. The packaged weight is 64.92 kg, so you will want a helper on delivery day.</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="I10" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: intex.fr</t>
         </is>
@@ -2596,12 +2700,12 @@
       <c r="N10" s="13" t="n">
         <v>64.92</v>
       </c>
-      <c r="O10" s="7" t="inlineStr">
+      <c r="O10" s="40" t="inlineStr">
         <is>
           <t>https://media.intex.fr/7743-large_default_x2/28464ex-spa-gonflable-calacatta-4-places.jpg</t>
         </is>
       </c>
-      <c r="P10" s="22" t="inlineStr">
+      <c r="P10" s="39" t="inlineStr">
         <is>
           <t>Verified — barcode: intex.fr</t>
         </is>
@@ -2651,7 +2755,7 @@
           <t>A 3.0 kg tub of hth stabiliser granules for outdoor swimming pools, used to protect chlorine from UV degradation and extend its effectiveness. A reliable way to get more mileage from your sanitiser on sunny days.</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="I11" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -2667,12 +2771,12 @@
       <c r="N11" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="O11" s="7" t="inlineStr">
+      <c r="O11" s="40" t="inlineStr">
         <is>
           <t>https://images.barcodelookup.com/12027/120276177-1.jpg</t>
         </is>
       </c>
-      <c r="P11" s="22" t="inlineStr">
+      <c r="P11" s="39" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
@@ -2744,12 +2848,12 @@
       <c r="N12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="O12" s="7" t="inlineStr">
+      <c r="O12" s="40" t="inlineStr">
         <is>
           <t>https://www.north-spa.de/wp-content/uploads/2025/02/Produktbild-1-hth-SPA-ANTIKALK-1-l-3521684700194-360x360.jpg</t>
         </is>
       </c>
-      <c r="P12" s="22" t="inlineStr">
+      <c r="P12" s="39" t="inlineStr">
         <is>
           <t>Verified — barcode: north-spa.de</t>
         </is>
@@ -2795,7 +2899,7 @@
           <t>A round, olive-green inflatable spa for up to 8 people, with a maximum water temperature of 40°C. It comes with 5 included accessories and makes a generous, sociable addition to any garden or terrace.</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="I13" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: intex.fr</t>
         </is>
@@ -2809,12 +2913,12 @@
       <c r="L13" s="23" t="n"/>
       <c r="M13" s="23" t="n"/>
       <c r="N13" s="23" t="n"/>
-      <c r="O13" s="7" t="inlineStr">
+      <c r="O13" s="40" t="inlineStr">
         <is>
           <t>https://media.intex.fr/11990-large_default_x2/28412np-spa-gonflable-olive-8-places.jpg</t>
         </is>
       </c>
-      <c r="P13" s="22" t="inlineStr">
+      <c r="P13" s="39" t="inlineStr">
         <is>
           <t>Verified — barcode: intex.fr</t>
         </is>
@@ -2864,7 +2968,7 @@
           <t>A replacement spa filter cartridge (SC750) compatible with Arctic, Fonteyn, Rota, and other brands, also cross-referencing Pleatco PWW10, Unicel C-4310, and Filbur FC-3077. It also matches several LeisureBay, PDC, Sedona, Viking, and Roto Spa models.</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="I14" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -2878,12 +2982,12 @@
       <c r="L14" s="23" t="n"/>
       <c r="M14" s="23" t="n"/>
       <c r="N14" s="23" t="n"/>
-      <c r="O14" s="7" t="inlineStr">
+      <c r="O14" s="40" t="inlineStr">
         <is>
           <t>https://images.barcodelookup.com/29338/293384728-1.jpg</t>
         </is>
       </c>
-      <c r="P14" s="22" t="inlineStr">
+      <c r="P14" s="39" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
@@ -2947,12 +3051,12 @@
       <c r="L15" s="23" t="n"/>
       <c r="M15" s="23" t="n"/>
       <c r="N15" s="23" t="n"/>
-      <c r="O15" s="7" t="inlineStr">
+      <c r="O15" s="40" t="inlineStr">
         <is>
           <t>https://www.spabalancer.ch/media/ae/20/d2/1728651174/sb111_clean-refresh_freigestellt.png?ts=1777362921</t>
         </is>
       </c>
-      <c r="P15" s="22" t="inlineStr">
+      <c r="P15" s="39" t="inlineStr">
         <is>
           <t>Verified — barcode: spabalancer.ch</t>
         </is>
@@ -3126,12 +3230,12 @@
       <c r="L18" s="23" t="n"/>
       <c r="M18" s="23" t="n"/>
       <c r="N18" s="23" t="n"/>
-      <c r="O18" s="7" t="inlineStr">
+      <c r="O18" s="40" t="inlineStr">
         <is>
           <t>https://www.poolpowershop.de/media/46/63/13/1743521499/phenol-red-testtabletten-fuer-poollab-500-stk.jpg</t>
         </is>
       </c>
-      <c r="P18" s="22" t="inlineStr">
+      <c r="P18" s="39" t="inlineStr">
         <is>
           <t>Verified — barcode: poolpowershop.de</t>
         </is>
@@ -3181,7 +3285,7 @@
           <t>An alkaline liquid edge and tile cleaner for pools, formulated to be safe on liners and plastic surfaces. It removes grease, dirt, and waterline residue, and is supplied in a 1-litre bottle.</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="I19" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -3195,12 +3299,12 @@
       <c r="L19" s="23" t="n"/>
       <c r="M19" s="23" t="n"/>
       <c r="N19" s="23" t="n"/>
-      <c r="O19" s="7" t="inlineStr">
+      <c r="O19" s="40" t="inlineStr">
         <is>
           <t>https://images.barcodelookup.com/21057/210579756-1.jpg</t>
         </is>
       </c>
-      <c r="P19" s="22" t="inlineStr">
+      <c r="P19" s="39" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
@@ -3250,7 +3354,7 @@
           <t>A pool cleaner designed to remove sunscreen oil and greasy residues from the water surface, supplied in a 1-litre bottle. Formulated for pools with heavy swimming loads and warm climates.</t>
         </is>
       </c>
-      <c r="I20" s="22" t="inlineStr">
+      <c r="I20" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: mangas.com.cy</t>
         </is>
@@ -3264,12 +3368,12 @@
       <c r="L20" s="23" t="n"/>
       <c r="M20" s="23" t="n"/>
       <c r="N20" s="23" t="n"/>
-      <c r="O20" s="7" t="inlineStr">
+      <c r="O20" s="40" t="inlineStr">
         <is>
           <t>http://mangas.com.cy/media/products/5292638000223.jpg</t>
         </is>
       </c>
-      <c r="P20" s="22" t="inlineStr">
+      <c r="P20" s="39" t="inlineStr">
         <is>
           <t>Verified — barcode: mangas.com.cy</t>
         </is>
@@ -3319,7 +3423,7 @@
           <t>A super-concentrated cationic polymer pool clarifier in a 1-litre viscous blue liquid format, designed to bind microscopic particles such as dust, pollen, and oils into larger clusters that filtration systems can capture. pH-neutral and compatible with sand, zeolite, and glass filter media, it is applied at 60 ml per 10 m³ for cloudy water treatment.</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="I21" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: poolservices.cy</t>
         </is>
@@ -3333,12 +3437,12 @@
       <c r="L21" s="23" t="n"/>
       <c r="M21" s="23" t="n"/>
       <c r="N21" s="23" t="n"/>
-      <c r="O21" s="7" t="inlineStr">
+      <c r="O21" s="40" t="inlineStr">
         <is>
           <t>https://poolservices.cy/storage/2026/05/California-Clear-Blue-1L-Aquality-2.jpeg</t>
         </is>
       </c>
-      <c r="P21" s="22" t="inlineStr">
+      <c r="P21" s="39" t="inlineStr">
         <is>
           <t>Verified — barcode: poolservices.cy</t>
         </is>
@@ -3388,7 +3492,7 @@
           <t>A 1-litre vinyl and tile cleaner for pools, safe for use on pool surfaces including liners. Beyond the product name, the source provides no further detail on its formulation or specific application instructions.</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="I22" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: mangas.com.cy</t>
         </is>
@@ -3402,12 +3506,12 @@
       <c r="L22" s="23" t="n"/>
       <c r="M22" s="23" t="n"/>
       <c r="N22" s="23" t="n"/>
-      <c r="O22" s="7" t="inlineStr">
+      <c r="O22" s="40" t="inlineStr">
         <is>
           <t>http://mangas.com.cy/media/products/5292638000162.jpg</t>
         </is>
       </c>
-      <c r="P22" s="22" t="inlineStr">
+      <c r="P22" s="39" t="inlineStr">
         <is>
           <t>Verified — barcode: mangas.com.cy</t>
         </is>
@@ -3471,12 +3575,12 @@
       <c r="L23" s="23" t="n"/>
       <c r="M23" s="23" t="n"/>
       <c r="N23" s="23" t="n"/>
-      <c r="O23" s="7" t="inlineStr">
+      <c r="O23" s="40" t="inlineStr">
         <is>
           <t>https://hoefer-shop.com/cdn/shop/files/1x1L-BAYZID-Spa-Poolclear-v1-RS_1.jpg?v=1785600487&amp;width=800</t>
         </is>
       </c>
-      <c r="P23" s="22" t="inlineStr">
+      <c r="P23" s="39" t="inlineStr">
         <is>
           <t>Verified — barcode: hoefer-shop.com</t>
         </is>
@@ -3540,12 +3644,12 @@
       <c r="L24" s="23" t="n"/>
       <c r="M24" s="23" t="n"/>
       <c r="N24" s="23" t="n"/>
-      <c r="O24" s="7" t="inlineStr">
+      <c r="O24" s="40" t="inlineStr">
         <is>
           <t>https://hoefer-shop.com/cdn/shop/files/1x1L-Wasserstoffperoxid-Flasche-hinten-26.jpg?v=1783777627&amp;width=1000</t>
         </is>
       </c>
-      <c r="P24" s="22" t="inlineStr">
+      <c r="P24" s="39" t="inlineStr">
         <is>
           <t>Verified — barcode: hoefer-shop.com</t>
         </is>
@@ -3666,7 +3770,7 @@
           <t>A hot-tub water disinfection treatment for use as a shock dose to sanitise spa water. Note that the product has a limited shelf life and loses roughly 8 to 10% of its efficacy per month, so buying in advance is not recommended.</t>
         </is>
       </c>
-      <c r="I26" s="22" t="inlineStr">
+      <c r="I26" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -3680,12 +3784,12 @@
       <c r="L26" s="23" t="n"/>
       <c r="M26" s="23" t="n"/>
       <c r="N26" s="23" t="n"/>
-      <c r="O26" s="7" t="inlineStr">
+      <c r="O26" s="40" t="inlineStr">
         <is>
           <t>https://images.barcodelookup.com/16704/167043133-1.jpg</t>
         </is>
       </c>
-      <c r="P26" s="22" t="inlineStr">
+      <c r="P26" s="39" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
@@ -3731,7 +3835,7 @@
           <t>A patented foam eraser that hardens when wet, designed for cleaning the waterline and surfaces of liner and tiled pools without detergents or chemicals. Each box contains 3 sponges, and the eraser also works on skimmers, ladders, pool covers, and plastic garden furniture.</t>
         </is>
       </c>
-      <c r="I27" s="22" t="inlineStr">
+      <c r="I27" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: piscinarium.com</t>
         </is>
@@ -3745,12 +3849,12 @@
       <c r="L27" s="23" t="n"/>
       <c r="M27" s="23" t="n"/>
       <c r="N27" s="23" t="n"/>
-      <c r="O27" s="7" t="inlineStr">
+      <c r="O27" s="40" t="inlineStr">
         <is>
           <t>https://www.piscinarium.com/2908-thickbox_default/pool-gom-magic-rubber-eraser.jpg</t>
         </is>
       </c>
-      <c r="P27" s="22" t="inlineStr">
+      <c r="P27" s="39" t="inlineStr">
         <is>
           <t>Verified — barcode: piscinarium.com</t>
         </is>
@@ -3934,7 +4038,7 @@
           <t>A periodic spa cleaner that removes mineral deposits including limescale and rust, while cleaning and polishing aluminium, chrome, stainless steel, and enamel surfaces. Its high concentration of active ingredients and pine fragrance make routine maintenance a little more pleasant.</t>
         </is>
       </c>
-      <c r="I30" s="22" t="inlineStr">
+      <c r="I30" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: cdiscount.com</t>
         </is>
@@ -3948,12 +4052,12 @@
       <c r="L30" s="23" t="n"/>
       <c r="M30" s="23" t="n"/>
       <c r="N30" s="23" t="n"/>
-      <c r="O30" s="7" t="inlineStr">
+      <c r="O30" s="40" t="inlineStr">
         <is>
           <t>https://www.cdiscount.com/pdt2/0/5/1/1/700x700/auc2009356289051/rw/hth-spa-nettoyant-spa-3521686010178.jpg</t>
         </is>
       </c>
-      <c r="P30" s="22" t="inlineStr">
+      <c r="P30" s="39" t="inlineStr">
         <is>
           <t>Verified — barcode: cdiscount.com</t>
         </is>
@@ -3999,7 +4103,7 @@
           <t>A 25 kg sack of pure boiling salt (minimum 99.6% NaCl) without an anti-caking agent, meeting EN 973 Type A standard and suitable for use in pool salt electrolysis systems. Not intended for human consumption or animal feed.</t>
         </is>
       </c>
-      <c r="I31" s="22" t="inlineStr">
+      <c r="I31" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: altruan.com</t>
         </is>
@@ -4015,12 +4119,12 @@
       <c r="N31" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="O31" s="7" t="inlineStr">
+      <c r="O31" s="40" t="inlineStr">
         <is>
           <t>http://altruan.com/cdn/shop/files/SalinenPoolSalz25kgSack.png?v=1778597596</t>
         </is>
       </c>
-      <c r="P31" s="22" t="inlineStr">
+      <c r="P31" s="39" t="inlineStr">
         <is>
           <t>Verified — barcode: altruan.com</t>
         </is>
@@ -4088,12 +4192,12 @@
       <c r="L32" s="23" t="n"/>
       <c r="M32" s="23" t="n"/>
       <c r="N32" s="23" t="n"/>
-      <c r="O32" s="7" t="inlineStr">
+      <c r="O32" s="40" t="inlineStr">
         <is>
           <t>https://images.barcodelookup.com/176692/1766920801-1.jpg</t>
         </is>
       </c>
-      <c r="P32" s="22" t="inlineStr">
+      <c r="P32" s="39" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
@@ -4139,7 +4243,7 @@
           <t>A cordless robotic pool cleaner from Aiper, designed to clean both the floor and vertical walls of a pool without a cable getting in the way. It suits those who want a tidy pool without the tangle.</t>
         </is>
       </c>
-      <c r="I33" s="22" t="inlineStr">
+      <c r="I33" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -4153,12 +4257,12 @@
       <c r="L33" s="23" t="n"/>
       <c r="M33" s="23" t="n"/>
       <c r="N33" s="23" t="n"/>
-      <c r="O33" s="7" t="inlineStr">
+      <c r="O33" s="40" t="inlineStr">
         <is>
           <t>https://images.barcodelookup.com/124722/1247228758-1.jpg</t>
         </is>
       </c>
-      <c r="P33" s="22" t="inlineStr">
+      <c r="P33" s="39" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
@@ -4204,7 +4308,7 @@
           <t>A battery powered robotic pool cleaner made from PVC, suited to above ground pools up to 12 m in size and depths of up to 3 m, with a 2 hour cleaning cycle and an 8 hour charge time. Measuring 38.5 x 35.5 x 23.9 cm and weighing 5.2 kg, it works across flat and gently sloping pool floors with all surface types.</t>
         </is>
       </c>
-      <c r="I34" s="22" t="inlineStr">
+      <c r="I34" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -4226,12 +4330,12 @@
       <c r="N34" s="13" t="n">
         <v>5.2</v>
       </c>
-      <c r="O34" s="7" t="inlineStr">
+      <c r="O34" s="40" t="inlineStr">
         <is>
           <t>https://images.barcodelookup.com/124726/1247268298-1.jpg</t>
         </is>
       </c>
-      <c r="P34" s="22" t="inlineStr">
+      <c r="P34" s="39" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
@@ -4277,7 +4381,7 @@
           <t>A twin-size inflatable airbed measuring 99 x 191 x 25 cm, built with Fiber-Tech internal construction using polyester fibres for comfort, vinyl sides and base, and a water-resistant flocked top surface with an anti-deflation valve. It supports a maximum weight of 136 kg and packs down compactly when deflated.</t>
         </is>
       </c>
-      <c r="I35" s="22" t="inlineStr">
+      <c r="I35" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: ecoperation.com</t>
         </is>
@@ -4297,12 +4401,12 @@
         <v>25</v>
       </c>
       <c r="N35" s="23" t="n"/>
-      <c r="O35" s="7" t="inlineStr">
+      <c r="O35" s="40" t="inlineStr">
         <is>
           <t>https://www.ecoperation.com/media/catalog/product/cache/b76cf1d99a7811daa83ba86e6ad91c89/6/4/64757.jpg</t>
         </is>
       </c>
-      <c r="P35" s="22" t="inlineStr">
+      <c r="P35" s="39" t="inlineStr">
         <is>
           <t>Verified — barcode: ecoperation.com</t>
         </is>
@@ -4352,7 +4456,7 @@
           <t>A plastic chlorine dosing lock from Steinbach, designed exclusively for use with long-term chlorine tablets, with a 1.5-inch connection fitting. It measures 37 cm in length, 22.5 cm in width, and 15 cm in height, making it a sturdy inline dosing unit for pool water treatment systems.</t>
         </is>
       </c>
-      <c r="I36" s="22" t="inlineStr">
+      <c r="I36" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: ebay.de</t>
         </is>
@@ -4372,12 +4476,12 @@
         <v>15</v>
       </c>
       <c r="N36" s="23" t="n"/>
-      <c r="O36" s="7" t="inlineStr">
+      <c r="O36" s="40" t="inlineStr">
         <is>
           <t>https://i.ebayimg.com/images/g/CrUAAeSwkOdqeaRR/s-l400.jpg</t>
         </is>
       </c>
-      <c r="P36" s="22" t="inlineStr">
+      <c r="P36" s="39" t="inlineStr">
         <is>
           <t>Verified — barcode: ebay.de</t>
         </is>
@@ -4427,7 +4531,7 @@
           <t>A filter cleaning system designed for hot tub and pool cartridge filters, with a water saving design that makes keeping filters in good condition straightforward. A practical addition to any spa maintenance routine.</t>
         </is>
       </c>
-      <c r="I37" s="22" t="inlineStr">
+      <c r="I37" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: ebay.com</t>
         </is>
@@ -4441,12 +4545,12 @@
       <c r="L37" s="23" t="n"/>
       <c r="M37" s="23" t="n"/>
       <c r="N37" s="23" t="n"/>
-      <c r="O37" s="7" t="inlineStr">
+      <c r="O37" s="40" t="inlineStr">
         <is>
           <t>https://i.ebayimg.com/images/g/0e0AAOSweaplqO77/s-l400.jpg</t>
         </is>
       </c>
-      <c r="P37" s="22" t="inlineStr">
+      <c r="P37" s="39" t="inlineStr">
         <is>
           <t>Verified — barcode: ebay.com</t>
         </is>
@@ -4567,7 +4671,7 @@
           <t>An inflatable PVC headrest pillow for the Intex inflatable spa (model 28506), measuring 24 x 19 x 6 cm and weighing 0.22 kg, designed to support the head and neck comfortably during use. It attaches to the spa rim and can also be filled with water for added stability.</t>
         </is>
       </c>
-      <c r="I39" s="22" t="inlineStr">
+      <c r="I39" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: rozetka.pl</t>
         </is>
@@ -4589,12 +4693,12 @@
       <c r="N39" s="13" t="n">
         <v>0.22</v>
       </c>
-      <c r="O39" s="7" t="inlineStr">
+      <c r="O39" s="40" t="inlineStr">
         <is>
           <t>https://content2.rozetka.com.ua/goods/images/big/570260745.jpg</t>
         </is>
       </c>
-      <c r="P39" s="22" t="inlineStr">
+      <c r="P39" s="39" t="inlineStr">
         <is>
           <t>Verified — barcode: rozetka.pl</t>
         </is>
@@ -4640,7 +4744,7 @@
           <t>A DPD pool test kit for active oxygen pools, containing 20 DPD No. 4 tablets and 20 phenol red tablets to measure both active oxygen levels and pH in pool water. Simply dissolve a tablet in the provided container, agitate, and read the result immediately for a quick and straightforward water check.</t>
         </is>
       </c>
-      <c r="I40" s="22" t="inlineStr">
+      <c r="I40" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: carrefour.fr</t>
         </is>
@@ -4654,12 +4758,12 @@
       <c r="L40" s="23" t="n"/>
       <c r="M40" s="23" t="n"/>
       <c r="N40" s="23" t="n"/>
-      <c r="O40" s="7" t="inlineStr">
+      <c r="O40" s="40" t="inlineStr">
         <is>
           <t>https://media.carrefour.fr/medias/8f94161f683b4e589024a5b5ebaa6873/p_200x200/cad3db6a00ef414a804b9226119bae96_image.jpg</t>
         </is>
       </c>
-      <c r="P40" s="22" t="inlineStr">
+      <c r="P40" s="39" t="inlineStr">
         <is>
           <t>Verified — barcode: carrefour.fr</t>
         </is>
@@ -4723,12 +4827,12 @@
       <c r="L41" s="23" t="n"/>
       <c r="M41" s="23" t="n"/>
       <c r="N41" s="23" t="n"/>
-      <c r="O41" s="7" t="inlineStr">
+      <c r="O41" s="40" t="inlineStr">
         <is>
           <t>https://a.allegroimg.com/original/11923c/a79785a04d36aa54f0d87384f038/Filtracni-kartuse-Intex-D-3BTZ0023-SC828</t>
         </is>
       </c>
-      <c r="P41" s="22" t="inlineStr">
+      <c r="P41" s="39" t="inlineStr">
         <is>
           <t>Verified — barcode: allegro.cz</t>
         </is>
@@ -4778,7 +4882,7 @@
           <t>A Darlly replacement spa filter cartridge with dimensions of 22 cm diameter by 27 cm height, compatible with SC713 and C-8465 references. A reliable like-for-like swap to keep your spa filtration running smoothly.</t>
         </is>
       </c>
-      <c r="I42" s="22" t="inlineStr">
+      <c r="I42" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -4796,12 +4900,12 @@
         <v>27</v>
       </c>
       <c r="N42" s="23" t="n"/>
-      <c r="O42" s="7" t="inlineStr">
+      <c r="O42" s="40" t="inlineStr">
         <is>
           <t>https://images.barcodelookup.com/142259/1422591231-1.jpg</t>
         </is>
       </c>
-      <c r="P42" s="22" t="inlineStr">
+      <c r="P42" s="39" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
@@ -4851,7 +4955,7 @@
           <t>A 1 kg pack of 20g multitabs for swimming pools, offering a 5-in-1 treatment that combines multiple water care functions in a single slow-dissolving tablet. Convenient all-in-one dosing that keeps pool maintenance simple.</t>
         </is>
       </c>
-      <c r="I43" s="22" t="inlineStr">
+      <c r="I43" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: barcodelookup.com</t>
         </is>
@@ -4867,12 +4971,12 @@
       <c r="N43" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="O43" s="7" t="inlineStr">
+      <c r="O43" s="40" t="inlineStr">
         <is>
           <t>https://images.barcodelookup.com/17422/174228560-1.jpg</t>
         </is>
       </c>
-      <c r="P43" s="22" t="inlineStr">
+      <c r="P43" s="39" t="inlineStr">
         <is>
           <t>Verified — Barcode Lookup (barcode)</t>
         </is>
@@ -4922,7 +5026,7 @@
           <t>A ready-to-use alkaline spray cleaner for removing grease and dirt marks at the waterline of pools and for cleaning skimmers. The spray bottle makes application straightforward, and it can be used on a filled pool on all alkali-resistant surfaces.</t>
         </is>
       </c>
-      <c r="I44" s="22" t="inlineStr">
+      <c r="I44" s="39" t="inlineStr">
         <is>
           <t>Verified — product page: north-spa.de</t>
         </is>
@@ -4938,12 +5042,12 @@
       <c r="N44" s="13" t="n">
         <v>0.7</v>
       </c>
-      <c r="O44" s="7" t="inlineStr">
+      <c r="O44" s="40" t="inlineStr">
         <is>
           <t>https://www.north-spa.de/wp-content/uploads/2023/02/Produktbild-1-Bayrol-Randfix-07-l-4008367154134.jpg</t>
         </is>
       </c>
-      <c r="P44" s="22" t="inlineStr">
+      <c r="P44" s="39" t="inlineStr">
         <is>
           <t>Verified — barcode: north-spa.de</t>
         </is>
@@ -5355,17 +5459,17 @@
           <t>A cartridge filter for hot tubs and swim spas, with a 26 cm outer diameter, 13 cm bottom section, and 3.8 cm inner thread. Compatible with Darlly SC779 / 40372 and a wide range of other brands, it traps dirt, grease, and fine particles to keep your water clean.</t>
         </is>
       </c>
-      <c r="D2" s="36" t="inlineStr">
+      <c r="D2" s="41" t="inlineStr">
         <is>
           <t>Rising Dragon</t>
         </is>
       </c>
-      <c r="E2" s="36" t="inlineStr">
+      <c r="E2" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F2" s="36" t="inlineStr">
+      <c r="F2" s="41" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5375,71 +5479,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H2" s="36" t="inlineStr">
+      <c r="H2" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I2" s="36" t="inlineStr">
+      <c r="I2" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J2" s="36" t="inlineStr">
+      <c r="J2" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K2" s="36" t="inlineStr">
+      <c r="K2" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L2" s="36" t="inlineStr">
+      <c r="L2" s="41" t="inlineStr">
         <is>
           <t>RIS-FIL-2406</t>
         </is>
       </c>
-      <c r="M2" s="37" t="inlineStr">
+      <c r="M2" s="42" t="inlineStr">
         <is>
           <t>700175992406</t>
         </is>
       </c>
-      <c r="N2" s="38" t="inlineStr"/>
-      <c r="O2" s="38" t="inlineStr"/>
-      <c r="P2" s="38" t="inlineStr"/>
-      <c r="Q2" s="36" t="inlineStr">
+      <c r="N2" s="43" t="inlineStr"/>
+      <c r="O2" s="43" t="inlineStr"/>
+      <c r="P2" s="43" t="inlineStr"/>
+      <c r="Q2" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R2" s="36" t="inlineStr">
+      <c r="R2" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S2" s="36" t="inlineStr">
+      <c r="S2" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T2" s="36" t="inlineStr">
+      <c r="T2" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U2" s="36" t="inlineStr"/>
-      <c r="V2" s="36" t="inlineStr">
+      <c r="U2" s="41" t="inlineStr"/>
+      <c r="V2" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W2" s="36" t="inlineStr">
+      <c r="W2" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X2" s="36" t="inlineStr">
+      <c r="X2" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5449,7 +5553,7 @@
           <t>https://www.spa-components.com/user/shop/big/1473-1_filter-cartridge-sc779-rising-dragon-plastics--eago-whirlpools.jpg?ff=1&amp;x=1024&amp;y=768&amp;q=85&amp;ts=6720c4a0&amp;sg=161563f2</t>
         </is>
       </c>
-      <c r="Z2" s="36" t="inlineStr">
+      <c r="Z2" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5459,7 +5563,7 @@
           <t>Filter Cartridge SC779 - Rising Dragon Plastics, EAGO Whirlpools - Spa Components</t>
         </is>
       </c>
-      <c r="AB2" s="36" t="inlineStr">
+      <c r="AB2" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5471,14 +5575,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF2" s="36" t="inlineStr"/>
-      <c r="AG2" s="36" t="inlineStr"/>
-      <c r="AH2" s="36" t="inlineStr">
+      <c r="AF2" s="41" t="inlineStr"/>
+      <c r="AG2" s="41" t="inlineStr"/>
+      <c r="AH2" s="41" t="inlineStr">
         <is>
           <t>26.0cm</t>
         </is>
       </c>
-      <c r="AI2" s="36" t="inlineStr"/>
+      <c r="AI2" s="41" t="inlineStr"/>
     </row>
     <row r="3" ht="62" customHeight="1">
       <c r="A3" s="25" t="inlineStr">
@@ -5496,13 +5600,13 @@
           <t>A twin pack of Size II replacement filter cartridges measuring 10.6 x 13.6 cm, designed for compatible pool and spa filtration systems. The fine lamellar structure delivers thorough water cleaning and the cartridges are easy to rinse clean.</t>
         </is>
       </c>
-      <c r="D3" s="36" t="inlineStr"/>
-      <c r="E3" s="36" t="inlineStr">
+      <c r="D3" s="41" t="inlineStr"/>
+      <c r="E3" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F3" s="36" t="inlineStr">
+      <c r="F3" s="41" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5512,71 +5616,71 @@
           <t>filters, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H3" s="36" t="inlineStr">
+      <c r="H3" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I3" s="36" t="inlineStr">
+      <c r="I3" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J3" s="36" t="inlineStr">
+      <c r="J3" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K3" s="36" t="inlineStr">
+      <c r="K3" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L3" s="36" t="inlineStr">
+      <c r="L3" s="41" t="inlineStr">
         <is>
           <t>GEN-FIL-3615</t>
         </is>
       </c>
-      <c r="M3" s="37" t="inlineStr">
+      <c r="M3" s="42" t="inlineStr">
         <is>
           <t>6941607353615</t>
         </is>
       </c>
-      <c r="N3" s="38" t="inlineStr"/>
-      <c r="O3" s="38" t="inlineStr"/>
-      <c r="P3" s="38" t="inlineStr"/>
-      <c r="Q3" s="36" t="inlineStr">
+      <c r="N3" s="43" t="inlineStr"/>
+      <c r="O3" s="43" t="inlineStr"/>
+      <c r="P3" s="43" t="inlineStr"/>
+      <c r="Q3" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R3" s="36" t="inlineStr">
+      <c r="R3" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S3" s="36" t="inlineStr">
+      <c r="S3" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T3" s="36" t="inlineStr">
+      <c r="T3" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U3" s="36" t="inlineStr"/>
-      <c r="V3" s="36" t="inlineStr">
+      <c r="U3" s="41" t="inlineStr"/>
+      <c r="V3" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W3" s="36" t="inlineStr">
+      <c r="W3" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X3" s="36" t="inlineStr">
+      <c r="X3" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5586,7 +5690,7 @@
           <t>https://www.bestwaystore.de/media/c6/f8/ba/1756384660/6941607353615-main-jpg.jpg?ts=1756384660</t>
         </is>
       </c>
-      <c r="Z3" s="36" t="inlineStr">
+      <c r="Z3" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5596,7 +5700,7 @@
           <t>Filter cartridge Size II double pack, 10.6 x 13.6 cm | 58094_26</t>
         </is>
       </c>
-      <c r="AB3" s="36" t="inlineStr">
+      <c r="AB3" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5608,14 +5712,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF3" s="36" t="inlineStr"/>
-      <c r="AG3" s="36" t="inlineStr"/>
-      <c r="AH3" s="36" t="inlineStr">
+      <c r="AF3" s="41" t="inlineStr"/>
+      <c r="AG3" s="41" t="inlineStr"/>
+      <c r="AH3" s="41" t="inlineStr">
         <is>
           <t>10.6cm</t>
         </is>
       </c>
-      <c r="AI3" s="36" t="inlineStr">
+      <c r="AI3" s="41" t="inlineStr">
         <is>
           <t>13.6cm</t>
         </is>
@@ -5637,17 +5741,17 @@
           <t>A Size 3 replacement filter cartridge for Bestway Flowclear filtration systems, designed to remove deposits and dirt from pool water. Its fine lamellar structure makes it easy to clean and maintain.</t>
         </is>
       </c>
-      <c r="D4" s="36" t="inlineStr">
+      <c r="D4" s="41" t="inlineStr">
         <is>
           <t>Bestway</t>
         </is>
       </c>
-      <c r="E4" s="36" t="inlineStr">
+      <c r="E4" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F4" s="36" t="inlineStr">
+      <c r="F4" s="41" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5657,71 +5761,71 @@
           <t>filters, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H4" s="36" t="inlineStr">
+      <c r="H4" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I4" s="36" t="inlineStr">
+      <c r="I4" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J4" s="36" t="inlineStr">
+      <c r="J4" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K4" s="36" t="inlineStr">
+      <c r="K4" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L4" s="36" t="inlineStr">
+      <c r="L4" s="41" t="inlineStr">
         <is>
           <t>BES-FIL-3592</t>
         </is>
       </c>
-      <c r="M4" s="37" t="inlineStr">
+      <c r="M4" s="42" t="inlineStr">
         <is>
           <t>6941607353592</t>
         </is>
       </c>
-      <c r="N4" s="38" t="inlineStr"/>
-      <c r="O4" s="38" t="inlineStr"/>
-      <c r="P4" s="38" t="inlineStr"/>
-      <c r="Q4" s="36" t="inlineStr">
+      <c r="N4" s="43" t="inlineStr"/>
+      <c r="O4" s="43" t="inlineStr"/>
+      <c r="P4" s="43" t="inlineStr"/>
+      <c r="Q4" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R4" s="36" t="inlineStr">
+      <c r="R4" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S4" s="36" t="inlineStr">
+      <c r="S4" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T4" s="36" t="inlineStr">
+      <c r="T4" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U4" s="36" t="inlineStr"/>
-      <c r="V4" s="36" t="inlineStr">
+      <c r="U4" s="41" t="inlineStr"/>
+      <c r="V4" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W4" s="36" t="inlineStr">
+      <c r="W4" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X4" s="36" t="inlineStr">
+      <c r="X4" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5731,7 +5835,7 @@
           <t>https://ap.nice-cdn.com/upload/image/product/large/default/bestway-flowclear-filter-cartridge-size-3-1-item-638140-en.jpg</t>
         </is>
       </c>
-      <c r="Z4" s="36" t="inlineStr">
+      <c r="Z4" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5741,7 +5845,7 @@
           <t>Bestway Flowclear™ Filter Cartridge Size 3, 1 item</t>
         </is>
       </c>
-      <c r="AB4" s="36" t="inlineStr">
+      <c r="AB4" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5753,10 +5857,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF4" s="36" t="inlineStr"/>
-      <c r="AG4" s="36" t="inlineStr"/>
-      <c r="AH4" s="36" t="inlineStr"/>
-      <c r="AI4" s="36" t="inlineStr"/>
+      <c r="AF4" s="41" t="inlineStr"/>
+      <c r="AG4" s="41" t="inlineStr"/>
+      <c r="AH4" s="41" t="inlineStr"/>
+      <c r="AI4" s="41" t="inlineStr"/>
     </row>
     <row r="5" ht="76" customHeight="1">
       <c r="A5" s="25" t="inlineStr">
@@ -5774,17 +5878,17 @@
           <t>A hot tub and spa filter cartridge measuring 125 mm in diameter and 235 mm in length, with 54 mm openings at both ends. Sold as a 2-pack, it is compatible with Unicel C-4335, Pleatco PRB35-IN, Filbur FC-2385, and a long list of other manufacturer codes including Sundance Spas and Jacuzzi 6000-136.</t>
         </is>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D5" s="41" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E5" s="36" t="inlineStr">
+      <c r="E5" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F5" s="36" t="inlineStr">
+      <c r="F5" s="41" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5794,71 +5898,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H5" s="36" t="inlineStr">
+      <c r="H5" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I5" s="36" t="inlineStr">
+      <c r="I5" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J5" s="36" t="inlineStr">
+      <c r="J5" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K5" s="36" t="inlineStr">
+      <c r="K5" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L5" s="36" t="inlineStr">
+      <c r="L5" s="41" t="inlineStr">
         <is>
           <t>DAR-FIL-1669</t>
         </is>
       </c>
-      <c r="M5" s="37" t="inlineStr">
+      <c r="M5" s="42" t="inlineStr">
         <is>
           <t>700175991669</t>
         </is>
       </c>
-      <c r="N5" s="38" t="inlineStr"/>
-      <c r="O5" s="38" t="inlineStr"/>
-      <c r="P5" s="38" t="inlineStr"/>
-      <c r="Q5" s="36" t="inlineStr">
+      <c r="N5" s="43" t="inlineStr"/>
+      <c r="O5" s="43" t="inlineStr"/>
+      <c r="P5" s="43" t="inlineStr"/>
+      <c r="Q5" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R5" s="36" t="inlineStr">
+      <c r="R5" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S5" s="36" t="inlineStr">
+      <c r="S5" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T5" s="36" t="inlineStr">
+      <c r="T5" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U5" s="36" t="inlineStr"/>
-      <c r="V5" s="36" t="inlineStr">
+      <c r="U5" s="41" t="inlineStr"/>
+      <c r="V5" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W5" s="36" t="inlineStr">
+      <c r="W5" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X5" s="36" t="inlineStr">
+      <c r="X5" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -5868,7 +5972,7 @@
           <t>https://images.barcodelookup.com/29361/293617958-1.jpg</t>
         </is>
       </c>
-      <c r="Z5" s="36" t="inlineStr">
+      <c r="Z5" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5878,7 +5982,7 @@
           <t>Darlly Hot Tub Spa Filter SC705 40353 Compatible with Unicel C-4335 PRB35-IN Filbur FC-2385 2 Pack</t>
         </is>
       </c>
-      <c r="AB5" s="36" t="inlineStr">
+      <c r="AB5" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5890,14 +5994,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF5" s="36" t="inlineStr"/>
-      <c r="AG5" s="36" t="inlineStr"/>
-      <c r="AH5" s="36" t="inlineStr">
+      <c r="AF5" s="41" t="inlineStr"/>
+      <c r="AG5" s="41" t="inlineStr"/>
+      <c r="AH5" s="41" t="inlineStr">
         <is>
           <t>12.5cm</t>
         </is>
       </c>
-      <c r="AI5" s="36" t="inlineStr">
+      <c r="AI5" s="41" t="inlineStr">
         <is>
           <t>23.5cm</t>
         </is>
@@ -5919,13 +6023,13 @@
           <t>A single Size IV replacement filter cartridge measuring 14.2 x 25.4 cm, compatible with Bestway filter pump 58391 (9,463 l/h). Its deep-fold, fine-structure media delivers thorough water cleaning and can be rinsed clean with minimal effort.</t>
         </is>
       </c>
-      <c r="D6" s="36" t="inlineStr"/>
-      <c r="E6" s="36" t="inlineStr">
+      <c r="D6" s="41" t="inlineStr"/>
+      <c r="E6" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F6" s="36" t="inlineStr">
+      <c r="F6" s="41" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -5935,71 +6039,71 @@
           <t>filters, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H6" s="36" t="inlineStr">
+      <c r="H6" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I6" s="36" t="inlineStr">
+      <c r="I6" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J6" s="36" t="inlineStr">
+      <c r="J6" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K6" s="36" t="inlineStr">
+      <c r="K6" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L6" s="36" t="inlineStr">
+      <c r="L6" s="41" t="inlineStr">
         <is>
           <t>GEN-FIL-3622</t>
         </is>
       </c>
-      <c r="M6" s="37" t="inlineStr">
+      <c r="M6" s="42" t="inlineStr">
         <is>
           <t>6941607353622</t>
         </is>
       </c>
-      <c r="N6" s="38" t="inlineStr"/>
-      <c r="O6" s="38" t="inlineStr"/>
-      <c r="P6" s="38" t="inlineStr"/>
-      <c r="Q6" s="36" t="inlineStr">
+      <c r="N6" s="43" t="inlineStr"/>
+      <c r="O6" s="43" t="inlineStr"/>
+      <c r="P6" s="43" t="inlineStr"/>
+      <c r="Q6" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R6" s="36" t="inlineStr">
+      <c r="R6" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S6" s="36" t="inlineStr">
+      <c r="S6" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T6" s="36" t="inlineStr">
+      <c r="T6" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U6" s="36" t="inlineStr"/>
-      <c r="V6" s="36" t="inlineStr">
+      <c r="U6" s="41" t="inlineStr"/>
+      <c r="V6" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W6" s="36" t="inlineStr">
+      <c r="W6" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X6" s="36" t="inlineStr">
+      <c r="X6" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6009,7 +6113,7 @@
           <t>https://www.bestwaystore.de/media/53/6c/e9/1756384676/6941607353622-main-jpg.jpg?ts=1756384676</t>
         </is>
       </c>
-      <c r="Z6" s="36" t="inlineStr">
+      <c r="Z6" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6019,7 +6123,7 @@
           <t>Filter cartridge Size IV 14.2 x 25.4 cm | 58095_26</t>
         </is>
       </c>
-      <c r="AB6" s="36" t="inlineStr">
+      <c r="AB6" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6031,14 +6135,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF6" s="36" t="inlineStr"/>
-      <c r="AG6" s="36" t="inlineStr"/>
-      <c r="AH6" s="36" t="inlineStr">
+      <c r="AF6" s="41" t="inlineStr"/>
+      <c r="AG6" s="41" t="inlineStr"/>
+      <c r="AH6" s="41" t="inlineStr">
         <is>
           <t>14.2cm</t>
         </is>
       </c>
-      <c r="AI6" s="36" t="inlineStr">
+      <c r="AI6" s="41" t="inlineStr">
         <is>
           <t>25.4cm</t>
         </is>
@@ -6060,17 +6164,17 @@
           <t>A pair of spa and whirlpool replacement filter cartridges, compatible with Unicel C-4401 and Pleatco PRB17.5SF PR (code SC726). Sold as a set of two, they suit a range of hot tub brands.</t>
         </is>
       </c>
-      <c r="D7" s="36" t="inlineStr">
+      <c r="D7" s="41" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E7" s="36" t="inlineStr">
+      <c r="E7" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F7" s="36" t="inlineStr">
+      <c r="F7" s="41" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6080,71 +6184,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H7" s="36" t="inlineStr">
+      <c r="H7" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I7" s="36" t="inlineStr">
+      <c r="I7" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J7" s="36" t="inlineStr">
+      <c r="J7" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K7" s="36" t="inlineStr">
+      <c r="K7" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L7" s="36" t="inlineStr">
+      <c r="L7" s="41" t="inlineStr">
         <is>
           <t>DAR-FIL-1874</t>
         </is>
       </c>
-      <c r="M7" s="37" t="inlineStr">
+      <c r="M7" s="42" t="inlineStr">
         <is>
           <t>700175991874</t>
         </is>
       </c>
-      <c r="N7" s="38" t="inlineStr"/>
-      <c r="O7" s="38" t="inlineStr"/>
-      <c r="P7" s="38" t="inlineStr"/>
-      <c r="Q7" s="36" t="inlineStr">
+      <c r="N7" s="43" t="inlineStr"/>
+      <c r="O7" s="43" t="inlineStr"/>
+      <c r="P7" s="43" t="inlineStr"/>
+      <c r="Q7" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R7" s="36" t="inlineStr">
+      <c r="R7" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S7" s="36" t="inlineStr">
+      <c r="S7" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T7" s="36" t="inlineStr">
+      <c r="T7" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U7" s="36" t="inlineStr"/>
-      <c r="V7" s="36" t="inlineStr">
+      <c r="U7" s="41" t="inlineStr"/>
+      <c r="V7" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W7" s="36" t="inlineStr">
+      <c r="W7" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X7" s="36" t="inlineStr">
+      <c r="X7" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6154,7 +6258,7 @@
           <t>https://images.barcodelookup.com/4378/43786454-1.jpg</t>
         </is>
       </c>
-      <c r="Z7" s="36" t="inlineStr">
+      <c r="Z7" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6164,7 +6268,7 @@
           <t>Darlly Spa Filter C-4401, PRB17.5SF PR, SC726 (Pair)</t>
         </is>
       </c>
-      <c r="AB7" s="36" t="inlineStr">
+      <c r="AB7" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6176,10 +6280,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF7" s="36" t="inlineStr"/>
-      <c r="AG7" s="36" t="inlineStr"/>
-      <c r="AH7" s="36" t="inlineStr"/>
-      <c r="AI7" s="36" t="inlineStr"/>
+      <c r="AF7" s="41" t="inlineStr"/>
+      <c r="AG7" s="41" t="inlineStr"/>
+      <c r="AH7" s="41" t="inlineStr"/>
+      <c r="AI7" s="41" t="inlineStr"/>
     </row>
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="25" t="inlineStr">
@@ -6197,17 +6301,17 @@
           <t>A replacement spa filter cartridge compatible with Arctic, Beachcomber, Canadian, Hydropool and Jacuzzi spas, sold under cross-reference codes including Unicel C-4950, Pleatco PRB50-IN and Darlly 40506. It keeps hot tub water clean by trapping debris and particles as water cycles through the filtration system.</t>
         </is>
       </c>
-      <c r="D8" s="36" t="inlineStr">
+      <c r="D8" s="41" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E8" s="36" t="inlineStr">
+      <c r="E8" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F8" s="36" t="inlineStr">
+      <c r="F8" s="41" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6217,71 +6321,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H8" s="36" t="inlineStr">
+      <c r="H8" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I8" s="36" t="inlineStr">
+      <c r="I8" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J8" s="36" t="inlineStr">
+      <c r="J8" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K8" s="36" t="inlineStr">
+      <c r="K8" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L8" s="36" t="inlineStr">
+      <c r="L8" s="41" t="inlineStr">
         <is>
           <t>DAR-FIL-1676</t>
         </is>
       </c>
-      <c r="M8" s="37" t="inlineStr">
+      <c r="M8" s="42" t="inlineStr">
         <is>
           <t>700175991676</t>
         </is>
       </c>
-      <c r="N8" s="38" t="inlineStr"/>
-      <c r="O8" s="38" t="inlineStr"/>
-      <c r="P8" s="38" t="inlineStr"/>
-      <c r="Q8" s="36" t="inlineStr">
+      <c r="N8" s="43" t="inlineStr"/>
+      <c r="O8" s="43" t="inlineStr"/>
+      <c r="P8" s="43" t="inlineStr"/>
+      <c r="Q8" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R8" s="36" t="inlineStr">
+      <c r="R8" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S8" s="36" t="inlineStr">
+      <c r="S8" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T8" s="36" t="inlineStr">
+      <c r="T8" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U8" s="36" t="inlineStr"/>
-      <c r="V8" s="36" t="inlineStr">
+      <c r="U8" s="41" t="inlineStr"/>
+      <c r="V8" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W8" s="36" t="inlineStr">
+      <c r="W8" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X8" s="36" t="inlineStr">
+      <c r="X8" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6291,7 +6395,7 @@
           <t>https://images.barcodelookup.com/4469/44699532-1.jpg</t>
         </is>
       </c>
-      <c r="Z8" s="36" t="inlineStr">
+      <c r="Z8" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6301,7 +6405,7 @@
           <t>Hot Tub Filter Unicel C4950 / C-4950 50' Spa Cartridge Pleatco PRB501N Darlly 40506 for Arctic, Beachcomber, Canadian,…</t>
         </is>
       </c>
-      <c r="AB8" s="36" t="inlineStr">
+      <c r="AB8" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6313,10 +6417,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF8" s="36" t="inlineStr"/>
-      <c r="AG8" s="36" t="inlineStr"/>
-      <c r="AH8" s="36" t="inlineStr"/>
-      <c r="AI8" s="36" t="inlineStr"/>
+      <c r="AF8" s="41" t="inlineStr"/>
+      <c r="AG8" s="41" t="inlineStr"/>
+      <c r="AH8" s="41" t="inlineStr"/>
+      <c r="AI8" s="41" t="inlineStr"/>
     </row>
     <row r="9" ht="76" customHeight="1">
       <c r="A9" s="25" t="inlineStr">
@@ -6334,13 +6438,13 @@
           <t>A square inflatable hot tub for up to four people, with an overall outer diameter of 2.45 m and a structure measuring 1.75 x 1.75 x 0.71 m, built from high-resistance polyester for good rigidity and durability. The packaged weight is 64.92 kg, so you will want a helper on delivery day.</t>
         </is>
       </c>
-      <c r="D9" s="36" t="inlineStr"/>
-      <c r="E9" s="36" t="inlineStr">
+      <c r="D9" s="41" t="inlineStr"/>
+      <c r="E9" s="41" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F9" s="36" t="inlineStr">
+      <c r="F9" s="41" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -6350,75 +6454,75 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H9" s="36" t="inlineStr">
+      <c r="H9" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I9" s="36" t="inlineStr">
+      <c r="I9" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J9" s="36" t="inlineStr">
+      <c r="J9" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K9" s="36" t="inlineStr">
+      <c r="K9" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L9" s="36" t="inlineStr">
+      <c r="L9" s="41" t="inlineStr">
         <is>
           <t>GEN-SPA-3395</t>
         </is>
       </c>
-      <c r="M9" s="37" t="inlineStr">
+      <c r="M9" s="42" t="inlineStr">
         <is>
           <t>6941057423395</t>
         </is>
       </c>
-      <c r="N9" s="38" t="inlineStr"/>
-      <c r="O9" s="38" t="inlineStr"/>
-      <c r="P9" s="38" t="inlineStr"/>
-      <c r="Q9" s="36" t="inlineStr">
+      <c r="N9" s="43" t="inlineStr"/>
+      <c r="O9" s="43" t="inlineStr"/>
+      <c r="P9" s="43" t="inlineStr"/>
+      <c r="Q9" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R9" s="36" t="inlineStr">
+      <c r="R9" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S9" s="36" t="inlineStr">
+      <c r="S9" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T9" s="36" t="inlineStr">
+      <c r="T9" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U9" s="36" t="inlineStr">
+      <c r="U9" s="41" t="inlineStr">
         <is>
           <t>64920</t>
         </is>
       </c>
-      <c r="V9" s="36" t="inlineStr">
+      <c r="V9" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W9" s="36" t="inlineStr">
+      <c r="W9" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X9" s="36" t="inlineStr">
+      <c r="X9" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6428,7 +6532,7 @@
           <t>https://media.intex.fr/7743-large_default_x2/28464ex-spa-gonflable-calacatta-4-places.jpg</t>
         </is>
       </c>
-      <c r="Z9" s="36" t="inlineStr">
+      <c r="Z9" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6438,7 +6542,7 @@
           <t>Calacatta 4-person inflatable spa</t>
         </is>
       </c>
-      <c r="AB9" s="36" t="inlineStr">
+      <c r="AB9" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6450,18 +6554,18 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF9" s="36" t="inlineStr"/>
-      <c r="AG9" s="36" t="inlineStr">
+      <c r="AF9" s="41" t="inlineStr"/>
+      <c r="AG9" s="41" t="inlineStr">
         <is>
           <t>175.0cm</t>
         </is>
       </c>
-      <c r="AH9" s="36" t="inlineStr">
+      <c r="AH9" s="41" t="inlineStr">
         <is>
           <t>175.0cm</t>
         </is>
       </c>
-      <c r="AI9" s="36" t="inlineStr">
+      <c r="AI9" s="41" t="inlineStr">
         <is>
           <t>71.0cm</t>
         </is>
@@ -6483,17 +6587,17 @@
           <t>A 3.0 kg tub of hth stabiliser granules for outdoor swimming pools, used to protect chlorine from UV degradation and extend its effectiveness. A reliable way to get more mileage from your sanitiser on sunny days.</t>
         </is>
       </c>
-      <c r="D10" s="36" t="inlineStr">
+      <c r="D10" s="41" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E10" s="36" t="inlineStr">
+      <c r="E10" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F10" s="36" t="inlineStr">
+      <c r="F10" s="41" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -6503,75 +6607,75 @@
           <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H10" s="36" t="inlineStr">
+      <c r="H10" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I10" s="36" t="inlineStr">
+      <c r="I10" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J10" s="36" t="inlineStr">
+      <c r="J10" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K10" s="36" t="inlineStr">
+      <c r="K10" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L10" s="36" t="inlineStr">
+      <c r="L10" s="41" t="inlineStr">
         <is>
           <t>HTH-CHM-5716</t>
         </is>
       </c>
-      <c r="M10" s="37" t="inlineStr">
+      <c r="M10" s="42" t="inlineStr">
         <is>
           <t>3521686005716</t>
         </is>
       </c>
-      <c r="N10" s="38" t="inlineStr"/>
-      <c r="O10" s="38" t="inlineStr"/>
-      <c r="P10" s="38" t="inlineStr"/>
-      <c r="Q10" s="36" t="inlineStr">
+      <c r="N10" s="43" t="inlineStr"/>
+      <c r="O10" s="43" t="inlineStr"/>
+      <c r="P10" s="43" t="inlineStr"/>
+      <c r="Q10" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R10" s="36" t="inlineStr">
+      <c r="R10" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S10" s="36" t="inlineStr">
+      <c r="S10" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T10" s="36" t="inlineStr">
+      <c r="T10" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U10" s="36" t="inlineStr">
+      <c r="U10" s="41" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="V10" s="36" t="inlineStr">
+      <c r="V10" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W10" s="36" t="inlineStr">
+      <c r="W10" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X10" s="36" t="inlineStr">
+      <c r="X10" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6581,7 +6685,7 @@
           <t>https://images.barcodelookup.com/12027/120276177-1.jpg</t>
         </is>
       </c>
-      <c r="Z10" s="36" t="inlineStr">
+      <c r="Z10" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6591,7 +6695,7 @@
           <t>Hth Stabilizer Granulat 3,0 Kg</t>
         </is>
       </c>
-      <c r="AB10" s="36" t="inlineStr">
+      <c r="AB10" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6603,10 +6707,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF10" s="36" t="inlineStr"/>
-      <c r="AG10" s="36" t="inlineStr"/>
-      <c r="AH10" s="36" t="inlineStr"/>
-      <c r="AI10" s="36" t="inlineStr"/>
+      <c r="AF10" s="41" t="inlineStr"/>
+      <c r="AG10" s="41" t="inlineStr"/>
+      <c r="AH10" s="41" t="inlineStr"/>
+      <c r="AI10" s="41" t="inlineStr"/>
     </row>
     <row r="11" ht="76" customHeight="1">
       <c r="A11" s="25" t="inlineStr">
@@ -6624,17 +6728,17 @@
           <t>A liquid anti-scale treatment for hot tubs, supplied in a 1-litre bottle, that reduces limescale build-up on surfaces and fittings without affecting pH levels. Non-foaming at recommended doses, it is intended for regular use in water with a total hardness above 250 mg/l.</t>
         </is>
       </c>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="D11" s="41" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E11" s="36" t="inlineStr">
+      <c r="E11" s="41" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F11" s="36" t="inlineStr">
+      <c r="F11" s="41" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -6644,75 +6748,75 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H11" s="36" t="inlineStr">
+      <c r="H11" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I11" s="36" t="inlineStr">
+      <c r="I11" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J11" s="36" t="inlineStr">
+      <c r="J11" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K11" s="36" t="inlineStr">
+      <c r="K11" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L11" s="36" t="inlineStr">
+      <c r="L11" s="41" t="inlineStr">
         <is>
           <t>HTH-SPA-0194</t>
         </is>
       </c>
-      <c r="M11" s="37" t="inlineStr">
+      <c r="M11" s="42" t="inlineStr">
         <is>
           <t>3521684700194</t>
         </is>
       </c>
-      <c r="N11" s="38" t="inlineStr"/>
-      <c r="O11" s="38" t="inlineStr"/>
-      <c r="P11" s="38" t="inlineStr"/>
-      <c r="Q11" s="36" t="inlineStr">
+      <c r="N11" s="43" t="inlineStr"/>
+      <c r="O11" s="43" t="inlineStr"/>
+      <c r="P11" s="43" t="inlineStr"/>
+      <c r="Q11" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R11" s="36" t="inlineStr">
+      <c r="R11" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S11" s="36" t="inlineStr">
+      <c r="S11" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T11" s="36" t="inlineStr">
+      <c r="T11" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U11" s="36" t="inlineStr">
+      <c r="U11" s="41" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="V11" s="36" t="inlineStr">
+      <c r="V11" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W11" s="36" t="inlineStr">
+      <c r="W11" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X11" s="36" t="inlineStr">
+      <c r="X11" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6722,7 +6826,7 @@
           <t>https://www.north-spa.de/wp-content/uploads/2025/02/Produktbild-1-hth-SPA-ANTIKALK-1-l-3521684700194-360x360.jpg</t>
         </is>
       </c>
-      <c r="Z11" s="36" t="inlineStr">
+      <c r="Z11" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6732,7 +6836,7 @@
           <t>1 l - hth® Spa ANTIKALK</t>
         </is>
       </c>
-      <c r="AB11" s="36" t="inlineStr">
+      <c r="AB11" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6744,18 +6848,18 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF11" s="36" t="inlineStr"/>
-      <c r="AG11" s="36" t="inlineStr">
+      <c r="AF11" s="41" t="inlineStr"/>
+      <c r="AG11" s="41" t="inlineStr">
         <is>
           <t>18.0cm</t>
         </is>
       </c>
-      <c r="AH11" s="36" t="inlineStr">
+      <c r="AH11" s="41" t="inlineStr">
         <is>
           <t>24.0cm</t>
         </is>
       </c>
-      <c r="AI11" s="36" t="inlineStr">
+      <c r="AI11" s="41" t="inlineStr">
         <is>
           <t>27.0cm</t>
         </is>
@@ -6777,13 +6881,13 @@
           <t>A round, olive-green inflatable spa for up to 8 people, with a maximum water temperature of 40°C. It comes with 5 included accessories and makes a generous, sociable addition to any garden or terrace.</t>
         </is>
       </c>
-      <c r="D12" s="36" t="inlineStr"/>
-      <c r="E12" s="36" t="inlineStr">
+      <c r="D12" s="41" t="inlineStr"/>
+      <c r="E12" s="41" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F12" s="36" t="inlineStr">
+      <c r="F12" s="41" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -6793,71 +6897,71 @@
           <t>spa-hot-tub, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H12" s="36" t="inlineStr">
+      <c r="H12" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I12" s="36" t="inlineStr">
+      <c r="I12" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J12" s="36" t="inlineStr">
+      <c r="J12" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K12" s="36" t="inlineStr">
+      <c r="K12" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L12" s="36" t="inlineStr">
+      <c r="L12" s="41" t="inlineStr">
         <is>
           <t>GEN-SPA-9274</t>
         </is>
       </c>
-      <c r="M12" s="37" t="inlineStr">
+      <c r="M12" s="42" t="inlineStr">
         <is>
           <t>6941057429274</t>
         </is>
       </c>
-      <c r="N12" s="38" t="inlineStr"/>
-      <c r="O12" s="38" t="inlineStr"/>
-      <c r="P12" s="38" t="inlineStr"/>
-      <c r="Q12" s="36" t="inlineStr">
+      <c r="N12" s="43" t="inlineStr"/>
+      <c r="O12" s="43" t="inlineStr"/>
+      <c r="P12" s="43" t="inlineStr"/>
+      <c r="Q12" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R12" s="36" t="inlineStr">
+      <c r="R12" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S12" s="36" t="inlineStr">
+      <c r="S12" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T12" s="36" t="inlineStr">
+      <c r="T12" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U12" s="36" t="inlineStr"/>
-      <c r="V12" s="36" t="inlineStr">
+      <c r="U12" s="41" t="inlineStr"/>
+      <c r="V12" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W12" s="36" t="inlineStr">
+      <c r="W12" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X12" s="36" t="inlineStr">
+      <c r="X12" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -6867,7 +6971,7 @@
           <t>https://media.intex.fr/11990-large_default_x2/28412np-spa-gonflable-olive-8-places.jpg</t>
         </is>
       </c>
-      <c r="Z12" s="36" t="inlineStr">
+      <c r="Z12" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6877,7 +6981,7 @@
           <t>Olive 8-person inflatable spa</t>
         </is>
       </c>
-      <c r="AB12" s="36" t="inlineStr">
+      <c r="AB12" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -6889,10 +6993,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF12" s="36" t="inlineStr"/>
-      <c r="AG12" s="36" t="inlineStr"/>
-      <c r="AH12" s="36" t="inlineStr"/>
-      <c r="AI12" s="36" t="inlineStr"/>
+      <c r="AF12" s="41" t="inlineStr"/>
+      <c r="AG12" s="41" t="inlineStr"/>
+      <c r="AH12" s="41" t="inlineStr"/>
+      <c r="AI12" s="41" t="inlineStr"/>
     </row>
     <row r="13" ht="76" customHeight="1">
       <c r="A13" s="25" t="inlineStr">
@@ -6910,17 +7014,17 @@
           <t>A replacement spa filter cartridge (SC750) compatible with Arctic, Fonteyn, Rota, and other brands, also cross-referencing Pleatco PWW10, Unicel C-4310, and Filbur FC-3077. It also matches several LeisureBay, PDC, Sedona, Viking, and Roto Spa models.</t>
         </is>
       </c>
-      <c r="D13" s="36" t="inlineStr">
+      <c r="D13" s="41" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E13" s="36" t="inlineStr">
+      <c r="E13" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F13" s="36" t="inlineStr">
+      <c r="F13" s="41" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -6930,71 +7034,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H13" s="36" t="inlineStr">
+      <c r="H13" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I13" s="36" t="inlineStr">
+      <c r="I13" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J13" s="36" t="inlineStr">
+      <c r="J13" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K13" s="36" t="inlineStr">
+      <c r="K13" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L13" s="36" t="inlineStr">
+      <c r="L13" s="41" t="inlineStr">
         <is>
           <t>DAR-FIL-2116</t>
         </is>
       </c>
-      <c r="M13" s="37" t="inlineStr">
+      <c r="M13" s="42" t="inlineStr">
         <is>
           <t>700175992116</t>
         </is>
       </c>
-      <c r="N13" s="38" t="inlineStr"/>
-      <c r="O13" s="38" t="inlineStr"/>
-      <c r="P13" s="38" t="inlineStr"/>
-      <c r="Q13" s="36" t="inlineStr">
+      <c r="N13" s="43" t="inlineStr"/>
+      <c r="O13" s="43" t="inlineStr"/>
+      <c r="P13" s="43" t="inlineStr"/>
+      <c r="Q13" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R13" s="36" t="inlineStr">
+      <c r="R13" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S13" s="36" t="inlineStr">
+      <c r="S13" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T13" s="36" t="inlineStr">
+      <c r="T13" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U13" s="36" t="inlineStr"/>
-      <c r="V13" s="36" t="inlineStr">
+      <c r="U13" s="41" t="inlineStr"/>
+      <c r="V13" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W13" s="36" t="inlineStr">
+      <c r="W13" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X13" s="36" t="inlineStr">
+      <c r="X13" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7004,7 +7108,7 @@
           <t>https://images.barcodelookup.com/29338/293384728-1.jpg</t>
         </is>
       </c>
-      <c r="Z13" s="36" t="inlineStr">
+      <c r="Z13" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7014,7 +7118,7 @@
           <t>SC750 Filter replacement filter lamellar filter Arctic Fonteyn Rota Strong Spa - Darlly</t>
         </is>
       </c>
-      <c r="AB13" s="36" t="inlineStr">
+      <c r="AB13" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7026,10 +7130,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF13" s="36" t="inlineStr"/>
-      <c r="AG13" s="36" t="inlineStr"/>
-      <c r="AH13" s="36" t="inlineStr"/>
-      <c r="AI13" s="36" t="inlineStr"/>
+      <c r="AF13" s="41" t="inlineStr"/>
+      <c r="AG13" s="41" t="inlineStr"/>
+      <c r="AH13" s="41" t="inlineStr"/>
+      <c r="AI13" s="41" t="inlineStr"/>
     </row>
     <row r="14" ht="76" customHeight="1">
       <c r="A14" s="25" t="inlineStr">
@@ -7047,17 +7151,17 @@
           <t>A mild spray-on cleaner for spa surfaces, designed for the underside of the insulating cover, the acrylic shell, and cushions. It removes dirt and odours using a plant-based active ingredient, and is simply sprayed on, left briefly, then rinsed off with water.</t>
         </is>
       </c>
-      <c r="D14" s="36" t="inlineStr">
+      <c r="D14" s="41" t="inlineStr">
         <is>
           <t>SpaBalancer</t>
         </is>
       </c>
-      <c r="E14" s="36" t="inlineStr">
+      <c r="E14" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F14" s="36" t="inlineStr">
+      <c r="F14" s="41" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -7067,71 +7171,71 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H14" s="36" t="inlineStr">
+      <c r="H14" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I14" s="36" t="inlineStr">
+      <c r="I14" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J14" s="36" t="inlineStr">
+      <c r="J14" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K14" s="36" t="inlineStr">
+      <c r="K14" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L14" s="36" t="inlineStr">
+      <c r="L14" s="41" t="inlineStr">
         <is>
           <t>SPA-CLN-0117</t>
         </is>
       </c>
-      <c r="M14" s="37" t="inlineStr">
+      <c r="M14" s="42" t="inlineStr">
         <is>
           <t>4260374980117</t>
         </is>
       </c>
-      <c r="N14" s="38" t="inlineStr"/>
-      <c r="O14" s="38" t="inlineStr"/>
-      <c r="P14" s="38" t="inlineStr"/>
-      <c r="Q14" s="36" t="inlineStr">
+      <c r="N14" s="43" t="inlineStr"/>
+      <c r="O14" s="43" t="inlineStr"/>
+      <c r="P14" s="43" t="inlineStr"/>
+      <c r="Q14" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R14" s="36" t="inlineStr">
+      <c r="R14" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S14" s="36" t="inlineStr">
+      <c r="S14" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T14" s="36" t="inlineStr">
+      <c r="T14" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U14" s="36" t="inlineStr"/>
-      <c r="V14" s="36" t="inlineStr">
+      <c r="U14" s="41" t="inlineStr"/>
+      <c r="V14" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W14" s="36" t="inlineStr">
+      <c r="W14" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X14" s="36" t="inlineStr">
+      <c r="X14" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7141,7 +7245,7 @@
           <t>https://www.spabalancer.ch/media/ae/20/d2/1728651174/sb111_clean-refresh_freigestellt.png?ts=1777362921</t>
         </is>
       </c>
-      <c r="Z14" s="36" t="inlineStr">
+      <c r="Z14" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7151,7 +7255,7 @@
           <t>SpaBalancer Clean &amp; Refresh (+ sprayer)</t>
         </is>
       </c>
-      <c r="AB14" s="36" t="inlineStr">
+      <c r="AB14" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7163,10 +7267,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF14" s="36" t="inlineStr"/>
-      <c r="AG14" s="36" t="inlineStr"/>
-      <c r="AH14" s="36" t="inlineStr"/>
-      <c r="AI14" s="36" t="inlineStr"/>
+      <c r="AF14" s="41" t="inlineStr"/>
+      <c r="AG14" s="41" t="inlineStr"/>
+      <c r="AH14" s="41" t="inlineStr"/>
+      <c r="AI14" s="41" t="inlineStr"/>
     </row>
     <row r="15" ht="76" customHeight="1">
       <c r="A15" s="25" t="inlineStr">
@@ -7184,17 +7288,17 @@
           <t>DPD No. 1 photometer reagent tablets for testing bromine, chloramine, chlorine, chlorine dioxide, and ozone in water, with a measuring range of 0 to 8 mg/L. This pack of 500 tablets suits routine water quality monitoring in pools, spas, laboratories, or field use.</t>
         </is>
       </c>
-      <c r="D15" s="36" t="inlineStr">
+      <c r="D15" s="41" t="inlineStr">
         <is>
           <t>Water-i.d.</t>
         </is>
       </c>
-      <c r="E15" s="36" t="inlineStr">
+      <c r="E15" s="41" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F15" s="36" t="inlineStr">
+      <c r="F15" s="41" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -7204,71 +7308,71 @@
           <t>test-measure, add-on, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H15" s="36" t="inlineStr">
+      <c r="H15" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I15" s="36" t="inlineStr">
+      <c r="I15" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J15" s="36" t="inlineStr">
+      <c r="J15" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K15" s="36" t="inlineStr">
+      <c r="K15" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L15" s="36" t="inlineStr">
+      <c r="L15" s="41" t="inlineStr">
         <is>
           <t>WAT-TST-1702</t>
         </is>
       </c>
-      <c r="M15" s="37" t="inlineStr">
+      <c r="M15" s="42" t="inlineStr">
         <is>
           <t>4260431461702</t>
         </is>
       </c>
-      <c r="N15" s="38" t="inlineStr"/>
-      <c r="O15" s="38" t="inlineStr"/>
-      <c r="P15" s="38" t="inlineStr"/>
-      <c r="Q15" s="36" t="inlineStr">
+      <c r="N15" s="43" t="inlineStr"/>
+      <c r="O15" s="43" t="inlineStr"/>
+      <c r="P15" s="43" t="inlineStr"/>
+      <c r="Q15" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R15" s="36" t="inlineStr">
+      <c r="R15" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S15" s="36" t="inlineStr">
+      <c r="S15" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T15" s="36" t="inlineStr">
+      <c r="T15" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U15" s="36" t="inlineStr"/>
-      <c r="V15" s="36" t="inlineStr">
+      <c r="U15" s="41" t="inlineStr"/>
+      <c r="V15" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W15" s="36" t="inlineStr">
+      <c r="W15" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X15" s="36" t="inlineStr">
+      <c r="X15" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7278,7 +7382,7 @@
           <t>https://labfriendcoredataprod.blob.core.windows.net/johnmorriscore-data-prod/images/thumbs/1913450_primelab-reagent-50-tablets-dpd-n-1-photometer_2194587_415.jpeg</t>
         </is>
       </c>
-      <c r="Z15" s="36" t="inlineStr">
+      <c r="Z15" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7288,7 +7392,7 @@
           <t>WATER-I.D. Water-ID Reagenzien DPD 1 Photometer 500</t>
         </is>
       </c>
-      <c r="AB15" s="36" t="inlineStr">
+      <c r="AB15" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7300,10 +7404,10 @@
           <t>Pool Accessories</t>
         </is>
       </c>
-      <c r="AF15" s="36" t="inlineStr"/>
-      <c r="AG15" s="36" t="inlineStr"/>
-      <c r="AH15" s="36" t="inlineStr"/>
-      <c r="AI15" s="36" t="inlineStr"/>
+      <c r="AF15" s="41" t="inlineStr"/>
+      <c r="AG15" s="41" t="inlineStr"/>
+      <c r="AH15" s="41" t="inlineStr"/>
+      <c r="AI15" s="41" t="inlineStr"/>
     </row>
     <row r="16" ht="62" customHeight="1">
       <c r="A16" s="25" t="inlineStr">
@@ -7321,17 +7425,17 @@
           <t>Phenol Red reagent tablets for use with a compatible photometer to test pH levels in pool or spa water. The source information does not provide further specifics for this variant beyond the reagent type.</t>
         </is>
       </c>
-      <c r="D16" s="36" t="inlineStr">
+      <c r="D16" s="41" t="inlineStr">
         <is>
           <t>Water-i.d.</t>
         </is>
       </c>
-      <c r="E16" s="36" t="inlineStr">
+      <c r="E16" s="41" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F16" s="36" t="inlineStr">
+      <c r="F16" s="41" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -7341,71 +7445,71 @@
           <t>test-measure, add-on, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H16" s="36" t="inlineStr">
+      <c r="H16" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I16" s="36" t="inlineStr">
+      <c r="I16" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J16" s="36" t="inlineStr">
+      <c r="J16" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K16" s="36" t="inlineStr">
+      <c r="K16" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L16" s="36" t="inlineStr">
+      <c r="L16" s="41" t="inlineStr">
         <is>
           <t>WAT-TST-1801</t>
         </is>
       </c>
-      <c r="M16" s="37" t="inlineStr">
+      <c r="M16" s="42" t="inlineStr">
         <is>
           <t>4260431461801</t>
         </is>
       </c>
-      <c r="N16" s="38" t="inlineStr"/>
-      <c r="O16" s="38" t="inlineStr"/>
-      <c r="P16" s="38" t="inlineStr"/>
-      <c r="Q16" s="36" t="inlineStr">
+      <c r="N16" s="43" t="inlineStr"/>
+      <c r="O16" s="43" t="inlineStr"/>
+      <c r="P16" s="43" t="inlineStr"/>
+      <c r="Q16" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R16" s="36" t="inlineStr">
+      <c r="R16" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S16" s="36" t="inlineStr">
+      <c r="S16" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T16" s="36" t="inlineStr">
+      <c r="T16" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U16" s="36" t="inlineStr"/>
-      <c r="V16" s="36" t="inlineStr">
+      <c r="U16" s="41" t="inlineStr"/>
+      <c r="V16" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W16" s="36" t="inlineStr">
+      <c r="W16" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X16" s="36" t="inlineStr">
+      <c r="X16" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7415,7 +7519,7 @@
           <t>https://www.poolpowershop.de/media/46/63/13/1743521499/phenol-red-testtabletten-fuer-poollab-500-stk.jpg</t>
         </is>
       </c>
-      <c r="Z16" s="36" t="inlineStr">
+      <c r="Z16" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7425,7 +7529,7 @@
           <t>WATER-I.D. Water-ID Reagenzien Phenol Red Photometer 500</t>
         </is>
       </c>
-      <c r="AB16" s="36" t="inlineStr">
+      <c r="AB16" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7437,10 +7541,10 @@
           <t>Pool Accessories</t>
         </is>
       </c>
-      <c r="AF16" s="36" t="inlineStr"/>
-      <c r="AG16" s="36" t="inlineStr"/>
-      <c r="AH16" s="36" t="inlineStr"/>
-      <c r="AI16" s="36" t="inlineStr"/>
+      <c r="AF16" s="41" t="inlineStr"/>
+      <c r="AG16" s="41" t="inlineStr"/>
+      <c r="AH16" s="41" t="inlineStr"/>
+      <c r="AI16" s="41" t="inlineStr"/>
     </row>
     <row r="17" ht="62" customHeight="1">
       <c r="A17" s="25" t="inlineStr">
@@ -7458,17 +7562,17 @@
           <t>An alkaline liquid edge and tile cleaner for pools, formulated to be safe on liners and plastic surfaces. It removes grease, dirt, and waterline residue, and is supplied in a 1-litre bottle.</t>
         </is>
       </c>
-      <c r="D17" s="36" t="inlineStr">
+      <c r="D17" s="41" t="inlineStr">
         <is>
           <t>Cristal</t>
         </is>
       </c>
-      <c r="E17" s="36" t="inlineStr">
+      <c r="E17" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F17" s="36" t="inlineStr">
+      <c r="F17" s="41" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -7478,71 +7582,71 @@
           <t>pool, water-treatment, cleaning, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H17" s="36" t="inlineStr">
+      <c r="H17" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I17" s="36" t="inlineStr">
+      <c r="I17" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J17" s="36" t="inlineStr">
+      <c r="J17" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K17" s="36" t="inlineStr">
+      <c r="K17" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L17" s="36" t="inlineStr">
+      <c r="L17" s="41" t="inlineStr">
         <is>
           <t>CRI-CHM-5212</t>
         </is>
       </c>
-      <c r="M17" s="37" t="inlineStr">
+      <c r="M17" s="42" t="inlineStr">
         <is>
           <t>4002369155212</t>
         </is>
       </c>
-      <c r="N17" s="38" t="inlineStr"/>
-      <c r="O17" s="38" t="inlineStr"/>
-      <c r="P17" s="38" t="inlineStr"/>
-      <c r="Q17" s="36" t="inlineStr">
+      <c r="N17" s="43" t="inlineStr"/>
+      <c r="O17" s="43" t="inlineStr"/>
+      <c r="P17" s="43" t="inlineStr"/>
+      <c r="Q17" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R17" s="36" t="inlineStr">
+      <c r="R17" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S17" s="36" t="inlineStr">
+      <c r="S17" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T17" s="36" t="inlineStr">
+      <c r="T17" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U17" s="36" t="inlineStr"/>
-      <c r="V17" s="36" t="inlineStr">
+      <c r="U17" s="41" t="inlineStr"/>
+      <c r="V17" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W17" s="36" t="inlineStr">
+      <c r="W17" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X17" s="36" t="inlineStr">
+      <c r="X17" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7552,7 +7656,7 @@
           <t>https://images.barcodelookup.com/21057/210579756-1.jpg</t>
         </is>
       </c>
-      <c r="Z17" s="36" t="inlineStr">
+      <c r="Z17" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7562,7 +7666,7 @@
           <t>Cristal Poolpflege CRISTAL edge cleaner alkaline 1,0 l, (material-safe, for liners, plastic</t>
         </is>
       </c>
-      <c r="AB17" s="36" t="inlineStr">
+      <c r="AB17" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7574,10 +7678,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF17" s="36" t="inlineStr"/>
-      <c r="AG17" s="36" t="inlineStr"/>
-      <c r="AH17" s="36" t="inlineStr"/>
-      <c r="AI17" s="36" t="inlineStr"/>
+      <c r="AF17" s="41" t="inlineStr"/>
+      <c r="AG17" s="41" t="inlineStr"/>
+      <c r="AH17" s="41" t="inlineStr"/>
+      <c r="AI17" s="41" t="inlineStr"/>
     </row>
     <row r="18" ht="62" customHeight="1">
       <c r="A18" s="25" t="inlineStr">
@@ -7595,17 +7699,17 @@
           <t>A pool cleaner designed to remove sunscreen oil and greasy residues from the water surface, supplied in a 1-litre bottle. Formulated for pools with heavy swimming loads and warm climates.</t>
         </is>
       </c>
-      <c r="D18" s="36" t="inlineStr">
+      <c r="D18" s="41" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E18" s="36" t="inlineStr">
+      <c r="E18" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F18" s="36" t="inlineStr">
+      <c r="F18" s="41" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -7615,71 +7719,71 @@
           <t>pool, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H18" s="36" t="inlineStr">
+      <c r="H18" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I18" s="36" t="inlineStr">
+      <c r="I18" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J18" s="36" t="inlineStr">
+      <c r="J18" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K18" s="36" t="inlineStr">
+      <c r="K18" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L18" s="36" t="inlineStr">
+      <c r="L18" s="41" t="inlineStr">
         <is>
           <t>AQU-CLN-0223</t>
         </is>
       </c>
-      <c r="M18" s="37" t="inlineStr">
+      <c r="M18" s="42" t="inlineStr">
         <is>
           <t>5292638000223</t>
         </is>
       </c>
-      <c r="N18" s="38" t="inlineStr"/>
-      <c r="O18" s="38" t="inlineStr"/>
-      <c r="P18" s="38" t="inlineStr"/>
-      <c r="Q18" s="36" t="inlineStr">
+      <c r="N18" s="43" t="inlineStr"/>
+      <c r="O18" s="43" t="inlineStr"/>
+      <c r="P18" s="43" t="inlineStr"/>
+      <c r="Q18" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R18" s="36" t="inlineStr">
+      <c r="R18" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S18" s="36" t="inlineStr">
+      <c r="S18" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T18" s="36" t="inlineStr">
+      <c r="T18" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U18" s="36" t="inlineStr"/>
-      <c r="V18" s="36" t="inlineStr">
+      <c r="U18" s="41" t="inlineStr"/>
+      <c r="V18" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W18" s="36" t="inlineStr">
+      <c r="W18" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X18" s="36" t="inlineStr">
+      <c r="X18" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7689,7 +7793,7 @@
           <t>http://mangas.com.cy/media/products/5292638000223.jpg</t>
         </is>
       </c>
-      <c r="Z18" s="36" t="inlineStr">
+      <c r="Z18" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7699,7 +7803,7 @@
           <t>AQUALITY Pool cleaner for greasy residue 1L</t>
         </is>
       </c>
-      <c r="AB18" s="36" t="inlineStr">
+      <c r="AB18" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7711,10 +7815,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF18" s="36" t="inlineStr"/>
-      <c r="AG18" s="36" t="inlineStr"/>
-      <c r="AH18" s="36" t="inlineStr"/>
-      <c r="AI18" s="36" t="inlineStr"/>
+      <c r="AF18" s="41" t="inlineStr"/>
+      <c r="AG18" s="41" t="inlineStr"/>
+      <c r="AH18" s="41" t="inlineStr"/>
+      <c r="AI18" s="41" t="inlineStr"/>
     </row>
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="25" t="inlineStr">
@@ -7732,17 +7836,17 @@
           <t>A super-concentrated cationic polymer pool clarifier in a 1-litre viscous blue liquid format, designed to bind microscopic particles such as dust, pollen, and oils into larger clusters that filtration systems can capture. pH-neutral and compatible with sand, zeolite, and glass filter media, it is applied at 60 ml per 10 m³ for cloudy water treatment.</t>
         </is>
       </c>
-      <c r="D19" s="36" t="inlineStr">
+      <c r="D19" s="41" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E19" s="36" t="inlineStr">
+      <c r="E19" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F19" s="36" t="inlineStr">
+      <c r="F19" s="41" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -7752,71 +7856,71 @@
           <t>pool, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H19" s="36" t="inlineStr">
+      <c r="H19" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I19" s="36" t="inlineStr">
+      <c r="I19" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J19" s="36" t="inlineStr">
+      <c r="J19" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K19" s="36" t="inlineStr">
+      <c r="K19" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L19" s="36" t="inlineStr">
+      <c r="L19" s="41" t="inlineStr">
         <is>
           <t>AQU-CHM-0070</t>
         </is>
       </c>
-      <c r="M19" s="37" t="inlineStr">
+      <c r="M19" s="42" t="inlineStr">
         <is>
           <t>5292638000070</t>
         </is>
       </c>
-      <c r="N19" s="38" t="inlineStr"/>
-      <c r="O19" s="38" t="inlineStr"/>
-      <c r="P19" s="38" t="inlineStr"/>
-      <c r="Q19" s="36" t="inlineStr">
+      <c r="N19" s="43" t="inlineStr"/>
+      <c r="O19" s="43" t="inlineStr"/>
+      <c r="P19" s="43" t="inlineStr"/>
+      <c r="Q19" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R19" s="36" t="inlineStr">
+      <c r="R19" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S19" s="36" t="inlineStr">
+      <c r="S19" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T19" s="36" t="inlineStr">
+      <c r="T19" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U19" s="36" t="inlineStr"/>
-      <c r="V19" s="36" t="inlineStr">
+      <c r="U19" s="41" t="inlineStr"/>
+      <c r="V19" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W19" s="36" t="inlineStr">
+      <c r="W19" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X19" s="36" t="inlineStr">
+      <c r="X19" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7826,7 +7930,7 @@
           <t>https://poolservices.cy/storage/2026/05/California-Clear-Blue-1L-Aquality-2.jpeg</t>
         </is>
       </c>
-      <c r="Z19" s="36" t="inlineStr">
+      <c r="Z19" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7836,7 +7940,7 @@
           <t>Pool Clarifier California Clear Blue Aquality 1L</t>
         </is>
       </c>
-      <c r="AB19" s="36" t="inlineStr">
+      <c r="AB19" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7848,10 +7952,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF19" s="36" t="inlineStr"/>
-      <c r="AG19" s="36" t="inlineStr"/>
-      <c r="AH19" s="36" t="inlineStr"/>
-      <c r="AI19" s="36" t="inlineStr"/>
+      <c r="AF19" s="41" t="inlineStr"/>
+      <c r="AG19" s="41" t="inlineStr"/>
+      <c r="AH19" s="41" t="inlineStr"/>
+      <c r="AI19" s="41" t="inlineStr"/>
     </row>
     <row r="20" ht="62" customHeight="1">
       <c r="A20" s="25" t="inlineStr">
@@ -7869,17 +7973,17 @@
           <t>A 1-litre vinyl and tile cleaner for pools, safe for use on pool surfaces including liners. Beyond the product name, the source provides no further detail on its formulation or specific application instructions.</t>
         </is>
       </c>
-      <c r="D20" s="36" t="inlineStr">
+      <c r="D20" s="41" t="inlineStr">
         <is>
           <t>Aquality</t>
         </is>
       </c>
-      <c r="E20" s="36" t="inlineStr">
+      <c r="E20" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F20" s="36" t="inlineStr">
+      <c r="F20" s="41" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -7889,71 +7993,71 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H20" s="36" t="inlineStr">
+      <c r="H20" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I20" s="36" t="inlineStr">
+      <c r="I20" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J20" s="36" t="inlineStr">
+      <c r="J20" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K20" s="36" t="inlineStr">
+      <c r="K20" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L20" s="36" t="inlineStr">
+      <c r="L20" s="41" t="inlineStr">
         <is>
           <t>AQU-CLN-0162</t>
         </is>
       </c>
-      <c r="M20" s="37" t="inlineStr">
+      <c r="M20" s="42" t="inlineStr">
         <is>
           <t>5292638000162</t>
         </is>
       </c>
-      <c r="N20" s="38" t="inlineStr"/>
-      <c r="O20" s="38" t="inlineStr"/>
-      <c r="P20" s="38" t="inlineStr"/>
-      <c r="Q20" s="36" t="inlineStr">
+      <c r="N20" s="43" t="inlineStr"/>
+      <c r="O20" s="43" t="inlineStr"/>
+      <c r="P20" s="43" t="inlineStr"/>
+      <c r="Q20" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R20" s="36" t="inlineStr">
+      <c r="R20" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S20" s="36" t="inlineStr">
+      <c r="S20" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T20" s="36" t="inlineStr">
+      <c r="T20" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U20" s="36" t="inlineStr"/>
-      <c r="V20" s="36" t="inlineStr">
+      <c r="U20" s="41" t="inlineStr"/>
+      <c r="V20" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W20" s="36" t="inlineStr">
+      <c r="W20" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X20" s="36" t="inlineStr">
+      <c r="X20" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -7963,7 +8067,7 @@
           <t>http://mangas.com.cy/media/products/5292638000162.jpg</t>
         </is>
       </c>
-      <c r="Z20" s="36" t="inlineStr">
+      <c r="Z20" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7973,7 +8077,7 @@
           <t>AQUALITY Magic tile 4 vinyl cleaner 1L</t>
         </is>
       </c>
-      <c r="AB20" s="36" t="inlineStr">
+      <c r="AB20" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -7985,10 +8089,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF20" s="36" t="inlineStr"/>
-      <c r="AG20" s="36" t="inlineStr"/>
-      <c r="AH20" s="36" t="inlineStr"/>
-      <c r="AI20" s="36" t="inlineStr"/>
+      <c r="AF20" s="41" t="inlineStr"/>
+      <c r="AG20" s="41" t="inlineStr"/>
+      <c r="AH20" s="41" t="inlineStr"/>
+      <c r="AI20" s="41" t="inlineStr"/>
     </row>
     <row r="21" ht="62" customHeight="1">
       <c r="A21" s="25" t="inlineStr">
@@ -8006,17 +8110,17 @@
           <t>A liquid turbidity remover for spas and pools, supplied in a 1-litre bottle, that clears cloudy or hazy water. The source does not specify its active compounds, so the description stays with what is stated.</t>
         </is>
       </c>
-      <c r="D21" s="36" t="inlineStr">
+      <c r="D21" s="41" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E21" s="36" t="inlineStr">
+      <c r="E21" s="41" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F21" s="36" t="inlineStr">
+      <c r="F21" s="41" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -8026,71 +8130,71 @@
           <t>spa-hot-tub, pool, water-treatment, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H21" s="36" t="inlineStr">
+      <c r="H21" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I21" s="36" t="inlineStr">
+      <c r="I21" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J21" s="36" t="inlineStr">
+      <c r="J21" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K21" s="36" t="inlineStr">
+      <c r="K21" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L21" s="36" t="inlineStr">
+      <c r="L21" s="41" t="inlineStr">
         <is>
           <t>HFE-SPA-7202</t>
         </is>
       </c>
-      <c r="M21" s="37" t="inlineStr">
+      <c r="M21" s="42" t="inlineStr">
         <is>
           <t>4250463127202</t>
         </is>
       </c>
-      <c r="N21" s="38" t="inlineStr"/>
-      <c r="O21" s="38" t="inlineStr"/>
-      <c r="P21" s="38" t="inlineStr"/>
-      <c r="Q21" s="36" t="inlineStr">
+      <c r="N21" s="43" t="inlineStr"/>
+      <c r="O21" s="43" t="inlineStr"/>
+      <c r="P21" s="43" t="inlineStr"/>
+      <c r="Q21" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R21" s="36" t="inlineStr">
+      <c r="R21" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S21" s="36" t="inlineStr">
+      <c r="S21" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T21" s="36" t="inlineStr">
+      <c r="T21" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U21" s="36" t="inlineStr"/>
-      <c r="V21" s="36" t="inlineStr">
+      <c r="U21" s="41" t="inlineStr"/>
+      <c r="V21" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W21" s="36" t="inlineStr">
+      <c r="W21" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X21" s="36" t="inlineStr">
+      <c r="X21" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8100,7 +8204,7 @@
           <t>https://hoefer-shop.com/cdn/shop/files/1x1L-BAYZID-Spa-Poolclear-v1-RS_1.jpg?v=1785600487&amp;width=800</t>
         </is>
       </c>
-      <c r="Z21" s="36" t="inlineStr">
+      <c r="Z21" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8110,7 +8214,7 @@
           <t>Höfer Chemie GmbH pool care 1 L BAYZID® SPA Poolclear turbidity remover</t>
         </is>
       </c>
-      <c r="AB21" s="36" t="inlineStr">
+      <c r="AB21" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8122,10 +8226,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF21" s="36" t="inlineStr"/>
-      <c r="AG21" s="36" t="inlineStr"/>
-      <c r="AH21" s="36" t="inlineStr"/>
-      <c r="AI21" s="36" t="inlineStr"/>
+      <c r="AF21" s="41" t="inlineStr"/>
+      <c r="AG21" s="41" t="inlineStr"/>
+      <c r="AH21" s="41" t="inlineStr"/>
+      <c r="AI21" s="41" t="inlineStr"/>
     </row>
     <row r="22" ht="76" customHeight="1">
       <c r="A22" s="25" t="inlineStr">
@@ -8143,17 +8247,17 @@
           <t>An 11.9% concentration hydrogen peroxide solution in a 1-litre bottle, suitable for stain removal, disinfection, and oxidation applications. As with all hydrogen peroxide products, it should be handled carefully and kept away from incompatible materials.</t>
         </is>
       </c>
-      <c r="D22" s="36" t="inlineStr">
+      <c r="D22" s="41" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E22" s="36" t="inlineStr">
+      <c r="E22" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F22" s="36" t="inlineStr">
+      <c r="F22" s="41" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8163,71 +8267,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H22" s="36" t="inlineStr">
+      <c r="H22" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I22" s="36" t="inlineStr">
+      <c r="I22" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J22" s="36" t="inlineStr">
+      <c r="J22" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K22" s="36" t="inlineStr">
+      <c r="K22" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L22" s="36" t="inlineStr">
+      <c r="L22" s="41" t="inlineStr">
         <is>
           <t>HFE-CHM-6788</t>
         </is>
       </c>
-      <c r="M22" s="37" t="inlineStr">
+      <c r="M22" s="42" t="inlineStr">
         <is>
           <t>4250463106788</t>
         </is>
       </c>
-      <c r="N22" s="38" t="inlineStr"/>
-      <c r="O22" s="38" t="inlineStr"/>
-      <c r="P22" s="38" t="inlineStr"/>
-      <c r="Q22" s="36" t="inlineStr">
+      <c r="N22" s="43" t="inlineStr"/>
+      <c r="O22" s="43" t="inlineStr"/>
+      <c r="P22" s="43" t="inlineStr"/>
+      <c r="Q22" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R22" s="36" t="inlineStr">
+      <c r="R22" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S22" s="36" t="inlineStr">
+      <c r="S22" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T22" s="36" t="inlineStr">
+      <c r="T22" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U22" s="36" t="inlineStr"/>
-      <c r="V22" s="36" t="inlineStr">
+      <c r="U22" s="41" t="inlineStr"/>
+      <c r="V22" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W22" s="36" t="inlineStr">
+      <c r="W22" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X22" s="36" t="inlineStr">
+      <c r="X22" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8237,7 +8341,7 @@
           <t>https://hoefer-shop.com/cdn/shop/files/1x1L-Wasserstoffperoxid-Flasche-hinten-26.jpg?v=1783777627&amp;width=1000</t>
         </is>
       </c>
-      <c r="Z22" s="36" t="inlineStr">
+      <c r="Z22" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8247,7 +8351,7 @@
           <t>HÖFER CHEMIE GMBH 1 l hydrogen peroxide 11,9%</t>
         </is>
       </c>
-      <c r="AB22" s="36" t="inlineStr">
+      <c r="AB22" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8259,10 +8363,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF22" s="36" t="inlineStr"/>
-      <c r="AG22" s="36" t="inlineStr"/>
-      <c r="AH22" s="36" t="inlineStr"/>
-      <c r="AI22" s="36" t="inlineStr"/>
+      <c r="AF22" s="41" t="inlineStr"/>
+      <c r="AG22" s="41" t="inlineStr"/>
+      <c r="AH22" s="41" t="inlineStr"/>
+      <c r="AI22" s="41" t="inlineStr"/>
     </row>
     <row r="23" ht="90" customHeight="1">
       <c r="A23" s="25" t="inlineStr">
@@ -8280,17 +8384,17 @@
           <t>A granulated chlorine stabiliser for swimming pools, supplied in a 4.5 kg pack, that shields chlorine from UV degradation and prolongs its disinfecting action. Applied via skimmers or pump pre-filter at the start of the season, it includes a dispenser and is recommended by the Royal Spanish Swimming Federation.</t>
         </is>
       </c>
-      <c r="D23" s="36" t="inlineStr">
+      <c r="D23" s="41" t="inlineStr">
         <is>
           <t>AstralPool</t>
         </is>
       </c>
-      <c r="E23" s="36" t="inlineStr">
+      <c r="E23" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F23" s="36" t="inlineStr">
+      <c r="F23" s="41" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8300,75 +8404,75 @@
           <t>water-treatment, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H23" s="36" t="inlineStr">
+      <c r="H23" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I23" s="36" t="inlineStr">
+      <c r="I23" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J23" s="36" t="inlineStr">
+      <c r="J23" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K23" s="36" t="inlineStr">
+      <c r="K23" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L23" s="36" t="inlineStr">
+      <c r="L23" s="41" t="inlineStr">
         <is>
           <t>AST-CHM-0626</t>
         </is>
       </c>
-      <c r="M23" s="37" t="inlineStr">
+      <c r="M23" s="42" t="inlineStr">
         <is>
           <t>8432611960626</t>
         </is>
       </c>
-      <c r="N23" s="38" t="inlineStr"/>
-      <c r="O23" s="38" t="inlineStr"/>
-      <c r="P23" s="38" t="inlineStr"/>
-      <c r="Q23" s="36" t="inlineStr">
+      <c r="N23" s="43" t="inlineStr"/>
+      <c r="O23" s="43" t="inlineStr"/>
+      <c r="P23" s="43" t="inlineStr"/>
+      <c r="Q23" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R23" s="36" t="inlineStr">
+      <c r="R23" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S23" s="36" t="inlineStr">
+      <c r="S23" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T23" s="36" t="inlineStr">
+      <c r="T23" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U23" s="36" t="inlineStr">
+      <c r="U23" s="41" t="inlineStr">
         <is>
           <t>4500</t>
         </is>
       </c>
-      <c r="V23" s="36" t="inlineStr">
+      <c r="V23" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W23" s="36" t="inlineStr">
+      <c r="W23" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X23" s="36" t="inlineStr">
+      <c r="X23" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8378,7 +8482,7 @@
           <t>https://yokando.com/img/p/2/8/2/9/3/28293.jpg</t>
         </is>
       </c>
-      <c r="Z23" s="36" t="inlineStr">
+      <c r="Z23" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8388,7 +8492,7 @@
           <t>Astralpool water care Astralpool Chlorine Stabilizer 4,5 kg</t>
         </is>
       </c>
-      <c r="AB23" s="36" t="inlineStr">
+      <c r="AB23" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8400,10 +8504,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF23" s="36" t="inlineStr"/>
-      <c r="AG23" s="36" t="inlineStr"/>
-      <c r="AH23" s="36" t="inlineStr"/>
-      <c r="AI23" s="36" t="inlineStr"/>
+      <c r="AF23" s="41" t="inlineStr"/>
+      <c r="AG23" s="41" t="inlineStr"/>
+      <c r="AH23" s="41" t="inlineStr"/>
+      <c r="AI23" s="41" t="inlineStr"/>
     </row>
     <row r="24" ht="62" customHeight="1">
       <c r="A24" s="25" t="inlineStr">
@@ -8421,17 +8525,17 @@
           <t>A hot-tub water disinfection treatment for use as a shock dose to sanitise spa water. Note that the product has a limited shelf life and loses roughly 8 to 10% of its efficacy per month, so buying in advance is not recommended.</t>
         </is>
       </c>
-      <c r="D24" s="36" t="inlineStr">
+      <c r="D24" s="41" t="inlineStr">
         <is>
           <t>SpaBalancer</t>
         </is>
       </c>
-      <c r="E24" s="36" t="inlineStr">
+      <c r="E24" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F24" s="36" t="inlineStr">
+      <c r="F24" s="41" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -8441,71 +8545,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H24" s="36" t="inlineStr">
+      <c r="H24" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I24" s="36" t="inlineStr">
+      <c r="I24" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J24" s="36" t="inlineStr">
+      <c r="J24" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K24" s="36" t="inlineStr">
+      <c r="K24" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L24" s="36" t="inlineStr">
+      <c r="L24" s="41" t="inlineStr">
         <is>
           <t>SPA-CHM-0025</t>
         </is>
       </c>
-      <c r="M24" s="37" t="inlineStr">
+      <c r="M24" s="42" t="inlineStr">
         <is>
           <t>4260374980025</t>
         </is>
       </c>
-      <c r="N24" s="38" t="inlineStr"/>
-      <c r="O24" s="38" t="inlineStr"/>
-      <c r="P24" s="38" t="inlineStr"/>
-      <c r="Q24" s="36" t="inlineStr">
+      <c r="N24" s="43" t="inlineStr"/>
+      <c r="O24" s="43" t="inlineStr"/>
+      <c r="P24" s="43" t="inlineStr"/>
+      <c r="Q24" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R24" s="36" t="inlineStr">
+      <c r="R24" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S24" s="36" t="inlineStr">
+      <c r="S24" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T24" s="36" t="inlineStr">
+      <c r="T24" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U24" s="36" t="inlineStr"/>
-      <c r="V24" s="36" t="inlineStr">
+      <c r="U24" s="41" t="inlineStr"/>
+      <c r="V24" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W24" s="36" t="inlineStr">
+      <c r="W24" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X24" s="36" t="inlineStr">
+      <c r="X24" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8515,7 +8619,7 @@
           <t>https://images.barcodelookup.com/16704/167043133-1.jpg</t>
         </is>
       </c>
-      <c r="Z24" s="36" t="inlineStr">
+      <c r="Z24" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8525,7 +8629,7 @@
           <t>SpaBalancer UltraShock</t>
         </is>
       </c>
-      <c r="AB24" s="36" t="inlineStr">
+      <c r="AB24" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8537,10 +8641,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF24" s="36" t="inlineStr"/>
-      <c r="AG24" s="36" t="inlineStr"/>
-      <c r="AH24" s="36" t="inlineStr"/>
-      <c r="AI24" s="36" t="inlineStr"/>
+      <c r="AF24" s="41" t="inlineStr"/>
+      <c r="AG24" s="41" t="inlineStr"/>
+      <c r="AH24" s="41" t="inlineStr"/>
+      <c r="AI24" s="41" t="inlineStr"/>
     </row>
     <row r="25" ht="76" customHeight="1">
       <c r="A25" s="25" t="inlineStr">
@@ -8558,13 +8662,13 @@
           <t>A patented foam eraser that hardens when wet, designed for cleaning the waterline and surfaces of liner and tiled pools without detergents or chemicals. Each box contains 3 sponges, and the eraser also works on skimmers, ladders, pool covers, and plastic garden furniture.</t>
         </is>
       </c>
-      <c r="D25" s="36" t="inlineStr"/>
-      <c r="E25" s="36" t="inlineStr">
+      <c r="D25" s="41" t="inlineStr"/>
+      <c r="E25" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F25" s="36" t="inlineStr">
+      <c r="F25" s="41" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8574,71 +8678,71 @@
           <t>pool, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H25" s="36" t="inlineStr">
+      <c r="H25" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I25" s="36" t="inlineStr">
+      <c r="I25" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J25" s="36" t="inlineStr">
+      <c r="J25" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K25" s="36" t="inlineStr">
+      <c r="K25" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L25" s="36" t="inlineStr">
+      <c r="L25" s="41" t="inlineStr">
         <is>
           <t>GEN-CLN-0062</t>
         </is>
       </c>
-      <c r="M25" s="37" t="inlineStr">
+      <c r="M25" s="42" t="inlineStr">
         <is>
           <t>3760015880062</t>
         </is>
       </c>
-      <c r="N25" s="38" t="inlineStr"/>
-      <c r="O25" s="38" t="inlineStr"/>
-      <c r="P25" s="38" t="inlineStr"/>
-      <c r="Q25" s="36" t="inlineStr">
+      <c r="N25" s="43" t="inlineStr"/>
+      <c r="O25" s="43" t="inlineStr"/>
+      <c r="P25" s="43" t="inlineStr"/>
+      <c r="Q25" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R25" s="36" t="inlineStr">
+      <c r="R25" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S25" s="36" t="inlineStr">
+      <c r="S25" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T25" s="36" t="inlineStr">
+      <c r="T25" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U25" s="36" t="inlineStr"/>
-      <c r="V25" s="36" t="inlineStr">
+      <c r="U25" s="41" t="inlineStr"/>
+      <c r="V25" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W25" s="36" t="inlineStr">
+      <c r="W25" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X25" s="36" t="inlineStr">
+      <c r="X25" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8648,7 +8752,7 @@
           <t>https://www.piscinarium.com/2908-thickbox_default/pool-gom-magic-rubber-eraser.jpg</t>
         </is>
       </c>
-      <c r="Z25" s="36" t="inlineStr">
+      <c r="Z25" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8658,7 +8762,7 @@
           <t>Pool'Gom Magic Rubber Eraser</t>
         </is>
       </c>
-      <c r="AB25" s="36" t="inlineStr">
+      <c r="AB25" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8670,10 +8774,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF25" s="36" t="inlineStr"/>
-      <c r="AG25" s="36" t="inlineStr"/>
-      <c r="AH25" s="36" t="inlineStr"/>
-      <c r="AI25" s="36" t="inlineStr"/>
+      <c r="AF25" s="41" t="inlineStr"/>
+      <c r="AG25" s="41" t="inlineStr"/>
+      <c r="AH25" s="41" t="inlineStr"/>
+      <c r="AI25" s="41" t="inlineStr"/>
     </row>
     <row r="26" ht="76" customHeight="1">
       <c r="A26" s="25" t="inlineStr">
@@ -8691,13 +8795,13 @@
           <t>Spa Industries Europe is a family-run wellness business, founded in 2006, specialising in hot tubs, saunas, and swimming pool products for the European market. The source information describes the company rather than a specific product, so no product details can be provided.</t>
         </is>
       </c>
-      <c r="D26" s="36" t="inlineStr"/>
-      <c r="E26" s="36" t="inlineStr">
+      <c r="D26" s="41" t="inlineStr"/>
+      <c r="E26" s="41" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F26" s="36" t="inlineStr">
+      <c r="F26" s="41" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -8707,71 +8811,71 @@
           <t>spa-hot-tub, considered-purchase, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H26" s="36" t="inlineStr">
+      <c r="H26" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I26" s="36" t="inlineStr">
+      <c r="I26" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J26" s="36" t="inlineStr">
+      <c r="J26" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K26" s="36" t="inlineStr">
+      <c r="K26" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L26" s="36" t="inlineStr">
+      <c r="L26" s="41" t="inlineStr">
         <is>
           <t>GEN-SPA-1968</t>
         </is>
       </c>
-      <c r="M26" s="37" t="inlineStr">
+      <c r="M26" s="42" t="inlineStr">
         <is>
           <t>5425021871968</t>
         </is>
       </c>
-      <c r="N26" s="38" t="inlineStr"/>
-      <c r="O26" s="38" t="inlineStr"/>
-      <c r="P26" s="38" t="inlineStr"/>
-      <c r="Q26" s="36" t="inlineStr">
+      <c r="N26" s="43" t="inlineStr"/>
+      <c r="O26" s="43" t="inlineStr"/>
+      <c r="P26" s="43" t="inlineStr"/>
+      <c r="Q26" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R26" s="36" t="inlineStr">
+      <c r="R26" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S26" s="36" t="inlineStr">
+      <c r="S26" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T26" s="36" t="inlineStr">
+      <c r="T26" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U26" s="36" t="inlineStr"/>
-      <c r="V26" s="36" t="inlineStr">
+      <c r="U26" s="41" t="inlineStr"/>
+      <c r="V26" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W26" s="36" t="inlineStr">
+      <c r="W26" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X26" s="36" t="inlineStr">
+      <c r="X26" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -8781,7 +8885,7 @@
           <t>https://www.spa-industries.eu/wp-content/uploads/2021/06/AWT-Spa-basic-sterling-silver-cover.jpeg</t>
         </is>
       </c>
-      <c r="Z26" s="36" t="inlineStr">
+      <c r="Z26" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8791,7 +8895,7 @@
           <t>Spa Industries Europe</t>
         </is>
       </c>
-      <c r="AB26" s="36" t="inlineStr">
+      <c r="AB26" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8803,10 +8907,10 @@
           <t>Hot Tubs</t>
         </is>
       </c>
-      <c r="AF26" s="36" t="inlineStr"/>
-      <c r="AG26" s="36" t="inlineStr"/>
-      <c r="AH26" s="36" t="inlineStr"/>
-      <c r="AI26" s="36" t="inlineStr"/>
+      <c r="AF26" s="41" t="inlineStr"/>
+      <c r="AG26" s="41" t="inlineStr"/>
+      <c r="AH26" s="41" t="inlineStr"/>
+      <c r="AI26" s="41" t="inlineStr"/>
     </row>
     <row r="27" ht="62" customHeight="1">
       <c r="A27" s="25" t="inlineStr">
@@ -8824,17 +8928,17 @@
           <t>A 1-litre high-concentrate sauna cleaner with eucalyptus fragrance, formulated as a deep-cleaning base cleaner for sauna surfaces. The concentrated formula means a little goes a long way, with a fresh scent to match.</t>
         </is>
       </c>
-      <c r="D27" s="36" t="inlineStr">
+      <c r="D27" s="41" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E27" s="36" t="inlineStr">
+      <c r="E27" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F27" s="36" t="inlineStr">
+      <c r="F27" s="41" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8844,79 +8948,79 @@
           <t>cleaning, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H27" s="36" t="inlineStr">
+      <c r="H27" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I27" s="36" t="inlineStr">
+      <c r="I27" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J27" s="36" t="inlineStr">
+      <c r="J27" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K27" s="36" t="inlineStr">
+      <c r="K27" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L27" s="36" t="inlineStr">
+      <c r="L27" s="41" t="inlineStr">
         <is>
           <t>HFE-CLN-7004</t>
         </is>
       </c>
-      <c r="M27" s="37" t="inlineStr">
+      <c r="M27" s="42" t="inlineStr">
         <is>
           <t>4250463127004</t>
         </is>
       </c>
-      <c r="N27" s="38" t="inlineStr"/>
-      <c r="O27" s="38" t="inlineStr"/>
-      <c r="P27" s="38" t="inlineStr"/>
-      <c r="Q27" s="36" t="inlineStr">
+      <c r="N27" s="43" t="inlineStr"/>
+      <c r="O27" s="43" t="inlineStr"/>
+      <c r="P27" s="43" t="inlineStr"/>
+      <c r="Q27" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R27" s="36" t="inlineStr">
+      <c r="R27" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S27" s="36" t="inlineStr">
+      <c r="S27" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T27" s="36" t="inlineStr">
+      <c r="T27" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U27" s="36" t="inlineStr"/>
-      <c r="V27" s="36" t="inlineStr">
+      <c r="U27" s="41" t="inlineStr"/>
+      <c r="V27" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W27" s="36" t="inlineStr">
+      <c r="W27" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X27" s="36" t="inlineStr">
+      <c r="X27" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y27" s="25" t="inlineStr"/>
-      <c r="Z27" s="36" t="inlineStr"/>
+      <c r="Z27" s="41" t="inlineStr"/>
       <c r="AA27" s="25" t="inlineStr"/>
-      <c r="AB27" s="36" t="inlineStr">
+      <c r="AB27" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -8928,10 +9032,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF27" s="36" t="inlineStr"/>
-      <c r="AG27" s="36" t="inlineStr"/>
-      <c r="AH27" s="36" t="inlineStr"/>
-      <c r="AI27" s="36" t="inlineStr"/>
+      <c r="AF27" s="41" t="inlineStr"/>
+      <c r="AG27" s="41" t="inlineStr"/>
+      <c r="AH27" s="41" t="inlineStr"/>
+      <c r="AI27" s="41" t="inlineStr"/>
     </row>
     <row r="28" ht="76" customHeight="1">
       <c r="A28" s="25" t="inlineStr">
@@ -8949,17 +9053,17 @@
           <t>A periodic spa cleaner that removes mineral deposits including limescale and rust, while cleaning and polishing aluminium, chrome, stainless steel, and enamel surfaces. Its high concentration of active ingredients and pine fragrance make routine maintenance a little more pleasant.</t>
         </is>
       </c>
-      <c r="D28" s="36" t="inlineStr">
+      <c r="D28" s="41" t="inlineStr">
         <is>
           <t>hth</t>
         </is>
       </c>
-      <c r="E28" s="36" t="inlineStr">
+      <c r="E28" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F28" s="36" t="inlineStr">
+      <c r="F28" s="41" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -8969,71 +9073,71 @@
           <t>spa-hot-tub, cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H28" s="36" t="inlineStr">
+      <c r="H28" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I28" s="36" t="inlineStr">
+      <c r="I28" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J28" s="36" t="inlineStr">
+      <c r="J28" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K28" s="36" t="inlineStr">
+      <c r="K28" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L28" s="36" t="inlineStr">
+      <c r="L28" s="41" t="inlineStr">
         <is>
           <t>HTH-CLN-0178</t>
         </is>
       </c>
-      <c r="M28" s="37" t="inlineStr">
+      <c r="M28" s="42" t="inlineStr">
         <is>
           <t>3521686010178</t>
         </is>
       </c>
-      <c r="N28" s="38" t="inlineStr"/>
-      <c r="O28" s="38" t="inlineStr"/>
-      <c r="P28" s="38" t="inlineStr"/>
-      <c r="Q28" s="36" t="inlineStr">
+      <c r="N28" s="43" t="inlineStr"/>
+      <c r="O28" s="43" t="inlineStr"/>
+      <c r="P28" s="43" t="inlineStr"/>
+      <c r="Q28" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R28" s="36" t="inlineStr">
+      <c r="R28" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S28" s="36" t="inlineStr">
+      <c r="S28" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T28" s="36" t="inlineStr">
+      <c r="T28" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U28" s="36" t="inlineStr"/>
-      <c r="V28" s="36" t="inlineStr">
+      <c r="U28" s="41" t="inlineStr"/>
+      <c r="V28" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W28" s="36" t="inlineStr">
+      <c r="W28" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X28" s="36" t="inlineStr">
+      <c r="X28" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9043,7 +9147,7 @@
           <t>https://www.cdiscount.com/pdt2/0/5/1/1/700x700/auc2009356289051/rw/hth-spa-nettoyant-spa-3521686010178.jpg</t>
         </is>
       </c>
-      <c r="Z28" s="36" t="inlineStr">
+      <c r="Z28" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9053,7 +9157,7 @@
           <t>HTH Spa spa cleaner</t>
         </is>
       </c>
-      <c r="AB28" s="36" t="inlineStr">
+      <c r="AB28" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9065,10 +9169,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF28" s="36" t="inlineStr"/>
-      <c r="AG28" s="36" t="inlineStr"/>
-      <c r="AH28" s="36" t="inlineStr"/>
-      <c r="AI28" s="36" t="inlineStr"/>
+      <c r="AF28" s="41" t="inlineStr"/>
+      <c r="AG28" s="41" t="inlineStr"/>
+      <c r="AH28" s="41" t="inlineStr"/>
+      <c r="AI28" s="41" t="inlineStr"/>
     </row>
     <row r="29" ht="62" customHeight="1">
       <c r="A29" s="25" t="inlineStr">
@@ -9086,13 +9190,13 @@
           <t>A 25 kg sack of pure boiling salt (minimum 99.6% NaCl) without an anti-caking agent, meeting EN 973 Type A standard and suitable for use in pool salt electrolysis systems. Not intended for human consumption or animal feed.</t>
         </is>
       </c>
-      <c r="D29" s="36" t="inlineStr"/>
-      <c r="E29" s="36" t="inlineStr">
+      <c r="D29" s="41" t="inlineStr"/>
+      <c r="E29" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F29" s="36" t="inlineStr">
+      <c r="F29" s="41" t="inlineStr">
         <is>
           <t>Pool salt</t>
         </is>
@@ -9102,75 +9206,75 @@
           <t>pool, salt, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H29" s="36" t="inlineStr">
+      <c r="H29" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I29" s="36" t="inlineStr">
+      <c r="I29" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J29" s="36" t="inlineStr">
+      <c r="J29" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K29" s="36" t="inlineStr">
+      <c r="K29" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L29" s="36" t="inlineStr">
+      <c r="L29" s="41" t="inlineStr">
         <is>
           <t>GEN-SLT-6110</t>
         </is>
       </c>
-      <c r="M29" s="37" t="inlineStr">
+      <c r="M29" s="42" t="inlineStr">
         <is>
           <t>9001880976110</t>
         </is>
       </c>
-      <c r="N29" s="38" t="inlineStr"/>
-      <c r="O29" s="38" t="inlineStr"/>
-      <c r="P29" s="38" t="inlineStr"/>
-      <c r="Q29" s="36" t="inlineStr">
+      <c r="N29" s="43" t="inlineStr"/>
+      <c r="O29" s="43" t="inlineStr"/>
+      <c r="P29" s="43" t="inlineStr"/>
+      <c r="Q29" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R29" s="36" t="inlineStr">
+      <c r="R29" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S29" s="36" t="inlineStr">
+      <c r="S29" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T29" s="36" t="inlineStr">
+      <c r="T29" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U29" s="36" t="inlineStr">
+      <c r="U29" s="41" t="inlineStr">
         <is>
           <t>25000</t>
         </is>
       </c>
-      <c r="V29" s="36" t="inlineStr">
+      <c r="V29" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W29" s="36" t="inlineStr">
+      <c r="W29" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X29" s="36" t="inlineStr">
+      <c r="X29" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9180,7 +9284,7 @@
           <t>http://altruan.com/cdn/shop/files/SalinenPoolSalz25kgSack.png?v=1778597596</t>
         </is>
       </c>
-      <c r="Z29" s="36" t="inlineStr">
+      <c r="Z29" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9190,7 +9294,7 @@
           <t>Saline pool salt pure boiling salt without separating agent | Sack (25 kg)</t>
         </is>
       </c>
-      <c r="AB29" s="36" t="inlineStr">
+      <c r="AB29" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9202,14 +9306,14 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF29" s="36" t="inlineStr">
+      <c r="AF29" s="41" t="inlineStr">
         <is>
           <t>Composition: Siedesalz (min. 99.6% NaCl) 100%; Separant/sodium ferrocyanide 4.0–12.0 mg/kg | Grain: &gt;0.63 mm approx. 20%, 0.2–0.63 mm approx. 75%, &lt;0.2 mm approx. 5% | Moisture: &lt;0.08%</t>
         </is>
       </c>
-      <c r="AG29" s="36" t="inlineStr"/>
-      <c r="AH29" s="36" t="inlineStr"/>
-      <c r="AI29" s="36" t="inlineStr"/>
+      <c r="AG29" s="41" t="inlineStr"/>
+      <c r="AH29" s="41" t="inlineStr"/>
+      <c r="AI29" s="41" t="inlineStr"/>
     </row>
     <row r="30" ht="76" customHeight="1">
       <c r="A30" s="25" t="inlineStr">
@@ -9227,17 +9331,17 @@
           <t>A cordless robotic pool cleaner that scrubs both floors and walls automatically, using WavePath navigation to map and cover the pool efficiently. Built-in high-performance filtration and smart control make it a hands-off solution for keeping pool water clear.</t>
         </is>
       </c>
-      <c r="D30" s="36" t="inlineStr">
+      <c r="D30" s="41" t="inlineStr">
         <is>
           <t>Aiper</t>
         </is>
       </c>
-      <c r="E30" s="36" t="inlineStr">
+      <c r="E30" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F30" s="36" t="inlineStr">
+      <c r="F30" s="41" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9247,71 +9351,71 @@
           <t>pool, cleaning, robot-cleaner, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H30" s="36" t="inlineStr">
+      <c r="H30" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I30" s="36" t="inlineStr">
+      <c r="I30" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J30" s="36" t="inlineStr">
+      <c r="J30" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K30" s="36" t="inlineStr">
+      <c r="K30" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L30" s="36" t="inlineStr">
+      <c r="L30" s="41" t="inlineStr">
         <is>
           <t>AIP-ROB-4940</t>
         </is>
       </c>
-      <c r="M30" s="37" t="inlineStr">
+      <c r="M30" s="42" t="inlineStr">
         <is>
           <t>6977676344940</t>
         </is>
       </c>
-      <c r="N30" s="38" t="inlineStr"/>
-      <c r="O30" s="38" t="inlineStr"/>
-      <c r="P30" s="38" t="inlineStr"/>
-      <c r="Q30" s="36" t="inlineStr">
+      <c r="N30" s="43" t="inlineStr"/>
+      <c r="O30" s="43" t="inlineStr"/>
+      <c r="P30" s="43" t="inlineStr"/>
+      <c r="Q30" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R30" s="36" t="inlineStr">
+      <c r="R30" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S30" s="36" t="inlineStr">
+      <c r="S30" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T30" s="36" t="inlineStr">
+      <c r="T30" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U30" s="36" t="inlineStr"/>
-      <c r="V30" s="36" t="inlineStr">
+      <c r="U30" s="41" t="inlineStr"/>
+      <c r="V30" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W30" s="36" t="inlineStr">
+      <c r="W30" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X30" s="36" t="inlineStr">
+      <c r="X30" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9321,7 +9425,7 @@
           <t>https://images.barcodelookup.com/176692/1766920801-1.jpg</t>
         </is>
       </c>
-      <c r="Z30" s="36" t="inlineStr">
+      <c r="Z30" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9331,7 +9435,7 @@
           <t>AIPER Scuba S3 cordless pool robot, automatic floor and wall cleaning, WavePath™ navigation, high-performance filtration…</t>
         </is>
       </c>
-      <c r="AB30" s="36" t="inlineStr">
+      <c r="AB30" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9343,10 +9447,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF30" s="36" t="inlineStr"/>
-      <c r="AG30" s="36" t="inlineStr"/>
-      <c r="AH30" s="36" t="inlineStr"/>
-      <c r="AI30" s="36" t="inlineStr"/>
+      <c r="AF30" s="41" t="inlineStr"/>
+      <c r="AG30" s="41" t="inlineStr"/>
+      <c r="AH30" s="41" t="inlineStr"/>
+      <c r="AI30" s="41" t="inlineStr"/>
     </row>
     <row r="31" ht="62" customHeight="1">
       <c r="A31" s="25" t="inlineStr">
@@ -9364,13 +9468,13 @@
           <t>A cordless robotic pool cleaner from Aiper, designed to clean both the floor and vertical walls of a pool without a cable getting in the way. It suits those who want a tidy pool without the tangle.</t>
         </is>
       </c>
-      <c r="D31" s="36" t="inlineStr"/>
-      <c r="E31" s="36" t="inlineStr">
+      <c r="D31" s="41" t="inlineStr"/>
+      <c r="E31" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F31" s="36" t="inlineStr">
+      <c r="F31" s="41" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9380,71 +9484,71 @@
           <t>robot-cleaner, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H31" s="36" t="inlineStr">
+      <c r="H31" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I31" s="36" t="inlineStr">
+      <c r="I31" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J31" s="36" t="inlineStr">
+      <c r="J31" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K31" s="36" t="inlineStr">
+      <c r="K31" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L31" s="36" t="inlineStr">
+      <c r="L31" s="41" t="inlineStr">
         <is>
           <t>GEN-ROB-5137</t>
         </is>
       </c>
-      <c r="M31" s="37" t="inlineStr">
+      <c r="M31" s="42" t="inlineStr">
         <is>
           <t>6975140315137</t>
         </is>
       </c>
-      <c r="N31" s="38" t="inlineStr"/>
-      <c r="O31" s="38" t="inlineStr"/>
-      <c r="P31" s="38" t="inlineStr"/>
-      <c r="Q31" s="36" t="inlineStr">
+      <c r="N31" s="43" t="inlineStr"/>
+      <c r="O31" s="43" t="inlineStr"/>
+      <c r="P31" s="43" t="inlineStr"/>
+      <c r="Q31" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R31" s="36" t="inlineStr">
+      <c r="R31" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S31" s="36" t="inlineStr">
+      <c r="S31" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T31" s="36" t="inlineStr">
+      <c r="T31" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U31" s="36" t="inlineStr"/>
-      <c r="V31" s="36" t="inlineStr">
+      <c r="U31" s="41" t="inlineStr"/>
+      <c r="V31" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W31" s="36" t="inlineStr">
+      <c r="W31" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X31" s="36" t="inlineStr">
+      <c r="X31" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9454,7 +9558,7 @@
           <t>https://images.barcodelookup.com/124722/1247228758-1.jpg</t>
         </is>
       </c>
-      <c r="Z31" s="36" t="inlineStr">
+      <c r="Z31" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9464,7 +9568,7 @@
           <t>Scuba L1 - EU</t>
         </is>
       </c>
-      <c r="AB31" s="36" t="inlineStr">
+      <c r="AB31" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9476,10 +9580,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF31" s="36" t="inlineStr"/>
-      <c r="AG31" s="36" t="inlineStr"/>
-      <c r="AH31" s="36" t="inlineStr"/>
-      <c r="AI31" s="36" t="inlineStr"/>
+      <c r="AF31" s="41" t="inlineStr"/>
+      <c r="AG31" s="41" t="inlineStr"/>
+      <c r="AH31" s="41" t="inlineStr"/>
+      <c r="AI31" s="41" t="inlineStr"/>
     </row>
     <row r="32" ht="90" customHeight="1">
       <c r="A32" s="25" t="inlineStr">
@@ -9497,13 +9601,13 @@
           <t>A battery powered robotic pool cleaner made from PVC, suited to above ground pools up to 12 m in size and depths of up to 3 m, with a 2 hour cleaning cycle and an 8 hour charge time. Measuring 38.5 x 35.5 x 23.9 cm and weighing 5.2 kg, it works across flat and gently sloping pool floors with all surface types.</t>
         </is>
       </c>
-      <c r="D32" s="36" t="inlineStr"/>
-      <c r="E32" s="36" t="inlineStr">
+      <c r="D32" s="41" t="inlineStr"/>
+      <c r="E32" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-16</t>
         </is>
       </c>
-      <c r="F32" s="36" t="inlineStr">
+      <c r="F32" s="41" t="inlineStr">
         <is>
           <t>Pool robot cleaner</t>
         </is>
@@ -9513,75 +9617,75 @@
           <t>robot-cleaner, considered-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H32" s="36" t="inlineStr">
+      <c r="H32" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I32" s="36" t="inlineStr">
+      <c r="I32" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J32" s="36" t="inlineStr">
+      <c r="J32" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K32" s="36" t="inlineStr">
+      <c r="K32" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L32" s="36" t="inlineStr">
+      <c r="L32" s="41" t="inlineStr">
         <is>
           <t>GEN-ROB-8500</t>
         </is>
       </c>
-      <c r="M32" s="37" t="inlineStr">
+      <c r="M32" s="42" t="inlineStr">
         <is>
           <t>8412081308500</t>
         </is>
       </c>
-      <c r="N32" s="38" t="inlineStr"/>
-      <c r="O32" s="38" t="inlineStr"/>
-      <c r="P32" s="38" t="inlineStr"/>
-      <c r="Q32" s="36" t="inlineStr">
+      <c r="N32" s="43" t="inlineStr"/>
+      <c r="O32" s="43" t="inlineStr"/>
+      <c r="P32" s="43" t="inlineStr"/>
+      <c r="Q32" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R32" s="36" t="inlineStr">
+      <c r="R32" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S32" s="36" t="inlineStr">
+      <c r="S32" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T32" s="36" t="inlineStr">
+      <c r="T32" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U32" s="36" t="inlineStr">
+      <c r="U32" s="41" t="inlineStr">
         <is>
           <t>5200</t>
         </is>
       </c>
-      <c r="V32" s="36" t="inlineStr">
+      <c r="V32" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W32" s="36" t="inlineStr">
+      <c r="W32" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X32" s="36" t="inlineStr">
+      <c r="X32" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9591,7 +9695,7 @@
           <t>https://images.barcodelookup.com/124726/1247268298-1.jpg</t>
         </is>
       </c>
-      <c r="Z32" s="36" t="inlineStr">
+      <c r="Z32" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9601,7 +9705,7 @@
           <t>Battery Powered Robot WET RUNNER XPERT</t>
         </is>
       </c>
-      <c r="AB32" s="36" t="inlineStr">
+      <c r="AB32" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9613,18 +9717,18 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF32" s="36" t="inlineStr"/>
-      <c r="AG32" s="36" t="inlineStr">
+      <c r="AF32" s="41" t="inlineStr"/>
+      <c r="AG32" s="41" t="inlineStr">
         <is>
           <t>23.9cm</t>
         </is>
       </c>
-      <c r="AH32" s="36" t="inlineStr">
+      <c r="AH32" s="41" t="inlineStr">
         <is>
           <t>35.5cm</t>
         </is>
       </c>
-      <c r="AI32" s="36" t="inlineStr">
+      <c r="AI32" s="41" t="inlineStr">
         <is>
           <t>38.5cm</t>
         </is>
@@ -9646,13 +9750,13 @@
           <t>A twin-size inflatable airbed measuring 99 x 191 x 25 cm, built with Fiber-Tech internal construction using polyester fibres for comfort, vinyl sides and base, and a water-resistant flocked top surface with an anti-deflation valve. It supports a maximum weight of 136 kg and packs down compactly when deflated.</t>
         </is>
       </c>
-      <c r="D33" s="36" t="inlineStr"/>
-      <c r="E33" s="36" t="inlineStr">
+      <c r="D33" s="41" t="inlineStr"/>
+      <c r="E33" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-11</t>
         </is>
       </c>
-      <c r="F33" s="36" t="inlineStr">
+      <c r="F33" s="41" t="inlineStr">
         <is>
           <t>Airbed / lounger</t>
         </is>
@@ -9662,71 +9766,71 @@
           <t>considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H33" s="36" t="inlineStr">
+      <c r="H33" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I33" s="36" t="inlineStr">
+      <c r="I33" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J33" s="36" t="inlineStr">
+      <c r="J33" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K33" s="36" t="inlineStr">
+      <c r="K33" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L33" s="36" t="inlineStr">
+      <c r="L33" s="41" t="inlineStr">
         <is>
           <t>GEN-BED-2443</t>
         </is>
       </c>
-      <c r="M33" s="37" t="inlineStr">
+      <c r="M33" s="42" t="inlineStr">
         <is>
           <t>6941057412443</t>
         </is>
       </c>
-      <c r="N33" s="38" t="inlineStr"/>
-      <c r="O33" s="38" t="inlineStr"/>
-      <c r="P33" s="38" t="inlineStr"/>
-      <c r="Q33" s="36" t="inlineStr">
+      <c r="N33" s="43" t="inlineStr"/>
+      <c r="O33" s="43" t="inlineStr"/>
+      <c r="P33" s="43" t="inlineStr"/>
+      <c r="Q33" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R33" s="36" t="inlineStr">
+      <c r="R33" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S33" s="36" t="inlineStr">
+      <c r="S33" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T33" s="36" t="inlineStr">
+      <c r="T33" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U33" s="36" t="inlineStr"/>
-      <c r="V33" s="36" t="inlineStr">
+      <c r="U33" s="41" t="inlineStr"/>
+      <c r="V33" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W33" s="36" t="inlineStr">
+      <c r="W33" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X33" s="36" t="inlineStr">
+      <c r="X33" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9736,7 +9840,7 @@
           <t>https://www.ecoperation.com/media/catalog/product/cache/b76cf1d99a7811daa83ba86e6ad91c89/6/4/64757.jpg</t>
         </is>
       </c>
-      <c r="Z33" s="36" t="inlineStr">
+      <c r="Z33" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9746,7 +9850,7 @@
           <t>Twin Dura-Beam Classic Downy Airbed 99x191x25 cm</t>
         </is>
       </c>
-      <c r="AB33" s="36" t="inlineStr">
+      <c r="AB33" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9758,18 +9862,18 @@
           <t>Inflatable Beds and Mattresses</t>
         </is>
       </c>
-      <c r="AF33" s="36" t="inlineStr"/>
-      <c r="AG33" s="36" t="inlineStr">
+      <c r="AF33" s="41" t="inlineStr"/>
+      <c r="AG33" s="41" t="inlineStr">
         <is>
           <t>99.0cm</t>
         </is>
       </c>
-      <c r="AH33" s="36" t="inlineStr">
+      <c r="AH33" s="41" t="inlineStr">
         <is>
           <t>191.0cm</t>
         </is>
       </c>
-      <c r="AI33" s="36" t="inlineStr">
+      <c r="AI33" s="41" t="inlineStr">
         <is>
           <t>25.0cm</t>
         </is>
@@ -9791,17 +9895,17 @@
           <t>A plastic chlorine dosing lock from Steinbach, designed exclusively for use with long-term chlorine tablets, with a 1.5-inch connection fitting. It measures 37 cm in length, 22.5 cm in width, and 15 cm in height, making it a sturdy inline dosing unit for pool water treatment systems.</t>
         </is>
       </c>
-      <c r="D34" s="36" t="inlineStr">
+      <c r="D34" s="41" t="inlineStr">
         <is>
           <t>Steinbach</t>
         </is>
       </c>
-      <c r="E34" s="36" t="inlineStr">
+      <c r="E34" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F34" s="36" t="inlineStr">
+      <c r="F34" s="41" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -9811,71 +9915,71 @@
           <t>water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H34" s="36" t="inlineStr">
+      <c r="H34" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I34" s="36" t="inlineStr">
+      <c r="I34" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J34" s="36" t="inlineStr">
+      <c r="J34" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K34" s="36" t="inlineStr">
+      <c r="K34" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L34" s="36" t="inlineStr">
+      <c r="L34" s="41" t="inlineStr">
         <is>
           <t>STE-CHM-0307</t>
         </is>
       </c>
-      <c r="M34" s="37" t="inlineStr">
+      <c r="M34" s="42" t="inlineStr">
         <is>
           <t>9008748790307</t>
         </is>
       </c>
-      <c r="N34" s="38" t="inlineStr"/>
-      <c r="O34" s="38" t="inlineStr"/>
-      <c r="P34" s="38" t="inlineStr"/>
-      <c r="Q34" s="36" t="inlineStr">
+      <c r="N34" s="43" t="inlineStr"/>
+      <c r="O34" s="43" t="inlineStr"/>
+      <c r="P34" s="43" t="inlineStr"/>
+      <c r="Q34" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R34" s="36" t="inlineStr">
+      <c r="R34" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S34" s="36" t="inlineStr">
+      <c r="S34" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T34" s="36" t="inlineStr">
+      <c r="T34" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U34" s="36" t="inlineStr"/>
-      <c r="V34" s="36" t="inlineStr">
+      <c r="U34" s="41" t="inlineStr"/>
+      <c r="V34" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W34" s="36" t="inlineStr">
+      <c r="W34" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X34" s="36" t="inlineStr">
+      <c r="X34" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -9885,7 +9989,7 @@
           <t>https://i.ebayimg.com/images/g/CrUAAeSwkOdqeaRR/s-l400.jpg</t>
         </is>
       </c>
-      <c r="Z34" s="36" t="inlineStr">
+      <c r="Z34" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9895,7 +9999,7 @@
           <t>STEINBACH Chlorine dosing lock, only for chlorine long-term tablets, plastic, connection 1.5 inch in</t>
         </is>
       </c>
-      <c r="AB34" s="36" t="inlineStr">
+      <c r="AB34" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -9907,18 +10011,18 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF34" s="36" t="inlineStr"/>
-      <c r="AG34" s="36" t="inlineStr">
+      <c r="AF34" s="41" t="inlineStr"/>
+      <c r="AG34" s="41" t="inlineStr">
         <is>
           <t>22.5cm</t>
         </is>
       </c>
-      <c r="AH34" s="36" t="inlineStr">
+      <c r="AH34" s="41" t="inlineStr">
         <is>
           <t>37.0cm</t>
         </is>
       </c>
-      <c r="AI34" s="36" t="inlineStr">
+      <c r="AI34" s="41" t="inlineStr">
         <is>
           <t>15.0cm</t>
         </is>
@@ -9940,17 +10044,17 @@
           <t>A filter cleaning system designed for hot tub and pool cartridge filters, with a water saving design that makes keeping filters in good condition straightforward. A practical addition to any spa maintenance routine.</t>
         </is>
       </c>
-      <c r="D35" s="36" t="inlineStr">
+      <c r="D35" s="41" t="inlineStr">
         <is>
           <t>Estelle</t>
         </is>
       </c>
-      <c r="E35" s="36" t="inlineStr">
+      <c r="E35" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F35" s="36" t="inlineStr">
+      <c r="F35" s="41" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -9960,71 +10064,71 @@
           <t>filters, spa-hot-tub, cleaning, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H35" s="36" t="inlineStr">
+      <c r="H35" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I35" s="36" t="inlineStr">
+      <c r="I35" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J35" s="36" t="inlineStr">
+      <c r="J35" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K35" s="36" t="inlineStr">
+      <c r="K35" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L35" s="36" t="inlineStr">
+      <c r="L35" s="41" t="inlineStr">
         <is>
           <t>EST-FIL-3669</t>
         </is>
       </c>
-      <c r="M35" s="37" t="inlineStr">
+      <c r="M35" s="42" t="inlineStr">
         <is>
           <t>8711842033669</t>
         </is>
       </c>
-      <c r="N35" s="38" t="inlineStr"/>
-      <c r="O35" s="38" t="inlineStr"/>
-      <c r="P35" s="38" t="inlineStr"/>
-      <c r="Q35" s="36" t="inlineStr">
+      <c r="N35" s="43" t="inlineStr"/>
+      <c r="O35" s="43" t="inlineStr"/>
+      <c r="P35" s="43" t="inlineStr"/>
+      <c r="Q35" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R35" s="36" t="inlineStr">
+      <c r="R35" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S35" s="36" t="inlineStr">
+      <c r="S35" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T35" s="36" t="inlineStr">
+      <c r="T35" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U35" s="36" t="inlineStr"/>
-      <c r="V35" s="36" t="inlineStr">
+      <c r="U35" s="41" t="inlineStr"/>
+      <c r="V35" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W35" s="36" t="inlineStr">
+      <c r="W35" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X35" s="36" t="inlineStr">
+      <c r="X35" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10034,7 +10138,7 @@
           <t>https://i.ebayimg.com/images/g/0e0AAOSweaplqO77/s-l400.jpg</t>
         </is>
       </c>
-      <c r="Z35" s="36" t="inlineStr">
+      <c r="Z35" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10044,7 +10148,7 @@
           <t>Estelle Filter Cleaning System Hot tubs Cartridge Filters Cleaner Spa Amazing!</t>
         </is>
       </c>
-      <c r="AB35" s="36" t="inlineStr">
+      <c r="AB35" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10056,10 +10160,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF35" s="36" t="inlineStr"/>
-      <c r="AG35" s="36" t="inlineStr"/>
-      <c r="AH35" s="36" t="inlineStr"/>
-      <c r="AI35" s="36" t="inlineStr"/>
+      <c r="AF35" s="41" t="inlineStr"/>
+      <c r="AG35" s="41" t="inlineStr"/>
+      <c r="AH35" s="41" t="inlineStr"/>
+      <c r="AI35" s="41" t="inlineStr"/>
     </row>
     <row r="36" ht="62" customHeight="1">
       <c r="A36" s="25" t="inlineStr">
@@ -10077,17 +10181,17 @@
           <t>A compact handy scrub brush for pool maintenance, measuring 15 x 9 x 8 cm, suited to scrubbing pool surfaces and hard-to-reach areas. Small enough to manoeuvre easily, and ready to tackle whatever the waterline throws at it.</t>
         </is>
       </c>
-      <c r="D36" s="36" t="inlineStr">
+      <c r="D36" s="41" t="inlineStr">
         <is>
           <t>WAYS</t>
         </is>
       </c>
-      <c r="E36" s="36" t="inlineStr">
+      <c r="E36" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F36" s="36" t="inlineStr">
+      <c r="F36" s="41" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -10097,79 +10201,79 @@
           <t>pool, cleaning, add-on, needs-photo, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H36" s="36" t="inlineStr">
+      <c r="H36" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I36" s="36" t="inlineStr">
+      <c r="I36" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J36" s="36" t="inlineStr">
+      <c r="J36" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K36" s="36" t="inlineStr">
+      <c r="K36" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L36" s="36" t="inlineStr">
+      <c r="L36" s="41" t="inlineStr">
         <is>
           <t>WAY-CLN-2219</t>
         </is>
       </c>
-      <c r="M36" s="37" t="inlineStr">
+      <c r="M36" s="42" t="inlineStr">
         <is>
           <t>8720299182219</t>
         </is>
       </c>
-      <c r="N36" s="38" t="inlineStr"/>
-      <c r="O36" s="38" t="inlineStr"/>
-      <c r="P36" s="38" t="inlineStr"/>
-      <c r="Q36" s="36" t="inlineStr">
+      <c r="N36" s="43" t="inlineStr"/>
+      <c r="O36" s="43" t="inlineStr"/>
+      <c r="P36" s="43" t="inlineStr"/>
+      <c r="Q36" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R36" s="36" t="inlineStr">
+      <c r="R36" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S36" s="36" t="inlineStr">
+      <c r="S36" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T36" s="36" t="inlineStr">
+      <c r="T36" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U36" s="36" t="inlineStr"/>
-      <c r="V36" s="36" t="inlineStr">
+      <c r="U36" s="41" t="inlineStr"/>
+      <c r="V36" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W36" s="36" t="inlineStr">
+      <c r="W36" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X36" s="36" t="inlineStr">
+      <c r="X36" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
       <c r="Y36" s="25" t="inlineStr"/>
-      <c r="Z36" s="36" t="inlineStr"/>
+      <c r="Z36" s="41" t="inlineStr"/>
       <c r="AA36" s="25" t="inlineStr"/>
-      <c r="AB36" s="36" t="inlineStr">
+      <c r="AB36" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10181,18 +10285,18 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF36" s="36" t="inlineStr"/>
-      <c r="AG36" s="36" t="inlineStr">
+      <c r="AF36" s="41" t="inlineStr"/>
+      <c r="AG36" s="41" t="inlineStr">
         <is>
           <t>8.0cm</t>
         </is>
       </c>
-      <c r="AH36" s="36" t="inlineStr">
+      <c r="AH36" s="41" t="inlineStr">
         <is>
           <t>15.0cm</t>
         </is>
       </c>
-      <c r="AI36" s="36" t="inlineStr">
+      <c r="AI36" s="41" t="inlineStr">
         <is>
           <t>9.0cm</t>
         </is>
@@ -10214,17 +10318,17 @@
           <t>An inflatable PVC headrest pillow for the Intex inflatable spa (model 28506), measuring 24 x 19 x 6 cm and weighing 0.22 kg, designed to support the head and neck comfortably during use. It attaches to the spa rim and can also be filled with water for added stability.</t>
         </is>
       </c>
-      <c r="D37" s="36" t="inlineStr">
+      <c r="D37" s="41" t="inlineStr">
         <is>
           <t>Intex</t>
         </is>
       </c>
-      <c r="E37" s="36" t="inlineStr">
+      <c r="E37" s="41" t="inlineStr">
         <is>
           <t>hg-18-4</t>
         </is>
       </c>
-      <c r="F37" s="36" t="inlineStr">
+      <c r="F37" s="41" t="inlineStr">
         <is>
           <t>Inflatable spa</t>
         </is>
@@ -10234,75 +10338,75 @@
           <t>spa-hot-tub, accessories, considered-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H37" s="36" t="inlineStr">
+      <c r="H37" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I37" s="36" t="inlineStr">
+      <c r="I37" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J37" s="36" t="inlineStr">
+      <c r="J37" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K37" s="36" t="inlineStr">
+      <c r="K37" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L37" s="36" t="inlineStr">
+      <c r="L37" s="41" t="inlineStr">
         <is>
           <t>INT-SPA-6075</t>
         </is>
       </c>
-      <c r="M37" s="37" t="inlineStr">
+      <c r="M37" s="42" t="inlineStr">
         <is>
           <t>6941057426075</t>
         </is>
       </c>
-      <c r="N37" s="38" t="inlineStr"/>
-      <c r="O37" s="38" t="inlineStr"/>
-      <c r="P37" s="38" t="inlineStr"/>
-      <c r="Q37" s="36" t="inlineStr">
+      <c r="N37" s="43" t="inlineStr"/>
+      <c r="O37" s="43" t="inlineStr"/>
+      <c r="P37" s="43" t="inlineStr"/>
+      <c r="Q37" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R37" s="36" t="inlineStr">
+      <c r="R37" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S37" s="36" t="inlineStr">
+      <c r="S37" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T37" s="36" t="inlineStr">
+      <c r="T37" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U37" s="36" t="inlineStr">
+      <c r="U37" s="41" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="V37" s="36" t="inlineStr">
+      <c r="V37" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W37" s="36" t="inlineStr">
+      <c r="W37" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X37" s="36" t="inlineStr">
+      <c r="X37" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10312,7 +10416,7 @@
           <t>https://content2.rozetka.com.ua/goods/images/big/570260745.jpg</t>
         </is>
       </c>
-      <c r="Z37" s="36" t="inlineStr">
+      <c r="Z37" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10322,7 +10426,7 @@
           <t>Pillow for inflatable SPA INTEX 28506</t>
         </is>
       </c>
-      <c r="AB37" s="36" t="inlineStr">
+      <c r="AB37" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10334,18 +10438,18 @@
           <t>Intex Pure Spa Accessories</t>
         </is>
       </c>
-      <c r="AF37" s="36" t="inlineStr"/>
-      <c r="AG37" s="36" t="inlineStr">
+      <c r="AF37" s="41" t="inlineStr"/>
+      <c r="AG37" s="41" t="inlineStr">
         <is>
           <t>19.0cm</t>
         </is>
       </c>
-      <c r="AH37" s="36" t="inlineStr">
+      <c r="AH37" s="41" t="inlineStr">
         <is>
           <t>24.0cm</t>
         </is>
       </c>
-      <c r="AI37" s="36" t="inlineStr">
+      <c r="AI37" s="41" t="inlineStr">
         <is>
           <t>6.0cm</t>
         </is>
@@ -10367,13 +10471,13 @@
           <t>A DPD pool test kit for active oxygen pools, containing 20 DPD No. 4 tablets and 20 phenol red tablets to measure both active oxygen levels and pH in pool water. Simply dissolve a tablet in the provided container, agitate, and read the result immediately for a quick and straightforward water check.</t>
         </is>
       </c>
-      <c r="D38" s="36" t="inlineStr"/>
-      <c r="E38" s="36" t="inlineStr">
+      <c r="D38" s="41" t="inlineStr"/>
+      <c r="E38" s="41" t="inlineStr">
         <is>
           <t>hg-18-1</t>
         </is>
       </c>
-      <c r="F38" s="36" t="inlineStr">
+      <c r="F38" s="41" t="inlineStr">
         <is>
           <t>Water test kit</t>
         </is>
@@ -10383,71 +10487,71 @@
           <t>water-treatment, test-measure, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H38" s="36" t="inlineStr">
+      <c r="H38" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I38" s="36" t="inlineStr">
+      <c r="I38" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J38" s="36" t="inlineStr">
+      <c r="J38" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K38" s="36" t="inlineStr">
+      <c r="K38" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L38" s="36" t="inlineStr">
+      <c r="L38" s="41" t="inlineStr">
         <is>
           <t>GEN-TST-1347</t>
         </is>
       </c>
-      <c r="M38" s="37" t="inlineStr">
+      <c r="M38" s="42" t="inlineStr">
         <is>
           <t>4250463121347</t>
         </is>
       </c>
-      <c r="N38" s="38" t="inlineStr"/>
-      <c r="O38" s="38" t="inlineStr"/>
-      <c r="P38" s="38" t="inlineStr"/>
-      <c r="Q38" s="36" t="inlineStr">
+      <c r="N38" s="43" t="inlineStr"/>
+      <c r="O38" s="43" t="inlineStr"/>
+      <c r="P38" s="43" t="inlineStr"/>
+      <c r="Q38" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R38" s="36" t="inlineStr">
+      <c r="R38" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S38" s="36" t="inlineStr">
+      <c r="S38" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T38" s="36" t="inlineStr">
+      <c r="T38" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U38" s="36" t="inlineStr"/>
-      <c r="V38" s="36" t="inlineStr">
+      <c r="U38" s="41" t="inlineStr"/>
+      <c r="V38" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W38" s="36" t="inlineStr">
+      <c r="W38" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X38" s="36" t="inlineStr">
+      <c r="X38" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10457,7 +10561,7 @@
           <t>https://media.carrefour.fr/medias/8f94161f683b4e589024a5b5ebaa6873/p_200x200/cad3db6a00ef414a804b9226119bae96_image.jpg</t>
         </is>
       </c>
-      <c r="Z38" s="36" t="inlineStr">
+      <c r="Z38" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10467,7 +10571,7 @@
           <t>Active oxygen test kit x1</t>
         </is>
       </c>
-      <c r="AB38" s="36" t="inlineStr">
+      <c r="AB38" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10479,10 +10583,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF38" s="36" t="inlineStr"/>
-      <c r="AG38" s="36" t="inlineStr"/>
-      <c r="AH38" s="36" t="inlineStr"/>
-      <c r="AI38" s="36" t="inlineStr"/>
+      <c r="AF38" s="41" t="inlineStr"/>
+      <c r="AG38" s="41" t="inlineStr"/>
+      <c r="AH38" s="41" t="inlineStr"/>
+      <c r="AI38" s="41" t="inlineStr"/>
     </row>
     <row r="39" ht="62" customHeight="1">
       <c r="A39" s="25" t="inlineStr">
@@ -10500,17 +10604,17 @@
           <t>A pack of two Darlly replacement filter cartridges compatible with Intex type H filtration systems, making it easy to keep a pool or spa running cleanly. A straightforward swap when your current cartridge has done its time.</t>
         </is>
       </c>
-      <c r="D39" s="36" t="inlineStr">
+      <c r="D39" s="41" t="inlineStr">
         <is>
           <t>Intex</t>
         </is>
       </c>
-      <c r="E39" s="36" t="inlineStr">
+      <c r="E39" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F39" s="36" t="inlineStr">
+      <c r="F39" s="41" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -10520,71 +10624,71 @@
           <t>filters, repeat-purchase, barcode-verified, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H39" s="36" t="inlineStr">
+      <c r="H39" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I39" s="36" t="inlineStr">
+      <c r="I39" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J39" s="36" t="inlineStr">
+      <c r="J39" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K39" s="36" t="inlineStr">
+      <c r="K39" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L39" s="36" t="inlineStr">
+      <c r="L39" s="41" t="inlineStr">
         <is>
           <t>INT-FIL-2895</t>
         </is>
       </c>
-      <c r="M39" s="37" t="inlineStr">
+      <c r="M39" s="42" t="inlineStr">
         <is>
           <t>700175992895</t>
         </is>
       </c>
-      <c r="N39" s="38" t="inlineStr"/>
-      <c r="O39" s="38" t="inlineStr"/>
-      <c r="P39" s="38" t="inlineStr"/>
-      <c r="Q39" s="36" t="inlineStr">
+      <c r="N39" s="43" t="inlineStr"/>
+      <c r="O39" s="43" t="inlineStr"/>
+      <c r="P39" s="43" t="inlineStr"/>
+      <c r="Q39" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R39" s="36" t="inlineStr">
+      <c r="R39" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S39" s="36" t="inlineStr">
+      <c r="S39" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T39" s="36" t="inlineStr">
+      <c r="T39" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U39" s="36" t="inlineStr"/>
-      <c r="V39" s="36" t="inlineStr">
+      <c r="U39" s="41" t="inlineStr"/>
+      <c r="V39" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W39" s="36" t="inlineStr">
+      <c r="W39" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X39" s="36" t="inlineStr">
+      <c r="X39" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10594,7 +10698,7 @@
           <t>https://a.allegroimg.com/original/11923c/a79785a04d36aa54f0d87384f038/Filtracni-kartuse-Intex-D-3BTZ0023-SC828</t>
         </is>
       </c>
-      <c r="Z39" s="36" t="inlineStr">
+      <c r="Z39" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10604,7 +10708,7 @@
           <t>Darlly filter cartridge pack of 2 filter cartridges compatible with Intex type H</t>
         </is>
       </c>
-      <c r="AB39" s="36" t="inlineStr">
+      <c r="AB39" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10616,10 +10720,10 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF39" s="36" t="inlineStr"/>
-      <c r="AG39" s="36" t="inlineStr"/>
-      <c r="AH39" s="36" t="inlineStr"/>
-      <c r="AI39" s="36" t="inlineStr"/>
+      <c r="AF39" s="41" t="inlineStr"/>
+      <c r="AG39" s="41" t="inlineStr"/>
+      <c r="AH39" s="41" t="inlineStr"/>
+      <c r="AI39" s="41" t="inlineStr"/>
     </row>
     <row r="40" ht="62" customHeight="1">
       <c r="A40" s="25" t="inlineStr">
@@ -10637,17 +10741,17 @@
           <t>A Darlly replacement spa filter cartridge with dimensions of 22 cm diameter by 27 cm height, compatible with SC713 and C-8465 references. A reliable like-for-like swap to keep your spa filtration running smoothly.</t>
         </is>
       </c>
-      <c r="D40" s="36" t="inlineStr">
+      <c r="D40" s="41" t="inlineStr">
         <is>
           <t>Darlly</t>
         </is>
       </c>
-      <c r="E40" s="36" t="inlineStr">
+      <c r="E40" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-3-1</t>
         </is>
       </c>
-      <c r="F40" s="36" t="inlineStr">
+      <c r="F40" s="41" t="inlineStr">
         <is>
           <t>Filter cartridge</t>
         </is>
@@ -10657,71 +10761,71 @@
           <t>filters, spa-hot-tub, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H40" s="36" t="inlineStr">
+      <c r="H40" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I40" s="36" t="inlineStr">
+      <c r="I40" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J40" s="36" t="inlineStr">
+      <c r="J40" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K40" s="36" t="inlineStr">
+      <c r="K40" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L40" s="36" t="inlineStr">
+      <c r="L40" s="41" t="inlineStr">
         <is>
           <t>DAR-FIL-1744</t>
         </is>
       </c>
-      <c r="M40" s="37" t="inlineStr">
+      <c r="M40" s="42" t="inlineStr">
         <is>
           <t>700175991744</t>
         </is>
       </c>
-      <c r="N40" s="38" t="inlineStr"/>
-      <c r="O40" s="38" t="inlineStr"/>
-      <c r="P40" s="38" t="inlineStr"/>
-      <c r="Q40" s="36" t="inlineStr">
+      <c r="N40" s="43" t="inlineStr"/>
+      <c r="O40" s="43" t="inlineStr"/>
+      <c r="P40" s="43" t="inlineStr"/>
+      <c r="Q40" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R40" s="36" t="inlineStr">
+      <c r="R40" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S40" s="36" t="inlineStr">
+      <c r="S40" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T40" s="36" t="inlineStr">
+      <c r="T40" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U40" s="36" t="inlineStr"/>
-      <c r="V40" s="36" t="inlineStr">
+      <c r="U40" s="41" t="inlineStr"/>
+      <c r="V40" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W40" s="36" t="inlineStr">
+      <c r="W40" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X40" s="36" t="inlineStr">
+      <c r="X40" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10731,7 +10835,7 @@
           <t>https://images.barcodelookup.com/142259/1422591231-1.jpg</t>
         </is>
       </c>
-      <c r="Z40" s="36" t="inlineStr">
+      <c r="Z40" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10741,7 +10845,7 @@
           <t>Spa replacement filter Ø 22 cm x 27 cm SC713, C-8465 - Darlly</t>
         </is>
       </c>
-      <c r="AB40" s="36" t="inlineStr">
+      <c r="AB40" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10753,14 +10857,14 @@
           <t>Filter cartridges and filter media for water pumps</t>
         </is>
       </c>
-      <c r="AF40" s="36" t="inlineStr"/>
-      <c r="AG40" s="36" t="inlineStr"/>
-      <c r="AH40" s="36" t="inlineStr">
+      <c r="AF40" s="41" t="inlineStr"/>
+      <c r="AG40" s="41" t="inlineStr"/>
+      <c r="AH40" s="41" t="inlineStr">
         <is>
           <t>22.0cm</t>
         </is>
       </c>
-      <c r="AI40" s="36" t="inlineStr">
+      <c r="AI40" s="41" t="inlineStr">
         <is>
           <t>27.0cm</t>
         </is>
@@ -10782,17 +10886,17 @@
           <t>A 1 kg pack of 20g multitabs for swimming pools, offering a 5-in-1 treatment that combines multiple water care functions in a single slow-dissolving tablet. Convenient all-in-one dosing that keeps pool maintenance simple.</t>
         </is>
       </c>
-      <c r="D41" s="36" t="inlineStr">
+      <c r="D41" s="41" t="inlineStr">
         <is>
           <t>Höfer Chemie</t>
         </is>
       </c>
-      <c r="E41" s="36" t="inlineStr">
+      <c r="E41" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F41" s="36" t="inlineStr">
+      <c r="F41" s="41" t="inlineStr">
         <is>
           <t>Pool chemical</t>
         </is>
@@ -10802,75 +10906,75 @@
           <t>pool, water-treatment, repeat-purchase, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H41" s="36" t="inlineStr">
+      <c r="H41" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I41" s="36" t="inlineStr">
+      <c r="I41" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J41" s="36" t="inlineStr">
+      <c r="J41" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K41" s="36" t="inlineStr">
+      <c r="K41" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L41" s="36" t="inlineStr">
+      <c r="L41" s="41" t="inlineStr">
         <is>
           <t>HFE-CHM-8430</t>
         </is>
       </c>
-      <c r="M41" s="37" t="inlineStr">
+      <c r="M41" s="42" t="inlineStr">
         <is>
           <t>4250463108430</t>
         </is>
       </c>
-      <c r="N41" s="38" t="inlineStr"/>
-      <c r="O41" s="38" t="inlineStr"/>
-      <c r="P41" s="38" t="inlineStr"/>
-      <c r="Q41" s="36" t="inlineStr">
+      <c r="N41" s="43" t="inlineStr"/>
+      <c r="O41" s="43" t="inlineStr"/>
+      <c r="P41" s="43" t="inlineStr"/>
+      <c r="Q41" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R41" s="36" t="inlineStr">
+      <c r="R41" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S41" s="36" t="inlineStr">
+      <c r="S41" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T41" s="36" t="inlineStr">
+      <c r="T41" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U41" s="36" t="inlineStr">
+      <c r="U41" s="41" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="V41" s="36" t="inlineStr">
+      <c r="V41" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W41" s="36" t="inlineStr">
+      <c r="W41" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X41" s="36" t="inlineStr">
+      <c r="X41" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -10880,7 +10984,7 @@
           <t>https://images.barcodelookup.com/17422/174228560-1.jpg</t>
         </is>
       </c>
-      <c r="Z41" s="36" t="inlineStr">
+      <c r="Z41" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10890,7 +10994,7 @@
           <t>1 x 1 kg BAYZID® multitabs 20g 5in1 for pools - HöFER CHEMIE</t>
         </is>
       </c>
-      <c r="AB41" s="36" t="inlineStr">
+      <c r="AB41" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -10902,10 +11006,10 @@
           <t>Water Chemicals and Chlorine</t>
         </is>
       </c>
-      <c r="AF41" s="36" t="inlineStr"/>
-      <c r="AG41" s="36" t="inlineStr"/>
-      <c r="AH41" s="36" t="inlineStr"/>
-      <c r="AI41" s="36" t="inlineStr"/>
+      <c r="AF41" s="41" t="inlineStr"/>
+      <c r="AG41" s="41" t="inlineStr"/>
+      <c r="AH41" s="41" t="inlineStr"/>
+      <c r="AI41" s="41" t="inlineStr"/>
     </row>
     <row r="42" ht="76" customHeight="1">
       <c r="A42" s="25" t="inlineStr">
@@ -10923,17 +11027,17 @@
           <t>A ready-to-use alkaline spray cleaner for removing grease and dirt marks at the waterline of pools and for cleaning skimmers. The spray bottle makes application straightforward, and it can be used on a filled pool on all alkali-resistant surfaces.</t>
         </is>
       </c>
-      <c r="D42" s="36" t="inlineStr">
+      <c r="D42" s="41" t="inlineStr">
         <is>
           <t>Bayrol</t>
         </is>
       </c>
-      <c r="E42" s="36" t="inlineStr">
+      <c r="E42" s="41" t="inlineStr">
         <is>
           <t>hg-18-1-7</t>
         </is>
       </c>
-      <c r="F42" s="36" t="inlineStr">
+      <c r="F42" s="41" t="inlineStr">
         <is>
           <t>Pool cleaning product</t>
         </is>
@@ -10943,75 +11047,75 @@
           <t>cleaning, add-on, barcode-verified, multi-source-confirmed, needs-review, scanned-stock</t>
         </is>
       </c>
-      <c r="H42" s="36" t="inlineStr">
+      <c r="H42" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I42" s="36" t="inlineStr">
+      <c r="I42" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="J42" s="36" t="inlineStr">
+      <c r="J42" s="41" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="K42" s="36" t="inlineStr">
+      <c r="K42" s="41" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="L42" s="36" t="inlineStr">
+      <c r="L42" s="41" t="inlineStr">
         <is>
           <t>BAY-CLN-4134</t>
         </is>
       </c>
-      <c r="M42" s="37" t="inlineStr">
+      <c r="M42" s="42" t="inlineStr">
         <is>
           <t>4008367154134</t>
         </is>
       </c>
-      <c r="N42" s="38" t="inlineStr"/>
-      <c r="O42" s="38" t="inlineStr"/>
-      <c r="P42" s="38" t="inlineStr"/>
-      <c r="Q42" s="36" t="inlineStr">
+      <c r="N42" s="43" t="inlineStr"/>
+      <c r="O42" s="43" t="inlineStr"/>
+      <c r="P42" s="43" t="inlineStr"/>
+      <c r="Q42" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="R42" s="36" t="inlineStr">
+      <c r="R42" s="41" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="S42" s="36" t="inlineStr">
+      <c r="S42" s="41" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="T42" s="36" t="inlineStr">
+      <c r="T42" s="41" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="U42" s="36" t="inlineStr">
+      <c r="U42" s="41" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="V42" s="36" t="inlineStr">
+      <c r="V42" s="41" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="W42" s="36" t="inlineStr">
+      <c r="W42" s="41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="X42" s="36" t="inlineStr">
+      <c r="X42" s="41" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -11021,7 +11125,7 @@
           <t>https://www.north-spa.de/wp-content/uploads/2023/02/Produktbild-1-Bayrol-Randfix-07-l-4008367154134.jpg</t>
         </is>
       </c>
-      <c r="Z42" s="36" t="inlineStr">
+      <c r="Z42" s="41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -11031,7 +11135,7 @@
           <t>Bayrol Randfix 0,7 l</t>
         </is>
       </c>
-      <c r="AB42" s="36" t="inlineStr">
+      <c r="AB42" s="41" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -11043,10 +11147,10 @@
           <t>Pool Cleaning Equipment</t>
         </is>
       </c>
-      <c r="AF42" s="36" t="inlineStr"/>
-      <c r="AG42" s="36" t="inlineStr"/>
-      <c r="AH42" s="36" t="inlineStr"/>
-      <c r="AI42" s="36" t="inlineStr"/>
+      <c r="AF42" s="41" t="inlineStr"/>
+      <c r="AG42" s="41" t="inlineStr"/>
+      <c r="AH42" s="41" t="inlineStr"/>
+      <c r="AI42" s="41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projects/splashstore/docs/splashstore-scan-curation-260816.xlsx
+++ b/projects/splashstore/docs/splashstore-scan-curation-260816.xlsx
@@ -87,12 +87,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="009BC2E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E4DFEC"/>
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -113,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -170,11 +170,14 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -210,30 +213,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -337,26 +316,6 @@
 Three sources agreeing is stronger evidence than one, though both are green.</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>Colour applies to THIS FIELD ONLY, and is judged separately from the photo.
-GREEN = written from the barcode-confirmed page for this exact product.
-YELLOW = written from a name-matched page, so it may describe a variant.
-RED = no description.
-A yellow description beside a green image is normal: the photo was proven by the barcode, the wording was not.
-The cell names the page the wording came from, or says 'generic (from name)' when there was no page at all.</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>Colour applies to THIS FIELD ONLY, and is judged separately from the photo.
-GREEN = written from the barcode-confirmed page for this exact product.
-YELLOW = written from a name-matched page, so it may describe a variant.
-RED = no description.
-A yellow description beside a green image is normal: the photo was proven by the barcode, the wording was not.
-The cell names the page the wording came from, or says 'generic (from name)' when there was no page at all.</t>
-      </text>
-    </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>Colour applies to THIS FIELD ONLY, and is judged separately from the photo.
@@ -365,24 +324,6 @@
 RED = no description.
 A yellow description beside a green image is normal: the photo was proven by the barcode, the wording was not.
 The cell names the page the wording came from, or says 'generic (from name)' when there was no page at all.</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>Colour applies to THIS FIELD ONLY.
-GREEN = the barcode was found literally on the page the photo came from.
-YELLOW = the right product, but the photo needs a look (crop, multipack, unclear).
-RED = no usable photo was found.
-The cell names the site the photo came from. Compare it with Description Source: a different site there means the two fields were proven separately.</t>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
-      <text>
-        <t>Colour applies to THIS FIELD ONLY.
-GREEN = the barcode was found literally on the page the photo came from.
-YELLOW = the right product, but the photo needs a look (crop, multipack, unclear).
-RED = no usable photo was found.
-The cell names the site the photo came from. Compare it with Description Source: a different site there means the two fields were proven separately.</t>
       </text>
     </comment>
     <comment ref="P1" authorId="0" shapeId="0">
@@ -403,28 +344,6 @@
 RED = missing on an edible product.</t>
       </text>
     </comment>
-    <comment ref="L5" authorId="0" shapeId="0">
-      <text>
-        <t>No source anywhere confirmed this barcode, so the product has no name — and with no name there is nothing to search an image with.
-Identify it by hand: check the packaging, or search the code on the brand's own site.
-Avenues tried (4):
-- db: 5061066600127 -&gt; miss
-- barcode-image: 5061066600127 -&gt; 6 candidates
-- ean-web: 5061066600127 -&gt; 7 pages found
-- ebay: 5061066600127 -&gt; 0 listing(s)</t>
-      </text>
-    </comment>
-    <comment ref="N5" authorId="0" shapeId="0">
-      <text>
-        <t>No source anywhere confirmed this barcode, so the product has no name — and with no name there is nothing to search an image with.
-Identify it by hand: check the packaging, or search the code on the brand's own site.
-Avenues tried (4):
-- db: 5061066600127 -&gt; miss
-- barcode-image: 5061066600127 -&gt; 6 candidates
-- ean-web: 5061066600127 -&gt; 7 pages found
-- ebay: 5061066600127 -&gt; 0 listing(s)</t>
-      </text>
-    </comment>
     <comment ref="P5" authorId="0" shapeId="0">
       <text>
         <t>No source anywhere confirmed this barcode, so the product has no name — and with no name there is nothing to search an image with.
@@ -434,28 +353,6 @@
 - barcode-image: 5061066600127 -&gt; 6 candidates
 - ean-web: 5061066600127 -&gt; 7 pages found
 - ebay: 5061066600127 -&gt; 0 listing(s)</t>
-      </text>
-    </comment>
-    <comment ref="L16" authorId="0" shapeId="0">
-      <text>
-        <t>No source anywhere confirmed this barcode, so the product has no name — and with no name there is nothing to search an image with.
-Identify it by hand: check the packaging, or search the code on the brand's own site.
-Avenues tried (4):
-- db: 5292638000759 -&gt; miss
-- barcode-image: 5292638000759 -&gt; 6 candidates
-- ean-web: 5292638000759 -&gt; 7 pages found
-- ebay: 5292638000759 -&gt; 0 listing(s)</t>
-      </text>
-    </comment>
-    <comment ref="N16" authorId="0" shapeId="0">
-      <text>
-        <t>No source anywhere confirmed this barcode, so the product has no name — and with no name there is nothing to search an image with.
-Identify it by hand: check the packaging, or search the code on the brand's own site.
-Avenues tried (4):
-- db: 5292638000759 -&gt; miss
-- barcode-image: 5292638000759 -&gt; 6 candidates
-- ean-web: 5292638000759 -&gt; 7 pages found
-- ebay: 5292638000759 -&gt; 0 listing(s)</t>
       </text>
     </comment>
     <comment ref="P16" authorId="0" shapeId="0">
@@ -469,45 +366,9 @@
 - ebay: 5292638000759 -&gt; 0 listing(s)</t>
       </text>
     </comment>
-    <comment ref="L17" authorId="0" shapeId="0">
-      <text>
-        <t>The image AI judged this photo to be the SAME product line in a DIFFERENT pack size or count than this barcode's. Adopted as yellow by policy: a recognisable variant photo beats an empty cell, but verify the size before it goes live.</t>
-      </text>
-    </comment>
-    <comment ref="N17" authorId="0" shapeId="0">
-      <text>
-        <t>The image AI judged this photo to be the SAME product line in a DIFFERENT pack size or count than this barcode's. Adopted as yellow by policy: a recognisable variant photo beats an empty cell, but verify the size before it goes live.</t>
-      </text>
-    </comment>
     <comment ref="P17" authorId="0" shapeId="0">
       <text>
         <t>The image AI judged this photo to be the SAME product line in a DIFFERENT pack size or count than this barcode's. Adopted as yellow by policy: a recognisable variant photo beats an empty cell, but verify the size before it goes live.</t>
-      </text>
-    </comment>
-    <comment ref="L29" authorId="0" shapeId="0">
-      <text>
-        <t>A photo WAS found and checked against this product's confirmed name.
-The image AI judged it a different product, so it was not used:
-0.97: The image shows a 3D animated purple dinosaur/dragon cartoon character
-This one wants photographing in the garage, not more searching.
-Avenues tried (4):
-- db: 4250463127004 -&gt; miss
-- barcode-image: 4250463127004 -&gt; 6 candidates
-- ean-web: 4250463127004 -&gt; 7 pages found
-- name-ladder:full: Deutschland Card -&gt; 6 candidates</t>
-      </text>
-    </comment>
-    <comment ref="N29" authorId="0" shapeId="0">
-      <text>
-        <t>A photo WAS found and checked against this product's confirmed name.
-The image AI judged it a different product, so it was not used:
-0.97: The image shows a 3D animated purple dinosaur/dragon cartoon character
-This one wants photographing in the garage, not more searching.
-Avenues tried (4):
-- db: 4250463127004 -&gt; miss
-- barcode-image: 4250463127004 -&gt; 6 candidates
-- ean-web: 4250463127004 -&gt; 7 pages found
-- name-ladder:full: Deutschland Card -&gt; 6 candidates</t>
       </text>
     </comment>
     <comment ref="P29" authorId="0" shapeId="0">
@@ -523,34 +384,6 @@
 - name-ladder:full: Deutschland Card -&gt; 6 candidates</t>
       </text>
     </comment>
-    <comment ref="L38" authorId="0" shapeId="0">
-      <text>
-        <t>The product IS identified from its barcode, but no usable photo was found by any source we sear